--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\Brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA74EDA6-B5F7-4838-820E-586E882C03A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB69D81-D0C5-495D-8C82-25A27A546F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,16 +585,16 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>123259719</v>
+        <v>123671258</v>
       </c>
       <c r="E2">
         <v>2002</v>
       </c>
       <c r="F2" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G2" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="I2">
         <v>42</v>
@@ -623,16 +623,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>125924735</v>
+        <v>125773042</v>
       </c>
       <c r="E3">
         <v>2002</v>
       </c>
       <c r="F3" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G3" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="I3">
         <v>42</v>
@@ -661,22 +661,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>122746799</v>
+        <v>126086564</v>
       </c>
       <c r="E4">
-        <v>1211</v>
+        <v>2002</v>
       </c>
       <c r="F4" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G4" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,22 +699,22 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>122840376</v>
+        <v>126246588</v>
       </c>
       <c r="E5">
-        <v>1211</v>
+        <v>2002</v>
       </c>
       <c r="F5" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G5" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="I5">
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,22 +737,22 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>123231763</v>
+        <v>126538025</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45322</v>
+        <v>45320</v>
       </c>
       <c r="G6" s="2">
-        <v>45317</v>
+        <v>45320</v>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -775,22 +775,22 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>123268639</v>
+        <v>126540986</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45322</v>
+        <v>45320</v>
       </c>
       <c r="G7" s="2">
-        <v>45322</v>
+        <v>45320</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -813,22 +813,22 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>123814210</v>
+        <v>126544983</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45322</v>
+        <v>45320</v>
       </c>
       <c r="G8" s="2">
-        <v>45322</v>
+        <v>45320</v>
       </c>
       <c r="I8">
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -851,16 +851,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>123825738</v>
+        <v>122946193</v>
       </c>
       <c r="E9">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G9" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -889,13 +889,13 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>123887356</v>
+        <v>123376039</v>
       </c>
       <c r="E10">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F10" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G10" s="2">
         <v>45322</v>
@@ -927,16 +927,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>123894592</v>
+        <v>123626869</v>
       </c>
       <c r="E11">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F11" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G11" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -965,13 +965,13 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>124423806</v>
+        <v>123740028</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G12" s="2">
         <v>45320</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>124565223</v>
+        <v>123836654</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G13" s="2">
-        <v>45322</v>
+        <v>45321</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>124725174</v>
+        <v>123943000</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G14" s="2">
-        <v>45322</v>
+        <v>45317</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>124898088</v>
+        <v>124460847</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G15" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,13 +1117,13 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>125103149</v>
+        <v>124516805</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G16" s="2">
         <v>45320</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>125215989</v>
+        <v>124969016</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G17" s="2">
-        <v>45320</v>
+        <v>45323</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>125726000</v>
+        <v>125320666</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
+        <v>45323</v>
+      </c>
+      <c r="G18" s="2">
         <v>45322</v>
-      </c>
-      <c r="G18" s="2">
-        <v>45320</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>125804286</v>
+        <v>125679178</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G19" s="2">
-        <v>45321</v>
+        <v>45323</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>126272291</v>
+        <v>125689312</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="G20" s="2">
-        <v>45320</v>
+        <v>45323</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,22 +1307,22 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>110074933</v>
+        <v>125954653</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>43453</v>
+        <v>45323</v>
       </c>
       <c r="G21" s="2">
-        <v>43441</v>
+        <v>45322</v>
       </c>
       <c r="I21">
         <v>42</v>
       </c>
       <c r="J21">
-        <v>8023</v>
+        <v>8001</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>123058958</v>
+        <v>126423932</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>44995</v>
+        <v>45323</v>
       </c>
       <c r="G22" s="2">
-        <v>44993</v>
+        <v>45323</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1383,22 +1383,22 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>126470005</v>
+        <v>110074933</v>
       </c>
       <c r="E23">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45313</v>
+        <v>43453</v>
       </c>
       <c r="G23" s="2">
-        <v>45313</v>
+        <v>43441</v>
       </c>
       <c r="I23">
         <v>42</v>
       </c>
       <c r="J23">
-        <v>8004</v>
+        <v>8023</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1421,22 +1421,22 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>126470875</v>
+        <v>123058958</v>
       </c>
       <c r="E24">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45313</v>
+        <v>44995</v>
       </c>
       <c r="G24" s="2">
-        <v>45313</v>
+        <v>44993</v>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1459,22 +1459,22 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>126473056</v>
+        <v>126478856</v>
       </c>
       <c r="E25">
         <v>601</v>
       </c>
       <c r="F25" s="2">
-        <v>45316</v>
+        <v>45314</v>
       </c>
       <c r="G25" s="2">
-        <v>45313</v>
+        <v>45314</v>
       </c>
       <c r="I25">
         <v>42</v>
       </c>
       <c r="J25">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1492,6 +1492,690 @@
         <v>0</v>
       </c>
       <c r="Q25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>126478886</v>
+      </c>
+      <c r="E26">
+        <v>601</v>
+      </c>
+      <c r="F26" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G26" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I26">
+        <v>42</v>
+      </c>
+      <c r="J26">
+        <v>8004</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>126478926</v>
+      </c>
+      <c r="E27">
+        <v>601</v>
+      </c>
+      <c r="F27" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G27" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I27">
+        <v>42</v>
+      </c>
+      <c r="J27">
+        <v>8004</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>126480635</v>
+      </c>
+      <c r="E28">
+        <v>601</v>
+      </c>
+      <c r="F28" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G28" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I28">
+        <v>42</v>
+      </c>
+      <c r="J28">
+        <v>8004</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>126486551</v>
+      </c>
+      <c r="E29">
+        <v>601</v>
+      </c>
+      <c r="F29" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G29" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I29">
+        <v>42</v>
+      </c>
+      <c r="J29">
+        <v>8001</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>126487044</v>
+      </c>
+      <c r="E30">
+        <v>601</v>
+      </c>
+      <c r="F30" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G30" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I30">
+        <v>42</v>
+      </c>
+      <c r="J30">
+        <v>8001</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>126487805</v>
+      </c>
+      <c r="E31">
+        <v>601</v>
+      </c>
+      <c r="F31" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G31" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I31">
+        <v>42</v>
+      </c>
+      <c r="J31">
+        <v>8001</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>126488415</v>
+      </c>
+      <c r="E32">
+        <v>601</v>
+      </c>
+      <c r="F32" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G32" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I32">
+        <v>42</v>
+      </c>
+      <c r="J32">
+        <v>8001</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>126488859</v>
+      </c>
+      <c r="E33">
+        <v>601</v>
+      </c>
+      <c r="F33" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G33" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I33">
+        <v>42</v>
+      </c>
+      <c r="J33">
+        <v>8001</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>126489133</v>
+      </c>
+      <c r="E34">
+        <v>601</v>
+      </c>
+      <c r="F34" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G34" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I34">
+        <v>42</v>
+      </c>
+      <c r="J34">
+        <v>8001</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>126489546</v>
+      </c>
+      <c r="E35">
+        <v>601</v>
+      </c>
+      <c r="F35" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G35" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I35">
+        <v>42</v>
+      </c>
+      <c r="J35">
+        <v>8001</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>126489872</v>
+      </c>
+      <c r="E36">
+        <v>601</v>
+      </c>
+      <c r="F36" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G36" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I36">
+        <v>42</v>
+      </c>
+      <c r="J36">
+        <v>8001</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>126490085</v>
+      </c>
+      <c r="E37">
+        <v>601</v>
+      </c>
+      <c r="F37" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G37" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I37">
+        <v>42</v>
+      </c>
+      <c r="J37">
+        <v>8001</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>126490481</v>
+      </c>
+      <c r="E38">
+        <v>601</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I38">
+        <v>42</v>
+      </c>
+      <c r="J38">
+        <v>8001</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>126490671</v>
+      </c>
+      <c r="E39">
+        <v>601</v>
+      </c>
+      <c r="F39" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G39" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I39">
+        <v>42</v>
+      </c>
+      <c r="J39">
+        <v>8001</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>126490881</v>
+      </c>
+      <c r="E40">
+        <v>601</v>
+      </c>
+      <c r="F40" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G40" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I40">
+        <v>42</v>
+      </c>
+      <c r="J40">
+        <v>8001</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>126491015</v>
+      </c>
+      <c r="E41">
+        <v>601</v>
+      </c>
+      <c r="F41" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G41" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I41">
+        <v>42</v>
+      </c>
+      <c r="J41">
+        <v>8001</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>126480635</v>
+      </c>
+      <c r="E42">
+        <v>601</v>
+      </c>
+      <c r="F42" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G42" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I42">
+        <v>42</v>
+      </c>
+      <c r="J42">
+        <v>8004</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>126488343</v>
+      </c>
+      <c r="E43">
+        <v>601</v>
+      </c>
+      <c r="F43" s="2">
+        <v>45314</v>
+      </c>
+      <c r="G43" s="2">
+        <v>45314</v>
+      </c>
+      <c r="I43">
+        <v>42</v>
+      </c>
+      <c r="J43">
+        <v>8004</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
         <v>61</v>
       </c>
     </row>
@@ -9085,31 +9769,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\Brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB69D81-D0C5-495D-8C82-25A27A546F08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79C86FE-1872-4F2F-BD82-D0E69D62612B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:Q143"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,16 +585,16 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>123671258</v>
+        <v>123045833</v>
       </c>
       <c r="E2">
         <v>2002</v>
       </c>
       <c r="F2" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="G2" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="I2">
         <v>42</v>
@@ -623,16 +623,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>125773042</v>
+        <v>126394973</v>
       </c>
       <c r="E3">
         <v>2002</v>
       </c>
       <c r="F3" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="G3" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="I3">
         <v>42</v>
@@ -661,22 +661,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>126086564</v>
+        <v>126557468</v>
       </c>
       <c r="E4">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45323</v>
+        <v>45321</v>
       </c>
       <c r="G4" s="2">
-        <v>45323</v>
+        <v>45321</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,22 +699,22 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>126246588</v>
+        <v>126558089</v>
       </c>
       <c r="E5">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45323</v>
+        <v>45322</v>
       </c>
       <c r="G5" s="2">
-        <v>45323</v>
+        <v>45321</v>
       </c>
       <c r="I5">
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,16 +737,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>126538025</v>
+        <v>126564931</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45320</v>
+        <v>45323</v>
       </c>
       <c r="G6" s="2">
-        <v>45320</v>
+        <v>45322</v>
       </c>
       <c r="I6">
         <v>42</v>
@@ -775,16 +775,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>126540986</v>
+        <v>126576587</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45320</v>
+        <v>45322</v>
       </c>
       <c r="G7" s="2">
-        <v>45320</v>
+        <v>45322</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -813,16 +813,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>126544983</v>
+        <v>126579037</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45320</v>
+        <v>45323</v>
       </c>
       <c r="G8" s="2">
-        <v>45320</v>
+        <v>45323</v>
       </c>
       <c r="I8">
         <v>42</v>
@@ -851,16 +851,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>122946193</v>
+        <v>123031030</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45323</v>
+        <v>45325</v>
       </c>
       <c r="G9" s="2">
-        <v>45323</v>
+        <v>45325</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -889,16 +889,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>123376039</v>
+        <v>123101850</v>
       </c>
       <c r="E10">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45323</v>
+        <v>45325</v>
       </c>
       <c r="G10" s="2">
-        <v>45322</v>
+        <v>45325</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -927,16 +927,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>123626869</v>
+        <v>123286199</v>
       </c>
       <c r="E11">
         <v>1212</v>
       </c>
       <c r="F11" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="G11" s="2">
-        <v>45323</v>
+        <v>45322</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -965,16 +965,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>123740028</v>
+        <v>123375539</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
+        <v>45325</v>
+      </c>
+      <c r="G12" s="2">
         <v>45323</v>
-      </c>
-      <c r="G12" s="2">
-        <v>45320</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>123836654</v>
+        <v>123476736</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45323</v>
+        <v>45325</v>
       </c>
       <c r="G13" s="2">
-        <v>45321</v>
+        <v>45325</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>123943000</v>
+        <v>123586015</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="G14" s="2">
-        <v>45317</v>
+        <v>45324</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>124460847</v>
+        <v>123624796</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45323</v>
+        <v>45325</v>
       </c>
       <c r="G15" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>124516805</v>
+        <v>123684004</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45323</v>
+        <v>45325</v>
       </c>
       <c r="G16" s="2">
-        <v>45320</v>
+        <v>45325</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>124969016</v>
+        <v>123832801</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="G17" s="2">
-        <v>45323</v>
+        <v>45322</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>125320666</v>
+        <v>123997195</v>
       </c>
       <c r="E18">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F18" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="G18" s="2">
-        <v>45322</v>
+        <v>45315</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>125679178</v>
+        <v>124051506</v>
       </c>
       <c r="E19">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F19" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="G19" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>125689312</v>
+        <v>124183151</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="G20" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>125954653</v>
+        <v>124220640</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="G21" s="2">
-        <v>45322</v>
+        <v>45324</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>126423932</v>
+        <v>124285536</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45323</v>
+        <v>45324</v>
       </c>
       <c r="G22" s="2">
-        <v>45323</v>
+        <v>45322</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1383,22 +1383,22 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>110074933</v>
+        <v>124529298</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>43453</v>
+        <v>45324</v>
       </c>
       <c r="G23" s="2">
-        <v>43441</v>
+        <v>45324</v>
       </c>
       <c r="I23">
         <v>42</v>
       </c>
       <c r="J23">
-        <v>8023</v>
+        <v>8001</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1421,16 +1421,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>123058958</v>
+        <v>124541408</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>44995</v>
+        <v>45324</v>
       </c>
       <c r="G24" s="2">
-        <v>44993</v>
+        <v>45322</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1459,22 +1459,22 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>126478856</v>
+        <v>124542863</v>
       </c>
       <c r="E25">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45314</v>
+        <v>45325</v>
       </c>
       <c r="G25" s="2">
-        <v>45314</v>
+        <v>45325</v>
       </c>
       <c r="I25">
         <v>42</v>
       </c>
       <c r="J25">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>126478886</v>
+        <v>124637708</v>
       </c>
       <c r="E26">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="G26" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="I26">
         <v>42</v>
       </c>
       <c r="J26">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>126478926</v>
+        <v>124778733</v>
       </c>
       <c r="E27">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="G27" s="2">
-        <v>45314</v>
+        <v>45320</v>
       </c>
       <c r="I27">
         <v>42</v>
       </c>
       <c r="J27">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>126480635</v>
+        <v>124786737</v>
       </c>
       <c r="E28">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="G28" s="2">
-        <v>45314</v>
+        <v>45320</v>
       </c>
       <c r="I28">
         <v>42</v>
       </c>
       <c r="J28">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -1611,16 +1611,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>126486551</v>
+        <v>125042388</v>
       </c>
       <c r="E29">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="G29" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="I29">
         <v>42</v>
@@ -1649,16 +1649,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>126487044</v>
+        <v>125213165</v>
       </c>
       <c r="E30">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="G30" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="I30">
         <v>42</v>
@@ -1687,16 +1687,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>126487805</v>
+        <v>125267354</v>
       </c>
       <c r="E31">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="G31" s="2">
-        <v>45314</v>
+        <v>45316</v>
       </c>
       <c r="I31">
         <v>42</v>
@@ -1725,16 +1725,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>126488415</v>
+        <v>125296638</v>
       </c>
       <c r="E32">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="G32" s="2">
-        <v>45314</v>
+        <v>45322</v>
       </c>
       <c r="I32">
         <v>42</v>
@@ -1763,16 +1763,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>126488859</v>
+        <v>125523318</v>
       </c>
       <c r="E33">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F33" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="G33" s="2">
-        <v>45314</v>
+        <v>45322</v>
       </c>
       <c r="I33">
         <v>42</v>
@@ -1801,16 +1801,16 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>126489133</v>
+        <v>125931219</v>
       </c>
       <c r="E34">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F34" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="G34" s="2">
-        <v>45314</v>
+        <v>45323</v>
       </c>
       <c r="I34">
         <v>42</v>
@@ -1839,16 +1839,16 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>126489546</v>
+        <v>126007189</v>
       </c>
       <c r="E35">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F35" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="G35" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="I35">
         <v>42</v>
@@ -1877,16 +1877,16 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>126489872</v>
+        <v>126062976</v>
       </c>
       <c r="E36">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F36" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="G36" s="2">
-        <v>45314</v>
+        <v>45323</v>
       </c>
       <c r="I36">
         <v>42</v>
@@ -1915,16 +1915,16 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>126490085</v>
+        <v>126294536</v>
       </c>
       <c r="E37">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F37" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="G37" s="2">
-        <v>45314</v>
+        <v>45317</v>
       </c>
       <c r="I37">
         <v>42</v>
@@ -1953,16 +1953,16 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>126490481</v>
+        <v>126321875</v>
       </c>
       <c r="E38">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="G38" s="2">
-        <v>45314</v>
+        <v>45324</v>
       </c>
       <c r="I38">
         <v>42</v>
@@ -1991,22 +1991,22 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>126490671</v>
+        <v>110074933</v>
       </c>
       <c r="E39">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F39" s="2">
-        <v>45314</v>
+        <v>43453</v>
       </c>
       <c r="G39" s="2">
-        <v>45314</v>
+        <v>43441</v>
       </c>
       <c r="I39">
         <v>42</v>
       </c>
       <c r="J39">
-        <v>8001</v>
+        <v>8023</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2029,16 +2029,16 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>126490881</v>
+        <v>123058958</v>
       </c>
       <c r="E40">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F40" s="2">
-        <v>45314</v>
+        <v>44995</v>
       </c>
       <c r="G40" s="2">
-        <v>45314</v>
+        <v>44993</v>
       </c>
       <c r="I40">
         <v>42</v>
@@ -2067,22 +2067,22 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>126491015</v>
+        <v>126493858</v>
       </c>
       <c r="E41">
         <v>601</v>
       </c>
       <c r="F41" s="2">
-        <v>45314</v>
+        <v>45315</v>
       </c>
       <c r="G41" s="2">
-        <v>45314</v>
+        <v>45315</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>126480635</v>
+        <v>126494202</v>
       </c>
       <c r="E42">
         <v>601</v>
       </c>
       <c r="F42" s="2">
-        <v>45314</v>
+        <v>45315</v>
       </c>
       <c r="G42" s="2">
-        <v>45314</v>
+        <v>45315</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2143,22 +2143,22 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>126488343</v>
+        <v>126494422</v>
       </c>
       <c r="E43">
         <v>601</v>
       </c>
       <c r="F43" s="2">
-        <v>45314</v>
+        <v>45315</v>
       </c>
       <c r="G43" s="2">
-        <v>45314</v>
+        <v>45315</v>
       </c>
       <c r="I43">
         <v>42</v>
       </c>
       <c r="J43">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2176,6 +2176,3806 @@
         <v>0</v>
       </c>
       <c r="Q43">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>126494619</v>
+      </c>
+      <c r="E44">
+        <v>601</v>
+      </c>
+      <c r="F44" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G44" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I44">
+        <v>42</v>
+      </c>
+      <c r="J44">
+        <v>8001</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>126494925</v>
+      </c>
+      <c r="E45">
+        <v>601</v>
+      </c>
+      <c r="F45" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G45" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I45">
+        <v>42</v>
+      </c>
+      <c r="J45">
+        <v>8001</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>126495279</v>
+      </c>
+      <c r="E46">
+        <v>601</v>
+      </c>
+      <c r="F46" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G46" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I46">
+        <v>42</v>
+      </c>
+      <c r="J46">
+        <v>8004</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>126495359</v>
+      </c>
+      <c r="E47">
+        <v>601</v>
+      </c>
+      <c r="F47" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G47" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I47">
+        <v>42</v>
+      </c>
+      <c r="J47">
+        <v>8004</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>126495366</v>
+      </c>
+      <c r="E48">
+        <v>601</v>
+      </c>
+      <c r="F48" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G48" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I48">
+        <v>42</v>
+      </c>
+      <c r="J48">
+        <v>8001</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>126495984</v>
+      </c>
+      <c r="E49">
+        <v>601</v>
+      </c>
+      <c r="F49" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G49" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I49">
+        <v>42</v>
+      </c>
+      <c r="J49">
+        <v>8001</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>126496016</v>
+      </c>
+      <c r="E50">
+        <v>601</v>
+      </c>
+      <c r="F50" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G50" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I50">
+        <v>42</v>
+      </c>
+      <c r="J50">
+        <v>8004</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>126496289</v>
+      </c>
+      <c r="E51">
+        <v>601</v>
+      </c>
+      <c r="F51" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G51" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I51">
+        <v>42</v>
+      </c>
+      <c r="J51">
+        <v>8001</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>126496523</v>
+      </c>
+      <c r="E52">
+        <v>601</v>
+      </c>
+      <c r="F52" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G52" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I52">
+        <v>42</v>
+      </c>
+      <c r="J52">
+        <v>8004</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>126496743</v>
+      </c>
+      <c r="E53">
+        <v>601</v>
+      </c>
+      <c r="F53" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G53" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I53">
+        <v>42</v>
+      </c>
+      <c r="J53">
+        <v>8004</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>126502144</v>
+      </c>
+      <c r="E54">
+        <v>601</v>
+      </c>
+      <c r="F54" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G54" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I54">
+        <v>42</v>
+      </c>
+      <c r="J54">
+        <v>8001</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>126502348</v>
+      </c>
+      <c r="E55">
+        <v>601</v>
+      </c>
+      <c r="F55" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G55" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I55">
+        <v>42</v>
+      </c>
+      <c r="J55">
+        <v>8001</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>126502830</v>
+      </c>
+      <c r="E56">
+        <v>601</v>
+      </c>
+      <c r="F56" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G56" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I56">
+        <v>42</v>
+      </c>
+      <c r="J56">
+        <v>8001</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>126503301</v>
+      </c>
+      <c r="E57">
+        <v>601</v>
+      </c>
+      <c r="F57" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G57" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I57">
+        <v>42</v>
+      </c>
+      <c r="J57">
+        <v>8001</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>126504004</v>
+      </c>
+      <c r="E58">
+        <v>601</v>
+      </c>
+      <c r="F58" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G58" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I58">
+        <v>42</v>
+      </c>
+      <c r="J58">
+        <v>8001</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>126504329</v>
+      </c>
+      <c r="E59">
+        <v>601</v>
+      </c>
+      <c r="F59" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G59" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I59">
+        <v>42</v>
+      </c>
+      <c r="J59">
+        <v>8001</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>126504558</v>
+      </c>
+      <c r="E60">
+        <v>601</v>
+      </c>
+      <c r="F60" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G60" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I60">
+        <v>42</v>
+      </c>
+      <c r="J60">
+        <v>8001</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>126504908</v>
+      </c>
+      <c r="E61">
+        <v>601</v>
+      </c>
+      <c r="F61" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G61" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I61">
+        <v>42</v>
+      </c>
+      <c r="J61">
+        <v>8001</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>126504969</v>
+      </c>
+      <c r="E62">
+        <v>601</v>
+      </c>
+      <c r="F62" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G62" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I62">
+        <v>42</v>
+      </c>
+      <c r="J62">
+        <v>8004</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>126505148</v>
+      </c>
+      <c r="E63">
+        <v>601</v>
+      </c>
+      <c r="F63" s="2">
+        <v>45315</v>
+      </c>
+      <c r="G63" s="2">
+        <v>45315</v>
+      </c>
+      <c r="I63">
+        <v>42</v>
+      </c>
+      <c r="J63">
+        <v>8004</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>126507171</v>
+      </c>
+      <c r="E64">
+        <v>601</v>
+      </c>
+      <c r="F64" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G64" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I64">
+        <v>42</v>
+      </c>
+      <c r="J64">
+        <v>8001</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>126507271</v>
+      </c>
+      <c r="E65">
+        <v>601</v>
+      </c>
+      <c r="F65" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G65" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I65">
+        <v>42</v>
+      </c>
+      <c r="J65">
+        <v>8001</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>126507420</v>
+      </c>
+      <c r="E66">
+        <v>601</v>
+      </c>
+      <c r="F66" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G66" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I66">
+        <v>42</v>
+      </c>
+      <c r="J66">
+        <v>8001</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>126507614</v>
+      </c>
+      <c r="E67">
+        <v>601</v>
+      </c>
+      <c r="F67" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G67" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I67">
+        <v>42</v>
+      </c>
+      <c r="J67">
+        <v>8001</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>126507692</v>
+      </c>
+      <c r="E68">
+        <v>601</v>
+      </c>
+      <c r="F68" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G68" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I68">
+        <v>42</v>
+      </c>
+      <c r="J68">
+        <v>8004</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>126508287</v>
+      </c>
+      <c r="E69">
+        <v>601</v>
+      </c>
+      <c r="F69" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G69" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I69">
+        <v>42</v>
+      </c>
+      <c r="J69">
+        <v>8001</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>126508783</v>
+      </c>
+      <c r="E70">
+        <v>601</v>
+      </c>
+      <c r="F70" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G70" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I70">
+        <v>42</v>
+      </c>
+      <c r="J70">
+        <v>8004</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>126509932</v>
+      </c>
+      <c r="E71">
+        <v>601</v>
+      </c>
+      <c r="F71" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G71" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I71">
+        <v>42</v>
+      </c>
+      <c r="J71">
+        <v>8004</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>126510209</v>
+      </c>
+      <c r="E72">
+        <v>601</v>
+      </c>
+      <c r="F72" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G72" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I72">
+        <v>42</v>
+      </c>
+      <c r="J72">
+        <v>8004</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>126510236</v>
+      </c>
+      <c r="E73">
+        <v>601</v>
+      </c>
+      <c r="F73" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G73" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I73">
+        <v>42</v>
+      </c>
+      <c r="J73">
+        <v>8001</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>126510798</v>
+      </c>
+      <c r="E74">
+        <v>601</v>
+      </c>
+      <c r="F74" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G74" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I74">
+        <v>42</v>
+      </c>
+      <c r="J74">
+        <v>8001</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>126512161</v>
+      </c>
+      <c r="E75">
+        <v>601</v>
+      </c>
+      <c r="F75" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G75" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I75">
+        <v>42</v>
+      </c>
+      <c r="J75">
+        <v>8001</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>126512256</v>
+      </c>
+      <c r="E76">
+        <v>601</v>
+      </c>
+      <c r="F76" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G76" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I76">
+        <v>42</v>
+      </c>
+      <c r="J76">
+        <v>8004</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>126512524</v>
+      </c>
+      <c r="E77">
+        <v>601</v>
+      </c>
+      <c r="F77" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G77" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I77">
+        <v>42</v>
+      </c>
+      <c r="J77">
+        <v>8001</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>126513189</v>
+      </c>
+      <c r="E78">
+        <v>601</v>
+      </c>
+      <c r="F78" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G78" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I78">
+        <v>42</v>
+      </c>
+      <c r="J78">
+        <v>8001</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>126514494</v>
+      </c>
+      <c r="E79">
+        <v>601</v>
+      </c>
+      <c r="F79" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G79" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I79">
+        <v>42</v>
+      </c>
+      <c r="J79">
+        <v>8001</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>126514971</v>
+      </c>
+      <c r="E80">
+        <v>601</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I80">
+        <v>42</v>
+      </c>
+      <c r="J80">
+        <v>8004</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>126516651</v>
+      </c>
+      <c r="E81">
+        <v>601</v>
+      </c>
+      <c r="F81" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G81" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I81">
+        <v>42</v>
+      </c>
+      <c r="J81">
+        <v>8001</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>126521731</v>
+      </c>
+      <c r="E82">
+        <v>601</v>
+      </c>
+      <c r="F82" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G82" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I82">
+        <v>42</v>
+      </c>
+      <c r="J82">
+        <v>8001</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>126522088</v>
+      </c>
+      <c r="E83">
+        <v>601</v>
+      </c>
+      <c r="F83" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G83" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I83">
+        <v>42</v>
+      </c>
+      <c r="J83">
+        <v>8001</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>126522209</v>
+      </c>
+      <c r="E84">
+        <v>601</v>
+      </c>
+      <c r="F84" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G84" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I84">
+        <v>42</v>
+      </c>
+      <c r="J84">
+        <v>8004</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>126522282</v>
+      </c>
+      <c r="E85">
+        <v>601</v>
+      </c>
+      <c r="F85" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G85" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I85">
+        <v>42</v>
+      </c>
+      <c r="J85">
+        <v>8004</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>126522315</v>
+      </c>
+      <c r="E86">
+        <v>601</v>
+      </c>
+      <c r="F86" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G86" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I86">
+        <v>42</v>
+      </c>
+      <c r="J86">
+        <v>8001</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>126522612</v>
+      </c>
+      <c r="E87">
+        <v>601</v>
+      </c>
+      <c r="F87" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G87" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I87">
+        <v>42</v>
+      </c>
+      <c r="J87">
+        <v>8004</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>126522702</v>
+      </c>
+      <c r="E88">
+        <v>601</v>
+      </c>
+      <c r="F88" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G88" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I88">
+        <v>42</v>
+      </c>
+      <c r="J88">
+        <v>8001</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>126522750</v>
+      </c>
+      <c r="E89">
+        <v>601</v>
+      </c>
+      <c r="F89" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G89" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I89">
+        <v>42</v>
+      </c>
+      <c r="J89">
+        <v>8001</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>126523016</v>
+      </c>
+      <c r="E90">
+        <v>601</v>
+      </c>
+      <c r="F90" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G90" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I90">
+        <v>42</v>
+      </c>
+      <c r="J90">
+        <v>8001</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>126523190</v>
+      </c>
+      <c r="E91">
+        <v>601</v>
+      </c>
+      <c r="F91" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G91" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I91">
+        <v>42</v>
+      </c>
+      <c r="J91">
+        <v>8004</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>126523228</v>
+      </c>
+      <c r="E92">
+        <v>601</v>
+      </c>
+      <c r="F92" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G92" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I92">
+        <v>42</v>
+      </c>
+      <c r="J92">
+        <v>8004</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>126523252</v>
+      </c>
+      <c r="E93">
+        <v>601</v>
+      </c>
+      <c r="F93" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G93" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I93">
+        <v>42</v>
+      </c>
+      <c r="J93">
+        <v>8001</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>126523426</v>
+      </c>
+      <c r="E94">
+        <v>601</v>
+      </c>
+      <c r="F94" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G94" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I94">
+        <v>42</v>
+      </c>
+      <c r="J94">
+        <v>8001</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>126523737</v>
+      </c>
+      <c r="E95">
+        <v>601</v>
+      </c>
+      <c r="F95" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G95" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I95">
+        <v>42</v>
+      </c>
+      <c r="J95">
+        <v>8001</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>126525380</v>
+      </c>
+      <c r="E96">
+        <v>601</v>
+      </c>
+      <c r="F96" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G96" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I96">
+        <v>42</v>
+      </c>
+      <c r="J96">
+        <v>8001</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>126525469</v>
+      </c>
+      <c r="E97">
+        <v>601</v>
+      </c>
+      <c r="F97" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G97" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I97">
+        <v>42</v>
+      </c>
+      <c r="J97">
+        <v>8004</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>126525496</v>
+      </c>
+      <c r="E98">
+        <v>601</v>
+      </c>
+      <c r="F98" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G98" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I98">
+        <v>42</v>
+      </c>
+      <c r="J98">
+        <v>8001</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>126525551</v>
+      </c>
+      <c r="E99">
+        <v>601</v>
+      </c>
+      <c r="F99" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G99" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I99">
+        <v>42</v>
+      </c>
+      <c r="J99">
+        <v>8004</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>126525570</v>
+      </c>
+      <c r="E100">
+        <v>601</v>
+      </c>
+      <c r="F100" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G100" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I100">
+        <v>42</v>
+      </c>
+      <c r="J100">
+        <v>8001</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>126525742</v>
+      </c>
+      <c r="E101">
+        <v>601</v>
+      </c>
+      <c r="F101" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G101" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I101">
+        <v>42</v>
+      </c>
+      <c r="J101">
+        <v>8001</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>126525950</v>
+      </c>
+      <c r="E102">
+        <v>601</v>
+      </c>
+      <c r="F102" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G102" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I102">
+        <v>42</v>
+      </c>
+      <c r="J102">
+        <v>8001</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>126525982</v>
+      </c>
+      <c r="E103">
+        <v>601</v>
+      </c>
+      <c r="F103" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G103" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I103">
+        <v>42</v>
+      </c>
+      <c r="J103">
+        <v>8001</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>126526116</v>
+      </c>
+      <c r="E104">
+        <v>601</v>
+      </c>
+      <c r="F104" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G104" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I104">
+        <v>42</v>
+      </c>
+      <c r="J104">
+        <v>8001</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>126526125</v>
+      </c>
+      <c r="E105">
+        <v>601</v>
+      </c>
+      <c r="F105" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G105" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I105">
+        <v>42</v>
+      </c>
+      <c r="J105">
+        <v>8001</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>126526315</v>
+      </c>
+      <c r="E106">
+        <v>601</v>
+      </c>
+      <c r="F106" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G106" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I106">
+        <v>42</v>
+      </c>
+      <c r="J106">
+        <v>8001</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>126526324</v>
+      </c>
+      <c r="E107">
+        <v>601</v>
+      </c>
+      <c r="F107" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G107" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I107">
+        <v>42</v>
+      </c>
+      <c r="J107">
+        <v>8001</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>126526432</v>
+      </c>
+      <c r="E108">
+        <v>601</v>
+      </c>
+      <c r="F108" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G108" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I108">
+        <v>42</v>
+      </c>
+      <c r="J108">
+        <v>8001</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>126526501</v>
+      </c>
+      <c r="E109">
+        <v>601</v>
+      </c>
+      <c r="F109" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G109" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I109">
+        <v>42</v>
+      </c>
+      <c r="J109">
+        <v>8001</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>126526566</v>
+      </c>
+      <c r="E110">
+        <v>601</v>
+      </c>
+      <c r="F110" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G110" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I110">
+        <v>42</v>
+      </c>
+      <c r="J110">
+        <v>8004</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>126526599</v>
+      </c>
+      <c r="E111">
+        <v>601</v>
+      </c>
+      <c r="F111" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G111" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I111">
+        <v>42</v>
+      </c>
+      <c r="J111">
+        <v>8001</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>126526707</v>
+      </c>
+      <c r="E112">
+        <v>601</v>
+      </c>
+      <c r="F112" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G112" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I112">
+        <v>42</v>
+      </c>
+      <c r="J112">
+        <v>8001</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>126526894</v>
+      </c>
+      <c r="E113">
+        <v>601</v>
+      </c>
+      <c r="F113" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G113" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I113">
+        <v>42</v>
+      </c>
+      <c r="J113">
+        <v>8001</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>126526964</v>
+      </c>
+      <c r="E114">
+        <v>601</v>
+      </c>
+      <c r="F114" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G114" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I114">
+        <v>42</v>
+      </c>
+      <c r="J114">
+        <v>8001</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>126527040</v>
+      </c>
+      <c r="E115">
+        <v>601</v>
+      </c>
+      <c r="F115" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G115" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I115">
+        <v>42</v>
+      </c>
+      <c r="J115">
+        <v>8001</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>126527098</v>
+      </c>
+      <c r="E116">
+        <v>601</v>
+      </c>
+      <c r="F116" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G116" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I116">
+        <v>42</v>
+      </c>
+      <c r="J116">
+        <v>8001</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>126527274</v>
+      </c>
+      <c r="E117">
+        <v>601</v>
+      </c>
+      <c r="F117" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G117" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I117">
+        <v>42</v>
+      </c>
+      <c r="J117">
+        <v>8001</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>126527330</v>
+      </c>
+      <c r="E118">
+        <v>601</v>
+      </c>
+      <c r="F118" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G118" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I118">
+        <v>42</v>
+      </c>
+      <c r="J118">
+        <v>8001</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>126527554</v>
+      </c>
+      <c r="E119">
+        <v>601</v>
+      </c>
+      <c r="F119" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G119" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I119">
+        <v>42</v>
+      </c>
+      <c r="J119">
+        <v>8001</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>126527566</v>
+      </c>
+      <c r="E120">
+        <v>601</v>
+      </c>
+      <c r="F120" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G120" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I120">
+        <v>42</v>
+      </c>
+      <c r="J120">
+        <v>8001</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>126527735</v>
+      </c>
+      <c r="E121">
+        <v>601</v>
+      </c>
+      <c r="F121" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G121" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I121">
+        <v>42</v>
+      </c>
+      <c r="J121">
+        <v>8001</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>126527906</v>
+      </c>
+      <c r="E122">
+        <v>601</v>
+      </c>
+      <c r="F122" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G122" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I122">
+        <v>42</v>
+      </c>
+      <c r="J122">
+        <v>8001</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>126528010</v>
+      </c>
+      <c r="E123">
+        <v>601</v>
+      </c>
+      <c r="F123" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G123" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I123">
+        <v>42</v>
+      </c>
+      <c r="J123">
+        <v>8001</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+      <c r="Q123">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>126528056</v>
+      </c>
+      <c r="E124">
+        <v>601</v>
+      </c>
+      <c r="F124" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G124" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I124">
+        <v>42</v>
+      </c>
+      <c r="J124">
+        <v>8001</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>126528167</v>
+      </c>
+      <c r="E125">
+        <v>601</v>
+      </c>
+      <c r="F125" s="2">
+        <v>45322</v>
+      </c>
+      <c r="G125" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I125">
+        <v>42</v>
+      </c>
+      <c r="J125">
+        <v>8013</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="Q125">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>126528296</v>
+      </c>
+      <c r="E126">
+        <v>601</v>
+      </c>
+      <c r="F126" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G126" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I126">
+        <v>42</v>
+      </c>
+      <c r="J126">
+        <v>8004</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>126528482</v>
+      </c>
+      <c r="E127">
+        <v>601</v>
+      </c>
+      <c r="F127" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G127" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I127">
+        <v>42</v>
+      </c>
+      <c r="J127">
+        <v>8001</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>126528500</v>
+      </c>
+      <c r="E128">
+        <v>601</v>
+      </c>
+      <c r="F128" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G128" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I128">
+        <v>42</v>
+      </c>
+      <c r="J128">
+        <v>8004</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>126528587</v>
+      </c>
+      <c r="E129">
+        <v>601</v>
+      </c>
+      <c r="F129" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G129" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I129">
+        <v>42</v>
+      </c>
+      <c r="J129">
+        <v>8004</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+      <c r="Q129">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>126528874</v>
+      </c>
+      <c r="E130">
+        <v>601</v>
+      </c>
+      <c r="F130" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G130" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I130">
+        <v>42</v>
+      </c>
+      <c r="J130">
+        <v>8001</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>126528893</v>
+      </c>
+      <c r="E131">
+        <v>601</v>
+      </c>
+      <c r="F131" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G131" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I131">
+        <v>42</v>
+      </c>
+      <c r="J131">
+        <v>8001</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>126528956</v>
+      </c>
+      <c r="E132">
+        <v>601</v>
+      </c>
+      <c r="F132" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G132" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I132">
+        <v>42</v>
+      </c>
+      <c r="J132">
+        <v>8001</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>126529010</v>
+      </c>
+      <c r="E133">
+        <v>601</v>
+      </c>
+      <c r="F133" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G133" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I133">
+        <v>42</v>
+      </c>
+      <c r="J133">
+        <v>8001</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>126529257</v>
+      </c>
+      <c r="E134">
+        <v>601</v>
+      </c>
+      <c r="F134" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G134" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I134">
+        <v>42</v>
+      </c>
+      <c r="J134">
+        <v>8001</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>126529376</v>
+      </c>
+      <c r="E135">
+        <v>601</v>
+      </c>
+      <c r="F135" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G135" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I135">
+        <v>42</v>
+      </c>
+      <c r="J135">
+        <v>8001</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>126529570</v>
+      </c>
+      <c r="E136">
+        <v>601</v>
+      </c>
+      <c r="F136" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G136" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I136">
+        <v>42</v>
+      </c>
+      <c r="J136">
+        <v>8004</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>126530158</v>
+      </c>
+      <c r="E137">
+        <v>601</v>
+      </c>
+      <c r="F137" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G137" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I137">
+        <v>42</v>
+      </c>
+      <c r="J137">
+        <v>8001</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>126530759</v>
+      </c>
+      <c r="E138">
+        <v>601</v>
+      </c>
+      <c r="F138" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G138" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I138">
+        <v>42</v>
+      </c>
+      <c r="J138">
+        <v>8004</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>126531774</v>
+      </c>
+      <c r="E139">
+        <v>601</v>
+      </c>
+      <c r="F139" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G139" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I139">
+        <v>42</v>
+      </c>
+      <c r="J139">
+        <v>8004</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>126532383</v>
+      </c>
+      <c r="E140">
+        <v>601</v>
+      </c>
+      <c r="F140" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G140" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I140">
+        <v>42</v>
+      </c>
+      <c r="J140">
+        <v>8004</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>126532826</v>
+      </c>
+      <c r="E141">
+        <v>601</v>
+      </c>
+      <c r="F141" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G141" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I141">
+        <v>42</v>
+      </c>
+      <c r="J141">
+        <v>8004</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>126512256</v>
+      </c>
+      <c r="E142">
+        <v>601</v>
+      </c>
+      <c r="F142" s="2">
+        <v>45316</v>
+      </c>
+      <c r="G142" s="2">
+        <v>45316</v>
+      </c>
+      <c r="I142">
+        <v>42</v>
+      </c>
+      <c r="J142">
+        <v>8004</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>126523190</v>
+      </c>
+      <c r="E143">
+        <v>601</v>
+      </c>
+      <c r="F143" s="2">
+        <v>45317</v>
+      </c>
+      <c r="G143" s="2">
+        <v>45317</v>
+      </c>
+      <c r="I143">
+        <v>42</v>
+      </c>
+      <c r="J143">
+        <v>8004</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
         <v>61</v>
       </c>
     </row>
@@ -9769,31 +13569,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\Brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172833C9-4019-4825-AAD0-50D57027AD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BFBCE5-B3DC-45AE-83EA-19245A8B7C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,16 +585,16 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>123643974</v>
+        <v>126301011</v>
       </c>
       <c r="E2">
         <v>2002</v>
       </c>
       <c r="F2" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G2" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="I2">
         <v>42</v>
@@ -623,22 +623,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>125380589</v>
+        <v>126756534</v>
       </c>
       <c r="E3">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F3" s="2">
-        <v>45341</v>
+        <v>45339</v>
       </c>
       <c r="G3" s="2">
-        <v>45341</v>
+        <v>45339</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -661,22 +661,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>126737663</v>
+        <v>123080662</v>
       </c>
       <c r="E4">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F4" s="2">
-        <v>45338</v>
+        <v>45342</v>
       </c>
       <c r="G4" s="2">
-        <v>45338</v>
+        <v>45342</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,22 +699,22 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>126743930</v>
+        <v>123228022</v>
       </c>
       <c r="E5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F5" s="2">
-        <v>45338</v>
+        <v>45342</v>
       </c>
       <c r="G5" s="2">
-        <v>45338</v>
+        <v>45342</v>
       </c>
       <c r="I5">
         <v>42</v>
       </c>
       <c r="J5">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,22 +737,22 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>126754623</v>
+        <v>123875034</v>
       </c>
       <c r="E6">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F6" s="2">
-        <v>45338</v>
+        <v>45342</v>
       </c>
       <c r="G6" s="2">
-        <v>45338</v>
+        <v>45341</v>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -775,16 +775,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>123372969</v>
+        <v>123895521</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G7" s="2">
-        <v>45338</v>
+        <v>45342</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -813,16 +813,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>123792391</v>
+        <v>124340469</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G8" s="2">
-        <v>45338</v>
+        <v>45342</v>
       </c>
       <c r="I8">
         <v>42</v>
@@ -851,16 +851,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>123984757</v>
+        <v>124609406</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G9" s="2">
-        <v>45339</v>
+        <v>45338</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -889,16 +889,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>124122110</v>
+        <v>124685842</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G10" s="2">
-        <v>45338</v>
+        <v>45342</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -927,13 +927,13 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>124167448</v>
+        <v>124729939</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G11" s="2">
         <v>45338</v>
@@ -965,16 +965,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>124378395</v>
+        <v>125002698</v>
       </c>
       <c r="E12">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F12" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G12" s="2">
-        <v>45338</v>
+        <v>45342</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>124435375</v>
+        <v>125160504</v>
       </c>
       <c r="E13">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F13" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G13" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>124681692</v>
+        <v>125684095</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G14" s="2">
-        <v>45338</v>
+        <v>45342</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>124905856</v>
+        <v>125781456</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G15" s="2">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>125163123</v>
+        <v>125890696</v>
       </c>
       <c r="E16">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F16" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G16" s="2">
-        <v>45336</v>
+        <v>45342</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>125190078</v>
+        <v>126017227</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G17" s="2">
-        <v>45339</v>
+        <v>45342</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,13 +1193,13 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>125251586</v>
+        <v>126286372</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G18" s="2">
         <v>45338</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>125378503</v>
+        <v>126525438</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G19" s="2">
-        <v>45338</v>
+        <v>45342</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1264,766 +1264,6 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>125698587</v>
-      </c>
-      <c r="E20">
-        <v>1211</v>
-      </c>
-      <c r="F20" s="2">
-        <v>45341</v>
-      </c>
-      <c r="G20" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I20">
-        <v>42</v>
-      </c>
-      <c r="J20">
-        <v>8001</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>125823502</v>
-      </c>
-      <c r="E21">
-        <v>1211</v>
-      </c>
-      <c r="F21" s="2">
-        <v>45341</v>
-      </c>
-      <c r="G21" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I21">
-        <v>42</v>
-      </c>
-      <c r="J21">
-        <v>8001</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>126013319</v>
-      </c>
-      <c r="E22">
-        <v>1211</v>
-      </c>
-      <c r="F22" s="2">
-        <v>45341</v>
-      </c>
-      <c r="G22" s="2">
-        <v>45341</v>
-      </c>
-      <c r="I22">
-        <v>42</v>
-      </c>
-      <c r="J22">
-        <v>8001</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>126275180</v>
-      </c>
-      <c r="E23">
-        <v>1212</v>
-      </c>
-      <c r="F23" s="2">
-        <v>45341</v>
-      </c>
-      <c r="G23" s="2">
-        <v>45341</v>
-      </c>
-      <c r="I23">
-        <v>42</v>
-      </c>
-      <c r="J23">
-        <v>8001</v>
-      </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>126349853</v>
-      </c>
-      <c r="E24">
-        <v>1211</v>
-      </c>
-      <c r="F24" s="2">
-        <v>45341</v>
-      </c>
-      <c r="G24" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I24">
-        <v>42</v>
-      </c>
-      <c r="J24">
-        <v>8001</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>126358696</v>
-      </c>
-      <c r="E25">
-        <v>1211</v>
-      </c>
-      <c r="F25" s="2">
-        <v>45341</v>
-      </c>
-      <c r="G25" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I25">
-        <v>42</v>
-      </c>
-      <c r="J25">
-        <v>8001</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>126416318</v>
-      </c>
-      <c r="E26">
-        <v>1211</v>
-      </c>
-      <c r="F26" s="2">
-        <v>45341</v>
-      </c>
-      <c r="G26" s="2">
-        <v>45341</v>
-      </c>
-      <c r="I26">
-        <v>42</v>
-      </c>
-      <c r="J26">
-        <v>8001</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>126538980</v>
-      </c>
-      <c r="E27">
-        <v>1211</v>
-      </c>
-      <c r="F27" s="2">
-        <v>45341</v>
-      </c>
-      <c r="G27" s="2">
-        <v>45341</v>
-      </c>
-      <c r="I27">
-        <v>42</v>
-      </c>
-      <c r="J27">
-        <v>8001</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>126655325</v>
-      </c>
-      <c r="E28">
-        <v>1211</v>
-      </c>
-      <c r="F28" s="2">
-        <v>45329</v>
-      </c>
-      <c r="G28" s="2">
-        <v>45329</v>
-      </c>
-      <c r="I28">
-        <v>42</v>
-      </c>
-      <c r="J28">
-        <v>8001</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>126697180</v>
-      </c>
-      <c r="E29">
-        <v>1211</v>
-      </c>
-      <c r="F29" s="2">
-        <v>45334</v>
-      </c>
-      <c r="G29" s="2">
-        <v>45331</v>
-      </c>
-      <c r="I29">
-        <v>42</v>
-      </c>
-      <c r="J29">
-        <v>8001</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>126691670</v>
-      </c>
-      <c r="E30">
-        <v>601</v>
-      </c>
-      <c r="F30" s="2">
-        <v>45331</v>
-      </c>
-      <c r="G30" s="2">
-        <v>45331</v>
-      </c>
-      <c r="I30">
-        <v>42</v>
-      </c>
-      <c r="J30">
-        <v>8004</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>126691944</v>
-      </c>
-      <c r="E31">
-        <v>601</v>
-      </c>
-      <c r="F31" s="2">
-        <v>45331</v>
-      </c>
-      <c r="G31" s="2">
-        <v>45331</v>
-      </c>
-      <c r="I31">
-        <v>42</v>
-      </c>
-      <c r="J31">
-        <v>8004</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>126697370</v>
-      </c>
-      <c r="E32">
-        <v>601</v>
-      </c>
-      <c r="F32" s="2">
-        <v>45331</v>
-      </c>
-      <c r="G32" s="2">
-        <v>45331</v>
-      </c>
-      <c r="I32">
-        <v>42</v>
-      </c>
-      <c r="J32">
-        <v>8004</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>126697994</v>
-      </c>
-      <c r="E33">
-        <v>601</v>
-      </c>
-      <c r="F33" s="2">
-        <v>45331</v>
-      </c>
-      <c r="G33" s="2">
-        <v>45331</v>
-      </c>
-      <c r="I33">
-        <v>42</v>
-      </c>
-      <c r="J33">
-        <v>8004</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>126698059</v>
-      </c>
-      <c r="E34">
-        <v>601</v>
-      </c>
-      <c r="F34" s="2">
-        <v>45331</v>
-      </c>
-      <c r="G34" s="2">
-        <v>45331</v>
-      </c>
-      <c r="I34">
-        <v>42</v>
-      </c>
-      <c r="J34">
-        <v>8004</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>126698693</v>
-      </c>
-      <c r="E35">
-        <v>601</v>
-      </c>
-      <c r="F35" s="2">
-        <v>45331</v>
-      </c>
-      <c r="G35" s="2">
-        <v>45331</v>
-      </c>
-      <c r="I35">
-        <v>42</v>
-      </c>
-      <c r="J35">
-        <v>8004</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>126698786</v>
-      </c>
-      <c r="E36">
-        <v>601</v>
-      </c>
-      <c r="F36" s="2">
-        <v>45331</v>
-      </c>
-      <c r="G36" s="2">
-        <v>45331</v>
-      </c>
-      <c r="I36">
-        <v>42</v>
-      </c>
-      <c r="J36">
-        <v>8004</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>126699235</v>
-      </c>
-      <c r="E37">
-        <v>601</v>
-      </c>
-      <c r="F37" s="2">
-        <v>45331</v>
-      </c>
-      <c r="G37" s="2">
-        <v>45331</v>
-      </c>
-      <c r="I37">
-        <v>42</v>
-      </c>
-      <c r="J37">
-        <v>8004</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>126699739</v>
-      </c>
-      <c r="E38">
-        <v>601</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45331</v>
-      </c>
-      <c r="G38" s="2">
-        <v>45331</v>
-      </c>
-      <c r="I38">
-        <v>42</v>
-      </c>
-      <c r="J38">
-        <v>8004</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>126700300</v>
-      </c>
-      <c r="E39">
-        <v>601</v>
-      </c>
-      <c r="F39" s="2">
-        <v>45331</v>
-      </c>
-      <c r="G39" s="2">
-        <v>45331</v>
-      </c>
-      <c r="I39">
-        <v>42</v>
-      </c>
-      <c r="J39">
-        <v>8004</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
         <v>61</v>
       </c>
     </row>
@@ -9617,31 +8857,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPasta_de_trabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\Brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD78466E-532C-4275-9125-E7EB97AE6F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09124B1D-4CC3-4970-82DC-8998F936C7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiel" sheetId="28" r:id="rId1"/>
@@ -507,18 +507,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q38"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Q139"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
@@ -526,11 +526,11 @@
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,18 +583,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>125946555</v>
+        <v>126816802</v>
       </c>
       <c r="E2">
         <v>2013</v>
       </c>
       <c r="F2" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G2" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="I2">
         <v>42</v>
@@ -621,24 +621,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>126645849</v>
+        <v>126816976</v>
       </c>
       <c r="E3">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="F3" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G3" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -659,24 +659,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>126735514</v>
+        <v>126774800</v>
       </c>
       <c r="E4">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45344</v>
+        <v>45342</v>
       </c>
       <c r="G4" s="2">
-        <v>45344</v>
+        <v>45342</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -697,9 +697,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>126759821</v>
+        <v>126775879</v>
       </c>
       <c r="E5">
         <v>1211</v>
@@ -708,7 +708,7 @@
         <v>45342</v>
       </c>
       <c r="G5" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="I5">
         <v>42</v>
@@ -735,18 +735,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>126761926</v>
+        <v>126783644</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G6" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="I6">
         <v>42</v>
@@ -773,18 +773,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>126764027</v>
+        <v>126787923</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="G7" s="2">
-        <v>45341</v>
+        <v>45342</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -811,18 +811,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>126767248</v>
+        <v>126792177</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45341</v>
+        <v>45343</v>
       </c>
       <c r="G8" s="2">
-        <v>45341</v>
+        <v>45343</v>
       </c>
       <c r="I8">
         <v>42</v>
@@ -849,18 +849,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>126768532</v>
+        <v>126794289</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45341</v>
+        <v>45343</v>
       </c>
       <c r="G9" s="2">
-        <v>45341</v>
+        <v>45343</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -887,18 +887,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>126769207</v>
+        <v>126817353</v>
       </c>
       <c r="E10">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F10" s="2">
-        <v>45343</v>
+        <v>45345</v>
       </c>
       <c r="G10" s="2">
-        <v>45341</v>
+        <v>45344</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -925,62 +925,62 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>126769550</v>
+        <v>123321677</v>
       </c>
       <c r="E11">
+        <v>1211</v>
+      </c>
+      <c r="F11" s="2">
+        <v>45346</v>
+      </c>
+      <c r="G11" s="2">
+        <v>45346</v>
+      </c>
+      <c r="I11">
+        <v>42</v>
+      </c>
+      <c r="J11">
+        <v>8001</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>123355161</v>
+      </c>
+      <c r="E12">
         <v>1212</v>
       </c>
-      <c r="F11" s="2">
-        <v>45341</v>
-      </c>
-      <c r="G11" s="2">
-        <v>45341</v>
-      </c>
-      <c r="I11">
-        <v>42</v>
-      </c>
-      <c r="J11">
-        <v>1735</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>126772248</v>
-      </c>
-      <c r="E12">
-        <v>1211</v>
-      </c>
       <c r="F12" s="2">
-        <v>45341</v>
+        <v>45345</v>
       </c>
       <c r="G12" s="2">
-        <v>45341</v>
+        <v>45345</v>
       </c>
       <c r="I12">
         <v>42</v>
       </c>
       <c r="J12">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1001,18 +1001,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>123142361</v>
+        <v>123378206</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45344</v>
+        <v>45346</v>
       </c>
       <c r="G13" s="2">
-        <v>45342</v>
+        <v>45345</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1039,15 +1039,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>123364606</v>
+        <v>123449409</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G14" s="2">
         <v>45344</v>
@@ -1077,18 +1077,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>123512478</v>
+        <v>123546216</v>
       </c>
       <c r="E15">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G15" s="2">
-        <v>45337</v>
+        <v>45345</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1115,18 +1115,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>123594547</v>
+        <v>123573203</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G16" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1153,15 +1153,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>123616666</v>
+        <v>123598238</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G17" s="2">
         <v>45343</v>
@@ -1191,18 +1191,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>123682270</v>
+        <v>123600663</v>
       </c>
       <c r="E18">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G18" s="2">
-        <v>45342</v>
+        <v>45345</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1229,18 +1229,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>123692923</v>
+        <v>123606573</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G19" s="2">
-        <v>45344</v>
+        <v>45343</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1267,18 +1267,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>123904373</v>
+        <v>123681613</v>
       </c>
       <c r="E20">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F20" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G20" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1305,18 +1305,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>123993076</v>
+        <v>123728200</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G21" s="2">
-        <v>45338</v>
+        <v>45345</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1343,18 +1343,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>124656997</v>
+        <v>123849780</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
+        <v>45346</v>
+      </c>
+      <c r="G22" s="2">
         <v>45344</v>
-      </c>
-      <c r="G22" s="2">
-        <v>45343</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1381,18 +1381,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>124661233</v>
+        <v>123854747</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G23" s="2">
-        <v>45343</v>
+        <v>45345</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1419,18 +1419,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>124871818</v>
+        <v>123864928</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G24" s="2">
         <v>45344</v>
-      </c>
-      <c r="G24" s="2">
-        <v>45342</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1457,18 +1457,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>124963950</v>
+        <v>123910727</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G25" s="2">
-        <v>45343</v>
+        <v>45345</v>
       </c>
       <c r="I25">
         <v>42</v>
@@ -1495,15 +1495,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>125054621</v>
+        <v>123926279</v>
       </c>
       <c r="E26">
         <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G26" s="2">
         <v>45343</v>
@@ -1533,18 +1533,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>125086505</v>
+        <v>123956437</v>
       </c>
       <c r="E27">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F27" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G27" s="2">
         <v>45344</v>
-      </c>
-      <c r="G27" s="2">
-        <v>45343</v>
       </c>
       <c r="I27">
         <v>42</v>
@@ -1571,18 +1571,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>125433713</v>
+        <v>124441091</v>
       </c>
       <c r="E28">
         <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G28" s="2">
-        <v>45343</v>
+        <v>45345</v>
       </c>
       <c r="I28">
         <v>42</v>
@@ -1609,18 +1609,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>125842880</v>
+        <v>124499648</v>
       </c>
       <c r="E29">
         <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G29" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="I29">
         <v>42</v>
@@ -1647,18 +1647,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>126097117</v>
+        <v>124551135</v>
       </c>
       <c r="E30">
         <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G30" s="2">
-        <v>45343</v>
+        <v>45345</v>
       </c>
       <c r="I30">
         <v>42</v>
@@ -1685,18 +1685,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>126180255</v>
+        <v>124601503</v>
       </c>
       <c r="E31">
         <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G31" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="I31">
         <v>42</v>
@@ -1723,18 +1723,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>126421736</v>
+        <v>124610916</v>
       </c>
       <c r="E32">
         <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G32" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="I32">
         <v>42</v>
@@ -1761,18 +1761,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>126604338</v>
+        <v>124667962</v>
       </c>
       <c r="E33">
         <v>1211</v>
       </c>
       <c r="F33" s="2">
-        <v>45344</v>
+        <v>45346</v>
       </c>
       <c r="G33" s="2">
-        <v>45344</v>
+        <v>45343</v>
       </c>
       <c r="I33">
         <v>42</v>
@@ -1799,18 +1799,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>126658494</v>
+        <v>124692461</v>
       </c>
       <c r="E34">
         <v>1211</v>
       </c>
       <c r="F34" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="G34" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="I34">
         <v>42</v>
@@ -1837,18 +1837,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>126697078</v>
+        <v>124781063</v>
       </c>
       <c r="E35">
         <v>1211</v>
       </c>
       <c r="F35" s="2">
-        <v>45344</v>
+        <v>45346</v>
       </c>
       <c r="G35" s="2">
-        <v>45344</v>
+        <v>45343</v>
       </c>
       <c r="I35">
         <v>42</v>
@@ -1875,24 +1875,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>110074933</v>
+        <v>124815427</v>
       </c>
       <c r="E36">
         <v>1211</v>
       </c>
       <c r="F36" s="2">
-        <v>43453</v>
+        <v>45345</v>
       </c>
       <c r="G36" s="2">
-        <v>43441</v>
+        <v>45345</v>
       </c>
       <c r="I36">
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8023</v>
+        <v>8001</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -1913,18 +1913,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>123058958</v>
+        <v>124884121</v>
       </c>
       <c r="E37">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F37" s="2">
-        <v>44995</v>
+        <v>45345</v>
       </c>
       <c r="G37" s="2">
-        <v>44993</v>
+        <v>45345</v>
       </c>
       <c r="I37">
         <v>42</v>
@@ -1951,18 +1951,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>126697180</v>
+        <v>125012996</v>
       </c>
       <c r="E38">
         <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>45334</v>
+        <v>45345</v>
       </c>
       <c r="G38" s="2">
-        <v>45331</v>
+        <v>45345</v>
       </c>
       <c r="I38">
         <v>42</v>
@@ -1986,6 +1986,3844 @@
         <v>0</v>
       </c>
       <c r="Q38">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>125020215</v>
+      </c>
+      <c r="E39">
+        <v>1211</v>
+      </c>
+      <c r="F39" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G39" s="2">
+        <v>45342</v>
+      </c>
+      <c r="I39">
+        <v>42</v>
+      </c>
+      <c r="J39">
+        <v>8001</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>125172235</v>
+      </c>
+      <c r="E40">
+        <v>1211</v>
+      </c>
+      <c r="F40" s="2">
+        <v>45346</v>
+      </c>
+      <c r="G40" s="2">
+        <v>45345</v>
+      </c>
+      <c r="I40">
+        <v>42</v>
+      </c>
+      <c r="J40">
+        <v>8001</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>125205170</v>
+      </c>
+      <c r="E41">
+        <v>1211</v>
+      </c>
+      <c r="F41" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G41" s="2">
+        <v>45344</v>
+      </c>
+      <c r="I41">
+        <v>42</v>
+      </c>
+      <c r="J41">
+        <v>8001</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>125245636</v>
+      </c>
+      <c r="E42">
+        <v>1212</v>
+      </c>
+      <c r="F42" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G42" s="2">
+        <v>45345</v>
+      </c>
+      <c r="I42">
+        <v>42</v>
+      </c>
+      <c r="J42">
+        <v>8001</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>125303672</v>
+      </c>
+      <c r="E43">
+        <v>1211</v>
+      </c>
+      <c r="F43" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G43" s="2">
+        <v>45345</v>
+      </c>
+      <c r="I43">
+        <v>42</v>
+      </c>
+      <c r="J43">
+        <v>8001</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>125413419</v>
+      </c>
+      <c r="E44">
+        <v>1211</v>
+      </c>
+      <c r="F44" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G44" s="2">
+        <v>45342</v>
+      </c>
+      <c r="I44">
+        <v>42</v>
+      </c>
+      <c r="J44">
+        <v>8001</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>125528371</v>
+      </c>
+      <c r="E45">
+        <v>1211</v>
+      </c>
+      <c r="F45" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G45" s="2">
+        <v>45344</v>
+      </c>
+      <c r="I45">
+        <v>42</v>
+      </c>
+      <c r="J45">
+        <v>8001</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>125642845</v>
+      </c>
+      <c r="E46">
+        <v>1211</v>
+      </c>
+      <c r="F46" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G46" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I46">
+        <v>42</v>
+      </c>
+      <c r="J46">
+        <v>8001</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>125706834</v>
+      </c>
+      <c r="E47">
+        <v>1211</v>
+      </c>
+      <c r="F47" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G47" s="2">
+        <v>45345</v>
+      </c>
+      <c r="I47">
+        <v>42</v>
+      </c>
+      <c r="J47">
+        <v>8001</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>125718814</v>
+      </c>
+      <c r="E48">
+        <v>1211</v>
+      </c>
+      <c r="F48" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G48" s="2">
+        <v>45344</v>
+      </c>
+      <c r="I48">
+        <v>42</v>
+      </c>
+      <c r="J48">
+        <v>8001</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>125803590</v>
+      </c>
+      <c r="E49">
+        <v>1211</v>
+      </c>
+      <c r="F49" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G49" s="2">
+        <v>45345</v>
+      </c>
+      <c r="I49">
+        <v>42</v>
+      </c>
+      <c r="J49">
+        <v>8001</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>125871031</v>
+      </c>
+      <c r="E50">
+        <v>1211</v>
+      </c>
+      <c r="F50" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G50" s="2">
+        <v>45341</v>
+      </c>
+      <c r="I50">
+        <v>42</v>
+      </c>
+      <c r="J50">
+        <v>8001</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>125932613</v>
+      </c>
+      <c r="E51">
+        <v>1211</v>
+      </c>
+      <c r="F51" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G51" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I51">
+        <v>42</v>
+      </c>
+      <c r="J51">
+        <v>8001</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>125965709</v>
+      </c>
+      <c r="E52">
+        <v>1211</v>
+      </c>
+      <c r="F52" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G52" s="2">
+        <v>45344</v>
+      </c>
+      <c r="I52">
+        <v>42</v>
+      </c>
+      <c r="J52">
+        <v>8001</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>126030314</v>
+      </c>
+      <c r="E53">
+        <v>1211</v>
+      </c>
+      <c r="F53" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G53" s="2">
+        <v>45345</v>
+      </c>
+      <c r="I53">
+        <v>42</v>
+      </c>
+      <c r="J53">
+        <v>8001</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>126032436</v>
+      </c>
+      <c r="E54">
+        <v>1211</v>
+      </c>
+      <c r="F54" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G54" s="2">
+        <v>45344</v>
+      </c>
+      <c r="I54">
+        <v>42</v>
+      </c>
+      <c r="J54">
+        <v>8001</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>126048532</v>
+      </c>
+      <c r="E55">
+        <v>1211</v>
+      </c>
+      <c r="F55" s="2">
+        <v>45346</v>
+      </c>
+      <c r="G55" s="2">
+        <v>45346</v>
+      </c>
+      <c r="I55">
+        <v>42</v>
+      </c>
+      <c r="J55">
+        <v>8001</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>126173911</v>
+      </c>
+      <c r="E56">
+        <v>1211</v>
+      </c>
+      <c r="F56" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G56" s="2">
+        <v>45345</v>
+      </c>
+      <c r="I56">
+        <v>42</v>
+      </c>
+      <c r="J56">
+        <v>8001</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>126270618</v>
+      </c>
+      <c r="E57">
+        <v>1211</v>
+      </c>
+      <c r="F57" s="2">
+        <v>45346</v>
+      </c>
+      <c r="G57" s="2">
+        <v>45344</v>
+      </c>
+      <c r="I57">
+        <v>42</v>
+      </c>
+      <c r="J57">
+        <v>8001</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>126355790</v>
+      </c>
+      <c r="E58">
+        <v>1211</v>
+      </c>
+      <c r="F58" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G58" s="2">
+        <v>45345</v>
+      </c>
+      <c r="I58">
+        <v>42</v>
+      </c>
+      <c r="J58">
+        <v>8001</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>126559391</v>
+      </c>
+      <c r="E59">
+        <v>1211</v>
+      </c>
+      <c r="F59" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G59" s="2">
+        <v>45343</v>
+      </c>
+      <c r="I59">
+        <v>42</v>
+      </c>
+      <c r="J59">
+        <v>8001</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>126564024</v>
+      </c>
+      <c r="E60">
+        <v>1211</v>
+      </c>
+      <c r="F60" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G60" s="2">
+        <v>45345</v>
+      </c>
+      <c r="I60">
+        <v>42</v>
+      </c>
+      <c r="J60">
+        <v>8001</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>126589487</v>
+      </c>
+      <c r="E61">
+        <v>1211</v>
+      </c>
+      <c r="F61" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G61" s="2">
+        <v>45345</v>
+      </c>
+      <c r="I61">
+        <v>42</v>
+      </c>
+      <c r="J61">
+        <v>8001</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>126708996</v>
+      </c>
+      <c r="E62">
+        <v>1211</v>
+      </c>
+      <c r="F62" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G62" s="2">
+        <v>45342</v>
+      </c>
+      <c r="I62">
+        <v>42</v>
+      </c>
+      <c r="J62">
+        <v>8001</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>110074933</v>
+      </c>
+      <c r="E63">
+        <v>1211</v>
+      </c>
+      <c r="F63" s="2">
+        <v>43453</v>
+      </c>
+      <c r="G63" s="2">
+        <v>43441</v>
+      </c>
+      <c r="I63">
+        <v>42</v>
+      </c>
+      <c r="J63">
+        <v>8023</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>123058958</v>
+      </c>
+      <c r="E64">
+        <v>1211</v>
+      </c>
+      <c r="F64" s="2">
+        <v>44995</v>
+      </c>
+      <c r="G64" s="2">
+        <v>44993</v>
+      </c>
+      <c r="I64">
+        <v>42</v>
+      </c>
+      <c r="J64">
+        <v>8001</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>126697180</v>
+      </c>
+      <c r="E65">
+        <v>1211</v>
+      </c>
+      <c r="F65" s="2">
+        <v>45334</v>
+      </c>
+      <c r="G65" s="2">
+        <v>45331</v>
+      </c>
+      <c r="I65">
+        <v>42</v>
+      </c>
+      <c r="J65">
+        <v>8001</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>126695348</v>
+      </c>
+      <c r="E66">
+        <v>601</v>
+      </c>
+      <c r="F66" s="2">
+        <v>45344</v>
+      </c>
+      <c r="G66" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I66">
+        <v>42</v>
+      </c>
+      <c r="J66">
+        <v>8013</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>126711296</v>
+      </c>
+      <c r="E67">
+        <v>601</v>
+      </c>
+      <c r="F67" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G67" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I67">
+        <v>42</v>
+      </c>
+      <c r="J67">
+        <v>8001</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>126711646</v>
+      </c>
+      <c r="E68">
+        <v>601</v>
+      </c>
+      <c r="F68" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G68" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I68">
+        <v>42</v>
+      </c>
+      <c r="J68">
+        <v>8001</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>126711851</v>
+      </c>
+      <c r="E69">
+        <v>601</v>
+      </c>
+      <c r="F69" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G69" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I69">
+        <v>42</v>
+      </c>
+      <c r="J69">
+        <v>8001</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>126711987</v>
+      </c>
+      <c r="E70">
+        <v>601</v>
+      </c>
+      <c r="F70" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G70" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I70">
+        <v>42</v>
+      </c>
+      <c r="J70">
+        <v>8001</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>126712132</v>
+      </c>
+      <c r="E71">
+        <v>601</v>
+      </c>
+      <c r="F71" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G71" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I71">
+        <v>42</v>
+      </c>
+      <c r="J71">
+        <v>8001</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>126712467</v>
+      </c>
+      <c r="E72">
+        <v>601</v>
+      </c>
+      <c r="F72" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G72" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I72">
+        <v>42</v>
+      </c>
+      <c r="J72">
+        <v>8001</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>126712579</v>
+      </c>
+      <c r="E73">
+        <v>601</v>
+      </c>
+      <c r="F73" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G73" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I73">
+        <v>42</v>
+      </c>
+      <c r="J73">
+        <v>8004</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>126712672</v>
+      </c>
+      <c r="E74">
+        <v>601</v>
+      </c>
+      <c r="F74" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G74" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I74">
+        <v>42</v>
+      </c>
+      <c r="J74">
+        <v>8001</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>126716557</v>
+      </c>
+      <c r="E75">
+        <v>601</v>
+      </c>
+      <c r="F75" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G75" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I75">
+        <v>42</v>
+      </c>
+      <c r="J75">
+        <v>8004</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>126716869</v>
+      </c>
+      <c r="E76">
+        <v>601</v>
+      </c>
+      <c r="F76" s="2">
+        <v>45343</v>
+      </c>
+      <c r="G76" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I76">
+        <v>42</v>
+      </c>
+      <c r="J76">
+        <v>8013</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>126716898</v>
+      </c>
+      <c r="E77">
+        <v>601</v>
+      </c>
+      <c r="F77" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G77" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I77">
+        <v>42</v>
+      </c>
+      <c r="J77">
+        <v>8004</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>126717515</v>
+      </c>
+      <c r="E78">
+        <v>601</v>
+      </c>
+      <c r="F78" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G78" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I78">
+        <v>42</v>
+      </c>
+      <c r="J78">
+        <v>8004</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>126717789</v>
+      </c>
+      <c r="E79">
+        <v>601</v>
+      </c>
+      <c r="F79" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G79" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I79">
+        <v>42</v>
+      </c>
+      <c r="J79">
+        <v>8004</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>126718311</v>
+      </c>
+      <c r="E80">
+        <v>601</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I80">
+        <v>42</v>
+      </c>
+      <c r="J80">
+        <v>8004</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>126722395</v>
+      </c>
+      <c r="E81">
+        <v>601</v>
+      </c>
+      <c r="F81" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G81" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I81">
+        <v>42</v>
+      </c>
+      <c r="J81">
+        <v>8013</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>126723481</v>
+      </c>
+      <c r="E82">
+        <v>601</v>
+      </c>
+      <c r="F82" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G82" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I82">
+        <v>42</v>
+      </c>
+      <c r="J82">
+        <v>8013</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>126724150</v>
+      </c>
+      <c r="E83">
+        <v>601</v>
+      </c>
+      <c r="F83" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G83" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I83">
+        <v>42</v>
+      </c>
+      <c r="J83">
+        <v>8004</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>126724317</v>
+      </c>
+      <c r="E84">
+        <v>601</v>
+      </c>
+      <c r="F84" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G84" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I84">
+        <v>42</v>
+      </c>
+      <c r="J84">
+        <v>8013</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>126724408</v>
+      </c>
+      <c r="E85">
+        <v>601</v>
+      </c>
+      <c r="F85" s="2">
+        <v>45339</v>
+      </c>
+      <c r="G85" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I85">
+        <v>42</v>
+      </c>
+      <c r="J85">
+        <v>8013</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>126725845</v>
+      </c>
+      <c r="E86">
+        <v>601</v>
+      </c>
+      <c r="F86" s="2">
+        <v>45343</v>
+      </c>
+      <c r="G86" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I86">
+        <v>42</v>
+      </c>
+      <c r="J86">
+        <v>8013</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>126727475</v>
+      </c>
+      <c r="E87">
+        <v>601</v>
+      </c>
+      <c r="F87" s="2">
+        <v>45343</v>
+      </c>
+      <c r="G87" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I87">
+        <v>42</v>
+      </c>
+      <c r="J87">
+        <v>8013</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>126728229</v>
+      </c>
+      <c r="E88">
+        <v>601</v>
+      </c>
+      <c r="F88" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G88" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I88">
+        <v>42</v>
+      </c>
+      <c r="J88">
+        <v>8004</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>126728767</v>
+      </c>
+      <c r="E89">
+        <v>601</v>
+      </c>
+      <c r="F89" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G89" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I89">
+        <v>42</v>
+      </c>
+      <c r="J89">
+        <v>8004</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>126729421</v>
+      </c>
+      <c r="E90">
+        <v>601</v>
+      </c>
+      <c r="F90" s="2">
+        <v>45343</v>
+      </c>
+      <c r="G90" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I90">
+        <v>42</v>
+      </c>
+      <c r="J90">
+        <v>8013</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>126730182</v>
+      </c>
+      <c r="E91">
+        <v>601</v>
+      </c>
+      <c r="F91" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G91" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I91">
+        <v>42</v>
+      </c>
+      <c r="J91">
+        <v>8004</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>126734101</v>
+      </c>
+      <c r="E92">
+        <v>601</v>
+      </c>
+      <c r="F92" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G92" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I92">
+        <v>42</v>
+      </c>
+      <c r="J92">
+        <v>8004</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>126734273</v>
+      </c>
+      <c r="E93">
+        <v>601</v>
+      </c>
+      <c r="F93" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G93" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I93">
+        <v>42</v>
+      </c>
+      <c r="J93">
+        <v>8004</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>126734892</v>
+      </c>
+      <c r="E94">
+        <v>601</v>
+      </c>
+      <c r="F94" s="2">
+        <v>45342</v>
+      </c>
+      <c r="G94" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I94">
+        <v>42</v>
+      </c>
+      <c r="J94">
+        <v>8013</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>126735153</v>
+      </c>
+      <c r="E95">
+        <v>601</v>
+      </c>
+      <c r="F95" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G95" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I95">
+        <v>42</v>
+      </c>
+      <c r="J95">
+        <v>1118</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>126735286</v>
+      </c>
+      <c r="E96">
+        <v>601</v>
+      </c>
+      <c r="F96" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G96" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I96">
+        <v>42</v>
+      </c>
+      <c r="J96">
+        <v>8004</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>126737061</v>
+      </c>
+      <c r="E97">
+        <v>601</v>
+      </c>
+      <c r="F97" s="2">
+        <v>45343</v>
+      </c>
+      <c r="G97" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I97">
+        <v>42</v>
+      </c>
+      <c r="J97">
+        <v>8013</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>126737290</v>
+      </c>
+      <c r="E98">
+        <v>601</v>
+      </c>
+      <c r="F98" s="2">
+        <v>45343</v>
+      </c>
+      <c r="G98" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I98">
+        <v>42</v>
+      </c>
+      <c r="J98">
+        <v>8013</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>126737366</v>
+      </c>
+      <c r="E99">
+        <v>601</v>
+      </c>
+      <c r="F99" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G99" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I99">
+        <v>42</v>
+      </c>
+      <c r="J99">
+        <v>8004</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>126737930</v>
+      </c>
+      <c r="E100">
+        <v>601</v>
+      </c>
+      <c r="F100" s="2">
+        <v>45345</v>
+      </c>
+      <c r="G100" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I100">
+        <v>42</v>
+      </c>
+      <c r="J100">
+        <v>8013</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>126738573</v>
+      </c>
+      <c r="E101">
+        <v>601</v>
+      </c>
+      <c r="F101" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G101" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I101">
+        <v>42</v>
+      </c>
+      <c r="J101">
+        <v>8004</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>126741164</v>
+      </c>
+      <c r="E102">
+        <v>601</v>
+      </c>
+      <c r="F102" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G102" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I102">
+        <v>42</v>
+      </c>
+      <c r="J102">
+        <v>8004</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>126742492</v>
+      </c>
+      <c r="E103">
+        <v>601</v>
+      </c>
+      <c r="F103" s="2">
+        <v>45346</v>
+      </c>
+      <c r="G103" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I103">
+        <v>42</v>
+      </c>
+      <c r="J103">
+        <v>8013</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>126743974</v>
+      </c>
+      <c r="E104">
+        <v>601</v>
+      </c>
+      <c r="F104" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G104" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I104">
+        <v>42</v>
+      </c>
+      <c r="J104">
+        <v>8004</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>126745128</v>
+      </c>
+      <c r="E105">
+        <v>601</v>
+      </c>
+      <c r="F105" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G105" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I105">
+        <v>42</v>
+      </c>
+      <c r="J105">
+        <v>8004</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>126745183</v>
+      </c>
+      <c r="E106">
+        <v>601</v>
+      </c>
+      <c r="F106" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G106" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I106">
+        <v>42</v>
+      </c>
+      <c r="J106">
+        <v>8004</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>126745400</v>
+      </c>
+      <c r="E107">
+        <v>601</v>
+      </c>
+      <c r="F107" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G107" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I107">
+        <v>42</v>
+      </c>
+      <c r="J107">
+        <v>8004</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>126745423</v>
+      </c>
+      <c r="E108">
+        <v>601</v>
+      </c>
+      <c r="F108" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G108" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I108">
+        <v>42</v>
+      </c>
+      <c r="J108">
+        <v>8004</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>126745991</v>
+      </c>
+      <c r="E109">
+        <v>601</v>
+      </c>
+      <c r="F109" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G109" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I109">
+        <v>42</v>
+      </c>
+      <c r="J109">
+        <v>8004</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>126747679</v>
+      </c>
+      <c r="E110">
+        <v>601</v>
+      </c>
+      <c r="F110" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G110" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I110">
+        <v>42</v>
+      </c>
+      <c r="J110">
+        <v>8004</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>126748249</v>
+      </c>
+      <c r="E111">
+        <v>601</v>
+      </c>
+      <c r="F111" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G111" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I111">
+        <v>42</v>
+      </c>
+      <c r="J111">
+        <v>8004</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>126748558</v>
+      </c>
+      <c r="E112">
+        <v>601</v>
+      </c>
+      <c r="F112" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G112" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I112">
+        <v>42</v>
+      </c>
+      <c r="J112">
+        <v>8004</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>126749388</v>
+      </c>
+      <c r="E113">
+        <v>601</v>
+      </c>
+      <c r="F113" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G113" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I113">
+        <v>42</v>
+      </c>
+      <c r="J113">
+        <v>8013</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>126749809</v>
+      </c>
+      <c r="E114">
+        <v>601</v>
+      </c>
+      <c r="F114" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G114" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I114">
+        <v>42</v>
+      </c>
+      <c r="J114">
+        <v>8004</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>126750157</v>
+      </c>
+      <c r="E115">
+        <v>601</v>
+      </c>
+      <c r="F115" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G115" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I115">
+        <v>42</v>
+      </c>
+      <c r="J115">
+        <v>8004</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>126750746</v>
+      </c>
+      <c r="E116">
+        <v>601</v>
+      </c>
+      <c r="F116" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G116" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I116">
+        <v>42</v>
+      </c>
+      <c r="J116">
+        <v>8004</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>126750793</v>
+      </c>
+      <c r="E117">
+        <v>601</v>
+      </c>
+      <c r="F117" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G117" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I117">
+        <v>42</v>
+      </c>
+      <c r="J117">
+        <v>8004</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>126750967</v>
+      </c>
+      <c r="E118">
+        <v>601</v>
+      </c>
+      <c r="F118" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G118" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I118">
+        <v>42</v>
+      </c>
+      <c r="J118">
+        <v>8004</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>126751878</v>
+      </c>
+      <c r="E119">
+        <v>601</v>
+      </c>
+      <c r="F119" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G119" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I119">
+        <v>42</v>
+      </c>
+      <c r="J119">
+        <v>8004</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>126752839</v>
+      </c>
+      <c r="E120">
+        <v>601</v>
+      </c>
+      <c r="F120" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G120" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I120">
+        <v>42</v>
+      </c>
+      <c r="J120">
+        <v>8004</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>126753255</v>
+      </c>
+      <c r="E121">
+        <v>601</v>
+      </c>
+      <c r="F121" s="2">
+        <v>45346</v>
+      </c>
+      <c r="G121" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I121">
+        <v>42</v>
+      </c>
+      <c r="J121">
+        <v>8013</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>126755187</v>
+      </c>
+      <c r="E122">
+        <v>601</v>
+      </c>
+      <c r="F122" s="2">
+        <v>45343</v>
+      </c>
+      <c r="G122" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I122">
+        <v>42</v>
+      </c>
+      <c r="J122">
+        <v>8013</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>126748249</v>
+      </c>
+      <c r="E123">
+        <v>601</v>
+      </c>
+      <c r="F123" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G123" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I123">
+        <v>42</v>
+      </c>
+      <c r="J123">
+        <v>8004</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+      <c r="Q123">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>126714759</v>
+      </c>
+      <c r="E124">
+        <v>601</v>
+      </c>
+      <c r="F124" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G124" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I124">
+        <v>42</v>
+      </c>
+      <c r="J124">
+        <v>8004</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>126715244</v>
+      </c>
+      <c r="E125">
+        <v>601</v>
+      </c>
+      <c r="F125" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G125" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I125">
+        <v>42</v>
+      </c>
+      <c r="J125">
+        <v>8004</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="Q125">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>126715447</v>
+      </c>
+      <c r="E126">
+        <v>601</v>
+      </c>
+      <c r="F126" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G126" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I126">
+        <v>42</v>
+      </c>
+      <c r="J126">
+        <v>8004</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>126718505</v>
+      </c>
+      <c r="E127">
+        <v>601</v>
+      </c>
+      <c r="F127" s="2">
+        <v>45336</v>
+      </c>
+      <c r="G127" s="2">
+        <v>45336</v>
+      </c>
+      <c r="I127">
+        <v>42</v>
+      </c>
+      <c r="J127">
+        <v>8004</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>126722465</v>
+      </c>
+      <c r="E128">
+        <v>601</v>
+      </c>
+      <c r="F128" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G128" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I128">
+        <v>42</v>
+      </c>
+      <c r="J128">
+        <v>8004</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>126724276</v>
+      </c>
+      <c r="E129">
+        <v>601</v>
+      </c>
+      <c r="F129" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G129" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I129">
+        <v>42</v>
+      </c>
+      <c r="J129">
+        <v>8004</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+      <c r="Q129">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>126724447</v>
+      </c>
+      <c r="E130">
+        <v>601</v>
+      </c>
+      <c r="F130" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G130" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I130">
+        <v>42</v>
+      </c>
+      <c r="J130">
+        <v>8004</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>126724814</v>
+      </c>
+      <c r="E131">
+        <v>601</v>
+      </c>
+      <c r="F131" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G131" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I131">
+        <v>42</v>
+      </c>
+      <c r="J131">
+        <v>8004</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>126724886</v>
+      </c>
+      <c r="E132">
+        <v>601</v>
+      </c>
+      <c r="F132" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G132" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I132">
+        <v>42</v>
+      </c>
+      <c r="J132">
+        <v>8004</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>126726589</v>
+      </c>
+      <c r="E133">
+        <v>601</v>
+      </c>
+      <c r="F133" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G133" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I133">
+        <v>42</v>
+      </c>
+      <c r="J133">
+        <v>8004</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>126729783</v>
+      </c>
+      <c r="E134">
+        <v>601</v>
+      </c>
+      <c r="F134" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G134" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I134">
+        <v>42</v>
+      </c>
+      <c r="J134">
+        <v>8004</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>126731113</v>
+      </c>
+      <c r="E135">
+        <v>601</v>
+      </c>
+      <c r="F135" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G135" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I135">
+        <v>42</v>
+      </c>
+      <c r="J135">
+        <v>1117</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>126733738</v>
+      </c>
+      <c r="E136">
+        <v>601</v>
+      </c>
+      <c r="F136" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G136" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I136">
+        <v>42</v>
+      </c>
+      <c r="J136">
+        <v>8004</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>126734025</v>
+      </c>
+      <c r="E137">
+        <v>601</v>
+      </c>
+      <c r="F137" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G137" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I137">
+        <v>42</v>
+      </c>
+      <c r="J137">
+        <v>8004</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>126735201</v>
+      </c>
+      <c r="E138">
+        <v>601</v>
+      </c>
+      <c r="F138" s="2">
+        <v>45337</v>
+      </c>
+      <c r="G138" s="2">
+        <v>45337</v>
+      </c>
+      <c r="I138">
+        <v>42</v>
+      </c>
+      <c r="J138">
+        <v>1118</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>126748756</v>
+      </c>
+      <c r="E139">
+        <v>601</v>
+      </c>
+      <c r="F139" s="2">
+        <v>45338</v>
+      </c>
+      <c r="G139" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I139">
+        <v>42</v>
+      </c>
+      <c r="J139">
+        <v>8004</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
         <v>61</v>
       </c>
     </row>
@@ -2004,12 +5842,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{249CD703-0AE7-46A1-BA6D-A19361B97C73}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:Q198"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -2062,7 +5900,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>125887260</v>
       </c>
@@ -2100,7 +5938,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>125890823</v>
       </c>
@@ -2138,7 +5976,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>125891086</v>
       </c>
@@ -2176,7 +6014,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>125892224</v>
       </c>
@@ -2214,7 +6052,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>125892709</v>
       </c>
@@ -2252,7 +6090,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>125892901</v>
       </c>
@@ -2290,7 +6128,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>125892906</v>
       </c>
@@ -2328,7 +6166,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>125893564</v>
       </c>
@@ -2366,7 +6204,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>125893722</v>
       </c>
@@ -2404,7 +6242,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>125895193</v>
       </c>
@@ -2442,7 +6280,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>125896177</v>
       </c>
@@ -2480,7 +6318,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>125898007</v>
       </c>
@@ -2518,7 +6356,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>125900254</v>
       </c>
@@ -2556,7 +6394,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>125901787</v>
       </c>
@@ -2594,7 +6432,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>125901795</v>
       </c>
@@ -2632,7 +6470,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>125903262</v>
       </c>
@@ -2670,7 +6508,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>125904221</v>
       </c>
@@ -2708,7 +6546,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>125904238</v>
       </c>
@@ -2746,7 +6584,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>125907420</v>
       </c>
@@ -2784,7 +6622,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>125907797</v>
       </c>
@@ -2822,7 +6660,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>125908056</v>
       </c>
@@ -2860,7 +6698,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>125908177</v>
       </c>
@@ -2898,7 +6736,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>125908231</v>
       </c>
@@ -2936,7 +6774,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>125908843</v>
       </c>
@@ -2974,7 +6812,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>125909142</v>
       </c>
@@ -3012,7 +6850,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>125909933</v>
       </c>
@@ -3050,7 +6888,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>125910114</v>
       </c>
@@ -3088,7 +6926,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>125910400</v>
       </c>
@@ -3126,7 +6964,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>125910838</v>
       </c>
@@ -3164,7 +7002,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>125912176</v>
       </c>
@@ -3202,7 +7040,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>125912843</v>
       </c>
@@ -3240,7 +7078,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>125913133</v>
       </c>
@@ -3278,7 +7116,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>125913427</v>
       </c>
@@ -3316,7 +7154,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>125914356</v>
       </c>
@@ -3354,7 +7192,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>125914668</v>
       </c>
@@ -3392,7 +7230,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>125914978</v>
       </c>
@@ -3430,7 +7268,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>125918666</v>
       </c>
@@ -3468,7 +7306,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>125920065</v>
       </c>
@@ -3506,7 +7344,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>125924508</v>
       </c>
@@ -3544,7 +7382,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>125926112</v>
       </c>
@@ -3582,7 +7420,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>125927235</v>
       </c>
@@ -3620,7 +7458,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>125927477</v>
       </c>
@@ -3658,7 +7496,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>125927712</v>
       </c>
@@ -3696,7 +7534,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>125927811</v>
       </c>
@@ -3734,7 +7572,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>125928500</v>
       </c>
@@ -3772,7 +7610,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>125928781</v>
       </c>
@@ -3810,7 +7648,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>125928935</v>
       </c>
@@ -3848,7 +7686,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>125929845</v>
       </c>
@@ -3886,7 +7724,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>125930432</v>
       </c>
@@ -3924,7 +7762,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>125931903</v>
       </c>
@@ -3962,7 +7800,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>125932521</v>
       </c>
@@ -4000,7 +7838,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>125932669</v>
       </c>
@@ -4038,7 +7876,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>125933582</v>
       </c>
@@ -4076,7 +7914,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>125933608</v>
       </c>
@@ -4114,7 +7952,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>125935767</v>
       </c>
@@ -4152,7 +7990,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>125938612</v>
       </c>
@@ -4190,7 +8028,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>125944749</v>
       </c>
@@ -4228,7 +8066,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>125945240</v>
       </c>
@@ -4266,7 +8104,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>125949456</v>
       </c>
@@ -4304,7 +8142,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>125958349</v>
       </c>
@@ -4342,7 +8180,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>125958503</v>
       </c>
@@ -4380,7 +8218,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>125960344</v>
       </c>
@@ -4418,7 +8256,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>125962131</v>
       </c>
@@ -4456,7 +8294,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>125965767</v>
       </c>
@@ -4494,7 +8332,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>125965877</v>
       </c>
@@ -4532,7 +8370,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>125969356</v>
       </c>
@@ -4570,7 +8408,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>125971901</v>
       </c>
@@ -4608,7 +8446,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>125976084</v>
       </c>
@@ -4646,7 +8484,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>125976278</v>
       </c>
@@ -4684,7 +8522,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>125977146</v>
       </c>
@@ -4722,7 +8560,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>125977504</v>
       </c>
@@ -4760,7 +8598,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>125981162</v>
       </c>
@@ -4798,7 +8636,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>125983181</v>
       </c>
@@ -4836,7 +8674,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>125983593</v>
       </c>
@@ -4874,7 +8712,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>125984782</v>
       </c>
@@ -4912,7 +8750,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>125992174</v>
       </c>
@@ -4950,7 +8788,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>125992452</v>
       </c>
@@ -4988,7 +8826,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>125997050</v>
       </c>
@@ -5026,7 +8864,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>126009389</v>
       </c>
@@ -5064,7 +8902,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>126012544</v>
       </c>
@@ -5102,7 +8940,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>126013965</v>
       </c>
@@ -5140,7 +8978,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>126015225</v>
       </c>
@@ -5178,7 +9016,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>126015257</v>
       </c>
@@ -5216,7 +9054,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>126020235</v>
       </c>
@@ -5254,7 +9092,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>126028210</v>
       </c>
@@ -5292,7 +9130,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>126028956</v>
       </c>
@@ -5330,7 +9168,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>126029328</v>
       </c>
@@ -5368,7 +9206,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>126029650</v>
       </c>
@@ -5406,7 +9244,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>126029868</v>
       </c>
@@ -5444,7 +9282,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>126033233</v>
       </c>
@@ -5482,7 +9320,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>126036666</v>
       </c>
@@ -5520,7 +9358,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>126037292</v>
       </c>
@@ -5558,7 +9396,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>126040785</v>
       </c>
@@ -5596,7 +9434,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>126040979</v>
       </c>
@@ -5634,7 +9472,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>126041187</v>
       </c>
@@ -5672,7 +9510,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>126043144</v>
       </c>
@@ -5710,7 +9548,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>126045060</v>
       </c>
@@ -5748,7 +9586,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>126045520</v>
       </c>
@@ -5786,7 +9624,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>126049650</v>
       </c>
@@ -5824,7 +9662,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>126051286</v>
       </c>
@@ -5862,7 +9700,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>126052567</v>
       </c>
@@ -5900,7 +9738,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>126057040</v>
       </c>
@@ -5938,7 +9776,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>126057529</v>
       </c>
@@ -5976,7 +9814,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>126057835</v>
       </c>
@@ -6014,7 +9852,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>126058412</v>
       </c>
@@ -6052,7 +9890,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>126063955</v>
       </c>
@@ -6090,7 +9928,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>126064498</v>
       </c>
@@ -6128,7 +9966,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>126065211</v>
       </c>
@@ -6166,7 +10004,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>126074608</v>
       </c>
@@ -6204,7 +10042,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>126078394</v>
       </c>
@@ -6242,7 +10080,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>126080342</v>
       </c>
@@ -6280,7 +10118,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>126082448</v>
       </c>
@@ -6318,7 +10156,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>126082622</v>
       </c>
@@ -6356,7 +10194,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>126084723</v>
       </c>
@@ -6394,7 +10232,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>126086747</v>
       </c>
@@ -6432,7 +10270,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>126088025</v>
       </c>
@@ -6470,7 +10308,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>126088302</v>
       </c>
@@ -6508,7 +10346,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>126088413</v>
       </c>
@@ -6546,7 +10384,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>126088528</v>
       </c>
@@ -6584,7 +10422,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>126089277</v>
       </c>
@@ -6622,7 +10460,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>126089435</v>
       </c>
@@ -6660,7 +10498,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>126090634</v>
       </c>
@@ -6698,7 +10536,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>126093282</v>
       </c>
@@ -6736,7 +10574,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>126093649</v>
       </c>
@@ -6774,7 +10612,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>126097132</v>
       </c>
@@ -6812,7 +10650,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126098812</v>
       </c>
@@ -6850,7 +10688,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>126099189</v>
       </c>
@@ -6888,7 +10726,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>126099880</v>
       </c>
@@ -6926,7 +10764,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>126100047</v>
       </c>
@@ -6964,7 +10802,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>126101516</v>
       </c>
@@ -7002,7 +10840,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>126102394</v>
       </c>
@@ -7040,7 +10878,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>126104952</v>
       </c>
@@ -7078,7 +10916,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>126106789</v>
       </c>
@@ -7116,7 +10954,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>126111482</v>
       </c>
@@ -7154,7 +10992,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>126111872</v>
       </c>
@@ -7192,7 +11030,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>126119068</v>
       </c>
@@ -7230,7 +11068,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>126120069</v>
       </c>
@@ -7268,7 +11106,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>126120915</v>
       </c>
@@ -7306,7 +11144,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>126120976</v>
       </c>
@@ -7344,7 +11182,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>126122910</v>
       </c>
@@ -7382,7 +11220,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>126130699</v>
       </c>
@@ -7420,7 +11258,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>126131117</v>
       </c>
@@ -7458,7 +11296,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>126136404</v>
       </c>
@@ -7496,7 +11334,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>126140055</v>
       </c>
@@ -7534,7 +11372,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>126147040</v>
       </c>
@@ -7572,7 +11410,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>126155748</v>
       </c>
@@ -7610,7 +11448,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>126155838</v>
       </c>
@@ -7648,7 +11486,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>126157906</v>
       </c>
@@ -7686,7 +11524,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>126158151</v>
       </c>
@@ -7724,7 +11562,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>126162518</v>
       </c>
@@ -7762,7 +11600,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>126164369</v>
       </c>
@@ -7800,7 +11638,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>126164882</v>
       </c>
@@ -7838,7 +11676,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>126165476</v>
       </c>
@@ -7876,7 +11714,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>126165996</v>
       </c>
@@ -7914,7 +11752,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>126167070</v>
       </c>
@@ -7952,7 +11790,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>126168025</v>
       </c>
@@ -7990,7 +11828,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>126168249</v>
       </c>
@@ -8028,7 +11866,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>126173180</v>
       </c>
@@ -8066,7 +11904,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>126174316</v>
       </c>
@@ -8104,7 +11942,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>126174669</v>
       </c>
@@ -8142,7 +11980,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>126176463</v>
       </c>
@@ -8180,7 +12018,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>126176884</v>
       </c>
@@ -8218,7 +12056,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>126185047</v>
       </c>
@@ -8256,7 +12094,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>126185760</v>
       </c>
@@ -8294,7 +12132,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>126187183</v>
       </c>
@@ -8332,7 +12170,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>126187745</v>
       </c>
@@ -8370,7 +12208,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>126192174</v>
       </c>
@@ -8408,7 +12246,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>126192469</v>
       </c>
@@ -8446,7 +12284,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>126192814</v>
       </c>
@@ -8484,7 +12322,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>126193665</v>
       </c>
@@ -8522,7 +12360,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>126193855</v>
       </c>
@@ -8560,7 +12398,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>126194373</v>
       </c>
@@ -8598,7 +12436,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>126195588</v>
       </c>
@@ -8636,7 +12474,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>126197992</v>
       </c>
@@ -8674,7 +12512,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>126198450</v>
       </c>
@@ -8712,7 +12550,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>126198510</v>
       </c>
@@ -8750,7 +12588,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>126198929</v>
       </c>
@@ -8788,7 +12626,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>126201454</v>
       </c>
@@ -8826,7 +12664,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>126201460</v>
       </c>
@@ -8864,7 +12702,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>126201930</v>
       </c>
@@ -8902,7 +12740,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>126201991</v>
       </c>
@@ -8940,7 +12778,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>126212316</v>
       </c>
@@ -8978,7 +12816,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>126213617</v>
       </c>
@@ -9016,7 +12854,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>126216332</v>
       </c>
@@ -9054,7 +12892,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>126218950</v>
       </c>
@@ -9092,7 +12930,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>126230676</v>
       </c>
@@ -9130,7 +12968,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>126231536</v>
       </c>
@@ -9168,7 +13006,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>126237618</v>
       </c>
@@ -9206,7 +13044,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>126245598</v>
       </c>
@@ -9244,7 +13082,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>126265244</v>
       </c>
@@ -9282,7 +13120,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>126265499</v>
       </c>
@@ -9320,7 +13158,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>126266542</v>
       </c>
@@ -9358,7 +13196,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>126268776</v>
       </c>
@@ -9396,7 +13234,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>126280119</v>
       </c>
@@ -9434,7 +13272,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>126280477</v>
       </c>
@@ -9472,7 +13310,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>126281587</v>
       </c>
@@ -9510,7 +13348,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>126281992</v>
       </c>
@@ -9579,31 +13417,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPasta_de_trabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\Brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09124B1D-4CC3-4970-82DC-8998F936C7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C7131A-D8FF-49EC-8EE8-9CA67EECDAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiel" sheetId="28" r:id="rId1"/>
@@ -507,18 +507,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q139"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q65"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
@@ -526,11 +526,11 @@
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,18 +583,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>126816802</v>
+        <v>126264870</v>
       </c>
       <c r="E2">
         <v>2013</v>
       </c>
       <c r="F2" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G2" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="I2">
         <v>42</v>
@@ -621,12 +621,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>126816976</v>
+        <v>126821618</v>
       </c>
       <c r="E3">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F3" s="2">
         <v>45345</v>
@@ -638,7 +638,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -659,18 +659,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>126774800</v>
+        <v>126823257</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45342</v>
+        <v>45345</v>
       </c>
       <c r="G4" s="2">
-        <v>45342</v>
+        <v>45345</v>
       </c>
       <c r="I4">
         <v>42</v>
@@ -697,18 +697,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>126775879</v>
+        <v>126824705</v>
       </c>
       <c r="E5">
         <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45342</v>
+        <v>45345</v>
       </c>
       <c r="G5" s="2">
-        <v>45342</v>
+        <v>45345</v>
       </c>
       <c r="I5">
         <v>42</v>
@@ -735,18 +735,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>126783644</v>
+        <v>126825209</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45342</v>
+        <v>45345</v>
       </c>
       <c r="G6" s="2">
-        <v>45342</v>
+        <v>45345</v>
       </c>
       <c r="I6">
         <v>42</v>
@@ -773,18 +773,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>126787923</v>
+        <v>126827663</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45342</v>
+        <v>45345</v>
       </c>
       <c r="G7" s="2">
-        <v>45342</v>
+        <v>45345</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -811,18 +811,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>126792177</v>
+        <v>126828874</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45343</v>
+        <v>45346</v>
       </c>
       <c r="G8" s="2">
-        <v>45343</v>
+        <v>45345</v>
       </c>
       <c r="I8">
         <v>42</v>
@@ -849,18 +849,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>126794289</v>
+        <v>126832348</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45343</v>
+        <v>45345</v>
       </c>
       <c r="G9" s="2">
-        <v>45343</v>
+        <v>45345</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -887,24 +887,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>126817353</v>
+        <v>123328724</v>
       </c>
       <c r="E10">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G10" s="2">
-        <v>45344</v>
+        <v>45348</v>
       </c>
       <c r="I10">
         <v>42</v>
       </c>
       <c r="J10">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -925,18 +925,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>123321677</v>
+        <v>123405313</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45346</v>
+        <v>45348</v>
       </c>
       <c r="G11" s="2">
-        <v>45346</v>
+        <v>45343</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -963,15 +963,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>123355161</v>
+        <v>123597175</v>
       </c>
       <c r="E12">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G12" s="2">
         <v>45345</v>
@@ -1001,18 +1001,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>123378206</v>
+        <v>124059471</v>
       </c>
       <c r="E13">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F13" s="2">
-        <v>45346</v>
+        <v>45348</v>
       </c>
       <c r="G13" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1039,18 +1039,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>123449409</v>
+        <v>124108450</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G14" s="2">
-        <v>45344</v>
+        <v>45348</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1077,18 +1077,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>123546216</v>
+        <v>124160756</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G15" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1115,15 +1115,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>123573203</v>
+        <v>124340728</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G16" s="2">
         <v>45345</v>
@@ -1153,18 +1153,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>123598238</v>
+        <v>124388720</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G17" s="2">
-        <v>45343</v>
+        <v>45342</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1191,18 +1191,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>123600663</v>
+        <v>124687489</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G18" s="2">
-        <v>45345</v>
+        <v>45342</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1229,18 +1229,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>123606573</v>
+        <v>125050425</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
+        <v>45348</v>
+      </c>
+      <c r="G19" s="2">
         <v>45345</v>
-      </c>
-      <c r="G19" s="2">
-        <v>45343</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1267,15 +1267,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>123681613</v>
+        <v>125286139</v>
       </c>
       <c r="E20">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G20" s="2">
         <v>45345</v>
@@ -1305,18 +1305,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>123728200</v>
+        <v>125325985</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G21" s="2">
-        <v>45345</v>
+        <v>45344</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1343,18 +1343,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>123849780</v>
+        <v>125396915</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
+        <v>45348</v>
+      </c>
+      <c r="G22" s="2">
         <v>45346</v>
-      </c>
-      <c r="G22" s="2">
-        <v>45344</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1381,18 +1381,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>123854747</v>
+        <v>126082977</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G23" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1419,9 +1419,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>123864928</v>
+        <v>126173911</v>
       </c>
       <c r="E24">
         <v>1211</v>
@@ -1430,7 +1430,7 @@
         <v>45345</v>
       </c>
       <c r="G24" s="2">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1457,15 +1457,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>123910727</v>
+        <v>126310303</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G25" s="2">
         <v>45345</v>
@@ -1495,24 +1495,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>123926279</v>
+        <v>110074933</v>
       </c>
       <c r="E26">
         <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45345</v>
+        <v>43453</v>
       </c>
       <c r="G26" s="2">
-        <v>45343</v>
+        <v>43441</v>
       </c>
       <c r="I26">
         <v>42</v>
       </c>
       <c r="J26">
-        <v>8001</v>
+        <v>8023</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1533,18 +1533,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>123956437</v>
+        <v>123058958</v>
       </c>
       <c r="E27">
         <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45345</v>
+        <v>44995</v>
       </c>
       <c r="G27" s="2">
-        <v>45344</v>
+        <v>44993</v>
       </c>
       <c r="I27">
         <v>42</v>
@@ -1571,18 +1571,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>124441091</v>
+        <v>126697180</v>
       </c>
       <c r="E28">
         <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45345</v>
+        <v>45334</v>
       </c>
       <c r="G28" s="2">
-        <v>45345</v>
+        <v>45331</v>
       </c>
       <c r="I28">
         <v>42</v>
@@ -1609,18 +1609,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>124499648</v>
+        <v>126784614</v>
       </c>
       <c r="E29">
         <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45345</v>
+        <v>45342</v>
       </c>
       <c r="G29" s="2">
-        <v>45345</v>
+        <v>45342</v>
       </c>
       <c r="I29">
         <v>42</v>
@@ -1647,24 +1647,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>124551135</v>
+        <v>126745400</v>
       </c>
       <c r="E30">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F30" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G30" s="2">
-        <v>45345</v>
+        <v>45338</v>
       </c>
       <c r="I30">
         <v>42</v>
       </c>
       <c r="J30">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1685,24 +1685,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>124601503</v>
+        <v>126745423</v>
       </c>
       <c r="E31">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F31" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G31" s="2">
-        <v>45345</v>
+        <v>45338</v>
       </c>
       <c r="I31">
         <v>42</v>
       </c>
       <c r="J31">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -1723,24 +1723,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>124610916</v>
+        <v>126745991</v>
       </c>
       <c r="E32">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F32" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G32" s="2">
-        <v>45345</v>
+        <v>45338</v>
       </c>
       <c r="I32">
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -1761,442 +1761,442 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>124667962</v>
+        <v>126747679</v>
       </c>
       <c r="E33">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F33" s="2">
-        <v>45346</v>
+        <v>45348</v>
       </c>
       <c r="G33" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I33">
+        <v>42</v>
+      </c>
+      <c r="J33">
+        <v>8013</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>126748558</v>
+      </c>
+      <c r="E34">
+        <v>601</v>
+      </c>
+      <c r="F34" s="2">
+        <v>45348</v>
+      </c>
+      <c r="G34" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I34">
+        <v>42</v>
+      </c>
+      <c r="J34">
+        <v>8013</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>126749809</v>
+      </c>
+      <c r="E35">
+        <v>601</v>
+      </c>
+      <c r="F35" s="2">
+        <v>45348</v>
+      </c>
+      <c r="G35" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I35">
+        <v>42</v>
+      </c>
+      <c r="J35">
+        <v>8013</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>126750157</v>
+      </c>
+      <c r="E36">
+        <v>601</v>
+      </c>
+      <c r="F36" s="2">
+        <v>45348</v>
+      </c>
+      <c r="G36" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I36">
+        <v>42</v>
+      </c>
+      <c r="J36">
+        <v>8013</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>126750746</v>
+      </c>
+      <c r="E37">
+        <v>601</v>
+      </c>
+      <c r="F37" s="2">
+        <v>45348</v>
+      </c>
+      <c r="G37" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I37">
+        <v>42</v>
+      </c>
+      <c r="J37">
+        <v>8013</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>126750793</v>
+      </c>
+      <c r="E38">
+        <v>601</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45348</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I38">
+        <v>42</v>
+      </c>
+      <c r="J38">
+        <v>8013</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>126750967</v>
+      </c>
+      <c r="E39">
+        <v>601</v>
+      </c>
+      <c r="F39" s="2">
+        <v>45348</v>
+      </c>
+      <c r="G39" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I39">
+        <v>42</v>
+      </c>
+      <c r="J39">
+        <v>8013</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>126751878</v>
+      </c>
+      <c r="E40">
+        <v>601</v>
+      </c>
+      <c r="F40" s="2">
+        <v>45348</v>
+      </c>
+      <c r="G40" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I40">
+        <v>42</v>
+      </c>
+      <c r="J40">
+        <v>8013</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>126752839</v>
+      </c>
+      <c r="E41">
+        <v>601</v>
+      </c>
+      <c r="F41" s="2">
+        <v>45348</v>
+      </c>
+      <c r="G41" s="2">
+        <v>45338</v>
+      </c>
+      <c r="I41">
+        <v>42</v>
+      </c>
+      <c r="J41">
+        <v>8013</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>126755778</v>
+      </c>
+      <c r="E42">
+        <v>601</v>
+      </c>
+      <c r="F42" s="2">
+        <v>45339</v>
+      </c>
+      <c r="G42" s="2">
+        <v>45339</v>
+      </c>
+      <c r="I42">
+        <v>42</v>
+      </c>
+      <c r="J42">
+        <v>8004</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>126756984</v>
+      </c>
+      <c r="E43">
+        <v>601</v>
+      </c>
+      <c r="F43" s="2">
         <v>45343</v>
       </c>
-      <c r="I33">
-        <v>42</v>
-      </c>
-      <c r="J33">
-        <v>8001</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>124692461</v>
-      </c>
-      <c r="E34">
-        <v>1211</v>
-      </c>
-      <c r="F34" s="2">
-        <v>45345</v>
-      </c>
-      <c r="G34" s="2">
-        <v>45345</v>
-      </c>
-      <c r="I34">
-        <v>42</v>
-      </c>
-      <c r="J34">
-        <v>8001</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>124781063</v>
-      </c>
-      <c r="E35">
-        <v>1211</v>
-      </c>
-      <c r="F35" s="2">
-        <v>45346</v>
-      </c>
-      <c r="G35" s="2">
+      <c r="G43" s="2">
+        <v>45339</v>
+      </c>
+      <c r="I43">
+        <v>42</v>
+      </c>
+      <c r="J43">
+        <v>8013</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>126757023</v>
+      </c>
+      <c r="E44">
+        <v>601</v>
+      </c>
+      <c r="F44" s="2">
         <v>45343</v>
       </c>
-      <c r="I35">
-        <v>42</v>
-      </c>
-      <c r="J35">
-        <v>8001</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>124815427</v>
-      </c>
-      <c r="E36">
-        <v>1211</v>
-      </c>
-      <c r="F36" s="2">
-        <v>45345</v>
-      </c>
-      <c r="G36" s="2">
-        <v>45345</v>
-      </c>
-      <c r="I36">
-        <v>42</v>
-      </c>
-      <c r="J36">
-        <v>8001</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>124884121</v>
-      </c>
-      <c r="E37">
-        <v>1212</v>
-      </c>
-      <c r="F37" s="2">
-        <v>45345</v>
-      </c>
-      <c r="G37" s="2">
-        <v>45345</v>
-      </c>
-      <c r="I37">
-        <v>42</v>
-      </c>
-      <c r="J37">
-        <v>8001</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>125012996</v>
-      </c>
-      <c r="E38">
-        <v>1211</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45345</v>
-      </c>
-      <c r="G38" s="2">
-        <v>45345</v>
-      </c>
-      <c r="I38">
-        <v>42</v>
-      </c>
-      <c r="J38">
-        <v>8001</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>125020215</v>
-      </c>
-      <c r="E39">
-        <v>1211</v>
-      </c>
-      <c r="F39" s="2">
-        <v>45345</v>
-      </c>
-      <c r="G39" s="2">
-        <v>45342</v>
-      </c>
-      <c r="I39">
-        <v>42</v>
-      </c>
-      <c r="J39">
-        <v>8001</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>125172235</v>
-      </c>
-      <c r="E40">
-        <v>1211</v>
-      </c>
-      <c r="F40" s="2">
-        <v>45346</v>
-      </c>
-      <c r="G40" s="2">
-        <v>45345</v>
-      </c>
-      <c r="I40">
-        <v>42</v>
-      </c>
-      <c r="J40">
-        <v>8001</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>125205170</v>
-      </c>
-      <c r="E41">
-        <v>1211</v>
-      </c>
-      <c r="F41" s="2">
-        <v>45345</v>
-      </c>
-      <c r="G41" s="2">
-        <v>45344</v>
-      </c>
-      <c r="I41">
-        <v>42</v>
-      </c>
-      <c r="J41">
-        <v>8001</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>125245636</v>
-      </c>
-      <c r="E42">
-        <v>1212</v>
-      </c>
-      <c r="F42" s="2">
-        <v>45345</v>
-      </c>
-      <c r="G42" s="2">
-        <v>45345</v>
-      </c>
-      <c r="I42">
-        <v>42</v>
-      </c>
-      <c r="J42">
-        <v>8001</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>125303672</v>
-      </c>
-      <c r="E43">
-        <v>1211</v>
-      </c>
-      <c r="F43" s="2">
-        <v>45345</v>
-      </c>
-      <c r="G43" s="2">
-        <v>45345</v>
-      </c>
-      <c r="I43">
-        <v>42</v>
-      </c>
-      <c r="J43">
-        <v>8001</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>125413419</v>
-      </c>
-      <c r="E44">
-        <v>1211</v>
-      </c>
-      <c r="F44" s="2">
-        <v>45345</v>
-      </c>
       <c r="G44" s="2">
-        <v>45342</v>
+        <v>45339</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2217,24 +2217,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>125528371</v>
+        <v>126757222</v>
       </c>
       <c r="E45">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F45" s="2">
-        <v>45345</v>
+        <v>45343</v>
       </c>
       <c r="G45" s="2">
-        <v>45344</v>
+        <v>45339</v>
       </c>
       <c r="I45">
         <v>42</v>
       </c>
       <c r="J45">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2255,62 +2255,62 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>125642845</v>
+        <v>126757247</v>
       </c>
       <c r="E46">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F46" s="2">
-        <v>45345</v>
+        <v>45343</v>
       </c>
       <c r="G46" s="2">
+        <v>45339</v>
+      </c>
+      <c r="I46">
+        <v>42</v>
+      </c>
+      <c r="J46">
+        <v>8013</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>126757330</v>
+      </c>
+      <c r="E47">
+        <v>601</v>
+      </c>
+      <c r="F47" s="2">
         <v>45343</v>
       </c>
-      <c r="I46">
-        <v>42</v>
-      </c>
-      <c r="J46">
-        <v>8001</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>125706834</v>
-      </c>
-      <c r="E47">
-        <v>1211</v>
-      </c>
-      <c r="F47" s="2">
-        <v>45345</v>
-      </c>
       <c r="G47" s="2">
-        <v>45345</v>
+        <v>45339</v>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2331,24 +2331,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>125718814</v>
+        <v>126757361</v>
       </c>
       <c r="E48">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F48" s="2">
-        <v>45345</v>
+        <v>45343</v>
       </c>
       <c r="G48" s="2">
-        <v>45344</v>
+        <v>45339</v>
       </c>
       <c r="I48">
         <v>42</v>
       </c>
       <c r="J48">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2369,24 +2369,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>125803590</v>
+        <v>126757713</v>
       </c>
       <c r="E49">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F49" s="2">
-        <v>45345</v>
+        <v>45339</v>
       </c>
       <c r="G49" s="2">
-        <v>45345</v>
+        <v>45339</v>
       </c>
       <c r="I49">
         <v>42</v>
       </c>
       <c r="J49">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2407,24 +2407,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>125871031</v>
+        <v>126714759</v>
       </c>
       <c r="E50">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F50" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G50" s="2">
-        <v>45341</v>
+        <v>45336</v>
       </c>
       <c r="I50">
         <v>42</v>
       </c>
       <c r="J50">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2445,24 +2445,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>125932613</v>
+        <v>126715244</v>
       </c>
       <c r="E51">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F51" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G51" s="2">
-        <v>45343</v>
+        <v>45336</v>
       </c>
       <c r="I51">
         <v>42</v>
       </c>
       <c r="J51">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2483,24 +2483,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>125965709</v>
+        <v>126715447</v>
       </c>
       <c r="E52">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F52" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G52" s="2">
-        <v>45344</v>
+        <v>45336</v>
       </c>
       <c r="I52">
         <v>42</v>
       </c>
       <c r="J52">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -2521,24 +2521,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>126030314</v>
+        <v>126718505</v>
       </c>
       <c r="E53">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F53" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G53" s="2">
-        <v>45345</v>
+        <v>45336</v>
       </c>
       <c r="I53">
         <v>42</v>
       </c>
       <c r="J53">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -2559,24 +2559,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>126032436</v>
+        <v>126722465</v>
       </c>
       <c r="E54">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F54" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G54" s="2">
-        <v>45344</v>
+        <v>45337</v>
       </c>
       <c r="I54">
         <v>42</v>
       </c>
       <c r="J54">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -2597,24 +2597,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>126048532</v>
+        <v>126724276</v>
       </c>
       <c r="E55">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F55" s="2">
-        <v>45346</v>
+        <v>45348</v>
       </c>
       <c r="G55" s="2">
-        <v>45346</v>
+        <v>45338</v>
       </c>
       <c r="I55">
         <v>42</v>
       </c>
       <c r="J55">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -2635,24 +2635,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>126173911</v>
+        <v>126724447</v>
       </c>
       <c r="E56">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F56" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G56" s="2">
-        <v>45345</v>
+        <v>45337</v>
       </c>
       <c r="I56">
         <v>42</v>
       </c>
       <c r="J56">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -2673,24 +2673,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>126270618</v>
+        <v>126724814</v>
       </c>
       <c r="E57">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F57" s="2">
-        <v>45346</v>
+        <v>45348</v>
       </c>
       <c r="G57" s="2">
-        <v>45344</v>
+        <v>45337</v>
       </c>
       <c r="I57">
         <v>42</v>
       </c>
       <c r="J57">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -2711,24 +2711,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>126355790</v>
+        <v>126724886</v>
       </c>
       <c r="E58">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F58" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G58" s="2">
-        <v>45345</v>
+        <v>45337</v>
       </c>
       <c r="I58">
         <v>42</v>
       </c>
       <c r="J58">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -2749,24 +2749,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>126559391</v>
+        <v>126726589</v>
       </c>
       <c r="E59">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F59" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G59" s="2">
-        <v>45343</v>
+        <v>45337</v>
       </c>
       <c r="I59">
         <v>42</v>
       </c>
       <c r="J59">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -2787,24 +2787,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>126564024</v>
+        <v>126729783</v>
       </c>
       <c r="E60">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F60" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G60" s="2">
-        <v>45345</v>
+        <v>45337</v>
       </c>
       <c r="I60">
         <v>42</v>
       </c>
       <c r="J60">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -2825,24 +2825,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>126589487</v>
+        <v>126731113</v>
       </c>
       <c r="E61">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F61" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G61" s="2">
-        <v>45345</v>
+        <v>45337</v>
       </c>
       <c r="I61">
         <v>42</v>
       </c>
       <c r="J61">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -2863,24 +2863,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>126708996</v>
+        <v>126733738</v>
       </c>
       <c r="E62">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F62" s="2">
-        <v>45345</v>
+        <v>45348</v>
       </c>
       <c r="G62" s="2">
-        <v>45342</v>
+        <v>45337</v>
       </c>
       <c r="I62">
         <v>42</v>
       </c>
       <c r="J62">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -2901,24 +2901,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>110074933</v>
+        <v>126734025</v>
       </c>
       <c r="E63">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F63" s="2">
-        <v>43453</v>
+        <v>45348</v>
       </c>
       <c r="G63" s="2">
-        <v>43441</v>
+        <v>45337</v>
       </c>
       <c r="I63">
         <v>42</v>
       </c>
       <c r="J63">
-        <v>8023</v>
+        <v>8013</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -2939,24 +2939,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>123058958</v>
+        <v>126735201</v>
       </c>
       <c r="E64">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F64" s="2">
-        <v>44995</v>
+        <v>45348</v>
       </c>
       <c r="G64" s="2">
-        <v>44993</v>
+        <v>45337</v>
       </c>
       <c r="I64">
         <v>42</v>
       </c>
       <c r="J64">
-        <v>8001</v>
+        <v>1118</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -2977,24 +2977,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>126697180</v>
+        <v>126748756</v>
       </c>
       <c r="E65">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F65" s="2">
-        <v>45334</v>
+        <v>45348</v>
       </c>
       <c r="G65" s="2">
-        <v>45331</v>
+        <v>45338</v>
       </c>
       <c r="I65">
         <v>42</v>
       </c>
       <c r="J65">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -3012,2818 +3012,6 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>126695348</v>
-      </c>
-      <c r="E66">
-        <v>601</v>
-      </c>
-      <c r="F66" s="2">
-        <v>45344</v>
-      </c>
-      <c r="G66" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I66">
-        <v>42</v>
-      </c>
-      <c r="J66">
-        <v>8013</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>0</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>126711296</v>
-      </c>
-      <c r="E67">
-        <v>601</v>
-      </c>
-      <c r="F67" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G67" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I67">
-        <v>42</v>
-      </c>
-      <c r="J67">
-        <v>8001</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>126711646</v>
-      </c>
-      <c r="E68">
-        <v>601</v>
-      </c>
-      <c r="F68" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G68" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I68">
-        <v>42</v>
-      </c>
-      <c r="J68">
-        <v>8001</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>126711851</v>
-      </c>
-      <c r="E69">
-        <v>601</v>
-      </c>
-      <c r="F69" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G69" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I69">
-        <v>42</v>
-      </c>
-      <c r="J69">
-        <v>8001</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>126711987</v>
-      </c>
-      <c r="E70">
-        <v>601</v>
-      </c>
-      <c r="F70" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G70" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I70">
-        <v>42</v>
-      </c>
-      <c r="J70">
-        <v>8001</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>0</v>
-      </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>126712132</v>
-      </c>
-      <c r="E71">
-        <v>601</v>
-      </c>
-      <c r="F71" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G71" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I71">
-        <v>42</v>
-      </c>
-      <c r="J71">
-        <v>8001</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>126712467</v>
-      </c>
-      <c r="E72">
-        <v>601</v>
-      </c>
-      <c r="F72" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G72" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I72">
-        <v>42</v>
-      </c>
-      <c r="J72">
-        <v>8001</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <v>0</v>
-      </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <v>0</v>
-      </c>
-      <c r="P72">
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>126712579</v>
-      </c>
-      <c r="E73">
-        <v>601</v>
-      </c>
-      <c r="F73" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G73" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I73">
-        <v>42</v>
-      </c>
-      <c r="J73">
-        <v>8004</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <v>0</v>
-      </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73">
-        <v>0</v>
-      </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>126712672</v>
-      </c>
-      <c r="E74">
-        <v>601</v>
-      </c>
-      <c r="F74" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G74" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I74">
-        <v>42</v>
-      </c>
-      <c r="J74">
-        <v>8001</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <v>0</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <v>0</v>
-      </c>
-      <c r="P74">
-        <v>0</v>
-      </c>
-      <c r="Q74">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>126716557</v>
-      </c>
-      <c r="E75">
-        <v>601</v>
-      </c>
-      <c r="F75" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G75" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I75">
-        <v>42</v>
-      </c>
-      <c r="J75">
-        <v>8004</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
-      </c>
-      <c r="P75">
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>126716869</v>
-      </c>
-      <c r="E76">
-        <v>601</v>
-      </c>
-      <c r="F76" s="2">
-        <v>45343</v>
-      </c>
-      <c r="G76" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I76">
-        <v>42</v>
-      </c>
-      <c r="J76">
-        <v>8013</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76">
-        <v>0</v>
-      </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
-      <c r="O76">
-        <v>0</v>
-      </c>
-      <c r="P76">
-        <v>0</v>
-      </c>
-      <c r="Q76">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>126716898</v>
-      </c>
-      <c r="E77">
-        <v>601</v>
-      </c>
-      <c r="F77" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G77" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I77">
-        <v>42</v>
-      </c>
-      <c r="J77">
-        <v>8004</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <v>0</v>
-      </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
-      <c r="O77">
-        <v>0</v>
-      </c>
-      <c r="P77">
-        <v>0</v>
-      </c>
-      <c r="Q77">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>126717515</v>
-      </c>
-      <c r="E78">
-        <v>601</v>
-      </c>
-      <c r="F78" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G78" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I78">
-        <v>42</v>
-      </c>
-      <c r="J78">
-        <v>8004</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78">
-        <v>0</v>
-      </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
-      <c r="O78">
-        <v>0</v>
-      </c>
-      <c r="P78">
-        <v>0</v>
-      </c>
-      <c r="Q78">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>126717789</v>
-      </c>
-      <c r="E79">
-        <v>601</v>
-      </c>
-      <c r="F79" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G79" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I79">
-        <v>42</v>
-      </c>
-      <c r="J79">
-        <v>8004</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79">
-        <v>0</v>
-      </c>
-      <c r="P79">
-        <v>0</v>
-      </c>
-      <c r="Q79">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>126718311</v>
-      </c>
-      <c r="E80">
-        <v>601</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G80" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I80">
-        <v>42</v>
-      </c>
-      <c r="J80">
-        <v>8004</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>0</v>
-      </c>
-      <c r="P80">
-        <v>0</v>
-      </c>
-      <c r="Q80">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>126722395</v>
-      </c>
-      <c r="E81">
-        <v>601</v>
-      </c>
-      <c r="F81" s="2">
-        <v>45345</v>
-      </c>
-      <c r="G81" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I81">
-        <v>42</v>
-      </c>
-      <c r="J81">
-        <v>8013</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
-        <v>0</v>
-      </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
-      <c r="O81">
-        <v>0</v>
-      </c>
-      <c r="P81">
-        <v>0</v>
-      </c>
-      <c r="Q81">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>126723481</v>
-      </c>
-      <c r="E82">
-        <v>601</v>
-      </c>
-      <c r="F82" s="2">
-        <v>45345</v>
-      </c>
-      <c r="G82" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I82">
-        <v>42</v>
-      </c>
-      <c r="J82">
-        <v>8013</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>0</v>
-      </c>
-      <c r="P82">
-        <v>0</v>
-      </c>
-      <c r="Q82">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>126724150</v>
-      </c>
-      <c r="E83">
-        <v>601</v>
-      </c>
-      <c r="F83" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G83" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I83">
-        <v>42</v>
-      </c>
-      <c r="J83">
-        <v>8004</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
-      <c r="O83">
-        <v>0</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
-      <c r="Q83">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>126724317</v>
-      </c>
-      <c r="E84">
-        <v>601</v>
-      </c>
-      <c r="F84" s="2">
-        <v>45345</v>
-      </c>
-      <c r="G84" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I84">
-        <v>42</v>
-      </c>
-      <c r="J84">
-        <v>8013</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84">
-        <v>0</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>126724408</v>
-      </c>
-      <c r="E85">
-        <v>601</v>
-      </c>
-      <c r="F85" s="2">
-        <v>45339</v>
-      </c>
-      <c r="G85" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I85">
-        <v>42</v>
-      </c>
-      <c r="J85">
-        <v>8013</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
-        <v>0</v>
-      </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>0</v>
-      </c>
-      <c r="P85">
-        <v>0</v>
-      </c>
-      <c r="Q85">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>126725845</v>
-      </c>
-      <c r="E86">
-        <v>601</v>
-      </c>
-      <c r="F86" s="2">
-        <v>45343</v>
-      </c>
-      <c r="G86" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I86">
-        <v>42</v>
-      </c>
-      <c r="J86">
-        <v>8013</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86">
-        <v>0</v>
-      </c>
-      <c r="P86">
-        <v>0</v>
-      </c>
-      <c r="Q86">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>126727475</v>
-      </c>
-      <c r="E87">
-        <v>601</v>
-      </c>
-      <c r="F87" s="2">
-        <v>45343</v>
-      </c>
-      <c r="G87" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I87">
-        <v>42</v>
-      </c>
-      <c r="J87">
-        <v>8013</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
-      <c r="M87">
-        <v>0</v>
-      </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
-      <c r="O87">
-        <v>0</v>
-      </c>
-      <c r="P87">
-        <v>0</v>
-      </c>
-      <c r="Q87">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>126728229</v>
-      </c>
-      <c r="E88">
-        <v>601</v>
-      </c>
-      <c r="F88" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G88" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I88">
-        <v>42</v>
-      </c>
-      <c r="J88">
-        <v>8004</v>
-      </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88">
-        <v>0</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88">
-        <v>0</v>
-      </c>
-      <c r="P88">
-        <v>0</v>
-      </c>
-      <c r="Q88">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>126728767</v>
-      </c>
-      <c r="E89">
-        <v>601</v>
-      </c>
-      <c r="F89" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G89" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I89">
-        <v>42</v>
-      </c>
-      <c r="J89">
-        <v>8004</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
-        <v>0</v>
-      </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <v>0</v>
-      </c>
-      <c r="P89">
-        <v>0</v>
-      </c>
-      <c r="Q89">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>126729421</v>
-      </c>
-      <c r="E90">
-        <v>601</v>
-      </c>
-      <c r="F90" s="2">
-        <v>45343</v>
-      </c>
-      <c r="G90" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I90">
-        <v>42</v>
-      </c>
-      <c r="J90">
-        <v>8013</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>126730182</v>
-      </c>
-      <c r="E91">
-        <v>601</v>
-      </c>
-      <c r="F91" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G91" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I91">
-        <v>42</v>
-      </c>
-      <c r="J91">
-        <v>8004</v>
-      </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="M91">
-        <v>0</v>
-      </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
-      <c r="O91">
-        <v>0</v>
-      </c>
-      <c r="P91">
-        <v>0</v>
-      </c>
-      <c r="Q91">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>126734101</v>
-      </c>
-      <c r="E92">
-        <v>601</v>
-      </c>
-      <c r="F92" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G92" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I92">
-        <v>42</v>
-      </c>
-      <c r="J92">
-        <v>8004</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
-        <v>0</v>
-      </c>
-      <c r="N92">
-        <v>0</v>
-      </c>
-      <c r="O92">
-        <v>0</v>
-      </c>
-      <c r="P92">
-        <v>0</v>
-      </c>
-      <c r="Q92">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>126734273</v>
-      </c>
-      <c r="E93">
-        <v>601</v>
-      </c>
-      <c r="F93" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G93" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I93">
-        <v>42</v>
-      </c>
-      <c r="J93">
-        <v>8004</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
-        <v>0</v>
-      </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
-      <c r="O93">
-        <v>0</v>
-      </c>
-      <c r="P93">
-        <v>0</v>
-      </c>
-      <c r="Q93">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>126734892</v>
-      </c>
-      <c r="E94">
-        <v>601</v>
-      </c>
-      <c r="F94" s="2">
-        <v>45342</v>
-      </c>
-      <c r="G94" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I94">
-        <v>42</v>
-      </c>
-      <c r="J94">
-        <v>8013</v>
-      </c>
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="M94">
-        <v>0</v>
-      </c>
-      <c r="N94">
-        <v>0</v>
-      </c>
-      <c r="O94">
-        <v>0</v>
-      </c>
-      <c r="P94">
-        <v>0</v>
-      </c>
-      <c r="Q94">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>126735153</v>
-      </c>
-      <c r="E95">
-        <v>601</v>
-      </c>
-      <c r="F95" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G95" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I95">
-        <v>42</v>
-      </c>
-      <c r="J95">
-        <v>1118</v>
-      </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="M95">
-        <v>0</v>
-      </c>
-      <c r="N95">
-        <v>0</v>
-      </c>
-      <c r="O95">
-        <v>0</v>
-      </c>
-      <c r="P95">
-        <v>0</v>
-      </c>
-      <c r="Q95">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>126735286</v>
-      </c>
-      <c r="E96">
-        <v>601</v>
-      </c>
-      <c r="F96" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G96" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I96">
-        <v>42</v>
-      </c>
-      <c r="J96">
-        <v>8004</v>
-      </c>
-      <c r="L96">
-        <v>0</v>
-      </c>
-      <c r="M96">
-        <v>0</v>
-      </c>
-      <c r="N96">
-        <v>0</v>
-      </c>
-      <c r="O96">
-        <v>0</v>
-      </c>
-      <c r="P96">
-        <v>0</v>
-      </c>
-      <c r="Q96">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>126737061</v>
-      </c>
-      <c r="E97">
-        <v>601</v>
-      </c>
-      <c r="F97" s="2">
-        <v>45343</v>
-      </c>
-      <c r="G97" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I97">
-        <v>42</v>
-      </c>
-      <c r="J97">
-        <v>8013</v>
-      </c>
-      <c r="L97">
-        <v>0</v>
-      </c>
-      <c r="M97">
-        <v>0</v>
-      </c>
-      <c r="N97">
-        <v>0</v>
-      </c>
-      <c r="O97">
-        <v>0</v>
-      </c>
-      <c r="P97">
-        <v>0</v>
-      </c>
-      <c r="Q97">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>126737290</v>
-      </c>
-      <c r="E98">
-        <v>601</v>
-      </c>
-      <c r="F98" s="2">
-        <v>45343</v>
-      </c>
-      <c r="G98" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I98">
-        <v>42</v>
-      </c>
-      <c r="J98">
-        <v>8013</v>
-      </c>
-      <c r="L98">
-        <v>0</v>
-      </c>
-      <c r="M98">
-        <v>0</v>
-      </c>
-      <c r="N98">
-        <v>0</v>
-      </c>
-      <c r="O98">
-        <v>0</v>
-      </c>
-      <c r="P98">
-        <v>0</v>
-      </c>
-      <c r="Q98">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>126737366</v>
-      </c>
-      <c r="E99">
-        <v>601</v>
-      </c>
-      <c r="F99" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G99" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I99">
-        <v>42</v>
-      </c>
-      <c r="J99">
-        <v>8004</v>
-      </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-      <c r="M99">
-        <v>0</v>
-      </c>
-      <c r="N99">
-        <v>0</v>
-      </c>
-      <c r="O99">
-        <v>0</v>
-      </c>
-      <c r="P99">
-        <v>0</v>
-      </c>
-      <c r="Q99">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>126737930</v>
-      </c>
-      <c r="E100">
-        <v>601</v>
-      </c>
-      <c r="F100" s="2">
-        <v>45345</v>
-      </c>
-      <c r="G100" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I100">
-        <v>42</v>
-      </c>
-      <c r="J100">
-        <v>8013</v>
-      </c>
-      <c r="L100">
-        <v>0</v>
-      </c>
-      <c r="M100">
-        <v>0</v>
-      </c>
-      <c r="N100">
-        <v>0</v>
-      </c>
-      <c r="O100">
-        <v>0</v>
-      </c>
-      <c r="P100">
-        <v>0</v>
-      </c>
-      <c r="Q100">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>126738573</v>
-      </c>
-      <c r="E101">
-        <v>601</v>
-      </c>
-      <c r="F101" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G101" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I101">
-        <v>42</v>
-      </c>
-      <c r="J101">
-        <v>8004</v>
-      </c>
-      <c r="L101">
-        <v>0</v>
-      </c>
-      <c r="M101">
-        <v>0</v>
-      </c>
-      <c r="N101">
-        <v>0</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>0</v>
-      </c>
-      <c r="Q101">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>126741164</v>
-      </c>
-      <c r="E102">
-        <v>601</v>
-      </c>
-      <c r="F102" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G102" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I102">
-        <v>42</v>
-      </c>
-      <c r="J102">
-        <v>8004</v>
-      </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-      <c r="M102">
-        <v>0</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
-        <v>0</v>
-      </c>
-      <c r="P102">
-        <v>0</v>
-      </c>
-      <c r="Q102">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>126742492</v>
-      </c>
-      <c r="E103">
-        <v>601</v>
-      </c>
-      <c r="F103" s="2">
-        <v>45346</v>
-      </c>
-      <c r="G103" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I103">
-        <v>42</v>
-      </c>
-      <c r="J103">
-        <v>8013</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="M103">
-        <v>0</v>
-      </c>
-      <c r="N103">
-        <v>0</v>
-      </c>
-      <c r="O103">
-        <v>0</v>
-      </c>
-      <c r="P103">
-        <v>0</v>
-      </c>
-      <c r="Q103">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>126743974</v>
-      </c>
-      <c r="E104">
-        <v>601</v>
-      </c>
-      <c r="F104" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G104" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I104">
-        <v>42</v>
-      </c>
-      <c r="J104">
-        <v>8004</v>
-      </c>
-      <c r="L104">
-        <v>0</v>
-      </c>
-      <c r="M104">
-        <v>0</v>
-      </c>
-      <c r="N104">
-        <v>0</v>
-      </c>
-      <c r="O104">
-        <v>0</v>
-      </c>
-      <c r="P104">
-        <v>0</v>
-      </c>
-      <c r="Q104">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>126745128</v>
-      </c>
-      <c r="E105">
-        <v>601</v>
-      </c>
-      <c r="F105" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G105" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I105">
-        <v>42</v>
-      </c>
-      <c r="J105">
-        <v>8004</v>
-      </c>
-      <c r="L105">
-        <v>0</v>
-      </c>
-      <c r="M105">
-        <v>0</v>
-      </c>
-      <c r="N105">
-        <v>0</v>
-      </c>
-      <c r="O105">
-        <v>0</v>
-      </c>
-      <c r="P105">
-        <v>0</v>
-      </c>
-      <c r="Q105">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>126745183</v>
-      </c>
-      <c r="E106">
-        <v>601</v>
-      </c>
-      <c r="F106" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G106" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I106">
-        <v>42</v>
-      </c>
-      <c r="J106">
-        <v>8004</v>
-      </c>
-      <c r="L106">
-        <v>0</v>
-      </c>
-      <c r="M106">
-        <v>0</v>
-      </c>
-      <c r="N106">
-        <v>0</v>
-      </c>
-      <c r="O106">
-        <v>0</v>
-      </c>
-      <c r="P106">
-        <v>0</v>
-      </c>
-      <c r="Q106">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>126745400</v>
-      </c>
-      <c r="E107">
-        <v>601</v>
-      </c>
-      <c r="F107" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G107" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I107">
-        <v>42</v>
-      </c>
-      <c r="J107">
-        <v>8004</v>
-      </c>
-      <c r="L107">
-        <v>0</v>
-      </c>
-      <c r="M107">
-        <v>0</v>
-      </c>
-      <c r="N107">
-        <v>0</v>
-      </c>
-      <c r="O107">
-        <v>0</v>
-      </c>
-      <c r="P107">
-        <v>0</v>
-      </c>
-      <c r="Q107">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>126745423</v>
-      </c>
-      <c r="E108">
-        <v>601</v>
-      </c>
-      <c r="F108" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G108" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I108">
-        <v>42</v>
-      </c>
-      <c r="J108">
-        <v>8004</v>
-      </c>
-      <c r="L108">
-        <v>0</v>
-      </c>
-      <c r="M108">
-        <v>0</v>
-      </c>
-      <c r="N108">
-        <v>0</v>
-      </c>
-      <c r="O108">
-        <v>0</v>
-      </c>
-      <c r="P108">
-        <v>0</v>
-      </c>
-      <c r="Q108">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>126745991</v>
-      </c>
-      <c r="E109">
-        <v>601</v>
-      </c>
-      <c r="F109" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G109" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I109">
-        <v>42</v>
-      </c>
-      <c r="J109">
-        <v>8004</v>
-      </c>
-      <c r="L109">
-        <v>0</v>
-      </c>
-      <c r="M109">
-        <v>0</v>
-      </c>
-      <c r="N109">
-        <v>0</v>
-      </c>
-      <c r="O109">
-        <v>0</v>
-      </c>
-      <c r="P109">
-        <v>0</v>
-      </c>
-      <c r="Q109">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>126747679</v>
-      </c>
-      <c r="E110">
-        <v>601</v>
-      </c>
-      <c r="F110" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G110" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I110">
-        <v>42</v>
-      </c>
-      <c r="J110">
-        <v>8004</v>
-      </c>
-      <c r="L110">
-        <v>0</v>
-      </c>
-      <c r="M110">
-        <v>0</v>
-      </c>
-      <c r="N110">
-        <v>0</v>
-      </c>
-      <c r="O110">
-        <v>0</v>
-      </c>
-      <c r="P110">
-        <v>0</v>
-      </c>
-      <c r="Q110">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>126748249</v>
-      </c>
-      <c r="E111">
-        <v>601</v>
-      </c>
-      <c r="F111" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G111" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I111">
-        <v>42</v>
-      </c>
-      <c r="J111">
-        <v>8004</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="M111">
-        <v>0</v>
-      </c>
-      <c r="N111">
-        <v>0</v>
-      </c>
-      <c r="O111">
-        <v>0</v>
-      </c>
-      <c r="P111">
-        <v>0</v>
-      </c>
-      <c r="Q111">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <v>126748558</v>
-      </c>
-      <c r="E112">
-        <v>601</v>
-      </c>
-      <c r="F112" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G112" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I112">
-        <v>42</v>
-      </c>
-      <c r="J112">
-        <v>8004</v>
-      </c>
-      <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="M112">
-        <v>0</v>
-      </c>
-      <c r="N112">
-        <v>0</v>
-      </c>
-      <c r="O112">
-        <v>0</v>
-      </c>
-      <c r="P112">
-        <v>0</v>
-      </c>
-      <c r="Q112">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>126749388</v>
-      </c>
-      <c r="E113">
-        <v>601</v>
-      </c>
-      <c r="F113" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G113" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I113">
-        <v>42</v>
-      </c>
-      <c r="J113">
-        <v>8013</v>
-      </c>
-      <c r="L113">
-        <v>0</v>
-      </c>
-      <c r="M113">
-        <v>0</v>
-      </c>
-      <c r="N113">
-        <v>0</v>
-      </c>
-      <c r="O113">
-        <v>0</v>
-      </c>
-      <c r="P113">
-        <v>0</v>
-      </c>
-      <c r="Q113">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>126749809</v>
-      </c>
-      <c r="E114">
-        <v>601</v>
-      </c>
-      <c r="F114" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G114" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I114">
-        <v>42</v>
-      </c>
-      <c r="J114">
-        <v>8004</v>
-      </c>
-      <c r="L114">
-        <v>0</v>
-      </c>
-      <c r="M114">
-        <v>0</v>
-      </c>
-      <c r="N114">
-        <v>0</v>
-      </c>
-      <c r="O114">
-        <v>0</v>
-      </c>
-      <c r="P114">
-        <v>0</v>
-      </c>
-      <c r="Q114">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <v>126750157</v>
-      </c>
-      <c r="E115">
-        <v>601</v>
-      </c>
-      <c r="F115" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G115" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I115">
-        <v>42</v>
-      </c>
-      <c r="J115">
-        <v>8004</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="M115">
-        <v>0</v>
-      </c>
-      <c r="N115">
-        <v>0</v>
-      </c>
-      <c r="O115">
-        <v>0</v>
-      </c>
-      <c r="P115">
-        <v>0</v>
-      </c>
-      <c r="Q115">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <v>126750746</v>
-      </c>
-      <c r="E116">
-        <v>601</v>
-      </c>
-      <c r="F116" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G116" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I116">
-        <v>42</v>
-      </c>
-      <c r="J116">
-        <v>8004</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="M116">
-        <v>0</v>
-      </c>
-      <c r="N116">
-        <v>0</v>
-      </c>
-      <c r="O116">
-        <v>0</v>
-      </c>
-      <c r="P116">
-        <v>0</v>
-      </c>
-      <c r="Q116">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <v>126750793</v>
-      </c>
-      <c r="E117">
-        <v>601</v>
-      </c>
-      <c r="F117" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G117" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I117">
-        <v>42</v>
-      </c>
-      <c r="J117">
-        <v>8004</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="M117">
-        <v>0</v>
-      </c>
-      <c r="N117">
-        <v>0</v>
-      </c>
-      <c r="O117">
-        <v>0</v>
-      </c>
-      <c r="P117">
-        <v>0</v>
-      </c>
-      <c r="Q117">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <v>126750967</v>
-      </c>
-      <c r="E118">
-        <v>601</v>
-      </c>
-      <c r="F118" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G118" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I118">
-        <v>42</v>
-      </c>
-      <c r="J118">
-        <v>8004</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118">
-        <v>0</v>
-      </c>
-      <c r="N118">
-        <v>0</v>
-      </c>
-      <c r="O118">
-        <v>0</v>
-      </c>
-      <c r="P118">
-        <v>0</v>
-      </c>
-      <c r="Q118">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <v>126751878</v>
-      </c>
-      <c r="E119">
-        <v>601</v>
-      </c>
-      <c r="F119" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G119" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I119">
-        <v>42</v>
-      </c>
-      <c r="J119">
-        <v>8004</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119">
-        <v>0</v>
-      </c>
-      <c r="N119">
-        <v>0</v>
-      </c>
-      <c r="O119">
-        <v>0</v>
-      </c>
-      <c r="P119">
-        <v>0</v>
-      </c>
-      <c r="Q119">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A120">
-        <v>126752839</v>
-      </c>
-      <c r="E120">
-        <v>601</v>
-      </c>
-      <c r="F120" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G120" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I120">
-        <v>42</v>
-      </c>
-      <c r="J120">
-        <v>8004</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120">
-        <v>0</v>
-      </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120">
-        <v>0</v>
-      </c>
-      <c r="P120">
-        <v>0</v>
-      </c>
-      <c r="Q120">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <v>126753255</v>
-      </c>
-      <c r="E121">
-        <v>601</v>
-      </c>
-      <c r="F121" s="2">
-        <v>45346</v>
-      </c>
-      <c r="G121" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I121">
-        <v>42</v>
-      </c>
-      <c r="J121">
-        <v>8013</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="M121">
-        <v>0</v>
-      </c>
-      <c r="N121">
-        <v>0</v>
-      </c>
-      <c r="O121">
-        <v>0</v>
-      </c>
-      <c r="P121">
-        <v>0</v>
-      </c>
-      <c r="Q121">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A122">
-        <v>126755187</v>
-      </c>
-      <c r="E122">
-        <v>601</v>
-      </c>
-      <c r="F122" s="2">
-        <v>45343</v>
-      </c>
-      <c r="G122" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I122">
-        <v>42</v>
-      </c>
-      <c r="J122">
-        <v>8013</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122">
-        <v>0</v>
-      </c>
-      <c r="N122">
-        <v>0</v>
-      </c>
-      <c r="O122">
-        <v>0</v>
-      </c>
-      <c r="P122">
-        <v>0</v>
-      </c>
-      <c r="Q122">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A123">
-        <v>126748249</v>
-      </c>
-      <c r="E123">
-        <v>601</v>
-      </c>
-      <c r="F123" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G123" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I123">
-        <v>42</v>
-      </c>
-      <c r="J123">
-        <v>8004</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123">
-        <v>0</v>
-      </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
-      <c r="O123">
-        <v>0</v>
-      </c>
-      <c r="P123">
-        <v>0</v>
-      </c>
-      <c r="Q123">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <v>126714759</v>
-      </c>
-      <c r="E124">
-        <v>601</v>
-      </c>
-      <c r="F124" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G124" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I124">
-        <v>42</v>
-      </c>
-      <c r="J124">
-        <v>8004</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124">
-        <v>0</v>
-      </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
-      <c r="O124">
-        <v>0</v>
-      </c>
-      <c r="P124">
-        <v>0</v>
-      </c>
-      <c r="Q124">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>126715244</v>
-      </c>
-      <c r="E125">
-        <v>601</v>
-      </c>
-      <c r="F125" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G125" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I125">
-        <v>42</v>
-      </c>
-      <c r="J125">
-        <v>8004</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125">
-        <v>0</v>
-      </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
-      <c r="O125">
-        <v>0</v>
-      </c>
-      <c r="P125">
-        <v>0</v>
-      </c>
-      <c r="Q125">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A126">
-        <v>126715447</v>
-      </c>
-      <c r="E126">
-        <v>601</v>
-      </c>
-      <c r="F126" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G126" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I126">
-        <v>42</v>
-      </c>
-      <c r="J126">
-        <v>8004</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126">
-        <v>0</v>
-      </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
-      <c r="O126">
-        <v>0</v>
-      </c>
-      <c r="P126">
-        <v>0</v>
-      </c>
-      <c r="Q126">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <v>126718505</v>
-      </c>
-      <c r="E127">
-        <v>601</v>
-      </c>
-      <c r="F127" s="2">
-        <v>45336</v>
-      </c>
-      <c r="G127" s="2">
-        <v>45336</v>
-      </c>
-      <c r="I127">
-        <v>42</v>
-      </c>
-      <c r="J127">
-        <v>8004</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127">
-        <v>0</v>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A128">
-        <v>126722465</v>
-      </c>
-      <c r="E128">
-        <v>601</v>
-      </c>
-      <c r="F128" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G128" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I128">
-        <v>42</v>
-      </c>
-      <c r="J128">
-        <v>8004</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128">
-        <v>0</v>
-      </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
-      <c r="O128">
-        <v>0</v>
-      </c>
-      <c r="P128">
-        <v>0</v>
-      </c>
-      <c r="Q128">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <v>126724276</v>
-      </c>
-      <c r="E129">
-        <v>601</v>
-      </c>
-      <c r="F129" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G129" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I129">
-        <v>42</v>
-      </c>
-      <c r="J129">
-        <v>8004</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129">
-        <v>0</v>
-      </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>0</v>
-      </c>
-      <c r="P129">
-        <v>0</v>
-      </c>
-      <c r="Q129">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130">
-        <v>126724447</v>
-      </c>
-      <c r="E130">
-        <v>601</v>
-      </c>
-      <c r="F130" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G130" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I130">
-        <v>42</v>
-      </c>
-      <c r="J130">
-        <v>8004</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130">
-        <v>0</v>
-      </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
-        <v>0</v>
-      </c>
-      <c r="P130">
-        <v>0</v>
-      </c>
-      <c r="Q130">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A131">
-        <v>126724814</v>
-      </c>
-      <c r="E131">
-        <v>601</v>
-      </c>
-      <c r="F131" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G131" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I131">
-        <v>42</v>
-      </c>
-      <c r="J131">
-        <v>8004</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131">
-        <v>0</v>
-      </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>0</v>
-      </c>
-      <c r="P131">
-        <v>0</v>
-      </c>
-      <c r="Q131">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A132">
-        <v>126724886</v>
-      </c>
-      <c r="E132">
-        <v>601</v>
-      </c>
-      <c r="F132" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G132" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I132">
-        <v>42</v>
-      </c>
-      <c r="J132">
-        <v>8004</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132">
-        <v>0</v>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
-        <v>0</v>
-      </c>
-      <c r="Q132">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <v>126726589</v>
-      </c>
-      <c r="E133">
-        <v>601</v>
-      </c>
-      <c r="F133" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G133" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I133">
-        <v>42</v>
-      </c>
-      <c r="J133">
-        <v>8004</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133">
-        <v>0</v>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>0</v>
-      </c>
-      <c r="P133">
-        <v>0</v>
-      </c>
-      <c r="Q133">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A134">
-        <v>126729783</v>
-      </c>
-      <c r="E134">
-        <v>601</v>
-      </c>
-      <c r="F134" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G134" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I134">
-        <v>42</v>
-      </c>
-      <c r="J134">
-        <v>8004</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134">
-        <v>0</v>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
-        <v>0</v>
-      </c>
-      <c r="Q134">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A135">
-        <v>126731113</v>
-      </c>
-      <c r="E135">
-        <v>601</v>
-      </c>
-      <c r="F135" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G135" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I135">
-        <v>42</v>
-      </c>
-      <c r="J135">
-        <v>1117</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135">
-        <v>0</v>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
-        <v>0</v>
-      </c>
-      <c r="Q135">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <v>126733738</v>
-      </c>
-      <c r="E136">
-        <v>601</v>
-      </c>
-      <c r="F136" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G136" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I136">
-        <v>42</v>
-      </c>
-      <c r="J136">
-        <v>8004</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136">
-        <v>0</v>
-      </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
-        <v>0</v>
-      </c>
-      <c r="P136">
-        <v>0</v>
-      </c>
-      <c r="Q136">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <v>126734025</v>
-      </c>
-      <c r="E137">
-        <v>601</v>
-      </c>
-      <c r="F137" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G137" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I137">
-        <v>42</v>
-      </c>
-      <c r="J137">
-        <v>8004</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137">
-        <v>0</v>
-      </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A138">
-        <v>126735201</v>
-      </c>
-      <c r="E138">
-        <v>601</v>
-      </c>
-      <c r="F138" s="2">
-        <v>45337</v>
-      </c>
-      <c r="G138" s="2">
-        <v>45337</v>
-      </c>
-      <c r="I138">
-        <v>42</v>
-      </c>
-      <c r="J138">
-        <v>1118</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138">
-        <v>0</v>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A139">
-        <v>126748756</v>
-      </c>
-      <c r="E139">
-        <v>601</v>
-      </c>
-      <c r="F139" s="2">
-        <v>45338</v>
-      </c>
-      <c r="G139" s="2">
-        <v>45338</v>
-      </c>
-      <c r="I139">
-        <v>42</v>
-      </c>
-      <c r="J139">
-        <v>8004</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139">
-        <v>0</v>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
         <v>61</v>
       </c>
     </row>
@@ -5842,12 +3030,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{249CD703-0AE7-46A1-BA6D-A19361B97C73}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:Q198"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -5900,7 +3088,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>125887260</v>
       </c>
@@ -5938,7 +3126,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>125890823</v>
       </c>
@@ -5976,7 +3164,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>125891086</v>
       </c>
@@ -6014,7 +3202,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>125892224</v>
       </c>
@@ -6052,7 +3240,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>125892709</v>
       </c>
@@ -6090,7 +3278,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>125892901</v>
       </c>
@@ -6128,7 +3316,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>125892906</v>
       </c>
@@ -6166,7 +3354,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>125893564</v>
       </c>
@@ -6204,7 +3392,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>125893722</v>
       </c>
@@ -6242,7 +3430,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>125895193</v>
       </c>
@@ -6280,7 +3468,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>125896177</v>
       </c>
@@ -6318,7 +3506,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>125898007</v>
       </c>
@@ -6356,7 +3544,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>125900254</v>
       </c>
@@ -6394,7 +3582,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>125901787</v>
       </c>
@@ -6432,7 +3620,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>125901795</v>
       </c>
@@ -6470,7 +3658,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>125903262</v>
       </c>
@@ -6508,7 +3696,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>125904221</v>
       </c>
@@ -6546,7 +3734,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>125904238</v>
       </c>
@@ -6584,7 +3772,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>125907420</v>
       </c>
@@ -6622,7 +3810,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>125907797</v>
       </c>
@@ -6660,7 +3848,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>125908056</v>
       </c>
@@ -6698,7 +3886,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>125908177</v>
       </c>
@@ -6736,7 +3924,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>125908231</v>
       </c>
@@ -6774,7 +3962,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>125908843</v>
       </c>
@@ -6812,7 +4000,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>125909142</v>
       </c>
@@ -6850,7 +4038,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>125909933</v>
       </c>
@@ -6888,7 +4076,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>125910114</v>
       </c>
@@ -6926,7 +4114,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>125910400</v>
       </c>
@@ -6964,7 +4152,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>125910838</v>
       </c>
@@ -7002,7 +4190,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>125912176</v>
       </c>
@@ -7040,7 +4228,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>125912843</v>
       </c>
@@ -7078,7 +4266,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>125913133</v>
       </c>
@@ -7116,7 +4304,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>125913427</v>
       </c>
@@ -7154,7 +4342,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>125914356</v>
       </c>
@@ -7192,7 +4380,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>125914668</v>
       </c>
@@ -7230,7 +4418,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>125914978</v>
       </c>
@@ -7268,7 +4456,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>125918666</v>
       </c>
@@ -7306,7 +4494,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>125920065</v>
       </c>
@@ -7344,7 +4532,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>125924508</v>
       </c>
@@ -7382,7 +4570,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>125926112</v>
       </c>
@@ -7420,7 +4608,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>125927235</v>
       </c>
@@ -7458,7 +4646,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>125927477</v>
       </c>
@@ -7496,7 +4684,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>125927712</v>
       </c>
@@ -7534,7 +4722,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>125927811</v>
       </c>
@@ -7572,7 +4760,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>125928500</v>
       </c>
@@ -7610,7 +4798,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>125928781</v>
       </c>
@@ -7648,7 +4836,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>125928935</v>
       </c>
@@ -7686,7 +4874,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>125929845</v>
       </c>
@@ -7724,7 +4912,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>125930432</v>
       </c>
@@ -7762,7 +4950,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>125931903</v>
       </c>
@@ -7800,7 +4988,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>125932521</v>
       </c>
@@ -7838,7 +5026,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>125932669</v>
       </c>
@@ -7876,7 +5064,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>125933582</v>
       </c>
@@ -7914,7 +5102,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>125933608</v>
       </c>
@@ -7952,7 +5140,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>125935767</v>
       </c>
@@ -7990,7 +5178,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>125938612</v>
       </c>
@@ -8028,7 +5216,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>125944749</v>
       </c>
@@ -8066,7 +5254,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>125945240</v>
       </c>
@@ -8104,7 +5292,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>125949456</v>
       </c>
@@ -8142,7 +5330,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>125958349</v>
       </c>
@@ -8180,7 +5368,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>125958503</v>
       </c>
@@ -8218,7 +5406,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>125960344</v>
       </c>
@@ -8256,7 +5444,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>125962131</v>
       </c>
@@ -8294,7 +5482,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>125965767</v>
       </c>
@@ -8332,7 +5520,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>125965877</v>
       </c>
@@ -8370,7 +5558,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>125969356</v>
       </c>
@@ -8408,7 +5596,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>125971901</v>
       </c>
@@ -8446,7 +5634,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>125976084</v>
       </c>
@@ -8484,7 +5672,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>125976278</v>
       </c>
@@ -8522,7 +5710,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>125977146</v>
       </c>
@@ -8560,7 +5748,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>125977504</v>
       </c>
@@ -8598,7 +5786,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>125981162</v>
       </c>
@@ -8636,7 +5824,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>125983181</v>
       </c>
@@ -8674,7 +5862,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>125983593</v>
       </c>
@@ -8712,7 +5900,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>125984782</v>
       </c>
@@ -8750,7 +5938,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>125992174</v>
       </c>
@@ -8788,7 +5976,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>125992452</v>
       </c>
@@ -8826,7 +6014,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>125997050</v>
       </c>
@@ -8864,7 +6052,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>126009389</v>
       </c>
@@ -8902,7 +6090,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>126012544</v>
       </c>
@@ -8940,7 +6128,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>126013965</v>
       </c>
@@ -8978,7 +6166,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>126015225</v>
       </c>
@@ -9016,7 +6204,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>126015257</v>
       </c>
@@ -9054,7 +6242,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>126020235</v>
       </c>
@@ -9092,7 +6280,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>126028210</v>
       </c>
@@ -9130,7 +6318,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>126028956</v>
       </c>
@@ -9168,7 +6356,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>126029328</v>
       </c>
@@ -9206,7 +6394,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>126029650</v>
       </c>
@@ -9244,7 +6432,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>126029868</v>
       </c>
@@ -9282,7 +6470,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>126033233</v>
       </c>
@@ -9320,7 +6508,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>126036666</v>
       </c>
@@ -9358,7 +6546,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>126037292</v>
       </c>
@@ -9396,7 +6584,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>126040785</v>
       </c>
@@ -9434,7 +6622,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>126040979</v>
       </c>
@@ -9472,7 +6660,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>126041187</v>
       </c>
@@ -9510,7 +6698,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>126043144</v>
       </c>
@@ -9548,7 +6736,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>126045060</v>
       </c>
@@ -9586,7 +6774,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>126045520</v>
       </c>
@@ -9624,7 +6812,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>126049650</v>
       </c>
@@ -9662,7 +6850,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>126051286</v>
       </c>
@@ -9700,7 +6888,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>126052567</v>
       </c>
@@ -9738,7 +6926,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>126057040</v>
       </c>
@@ -9776,7 +6964,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>126057529</v>
       </c>
@@ -9814,7 +7002,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>126057835</v>
       </c>
@@ -9852,7 +7040,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>126058412</v>
       </c>
@@ -9890,7 +7078,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>126063955</v>
       </c>
@@ -9928,7 +7116,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>126064498</v>
       </c>
@@ -9966,7 +7154,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>126065211</v>
       </c>
@@ -10004,7 +7192,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>126074608</v>
       </c>
@@ -10042,7 +7230,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>126078394</v>
       </c>
@@ -10080,7 +7268,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>126080342</v>
       </c>
@@ -10118,7 +7306,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>126082448</v>
       </c>
@@ -10156,7 +7344,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>126082622</v>
       </c>
@@ -10194,7 +7382,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>126084723</v>
       </c>
@@ -10232,7 +7420,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>126086747</v>
       </c>
@@ -10270,7 +7458,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>126088025</v>
       </c>
@@ -10308,7 +7496,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>126088302</v>
       </c>
@@ -10346,7 +7534,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>126088413</v>
       </c>
@@ -10384,7 +7572,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>126088528</v>
       </c>
@@ -10422,7 +7610,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>126089277</v>
       </c>
@@ -10460,7 +7648,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>126089435</v>
       </c>
@@ -10498,7 +7686,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>126090634</v>
       </c>
@@ -10536,7 +7724,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>126093282</v>
       </c>
@@ -10574,7 +7762,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>126093649</v>
       </c>
@@ -10612,7 +7800,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>126097132</v>
       </c>
@@ -10650,7 +7838,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126098812</v>
       </c>
@@ -10688,7 +7876,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>126099189</v>
       </c>
@@ -10726,7 +7914,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>126099880</v>
       </c>
@@ -10764,7 +7952,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>126100047</v>
       </c>
@@ -10802,7 +7990,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>126101516</v>
       </c>
@@ -10840,7 +8028,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>126102394</v>
       </c>
@@ -10878,7 +8066,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>126104952</v>
       </c>
@@ -10916,7 +8104,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>126106789</v>
       </c>
@@ -10954,7 +8142,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>126111482</v>
       </c>
@@ -10992,7 +8180,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>126111872</v>
       </c>
@@ -11030,7 +8218,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>126119068</v>
       </c>
@@ -11068,7 +8256,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>126120069</v>
       </c>
@@ -11106,7 +8294,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>126120915</v>
       </c>
@@ -11144,7 +8332,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>126120976</v>
       </c>
@@ -11182,7 +8370,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>126122910</v>
       </c>
@@ -11220,7 +8408,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>126130699</v>
       </c>
@@ -11258,7 +8446,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>126131117</v>
       </c>
@@ -11296,7 +8484,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>126136404</v>
       </c>
@@ -11334,7 +8522,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>126140055</v>
       </c>
@@ -11372,7 +8560,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>126147040</v>
       </c>
@@ -11410,7 +8598,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>126155748</v>
       </c>
@@ -11448,7 +8636,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>126155838</v>
       </c>
@@ -11486,7 +8674,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>126157906</v>
       </c>
@@ -11524,7 +8712,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>126158151</v>
       </c>
@@ -11562,7 +8750,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>126162518</v>
       </c>
@@ -11600,7 +8788,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>126164369</v>
       </c>
@@ -11638,7 +8826,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>126164882</v>
       </c>
@@ -11676,7 +8864,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>126165476</v>
       </c>
@@ -11714,7 +8902,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>126165996</v>
       </c>
@@ -11752,7 +8940,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>126167070</v>
       </c>
@@ -11790,7 +8978,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>126168025</v>
       </c>
@@ -11828,7 +9016,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>126168249</v>
       </c>
@@ -11866,7 +9054,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>126173180</v>
       </c>
@@ -11904,7 +9092,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>126174316</v>
       </c>
@@ -11942,7 +9130,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>126174669</v>
       </c>
@@ -11980,7 +9168,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>126176463</v>
       </c>
@@ -12018,7 +9206,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>126176884</v>
       </c>
@@ -12056,7 +9244,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>126185047</v>
       </c>
@@ -12094,7 +9282,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>126185760</v>
       </c>
@@ -12132,7 +9320,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>126187183</v>
       </c>
@@ -12170,7 +9358,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>126187745</v>
       </c>
@@ -12208,7 +9396,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>126192174</v>
       </c>
@@ -12246,7 +9434,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>126192469</v>
       </c>
@@ -12284,7 +9472,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>126192814</v>
       </c>
@@ -12322,7 +9510,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>126193665</v>
       </c>
@@ -12360,7 +9548,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>126193855</v>
       </c>
@@ -12398,7 +9586,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>126194373</v>
       </c>
@@ -12436,7 +9624,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>126195588</v>
       </c>
@@ -12474,7 +9662,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>126197992</v>
       </c>
@@ -12512,7 +9700,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>126198450</v>
       </c>
@@ -12550,7 +9738,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>126198510</v>
       </c>
@@ -12588,7 +9776,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>126198929</v>
       </c>
@@ -12626,7 +9814,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>126201454</v>
       </c>
@@ -12664,7 +9852,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>126201460</v>
       </c>
@@ -12702,7 +9890,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>126201930</v>
       </c>
@@ -12740,7 +9928,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>126201991</v>
       </c>
@@ -12778,7 +9966,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>126212316</v>
       </c>
@@ -12816,7 +10004,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>126213617</v>
       </c>
@@ -12854,7 +10042,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>126216332</v>
       </c>
@@ -12892,7 +10080,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>126218950</v>
       </c>
@@ -12930,7 +10118,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>126230676</v>
       </c>
@@ -12968,7 +10156,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>126231536</v>
       </c>
@@ -13006,7 +10194,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>126237618</v>
       </c>
@@ -13044,7 +10232,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>126245598</v>
       </c>
@@ -13082,7 +10270,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>126265244</v>
       </c>
@@ -13120,7 +10308,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>126265499</v>
       </c>
@@ -13158,7 +10346,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>126266542</v>
       </c>
@@ -13196,7 +10384,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>126268776</v>
       </c>
@@ -13234,7 +10422,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>126280119</v>
       </c>
@@ -13272,7 +10460,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>126280477</v>
       </c>
@@ -13310,7 +10498,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>126281587</v>
       </c>
@@ -13348,7 +10536,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>126281992</v>
       </c>
@@ -13417,31 +10605,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C55651-A3DA-4B74-8A40-021D3789C898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBF77A2-4071-41AE-9521-A2BF091E2460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -623,22 +623,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>123509727</v>
+        <v>126684009</v>
       </c>
       <c r="E3">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="F3" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="G3" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -661,22 +661,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>123315700</v>
+        <v>126922025</v>
       </c>
       <c r="E4">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45356</v>
+        <v>45355</v>
       </c>
       <c r="G4" s="2">
-        <v>45356</v>
+        <v>45355</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,16 +699,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>123390235</v>
+        <v>123407776</v>
       </c>
       <c r="E5">
         <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="G5" s="2">
-        <v>45355</v>
+        <v>45358</v>
       </c>
       <c r="I5">
         <v>42</v>
@@ -737,16 +737,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>123474375</v>
+        <v>123905424</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45356</v>
+        <v>45349</v>
       </c>
       <c r="G6" s="2">
-        <v>45352</v>
+        <v>45348</v>
       </c>
       <c r="I6">
         <v>42</v>
@@ -775,16 +775,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>123513953</v>
+        <v>124052232</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="G7" s="2">
-        <v>45355</v>
+        <v>45352</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -813,16 +813,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>123694471</v>
+        <v>124263172</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="G8" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="I8">
         <v>42</v>
@@ -851,16 +851,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>123905424</v>
+        <v>124466733</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45349</v>
+        <v>45358</v>
       </c>
       <c r="G9" s="2">
-        <v>45348</v>
+        <v>45358</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -889,16 +889,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>123979478</v>
+        <v>124575725</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="G10" s="2">
-        <v>45357</v>
+        <v>45356</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -927,16 +927,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>123982935</v>
+        <v>125107629</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="G11" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -965,16 +965,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>124000737</v>
+        <v>125335581</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="G12" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>124244366</v>
+        <v>125340792</v>
       </c>
       <c r="E13">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F13" s="2">
-        <v>45356</v>
+        <v>45358</v>
       </c>
       <c r="G13" s="2">
-        <v>45356</v>
+        <v>45358</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,13 +1041,13 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>124306189</v>
+        <v>125659011</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45356</v>
+        <v>45358</v>
       </c>
       <c r="G14" s="2">
         <v>45356</v>
@@ -1079,13 +1079,13 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>124372274</v>
+        <v>125886645</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="G15" s="2">
         <v>45357</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>124466813</v>
+        <v>126038889</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="G16" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>124608580</v>
+        <v>126165789</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="G17" s="2">
-        <v>45356</v>
+        <v>45358</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>124637312</v>
+        <v>126238119</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="G18" s="2">
-        <v>45356</v>
+        <v>45358</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>124654154</v>
+        <v>126417304</v>
       </c>
       <c r="E19">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F19" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="G19" s="2">
-        <v>45352</v>
+        <v>45358</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>124654782</v>
+        <v>126556685</v>
       </c>
       <c r="E20">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="F20" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
       <c r="G20" s="2">
-        <v>45355</v>
+        <v>45358</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,22 +1307,22 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>124799236</v>
+        <v>110074933</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45356</v>
+        <v>43453</v>
       </c>
       <c r="G21" s="2">
-        <v>45351</v>
+        <v>43441</v>
       </c>
       <c r="I21">
         <v>42</v>
       </c>
       <c r="J21">
-        <v>8001</v>
+        <v>8023</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>124834065</v>
+        <v>123058958</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45357</v>
+        <v>44995</v>
       </c>
       <c r="G22" s="2">
-        <v>45356</v>
+        <v>44993</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1383,22 +1383,22 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>124839219</v>
+        <v>126825567</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45357</v>
+        <v>45346</v>
       </c>
       <c r="G23" s="2">
-        <v>45357</v>
+        <v>45345</v>
       </c>
       <c r="I23">
         <v>42</v>
       </c>
       <c r="J23">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1421,22 +1421,22 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>124882993</v>
+        <v>126855390</v>
       </c>
       <c r="E24">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F24" s="2">
-        <v>45357</v>
+        <v>45351</v>
       </c>
       <c r="G24" s="2">
-        <v>45355</v>
+        <v>45349</v>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1459,22 +1459,22 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>125018216</v>
+        <v>126859776</v>
       </c>
       <c r="E25">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F25" s="2">
-        <v>45357</v>
+        <v>45351</v>
       </c>
       <c r="G25" s="2">
-        <v>45351</v>
+        <v>45349</v>
       </c>
       <c r="I25">
         <v>42</v>
       </c>
       <c r="J25">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>125077419</v>
+        <v>126860139</v>
       </c>
       <c r="E26">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F26" s="2">
-        <v>45357</v>
+        <v>45351</v>
       </c>
       <c r="G26" s="2">
-        <v>45357</v>
+        <v>45349</v>
       </c>
       <c r="I26">
         <v>42</v>
       </c>
       <c r="J26">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>125123116</v>
+        <v>126860486</v>
       </c>
       <c r="E27">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F27" s="2">
-        <v>45357</v>
+        <v>45351</v>
       </c>
       <c r="G27" s="2">
-        <v>45356</v>
+        <v>45349</v>
       </c>
       <c r="I27">
         <v>42</v>
       </c>
       <c r="J27">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>125138510</v>
+        <v>126861555</v>
       </c>
       <c r="E28">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F28" s="2">
-        <v>45357</v>
+        <v>45351</v>
       </c>
       <c r="G28" s="2">
-        <v>45355</v>
+        <v>45349</v>
       </c>
       <c r="I28">
         <v>42</v>
       </c>
       <c r="J28">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -1611,22 +1611,22 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>125227450</v>
+        <v>126852394</v>
       </c>
       <c r="E29">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F29" s="2">
-        <v>45357</v>
+        <v>45351</v>
       </c>
       <c r="G29" s="2">
-        <v>45356</v>
+        <v>45349</v>
       </c>
       <c r="I29">
         <v>42</v>
       </c>
       <c r="J29">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>125235341</v>
+        <v>126855925</v>
       </c>
       <c r="E30">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F30" s="2">
-        <v>45356</v>
+        <v>45351</v>
       </c>
       <c r="G30" s="2">
-        <v>45356</v>
+        <v>45349</v>
       </c>
       <c r="I30">
         <v>42</v>
       </c>
       <c r="J30">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1682,842 +1682,6 @@
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>125261752</v>
-      </c>
-      <c r="E31">
-        <v>1211</v>
-      </c>
-      <c r="F31" s="2">
-        <v>45357</v>
-      </c>
-      <c r="G31" s="2">
-        <v>45356</v>
-      </c>
-      <c r="I31">
-        <v>42</v>
-      </c>
-      <c r="J31">
-        <v>8001</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>125428623</v>
-      </c>
-      <c r="E32">
-        <v>1211</v>
-      </c>
-      <c r="F32" s="2">
-        <v>45356</v>
-      </c>
-      <c r="G32" s="2">
-        <v>45356</v>
-      </c>
-      <c r="I32">
-        <v>42</v>
-      </c>
-      <c r="J32">
-        <v>8001</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>125445254</v>
-      </c>
-      <c r="E33">
-        <v>1211</v>
-      </c>
-      <c r="F33" s="2">
-        <v>45356</v>
-      </c>
-      <c r="G33" s="2">
-        <v>45356</v>
-      </c>
-      <c r="I33">
-        <v>42</v>
-      </c>
-      <c r="J33">
-        <v>8001</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>125461638</v>
-      </c>
-      <c r="E34">
-        <v>1211</v>
-      </c>
-      <c r="F34" s="2">
-        <v>45356</v>
-      </c>
-      <c r="G34" s="2">
-        <v>45356</v>
-      </c>
-      <c r="I34">
-        <v>42</v>
-      </c>
-      <c r="J34">
-        <v>8001</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>125517449</v>
-      </c>
-      <c r="E35">
-        <v>1211</v>
-      </c>
-      <c r="F35" s="2">
-        <v>45356</v>
-      </c>
-      <c r="G35" s="2">
-        <v>45356</v>
-      </c>
-      <c r="I35">
-        <v>42</v>
-      </c>
-      <c r="J35">
-        <v>8001</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>125607366</v>
-      </c>
-      <c r="E36">
-        <v>1211</v>
-      </c>
-      <c r="F36" s="2">
-        <v>45356</v>
-      </c>
-      <c r="G36" s="2">
-        <v>45356</v>
-      </c>
-      <c r="I36">
-        <v>42</v>
-      </c>
-      <c r="J36">
-        <v>8001</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>125780949</v>
-      </c>
-      <c r="E37">
-        <v>1212</v>
-      </c>
-      <c r="F37" s="2">
-        <v>45357</v>
-      </c>
-      <c r="G37" s="2">
-        <v>45357</v>
-      </c>
-      <c r="I37">
-        <v>42</v>
-      </c>
-      <c r="J37">
-        <v>8001</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>125935525</v>
-      </c>
-      <c r="E38">
-        <v>1212</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45357</v>
-      </c>
-      <c r="G38" s="2">
-        <v>45357</v>
-      </c>
-      <c r="I38">
-        <v>42</v>
-      </c>
-      <c r="J38">
-        <v>8001</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>126356343</v>
-      </c>
-      <c r="E39">
-        <v>1211</v>
-      </c>
-      <c r="F39" s="2">
-        <v>45356</v>
-      </c>
-      <c r="G39" s="2">
-        <v>45356</v>
-      </c>
-      <c r="I39">
-        <v>42</v>
-      </c>
-      <c r="J39">
-        <v>8001</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>126359415</v>
-      </c>
-      <c r="E40">
-        <v>1211</v>
-      </c>
-      <c r="F40" s="2">
-        <v>45357</v>
-      </c>
-      <c r="G40" s="2">
-        <v>45356</v>
-      </c>
-      <c r="I40">
-        <v>42</v>
-      </c>
-      <c r="J40">
-        <v>8001</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>126446445</v>
-      </c>
-      <c r="E41">
-        <v>1211</v>
-      </c>
-      <c r="F41" s="2">
-        <v>45357</v>
-      </c>
-      <c r="G41" s="2">
-        <v>45355</v>
-      </c>
-      <c r="I41">
-        <v>42</v>
-      </c>
-      <c r="J41">
-        <v>8001</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>126460685</v>
-      </c>
-      <c r="E42">
-        <v>1211</v>
-      </c>
-      <c r="F42" s="2">
-        <v>45356</v>
-      </c>
-      <c r="G42" s="2">
-        <v>45351</v>
-      </c>
-      <c r="I42">
-        <v>42</v>
-      </c>
-      <c r="J42">
-        <v>8001</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>126479200</v>
-      </c>
-      <c r="E43">
-        <v>1211</v>
-      </c>
-      <c r="F43" s="2">
-        <v>45357</v>
-      </c>
-      <c r="G43" s="2">
-        <v>45355</v>
-      </c>
-      <c r="I43">
-        <v>42</v>
-      </c>
-      <c r="J43">
-        <v>8001</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>126558715</v>
-      </c>
-      <c r="E44">
-        <v>1211</v>
-      </c>
-      <c r="F44" s="2">
-        <v>45356</v>
-      </c>
-      <c r="G44" s="2">
-        <v>45356</v>
-      </c>
-      <c r="I44">
-        <v>42</v>
-      </c>
-      <c r="J44">
-        <v>8001</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="Q44">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>126697982</v>
-      </c>
-      <c r="E45">
-        <v>1211</v>
-      </c>
-      <c r="F45" s="2">
-        <v>45356</v>
-      </c>
-      <c r="G45" s="2">
-        <v>45356</v>
-      </c>
-      <c r="I45">
-        <v>42</v>
-      </c>
-      <c r="J45">
-        <v>8001</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
-      <c r="P45">
-        <v>0</v>
-      </c>
-      <c r="Q45">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>126749429</v>
-      </c>
-      <c r="E46">
-        <v>1211</v>
-      </c>
-      <c r="F46" s="2">
-        <v>45356</v>
-      </c>
-      <c r="G46" s="2">
-        <v>45356</v>
-      </c>
-      <c r="I46">
-        <v>42</v>
-      </c>
-      <c r="J46">
-        <v>8001</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>126823927</v>
-      </c>
-      <c r="E47">
-        <v>1211</v>
-      </c>
-      <c r="F47" s="2">
-        <v>45357</v>
-      </c>
-      <c r="G47" s="2">
-        <v>45356</v>
-      </c>
-      <c r="I47">
-        <v>42</v>
-      </c>
-      <c r="J47">
-        <v>8001</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>126916876</v>
-      </c>
-      <c r="E48">
-        <v>1211</v>
-      </c>
-      <c r="F48" s="2">
-        <v>45356</v>
-      </c>
-      <c r="G48" s="2">
-        <v>45356</v>
-      </c>
-      <c r="I48">
-        <v>42</v>
-      </c>
-      <c r="J48">
-        <v>8001</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A49">
-        <v>110074933</v>
-      </c>
-      <c r="E49">
-        <v>1211</v>
-      </c>
-      <c r="F49" s="2">
-        <v>43453</v>
-      </c>
-      <c r="G49" s="2">
-        <v>43441</v>
-      </c>
-      <c r="I49">
-        <v>42</v>
-      </c>
-      <c r="J49">
-        <v>8023</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>123058958</v>
-      </c>
-      <c r="E50">
-        <v>1211</v>
-      </c>
-      <c r="F50" s="2">
-        <v>44995</v>
-      </c>
-      <c r="G50" s="2">
-        <v>44993</v>
-      </c>
-      <c r="I50">
-        <v>42</v>
-      </c>
-      <c r="J50">
-        <v>8001</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>126825567</v>
-      </c>
-      <c r="E51">
-        <v>1211</v>
-      </c>
-      <c r="F51" s="2">
-        <v>45346</v>
-      </c>
-      <c r="G51" s="2">
-        <v>45345</v>
-      </c>
-      <c r="I51">
-        <v>42</v>
-      </c>
-      <c r="J51">
-        <v>8021</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>0</v>
-      </c>
-      <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A52">
-        <v>126764334</v>
-      </c>
-      <c r="E52">
-        <v>601</v>
-      </c>
-      <c r="F52" s="2">
-        <v>45348</v>
-      </c>
-      <c r="G52" s="2">
-        <v>45348</v>
-      </c>
-      <c r="I52">
-        <v>42</v>
-      </c>
-      <c r="J52">
-        <v>8004</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
-        <v>0</v>
-      </c>
-      <c r="P52">
-        <v>0</v>
-      </c>
-      <c r="Q52">
         <v>61</v>
       </c>
     </row>

--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498140A2-D104-4D48-B7B3-9892C2230183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02026370-72AB-4019-A29E-C3B175FEE8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q99"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,22 +585,22 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>124761942</v>
+        <v>124820227</v>
       </c>
       <c r="E2">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="F2" s="2">
-        <v>45365</v>
+        <v>45368</v>
       </c>
       <c r="G2" s="2">
-        <v>45365</v>
+        <v>45368</v>
       </c>
       <c r="I2">
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -623,22 +623,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>126992445</v>
+        <v>126906719</v>
       </c>
       <c r="E3">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F3" s="2">
-        <v>45362</v>
+        <v>45366</v>
       </c>
       <c r="G3" s="2">
-        <v>45362</v>
+        <v>45366</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -661,22 +661,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>126998488</v>
+        <v>127023912</v>
       </c>
       <c r="E4">
-        <v>1211</v>
+        <v>2013</v>
       </c>
       <c r="F4" s="2">
-        <v>45362</v>
+        <v>45366</v>
       </c>
       <c r="G4" s="2">
-        <v>45362</v>
+        <v>45366</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,22 +699,22 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>123401230</v>
+        <v>126125943</v>
       </c>
       <c r="E5">
-        <v>1211</v>
+        <v>2002</v>
       </c>
       <c r="F5" s="2">
-        <v>45365</v>
+        <v>45368</v>
       </c>
       <c r="G5" s="2">
-        <v>45359</v>
+        <v>45366</v>
       </c>
       <c r="I5">
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,22 +737,22 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>123424628</v>
+        <v>127013520</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45365</v>
+        <v>45363</v>
       </c>
       <c r="G6" s="2">
-        <v>45365</v>
+        <v>45363</v>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -775,22 +775,22 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>123458617</v>
+        <v>127015049</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45365</v>
+        <v>45364</v>
       </c>
       <c r="G7" s="2">
-        <v>45365</v>
+        <v>45363</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -813,7 +813,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>123494302</v>
+        <v>127015472</v>
       </c>
       <c r="E8">
         <v>1211</v>
@@ -822,13 +822,13 @@
         <v>45365</v>
       </c>
       <c r="G8" s="2">
-        <v>45365</v>
+        <v>45363</v>
       </c>
       <c r="I8">
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -851,22 +851,22 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>123565605</v>
+        <v>127020951</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45365</v>
+        <v>45364</v>
       </c>
       <c r="G9" s="2">
-        <v>45365</v>
+        <v>45364</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -889,22 +889,22 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>123743141</v>
+        <v>127026866</v>
       </c>
       <c r="E10">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45365</v>
+        <v>45364</v>
       </c>
       <c r="G10" s="2">
-        <v>45365</v>
+        <v>45364</v>
       </c>
       <c r="I10">
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -927,22 +927,22 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>123767716</v>
+        <v>127033828</v>
       </c>
       <c r="E11">
         <v>1212</v>
       </c>
       <c r="F11" s="2">
+        <v>45366</v>
+      </c>
+      <c r="G11" s="2">
         <v>45365</v>
       </c>
-      <c r="G11" s="2">
-        <v>45364</v>
-      </c>
       <c r="I11">
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -965,7 +965,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>123927588</v>
+        <v>127034446</v>
       </c>
       <c r="E12">
         <v>1211</v>
@@ -974,13 +974,13 @@
         <v>45365</v>
       </c>
       <c r="G12" s="2">
-        <v>45364</v>
+        <v>45365</v>
       </c>
       <c r="I12">
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>124010501</v>
+        <v>127034694</v>
       </c>
       <c r="E13">
         <v>1211</v>
@@ -1018,7 +1018,7 @@
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1041,13 +1041,13 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>124143510</v>
+        <v>127036981</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G14" s="2">
         <v>45365</v>
@@ -1056,7 +1056,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>124205060</v>
+        <v>127038650</v>
       </c>
       <c r="E15">
         <v>1211</v>
@@ -1094,7 +1094,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1117,13 +1117,13 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>124206435</v>
+        <v>127042599</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G16" s="2">
         <v>45365</v>
@@ -1132,7 +1132,7 @@
         <v>42</v>
       </c>
       <c r="J16">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1155,13 +1155,13 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>124222912</v>
+        <v>127044056</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G17" s="2">
         <v>45365</v>
@@ -1170,7 +1170,7 @@
         <v>42</v>
       </c>
       <c r="J17">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>124450225</v>
+        <v>123623857</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G18" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>124750975</v>
+        <v>123681216</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
+        <v>45366</v>
+      </c>
+      <c r="G19" s="2">
         <v>45365</v>
-      </c>
-      <c r="G19" s="2">
-        <v>45364</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>124835141</v>
+        <v>123852974</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G20" s="2">
-        <v>45364</v>
+        <v>45366</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,13 +1307,13 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>124937983</v>
+        <v>124160286</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G21" s="2">
         <v>45365</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>125123914</v>
+        <v>124184342</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G22" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1383,16 +1383,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>125261492</v>
+        <v>124262561</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G23" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1421,16 +1421,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>125414225</v>
+        <v>124387163</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G24" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1459,16 +1459,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>125438756</v>
+        <v>124459458</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G25" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="I25">
         <v>42</v>
@@ -1497,16 +1497,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>125475423</v>
+        <v>124472086</v>
       </c>
       <c r="E26">
         <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45365</v>
+        <v>45367</v>
       </c>
       <c r="G26" s="2">
-        <v>45365</v>
+        <v>45367</v>
       </c>
       <c r="I26">
         <v>42</v>
@@ -1535,16 +1535,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>125591990</v>
+        <v>124520773</v>
       </c>
       <c r="E27">
         <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G27" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="I27">
         <v>42</v>
@@ -1573,16 +1573,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>125593594</v>
+        <v>124579045</v>
       </c>
       <c r="E28">
         <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45365</v>
+        <v>45367</v>
       </c>
       <c r="G28" s="2">
-        <v>45365</v>
+        <v>45367</v>
       </c>
       <c r="I28">
         <v>42</v>
@@ -1611,16 +1611,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>125833166</v>
+        <v>124600805</v>
       </c>
       <c r="E29">
         <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G29" s="2">
-        <v>45363</v>
+        <v>45366</v>
       </c>
       <c r="I29">
         <v>42</v>
@@ -1649,16 +1649,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>126027163</v>
+        <v>124627204</v>
       </c>
       <c r="E30">
         <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G30" s="2">
-        <v>45365</v>
+        <v>45363</v>
       </c>
       <c r="I30">
         <v>42</v>
@@ -1687,16 +1687,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>126065260</v>
+        <v>124731324</v>
       </c>
       <c r="E31">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G31" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="I31">
         <v>42</v>
@@ -1725,16 +1725,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>126084232</v>
+        <v>124764762</v>
       </c>
       <c r="E32">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G32" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="I32">
         <v>42</v>
@@ -1763,16 +1763,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>126323856</v>
+        <v>124781356</v>
       </c>
       <c r="E33">
         <v>1211</v>
       </c>
       <c r="F33" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G33" s="2">
-        <v>45362</v>
+        <v>45366</v>
       </c>
       <c r="I33">
         <v>42</v>
@@ -1801,16 +1801,16 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>126334088</v>
+        <v>124812940</v>
       </c>
       <c r="E34">
         <v>1212</v>
       </c>
       <c r="F34" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G34" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="I34">
         <v>42</v>
@@ -1839,16 +1839,16 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>126633077</v>
+        <v>124910896</v>
       </c>
       <c r="E35">
         <v>1211</v>
       </c>
       <c r="F35" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G35" s="2">
-        <v>45362</v>
+        <v>45366</v>
       </c>
       <c r="I35">
         <v>42</v>
@@ -1877,16 +1877,16 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>126783228</v>
+        <v>124938011</v>
       </c>
       <c r="E36">
         <v>1211</v>
       </c>
       <c r="F36" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="G36" s="2">
-        <v>45362</v>
+        <v>45366</v>
       </c>
       <c r="I36">
         <v>42</v>
@@ -1915,22 +1915,22 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>110074933</v>
+        <v>125106973</v>
       </c>
       <c r="E37">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F37" s="2">
-        <v>43453</v>
+        <v>45367</v>
       </c>
       <c r="G37" s="2">
-        <v>43441</v>
+        <v>45365</v>
       </c>
       <c r="I37">
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8023</v>
+        <v>8001</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -1953,16 +1953,16 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>123058958</v>
+        <v>125178953</v>
       </c>
       <c r="E38">
         <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>44995</v>
+        <v>45366</v>
       </c>
       <c r="G38" s="2">
-        <v>44993</v>
+        <v>45365</v>
       </c>
       <c r="I38">
         <v>42</v>
@@ -1991,22 +1991,22 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>126925740</v>
+        <v>125362668</v>
       </c>
       <c r="E39">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F39" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="G39" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="I39">
         <v>42</v>
       </c>
       <c r="J39">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>126926200</v>
+        <v>125398626</v>
       </c>
       <c r="E40">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F40" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="G40" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="I40">
         <v>42</v>
       </c>
       <c r="J40">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2067,22 +2067,22 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>126927286</v>
+        <v>125528692</v>
       </c>
       <c r="E41">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F41" s="2">
-        <v>45356</v>
+        <v>45367</v>
       </c>
       <c r="G41" s="2">
-        <v>45356</v>
+        <v>45367</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>126928500</v>
+        <v>125581178</v>
       </c>
       <c r="E42">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F42" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="G42" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2143,22 +2143,22 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>126931640</v>
+        <v>125694838</v>
       </c>
       <c r="E43">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F43" s="2">
-        <v>45364</v>
+        <v>45367</v>
       </c>
       <c r="G43" s="2">
-        <v>45356</v>
+        <v>45367</v>
       </c>
       <c r="I43">
         <v>42</v>
       </c>
       <c r="J43">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>126932043</v>
+        <v>125750100</v>
       </c>
       <c r="E44">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F44" s="2">
-        <v>45356</v>
+        <v>45368</v>
       </c>
       <c r="G44" s="2">
-        <v>45356</v>
+        <v>45365</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2219,22 +2219,22 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>126933913</v>
+        <v>125897697</v>
       </c>
       <c r="E45">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F45" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="G45" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="I45">
         <v>42</v>
       </c>
       <c r="J45">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>126933916</v>
+        <v>126118862</v>
       </c>
       <c r="E46">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F46" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="G46" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="I46">
         <v>42</v>
       </c>
       <c r="J46">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2295,22 +2295,22 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>126933917</v>
+        <v>126193337</v>
       </c>
       <c r="E47">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F47" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="G47" s="2">
-        <v>45356</v>
+        <v>45362</v>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2333,22 +2333,22 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>126933922</v>
+        <v>126438888</v>
       </c>
       <c r="E48">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F48" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="G48" s="2">
-        <v>45356</v>
+        <v>45365</v>
       </c>
       <c r="I48">
         <v>42</v>
       </c>
       <c r="J48">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2371,22 +2371,22 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>126934349</v>
+        <v>126532970</v>
       </c>
       <c r="E49">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F49" s="2">
+        <v>45366</v>
+      </c>
+      <c r="G49" s="2">
         <v>45363</v>
       </c>
-      <c r="G49" s="2">
-        <v>45356</v>
-      </c>
       <c r="I49">
         <v>42</v>
       </c>
       <c r="J49">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>126934601</v>
+        <v>126570156</v>
       </c>
       <c r="E50">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F50" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="G50" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="I50">
         <v>42</v>
       </c>
       <c r="J50">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2447,22 +2447,22 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>126937642</v>
+        <v>126602202</v>
       </c>
       <c r="E51">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F51" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="G51" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="I51">
         <v>42</v>
       </c>
       <c r="J51">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2485,22 +2485,22 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>126932338</v>
+        <v>126947295</v>
       </c>
       <c r="E52">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F52" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="G52" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="I52">
         <v>42</v>
       </c>
       <c r="J52">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>126932394</v>
+        <v>127004373</v>
       </c>
       <c r="E53">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F53" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="G53" s="2">
-        <v>45356</v>
+        <v>45366</v>
       </c>
       <c r="I53">
         <v>42</v>
       </c>
       <c r="J53">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -2561,22 +2561,22 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>126933890</v>
+        <v>110074933</v>
       </c>
       <c r="E54">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F54" s="2">
-        <v>45356</v>
+        <v>43453</v>
       </c>
       <c r="G54" s="2">
-        <v>45356</v>
+        <v>43441</v>
       </c>
       <c r="I54">
         <v>42</v>
       </c>
       <c r="J54">
-        <v>8004</v>
+        <v>8023</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -2599,22 +2599,22 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>126934978</v>
+        <v>123058958</v>
       </c>
       <c r="E55">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F55" s="2">
-        <v>45356</v>
+        <v>44995</v>
       </c>
       <c r="G55" s="2">
-        <v>45356</v>
+        <v>44993</v>
       </c>
       <c r="I55">
         <v>42</v>
       </c>
       <c r="J55">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -2632,6 +2632,1678 @@
         <v>0</v>
       </c>
       <c r="Q55">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>124370622</v>
+      </c>
+      <c r="E56">
+        <v>601</v>
+      </c>
+      <c r="F56" s="2">
+        <v>45359</v>
+      </c>
+      <c r="G56" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I56">
+        <v>42</v>
+      </c>
+      <c r="J56">
+        <v>8017</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>126943461</v>
+      </c>
+      <c r="E57">
+        <v>601</v>
+      </c>
+      <c r="F57" s="2">
+        <v>45357</v>
+      </c>
+      <c r="G57" s="2">
+        <v>45357</v>
+      </c>
+      <c r="I57">
+        <v>42</v>
+      </c>
+      <c r="J57">
+        <v>8004</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>126946898</v>
+      </c>
+      <c r="E58">
+        <v>601</v>
+      </c>
+      <c r="F58" s="2">
+        <v>45357</v>
+      </c>
+      <c r="G58" s="2">
+        <v>45357</v>
+      </c>
+      <c r="I58">
+        <v>42</v>
+      </c>
+      <c r="J58">
+        <v>8004</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>126948378</v>
+      </c>
+      <c r="E59">
+        <v>601</v>
+      </c>
+      <c r="F59" s="2">
+        <v>45357</v>
+      </c>
+      <c r="G59" s="2">
+        <v>45357</v>
+      </c>
+      <c r="I59">
+        <v>42</v>
+      </c>
+      <c r="J59">
+        <v>8004</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>126948381</v>
+      </c>
+      <c r="E60">
+        <v>601</v>
+      </c>
+      <c r="F60" s="2">
+        <v>45357</v>
+      </c>
+      <c r="G60" s="2">
+        <v>45357</v>
+      </c>
+      <c r="I60">
+        <v>42</v>
+      </c>
+      <c r="J60">
+        <v>8004</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>126949742</v>
+      </c>
+      <c r="E61">
+        <v>601</v>
+      </c>
+      <c r="F61" s="2">
+        <v>45357</v>
+      </c>
+      <c r="G61" s="2">
+        <v>45357</v>
+      </c>
+      <c r="I61">
+        <v>42</v>
+      </c>
+      <c r="J61">
+        <v>8004</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>126954503</v>
+      </c>
+      <c r="E62">
+        <v>601</v>
+      </c>
+      <c r="F62" s="2">
+        <v>45358</v>
+      </c>
+      <c r="G62" s="2">
+        <v>45358</v>
+      </c>
+      <c r="I62">
+        <v>42</v>
+      </c>
+      <c r="J62">
+        <v>8004</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>126955098</v>
+      </c>
+      <c r="E63">
+        <v>601</v>
+      </c>
+      <c r="F63" s="2">
+        <v>45363</v>
+      </c>
+      <c r="G63" s="2">
+        <v>45358</v>
+      </c>
+      <c r="I63">
+        <v>42</v>
+      </c>
+      <c r="J63">
+        <v>8013</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>126960328</v>
+      </c>
+      <c r="E64">
+        <v>609</v>
+      </c>
+      <c r="F64" s="2">
+        <v>45358</v>
+      </c>
+      <c r="G64" s="2">
+        <v>45358</v>
+      </c>
+      <c r="I64">
+        <v>42</v>
+      </c>
+      <c r="J64">
+        <v>8004</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>126964730</v>
+      </c>
+      <c r="E65">
+        <v>601</v>
+      </c>
+      <c r="F65" s="2">
+        <v>45358</v>
+      </c>
+      <c r="G65" s="2">
+        <v>45358</v>
+      </c>
+      <c r="I65">
+        <v>42</v>
+      </c>
+      <c r="J65">
+        <v>8004</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>126965157</v>
+      </c>
+      <c r="E66">
+        <v>601</v>
+      </c>
+      <c r="F66" s="2">
+        <v>45358</v>
+      </c>
+      <c r="G66" s="2">
+        <v>45358</v>
+      </c>
+      <c r="I66">
+        <v>42</v>
+      </c>
+      <c r="J66">
+        <v>8004</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>126969304</v>
+      </c>
+      <c r="E67">
+        <v>601</v>
+      </c>
+      <c r="F67" s="2">
+        <v>45359</v>
+      </c>
+      <c r="G67" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I67">
+        <v>42</v>
+      </c>
+      <c r="J67">
+        <v>1118</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>126975183</v>
+      </c>
+      <c r="E68">
+        <v>601</v>
+      </c>
+      <c r="F68" s="2">
+        <v>45367</v>
+      </c>
+      <c r="G68" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I68">
+        <v>42</v>
+      </c>
+      <c r="J68">
+        <v>8013</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>126975483</v>
+      </c>
+      <c r="E69">
+        <v>601</v>
+      </c>
+      <c r="F69" s="2">
+        <v>45367</v>
+      </c>
+      <c r="G69" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I69">
+        <v>42</v>
+      </c>
+      <c r="J69">
+        <v>8013</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>126976747</v>
+      </c>
+      <c r="E70">
+        <v>601</v>
+      </c>
+      <c r="F70" s="2">
+        <v>45363</v>
+      </c>
+      <c r="G70" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I70">
+        <v>42</v>
+      </c>
+      <c r="J70">
+        <v>8013</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>126979036</v>
+      </c>
+      <c r="E71">
+        <v>601</v>
+      </c>
+      <c r="F71" s="2">
+        <v>45363</v>
+      </c>
+      <c r="G71" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I71">
+        <v>42</v>
+      </c>
+      <c r="J71">
+        <v>8013</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>126979078</v>
+      </c>
+      <c r="E72">
+        <v>601</v>
+      </c>
+      <c r="F72" s="2">
+        <v>45363</v>
+      </c>
+      <c r="G72" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I72">
+        <v>42</v>
+      </c>
+      <c r="J72">
+        <v>8013</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>126979144</v>
+      </c>
+      <c r="E73">
+        <v>601</v>
+      </c>
+      <c r="F73" s="2">
+        <v>45365</v>
+      </c>
+      <c r="G73" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I73">
+        <v>42</v>
+      </c>
+      <c r="J73">
+        <v>8013</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>126979470</v>
+      </c>
+      <c r="E74">
+        <v>601</v>
+      </c>
+      <c r="F74" s="2">
+        <v>45359</v>
+      </c>
+      <c r="G74" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I74">
+        <v>42</v>
+      </c>
+      <c r="J74">
+        <v>8004</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>126979547</v>
+      </c>
+      <c r="E75">
+        <v>601</v>
+      </c>
+      <c r="F75" s="2">
+        <v>45365</v>
+      </c>
+      <c r="G75" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I75">
+        <v>42</v>
+      </c>
+      <c r="J75">
+        <v>8013</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>126979756</v>
+      </c>
+      <c r="E76">
+        <v>601</v>
+      </c>
+      <c r="F76" s="2">
+        <v>45363</v>
+      </c>
+      <c r="G76" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I76">
+        <v>42</v>
+      </c>
+      <c r="J76">
+        <v>8013</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>126980591</v>
+      </c>
+      <c r="E77">
+        <v>601</v>
+      </c>
+      <c r="F77" s="2">
+        <v>45363</v>
+      </c>
+      <c r="G77" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I77">
+        <v>42</v>
+      </c>
+      <c r="J77">
+        <v>8013</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>126980895</v>
+      </c>
+      <c r="E78">
+        <v>601</v>
+      </c>
+      <c r="F78" s="2">
+        <v>45359</v>
+      </c>
+      <c r="G78" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I78">
+        <v>42</v>
+      </c>
+      <c r="J78">
+        <v>8013</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>126982225</v>
+      </c>
+      <c r="E79">
+        <v>601</v>
+      </c>
+      <c r="F79" s="2">
+        <v>45359</v>
+      </c>
+      <c r="G79" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I79">
+        <v>42</v>
+      </c>
+      <c r="J79">
+        <v>8013</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>126983524</v>
+      </c>
+      <c r="E80">
+        <v>601</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45359</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I80">
+        <v>42</v>
+      </c>
+      <c r="J80">
+        <v>8004</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>126983612</v>
+      </c>
+      <c r="E81">
+        <v>601</v>
+      </c>
+      <c r="F81" s="2">
+        <v>45359</v>
+      </c>
+      <c r="G81" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I81">
+        <v>42</v>
+      </c>
+      <c r="J81">
+        <v>8004</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>126983689</v>
+      </c>
+      <c r="E82">
+        <v>601</v>
+      </c>
+      <c r="F82" s="2">
+        <v>45359</v>
+      </c>
+      <c r="G82" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I82">
+        <v>42</v>
+      </c>
+      <c r="J82">
+        <v>8004</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>126983875</v>
+      </c>
+      <c r="E83">
+        <v>601</v>
+      </c>
+      <c r="F83" s="2">
+        <v>45363</v>
+      </c>
+      <c r="G83" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I83">
+        <v>42</v>
+      </c>
+      <c r="J83">
+        <v>8013</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>126946898</v>
+      </c>
+      <c r="E84">
+        <v>601</v>
+      </c>
+      <c r="F84" s="2">
+        <v>45357</v>
+      </c>
+      <c r="G84" s="2">
+        <v>45357</v>
+      </c>
+      <c r="I84">
+        <v>42</v>
+      </c>
+      <c r="J84">
+        <v>8004</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>126949456</v>
+      </c>
+      <c r="E85">
+        <v>601</v>
+      </c>
+      <c r="F85" s="2">
+        <v>45357</v>
+      </c>
+      <c r="G85" s="2">
+        <v>45357</v>
+      </c>
+      <c r="I85">
+        <v>42</v>
+      </c>
+      <c r="J85">
+        <v>1118</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>126950702</v>
+      </c>
+      <c r="E86">
+        <v>601</v>
+      </c>
+      <c r="F86" s="2">
+        <v>45357</v>
+      </c>
+      <c r="G86" s="2">
+        <v>45357</v>
+      </c>
+      <c r="I86">
+        <v>42</v>
+      </c>
+      <c r="J86">
+        <v>8004</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>126951505</v>
+      </c>
+      <c r="E87">
+        <v>601</v>
+      </c>
+      <c r="F87" s="2">
+        <v>45357</v>
+      </c>
+      <c r="G87" s="2">
+        <v>45357</v>
+      </c>
+      <c r="I87">
+        <v>42</v>
+      </c>
+      <c r="J87">
+        <v>8004</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>126955025</v>
+      </c>
+      <c r="E88">
+        <v>601</v>
+      </c>
+      <c r="F88" s="2">
+        <v>45358</v>
+      </c>
+      <c r="G88" s="2">
+        <v>45358</v>
+      </c>
+      <c r="I88">
+        <v>42</v>
+      </c>
+      <c r="J88">
+        <v>8004</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>126957094</v>
+      </c>
+      <c r="E89">
+        <v>601</v>
+      </c>
+      <c r="F89" s="2">
+        <v>45358</v>
+      </c>
+      <c r="G89" s="2">
+        <v>45358</v>
+      </c>
+      <c r="I89">
+        <v>42</v>
+      </c>
+      <c r="J89">
+        <v>8004</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>126957504</v>
+      </c>
+      <c r="E90">
+        <v>601</v>
+      </c>
+      <c r="F90" s="2">
+        <v>45358</v>
+      </c>
+      <c r="G90" s="2">
+        <v>45358</v>
+      </c>
+      <c r="I90">
+        <v>42</v>
+      </c>
+      <c r="J90">
+        <v>8004</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>126961745</v>
+      </c>
+      <c r="E91">
+        <v>601</v>
+      </c>
+      <c r="F91" s="2">
+        <v>45358</v>
+      </c>
+      <c r="G91" s="2">
+        <v>45358</v>
+      </c>
+      <c r="I91">
+        <v>42</v>
+      </c>
+      <c r="J91">
+        <v>8004</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>126962754</v>
+      </c>
+      <c r="E92">
+        <v>601</v>
+      </c>
+      <c r="F92" s="2">
+        <v>45358</v>
+      </c>
+      <c r="G92" s="2">
+        <v>45358</v>
+      </c>
+      <c r="I92">
+        <v>42</v>
+      </c>
+      <c r="J92">
+        <v>8004</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>126963085</v>
+      </c>
+      <c r="E93">
+        <v>601</v>
+      </c>
+      <c r="F93" s="2">
+        <v>45358</v>
+      </c>
+      <c r="G93" s="2">
+        <v>45358</v>
+      </c>
+      <c r="I93">
+        <v>42</v>
+      </c>
+      <c r="J93">
+        <v>8004</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>126964052</v>
+      </c>
+      <c r="E94">
+        <v>601</v>
+      </c>
+      <c r="F94" s="2">
+        <v>45358</v>
+      </c>
+      <c r="G94" s="2">
+        <v>45358</v>
+      </c>
+      <c r="I94">
+        <v>42</v>
+      </c>
+      <c r="J94">
+        <v>8004</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>126976812</v>
+      </c>
+      <c r="E95">
+        <v>601</v>
+      </c>
+      <c r="F95" s="2">
+        <v>45359</v>
+      </c>
+      <c r="G95" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I95">
+        <v>42</v>
+      </c>
+      <c r="J95">
+        <v>8004</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>126980644</v>
+      </c>
+      <c r="E96">
+        <v>601</v>
+      </c>
+      <c r="F96" s="2">
+        <v>45359</v>
+      </c>
+      <c r="G96" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I96">
+        <v>42</v>
+      </c>
+      <c r="J96">
+        <v>8004</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>126981354</v>
+      </c>
+      <c r="E97">
+        <v>601</v>
+      </c>
+      <c r="F97" s="2">
+        <v>45359</v>
+      </c>
+      <c r="G97" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I97">
+        <v>42</v>
+      </c>
+      <c r="J97">
+        <v>8004</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>126981636</v>
+      </c>
+      <c r="E98">
+        <v>601</v>
+      </c>
+      <c r="F98" s="2">
+        <v>45359</v>
+      </c>
+      <c r="G98" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I98">
+        <v>42</v>
+      </c>
+      <c r="J98">
+        <v>8004</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>126981723</v>
+      </c>
+      <c r="E99">
+        <v>601</v>
+      </c>
+      <c r="F99" s="2">
+        <v>45359</v>
+      </c>
+      <c r="G99" s="2">
+        <v>45359</v>
+      </c>
+      <c r="I99">
+        <v>42</v>
+      </c>
+      <c r="J99">
+        <v>8004</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
         <v>61</v>
       </c>
     </row>
@@ -10225,31 +11897,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FAE837-214F-4172-B2C9-C8E9D642B92C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E22055-19E3-4C74-AF87-BCE0C1AFA14A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,22 +585,22 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>125356838</v>
+        <v>127018072</v>
       </c>
       <c r="E2">
-        <v>2013</v>
+        <v>2002</v>
       </c>
       <c r="F2" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G2" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I2">
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -623,22 +623,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>126250189</v>
+        <v>127084910</v>
       </c>
       <c r="E3">
-        <v>2013</v>
+        <v>2002</v>
       </c>
       <c r="F3" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G3" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -661,22 +661,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>127142596</v>
+        <v>123685720</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45374</v>
+        <v>45378</v>
       </c>
       <c r="G4" s="2">
-        <v>45374</v>
+        <v>45378</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,16 +699,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>123398129</v>
+        <v>123764361</v>
       </c>
       <c r="E5">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F5" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G5" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I5">
         <v>42</v>
@@ -737,16 +737,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>123463093</v>
+        <v>124098769</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G6" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I6">
         <v>42</v>
@@ -775,16 +775,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>123611183</v>
+        <v>124188427</v>
       </c>
       <c r="E7">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F7" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G7" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -813,16 +813,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>123627014</v>
+        <v>124468317</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G8" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I8">
         <v>42</v>
@@ -851,16 +851,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>123763483</v>
+        <v>124507548</v>
       </c>
       <c r="E9">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G9" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -889,16 +889,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>123955687</v>
+        <v>124729093</v>
       </c>
       <c r="E10">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F10" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G10" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -927,16 +927,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>124017072</v>
+        <v>124754144</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G11" s="2">
-        <v>45376</v>
+        <v>45378</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -965,16 +965,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>124095104</v>
+        <v>124813626</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G12" s="2">
-        <v>45376</v>
+        <v>45378</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>124191722</v>
+        <v>125004501</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G13" s="2">
-        <v>45376</v>
+        <v>45378</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>124204923</v>
+        <v>125353166</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
+        <v>45378</v>
+      </c>
+      <c r="G14" s="2">
         <v>45377</v>
-      </c>
-      <c r="G14" s="2">
-        <v>45376</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>124353490</v>
+        <v>125382470</v>
       </c>
       <c r="E15">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F15" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G15" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>124379529</v>
+        <v>125407382</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G16" s="2">
-        <v>45374</v>
+        <v>45378</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>124544550</v>
+        <v>125411073</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G17" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>124662665</v>
+        <v>125519194</v>
       </c>
       <c r="E18">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G18" s="2">
-        <v>45377</v>
+        <v>45376</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>124672527</v>
+        <v>125564339</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G19" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>124797731</v>
+        <v>125570845</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G20" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>124892243</v>
+        <v>125870768</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G21" s="2">
-        <v>45376</v>
+        <v>45378</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>124905131</v>
+        <v>125977738</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G22" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1383,16 +1383,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>124911434</v>
+        <v>126063867</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G23" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1421,16 +1421,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>124977044</v>
+        <v>126342887</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G24" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1459,16 +1459,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>124987526</v>
+        <v>126482307</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G25" s="2">
-        <v>45376</v>
+        <v>45378</v>
       </c>
       <c r="I25">
         <v>42</v>
@@ -1497,16 +1497,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>125013901</v>
+        <v>126591047</v>
       </c>
       <c r="E26">
         <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G26" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I26">
         <v>42</v>
@@ -1535,16 +1535,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>125061928</v>
+        <v>126705292</v>
       </c>
       <c r="E27">
         <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G27" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I27">
         <v>42</v>
@@ -1573,16 +1573,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>125172613</v>
+        <v>126806700</v>
       </c>
       <c r="E28">
         <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G28" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I28">
         <v>42</v>
@@ -1611,16 +1611,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>125363093</v>
+        <v>126887241</v>
       </c>
       <c r="E29">
         <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="G29" s="2">
-        <v>45377</v>
+        <v>45378</v>
       </c>
       <c r="I29">
         <v>42</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>125370486</v>
+        <v>110074933</v>
       </c>
       <c r="E30">
         <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45377</v>
+        <v>43453</v>
       </c>
       <c r="G30" s="2">
-        <v>45377</v>
+        <v>43441</v>
       </c>
       <c r="I30">
         <v>42</v>
       </c>
       <c r="J30">
-        <v>8001</v>
+        <v>8023</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1687,16 +1687,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>125401126</v>
+        <v>123058958</v>
       </c>
       <c r="E31">
         <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45377</v>
+        <v>44995</v>
       </c>
       <c r="G31" s="2">
-        <v>45377</v>
+        <v>44993</v>
       </c>
       <c r="I31">
         <v>42</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>125542005</v>
+        <v>127074654</v>
       </c>
       <c r="E32">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F32" s="2">
-        <v>45377</v>
+        <v>45369</v>
       </c>
       <c r="G32" s="2">
-        <v>45377</v>
+        <v>45369</v>
       </c>
       <c r="I32">
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -1758,424 +1758,6 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>125755649</v>
-      </c>
-      <c r="E33">
-        <v>1211</v>
-      </c>
-      <c r="F33" s="2">
-        <v>45377</v>
-      </c>
-      <c r="G33" s="2">
-        <v>45377</v>
-      </c>
-      <c r="I33">
-        <v>42</v>
-      </c>
-      <c r="J33">
-        <v>8001</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>126157774</v>
-      </c>
-      <c r="E34">
-        <v>1211</v>
-      </c>
-      <c r="F34" s="2">
-        <v>45377</v>
-      </c>
-      <c r="G34" s="2">
-        <v>45372</v>
-      </c>
-      <c r="I34">
-        <v>42</v>
-      </c>
-      <c r="J34">
-        <v>8001</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>126238254</v>
-      </c>
-      <c r="E35">
-        <v>1211</v>
-      </c>
-      <c r="F35" s="2">
-        <v>45377</v>
-      </c>
-      <c r="G35" s="2">
-        <v>45376</v>
-      </c>
-      <c r="I35">
-        <v>42</v>
-      </c>
-      <c r="J35">
-        <v>8001</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>126517394</v>
-      </c>
-      <c r="E36">
-        <v>1211</v>
-      </c>
-      <c r="F36" s="2">
-        <v>45377</v>
-      </c>
-      <c r="G36" s="2">
-        <v>45377</v>
-      </c>
-      <c r="I36">
-        <v>42</v>
-      </c>
-      <c r="J36">
-        <v>8001</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>126658977</v>
-      </c>
-      <c r="E37">
-        <v>1211</v>
-      </c>
-      <c r="F37" s="2">
-        <v>45377</v>
-      </c>
-      <c r="G37" s="2">
-        <v>45377</v>
-      </c>
-      <c r="I37">
-        <v>42</v>
-      </c>
-      <c r="J37">
-        <v>8001</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>126857371</v>
-      </c>
-      <c r="E38">
-        <v>1211</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45377</v>
-      </c>
-      <c r="G38" s="2">
-        <v>45377</v>
-      </c>
-      <c r="I38">
-        <v>42</v>
-      </c>
-      <c r="J38">
-        <v>8001</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>126891655</v>
-      </c>
-      <c r="E39">
-        <v>1211</v>
-      </c>
-      <c r="F39" s="2">
-        <v>45377</v>
-      </c>
-      <c r="G39" s="2">
-        <v>45373</v>
-      </c>
-      <c r="I39">
-        <v>42</v>
-      </c>
-      <c r="J39">
-        <v>8001</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>126947616</v>
-      </c>
-      <c r="E40">
-        <v>1211</v>
-      </c>
-      <c r="F40" s="2">
-        <v>45377</v>
-      </c>
-      <c r="G40" s="2">
-        <v>45377</v>
-      </c>
-      <c r="I40">
-        <v>42</v>
-      </c>
-      <c r="J40">
-        <v>8001</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>127026371</v>
-      </c>
-      <c r="E41">
-        <v>1212</v>
-      </c>
-      <c r="F41" s="2">
-        <v>45377</v>
-      </c>
-      <c r="G41" s="2">
-        <v>45377</v>
-      </c>
-      <c r="I41">
-        <v>42</v>
-      </c>
-      <c r="J41">
-        <v>8001</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>110074933</v>
-      </c>
-      <c r="E42">
-        <v>1211</v>
-      </c>
-      <c r="F42" s="2">
-        <v>43453</v>
-      </c>
-      <c r="G42" s="2">
-        <v>43441</v>
-      </c>
-      <c r="I42">
-        <v>42</v>
-      </c>
-      <c r="J42">
-        <v>8023</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>123058958</v>
-      </c>
-      <c r="E43">
-        <v>1211</v>
-      </c>
-      <c r="F43" s="2">
-        <v>44995</v>
-      </c>
-      <c r="G43" s="2">
-        <v>44993</v>
-      </c>
-      <c r="I43">
-        <v>42</v>
-      </c>
-      <c r="J43">
-        <v>8001</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
         <v>61</v>
       </c>
     </row>
@@ -9769,31 +9351,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7831C2E9-3C31-4B05-976E-1857BB3F5143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99361E29-B62A-4B9C-8D49-9FF038D100DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q58"/>
+  <dimension ref="A1:Q86"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -623,16 +623,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>127190191</v>
+        <v>125356838</v>
       </c>
       <c r="E3">
         <v>2013</v>
       </c>
       <c r="F3" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G3" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I3">
         <v>42</v>
@@ -661,10 +661,10 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>126845272</v>
+        <v>127190191</v>
       </c>
       <c r="E4">
-        <v>2002</v>
+        <v>2013</v>
       </c>
       <c r="F4" s="2">
         <v>45383</v>
@@ -676,7 +676,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>127029482</v>
+        <v>125446892</v>
       </c>
       <c r="E5">
         <v>2002</v>
@@ -737,10 +737,10 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>123378056</v>
+        <v>126845272</v>
       </c>
       <c r="E6">
-        <v>1211</v>
+        <v>2002</v>
       </c>
       <c r="F6" s="2">
         <v>45383</v>
@@ -752,7 +752,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -775,22 +775,22 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>123609782</v>
+        <v>127029482</v>
       </c>
       <c r="E7">
-        <v>1211</v>
+        <v>2002</v>
       </c>
       <c r="F7" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G7" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -813,22 +813,22 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>123849199</v>
+        <v>127162061</v>
       </c>
       <c r="E8">
-        <v>1211</v>
+        <v>2002</v>
       </c>
       <c r="F8" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G8" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I8">
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -851,22 +851,22 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>123989517</v>
+        <v>127205039</v>
       </c>
       <c r="E9">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F9" s="2">
-        <v>45383</v>
+        <v>45381</v>
       </c>
       <c r="G9" s="2">
-        <v>45383</v>
+        <v>45381</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>124105337</v>
+        <v>123609782</v>
       </c>
       <c r="E10">
         <v>1211</v>
@@ -927,16 +927,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>124290738</v>
+        <v>123614557</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G11" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -965,16 +965,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>124304122</v>
+        <v>123779038</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G12" s="2">
-        <v>45379</v>
+        <v>45384</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1003,13 +1003,13 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>124909810</v>
+        <v>123782667</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G13" s="2">
         <v>45383</v>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>125458599</v>
+        <v>123849199</v>
       </c>
       <c r="E14">
         <v>1211</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>125508315</v>
+        <v>123989517</v>
       </c>
       <c r="E15">
         <v>1211</v>
@@ -1088,7 +1088,7 @@
         <v>45383</v>
       </c>
       <c r="G15" s="2">
-        <v>45378</v>
+        <v>45383</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>125653546</v>
+        <v>124007826</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G16" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>125687194</v>
+        <v>124012647</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G17" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>125975675</v>
+        <v>124080713</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
+        <v>45384</v>
+      </c>
+      <c r="G18" s="2">
         <v>45383</v>
-      </c>
-      <c r="G18" s="2">
-        <v>45379</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,7 +1231,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>126019609</v>
+        <v>124105337</v>
       </c>
       <c r="E19">
         <v>1211</v>
@@ -1240,7 +1240,7 @@
         <v>45383</v>
       </c>
       <c r="G19" s="2">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>126174338</v>
+        <v>124236044</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G20" s="2">
-        <v>45378</v>
+        <v>45384</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>126187636</v>
+        <v>124290738</v>
       </c>
       <c r="E21">
         <v>1211</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>126420779</v>
+        <v>124634794</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G22" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1383,16 +1383,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>126489350</v>
+        <v>124757699</v>
       </c>
       <c r="E23">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F23" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G23" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1421,13 +1421,13 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>126573230</v>
+        <v>124792306</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G24" s="2">
         <v>45383</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>126605452</v>
+        <v>124909810</v>
       </c>
       <c r="E25">
         <v>1211</v>
@@ -1497,16 +1497,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>126629572</v>
+        <v>124911659</v>
       </c>
       <c r="E26">
         <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G26" s="2">
-        <v>45378</v>
+        <v>45384</v>
       </c>
       <c r="I26">
         <v>42</v>
@@ -1535,16 +1535,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>126819608</v>
+        <v>125055988</v>
       </c>
       <c r="E27">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G27" s="2">
-        <v>45378</v>
+        <v>45384</v>
       </c>
       <c r="I27">
         <v>42</v>
@@ -1573,13 +1573,13 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>126894930</v>
+        <v>125149231</v>
       </c>
       <c r="E28">
         <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G28" s="2">
         <v>45383</v>
@@ -1611,16 +1611,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>126906293</v>
+        <v>125281603</v>
       </c>
       <c r="E29">
         <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G29" s="2">
-        <v>45383</v>
+        <v>45377</v>
       </c>
       <c r="I29">
         <v>42</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>126932601</v>
+        <v>125458599</v>
       </c>
       <c r="E30">
         <v>1211</v>
@@ -1687,7 +1687,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>127044555</v>
+        <v>125508315</v>
       </c>
       <c r="E31">
         <v>1211</v>
@@ -1696,7 +1696,7 @@
         <v>45383</v>
       </c>
       <c r="G31" s="2">
-        <v>45383</v>
+        <v>45378</v>
       </c>
       <c r="I31">
         <v>42</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>110074933</v>
+        <v>125653546</v>
       </c>
       <c r="E32">
         <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>43453</v>
+        <v>45383</v>
       </c>
       <c r="G32" s="2">
-        <v>43441</v>
+        <v>45383</v>
       </c>
       <c r="I32">
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8023</v>
+        <v>8001</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -1763,16 +1763,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>123058958</v>
+        <v>125687194</v>
       </c>
       <c r="E33">
         <v>1211</v>
       </c>
       <c r="F33" s="2">
-        <v>44995</v>
+        <v>45383</v>
       </c>
       <c r="G33" s="2">
-        <v>44993</v>
+        <v>45383</v>
       </c>
       <c r="I33">
         <v>42</v>
@@ -1801,22 +1801,22 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>124411489</v>
+        <v>125809427</v>
       </c>
       <c r="E34">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F34" s="2">
-        <v>45371</v>
+        <v>45384</v>
       </c>
       <c r="G34" s="2">
-        <v>45371</v>
+        <v>45384</v>
       </c>
       <c r="I34">
         <v>42</v>
       </c>
       <c r="J34">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -1839,22 +1839,22 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>126410419</v>
+        <v>126090376</v>
       </c>
       <c r="E35">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F35" s="2">
-        <v>45371</v>
+        <v>45384</v>
       </c>
       <c r="G35" s="2">
-        <v>45371</v>
+        <v>45384</v>
       </c>
       <c r="I35">
         <v>42</v>
       </c>
       <c r="J35">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>126589910</v>
+        <v>126120268</v>
       </c>
       <c r="E36">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F36" s="2">
-        <v>45371</v>
+        <v>45384</v>
       </c>
       <c r="G36" s="2">
-        <v>45371</v>
+        <v>45384</v>
       </c>
       <c r="I36">
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -1915,22 +1915,22 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>126645220</v>
+        <v>126160676</v>
       </c>
       <c r="E37">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F37" s="2">
-        <v>45371</v>
+        <v>45384</v>
       </c>
       <c r="G37" s="2">
-        <v>45371</v>
+        <v>45384</v>
       </c>
       <c r="I37">
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>109403368</v>
+        <v>126162405</v>
       </c>
       <c r="E38">
         <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>43346</v>
+        <v>45384</v>
       </c>
       <c r="G38" s="2">
-        <v>43346</v>
+        <v>45384</v>
       </c>
       <c r="I38">
         <v>42</v>
       </c>
       <c r="J38">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -1991,22 +1991,22 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>109455583</v>
+        <v>126169563</v>
       </c>
       <c r="E39">
         <v>1211</v>
       </c>
       <c r="F39" s="2">
-        <v>43354</v>
+        <v>45384</v>
       </c>
       <c r="G39" s="2">
-        <v>43354</v>
+        <v>45384</v>
       </c>
       <c r="I39">
         <v>42</v>
       </c>
       <c r="J39">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>109707680</v>
+        <v>126174338</v>
       </c>
       <c r="E40">
         <v>1211</v>
       </c>
       <c r="F40" s="2">
-        <v>43396</v>
+        <v>45383</v>
       </c>
       <c r="G40" s="2">
-        <v>43396</v>
+        <v>45378</v>
       </c>
       <c r="I40">
         <v>42</v>
       </c>
       <c r="J40">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2067,22 +2067,22 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>113706291</v>
+        <v>126187636</v>
       </c>
       <c r="E41">
         <v>1211</v>
       </c>
       <c r="F41" s="2">
-        <v>43945</v>
+        <v>45383</v>
       </c>
       <c r="G41" s="2">
-        <v>43945</v>
+        <v>45383</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>114296869</v>
+        <v>126350951</v>
       </c>
       <c r="E42">
         <v>1211</v>
       </c>
       <c r="F42" s="2">
-        <v>44057</v>
+        <v>45384</v>
       </c>
       <c r="G42" s="2">
-        <v>44057</v>
+        <v>45379</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2143,22 +2143,22 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>114763565</v>
+        <v>126420779</v>
       </c>
       <c r="E43">
         <v>1211</v>
       </c>
       <c r="F43" s="2">
-        <v>44156</v>
+        <v>45383</v>
       </c>
       <c r="G43" s="2">
-        <v>44153</v>
+        <v>45383</v>
       </c>
       <c r="I43">
         <v>42</v>
       </c>
       <c r="J43">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>114852173</v>
+        <v>126484967</v>
       </c>
       <c r="E44">
         <v>1211</v>
       </c>
       <c r="F44" s="2">
-        <v>44171</v>
+        <v>45384</v>
       </c>
       <c r="G44" s="2">
-        <v>44168</v>
+        <v>45384</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>125011330</v>
+        <v>126489350</v>
       </c>
       <c r="E45">
         <v>1211</v>
@@ -2234,7 +2234,7 @@
         <v>42</v>
       </c>
       <c r="J45">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2257,7 +2257,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>127208432</v>
+        <v>126573230</v>
       </c>
       <c r="E46">
         <v>1211</v>
@@ -2272,7 +2272,7 @@
         <v>42</v>
       </c>
       <c r="J46">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>127209589</v>
+        <v>126605452</v>
       </c>
       <c r="E47">
         <v>1211</v>
@@ -2310,7 +2310,7 @@
         <v>42</v>
       </c>
       <c r="J47">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2333,22 +2333,22 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>127210074</v>
+        <v>126620775</v>
       </c>
       <c r="E48">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F48" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G48" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I48">
         <v>42</v>
       </c>
       <c r="J48">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2371,22 +2371,22 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>127210662</v>
+        <v>126627597</v>
       </c>
       <c r="E49">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F49" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G49" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I49">
         <v>42</v>
       </c>
       <c r="J49">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2409,7 +2409,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>127211023</v>
+        <v>126629572</v>
       </c>
       <c r="E50">
         <v>1211</v>
@@ -2418,13 +2418,13 @@
         <v>45383</v>
       </c>
       <c r="G50" s="2">
-        <v>45383</v>
+        <v>45378</v>
       </c>
       <c r="I50">
         <v>42</v>
       </c>
       <c r="J50">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2447,22 +2447,22 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>127211142</v>
+        <v>126745278</v>
       </c>
       <c r="E51">
         <v>1211</v>
       </c>
       <c r="F51" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G51" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I51">
         <v>42</v>
       </c>
       <c r="J51">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2485,7 +2485,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>127213082</v>
+        <v>126819608</v>
       </c>
       <c r="E52">
         <v>1212</v>
@@ -2494,13 +2494,13 @@
         <v>45383</v>
       </c>
       <c r="G52" s="2">
-        <v>45383</v>
+        <v>45378</v>
       </c>
       <c r="I52">
         <v>42</v>
       </c>
       <c r="J52">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>127215671</v>
+        <v>126832479</v>
       </c>
       <c r="E53">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F53" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G53" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I53">
         <v>42</v>
       </c>
       <c r="J53">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -2561,7 +2561,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>127215710</v>
+        <v>126894930</v>
       </c>
       <c r="E54">
         <v>1211</v>
@@ -2576,7 +2576,7 @@
         <v>42</v>
       </c>
       <c r="J54">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>127216126</v>
+        <v>126906293</v>
       </c>
       <c r="E55">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F55" s="2">
         <v>45383</v>
@@ -2614,7 +2614,7 @@
         <v>42</v>
       </c>
       <c r="J55">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>127217098</v>
+        <v>126932601</v>
       </c>
       <c r="E56">
         <v>1211</v>
@@ -2652,7 +2652,7 @@
         <v>42</v>
       </c>
       <c r="J56">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -2675,22 +2675,22 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>127217648</v>
+        <v>126968792</v>
       </c>
       <c r="E57">
         <v>1211</v>
       </c>
       <c r="F57" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G57" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I57">
         <v>42</v>
       </c>
       <c r="J57">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -2713,10 +2713,10 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>127217723</v>
+        <v>127044555</v>
       </c>
       <c r="E58">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F58" s="2">
         <v>45383</v>
@@ -2728,24 +2728,1088 @@
         <v>42</v>
       </c>
       <c r="J58">
+        <v>8001</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>110074933</v>
+      </c>
+      <c r="E59">
+        <v>1211</v>
+      </c>
+      <c r="F59" s="2">
+        <v>43453</v>
+      </c>
+      <c r="G59" s="2">
+        <v>43441</v>
+      </c>
+      <c r="I59">
+        <v>42</v>
+      </c>
+      <c r="J59">
+        <v>8023</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>123058958</v>
+      </c>
+      <c r="E60">
+        <v>1211</v>
+      </c>
+      <c r="F60" s="2">
+        <v>44995</v>
+      </c>
+      <c r="G60" s="2">
+        <v>44993</v>
+      </c>
+      <c r="I60">
+        <v>42</v>
+      </c>
+      <c r="J60">
+        <v>8001</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>124411489</v>
+      </c>
+      <c r="E61">
+        <v>601</v>
+      </c>
+      <c r="F61" s="2">
+        <v>45384</v>
+      </c>
+      <c r="G61" s="2">
+        <v>45371</v>
+      </c>
+      <c r="I61">
+        <v>42</v>
+      </c>
+      <c r="J61">
+        <v>8017</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>126410419</v>
+      </c>
+      <c r="E62">
+        <v>601</v>
+      </c>
+      <c r="F62" s="2">
+        <v>45371</v>
+      </c>
+      <c r="G62" s="2">
+        <v>45371</v>
+      </c>
+      <c r="I62">
+        <v>42</v>
+      </c>
+      <c r="J62">
+        <v>8017</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>126589910</v>
+      </c>
+      <c r="E63">
+        <v>601</v>
+      </c>
+      <c r="F63" s="2">
+        <v>45371</v>
+      </c>
+      <c r="G63" s="2">
+        <v>45371</v>
+      </c>
+      <c r="I63">
+        <v>42</v>
+      </c>
+      <c r="J63">
+        <v>8017</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>126645220</v>
+      </c>
+      <c r="E64">
+        <v>601</v>
+      </c>
+      <c r="F64" s="2">
+        <v>45371</v>
+      </c>
+      <c r="G64" s="2">
+        <v>45371</v>
+      </c>
+      <c r="I64">
+        <v>42</v>
+      </c>
+      <c r="J64">
+        <v>8017</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>109403368</v>
+      </c>
+      <c r="E65">
+        <v>1211</v>
+      </c>
+      <c r="F65" s="2">
+        <v>43346</v>
+      </c>
+      <c r="G65" s="2">
+        <v>43346</v>
+      </c>
+      <c r="I65">
+        <v>42</v>
+      </c>
+      <c r="J65">
         <v>715</v>
       </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58">
-        <v>0</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58">
-        <v>0</v>
-      </c>
-      <c r="P58">
-        <v>0</v>
-      </c>
-      <c r="Q58">
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>109455583</v>
+      </c>
+      <c r="E66">
+        <v>1211</v>
+      </c>
+      <c r="F66" s="2">
+        <v>43354</v>
+      </c>
+      <c r="G66" s="2">
+        <v>43354</v>
+      </c>
+      <c r="I66">
+        <v>42</v>
+      </c>
+      <c r="J66">
+        <v>715</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>109707680</v>
+      </c>
+      <c r="E67">
+        <v>1211</v>
+      </c>
+      <c r="F67" s="2">
+        <v>43396</v>
+      </c>
+      <c r="G67" s="2">
+        <v>43396</v>
+      </c>
+      <c r="I67">
+        <v>42</v>
+      </c>
+      <c r="J67">
+        <v>715</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>113706291</v>
+      </c>
+      <c r="E68">
+        <v>1211</v>
+      </c>
+      <c r="F68" s="2">
+        <v>43945</v>
+      </c>
+      <c r="G68" s="2">
+        <v>43945</v>
+      </c>
+      <c r="I68">
+        <v>42</v>
+      </c>
+      <c r="J68">
+        <v>715</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>114296869</v>
+      </c>
+      <c r="E69">
+        <v>1211</v>
+      </c>
+      <c r="F69" s="2">
+        <v>44057</v>
+      </c>
+      <c r="G69" s="2">
+        <v>44057</v>
+      </c>
+      <c r="I69">
+        <v>42</v>
+      </c>
+      <c r="J69">
+        <v>715</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>114763565</v>
+      </c>
+      <c r="E70">
+        <v>1211</v>
+      </c>
+      <c r="F70" s="2">
+        <v>44156</v>
+      </c>
+      <c r="G70" s="2">
+        <v>44153</v>
+      </c>
+      <c r="I70">
+        <v>42</v>
+      </c>
+      <c r="J70">
+        <v>715</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>114852173</v>
+      </c>
+      <c r="E71">
+        <v>1211</v>
+      </c>
+      <c r="F71" s="2">
+        <v>44171</v>
+      </c>
+      <c r="G71" s="2">
+        <v>44168</v>
+      </c>
+      <c r="I71">
+        <v>42</v>
+      </c>
+      <c r="J71">
+        <v>715</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>125011330</v>
+      </c>
+      <c r="E72">
+        <v>1211</v>
+      </c>
+      <c r="F72" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G72" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I72">
+        <v>42</v>
+      </c>
+      <c r="J72">
+        <v>715</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>125994157</v>
+      </c>
+      <c r="E73">
+        <v>1211</v>
+      </c>
+      <c r="F73" s="2">
+        <v>45384</v>
+      </c>
+      <c r="G73" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I73">
+        <v>42</v>
+      </c>
+      <c r="J73">
+        <v>715</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>127128345</v>
+      </c>
+      <c r="E74">
+        <v>1211</v>
+      </c>
+      <c r="F74" s="2">
+        <v>45384</v>
+      </c>
+      <c r="G74" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I74">
+        <v>42</v>
+      </c>
+      <c r="J74">
+        <v>715</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>127209589</v>
+      </c>
+      <c r="E75">
+        <v>1211</v>
+      </c>
+      <c r="F75" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G75" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I75">
+        <v>42</v>
+      </c>
+      <c r="J75">
+        <v>715</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>127210074</v>
+      </c>
+      <c r="E76">
+        <v>1212</v>
+      </c>
+      <c r="F76" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G76" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I76">
+        <v>42</v>
+      </c>
+      <c r="J76">
+        <v>715</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>127210662</v>
+      </c>
+      <c r="E77">
+        <v>1212</v>
+      </c>
+      <c r="F77" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G77" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I77">
+        <v>42</v>
+      </c>
+      <c r="J77">
+        <v>715</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>127211023</v>
+      </c>
+      <c r="E78">
+        <v>1211</v>
+      </c>
+      <c r="F78" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G78" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I78">
+        <v>42</v>
+      </c>
+      <c r="J78">
+        <v>715</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>127211142</v>
+      </c>
+      <c r="E79">
+        <v>1211</v>
+      </c>
+      <c r="F79" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G79" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I79">
+        <v>42</v>
+      </c>
+      <c r="J79">
+        <v>715</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>127213082</v>
+      </c>
+      <c r="E80">
+        <v>1212</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I80">
+        <v>42</v>
+      </c>
+      <c r="J80">
+        <v>715</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>127215671</v>
+      </c>
+      <c r="E81">
+        <v>1212</v>
+      </c>
+      <c r="F81" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G81" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I81">
+        <v>42</v>
+      </c>
+      <c r="J81">
+        <v>715</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>127215710</v>
+      </c>
+      <c r="E82">
+        <v>1211</v>
+      </c>
+      <c r="F82" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G82" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I82">
+        <v>42</v>
+      </c>
+      <c r="J82">
+        <v>715</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>127216126</v>
+      </c>
+      <c r="E83">
+        <v>1212</v>
+      </c>
+      <c r="F83" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G83" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I83">
+        <v>42</v>
+      </c>
+      <c r="J83">
+        <v>715</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>127217098</v>
+      </c>
+      <c r="E84">
+        <v>1211</v>
+      </c>
+      <c r="F84" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G84" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I84">
+        <v>42</v>
+      </c>
+      <c r="J84">
+        <v>715</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>127217648</v>
+      </c>
+      <c r="E85">
+        <v>1211</v>
+      </c>
+      <c r="F85" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G85" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I85">
+        <v>42</v>
+      </c>
+      <c r="J85">
+        <v>715</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>127217723</v>
+      </c>
+      <c r="E86">
+        <v>1212</v>
+      </c>
+      <c r="F86" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G86" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I86">
+        <v>42</v>
+      </c>
+      <c r="J86">
+        <v>715</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
         <v>61</v>
       </c>
     </row>
@@ -10339,31 +11403,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99361E29-B62A-4B9C-8D49-9FF038D100DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B9D0DB-978E-4828-968E-D81876ACA2A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q86"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,22 +585,22 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>124575588</v>
+        <v>125598623</v>
       </c>
       <c r="E2">
-        <v>2013</v>
+        <v>2002</v>
       </c>
       <c r="F2" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G2" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I2">
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -623,22 +623,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>125356838</v>
+        <v>127206437</v>
       </c>
       <c r="E3">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F3" s="2">
-        <v>45384</v>
+        <v>45382</v>
       </c>
       <c r="G3" s="2">
-        <v>45384</v>
+        <v>45382</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -661,16 +661,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>127190191</v>
+        <v>123673293</v>
       </c>
       <c r="E4">
-        <v>2013</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G4" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I4">
         <v>42</v>
@@ -699,22 +699,22 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>125446892</v>
+        <v>123751967</v>
       </c>
       <c r="E5">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G5" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I5">
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,22 +737,22 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>126845272</v>
+        <v>123780300</v>
       </c>
       <c r="E6">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G6" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -775,22 +775,22 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>127029482</v>
+        <v>123849528</v>
       </c>
       <c r="E7">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G7" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -813,22 +813,22 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>127162061</v>
+        <v>123862293</v>
       </c>
       <c r="E8">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G8" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I8">
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -851,22 +851,22 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>127205039</v>
+        <v>123938570</v>
       </c>
       <c r="E9">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45381</v>
+        <v>45385</v>
       </c>
       <c r="G9" s="2">
-        <v>45381</v>
+        <v>45385</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -889,16 +889,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>123609782</v>
+        <v>124236138</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G10" s="2">
-        <v>45383</v>
+        <v>45377</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -927,13 +927,13 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>123614557</v>
+        <v>124319286</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G11" s="2">
         <v>45384</v>
@@ -965,16 +965,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>123779038</v>
+        <v>124335284</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G12" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>123782667</v>
+        <v>124409211</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G13" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>123849199</v>
+        <v>124490600</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G14" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>123989517</v>
+        <v>124766549</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G15" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>124007826</v>
+        <v>125155796</v>
       </c>
       <c r="E16">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F16" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G16" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,13 +1155,13 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>124012647</v>
+        <v>125187864</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G17" s="2">
         <v>45384</v>
@@ -1193,13 +1193,13 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>124080713</v>
+        <v>125292591</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G18" s="2">
         <v>45383</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>124105337</v>
+        <v>125416679</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G19" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>124236044</v>
+        <v>125479477</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G20" s="2">
-        <v>45384</v>
+        <v>45383</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>124290738</v>
+        <v>125569788</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G21" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>124634794</v>
+        <v>125751530</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G22" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1383,16 +1383,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>124757699</v>
+        <v>125851473</v>
       </c>
       <c r="E23">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G23" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1421,16 +1421,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>124792306</v>
+        <v>126073250</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G24" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1459,16 +1459,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>124909810</v>
+        <v>126124625</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G25" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I25">
         <v>42</v>
@@ -1497,16 +1497,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>124911659</v>
+        <v>126134135</v>
       </c>
       <c r="E26">
         <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G26" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I26">
         <v>42</v>
@@ -1535,16 +1535,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>125055988</v>
+        <v>126166733</v>
       </c>
       <c r="E27">
         <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G27" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I27">
         <v>42</v>
@@ -1573,16 +1573,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>125149231</v>
+        <v>126272082</v>
       </c>
       <c r="E28">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F28" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G28" s="2">
-        <v>45383</v>
+        <v>45381</v>
       </c>
       <c r="I28">
         <v>42</v>
@@ -1611,16 +1611,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>125281603</v>
+        <v>126875800</v>
       </c>
       <c r="E29">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F29" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G29" s="2">
-        <v>45377</v>
+        <v>45383</v>
       </c>
       <c r="I29">
         <v>42</v>
@@ -1649,16 +1649,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>125458599</v>
+        <v>126893769</v>
       </c>
       <c r="E30">
         <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G30" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I30">
         <v>42</v>
@@ -1687,16 +1687,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>125508315</v>
+        <v>126972179</v>
       </c>
       <c r="E31">
         <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G31" s="2">
-        <v>45378</v>
+        <v>45385</v>
       </c>
       <c r="I31">
         <v>42</v>
@@ -1725,16 +1725,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>125653546</v>
+        <v>127113503</v>
       </c>
       <c r="E32">
         <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G32" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I32">
         <v>42</v>
@@ -1763,22 +1763,22 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>125687194</v>
+        <v>110074933</v>
       </c>
       <c r="E33">
         <v>1211</v>
       </c>
       <c r="F33" s="2">
-        <v>45383</v>
+        <v>43453</v>
       </c>
       <c r="G33" s="2">
-        <v>45383</v>
+        <v>43441</v>
       </c>
       <c r="I33">
         <v>42</v>
       </c>
       <c r="J33">
-        <v>8001</v>
+        <v>8023</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -1801,16 +1801,16 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>125809427</v>
+        <v>123058958</v>
       </c>
       <c r="E34">
         <v>1211</v>
       </c>
       <c r="F34" s="2">
-        <v>45384</v>
+        <v>44995</v>
       </c>
       <c r="G34" s="2">
-        <v>45384</v>
+        <v>44993</v>
       </c>
       <c r="I34">
         <v>42</v>
@@ -1839,22 +1839,22 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>126090376</v>
+        <v>124411489</v>
       </c>
       <c r="E35">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F35" s="2">
         <v>45384</v>
       </c>
       <c r="G35" s="2">
-        <v>45384</v>
+        <v>45371</v>
       </c>
       <c r="I35">
         <v>42</v>
       </c>
       <c r="J35">
-        <v>8001</v>
+        <v>8017</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>126120268</v>
+        <v>127149457</v>
       </c>
       <c r="E36">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F36" s="2">
-        <v>45384</v>
+        <v>45376</v>
       </c>
       <c r="G36" s="2">
-        <v>45384</v>
+        <v>45376</v>
       </c>
       <c r="I36">
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -1915,22 +1915,22 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>126160676</v>
+        <v>127149459</v>
       </c>
       <c r="E37">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F37" s="2">
-        <v>45384</v>
+        <v>45376</v>
       </c>
       <c r="G37" s="2">
-        <v>45384</v>
+        <v>45376</v>
       </c>
       <c r="I37">
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>126162405</v>
+        <v>127150185</v>
       </c>
       <c r="E38">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F38" s="2">
-        <v>45384</v>
+        <v>45376</v>
       </c>
       <c r="G38" s="2">
-        <v>45384</v>
+        <v>45376</v>
       </c>
       <c r="I38">
         <v>42</v>
       </c>
       <c r="J38">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -1991,22 +1991,22 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>126169563</v>
+        <v>127150197</v>
       </c>
       <c r="E39">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F39" s="2">
-        <v>45384</v>
+        <v>45376</v>
       </c>
       <c r="G39" s="2">
-        <v>45384</v>
+        <v>45376</v>
       </c>
       <c r="I39">
         <v>42</v>
       </c>
       <c r="J39">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>126174338</v>
+        <v>127150284</v>
       </c>
       <c r="E40">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F40" s="2">
-        <v>45383</v>
+        <v>45376</v>
       </c>
       <c r="G40" s="2">
-        <v>45378</v>
+        <v>45376</v>
       </c>
       <c r="I40">
         <v>42</v>
       </c>
       <c r="J40">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2067,22 +2067,22 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>126187636</v>
+        <v>109403368</v>
       </c>
       <c r="E41">
         <v>1211</v>
       </c>
       <c r="F41" s="2">
-        <v>45383</v>
+        <v>43346</v>
       </c>
       <c r="G41" s="2">
-        <v>45383</v>
+        <v>43346</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>126350951</v>
+        <v>109455583</v>
       </c>
       <c r="E42">
         <v>1211</v>
       </c>
       <c r="F42" s="2">
-        <v>45384</v>
+        <v>43354</v>
       </c>
       <c r="G42" s="2">
-        <v>45379</v>
+        <v>43354</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2143,22 +2143,22 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>126420779</v>
+        <v>109707680</v>
       </c>
       <c r="E43">
         <v>1211</v>
       </c>
       <c r="F43" s="2">
-        <v>45383</v>
+        <v>43396</v>
       </c>
       <c r="G43" s="2">
-        <v>45383</v>
+        <v>43396</v>
       </c>
       <c r="I43">
         <v>42</v>
       </c>
       <c r="J43">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>126484967</v>
+        <v>113706291</v>
       </c>
       <c r="E44">
         <v>1211</v>
       </c>
       <c r="F44" s="2">
-        <v>45384</v>
+        <v>43945</v>
       </c>
       <c r="G44" s="2">
-        <v>45384</v>
+        <v>43945</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2219,22 +2219,22 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>126489350</v>
+        <v>114296869</v>
       </c>
       <c r="E45">
         <v>1211</v>
       </c>
       <c r="F45" s="2">
-        <v>45383</v>
+        <v>44057</v>
       </c>
       <c r="G45" s="2">
-        <v>45383</v>
+        <v>44057</v>
       </c>
       <c r="I45">
         <v>42</v>
       </c>
       <c r="J45">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>126573230</v>
+        <v>114763565</v>
       </c>
       <c r="E46">
         <v>1211</v>
       </c>
       <c r="F46" s="2">
-        <v>45383</v>
+        <v>44156</v>
       </c>
       <c r="G46" s="2">
-        <v>45383</v>
+        <v>44153</v>
       </c>
       <c r="I46">
         <v>42</v>
       </c>
       <c r="J46">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2295,22 +2295,22 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>126605452</v>
+        <v>114852173</v>
       </c>
       <c r="E47">
         <v>1211</v>
       </c>
       <c r="F47" s="2">
-        <v>45383</v>
+        <v>44171</v>
       </c>
       <c r="G47" s="2">
-        <v>45383</v>
+        <v>44168</v>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2333,22 +2333,22 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>126620775</v>
+        <v>124072656</v>
       </c>
       <c r="E48">
         <v>1211</v>
       </c>
       <c r="F48" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G48" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I48">
         <v>42</v>
       </c>
       <c r="J48">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2371,7 +2371,7 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>126627597</v>
+        <v>125994157</v>
       </c>
       <c r="E49">
         <v>1211</v>
@@ -2386,7 +2386,7 @@
         <v>42</v>
       </c>
       <c r="J49">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>126629572</v>
+        <v>127128345</v>
       </c>
       <c r="E50">
         <v>1211</v>
       </c>
       <c r="F50" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G50" s="2">
-        <v>45378</v>
+        <v>45384</v>
       </c>
       <c r="I50">
         <v>42</v>
       </c>
       <c r="J50">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2447,22 +2447,22 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>126745278</v>
+        <v>127209589</v>
       </c>
       <c r="E51">
         <v>1211</v>
       </c>
       <c r="F51" s="2">
-        <v>45384</v>
+        <v>45383</v>
       </c>
       <c r="G51" s="2">
-        <v>45384</v>
+        <v>45383</v>
       </c>
       <c r="I51">
         <v>42</v>
       </c>
       <c r="J51">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2485,7 +2485,7 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>126819608</v>
+        <v>127210074</v>
       </c>
       <c r="E52">
         <v>1212</v>
@@ -2494,13 +2494,13 @@
         <v>45383</v>
       </c>
       <c r="G52" s="2">
-        <v>45378</v>
+        <v>45383</v>
       </c>
       <c r="I52">
         <v>42</v>
       </c>
       <c r="J52">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>126832479</v>
+        <v>127210662</v>
       </c>
       <c r="E53">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F53" s="2">
-        <v>45384</v>
+        <v>45383</v>
       </c>
       <c r="G53" s="2">
-        <v>45384</v>
+        <v>45383</v>
       </c>
       <c r="I53">
         <v>42</v>
       </c>
       <c r="J53">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -2561,7 +2561,7 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>126894930</v>
+        <v>127211023</v>
       </c>
       <c r="E54">
         <v>1211</v>
@@ -2576,7 +2576,7 @@
         <v>42</v>
       </c>
       <c r="J54">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -2599,7 +2599,7 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>126906293</v>
+        <v>127211142</v>
       </c>
       <c r="E55">
         <v>1211</v>
@@ -2614,7 +2614,7 @@
         <v>42</v>
       </c>
       <c r="J55">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -2637,10 +2637,10 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>126932601</v>
+        <v>127213082</v>
       </c>
       <c r="E56">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F56" s="2">
         <v>45383</v>
@@ -2652,7 +2652,7 @@
         <v>42</v>
       </c>
       <c r="J56">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -2675,13 +2675,13 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>126968792</v>
+        <v>127221992</v>
       </c>
       <c r="E57">
         <v>1211</v>
       </c>
       <c r="F57" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G57" s="2">
         <v>45384</v>
@@ -2690,7 +2690,7 @@
         <v>42</v>
       </c>
       <c r="J57">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -2713,22 +2713,22 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>127044555</v>
+        <v>127223257</v>
       </c>
       <c r="E58">
         <v>1211</v>
       </c>
       <c r="F58" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G58" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I58">
         <v>42</v>
       </c>
       <c r="J58">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -2751,22 +2751,22 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>110074933</v>
+        <v>127223585</v>
       </c>
       <c r="E59">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F59" s="2">
-        <v>43453</v>
+        <v>45385</v>
       </c>
       <c r="G59" s="2">
-        <v>43441</v>
+        <v>45384</v>
       </c>
       <c r="I59">
         <v>42</v>
       </c>
       <c r="J59">
-        <v>8023</v>
+        <v>715</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -2789,22 +2789,22 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>123058958</v>
+        <v>127224806</v>
       </c>
       <c r="E60">
         <v>1211</v>
       </c>
       <c r="F60" s="2">
-        <v>44995</v>
+        <v>45385</v>
       </c>
       <c r="G60" s="2">
-        <v>44993</v>
+        <v>45384</v>
       </c>
       <c r="I60">
         <v>42</v>
       </c>
       <c r="J60">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -2827,22 +2827,22 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>124411489</v>
+        <v>127225461</v>
       </c>
       <c r="E61">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F61" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G61" s="2">
         <v>45384</v>
       </c>
-      <c r="G61" s="2">
-        <v>45371</v>
-      </c>
       <c r="I61">
         <v>42</v>
       </c>
       <c r="J61">
-        <v>8017</v>
+        <v>715</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -2865,22 +2865,22 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>126410419</v>
+        <v>127225592</v>
       </c>
       <c r="E62">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F62" s="2">
-        <v>45371</v>
+        <v>45385</v>
       </c>
       <c r="G62" s="2">
-        <v>45371</v>
+        <v>45384</v>
       </c>
       <c r="I62">
         <v>42</v>
       </c>
       <c r="J62">
-        <v>8017</v>
+        <v>715</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -2903,22 +2903,22 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>126589910</v>
+        <v>127225618</v>
       </c>
       <c r="E63">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F63" s="2">
-        <v>45371</v>
+        <v>45385</v>
       </c>
       <c r="G63" s="2">
-        <v>45371</v>
+        <v>45384</v>
       </c>
       <c r="I63">
         <v>42</v>
       </c>
       <c r="J63">
-        <v>8017</v>
+        <v>715</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -2941,22 +2941,22 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>126645220</v>
+        <v>127228257</v>
       </c>
       <c r="E64">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F64" s="2">
-        <v>45371</v>
+        <v>45385</v>
       </c>
       <c r="G64" s="2">
-        <v>45371</v>
+        <v>45384</v>
       </c>
       <c r="I64">
         <v>42</v>
       </c>
       <c r="J64">
-        <v>8017</v>
+        <v>715</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -2979,16 +2979,16 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>109403368</v>
+        <v>127228923</v>
       </c>
       <c r="E65">
         <v>1211</v>
       </c>
       <c r="F65" s="2">
-        <v>43346</v>
+        <v>45385</v>
       </c>
       <c r="G65" s="2">
-        <v>43346</v>
+        <v>45384</v>
       </c>
       <c r="I65">
         <v>42</v>
@@ -3017,16 +3017,16 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>109455583</v>
+        <v>127231061</v>
       </c>
       <c r="E66">
         <v>1211</v>
       </c>
       <c r="F66" s="2">
-        <v>43354</v>
+        <v>45385</v>
       </c>
       <c r="G66" s="2">
-        <v>43354</v>
+        <v>45384</v>
       </c>
       <c r="I66">
         <v>42</v>
@@ -3055,16 +3055,16 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>109707680</v>
+        <v>127231434</v>
       </c>
       <c r="E67">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F67" s="2">
-        <v>43396</v>
+        <v>45385</v>
       </c>
       <c r="G67" s="2">
-        <v>43396</v>
+        <v>45384</v>
       </c>
       <c r="I67">
         <v>42</v>
@@ -3093,16 +3093,16 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>113706291</v>
+        <v>127232389</v>
       </c>
       <c r="E68">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F68" s="2">
-        <v>43945</v>
+        <v>45385</v>
       </c>
       <c r="G68" s="2">
-        <v>43945</v>
+        <v>45384</v>
       </c>
       <c r="I68">
         <v>42</v>
@@ -3131,16 +3131,16 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>114296869</v>
+        <v>127232466</v>
       </c>
       <c r="E69">
         <v>1211</v>
       </c>
       <c r="F69" s="2">
-        <v>44057</v>
+        <v>45385</v>
       </c>
       <c r="G69" s="2">
-        <v>44057</v>
+        <v>45384</v>
       </c>
       <c r="I69">
         <v>42</v>
@@ -3169,16 +3169,16 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>114763565</v>
+        <v>127238237</v>
       </c>
       <c r="E70">
         <v>1211</v>
       </c>
       <c r="F70" s="2">
-        <v>44156</v>
+        <v>45385</v>
       </c>
       <c r="G70" s="2">
-        <v>44153</v>
+        <v>45385</v>
       </c>
       <c r="I70">
         <v>42</v>
@@ -3207,16 +3207,16 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>114852173</v>
+        <v>127240902</v>
       </c>
       <c r="E71">
         <v>1211</v>
       </c>
       <c r="F71" s="2">
-        <v>44171</v>
+        <v>45385</v>
       </c>
       <c r="G71" s="2">
-        <v>44168</v>
+        <v>45385</v>
       </c>
       <c r="I71">
         <v>42</v>
@@ -3245,16 +3245,16 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>125011330</v>
+        <v>127241003</v>
       </c>
       <c r="E72">
         <v>1211</v>
       </c>
       <c r="F72" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G72" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I72">
         <v>42</v>
@@ -3283,16 +3283,16 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>125994157</v>
+        <v>127241421</v>
       </c>
       <c r="E73">
         <v>1211</v>
       </c>
       <c r="F73" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G73" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I73">
         <v>42</v>
@@ -3321,16 +3321,16 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>127128345</v>
+        <v>127241838</v>
       </c>
       <c r="E74">
         <v>1211</v>
       </c>
       <c r="F74" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G74" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I74">
         <v>42</v>
@@ -3359,16 +3359,16 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>127209589</v>
+        <v>127243348</v>
       </c>
       <c r="E75">
         <v>1211</v>
       </c>
       <c r="F75" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G75" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I75">
         <v>42</v>
@@ -3397,16 +3397,16 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>127210074</v>
+        <v>127243440</v>
       </c>
       <c r="E76">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F76" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G76" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I76">
         <v>42</v>
@@ -3435,16 +3435,16 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>127210662</v>
+        <v>127244338</v>
       </c>
       <c r="E77">
         <v>1212</v>
       </c>
       <c r="F77" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G77" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I77">
         <v>42</v>
@@ -3473,16 +3473,16 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>127211023</v>
+        <v>127245008</v>
       </c>
       <c r="E78">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F78" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G78" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I78">
         <v>42</v>
@@ -3511,16 +3511,16 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>127211142</v>
+        <v>127245138</v>
       </c>
       <c r="E79">
         <v>1211</v>
       </c>
       <c r="F79" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G79" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I79">
         <v>42</v>
@@ -3544,272 +3544,6 @@
         <v>0</v>
       </c>
       <c r="Q79">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A80">
-        <v>127213082</v>
-      </c>
-      <c r="E80">
-        <v>1212</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45383</v>
-      </c>
-      <c r="G80" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I80">
-        <v>42</v>
-      </c>
-      <c r="J80">
-        <v>715</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>0</v>
-      </c>
-      <c r="P80">
-        <v>0</v>
-      </c>
-      <c r="Q80">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A81">
-        <v>127215671</v>
-      </c>
-      <c r="E81">
-        <v>1212</v>
-      </c>
-      <c r="F81" s="2">
-        <v>45383</v>
-      </c>
-      <c r="G81" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I81">
-        <v>42</v>
-      </c>
-      <c r="J81">
-        <v>715</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
-        <v>0</v>
-      </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
-      <c r="O81">
-        <v>0</v>
-      </c>
-      <c r="P81">
-        <v>0</v>
-      </c>
-      <c r="Q81">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A82">
-        <v>127215710</v>
-      </c>
-      <c r="E82">
-        <v>1211</v>
-      </c>
-      <c r="F82" s="2">
-        <v>45383</v>
-      </c>
-      <c r="G82" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I82">
-        <v>42</v>
-      </c>
-      <c r="J82">
-        <v>715</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>0</v>
-      </c>
-      <c r="P82">
-        <v>0</v>
-      </c>
-      <c r="Q82">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A83">
-        <v>127216126</v>
-      </c>
-      <c r="E83">
-        <v>1212</v>
-      </c>
-      <c r="F83" s="2">
-        <v>45383</v>
-      </c>
-      <c r="G83" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I83">
-        <v>42</v>
-      </c>
-      <c r="J83">
-        <v>715</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
-      <c r="O83">
-        <v>0</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
-      <c r="Q83">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A84">
-        <v>127217098</v>
-      </c>
-      <c r="E84">
-        <v>1211</v>
-      </c>
-      <c r="F84" s="2">
-        <v>45383</v>
-      </c>
-      <c r="G84" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I84">
-        <v>42</v>
-      </c>
-      <c r="J84">
-        <v>715</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84">
-        <v>0</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A85">
-        <v>127217648</v>
-      </c>
-      <c r="E85">
-        <v>1211</v>
-      </c>
-      <c r="F85" s="2">
-        <v>45383</v>
-      </c>
-      <c r="G85" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I85">
-        <v>42</v>
-      </c>
-      <c r="J85">
-        <v>715</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
-        <v>0</v>
-      </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>0</v>
-      </c>
-      <c r="P85">
-        <v>0</v>
-      </c>
-      <c r="Q85">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A86">
-        <v>127217723</v>
-      </c>
-      <c r="E86">
-        <v>1212</v>
-      </c>
-      <c r="F86" s="2">
-        <v>45383</v>
-      </c>
-      <c r="G86" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I86">
-        <v>42</v>
-      </c>
-      <c r="J86">
-        <v>715</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86">
-        <v>0</v>
-      </c>
-      <c r="P86">
-        <v>0</v>
-      </c>
-      <c r="Q86">
         <v>61</v>
       </c>
     </row>
@@ -11403,31 +11137,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24DB7CC8-5EA5-4CE6-B6CA-1D81E9DAF2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A32530-7A9A-461A-BDC4-BEDBCFC81B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiel" sheetId="28" r:id="rId1"/>
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,18 +507,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q90"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Q150"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
@@ -526,11 +526,11 @@
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,7 +583,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>127208583</v>
       </c>
@@ -621,7 +621,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>127213295</v>
       </c>
@@ -659,7 +659,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>127213974</v>
       </c>
@@ -697,7 +697,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>127214844</v>
       </c>
@@ -735,7 +735,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>123487367</v>
       </c>
@@ -773,7 +773,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>123601906</v>
       </c>
@@ -811,7 +811,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>123703137</v>
       </c>
@@ -849,7 +849,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>123716326</v>
       </c>
@@ -887,7 +887,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>123875216</v>
       </c>
@@ -925,7 +925,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>123971580</v>
       </c>
@@ -963,7 +963,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>124044346</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>124184188</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>124196438</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>124322079</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>124322872</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>124329808</v>
       </c>
@@ -1191,7 +1191,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>124598258</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>124634661</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>124635455</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>124683975</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>124706213</v>
       </c>
@@ -1381,7 +1381,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>125250574</v>
       </c>
@@ -1419,7 +1419,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>125360318</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>125403476</v>
       </c>
@@ -1495,7 +1495,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>125485872</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>125717517</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>125807781</v>
       </c>
@@ -1609,7 +1609,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>125936370</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>125988584</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>126278313</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>126290624</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>126518639</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>126596251</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>126614625</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>126816319</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>126835056</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>127009794</v>
       </c>
@@ -1989,7 +1989,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>127071870</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>127190566</v>
       </c>
@@ -2065,138 +2065,138 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>110074933</v>
+        <v>124411489</v>
       </c>
       <c r="E41">
+        <v>601</v>
+      </c>
+      <c r="F41" s="2">
+        <v>45384</v>
+      </c>
+      <c r="G41" s="2">
+        <v>45371</v>
+      </c>
+      <c r="I41">
+        <v>42</v>
+      </c>
+      <c r="J41">
+        <v>8017</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>127169044</v>
+      </c>
+      <c r="E42">
+        <v>601</v>
+      </c>
+      <c r="F42" s="2">
+        <v>45377</v>
+      </c>
+      <c r="G42" s="2">
+        <v>45377</v>
+      </c>
+      <c r="I42">
+        <v>42</v>
+      </c>
+      <c r="J42">
+        <v>8004</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>124072656</v>
+      </c>
+      <c r="E43">
         <v>1211</v>
       </c>
-      <c r="F41" s="2">
-        <v>43453</v>
-      </c>
-      <c r="G41" s="2">
-        <v>43441</v>
-      </c>
-      <c r="I41">
-        <v>42</v>
-      </c>
-      <c r="J41">
-        <v>8023</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>123058958</v>
-      </c>
-      <c r="E42">
+      <c r="F43" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G43" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I43">
+        <v>42</v>
+      </c>
+      <c r="J43">
+        <v>715</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>125994157</v>
+      </c>
+      <c r="E44">
         <v>1211</v>
       </c>
-      <c r="F42" s="2">
-        <v>44995</v>
-      </c>
-      <c r="G42" s="2">
-        <v>44993</v>
-      </c>
-      <c r="I42">
-        <v>42</v>
-      </c>
-      <c r="J42">
-        <v>8001</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>124411489</v>
-      </c>
-      <c r="E43">
-        <v>601</v>
-      </c>
-      <c r="F43" s="2">
+      <c r="F44" s="2">
         <v>45384</v>
       </c>
-      <c r="G43" s="2">
-        <v>45371</v>
-      </c>
-      <c r="I43">
-        <v>42</v>
-      </c>
-      <c r="J43">
-        <v>8017</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>127169044</v>
-      </c>
-      <c r="E44">
-        <v>601</v>
-      </c>
-      <c r="F44" s="2">
-        <v>45377</v>
-      </c>
       <c r="G44" s="2">
-        <v>45377</v>
+        <v>45384</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2217,18 +2217,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>109403368</v>
+        <v>127210662</v>
       </c>
       <c r="E45">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F45" s="2">
-        <v>43346</v>
+        <v>45383</v>
       </c>
       <c r="G45" s="2">
-        <v>43346</v>
+        <v>45383</v>
       </c>
       <c r="I45">
         <v>42</v>
@@ -2255,18 +2255,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>109455583</v>
+        <v>127211023</v>
       </c>
       <c r="E46">
         <v>1211</v>
       </c>
       <c r="F46" s="2">
-        <v>43354</v>
+        <v>45383</v>
       </c>
       <c r="G46" s="2">
-        <v>43354</v>
+        <v>45383</v>
       </c>
       <c r="I46">
         <v>42</v>
@@ -2293,18 +2293,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>109707680</v>
+        <v>127211142</v>
       </c>
       <c r="E47">
         <v>1211</v>
       </c>
       <c r="F47" s="2">
-        <v>43396</v>
+        <v>45383</v>
       </c>
       <c r="G47" s="2">
-        <v>43396</v>
+        <v>45383</v>
       </c>
       <c r="I47">
         <v>42</v>
@@ -2331,18 +2331,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>113706291</v>
+        <v>127221992</v>
       </c>
       <c r="E48">
         <v>1211</v>
       </c>
       <c r="F48" s="2">
-        <v>43945</v>
+        <v>45385</v>
       </c>
       <c r="G48" s="2">
-        <v>43945</v>
+        <v>45384</v>
       </c>
       <c r="I48">
         <v>42</v>
@@ -2369,18 +2369,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>114296869</v>
+        <v>127223257</v>
       </c>
       <c r="E49">
         <v>1211</v>
       </c>
       <c r="F49" s="2">
-        <v>44057</v>
+        <v>45385</v>
       </c>
       <c r="G49" s="2">
-        <v>44057</v>
+        <v>45384</v>
       </c>
       <c r="I49">
         <v>42</v>
@@ -2407,18 +2407,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>114763565</v>
+        <v>127223585</v>
       </c>
       <c r="E50">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F50" s="2">
-        <v>44156</v>
+        <v>45385</v>
       </c>
       <c r="G50" s="2">
-        <v>44153</v>
+        <v>45384</v>
       </c>
       <c r="I50">
         <v>42</v>
@@ -2445,18 +2445,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>114852173</v>
+        <v>127224806</v>
       </c>
       <c r="E51">
         <v>1211</v>
       </c>
       <c r="F51" s="2">
-        <v>44171</v>
+        <v>45385</v>
       </c>
       <c r="G51" s="2">
-        <v>44168</v>
+        <v>45384</v>
       </c>
       <c r="I51">
         <v>42</v>
@@ -2483,9 +2483,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>124072656</v>
+        <v>127225592</v>
       </c>
       <c r="E52">
         <v>1211</v>
@@ -2494,7 +2494,7 @@
         <v>45385</v>
       </c>
       <c r="G52" s="2">
-        <v>45385</v>
+        <v>45384</v>
       </c>
       <c r="I52">
         <v>42</v>
@@ -2521,15 +2521,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>125994157</v>
+        <v>127225618</v>
       </c>
       <c r="E53">
         <v>1211</v>
       </c>
       <c r="F53" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="G53" s="2">
         <v>45384</v>
@@ -2559,18 +2559,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>127210662</v>
+        <v>127228923</v>
       </c>
       <c r="E54">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F54" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G54" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I54">
         <v>42</v>
@@ -2597,18 +2597,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>127211023</v>
+        <v>127231061</v>
       </c>
       <c r="E55">
         <v>1211</v>
       </c>
       <c r="F55" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G55" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I55">
         <v>42</v>
@@ -2635,18 +2635,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>127211142</v>
+        <v>127238237</v>
       </c>
       <c r="E56">
         <v>1211</v>
       </c>
       <c r="F56" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G56" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="I56">
         <v>42</v>
@@ -2673,9 +2673,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>127221992</v>
+        <v>127240902</v>
       </c>
       <c r="E57">
         <v>1211</v>
@@ -2684,7 +2684,7 @@
         <v>45385</v>
       </c>
       <c r="G57" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I57">
         <v>42</v>
@@ -2711,9 +2711,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>127223257</v>
+        <v>127241003</v>
       </c>
       <c r="E58">
         <v>1211</v>
@@ -2722,7 +2722,7 @@
         <v>45385</v>
       </c>
       <c r="G58" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I58">
         <v>42</v>
@@ -2749,18 +2749,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>127223585</v>
+        <v>127241421</v>
       </c>
       <c r="E59">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F59" s="2">
         <v>45385</v>
       </c>
       <c r="G59" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I59">
         <v>42</v>
@@ -2787,9 +2787,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>127224806</v>
+        <v>127241838</v>
       </c>
       <c r="E60">
         <v>1211</v>
@@ -2798,7 +2798,7 @@
         <v>45385</v>
       </c>
       <c r="G60" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I60">
         <v>42</v>
@@ -2825,9 +2825,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>127225592</v>
+        <v>127243348</v>
       </c>
       <c r="E61">
         <v>1211</v>
@@ -2836,7 +2836,7 @@
         <v>45385</v>
       </c>
       <c r="G61" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I61">
         <v>42</v>
@@ -2863,9 +2863,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>127225618</v>
+        <v>127243440</v>
       </c>
       <c r="E62">
         <v>1211</v>
@@ -2874,7 +2874,7 @@
         <v>45385</v>
       </c>
       <c r="G62" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I62">
         <v>42</v>
@@ -2901,18 +2901,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>127228923</v>
+        <v>127243860</v>
       </c>
       <c r="E63">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F63" s="2">
+        <v>45386</v>
+      </c>
+      <c r="G63" s="2">
         <v>45385</v>
-      </c>
-      <c r="G63" s="2">
-        <v>45384</v>
       </c>
       <c r="I63">
         <v>42</v>
@@ -2939,18 +2939,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>127231061</v>
+        <v>127244338</v>
       </c>
       <c r="E64">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F64" s="2">
         <v>45385</v>
       </c>
       <c r="G64" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="I64">
         <v>42</v>
@@ -2977,12 +2977,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>127238237</v>
+        <v>127245008</v>
       </c>
       <c r="E65">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F65" s="2">
         <v>45385</v>
@@ -3015,9 +3015,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>127240902</v>
+        <v>127245138</v>
       </c>
       <c r="E66">
         <v>1211</v>
@@ -3053,18 +3053,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>127241003</v>
+        <v>127248957</v>
       </c>
       <c r="E67">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F67" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="G67" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="I67">
         <v>42</v>
@@ -3091,18 +3091,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>127241421</v>
+        <v>127249438</v>
       </c>
       <c r="E68">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F68" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="G68" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="I68">
         <v>42</v>
@@ -3129,18 +3129,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>127241838</v>
+        <v>127251213</v>
       </c>
       <c r="E69">
         <v>1211</v>
       </c>
       <c r="F69" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="G69" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="I69">
         <v>42</v>
@@ -3167,18 +3167,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>127243348</v>
+        <v>127251298</v>
       </c>
       <c r="E70">
         <v>1211</v>
       </c>
       <c r="F70" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="G70" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="I70">
         <v>42</v>
@@ -3205,18 +3205,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>127243440</v>
+        <v>127251465</v>
       </c>
       <c r="E71">
         <v>1211</v>
       </c>
       <c r="F71" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="G71" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="I71">
         <v>42</v>
@@ -3243,18 +3243,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>127243860</v>
+        <v>127251846</v>
       </c>
       <c r="E72">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F72" s="2">
         <v>45386</v>
       </c>
       <c r="G72" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="I72">
         <v>42</v>
@@ -3281,18 +3281,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>127244338</v>
+        <v>127255428</v>
       </c>
       <c r="E73">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F73" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="G73" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="I73">
         <v>42</v>
@@ -3319,18 +3319,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>127245008</v>
+        <v>127255968</v>
       </c>
       <c r="E74">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F74" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="G74" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="I74">
         <v>42</v>
@@ -3357,18 +3357,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>127245138</v>
+        <v>127255987</v>
       </c>
       <c r="E75">
         <v>1211</v>
       </c>
       <c r="F75" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="G75" s="2">
-        <v>45385</v>
+        <v>45386</v>
       </c>
       <c r="I75">
         <v>42</v>
@@ -3395,9 +3395,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>127248957</v>
+        <v>127256985</v>
       </c>
       <c r="E76">
         <v>1212</v>
@@ -3433,12 +3433,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>127249438</v>
+        <v>127257054</v>
       </c>
       <c r="E77">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F77" s="2">
         <v>45386</v>
@@ -3471,9 +3471,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>127251213</v>
+        <v>127258945</v>
       </c>
       <c r="E78">
         <v>1211</v>
@@ -3509,9 +3509,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>127251298</v>
+        <v>127259090</v>
       </c>
       <c r="E79">
         <v>1211</v>
@@ -3547,12 +3547,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>127251465</v>
+        <v>127259721</v>
       </c>
       <c r="E80">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F80" s="2">
         <v>45386</v>
@@ -3585,9 +3585,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>127251846</v>
+        <v>127259957</v>
       </c>
       <c r="E81">
         <v>1211</v>
@@ -3623,24 +3623,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>127255428</v>
+        <v>125598623</v>
       </c>
       <c r="E82">
-        <v>1211</v>
+        <v>2002</v>
       </c>
       <c r="F82" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="G82" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="I82">
         <v>42</v>
       </c>
       <c r="J82">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -3661,24 +3661,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>127255968</v>
+        <v>127206437</v>
       </c>
       <c r="E83">
         <v>1211</v>
       </c>
       <c r="F83" s="2">
-        <v>45386</v>
+        <v>45382</v>
       </c>
       <c r="G83" s="2">
-        <v>45386</v>
+        <v>45382</v>
       </c>
       <c r="I83">
         <v>42</v>
       </c>
       <c r="J83">
-        <v>715</v>
+        <v>1735</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -3699,24 +3699,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>127255987</v>
+        <v>123673293</v>
       </c>
       <c r="E84">
         <v>1211</v>
       </c>
       <c r="F84" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="G84" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="I84">
         <v>42</v>
       </c>
       <c r="J84">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -3737,24 +3737,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>127256985</v>
+        <v>123751967</v>
       </c>
       <c r="E85">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F85" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="G85" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="I85">
         <v>42</v>
       </c>
       <c r="J85">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -3775,24 +3775,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>127257054</v>
+        <v>123780300</v>
       </c>
       <c r="E86">
         <v>1211</v>
       </c>
       <c r="F86" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="G86" s="2">
-        <v>45386</v>
+        <v>45384</v>
       </c>
       <c r="I86">
         <v>42</v>
       </c>
       <c r="J86">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -3813,24 +3813,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>127258945</v>
+        <v>123849528</v>
       </c>
       <c r="E87">
         <v>1211</v>
       </c>
       <c r="F87" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="G87" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="I87">
         <v>42</v>
       </c>
       <c r="J87">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -3851,24 +3851,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>127259090</v>
+        <v>123862293</v>
       </c>
       <c r="E88">
         <v>1211</v>
       </c>
       <c r="F88" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="G88" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="I88">
         <v>42</v>
       </c>
       <c r="J88">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -3889,24 +3889,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>127259721</v>
+        <v>123938570</v>
       </c>
       <c r="E89">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F89" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="G89" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="I89">
         <v>42</v>
       </c>
       <c r="J89">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -3927,41 +3927,2321 @@
         <v>61</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>127259957</v>
+        <v>124236138</v>
       </c>
       <c r="E90">
         <v>1211</v>
       </c>
       <c r="F90" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="G90" s="2">
-        <v>45386</v>
+        <v>45377</v>
       </c>
       <c r="I90">
         <v>42</v>
       </c>
       <c r="J90">
+        <v>8001</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>124319286</v>
+      </c>
+      <c r="E91">
+        <v>1211</v>
+      </c>
+      <c r="F91" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G91" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I91">
+        <v>42</v>
+      </c>
+      <c r="J91">
+        <v>8001</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>124335284</v>
+      </c>
+      <c r="E92">
+        <v>1211</v>
+      </c>
+      <c r="F92" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G92" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I92">
+        <v>42</v>
+      </c>
+      <c r="J92">
+        <v>8001</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>124409211</v>
+      </c>
+      <c r="E93">
+        <v>1211</v>
+      </c>
+      <c r="F93" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G93" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I93">
+        <v>42</v>
+      </c>
+      <c r="J93">
+        <v>8001</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>124490600</v>
+      </c>
+      <c r="E94">
+        <v>1211</v>
+      </c>
+      <c r="F94" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G94" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I94">
+        <v>42</v>
+      </c>
+      <c r="J94">
+        <v>8001</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>124766549</v>
+      </c>
+      <c r="E95">
+        <v>1211</v>
+      </c>
+      <c r="F95" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G95" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I95">
+        <v>42</v>
+      </c>
+      <c r="J95">
+        <v>8001</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>125155796</v>
+      </c>
+      <c r="E96">
+        <v>1212</v>
+      </c>
+      <c r="F96" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G96" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I96">
+        <v>42</v>
+      </c>
+      <c r="J96">
+        <v>8001</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>125187864</v>
+      </c>
+      <c r="E97">
+        <v>1211</v>
+      </c>
+      <c r="F97" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G97" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I97">
+        <v>42</v>
+      </c>
+      <c r="J97">
+        <v>8001</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>125292591</v>
+      </c>
+      <c r="E98">
+        <v>1211</v>
+      </c>
+      <c r="F98" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G98" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I98">
+        <v>42</v>
+      </c>
+      <c r="J98">
+        <v>8001</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>125416679</v>
+      </c>
+      <c r="E99">
+        <v>1211</v>
+      </c>
+      <c r="F99" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G99" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I99">
+        <v>42</v>
+      </c>
+      <c r="J99">
+        <v>8001</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>125479477</v>
+      </c>
+      <c r="E100">
+        <v>1211</v>
+      </c>
+      <c r="F100" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G100" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I100">
+        <v>42</v>
+      </c>
+      <c r="J100">
+        <v>8001</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>125569788</v>
+      </c>
+      <c r="E101">
+        <v>1211</v>
+      </c>
+      <c r="F101" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G101" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I101">
+        <v>42</v>
+      </c>
+      <c r="J101">
+        <v>8001</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>125751530</v>
+      </c>
+      <c r="E102">
+        <v>1211</v>
+      </c>
+      <c r="F102" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G102" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I102">
+        <v>42</v>
+      </c>
+      <c r="J102">
+        <v>8001</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>125851473</v>
+      </c>
+      <c r="E103">
+        <v>1211</v>
+      </c>
+      <c r="F103" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G103" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I103">
+        <v>42</v>
+      </c>
+      <c r="J103">
+        <v>8001</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>126073250</v>
+      </c>
+      <c r="E104">
+        <v>1211</v>
+      </c>
+      <c r="F104" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G104" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I104">
+        <v>42</v>
+      </c>
+      <c r="J104">
+        <v>8001</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>126124625</v>
+      </c>
+      <c r="E105">
+        <v>1211</v>
+      </c>
+      <c r="F105" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G105" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I105">
+        <v>42</v>
+      </c>
+      <c r="J105">
+        <v>8001</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>126134135</v>
+      </c>
+      <c r="E106">
+        <v>1211</v>
+      </c>
+      <c r="F106" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G106" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I106">
+        <v>42</v>
+      </c>
+      <c r="J106">
+        <v>8001</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>126166733</v>
+      </c>
+      <c r="E107">
+        <v>1211</v>
+      </c>
+      <c r="F107" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G107" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I107">
+        <v>42</v>
+      </c>
+      <c r="J107">
+        <v>8001</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>126272082</v>
+      </c>
+      <c r="E108">
+        <v>1212</v>
+      </c>
+      <c r="F108" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G108" s="2">
+        <v>45381</v>
+      </c>
+      <c r="I108">
+        <v>42</v>
+      </c>
+      <c r="J108">
+        <v>8001</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>126875800</v>
+      </c>
+      <c r="E109">
+        <v>1212</v>
+      </c>
+      <c r="F109" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G109" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I109">
+        <v>42</v>
+      </c>
+      <c r="J109">
+        <v>8001</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>126893769</v>
+      </c>
+      <c r="E110">
+        <v>1211</v>
+      </c>
+      <c r="F110" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G110" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I110">
+        <v>42</v>
+      </c>
+      <c r="J110">
+        <v>8001</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>126972179</v>
+      </c>
+      <c r="E111">
+        <v>1211</v>
+      </c>
+      <c r="F111" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G111" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I111">
+        <v>42</v>
+      </c>
+      <c r="J111">
+        <v>8001</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>127113503</v>
+      </c>
+      <c r="E112">
+        <v>1211</v>
+      </c>
+      <c r="F112" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G112" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I112">
+        <v>42</v>
+      </c>
+      <c r="J112">
+        <v>8001</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>124411489</v>
+      </c>
+      <c r="E113">
+        <v>601</v>
+      </c>
+      <c r="F113" s="2">
+        <v>45384</v>
+      </c>
+      <c r="G113" s="2">
+        <v>45371</v>
+      </c>
+      <c r="I113">
+        <v>42</v>
+      </c>
+      <c r="J113">
+        <v>8017</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>127149457</v>
+      </c>
+      <c r="E114">
+        <v>601</v>
+      </c>
+      <c r="F114" s="2">
+        <v>45376</v>
+      </c>
+      <c r="G114" s="2">
+        <v>45376</v>
+      </c>
+      <c r="I114">
+        <v>42</v>
+      </c>
+      <c r="J114">
+        <v>8013</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>127149459</v>
+      </c>
+      <c r="E115">
+        <v>601</v>
+      </c>
+      <c r="F115" s="2">
+        <v>45376</v>
+      </c>
+      <c r="G115" s="2">
+        <v>45376</v>
+      </c>
+      <c r="I115">
+        <v>42</v>
+      </c>
+      <c r="J115">
+        <v>8013</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>127150185</v>
+      </c>
+      <c r="E116">
+        <v>601</v>
+      </c>
+      <c r="F116" s="2">
+        <v>45376</v>
+      </c>
+      <c r="G116" s="2">
+        <v>45376</v>
+      </c>
+      <c r="I116">
+        <v>42</v>
+      </c>
+      <c r="J116">
+        <v>8013</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>127150197</v>
+      </c>
+      <c r="E117">
+        <v>601</v>
+      </c>
+      <c r="F117" s="2">
+        <v>45376</v>
+      </c>
+      <c r="G117" s="2">
+        <v>45376</v>
+      </c>
+      <c r="I117">
+        <v>42</v>
+      </c>
+      <c r="J117">
+        <v>8013</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>127150284</v>
+      </c>
+      <c r="E118">
+        <v>601</v>
+      </c>
+      <c r="F118" s="2">
+        <v>45376</v>
+      </c>
+      <c r="G118" s="2">
+        <v>45376</v>
+      </c>
+      <c r="I118">
+        <v>42</v>
+      </c>
+      <c r="J118">
+        <v>8013</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>124072656</v>
+      </c>
+      <c r="E119">
+        <v>1211</v>
+      </c>
+      <c r="F119" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G119" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I119">
+        <v>42</v>
+      </c>
+      <c r="J119">
         <v>715</v>
       </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>125994157</v>
+      </c>
+      <c r="E120">
+        <v>1211</v>
+      </c>
+      <c r="F120" s="2">
+        <v>45384</v>
+      </c>
+      <c r="G120" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I120">
+        <v>42</v>
+      </c>
+      <c r="J120">
+        <v>715</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>127128345</v>
+      </c>
+      <c r="E121">
+        <v>1211</v>
+      </c>
+      <c r="F121" s="2">
+        <v>45384</v>
+      </c>
+      <c r="G121" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I121">
+        <v>42</v>
+      </c>
+      <c r="J121">
+        <v>715</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>127209589</v>
+      </c>
+      <c r="E122">
+        <v>1211</v>
+      </c>
+      <c r="F122" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G122" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I122">
+        <v>42</v>
+      </c>
+      <c r="J122">
+        <v>715</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>127210074</v>
+      </c>
+      <c r="E123">
+        <v>1212</v>
+      </c>
+      <c r="F123" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G123" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I123">
+        <v>42</v>
+      </c>
+      <c r="J123">
+        <v>715</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+      <c r="Q123">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>127210662</v>
+      </c>
+      <c r="E124">
+        <v>1212</v>
+      </c>
+      <c r="F124" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G124" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I124">
+        <v>42</v>
+      </c>
+      <c r="J124">
+        <v>715</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>127211023</v>
+      </c>
+      <c r="E125">
+        <v>1211</v>
+      </c>
+      <c r="F125" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G125" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I125">
+        <v>42</v>
+      </c>
+      <c r="J125">
+        <v>715</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="Q125">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>127211142</v>
+      </c>
+      <c r="E126">
+        <v>1211</v>
+      </c>
+      <c r="F126" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G126" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I126">
+        <v>42</v>
+      </c>
+      <c r="J126">
+        <v>715</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>127213082</v>
+      </c>
+      <c r="E127">
+        <v>1212</v>
+      </c>
+      <c r="F127" s="2">
+        <v>45383</v>
+      </c>
+      <c r="G127" s="2">
+        <v>45383</v>
+      </c>
+      <c r="I127">
+        <v>42</v>
+      </c>
+      <c r="J127">
+        <v>715</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>127221992</v>
+      </c>
+      <c r="E128">
+        <v>1211</v>
+      </c>
+      <c r="F128" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G128" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I128">
+        <v>42</v>
+      </c>
+      <c r="J128">
+        <v>715</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>127223257</v>
+      </c>
+      <c r="E129">
+        <v>1211</v>
+      </c>
+      <c r="F129" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G129" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I129">
+        <v>42</v>
+      </c>
+      <c r="J129">
+        <v>715</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+      <c r="Q129">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>127223585</v>
+      </c>
+      <c r="E130">
+        <v>1212</v>
+      </c>
+      <c r="F130" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G130" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I130">
+        <v>42</v>
+      </c>
+      <c r="J130">
+        <v>715</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>127224806</v>
+      </c>
+      <c r="E131">
+        <v>1211</v>
+      </c>
+      <c r="F131" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G131" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I131">
+        <v>42</v>
+      </c>
+      <c r="J131">
+        <v>715</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>127225461</v>
+      </c>
+      <c r="E132">
+        <v>1211</v>
+      </c>
+      <c r="F132" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G132" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I132">
+        <v>42</v>
+      </c>
+      <c r="J132">
+        <v>715</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>127225592</v>
+      </c>
+      <c r="E133">
+        <v>1211</v>
+      </c>
+      <c r="F133" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G133" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I133">
+        <v>42</v>
+      </c>
+      <c r="J133">
+        <v>715</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>127225618</v>
+      </c>
+      <c r="E134">
+        <v>1211</v>
+      </c>
+      <c r="F134" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G134" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I134">
+        <v>42</v>
+      </c>
+      <c r="J134">
+        <v>715</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>127228257</v>
+      </c>
+      <c r="E135">
+        <v>1212</v>
+      </c>
+      <c r="F135" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G135" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I135">
+        <v>42</v>
+      </c>
+      <c r="J135">
+        <v>715</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>127228923</v>
+      </c>
+      <c r="E136">
+        <v>1211</v>
+      </c>
+      <c r="F136" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G136" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I136">
+        <v>42</v>
+      </c>
+      <c r="J136">
+        <v>715</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>127231061</v>
+      </c>
+      <c r="E137">
+        <v>1211</v>
+      </c>
+      <c r="F137" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G137" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I137">
+        <v>42</v>
+      </c>
+      <c r="J137">
+        <v>715</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>127231434</v>
+      </c>
+      <c r="E138">
+        <v>1212</v>
+      </c>
+      <c r="F138" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G138" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I138">
+        <v>42</v>
+      </c>
+      <c r="J138">
+        <v>715</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>127232389</v>
+      </c>
+      <c r="E139">
+        <v>1212</v>
+      </c>
+      <c r="F139" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G139" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I139">
+        <v>42</v>
+      </c>
+      <c r="J139">
+        <v>715</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>127232466</v>
+      </c>
+      <c r="E140">
+        <v>1211</v>
+      </c>
+      <c r="F140" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G140" s="2">
+        <v>45384</v>
+      </c>
+      <c r="I140">
+        <v>42</v>
+      </c>
+      <c r="J140">
+        <v>715</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>127238237</v>
+      </c>
+      <c r="E141">
+        <v>1211</v>
+      </c>
+      <c r="F141" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G141" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I141">
+        <v>42</v>
+      </c>
+      <c r="J141">
+        <v>715</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>127240902</v>
+      </c>
+      <c r="E142">
+        <v>1211</v>
+      </c>
+      <c r="F142" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G142" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I142">
+        <v>42</v>
+      </c>
+      <c r="J142">
+        <v>715</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>127241003</v>
+      </c>
+      <c r="E143">
+        <v>1211</v>
+      </c>
+      <c r="F143" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G143" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I143">
+        <v>42</v>
+      </c>
+      <c r="J143">
+        <v>715</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>127241421</v>
+      </c>
+      <c r="E144">
+        <v>1211</v>
+      </c>
+      <c r="F144" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G144" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I144">
+        <v>42</v>
+      </c>
+      <c r="J144">
+        <v>715</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>0</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>0</v>
+      </c>
+      <c r="Q144">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>127241838</v>
+      </c>
+      <c r="E145">
+        <v>1211</v>
+      </c>
+      <c r="F145" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G145" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I145">
+        <v>42</v>
+      </c>
+      <c r="J145">
+        <v>715</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>0</v>
+      </c>
+      <c r="Q145">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>127243348</v>
+      </c>
+      <c r="E146">
+        <v>1211</v>
+      </c>
+      <c r="F146" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G146" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I146">
+        <v>42</v>
+      </c>
+      <c r="J146">
+        <v>715</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>127243440</v>
+      </c>
+      <c r="E147">
+        <v>1211</v>
+      </c>
+      <c r="F147" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G147" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I147">
+        <v>42</v>
+      </c>
+      <c r="J147">
+        <v>715</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>0</v>
+      </c>
+      <c r="Q147">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>127244338</v>
+      </c>
+      <c r="E148">
+        <v>1212</v>
+      </c>
+      <c r="F148" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G148" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I148">
+        <v>42</v>
+      </c>
+      <c r="J148">
+        <v>715</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>0</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>0</v>
+      </c>
+      <c r="Q148">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>127245008</v>
+      </c>
+      <c r="E149">
+        <v>1212</v>
+      </c>
+      <c r="F149" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G149" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I149">
+        <v>42</v>
+      </c>
+      <c r="J149">
+        <v>715</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <v>0</v>
+      </c>
+      <c r="Q149">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>127245138</v>
+      </c>
+      <c r="E150">
+        <v>1211</v>
+      </c>
+      <c r="F150" s="2">
+        <v>45385</v>
+      </c>
+      <c r="G150" s="2">
+        <v>45385</v>
+      </c>
+      <c r="I150">
+        <v>42</v>
+      </c>
+      <c r="J150">
+        <v>715</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>0</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>0</v>
+      </c>
+      <c r="Q150">
         <v>61</v>
       </c>
     </row>
@@ -3980,12 +6260,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{249CD703-0AE7-46A1-BA6D-A19361B97C73}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:Q198"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -4038,7 +6318,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>125887260</v>
       </c>
@@ -4076,7 +6356,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>125890823</v>
       </c>
@@ -4114,7 +6394,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>125891086</v>
       </c>
@@ -4152,7 +6432,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>125892224</v>
       </c>
@@ -4190,7 +6470,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>125892709</v>
       </c>
@@ -4228,7 +6508,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>125892901</v>
       </c>
@@ -4266,7 +6546,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>125892906</v>
       </c>
@@ -4304,7 +6584,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>125893564</v>
       </c>
@@ -4342,7 +6622,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>125893722</v>
       </c>
@@ -4380,7 +6660,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>125895193</v>
       </c>
@@ -4418,7 +6698,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>125896177</v>
       </c>
@@ -4456,7 +6736,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>125898007</v>
       </c>
@@ -4494,7 +6774,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>125900254</v>
       </c>
@@ -4532,7 +6812,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>125901787</v>
       </c>
@@ -4570,7 +6850,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>125901795</v>
       </c>
@@ -4608,7 +6888,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>125903262</v>
       </c>
@@ -4646,7 +6926,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>125904221</v>
       </c>
@@ -4684,7 +6964,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>125904238</v>
       </c>
@@ -4722,7 +7002,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>125907420</v>
       </c>
@@ -4760,7 +7040,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>125907797</v>
       </c>
@@ -4798,7 +7078,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>125908056</v>
       </c>
@@ -4836,7 +7116,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>125908177</v>
       </c>
@@ -4874,7 +7154,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>125908231</v>
       </c>
@@ -4912,7 +7192,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>125908843</v>
       </c>
@@ -4950,7 +7230,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>125909142</v>
       </c>
@@ -4988,7 +7268,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>125909933</v>
       </c>
@@ -5026,7 +7306,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>125910114</v>
       </c>
@@ -5064,7 +7344,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>125910400</v>
       </c>
@@ -5102,7 +7382,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>125910838</v>
       </c>
@@ -5140,7 +7420,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>125912176</v>
       </c>
@@ -5178,7 +7458,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>125912843</v>
       </c>
@@ -5216,7 +7496,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>125913133</v>
       </c>
@@ -5254,7 +7534,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>125913427</v>
       </c>
@@ -5292,7 +7572,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>125914356</v>
       </c>
@@ -5330,7 +7610,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>125914668</v>
       </c>
@@ -5368,7 +7648,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>125914978</v>
       </c>
@@ -5406,7 +7686,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>125918666</v>
       </c>
@@ -5444,7 +7724,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>125920065</v>
       </c>
@@ -5482,7 +7762,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>125924508</v>
       </c>
@@ -5520,7 +7800,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>125926112</v>
       </c>
@@ -5558,7 +7838,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>125927235</v>
       </c>
@@ -5596,7 +7876,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>125927477</v>
       </c>
@@ -5634,7 +7914,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>125927712</v>
       </c>
@@ -5672,7 +7952,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>125927811</v>
       </c>
@@ -5710,7 +7990,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>125928500</v>
       </c>
@@ -5748,7 +8028,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>125928781</v>
       </c>
@@ -5786,7 +8066,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>125928935</v>
       </c>
@@ -5824,7 +8104,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>125929845</v>
       </c>
@@ -5862,7 +8142,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>125930432</v>
       </c>
@@ -5900,7 +8180,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>125931903</v>
       </c>
@@ -5938,7 +8218,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>125932521</v>
       </c>
@@ -5976,7 +8256,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>125932669</v>
       </c>
@@ -6014,7 +8294,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>125933582</v>
       </c>
@@ -6052,7 +8332,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>125933608</v>
       </c>
@@ -6090,7 +8370,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>125935767</v>
       </c>
@@ -6128,7 +8408,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>125938612</v>
       </c>
@@ -6166,7 +8446,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>125944749</v>
       </c>
@@ -6204,7 +8484,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>125945240</v>
       </c>
@@ -6242,7 +8522,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>125949456</v>
       </c>
@@ -6280,7 +8560,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>125958349</v>
       </c>
@@ -6318,7 +8598,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>125958503</v>
       </c>
@@ -6356,7 +8636,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>125960344</v>
       </c>
@@ -6394,7 +8674,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>125962131</v>
       </c>
@@ -6432,7 +8712,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>125965767</v>
       </c>
@@ -6470,7 +8750,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>125965877</v>
       </c>
@@ -6508,7 +8788,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>125969356</v>
       </c>
@@ -6546,7 +8826,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>125971901</v>
       </c>
@@ -6584,7 +8864,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>125976084</v>
       </c>
@@ -6622,7 +8902,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>125976278</v>
       </c>
@@ -6660,7 +8940,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>125977146</v>
       </c>
@@ -6698,7 +8978,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>125977504</v>
       </c>
@@ -6736,7 +9016,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>125981162</v>
       </c>
@@ -6774,7 +9054,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>125983181</v>
       </c>
@@ -6812,7 +9092,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>125983593</v>
       </c>
@@ -6850,7 +9130,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>125984782</v>
       </c>
@@ -6888,7 +9168,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>125992174</v>
       </c>
@@ -6926,7 +9206,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>125992452</v>
       </c>
@@ -6964,7 +9244,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>125997050</v>
       </c>
@@ -7002,7 +9282,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>126009389</v>
       </c>
@@ -7040,7 +9320,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>126012544</v>
       </c>
@@ -7078,7 +9358,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>126013965</v>
       </c>
@@ -7116,7 +9396,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>126015225</v>
       </c>
@@ -7154,7 +9434,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>126015257</v>
       </c>
@@ -7192,7 +9472,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>126020235</v>
       </c>
@@ -7230,7 +9510,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>126028210</v>
       </c>
@@ -7268,7 +9548,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>126028956</v>
       </c>
@@ -7306,7 +9586,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>126029328</v>
       </c>
@@ -7344,7 +9624,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>126029650</v>
       </c>
@@ -7382,7 +9662,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>126029868</v>
       </c>
@@ -7420,7 +9700,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>126033233</v>
       </c>
@@ -7458,7 +9738,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>126036666</v>
       </c>
@@ -7496,7 +9776,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>126037292</v>
       </c>
@@ -7534,7 +9814,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>126040785</v>
       </c>
@@ -7572,7 +9852,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>126040979</v>
       </c>
@@ -7610,7 +9890,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>126041187</v>
       </c>
@@ -7648,7 +9928,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>126043144</v>
       </c>
@@ -7686,7 +9966,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>126045060</v>
       </c>
@@ -7724,7 +10004,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>126045520</v>
       </c>
@@ -7762,7 +10042,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>126049650</v>
       </c>
@@ -7800,7 +10080,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>126051286</v>
       </c>
@@ -7838,7 +10118,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>126052567</v>
       </c>
@@ -7876,7 +10156,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>126057040</v>
       </c>
@@ -7914,7 +10194,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>126057529</v>
       </c>
@@ -7952,7 +10232,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>126057835</v>
       </c>
@@ -7990,7 +10270,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>126058412</v>
       </c>
@@ -8028,7 +10308,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>126063955</v>
       </c>
@@ -8066,7 +10346,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>126064498</v>
       </c>
@@ -8104,7 +10384,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>126065211</v>
       </c>
@@ -8142,7 +10422,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>126074608</v>
       </c>
@@ -8180,7 +10460,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>126078394</v>
       </c>
@@ -8218,7 +10498,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>126080342</v>
       </c>
@@ -8256,7 +10536,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>126082448</v>
       </c>
@@ -8294,7 +10574,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>126082622</v>
       </c>
@@ -8332,7 +10612,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>126084723</v>
       </c>
@@ -8370,7 +10650,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>126086747</v>
       </c>
@@ -8408,7 +10688,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>126088025</v>
       </c>
@@ -8446,7 +10726,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>126088302</v>
       </c>
@@ -8484,7 +10764,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>126088413</v>
       </c>
@@ -8522,7 +10802,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>126088528</v>
       </c>
@@ -8560,7 +10840,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>126089277</v>
       </c>
@@ -8598,7 +10878,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>126089435</v>
       </c>
@@ -8636,7 +10916,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>126090634</v>
       </c>
@@ -8674,7 +10954,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>126093282</v>
       </c>
@@ -8712,7 +10992,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>126093649</v>
       </c>
@@ -8750,7 +11030,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>126097132</v>
       </c>
@@ -8788,7 +11068,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126098812</v>
       </c>
@@ -8826,7 +11106,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>126099189</v>
       </c>
@@ -8864,7 +11144,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>126099880</v>
       </c>
@@ -8902,7 +11182,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>126100047</v>
       </c>
@@ -8940,7 +11220,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>126101516</v>
       </c>
@@ -8978,7 +11258,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>126102394</v>
       </c>
@@ -9016,7 +11296,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>126104952</v>
       </c>
@@ -9054,7 +11334,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>126106789</v>
       </c>
@@ -9092,7 +11372,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>126111482</v>
       </c>
@@ -9130,7 +11410,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>126111872</v>
       </c>
@@ -9168,7 +11448,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>126119068</v>
       </c>
@@ -9206,7 +11486,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>126120069</v>
       </c>
@@ -9244,7 +11524,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>126120915</v>
       </c>
@@ -9282,7 +11562,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>126120976</v>
       </c>
@@ -9320,7 +11600,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>126122910</v>
       </c>
@@ -9358,7 +11638,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>126130699</v>
       </c>
@@ -9396,7 +11676,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>126131117</v>
       </c>
@@ -9434,7 +11714,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>126136404</v>
       </c>
@@ -9472,7 +11752,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>126140055</v>
       </c>
@@ -9510,7 +11790,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>126147040</v>
       </c>
@@ -9548,7 +11828,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>126155748</v>
       </c>
@@ -9586,7 +11866,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>126155838</v>
       </c>
@@ -9624,7 +11904,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>126157906</v>
       </c>
@@ -9662,7 +11942,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>126158151</v>
       </c>
@@ -9700,7 +11980,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>126162518</v>
       </c>
@@ -9738,7 +12018,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>126164369</v>
       </c>
@@ -9776,7 +12056,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>126164882</v>
       </c>
@@ -9814,7 +12094,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>126165476</v>
       </c>
@@ -9852,7 +12132,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>126165996</v>
       </c>
@@ -9890,7 +12170,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>126167070</v>
       </c>
@@ -9928,7 +12208,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>126168025</v>
       </c>
@@ -9966,7 +12246,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>126168249</v>
       </c>
@@ -10004,7 +12284,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>126173180</v>
       </c>
@@ -10042,7 +12322,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>126174316</v>
       </c>
@@ -10080,7 +12360,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>126174669</v>
       </c>
@@ -10118,7 +12398,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>126176463</v>
       </c>
@@ -10156,7 +12436,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>126176884</v>
       </c>
@@ -10194,7 +12474,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>126185047</v>
       </c>
@@ -10232,7 +12512,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>126185760</v>
       </c>
@@ -10270,7 +12550,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>126187183</v>
       </c>
@@ -10308,7 +12588,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>126187745</v>
       </c>
@@ -10346,7 +12626,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>126192174</v>
       </c>
@@ -10384,7 +12664,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>126192469</v>
       </c>
@@ -10422,7 +12702,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>126192814</v>
       </c>
@@ -10460,7 +12740,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>126193665</v>
       </c>
@@ -10498,7 +12778,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>126193855</v>
       </c>
@@ -10536,7 +12816,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>126194373</v>
       </c>
@@ -10574,7 +12854,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>126195588</v>
       </c>
@@ -10612,7 +12892,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>126197992</v>
       </c>
@@ -10650,7 +12930,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>126198450</v>
       </c>
@@ -10688,7 +12968,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>126198510</v>
       </c>
@@ -10726,7 +13006,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>126198929</v>
       </c>
@@ -10764,7 +13044,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>126201454</v>
       </c>
@@ -10802,7 +13082,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>126201460</v>
       </c>
@@ -10840,7 +13120,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>126201930</v>
       </c>
@@ -10878,7 +13158,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>126201991</v>
       </c>
@@ -10916,7 +13196,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>126212316</v>
       </c>
@@ -10954,7 +13234,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>126213617</v>
       </c>
@@ -10992,7 +13272,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>126216332</v>
       </c>
@@ -11030,7 +13310,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>126218950</v>
       </c>
@@ -11068,7 +13348,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>126230676</v>
       </c>
@@ -11106,7 +13386,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>126231536</v>
       </c>
@@ -11144,7 +13424,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>126237618</v>
       </c>
@@ -11182,7 +13462,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>126245598</v>
       </c>
@@ -11220,7 +13500,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>126265244</v>
       </c>
@@ -11258,7 +13538,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>126265499</v>
       </c>
@@ -11296,7 +13576,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>126266542</v>
       </c>
@@ -11334,7 +13614,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>126268776</v>
       </c>
@@ -11372,7 +13652,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>126280119</v>
       </c>
@@ -11410,7 +13690,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>126280477</v>
       </c>
@@ -11448,7 +13728,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>126281587</v>
       </c>
@@ -11486,7 +13766,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>126281992</v>
       </c>
@@ -11555,31 +13835,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A32530-7A9A-461A-BDC4-BEDBCFC81B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68C7DC7-75D2-4179-912E-C0AEF3C320B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$77</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q150"/>
+  <dimension ref="A1:Q138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -585,22 +585,22 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>127208583</v>
+        <v>124891623</v>
       </c>
       <c r="E2">
-        <v>1211</v>
+        <v>2002</v>
       </c>
       <c r="F2" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
       <c r="G2" s="2">
-        <v>45383</v>
+        <v>45387</v>
       </c>
       <c r="I2">
         <v>42</v>
       </c>
       <c r="J2">
-        <v>1735</v>
+        <v>8004</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -623,22 +623,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>127213295</v>
+        <v>125266621</v>
       </c>
       <c r="E3">
-        <v>1211</v>
+        <v>2002</v>
       </c>
       <c r="F3" s="2">
-        <v>45383</v>
+        <v>45387</v>
       </c>
       <c r="G3" s="2">
-        <v>45383</v>
+        <v>45387</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>1735</v>
+        <v>8004</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -661,16 +661,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>127213974</v>
+        <v>127222638</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="G4" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I4">
         <v>42</v>
@@ -699,16 +699,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>127214844</v>
+        <v>127225835</v>
       </c>
       <c r="E5">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45383</v>
+        <v>45385</v>
       </c>
       <c r="G5" s="2">
-        <v>45383</v>
+        <v>45384</v>
       </c>
       <c r="I5">
         <v>42</v>
@@ -737,22 +737,22 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>123487367</v>
+        <v>127232212</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45386</v>
+        <v>45384</v>
       </c>
       <c r="G6" s="2">
-        <v>45386</v>
+        <v>45384</v>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -775,22 +775,22 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>123601906</v>
+        <v>127234893</v>
       </c>
       <c r="E7">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="G7" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -813,22 +813,22 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>123703137</v>
+        <v>127241760</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="G8" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="I8">
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -851,7 +851,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>123716326</v>
+        <v>127242453</v>
       </c>
       <c r="E9">
         <v>1211</v>
@@ -860,13 +860,13 @@
         <v>45386</v>
       </c>
       <c r="G9" s="2">
-        <v>45386</v>
+        <v>45385</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -889,22 +889,22 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>123875216</v>
+        <v>127249950</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
+        <v>45387</v>
+      </c>
+      <c r="G10" s="2">
         <v>45386</v>
       </c>
-      <c r="G10" s="2">
-        <v>45384</v>
-      </c>
       <c r="I10">
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -927,13 +927,13 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>123971580</v>
+        <v>127251464</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G11" s="2">
         <v>45386</v>
@@ -942,7 +942,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -965,7 +965,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>124044346</v>
+        <v>127256936</v>
       </c>
       <c r="E12">
         <v>1211</v>
@@ -980,7 +980,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1003,13 +1003,13 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>124184188</v>
+        <v>123687952</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G13" s="2">
         <v>45386</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>124196438</v>
+        <v>123743818</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G14" s="2">
-        <v>45377</v>
+        <v>45387</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>124322079</v>
+        <v>123805768</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G15" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>124322872</v>
+        <v>123821195</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G16" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>124329808</v>
+        <v>123824005</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
+        <v>45387</v>
+      </c>
+      <c r="G17" s="2">
         <v>45386</v>
-      </c>
-      <c r="G17" s="2">
-        <v>45384</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>124598258</v>
+        <v>123879266</v>
       </c>
       <c r="E18">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F18" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G18" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>124634661</v>
+        <v>123915789</v>
       </c>
       <c r="E19">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F19" s="2">
+        <v>45387</v>
+      </c>
+      <c r="G19" s="2">
         <v>45386</v>
-      </c>
-      <c r="G19" s="2">
-        <v>45383</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>124635455</v>
+        <v>123962647</v>
       </c>
       <c r="E20">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G20" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>124683975</v>
+        <v>123977848</v>
       </c>
       <c r="E21">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F21" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G21" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>124706213</v>
+        <v>124173447</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G22" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1383,16 +1383,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>125250574</v>
+        <v>124207490</v>
       </c>
       <c r="E23">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G23" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1421,16 +1421,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>125360318</v>
+        <v>124216496</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G24" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1459,16 +1459,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>125403476</v>
+        <v>124217292</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G25" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I25">
         <v>42</v>
@@ -1497,16 +1497,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>125485872</v>
+        <v>124254494</v>
       </c>
       <c r="E26">
         <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G26" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I26">
         <v>42</v>
@@ -1535,16 +1535,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>125717517</v>
+        <v>124351584</v>
       </c>
       <c r="E27">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F27" s="2">
-        <v>45386</v>
+        <v>45388</v>
       </c>
       <c r="G27" s="2">
-        <v>45386</v>
+        <v>45388</v>
       </c>
       <c r="I27">
         <v>42</v>
@@ -1573,16 +1573,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>125807781</v>
+        <v>124494755</v>
       </c>
       <c r="E28">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G28" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I28">
         <v>42</v>
@@ -1611,16 +1611,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>125936370</v>
+        <v>124754756</v>
       </c>
       <c r="E29">
         <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45386</v>
+        <v>45388</v>
       </c>
       <c r="G29" s="2">
-        <v>45386</v>
+        <v>45388</v>
       </c>
       <c r="I29">
         <v>42</v>
@@ -1649,16 +1649,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>125988584</v>
+        <v>124901324</v>
       </c>
       <c r="E30">
         <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G30" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I30">
         <v>42</v>
@@ -1687,16 +1687,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>126278313</v>
+        <v>124922681</v>
       </c>
       <c r="E31">
         <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G31" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I31">
         <v>42</v>
@@ -1725,16 +1725,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>126290624</v>
+        <v>125024343</v>
       </c>
       <c r="E32">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F32" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G32" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I32">
         <v>42</v>
@@ -1763,16 +1763,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>126518639</v>
+        <v>125578026</v>
       </c>
       <c r="E33">
         <v>1211</v>
       </c>
       <c r="F33" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G33" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I33">
         <v>42</v>
@@ -1801,16 +1801,16 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>126596251</v>
+        <v>125586006</v>
       </c>
       <c r="E34">
         <v>1211</v>
       </c>
       <c r="F34" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G34" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I34">
         <v>42</v>
@@ -1839,16 +1839,16 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>126614625</v>
+        <v>125623293</v>
       </c>
       <c r="E35">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F35" s="2">
+        <v>45387</v>
+      </c>
+      <c r="G35" s="2">
         <v>45386</v>
-      </c>
-      <c r="G35" s="2">
-        <v>45385</v>
       </c>
       <c r="I35">
         <v>42</v>
@@ -1877,16 +1877,16 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>126816319</v>
+        <v>125711157</v>
       </c>
       <c r="E36">
         <v>1211</v>
       </c>
       <c r="F36" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G36" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I36">
         <v>42</v>
@@ -1915,16 +1915,16 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>126835056</v>
+        <v>125790389</v>
       </c>
       <c r="E37">
         <v>1211</v>
       </c>
       <c r="F37" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G37" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I37">
         <v>42</v>
@@ -1953,16 +1953,16 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>127009794</v>
+        <v>125837967</v>
       </c>
       <c r="E38">
         <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G38" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I38">
         <v>42</v>
@@ -1991,16 +1991,16 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>127071870</v>
+        <v>125839602</v>
       </c>
       <c r="E39">
         <v>1211</v>
       </c>
       <c r="F39" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G39" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I39">
         <v>42</v>
@@ -2029,16 +2029,16 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>127190566</v>
+        <v>125935281</v>
       </c>
       <c r="E40">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F40" s="2">
-        <v>45386</v>
+        <v>45388</v>
       </c>
       <c r="G40" s="2">
-        <v>45386</v>
+        <v>45388</v>
       </c>
       <c r="I40">
         <v>42</v>
@@ -2067,22 +2067,22 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>124411489</v>
+        <v>125990369</v>
       </c>
       <c r="E41">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F41" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
       <c r="G41" s="2">
-        <v>45371</v>
+        <v>45387</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>127169044</v>
+        <v>126131697</v>
       </c>
       <c r="E42">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F42" s="2">
-        <v>45377</v>
+        <v>45387</v>
       </c>
       <c r="G42" s="2">
-        <v>45377</v>
+        <v>45387</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2143,13 +2143,13 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>124072656</v>
+        <v>126250706</v>
       </c>
       <c r="E43">
         <v>1211</v>
       </c>
       <c r="F43" s="2">
-        <v>45385</v>
+        <v>45388</v>
       </c>
       <c r="G43" s="2">
         <v>45385</v>
@@ -2158,7 +2158,7 @@
         <v>42</v>
       </c>
       <c r="J43">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>125994157</v>
+        <v>126303888</v>
       </c>
       <c r="E44">
         <v>1211</v>
       </c>
       <c r="F44" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
       <c r="G44" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2219,22 +2219,22 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>127210662</v>
+        <v>126366579</v>
       </c>
       <c r="E45">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F45" s="2">
-        <v>45383</v>
+        <v>45388</v>
       </c>
       <c r="G45" s="2">
-        <v>45383</v>
+        <v>45388</v>
       </c>
       <c r="I45">
         <v>42</v>
       </c>
       <c r="J45">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>127211023</v>
+        <v>126637858</v>
       </c>
       <c r="E46">
         <v>1211</v>
       </c>
       <c r="F46" s="2">
-        <v>45383</v>
+        <v>45387</v>
       </c>
       <c r="G46" s="2">
-        <v>45383</v>
+        <v>45387</v>
       </c>
       <c r="I46">
         <v>42</v>
       </c>
       <c r="J46">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2295,22 +2295,22 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>127211142</v>
+        <v>126726655</v>
       </c>
       <c r="E47">
         <v>1211</v>
       </c>
       <c r="F47" s="2">
-        <v>45383</v>
+        <v>45387</v>
       </c>
       <c r="G47" s="2">
-        <v>45383</v>
+        <v>45387</v>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2333,22 +2333,22 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>127221992</v>
+        <v>126766723</v>
       </c>
       <c r="E48">
         <v>1211</v>
       </c>
       <c r="F48" s="2">
-        <v>45385</v>
+        <v>45388</v>
       </c>
       <c r="G48" s="2">
-        <v>45384</v>
+        <v>45388</v>
       </c>
       <c r="I48">
         <v>42</v>
       </c>
       <c r="J48">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2371,22 +2371,22 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>127223257</v>
+        <v>126988819</v>
       </c>
       <c r="E49">
         <v>1211</v>
       </c>
       <c r="F49" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G49" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
       <c r="I49">
         <v>42</v>
       </c>
       <c r="J49">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>127223585</v>
+        <v>126991885</v>
       </c>
       <c r="E50">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F50" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G50" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
       <c r="I50">
         <v>42</v>
       </c>
       <c r="J50">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2447,22 +2447,22 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>127224806</v>
+        <v>127056754</v>
       </c>
       <c r="E51">
         <v>1211</v>
       </c>
       <c r="F51" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G51" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
       <c r="I51">
         <v>42</v>
       </c>
       <c r="J51">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2485,22 +2485,22 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>127225592</v>
+        <v>127185427</v>
       </c>
       <c r="E52">
         <v>1211</v>
       </c>
       <c r="F52" s="2">
-        <v>45385</v>
+        <v>45388</v>
       </c>
       <c r="G52" s="2">
-        <v>45384</v>
+        <v>45388</v>
       </c>
       <c r="I52">
         <v>42</v>
       </c>
       <c r="J52">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -2523,16 +2523,16 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>127225618</v>
+        <v>127263077</v>
       </c>
       <c r="E53">
         <v>1211</v>
       </c>
       <c r="F53" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G53" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
       <c r="I53">
         <v>42</v>
@@ -2561,16 +2561,16 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>127228923</v>
+        <v>127263567</v>
       </c>
       <c r="E54">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F54" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G54" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
       <c r="I54">
         <v>42</v>
@@ -2599,16 +2599,16 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>127231061</v>
+        <v>127264250</v>
       </c>
       <c r="E55">
         <v>1211</v>
       </c>
       <c r="F55" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G55" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
       <c r="I55">
         <v>42</v>
@@ -2637,16 +2637,16 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>127238237</v>
+        <v>127265481</v>
       </c>
       <c r="E56">
         <v>1211</v>
       </c>
       <c r="F56" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G56" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I56">
         <v>42</v>
@@ -2675,16 +2675,16 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>127240902</v>
+        <v>127265635</v>
       </c>
       <c r="E57">
         <v>1211</v>
       </c>
       <c r="F57" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G57" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I57">
         <v>42</v>
@@ -2713,16 +2713,16 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>127241003</v>
+        <v>127265688</v>
       </c>
       <c r="E58">
         <v>1211</v>
       </c>
       <c r="F58" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G58" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I58">
         <v>42</v>
@@ -2751,16 +2751,16 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>127241421</v>
+        <v>127265964</v>
       </c>
       <c r="E59">
         <v>1211</v>
       </c>
       <c r="F59" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G59" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I59">
         <v>42</v>
@@ -2789,16 +2789,16 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>127241838</v>
+        <v>127266215</v>
       </c>
       <c r="E60">
         <v>1211</v>
       </c>
       <c r="F60" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G60" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I60">
         <v>42</v>
@@ -2827,16 +2827,16 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>127243348</v>
+        <v>127267388</v>
       </c>
       <c r="E61">
         <v>1211</v>
       </c>
       <c r="F61" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G61" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I61">
         <v>42</v>
@@ -2865,16 +2865,16 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>127243440</v>
+        <v>127267923</v>
       </c>
       <c r="E62">
         <v>1211</v>
       </c>
       <c r="F62" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G62" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I62">
         <v>42</v>
@@ -2903,16 +2903,16 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>127243860</v>
+        <v>127267960</v>
       </c>
       <c r="E63">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F63" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G63" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I63">
         <v>42</v>
@@ -2941,16 +2941,16 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>127244338</v>
+        <v>127268795</v>
       </c>
       <c r="E64">
         <v>1212</v>
       </c>
       <c r="F64" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G64" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I64">
         <v>42</v>
@@ -2979,16 +2979,16 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>127245008</v>
+        <v>127269159</v>
       </c>
       <c r="E65">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F65" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G65" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I65">
         <v>42</v>
@@ -3017,16 +3017,16 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>127245138</v>
+        <v>127270356</v>
       </c>
       <c r="E66">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F66" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="G66" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
       <c r="I66">
         <v>42</v>
@@ -3055,16 +3055,16 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>127248957</v>
+        <v>127270672</v>
       </c>
       <c r="E67">
         <v>1212</v>
       </c>
       <c r="F67" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G67" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I67">
         <v>42</v>
@@ -3093,16 +3093,16 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>127249438</v>
+        <v>127271979</v>
       </c>
       <c r="E68">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F68" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G68" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I68">
         <v>42</v>
@@ -3131,16 +3131,16 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>127251213</v>
+        <v>127272700</v>
       </c>
       <c r="E69">
         <v>1211</v>
       </c>
       <c r="F69" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G69" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I69">
         <v>42</v>
@@ -3169,16 +3169,16 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>127251298</v>
+        <v>127272953</v>
       </c>
       <c r="E70">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F70" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G70" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I70">
         <v>42</v>
@@ -3207,16 +3207,16 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>127251465</v>
+        <v>127273080</v>
       </c>
       <c r="E71">
         <v>1211</v>
       </c>
       <c r="F71" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G71" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I71">
         <v>42</v>
@@ -3245,16 +3245,16 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>127251846</v>
+        <v>127273976</v>
       </c>
       <c r="E72">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F72" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G72" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I72">
         <v>42</v>
@@ -3283,16 +3283,16 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>127255428</v>
+        <v>127274504</v>
       </c>
       <c r="E73">
         <v>1211</v>
       </c>
       <c r="F73" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G73" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I73">
         <v>42</v>
@@ -3321,16 +3321,16 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>127255968</v>
+        <v>127274537</v>
       </c>
       <c r="E74">
         <v>1211</v>
       </c>
       <c r="F74" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G74" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I74">
         <v>42</v>
@@ -3359,16 +3359,16 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>127255987</v>
+        <v>127274749</v>
       </c>
       <c r="E75">
         <v>1211</v>
       </c>
       <c r="F75" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G75" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I75">
         <v>42</v>
@@ -3397,16 +3397,16 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>127256985</v>
+        <v>127275706</v>
       </c>
       <c r="E76">
         <v>1212</v>
       </c>
       <c r="F76" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G76" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I76">
         <v>42</v>
@@ -3435,16 +3435,16 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>127257054</v>
+        <v>127275804</v>
       </c>
       <c r="E77">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F77" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="G77" s="2">
-        <v>45386</v>
+        <v>45387</v>
       </c>
       <c r="I77">
         <v>42</v>
@@ -3472,2778 +3472,248 @@
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>127258945</v>
-      </c>
-      <c r="E78">
-        <v>1211</v>
-      </c>
-      <c r="F78" s="2">
-        <v>45386</v>
-      </c>
-      <c r="G78" s="2">
-        <v>45386</v>
-      </c>
-      <c r="I78">
-        <v>42</v>
-      </c>
-      <c r="J78">
-        <v>715</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78">
-        <v>0</v>
-      </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
-      <c r="O78">
-        <v>0</v>
-      </c>
-      <c r="P78">
-        <v>0</v>
-      </c>
-      <c r="Q78">
-        <v>61</v>
-      </c>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>127259090</v>
-      </c>
-      <c r="E79">
-        <v>1211</v>
-      </c>
-      <c r="F79" s="2">
-        <v>45386</v>
-      </c>
-      <c r="G79" s="2">
-        <v>45386</v>
-      </c>
-      <c r="I79">
-        <v>42</v>
-      </c>
-      <c r="J79">
-        <v>715</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79">
-        <v>0</v>
-      </c>
-      <c r="P79">
-        <v>0</v>
-      </c>
-      <c r="Q79">
-        <v>61</v>
-      </c>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>127259721</v>
-      </c>
-      <c r="E80">
-        <v>1212</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45386</v>
-      </c>
-      <c r="G80" s="2">
-        <v>45386</v>
-      </c>
-      <c r="I80">
-        <v>42</v>
-      </c>
-      <c r="J80">
-        <v>715</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>0</v>
-      </c>
-      <c r="P80">
-        <v>0</v>
-      </c>
-      <c r="Q80">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>127259957</v>
-      </c>
-      <c r="E81">
-        <v>1211</v>
-      </c>
-      <c r="F81" s="2">
-        <v>45386</v>
-      </c>
-      <c r="G81" s="2">
-        <v>45386</v>
-      </c>
-      <c r="I81">
-        <v>42</v>
-      </c>
-      <c r="J81">
-        <v>715</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
-        <v>0</v>
-      </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
-      <c r="O81">
-        <v>0</v>
-      </c>
-      <c r="P81">
-        <v>0</v>
-      </c>
-      <c r="Q81">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>125598623</v>
-      </c>
-      <c r="E82">
-        <v>2002</v>
-      </c>
-      <c r="F82" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G82" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I82">
-        <v>42</v>
-      </c>
-      <c r="J82">
-        <v>8004</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>0</v>
-      </c>
-      <c r="P82">
-        <v>0</v>
-      </c>
-      <c r="Q82">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>127206437</v>
-      </c>
-      <c r="E83">
-        <v>1211</v>
-      </c>
-      <c r="F83" s="2">
-        <v>45382</v>
-      </c>
-      <c r="G83" s="2">
-        <v>45382</v>
-      </c>
-      <c r="I83">
-        <v>42</v>
-      </c>
-      <c r="J83">
-        <v>1735</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
-      <c r="O83">
-        <v>0</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
-      <c r="Q83">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>123673293</v>
-      </c>
-      <c r="E84">
-        <v>1211</v>
-      </c>
-      <c r="F84" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G84" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I84">
-        <v>42</v>
-      </c>
-      <c r="J84">
-        <v>8001</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84">
-        <v>0</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>123751967</v>
-      </c>
-      <c r="E85">
-        <v>1211</v>
-      </c>
-      <c r="F85" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G85" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I85">
-        <v>42</v>
-      </c>
-      <c r="J85">
-        <v>8001</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
-        <v>0</v>
-      </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>0</v>
-      </c>
-      <c r="P85">
-        <v>0</v>
-      </c>
-      <c r="Q85">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>123780300</v>
-      </c>
-      <c r="E86">
-        <v>1211</v>
-      </c>
-      <c r="F86" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G86" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I86">
-        <v>42</v>
-      </c>
-      <c r="J86">
-        <v>8001</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86">
-        <v>0</v>
-      </c>
-      <c r="P86">
-        <v>0</v>
-      </c>
-      <c r="Q86">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>123849528</v>
-      </c>
-      <c r="E87">
-        <v>1211</v>
-      </c>
-      <c r="F87" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G87" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I87">
-        <v>42</v>
-      </c>
-      <c r="J87">
-        <v>8001</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
-      <c r="M87">
-        <v>0</v>
-      </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
-      <c r="O87">
-        <v>0</v>
-      </c>
-      <c r="P87">
-        <v>0</v>
-      </c>
-      <c r="Q87">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>123862293</v>
-      </c>
-      <c r="E88">
-        <v>1211</v>
-      </c>
-      <c r="F88" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G88" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I88">
-        <v>42</v>
-      </c>
-      <c r="J88">
-        <v>8001</v>
-      </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88">
-        <v>0</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88">
-        <v>0</v>
-      </c>
-      <c r="P88">
-        <v>0</v>
-      </c>
-      <c r="Q88">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>123938570</v>
-      </c>
-      <c r="E89">
-        <v>1211</v>
-      </c>
-      <c r="F89" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G89" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I89">
-        <v>42</v>
-      </c>
-      <c r="J89">
-        <v>8001</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
-        <v>0</v>
-      </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <v>0</v>
-      </c>
-      <c r="P89">
-        <v>0</v>
-      </c>
-      <c r="Q89">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>124236138</v>
-      </c>
-      <c r="E90">
-        <v>1211</v>
-      </c>
-      <c r="F90" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G90" s="2">
-        <v>45377</v>
-      </c>
-      <c r="I90">
-        <v>42</v>
-      </c>
-      <c r="J90">
-        <v>8001</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>124319286</v>
-      </c>
-      <c r="E91">
-        <v>1211</v>
-      </c>
-      <c r="F91" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G91" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I91">
-        <v>42</v>
-      </c>
-      <c r="J91">
-        <v>8001</v>
-      </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="M91">
-        <v>0</v>
-      </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
-      <c r="O91">
-        <v>0</v>
-      </c>
-      <c r="P91">
-        <v>0</v>
-      </c>
-      <c r="Q91">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>124335284</v>
-      </c>
-      <c r="E92">
-        <v>1211</v>
-      </c>
-      <c r="F92" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G92" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I92">
-        <v>42</v>
-      </c>
-      <c r="J92">
-        <v>8001</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
-        <v>0</v>
-      </c>
-      <c r="N92">
-        <v>0</v>
-      </c>
-      <c r="O92">
-        <v>0</v>
-      </c>
-      <c r="P92">
-        <v>0</v>
-      </c>
-      <c r="Q92">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>124409211</v>
-      </c>
-      <c r="E93">
-        <v>1211</v>
-      </c>
-      <c r="F93" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G93" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I93">
-        <v>42</v>
-      </c>
-      <c r="J93">
-        <v>8001</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
-        <v>0</v>
-      </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
-      <c r="O93">
-        <v>0</v>
-      </c>
-      <c r="P93">
-        <v>0</v>
-      </c>
-      <c r="Q93">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>124490600</v>
-      </c>
-      <c r="E94">
-        <v>1211</v>
-      </c>
-      <c r="F94" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G94" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I94">
-        <v>42</v>
-      </c>
-      <c r="J94">
-        <v>8001</v>
-      </c>
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="M94">
-        <v>0</v>
-      </c>
-      <c r="N94">
-        <v>0</v>
-      </c>
-      <c r="O94">
-        <v>0</v>
-      </c>
-      <c r="P94">
-        <v>0</v>
-      </c>
-      <c r="Q94">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>124766549</v>
-      </c>
-      <c r="E95">
-        <v>1211</v>
-      </c>
-      <c r="F95" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G95" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I95">
-        <v>42</v>
-      </c>
-      <c r="J95">
-        <v>8001</v>
-      </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="M95">
-        <v>0</v>
-      </c>
-      <c r="N95">
-        <v>0</v>
-      </c>
-      <c r="O95">
-        <v>0</v>
-      </c>
-      <c r="P95">
-        <v>0</v>
-      </c>
-      <c r="Q95">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>125155796</v>
-      </c>
-      <c r="E96">
-        <v>1212</v>
-      </c>
-      <c r="F96" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G96" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I96">
-        <v>42</v>
-      </c>
-      <c r="J96">
-        <v>8001</v>
-      </c>
-      <c r="L96">
-        <v>0</v>
-      </c>
-      <c r="M96">
-        <v>0</v>
-      </c>
-      <c r="N96">
-        <v>0</v>
-      </c>
-      <c r="O96">
-        <v>0</v>
-      </c>
-      <c r="P96">
-        <v>0</v>
-      </c>
-      <c r="Q96">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>125187864</v>
-      </c>
-      <c r="E97">
-        <v>1211</v>
-      </c>
-      <c r="F97" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G97" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I97">
-        <v>42</v>
-      </c>
-      <c r="J97">
-        <v>8001</v>
-      </c>
-      <c r="L97">
-        <v>0</v>
-      </c>
-      <c r="M97">
-        <v>0</v>
-      </c>
-      <c r="N97">
-        <v>0</v>
-      </c>
-      <c r="O97">
-        <v>0</v>
-      </c>
-      <c r="P97">
-        <v>0</v>
-      </c>
-      <c r="Q97">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>125292591</v>
-      </c>
-      <c r="E98">
-        <v>1211</v>
-      </c>
-      <c r="F98" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G98" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I98">
-        <v>42</v>
-      </c>
-      <c r="J98">
-        <v>8001</v>
-      </c>
-      <c r="L98">
-        <v>0</v>
-      </c>
-      <c r="M98">
-        <v>0</v>
-      </c>
-      <c r="N98">
-        <v>0</v>
-      </c>
-      <c r="O98">
-        <v>0</v>
-      </c>
-      <c r="P98">
-        <v>0</v>
-      </c>
-      <c r="Q98">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>125416679</v>
-      </c>
-      <c r="E99">
-        <v>1211</v>
-      </c>
-      <c r="F99" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G99" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I99">
-        <v>42</v>
-      </c>
-      <c r="J99">
-        <v>8001</v>
-      </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-      <c r="M99">
-        <v>0</v>
-      </c>
-      <c r="N99">
-        <v>0</v>
-      </c>
-      <c r="O99">
-        <v>0</v>
-      </c>
-      <c r="P99">
-        <v>0</v>
-      </c>
-      <c r="Q99">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>125479477</v>
-      </c>
-      <c r="E100">
-        <v>1211</v>
-      </c>
-      <c r="F100" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G100" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I100">
-        <v>42</v>
-      </c>
-      <c r="J100">
-        <v>8001</v>
-      </c>
-      <c r="L100">
-        <v>0</v>
-      </c>
-      <c r="M100">
-        <v>0</v>
-      </c>
-      <c r="N100">
-        <v>0</v>
-      </c>
-      <c r="O100">
-        <v>0</v>
-      </c>
-      <c r="P100">
-        <v>0</v>
-      </c>
-      <c r="Q100">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>125569788</v>
-      </c>
-      <c r="E101">
-        <v>1211</v>
-      </c>
-      <c r="F101" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G101" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I101">
-        <v>42</v>
-      </c>
-      <c r="J101">
-        <v>8001</v>
-      </c>
-      <c r="L101">
-        <v>0</v>
-      </c>
-      <c r="M101">
-        <v>0</v>
-      </c>
-      <c r="N101">
-        <v>0</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>0</v>
-      </c>
-      <c r="Q101">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>125751530</v>
-      </c>
-      <c r="E102">
-        <v>1211</v>
-      </c>
-      <c r="F102" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G102" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I102">
-        <v>42</v>
-      </c>
-      <c r="J102">
-        <v>8001</v>
-      </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-      <c r="M102">
-        <v>0</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
-        <v>0</v>
-      </c>
-      <c r="P102">
-        <v>0</v>
-      </c>
-      <c r="Q102">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>125851473</v>
-      </c>
-      <c r="E103">
-        <v>1211</v>
-      </c>
-      <c r="F103" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G103" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I103">
-        <v>42</v>
-      </c>
-      <c r="J103">
-        <v>8001</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="M103">
-        <v>0</v>
-      </c>
-      <c r="N103">
-        <v>0</v>
-      </c>
-      <c r="O103">
-        <v>0</v>
-      </c>
-      <c r="P103">
-        <v>0</v>
-      </c>
-      <c r="Q103">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>126073250</v>
-      </c>
-      <c r="E104">
-        <v>1211</v>
-      </c>
-      <c r="F104" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G104" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I104">
-        <v>42</v>
-      </c>
-      <c r="J104">
-        <v>8001</v>
-      </c>
-      <c r="L104">
-        <v>0</v>
-      </c>
-      <c r="M104">
-        <v>0</v>
-      </c>
-      <c r="N104">
-        <v>0</v>
-      </c>
-      <c r="O104">
-        <v>0</v>
-      </c>
-      <c r="P104">
-        <v>0</v>
-      </c>
-      <c r="Q104">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>126124625</v>
-      </c>
-      <c r="E105">
-        <v>1211</v>
-      </c>
-      <c r="F105" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G105" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I105">
-        <v>42</v>
-      </c>
-      <c r="J105">
-        <v>8001</v>
-      </c>
-      <c r="L105">
-        <v>0</v>
-      </c>
-      <c r="M105">
-        <v>0</v>
-      </c>
-      <c r="N105">
-        <v>0</v>
-      </c>
-      <c r="O105">
-        <v>0</v>
-      </c>
-      <c r="P105">
-        <v>0</v>
-      </c>
-      <c r="Q105">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>126134135</v>
-      </c>
-      <c r="E106">
-        <v>1211</v>
-      </c>
-      <c r="F106" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G106" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I106">
-        <v>42</v>
-      </c>
-      <c r="J106">
-        <v>8001</v>
-      </c>
-      <c r="L106">
-        <v>0</v>
-      </c>
-      <c r="M106">
-        <v>0</v>
-      </c>
-      <c r="N106">
-        <v>0</v>
-      </c>
-      <c r="O106">
-        <v>0</v>
-      </c>
-      <c r="P106">
-        <v>0</v>
-      </c>
-      <c r="Q106">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>126166733</v>
-      </c>
-      <c r="E107">
-        <v>1211</v>
-      </c>
-      <c r="F107" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G107" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I107">
-        <v>42</v>
-      </c>
-      <c r="J107">
-        <v>8001</v>
-      </c>
-      <c r="L107">
-        <v>0</v>
-      </c>
-      <c r="M107">
-        <v>0</v>
-      </c>
-      <c r="N107">
-        <v>0</v>
-      </c>
-      <c r="O107">
-        <v>0</v>
-      </c>
-      <c r="P107">
-        <v>0</v>
-      </c>
-      <c r="Q107">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>126272082</v>
-      </c>
-      <c r="E108">
-        <v>1212</v>
-      </c>
-      <c r="F108" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G108" s="2">
-        <v>45381</v>
-      </c>
-      <c r="I108">
-        <v>42</v>
-      </c>
-      <c r="J108">
-        <v>8001</v>
-      </c>
-      <c r="L108">
-        <v>0</v>
-      </c>
-      <c r="M108">
-        <v>0</v>
-      </c>
-      <c r="N108">
-        <v>0</v>
-      </c>
-      <c r="O108">
-        <v>0</v>
-      </c>
-      <c r="P108">
-        <v>0</v>
-      </c>
-      <c r="Q108">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>126875800</v>
-      </c>
-      <c r="E109">
-        <v>1212</v>
-      </c>
-      <c r="F109" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G109" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I109">
-        <v>42</v>
-      </c>
-      <c r="J109">
-        <v>8001</v>
-      </c>
-      <c r="L109">
-        <v>0</v>
-      </c>
-      <c r="M109">
-        <v>0</v>
-      </c>
-      <c r="N109">
-        <v>0</v>
-      </c>
-      <c r="O109">
-        <v>0</v>
-      </c>
-      <c r="P109">
-        <v>0</v>
-      </c>
-      <c r="Q109">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>126893769</v>
-      </c>
-      <c r="E110">
-        <v>1211</v>
-      </c>
-      <c r="F110" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G110" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I110">
-        <v>42</v>
-      </c>
-      <c r="J110">
-        <v>8001</v>
-      </c>
-      <c r="L110">
-        <v>0</v>
-      </c>
-      <c r="M110">
-        <v>0</v>
-      </c>
-      <c r="N110">
-        <v>0</v>
-      </c>
-      <c r="O110">
-        <v>0</v>
-      </c>
-      <c r="P110">
-        <v>0</v>
-      </c>
-      <c r="Q110">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>126972179</v>
-      </c>
-      <c r="E111">
-        <v>1211</v>
-      </c>
-      <c r="F111" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G111" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I111">
-        <v>42</v>
-      </c>
-      <c r="J111">
-        <v>8001</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="M111">
-        <v>0</v>
-      </c>
-      <c r="N111">
-        <v>0</v>
-      </c>
-      <c r="O111">
-        <v>0</v>
-      </c>
-      <c r="P111">
-        <v>0</v>
-      </c>
-      <c r="Q111">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <v>127113503</v>
-      </c>
-      <c r="E112">
-        <v>1211</v>
-      </c>
-      <c r="F112" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G112" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I112">
-        <v>42</v>
-      </c>
-      <c r="J112">
-        <v>8001</v>
-      </c>
-      <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="M112">
-        <v>0</v>
-      </c>
-      <c r="N112">
-        <v>0</v>
-      </c>
-      <c r="O112">
-        <v>0</v>
-      </c>
-      <c r="P112">
-        <v>0</v>
-      </c>
-      <c r="Q112">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>124411489</v>
-      </c>
-      <c r="E113">
-        <v>601</v>
-      </c>
-      <c r="F113" s="2">
-        <v>45384</v>
-      </c>
-      <c r="G113" s="2">
-        <v>45371</v>
-      </c>
-      <c r="I113">
-        <v>42</v>
-      </c>
-      <c r="J113">
-        <v>8017</v>
-      </c>
-      <c r="L113">
-        <v>0</v>
-      </c>
-      <c r="M113">
-        <v>0</v>
-      </c>
-      <c r="N113">
-        <v>0</v>
-      </c>
-      <c r="O113">
-        <v>0</v>
-      </c>
-      <c r="P113">
-        <v>0</v>
-      </c>
-      <c r="Q113">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <v>127149457</v>
-      </c>
-      <c r="E114">
-        <v>601</v>
-      </c>
-      <c r="F114" s="2">
-        <v>45376</v>
-      </c>
-      <c r="G114" s="2">
-        <v>45376</v>
-      </c>
-      <c r="I114">
-        <v>42</v>
-      </c>
-      <c r="J114">
-        <v>8013</v>
-      </c>
-      <c r="L114">
-        <v>0</v>
-      </c>
-      <c r="M114">
-        <v>0</v>
-      </c>
-      <c r="N114">
-        <v>0</v>
-      </c>
-      <c r="O114">
-        <v>0</v>
-      </c>
-      <c r="P114">
-        <v>0</v>
-      </c>
-      <c r="Q114">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <v>127149459</v>
-      </c>
-      <c r="E115">
-        <v>601</v>
-      </c>
-      <c r="F115" s="2">
-        <v>45376</v>
-      </c>
-      <c r="G115" s="2">
-        <v>45376</v>
-      </c>
-      <c r="I115">
-        <v>42</v>
-      </c>
-      <c r="J115">
-        <v>8013</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="M115">
-        <v>0</v>
-      </c>
-      <c r="N115">
-        <v>0</v>
-      </c>
-      <c r="O115">
-        <v>0</v>
-      </c>
-      <c r="P115">
-        <v>0</v>
-      </c>
-      <c r="Q115">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <v>127150185</v>
-      </c>
-      <c r="E116">
-        <v>601</v>
-      </c>
-      <c r="F116" s="2">
-        <v>45376</v>
-      </c>
-      <c r="G116" s="2">
-        <v>45376</v>
-      </c>
-      <c r="I116">
-        <v>42</v>
-      </c>
-      <c r="J116">
-        <v>8013</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="M116">
-        <v>0</v>
-      </c>
-      <c r="N116">
-        <v>0</v>
-      </c>
-      <c r="O116">
-        <v>0</v>
-      </c>
-      <c r="P116">
-        <v>0</v>
-      </c>
-      <c r="Q116">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <v>127150197</v>
-      </c>
-      <c r="E117">
-        <v>601</v>
-      </c>
-      <c r="F117" s="2">
-        <v>45376</v>
-      </c>
-      <c r="G117" s="2">
-        <v>45376</v>
-      </c>
-      <c r="I117">
-        <v>42</v>
-      </c>
-      <c r="J117">
-        <v>8013</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="M117">
-        <v>0</v>
-      </c>
-      <c r="N117">
-        <v>0</v>
-      </c>
-      <c r="O117">
-        <v>0</v>
-      </c>
-      <c r="P117">
-        <v>0</v>
-      </c>
-      <c r="Q117">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <v>127150284</v>
-      </c>
-      <c r="E118">
-        <v>601</v>
-      </c>
-      <c r="F118" s="2">
-        <v>45376</v>
-      </c>
-      <c r="G118" s="2">
-        <v>45376</v>
-      </c>
-      <c r="I118">
-        <v>42</v>
-      </c>
-      <c r="J118">
-        <v>8013</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118">
-        <v>0</v>
-      </c>
-      <c r="N118">
-        <v>0</v>
-      </c>
-      <c r="O118">
-        <v>0</v>
-      </c>
-      <c r="P118">
-        <v>0</v>
-      </c>
-      <c r="Q118">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <v>124072656</v>
-      </c>
-      <c r="E119">
-        <v>1211</v>
-      </c>
-      <c r="F119" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G119" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I119">
-        <v>42</v>
-      </c>
-      <c r="J119">
-        <v>715</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119">
-        <v>0</v>
-      </c>
-      <c r="N119">
-        <v>0</v>
-      </c>
-      <c r="O119">
-        <v>0</v>
-      </c>
-      <c r="P119">
-        <v>0</v>
-      </c>
-      <c r="Q119">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A120">
-        <v>125994157</v>
-      </c>
-      <c r="E120">
-        <v>1211</v>
-      </c>
-      <c r="F120" s="2">
-        <v>45384</v>
-      </c>
-      <c r="G120" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I120">
-        <v>42</v>
-      </c>
-      <c r="J120">
-        <v>715</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120">
-        <v>0</v>
-      </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120">
-        <v>0</v>
-      </c>
-      <c r="P120">
-        <v>0</v>
-      </c>
-      <c r="Q120">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <v>127128345</v>
-      </c>
-      <c r="E121">
-        <v>1211</v>
-      </c>
-      <c r="F121" s="2">
-        <v>45384</v>
-      </c>
-      <c r="G121" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I121">
-        <v>42</v>
-      </c>
-      <c r="J121">
-        <v>715</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="M121">
-        <v>0</v>
-      </c>
-      <c r="N121">
-        <v>0</v>
-      </c>
-      <c r="O121">
-        <v>0</v>
-      </c>
-      <c r="P121">
-        <v>0</v>
-      </c>
-      <c r="Q121">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A122">
-        <v>127209589</v>
-      </c>
-      <c r="E122">
-        <v>1211</v>
-      </c>
-      <c r="F122" s="2">
-        <v>45383</v>
-      </c>
-      <c r="G122" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I122">
-        <v>42</v>
-      </c>
-      <c r="J122">
-        <v>715</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122">
-        <v>0</v>
-      </c>
-      <c r="N122">
-        <v>0</v>
-      </c>
-      <c r="O122">
-        <v>0</v>
-      </c>
-      <c r="P122">
-        <v>0</v>
-      </c>
-      <c r="Q122">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A123">
-        <v>127210074</v>
-      </c>
-      <c r="E123">
-        <v>1212</v>
-      </c>
-      <c r="F123" s="2">
-        <v>45383</v>
-      </c>
-      <c r="G123" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I123">
-        <v>42</v>
-      </c>
-      <c r="J123">
-        <v>715</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123">
-        <v>0</v>
-      </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
-      <c r="O123">
-        <v>0</v>
-      </c>
-      <c r="P123">
-        <v>0</v>
-      </c>
-      <c r="Q123">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <v>127210662</v>
-      </c>
-      <c r="E124">
-        <v>1212</v>
-      </c>
-      <c r="F124" s="2">
-        <v>45383</v>
-      </c>
-      <c r="G124" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I124">
-        <v>42</v>
-      </c>
-      <c r="J124">
-        <v>715</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124">
-        <v>0</v>
-      </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
-      <c r="O124">
-        <v>0</v>
-      </c>
-      <c r="P124">
-        <v>0</v>
-      </c>
-      <c r="Q124">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <v>127211023</v>
-      </c>
-      <c r="E125">
-        <v>1211</v>
-      </c>
-      <c r="F125" s="2">
-        <v>45383</v>
-      </c>
-      <c r="G125" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I125">
-        <v>42</v>
-      </c>
-      <c r="J125">
-        <v>715</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125">
-        <v>0</v>
-      </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
-      <c r="O125">
-        <v>0</v>
-      </c>
-      <c r="P125">
-        <v>0</v>
-      </c>
-      <c r="Q125">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A126">
-        <v>127211142</v>
-      </c>
-      <c r="E126">
-        <v>1211</v>
-      </c>
-      <c r="F126" s="2">
-        <v>45383</v>
-      </c>
-      <c r="G126" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I126">
-        <v>42</v>
-      </c>
-      <c r="J126">
-        <v>715</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126">
-        <v>0</v>
-      </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
-      <c r="O126">
-        <v>0</v>
-      </c>
-      <c r="P126">
-        <v>0</v>
-      </c>
-      <c r="Q126">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <v>127213082</v>
-      </c>
-      <c r="E127">
-        <v>1212</v>
-      </c>
-      <c r="F127" s="2">
-        <v>45383</v>
-      </c>
-      <c r="G127" s="2">
-        <v>45383</v>
-      </c>
-      <c r="I127">
-        <v>42</v>
-      </c>
-      <c r="J127">
-        <v>715</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127">
-        <v>0</v>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A128">
-        <v>127221992</v>
-      </c>
-      <c r="E128">
-        <v>1211</v>
-      </c>
-      <c r="F128" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G128" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I128">
-        <v>42</v>
-      </c>
-      <c r="J128">
-        <v>715</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128">
-        <v>0</v>
-      </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
-      <c r="O128">
-        <v>0</v>
-      </c>
-      <c r="P128">
-        <v>0</v>
-      </c>
-      <c r="Q128">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <v>127223257</v>
-      </c>
-      <c r="E129">
-        <v>1211</v>
-      </c>
-      <c r="F129" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G129" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I129">
-        <v>42</v>
-      </c>
-      <c r="J129">
-        <v>715</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129">
-        <v>0</v>
-      </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>0</v>
-      </c>
-      <c r="P129">
-        <v>0</v>
-      </c>
-      <c r="Q129">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130">
-        <v>127223585</v>
-      </c>
-      <c r="E130">
-        <v>1212</v>
-      </c>
-      <c r="F130" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G130" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I130">
-        <v>42</v>
-      </c>
-      <c r="J130">
-        <v>715</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130">
-        <v>0</v>
-      </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
-        <v>0</v>
-      </c>
-      <c r="P130">
-        <v>0</v>
-      </c>
-      <c r="Q130">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A131">
-        <v>127224806</v>
-      </c>
-      <c r="E131">
-        <v>1211</v>
-      </c>
-      <c r="F131" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G131" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I131">
-        <v>42</v>
-      </c>
-      <c r="J131">
-        <v>715</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131">
-        <v>0</v>
-      </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>0</v>
-      </c>
-      <c r="P131">
-        <v>0</v>
-      </c>
-      <c r="Q131">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A132">
-        <v>127225461</v>
-      </c>
-      <c r="E132">
-        <v>1211</v>
-      </c>
-      <c r="F132" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G132" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I132">
-        <v>42</v>
-      </c>
-      <c r="J132">
-        <v>715</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132">
-        <v>0</v>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
-        <v>0</v>
-      </c>
-      <c r="Q132">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <v>127225592</v>
-      </c>
-      <c r="E133">
-        <v>1211</v>
-      </c>
-      <c r="F133" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G133" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I133">
-        <v>42</v>
-      </c>
-      <c r="J133">
-        <v>715</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133">
-        <v>0</v>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>0</v>
-      </c>
-      <c r="P133">
-        <v>0</v>
-      </c>
-      <c r="Q133">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A134">
-        <v>127225618</v>
-      </c>
-      <c r="E134">
-        <v>1211</v>
-      </c>
-      <c r="F134" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G134" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I134">
-        <v>42</v>
-      </c>
-      <c r="J134">
-        <v>715</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134">
-        <v>0</v>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
-        <v>0</v>
-      </c>
-      <c r="Q134">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A135">
-        <v>127228257</v>
-      </c>
-      <c r="E135">
-        <v>1212</v>
-      </c>
-      <c r="F135" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G135" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I135">
-        <v>42</v>
-      </c>
-      <c r="J135">
-        <v>715</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135">
-        <v>0</v>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
-        <v>0</v>
-      </c>
-      <c r="Q135">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <v>127228923</v>
-      </c>
-      <c r="E136">
-        <v>1211</v>
-      </c>
-      <c r="F136" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G136" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I136">
-        <v>42</v>
-      </c>
-      <c r="J136">
-        <v>715</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136">
-        <v>0</v>
-      </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
-        <v>0</v>
-      </c>
-      <c r="P136">
-        <v>0</v>
-      </c>
-      <c r="Q136">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <v>127231061</v>
-      </c>
-      <c r="E137">
-        <v>1211</v>
-      </c>
-      <c r="F137" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G137" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I137">
-        <v>42</v>
-      </c>
-      <c r="J137">
-        <v>715</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137">
-        <v>0</v>
-      </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A138">
-        <v>127231434</v>
-      </c>
-      <c r="E138">
-        <v>1212</v>
-      </c>
-      <c r="F138" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G138" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I138">
-        <v>42</v>
-      </c>
-      <c r="J138">
-        <v>715</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138">
-        <v>0</v>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A139">
-        <v>127232389</v>
-      </c>
-      <c r="E139">
-        <v>1212</v>
-      </c>
-      <c r="F139" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G139" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I139">
-        <v>42</v>
-      </c>
-      <c r="J139">
-        <v>715</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139">
-        <v>0</v>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A140">
-        <v>127232466</v>
-      </c>
-      <c r="E140">
-        <v>1211</v>
-      </c>
-      <c r="F140" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G140" s="2">
-        <v>45384</v>
-      </c>
-      <c r="I140">
-        <v>42</v>
-      </c>
-      <c r="J140">
-        <v>715</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140">
-        <v>0</v>
-      </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
-      <c r="O140">
-        <v>0</v>
-      </c>
-      <c r="P140">
-        <v>0</v>
-      </c>
-      <c r="Q140">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A141">
-        <v>127238237</v>
-      </c>
-      <c r="E141">
-        <v>1211</v>
-      </c>
-      <c r="F141" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G141" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I141">
-        <v>42</v>
-      </c>
-      <c r="J141">
-        <v>715</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141">
-        <v>0</v>
-      </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
-      <c r="O141">
-        <v>0</v>
-      </c>
-      <c r="P141">
-        <v>0</v>
-      </c>
-      <c r="Q141">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A142">
-        <v>127240902</v>
-      </c>
-      <c r="E142">
-        <v>1211</v>
-      </c>
-      <c r="F142" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G142" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I142">
-        <v>42</v>
-      </c>
-      <c r="J142">
-        <v>715</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="M142">
-        <v>0</v>
-      </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
-      <c r="O142">
-        <v>0</v>
-      </c>
-      <c r="P142">
-        <v>0</v>
-      </c>
-      <c r="Q142">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A143">
-        <v>127241003</v>
-      </c>
-      <c r="E143">
-        <v>1211</v>
-      </c>
-      <c r="F143" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G143" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I143">
-        <v>42</v>
-      </c>
-      <c r="J143">
-        <v>715</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="M143">
-        <v>0</v>
-      </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
-      <c r="O143">
-        <v>0</v>
-      </c>
-      <c r="P143">
-        <v>0</v>
-      </c>
-      <c r="Q143">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A144">
-        <v>127241421</v>
-      </c>
-      <c r="E144">
-        <v>1211</v>
-      </c>
-      <c r="F144" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G144" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I144">
-        <v>42</v>
-      </c>
-      <c r="J144">
-        <v>715</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="M144">
-        <v>0</v>
-      </c>
-      <c r="N144">
-        <v>0</v>
-      </c>
-      <c r="O144">
-        <v>0</v>
-      </c>
-      <c r="P144">
-        <v>0</v>
-      </c>
-      <c r="Q144">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A145">
-        <v>127241838</v>
-      </c>
-      <c r="E145">
-        <v>1211</v>
-      </c>
-      <c r="F145" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G145" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I145">
-        <v>42</v>
-      </c>
-      <c r="J145">
-        <v>715</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="M145">
-        <v>0</v>
-      </c>
-      <c r="N145">
-        <v>0</v>
-      </c>
-      <c r="O145">
-        <v>0</v>
-      </c>
-      <c r="P145">
-        <v>0</v>
-      </c>
-      <c r="Q145">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A146">
-        <v>127243348</v>
-      </c>
-      <c r="E146">
-        <v>1211</v>
-      </c>
-      <c r="F146" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G146" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I146">
-        <v>42</v>
-      </c>
-      <c r="J146">
-        <v>715</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146">
-        <v>0</v>
-      </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
-      <c r="O146">
-        <v>0</v>
-      </c>
-      <c r="P146">
-        <v>0</v>
-      </c>
-      <c r="Q146">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A147">
-        <v>127243440</v>
-      </c>
-      <c r="E147">
-        <v>1211</v>
-      </c>
-      <c r="F147" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G147" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I147">
-        <v>42</v>
-      </c>
-      <c r="J147">
-        <v>715</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147">
-        <v>0</v>
-      </c>
-      <c r="N147">
-        <v>0</v>
-      </c>
-      <c r="O147">
-        <v>0</v>
-      </c>
-      <c r="P147">
-        <v>0</v>
-      </c>
-      <c r="Q147">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A148">
-        <v>127244338</v>
-      </c>
-      <c r="E148">
-        <v>1212</v>
-      </c>
-      <c r="F148" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G148" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I148">
-        <v>42</v>
-      </c>
-      <c r="J148">
-        <v>715</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148">
-        <v>0</v>
-      </c>
-      <c r="N148">
-        <v>0</v>
-      </c>
-      <c r="O148">
-        <v>0</v>
-      </c>
-      <c r="P148">
-        <v>0</v>
-      </c>
-      <c r="Q148">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A149">
-        <v>127245008</v>
-      </c>
-      <c r="E149">
-        <v>1212</v>
-      </c>
-      <c r="F149" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G149" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I149">
-        <v>42</v>
-      </c>
-      <c r="J149">
-        <v>715</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="M149">
-        <v>0</v>
-      </c>
-      <c r="N149">
-        <v>0</v>
-      </c>
-      <c r="O149">
-        <v>0</v>
-      </c>
-      <c r="P149">
-        <v>0</v>
-      </c>
-      <c r="Q149">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A150">
-        <v>127245138</v>
-      </c>
-      <c r="E150">
-        <v>1211</v>
-      </c>
-      <c r="F150" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G150" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I150">
-        <v>42</v>
-      </c>
-      <c r="J150">
-        <v>715</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="M150">
-        <v>0</v>
-      </c>
-      <c r="N150">
-        <v>0</v>
-      </c>
-      <c r="O150">
-        <v>0</v>
-      </c>
-      <c r="P150">
-        <v>0</v>
-      </c>
-      <c r="Q150">
-        <v>61</v>
-      </c>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+    </row>
+    <row r="81" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+    </row>
+    <row r="82" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+    </row>
+    <row r="83" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+    </row>
+    <row r="84" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+    </row>
+    <row r="85" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F85" s="2"/>
+      <c r="G85" s="2"/>
+    </row>
+    <row r="86" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F86" s="2"/>
+      <c r="G86" s="2"/>
+    </row>
+    <row r="87" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+    </row>
+    <row r="88" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
+    </row>
+    <row r="89" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+    </row>
+    <row r="90" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F90" s="2"/>
+      <c r="G90" s="2"/>
+    </row>
+    <row r="91" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+    </row>
+    <row r="92" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
+    </row>
+    <row r="93" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+    </row>
+    <row r="94" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F94" s="2"/>
+      <c r="G94" s="2"/>
+    </row>
+    <row r="95" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F95" s="2"/>
+      <c r="G95" s="2"/>
+    </row>
+    <row r="96" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+    </row>
+    <row r="97" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+    </row>
+    <row r="98" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+    </row>
+    <row r="99" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F99" s="2"/>
+      <c r="G99" s="2"/>
+    </row>
+    <row r="100" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F100" s="2"/>
+      <c r="G100" s="2"/>
+    </row>
+    <row r="101" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+    </row>
+    <row r="102" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+    </row>
+    <row r="103" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
+    </row>
+    <row r="104" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F104" s="2"/>
+      <c r="G104" s="2"/>
+    </row>
+    <row r="105" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+    </row>
+    <row r="106" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F106" s="2"/>
+      <c r="G106" s="2"/>
+    </row>
+    <row r="107" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F107" s="2"/>
+      <c r="G107" s="2"/>
+    </row>
+    <row r="108" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
+    </row>
+    <row r="109" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F109" s="2"/>
+      <c r="G109" s="2"/>
+    </row>
+    <row r="110" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
+    </row>
+    <row r="111" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
+    </row>
+    <row r="112" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
+    </row>
+    <row r="113" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F113" s="2"/>
+      <c r="G113" s="2"/>
+    </row>
+    <row r="114" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F114" s="2"/>
+      <c r="G114" s="2"/>
+    </row>
+    <row r="115" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F115" s="2"/>
+      <c r="G115" s="2"/>
+    </row>
+    <row r="116" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F116" s="2"/>
+      <c r="G116" s="2"/>
+    </row>
+    <row r="117" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F117" s="2"/>
+      <c r="G117" s="2"/>
+    </row>
+    <row r="118" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
+    </row>
+    <row r="119" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F119" s="2"/>
+      <c r="G119" s="2"/>
+    </row>
+    <row r="120" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F120" s="2"/>
+      <c r="G120" s="2"/>
+    </row>
+    <row r="121" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F121" s="2"/>
+      <c r="G121" s="2"/>
+    </row>
+    <row r="122" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F122" s="2"/>
+      <c r="G122" s="2"/>
+    </row>
+    <row r="123" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F123" s="2"/>
+      <c r="G123" s="2"/>
+    </row>
+    <row r="124" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
+    </row>
+    <row r="125" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F125" s="2"/>
+      <c r="G125" s="2"/>
+    </row>
+    <row r="126" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F126" s="2"/>
+      <c r="G126" s="2"/>
+    </row>
+    <row r="127" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F127" s="2"/>
+      <c r="G127" s="2"/>
+    </row>
+    <row r="128" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F128" s="2"/>
+      <c r="G128" s="2"/>
+    </row>
+    <row r="129" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F129" s="2"/>
+      <c r="G129" s="2"/>
+    </row>
+    <row r="130" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F130" s="2"/>
+      <c r="G130" s="2"/>
+    </row>
+    <row r="131" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F131" s="2"/>
+      <c r="G131" s="2"/>
+    </row>
+    <row r="132" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F132" s="2"/>
+      <c r="G132" s="2"/>
+    </row>
+    <row r="133" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+    </row>
+    <row r="134" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F134" s="2"/>
+      <c r="G134" s="2"/>
+    </row>
+    <row r="135" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F135" s="2"/>
+      <c r="G135" s="2"/>
+    </row>
+    <row r="136" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+    </row>
+    <row r="137" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F137" s="2"/>
+      <c r="G137" s="2"/>
+    </row>
+    <row r="138" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F138" s="2"/>
+      <c r="G138" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -13835,31 +11305,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68C7DC7-75D2-4179-912E-C0AEF3C320B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E79A66E8-8A70-407E-B233-F88302CEA379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiel" sheetId="28" r:id="rId1"/>
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,18 +507,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q138"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q63"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
@@ -526,11 +526,11 @@
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,12 +583,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>124891623</v>
+        <v>127270485</v>
       </c>
       <c r="E2">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F2" s="2">
         <v>45387</v>
@@ -600,7 +600,7 @@
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -621,15 +621,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>125266621</v>
+        <v>127274048</v>
       </c>
       <c r="E3">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F3" s="2">
-        <v>45387</v>
+        <v>45388</v>
       </c>
       <c r="G3" s="2">
         <v>45387</v>
@@ -638,7 +638,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -659,24 +659,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>127222638</v>
+        <v>123696396</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45384</v>
+        <v>45390</v>
       </c>
       <c r="G4" s="2">
-        <v>45384</v>
+        <v>45390</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -697,24 +697,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>127225835</v>
+        <v>124218579</v>
       </c>
       <c r="E5">
         <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45385</v>
+        <v>45390</v>
       </c>
       <c r="G5" s="2">
-        <v>45384</v>
+        <v>45390</v>
       </c>
       <c r="I5">
         <v>42</v>
       </c>
       <c r="J5">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -735,24 +735,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>127232212</v>
+        <v>124306192</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45384</v>
+        <v>45390</v>
       </c>
       <c r="G6" s="2">
-        <v>45384</v>
+        <v>45390</v>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -773,24 +773,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>127234893</v>
+        <v>124610422</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45385</v>
+        <v>45390</v>
       </c>
       <c r="G7" s="2">
-        <v>45385</v>
+        <v>45388</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -811,24 +811,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>127241760</v>
+        <v>124767220</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45385</v>
+        <v>45390</v>
       </c>
       <c r="G8" s="2">
-        <v>45385</v>
+        <v>45390</v>
       </c>
       <c r="I8">
         <v>42</v>
       </c>
       <c r="J8">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -849,24 +849,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>127242453</v>
+        <v>124797558</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45386</v>
+        <v>45390</v>
       </c>
       <c r="G9" s="2">
-        <v>45385</v>
+        <v>45390</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -887,24 +887,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>127249950</v>
+        <v>124965405</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G10" s="2">
-        <v>45386</v>
+        <v>45390</v>
       </c>
       <c r="I10">
         <v>42</v>
       </c>
       <c r="J10">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -925,24 +925,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>127251464</v>
+        <v>125037343</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G11" s="2">
-        <v>45386</v>
+        <v>45390</v>
       </c>
       <c r="I11">
         <v>42</v>
       </c>
       <c r="J11">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -963,24 +963,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>127256936</v>
+        <v>125362092</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45386</v>
+        <v>45390</v>
       </c>
       <c r="G12" s="2">
-        <v>45386</v>
+        <v>45390</v>
       </c>
       <c r="I12">
         <v>42</v>
       </c>
       <c r="J12">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1001,18 +1001,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>123687952</v>
+        <v>125363711</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G13" s="2">
-        <v>45386</v>
+        <v>45390</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1039,18 +1039,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>123743818</v>
+        <v>125475500</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G14" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1077,18 +1077,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>123805768</v>
+        <v>125707952</v>
       </c>
       <c r="E15">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F15" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G15" s="2">
-        <v>45387</v>
+        <v>45389</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1115,18 +1115,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>123821195</v>
+        <v>125710842</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G16" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1153,18 +1153,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>123824005</v>
+        <v>125737927</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G17" s="2">
-        <v>45386</v>
+        <v>45390</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1191,18 +1191,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>123879266</v>
+        <v>125910077</v>
       </c>
       <c r="E18">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G18" s="2">
-        <v>45387</v>
+        <v>45385</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1229,18 +1229,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>123915789</v>
+        <v>126171882</v>
       </c>
       <c r="E19">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G19" s="2">
-        <v>45386</v>
+        <v>45388</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1267,18 +1267,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>123962647</v>
+        <v>126282894</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G20" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1305,15 +1305,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>123977848</v>
+        <v>126468942</v>
       </c>
       <c r="E21">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G21" s="2">
         <v>45387</v>
@@ -1343,15 +1343,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>124173447</v>
+        <v>126969498</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G22" s="2">
         <v>45387</v>
@@ -1381,18 +1381,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>124207490</v>
+        <v>126979904</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G23" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1419,18 +1419,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>124216496</v>
+        <v>127076246</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G24" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1457,15 +1457,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>124217292</v>
+        <v>127218377</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G25" s="2">
         <v>45387</v>
@@ -1495,18 +1495,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>124254494</v>
+        <v>127220056</v>
       </c>
       <c r="E26">
         <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G26" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="I26">
         <v>42</v>
@@ -1533,24 +1533,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>124351584</v>
+        <v>110074933</v>
       </c>
       <c r="E27">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45388</v>
+        <v>43453</v>
       </c>
       <c r="G27" s="2">
-        <v>45388</v>
+        <v>43441</v>
       </c>
       <c r="I27">
         <v>42</v>
       </c>
       <c r="J27">
-        <v>8001</v>
+        <v>8023</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1571,18 +1571,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>124494755</v>
+        <v>123058958</v>
       </c>
       <c r="E28">
         <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45387</v>
+        <v>44995</v>
       </c>
       <c r="G28" s="2">
-        <v>45387</v>
+        <v>44993</v>
       </c>
       <c r="I28">
         <v>42</v>
@@ -1609,24 +1609,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>124754756</v>
+        <v>124411489</v>
       </c>
       <c r="E29">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F29" s="2">
-        <v>45388</v>
+        <v>45384</v>
       </c>
       <c r="G29" s="2">
-        <v>45388</v>
+        <v>45371</v>
       </c>
       <c r="I29">
         <v>42</v>
       </c>
       <c r="J29">
-        <v>8001</v>
+        <v>8017</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -1647,24 +1647,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>124901324</v>
+        <v>126954503</v>
       </c>
       <c r="E30">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F30" s="2">
-        <v>45387</v>
+        <v>45378</v>
       </c>
       <c r="G30" s="2">
-        <v>45387</v>
+        <v>45378</v>
       </c>
       <c r="I30">
         <v>42</v>
       </c>
       <c r="J30">
-        <v>8001</v>
+        <v>8017</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1685,24 +1685,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>124922681</v>
+        <v>127177656</v>
       </c>
       <c r="E31">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F31" s="2">
-        <v>45387</v>
+        <v>45378</v>
       </c>
       <c r="G31" s="2">
-        <v>45387</v>
+        <v>45378</v>
       </c>
       <c r="I31">
         <v>42</v>
       </c>
       <c r="J31">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -1723,24 +1723,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>125024343</v>
+        <v>127199965</v>
       </c>
       <c r="E32">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F32" s="2">
-        <v>45387</v>
+        <v>45379</v>
       </c>
       <c r="G32" s="2">
-        <v>45387</v>
+        <v>45379</v>
       </c>
       <c r="I32">
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -1761,24 +1761,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>125578026</v>
+        <v>109403368</v>
       </c>
       <c r="E33">
         <v>1211</v>
       </c>
       <c r="F33" s="2">
-        <v>45387</v>
+        <v>43346</v>
       </c>
       <c r="G33" s="2">
-        <v>45387</v>
+        <v>43346</v>
       </c>
       <c r="I33">
         <v>42</v>
       </c>
       <c r="J33">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -1799,24 +1799,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>125586006</v>
+        <v>109455583</v>
       </c>
       <c r="E34">
         <v>1211</v>
       </c>
       <c r="F34" s="2">
-        <v>45387</v>
+        <v>43354</v>
       </c>
       <c r="G34" s="2">
-        <v>45387</v>
+        <v>43354</v>
       </c>
       <c r="I34">
         <v>42</v>
       </c>
       <c r="J34">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -1837,24 +1837,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>125623293</v>
+        <v>109707680</v>
       </c>
       <c r="E35">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F35" s="2">
-        <v>45387</v>
+        <v>43396</v>
       </c>
       <c r="G35" s="2">
-        <v>45386</v>
+        <v>43396</v>
       </c>
       <c r="I35">
         <v>42</v>
       </c>
       <c r="J35">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -1875,24 +1875,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>125711157</v>
+        <v>113706291</v>
       </c>
       <c r="E36">
         <v>1211</v>
       </c>
       <c r="F36" s="2">
-        <v>45387</v>
+        <v>43945</v>
       </c>
       <c r="G36" s="2">
-        <v>45387</v>
+        <v>43945</v>
       </c>
       <c r="I36">
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -1913,24 +1913,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>125790389</v>
+        <v>114296869</v>
       </c>
       <c r="E37">
         <v>1211</v>
       </c>
       <c r="F37" s="2">
-        <v>45387</v>
+        <v>44057</v>
       </c>
       <c r="G37" s="2">
-        <v>45387</v>
+        <v>44057</v>
       </c>
       <c r="I37">
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -1951,24 +1951,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>125837967</v>
+        <v>114763565</v>
       </c>
       <c r="E38">
         <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>45387</v>
+        <v>44156</v>
       </c>
       <c r="G38" s="2">
-        <v>45387</v>
+        <v>44153</v>
       </c>
       <c r="I38">
         <v>42</v>
       </c>
       <c r="J38">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -1989,24 +1989,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>125839602</v>
+        <v>114852173</v>
       </c>
       <c r="E39">
         <v>1211</v>
       </c>
       <c r="F39" s="2">
-        <v>45387</v>
+        <v>44171</v>
       </c>
       <c r="G39" s="2">
-        <v>45387</v>
+        <v>44168</v>
       </c>
       <c r="I39">
         <v>42</v>
       </c>
       <c r="J39">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2027,24 +2027,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>125935281</v>
+        <v>127282255</v>
       </c>
       <c r="E40">
         <v>1211</v>
       </c>
       <c r="F40" s="2">
-        <v>45388</v>
+        <v>45390</v>
       </c>
       <c r="G40" s="2">
-        <v>45388</v>
+        <v>45390</v>
       </c>
       <c r="I40">
         <v>42</v>
       </c>
       <c r="J40">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2065,24 +2065,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>125990369</v>
+        <v>127282891</v>
       </c>
       <c r="E41">
         <v>1211</v>
       </c>
       <c r="F41" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G41" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2103,24 +2103,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>126131697</v>
+        <v>127285341</v>
       </c>
       <c r="E42">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F42" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G42" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2141,24 +2141,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>126250706</v>
+        <v>127287181</v>
       </c>
       <c r="E43">
         <v>1211</v>
       </c>
       <c r="F43" s="2">
-        <v>45388</v>
+        <v>45390</v>
       </c>
       <c r="G43" s="2">
-        <v>45385</v>
+        <v>45390</v>
       </c>
       <c r="I43">
         <v>42</v>
       </c>
       <c r="J43">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2179,24 +2179,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>126303888</v>
+        <v>127287221</v>
       </c>
       <c r="E44">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F44" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G44" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2217,24 +2217,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>126366579</v>
+        <v>127287557</v>
       </c>
       <c r="E45">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F45" s="2">
-        <v>45388</v>
+        <v>45390</v>
       </c>
       <c r="G45" s="2">
-        <v>45388</v>
+        <v>45390</v>
       </c>
       <c r="I45">
         <v>42</v>
       </c>
       <c r="J45">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2255,24 +2255,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>126637858</v>
+        <v>127288397</v>
       </c>
       <c r="E46">
         <v>1211</v>
       </c>
       <c r="F46" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G46" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="I46">
         <v>42</v>
       </c>
       <c r="J46">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2293,24 +2293,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>126726655</v>
+        <v>127288727</v>
       </c>
       <c r="E47">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F47" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="G47" s="2">
-        <v>45387</v>
+        <v>45390</v>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2331,1389 +2331,69 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>126766723</v>
-      </c>
-      <c r="E48">
-        <v>1211</v>
-      </c>
-      <c r="F48" s="2">
-        <v>45388</v>
-      </c>
-      <c r="G48" s="2">
-        <v>45388</v>
-      </c>
-      <c r="I48">
-        <v>42</v>
-      </c>
-      <c r="J48">
-        <v>8001</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>126988819</v>
-      </c>
-      <c r="E49">
-        <v>1211</v>
-      </c>
-      <c r="F49" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G49" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I49">
-        <v>42</v>
-      </c>
-      <c r="J49">
-        <v>8001</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>126991885</v>
-      </c>
-      <c r="E50">
-        <v>1211</v>
-      </c>
-      <c r="F50" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G50" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I50">
-        <v>42</v>
-      </c>
-      <c r="J50">
-        <v>8001</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>127056754</v>
-      </c>
-      <c r="E51">
-        <v>1211</v>
-      </c>
-      <c r="F51" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G51" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I51">
-        <v>42</v>
-      </c>
-      <c r="J51">
-        <v>8001</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>0</v>
-      </c>
-      <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>127185427</v>
-      </c>
-      <c r="E52">
-        <v>1211</v>
-      </c>
-      <c r="F52" s="2">
-        <v>45388</v>
-      </c>
-      <c r="G52" s="2">
-        <v>45388</v>
-      </c>
-      <c r="I52">
-        <v>42</v>
-      </c>
-      <c r="J52">
-        <v>8001</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
-        <v>0</v>
-      </c>
-      <c r="P52">
-        <v>0</v>
-      </c>
-      <c r="Q52">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>127263077</v>
-      </c>
-      <c r="E53">
-        <v>1211</v>
-      </c>
-      <c r="F53" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G53" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I53">
-        <v>42</v>
-      </c>
-      <c r="J53">
-        <v>715</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53">
-        <v>0</v>
-      </c>
-      <c r="P53">
-        <v>0</v>
-      </c>
-      <c r="Q53">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>127263567</v>
-      </c>
-      <c r="E54">
-        <v>1212</v>
-      </c>
-      <c r="F54" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G54" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I54">
-        <v>42</v>
-      </c>
-      <c r="J54">
-        <v>715</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
-      <c r="O54">
-        <v>0</v>
-      </c>
-      <c r="P54">
-        <v>0</v>
-      </c>
-      <c r="Q54">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>127264250</v>
-      </c>
-      <c r="E55">
-        <v>1211</v>
-      </c>
-      <c r="F55" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G55" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I55">
-        <v>42</v>
-      </c>
-      <c r="J55">
-        <v>715</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55">
-        <v>0</v>
-      </c>
-      <c r="P55">
-        <v>0</v>
-      </c>
-      <c r="Q55">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>127265481</v>
-      </c>
-      <c r="E56">
-        <v>1211</v>
-      </c>
-      <c r="F56" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G56" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I56">
-        <v>42</v>
-      </c>
-      <c r="J56">
-        <v>715</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56">
-        <v>0</v>
-      </c>
-      <c r="P56">
-        <v>0</v>
-      </c>
-      <c r="Q56">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>127265635</v>
-      </c>
-      <c r="E57">
-        <v>1211</v>
-      </c>
-      <c r="F57" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G57" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I57">
-        <v>42</v>
-      </c>
-      <c r="J57">
-        <v>715</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57">
-        <v>0</v>
-      </c>
-      <c r="P57">
-        <v>0</v>
-      </c>
-      <c r="Q57">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>127265688</v>
-      </c>
-      <c r="E58">
-        <v>1211</v>
-      </c>
-      <c r="F58" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G58" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I58">
-        <v>42</v>
-      </c>
-      <c r="J58">
-        <v>715</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58">
-        <v>0</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58">
-        <v>0</v>
-      </c>
-      <c r="P58">
-        <v>0</v>
-      </c>
-      <c r="Q58">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>127265964</v>
-      </c>
-      <c r="E59">
-        <v>1211</v>
-      </c>
-      <c r="F59" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G59" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I59">
-        <v>42</v>
-      </c>
-      <c r="J59">
-        <v>715</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
-      <c r="M59">
-        <v>0</v>
-      </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="O59">
-        <v>0</v>
-      </c>
-      <c r="P59">
-        <v>0</v>
-      </c>
-      <c r="Q59">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>127266215</v>
-      </c>
-      <c r="E60">
-        <v>1211</v>
-      </c>
-      <c r="F60" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G60" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I60">
-        <v>42</v>
-      </c>
-      <c r="J60">
-        <v>715</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
-        <v>0</v>
-      </c>
-      <c r="P60">
-        <v>0</v>
-      </c>
-      <c r="Q60">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>127267388</v>
-      </c>
-      <c r="E61">
-        <v>1211</v>
-      </c>
-      <c r="F61" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G61" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I61">
-        <v>42</v>
-      </c>
-      <c r="J61">
-        <v>715</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>0</v>
-      </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>127267923</v>
-      </c>
-      <c r="E62">
-        <v>1211</v>
-      </c>
-      <c r="F62" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G62" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I62">
-        <v>42</v>
-      </c>
-      <c r="J62">
-        <v>715</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>127267960</v>
-      </c>
-      <c r="E63">
-        <v>1211</v>
-      </c>
-      <c r="F63" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G63" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I63">
-        <v>42</v>
-      </c>
-      <c r="J63">
-        <v>715</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>127268795</v>
-      </c>
-      <c r="E64">
-        <v>1212</v>
-      </c>
-      <c r="F64" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G64" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I64">
-        <v>42</v>
-      </c>
-      <c r="J64">
-        <v>715</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>127269159</v>
-      </c>
-      <c r="E65">
-        <v>1211</v>
-      </c>
-      <c r="F65" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G65" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I65">
-        <v>42</v>
-      </c>
-      <c r="J65">
-        <v>715</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>127270356</v>
-      </c>
-      <c r="E66">
-        <v>1212</v>
-      </c>
-      <c r="F66" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G66" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I66">
-        <v>42</v>
-      </c>
-      <c r="J66">
-        <v>715</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>0</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>127270672</v>
-      </c>
-      <c r="E67">
-        <v>1212</v>
-      </c>
-      <c r="F67" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G67" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I67">
-        <v>42</v>
-      </c>
-      <c r="J67">
-        <v>715</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>127271979</v>
-      </c>
-      <c r="E68">
-        <v>1211</v>
-      </c>
-      <c r="F68" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G68" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I68">
-        <v>42</v>
-      </c>
-      <c r="J68">
-        <v>715</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>127272700</v>
-      </c>
-      <c r="E69">
-        <v>1211</v>
-      </c>
-      <c r="F69" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G69" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I69">
-        <v>42</v>
-      </c>
-      <c r="J69">
-        <v>715</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>127272953</v>
-      </c>
-      <c r="E70">
-        <v>1212</v>
-      </c>
-      <c r="F70" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G70" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I70">
-        <v>42</v>
-      </c>
-      <c r="J70">
-        <v>715</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>0</v>
-      </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>127273080</v>
-      </c>
-      <c r="E71">
-        <v>1211</v>
-      </c>
-      <c r="F71" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G71" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I71">
-        <v>42</v>
-      </c>
-      <c r="J71">
-        <v>715</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>127273976</v>
-      </c>
-      <c r="E72">
-        <v>1212</v>
-      </c>
-      <c r="F72" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G72" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I72">
-        <v>42</v>
-      </c>
-      <c r="J72">
-        <v>715</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <v>0</v>
-      </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <v>0</v>
-      </c>
-      <c r="P72">
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>127274504</v>
-      </c>
-      <c r="E73">
-        <v>1211</v>
-      </c>
-      <c r="F73" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G73" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I73">
-        <v>42</v>
-      </c>
-      <c r="J73">
-        <v>715</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <v>0</v>
-      </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73">
-        <v>0</v>
-      </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>127274537</v>
-      </c>
-      <c r="E74">
-        <v>1211</v>
-      </c>
-      <c r="F74" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G74" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I74">
-        <v>42</v>
-      </c>
-      <c r="J74">
-        <v>715</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <v>0</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <v>0</v>
-      </c>
-      <c r="P74">
-        <v>0</v>
-      </c>
-      <c r="Q74">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>127274749</v>
-      </c>
-      <c r="E75">
-        <v>1211</v>
-      </c>
-      <c r="F75" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G75" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I75">
-        <v>42</v>
-      </c>
-      <c r="J75">
-        <v>715</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
-      </c>
-      <c r="P75">
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>127275706</v>
-      </c>
-      <c r="E76">
-        <v>1212</v>
-      </c>
-      <c r="F76" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G76" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I76">
-        <v>42</v>
-      </c>
-      <c r="J76">
-        <v>715</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76">
-        <v>0</v>
-      </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
-      <c r="O76">
-        <v>0</v>
-      </c>
-      <c r="P76">
-        <v>0</v>
-      </c>
-      <c r="Q76">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>127275804</v>
-      </c>
-      <c r="E77">
-        <v>1212</v>
-      </c>
-      <c r="F77" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G77" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I77">
-        <v>42</v>
-      </c>
-      <c r="J77">
-        <v>715</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <v>0</v>
-      </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
-      <c r="O77">
-        <v>0</v>
-      </c>
-      <c r="P77">
-        <v>0</v>
-      </c>
-      <c r="Q77">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F80" s="2"/>
-      <c r="G80" s="2"/>
-    </row>
-    <row r="81" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-    </row>
-    <row r="82" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-    </row>
-    <row r="83" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-    </row>
-    <row r="84" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-    </row>
-    <row r="85" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
-    </row>
-    <row r="86" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F86" s="2"/>
-      <c r="G86" s="2"/>
-    </row>
-    <row r="87" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-    </row>
-    <row r="88" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F88" s="2"/>
-      <c r="G88" s="2"/>
-    </row>
-    <row r="89" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-    </row>
-    <row r="90" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-    </row>
-    <row r="91" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-    </row>
-    <row r="92" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-    </row>
-    <row r="93" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-    </row>
-    <row r="94" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-    </row>
-    <row r="95" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-    </row>
-    <row r="96" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-    </row>
-    <row r="97" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-    </row>
-    <row r="98" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-    </row>
-    <row r="99" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-    </row>
-    <row r="100" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-    </row>
-    <row r="101" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-    </row>
-    <row r="102" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-    </row>
-    <row r="103" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-    </row>
-    <row r="104" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-    </row>
-    <row r="105" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-    </row>
-    <row r="106" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-    </row>
-    <row r="107" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-    </row>
-    <row r="108" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-    </row>
-    <row r="109" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-    </row>
-    <row r="110" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-    </row>
-    <row r="111" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-    </row>
-    <row r="112" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-    </row>
-    <row r="113" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-    </row>
-    <row r="114" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-    </row>
-    <row r="115" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-    </row>
-    <row r="116" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-    </row>
-    <row r="117" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-    </row>
-    <row r="118" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-    </row>
-    <row r="119" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-    </row>
-    <row r="120" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-    </row>
-    <row r="121" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-    </row>
-    <row r="122" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-    </row>
-    <row r="123" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-    </row>
-    <row r="124" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-    </row>
-    <row r="125" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-    </row>
-    <row r="126" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F126" s="2"/>
-      <c r="G126" s="2"/>
-    </row>
-    <row r="127" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F127" s="2"/>
-      <c r="G127" s="2"/>
-    </row>
-    <row r="128" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-    </row>
-    <row r="129" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-    </row>
-    <row r="130" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F130" s="2"/>
-      <c r="G130" s="2"/>
-    </row>
-    <row r="131" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-    </row>
-    <row r="132" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-    </row>
-    <row r="133" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-    </row>
-    <row r="134" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-    </row>
-    <row r="135" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-    </row>
-    <row r="136" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F136" s="2"/>
-      <c r="G136" s="2"/>
-    </row>
-    <row r="137" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-    </row>
-    <row r="138" spans="6:7" x14ac:dyDescent="0.25">
-      <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+    </row>
+    <row r="49" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+    </row>
+    <row r="54" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+    </row>
+    <row r="55" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+    </row>
+    <row r="56" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+    </row>
+    <row r="57" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+    </row>
+    <row r="59" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+    </row>
+    <row r="60" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+    </row>
+    <row r="63" spans="6:7" x14ac:dyDescent="0.35">
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -3730,12 +2410,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{249CD703-0AE7-46A1-BA6D-A19361B97C73}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:Q198"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -3788,7 +2468,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>125887260</v>
       </c>
@@ -3826,7 +2506,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>125890823</v>
       </c>
@@ -3864,7 +2544,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>125891086</v>
       </c>
@@ -3902,7 +2582,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>125892224</v>
       </c>
@@ -3940,7 +2620,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>125892709</v>
       </c>
@@ -3978,7 +2658,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>125892901</v>
       </c>
@@ -4016,7 +2696,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>125892906</v>
       </c>
@@ -4054,7 +2734,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>125893564</v>
       </c>
@@ -4092,7 +2772,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>125893722</v>
       </c>
@@ -4130,7 +2810,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>125895193</v>
       </c>
@@ -4168,7 +2848,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>125896177</v>
       </c>
@@ -4206,7 +2886,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>125898007</v>
       </c>
@@ -4244,7 +2924,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>125900254</v>
       </c>
@@ -4282,7 +2962,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>125901787</v>
       </c>
@@ -4320,7 +3000,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>125901795</v>
       </c>
@@ -4358,7 +3038,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>125903262</v>
       </c>
@@ -4396,7 +3076,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>125904221</v>
       </c>
@@ -4434,7 +3114,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>125904238</v>
       </c>
@@ -4472,7 +3152,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>125907420</v>
       </c>
@@ -4510,7 +3190,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>125907797</v>
       </c>
@@ -4548,7 +3228,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>125908056</v>
       </c>
@@ -4586,7 +3266,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>125908177</v>
       </c>
@@ -4624,7 +3304,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>125908231</v>
       </c>
@@ -4662,7 +3342,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>125908843</v>
       </c>
@@ -4700,7 +3380,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>125909142</v>
       </c>
@@ -4738,7 +3418,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>125909933</v>
       </c>
@@ -4776,7 +3456,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>125910114</v>
       </c>
@@ -4814,7 +3494,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>125910400</v>
       </c>
@@ -4852,7 +3532,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>125910838</v>
       </c>
@@ -4890,7 +3570,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>125912176</v>
       </c>
@@ -4928,7 +3608,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>125912843</v>
       </c>
@@ -4966,7 +3646,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>125913133</v>
       </c>
@@ -5004,7 +3684,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>125913427</v>
       </c>
@@ -5042,7 +3722,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>125914356</v>
       </c>
@@ -5080,7 +3760,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>125914668</v>
       </c>
@@ -5118,7 +3798,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>125914978</v>
       </c>
@@ -5156,7 +3836,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>125918666</v>
       </c>
@@ -5194,7 +3874,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>125920065</v>
       </c>
@@ -5232,7 +3912,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>125924508</v>
       </c>
@@ -5270,7 +3950,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>125926112</v>
       </c>
@@ -5308,7 +3988,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>125927235</v>
       </c>
@@ -5346,7 +4026,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>125927477</v>
       </c>
@@ -5384,7 +4064,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>125927712</v>
       </c>
@@ -5422,7 +4102,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>125927811</v>
       </c>
@@ -5460,7 +4140,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>125928500</v>
       </c>
@@ -5498,7 +4178,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>125928781</v>
       </c>
@@ -5536,7 +4216,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>125928935</v>
       </c>
@@ -5574,7 +4254,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>125929845</v>
       </c>
@@ -5612,7 +4292,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>125930432</v>
       </c>
@@ -5650,7 +4330,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>125931903</v>
       </c>
@@ -5688,7 +4368,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>125932521</v>
       </c>
@@ -5726,7 +4406,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>125932669</v>
       </c>
@@ -5764,7 +4444,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>125933582</v>
       </c>
@@ -5802,7 +4482,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>125933608</v>
       </c>
@@ -5840,7 +4520,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>125935767</v>
       </c>
@@ -5878,7 +4558,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>125938612</v>
       </c>
@@ -5916,7 +4596,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>125944749</v>
       </c>
@@ -5954,7 +4634,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>125945240</v>
       </c>
@@ -5992,7 +4672,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>125949456</v>
       </c>
@@ -6030,7 +4710,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>125958349</v>
       </c>
@@ -6068,7 +4748,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>125958503</v>
       </c>
@@ -6106,7 +4786,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>125960344</v>
       </c>
@@ -6144,7 +4824,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>125962131</v>
       </c>
@@ -6182,7 +4862,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>125965767</v>
       </c>
@@ -6220,7 +4900,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>125965877</v>
       </c>
@@ -6258,7 +4938,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>125969356</v>
       </c>
@@ -6296,7 +4976,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>125971901</v>
       </c>
@@ -6334,7 +5014,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>125976084</v>
       </c>
@@ -6372,7 +5052,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>125976278</v>
       </c>
@@ -6410,7 +5090,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>125977146</v>
       </c>
@@ -6448,7 +5128,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>125977504</v>
       </c>
@@ -6486,7 +5166,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>125981162</v>
       </c>
@@ -6524,7 +5204,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>125983181</v>
       </c>
@@ -6562,7 +5242,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>125983593</v>
       </c>
@@ -6600,7 +5280,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>125984782</v>
       </c>
@@ -6638,7 +5318,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>125992174</v>
       </c>
@@ -6676,7 +5356,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>125992452</v>
       </c>
@@ -6714,7 +5394,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>125997050</v>
       </c>
@@ -6752,7 +5432,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>126009389</v>
       </c>
@@ -6790,7 +5470,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>126012544</v>
       </c>
@@ -6828,7 +5508,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>126013965</v>
       </c>
@@ -6866,7 +5546,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>126015225</v>
       </c>
@@ -6904,7 +5584,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>126015257</v>
       </c>
@@ -6942,7 +5622,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>126020235</v>
       </c>
@@ -6980,7 +5660,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>126028210</v>
       </c>
@@ -7018,7 +5698,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>126028956</v>
       </c>
@@ -7056,7 +5736,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>126029328</v>
       </c>
@@ -7094,7 +5774,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>126029650</v>
       </c>
@@ -7132,7 +5812,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>126029868</v>
       </c>
@@ -7170,7 +5850,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>126033233</v>
       </c>
@@ -7208,7 +5888,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>126036666</v>
       </c>
@@ -7246,7 +5926,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>126037292</v>
       </c>
@@ -7284,7 +5964,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>126040785</v>
       </c>
@@ -7322,7 +6002,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>126040979</v>
       </c>
@@ -7360,7 +6040,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>126041187</v>
       </c>
@@ -7398,7 +6078,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>126043144</v>
       </c>
@@ -7436,7 +6116,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>126045060</v>
       </c>
@@ -7474,7 +6154,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>126045520</v>
       </c>
@@ -7512,7 +6192,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>126049650</v>
       </c>
@@ -7550,7 +6230,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>126051286</v>
       </c>
@@ -7588,7 +6268,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>126052567</v>
       </c>
@@ -7626,7 +6306,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>126057040</v>
       </c>
@@ -7664,7 +6344,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>126057529</v>
       </c>
@@ -7702,7 +6382,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>126057835</v>
       </c>
@@ -7740,7 +6420,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>126058412</v>
       </c>
@@ -7778,7 +6458,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>126063955</v>
       </c>
@@ -7816,7 +6496,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>126064498</v>
       </c>
@@ -7854,7 +6534,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>126065211</v>
       </c>
@@ -7892,7 +6572,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>126074608</v>
       </c>
@@ -7930,7 +6610,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>126078394</v>
       </c>
@@ -7968,7 +6648,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>126080342</v>
       </c>
@@ -8006,7 +6686,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>126082448</v>
       </c>
@@ -8044,7 +6724,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>126082622</v>
       </c>
@@ -8082,7 +6762,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>126084723</v>
       </c>
@@ -8120,7 +6800,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>126086747</v>
       </c>
@@ -8158,7 +6838,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>126088025</v>
       </c>
@@ -8196,7 +6876,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>126088302</v>
       </c>
@@ -8234,7 +6914,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>126088413</v>
       </c>
@@ -8272,7 +6952,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>126088528</v>
       </c>
@@ -8310,7 +6990,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>126089277</v>
       </c>
@@ -8348,7 +7028,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>126089435</v>
       </c>
@@ -8386,7 +7066,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>126090634</v>
       </c>
@@ -8424,7 +7104,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>126093282</v>
       </c>
@@ -8462,7 +7142,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>126093649</v>
       </c>
@@ -8500,7 +7180,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>126097132</v>
       </c>
@@ -8538,7 +7218,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126098812</v>
       </c>
@@ -8576,7 +7256,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>126099189</v>
       </c>
@@ -8614,7 +7294,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>126099880</v>
       </c>
@@ -8652,7 +7332,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>126100047</v>
       </c>
@@ -8690,7 +7370,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>126101516</v>
       </c>
@@ -8728,7 +7408,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>126102394</v>
       </c>
@@ -8766,7 +7446,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>126104952</v>
       </c>
@@ -8804,7 +7484,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>126106789</v>
       </c>
@@ -8842,7 +7522,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>126111482</v>
       </c>
@@ -8880,7 +7560,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>126111872</v>
       </c>
@@ -8918,7 +7598,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>126119068</v>
       </c>
@@ -8956,7 +7636,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>126120069</v>
       </c>
@@ -8994,7 +7674,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>126120915</v>
       </c>
@@ -9032,7 +7712,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>126120976</v>
       </c>
@@ -9070,7 +7750,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>126122910</v>
       </c>
@@ -9108,7 +7788,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>126130699</v>
       </c>
@@ -9146,7 +7826,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>126131117</v>
       </c>
@@ -9184,7 +7864,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>126136404</v>
       </c>
@@ -9222,7 +7902,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>126140055</v>
       </c>
@@ -9260,7 +7940,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>126147040</v>
       </c>
@@ -9298,7 +7978,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>126155748</v>
       </c>
@@ -9336,7 +8016,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>126155838</v>
       </c>
@@ -9374,7 +8054,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>126157906</v>
       </c>
@@ -9412,7 +8092,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>126158151</v>
       </c>
@@ -9450,7 +8130,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>126162518</v>
       </c>
@@ -9488,7 +8168,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>126164369</v>
       </c>
@@ -9526,7 +8206,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>126164882</v>
       </c>
@@ -9564,7 +8244,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>126165476</v>
       </c>
@@ -9602,7 +8282,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>126165996</v>
       </c>
@@ -9640,7 +8320,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>126167070</v>
       </c>
@@ -9678,7 +8358,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>126168025</v>
       </c>
@@ -9716,7 +8396,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>126168249</v>
       </c>
@@ -9754,7 +8434,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>126173180</v>
       </c>
@@ -9792,7 +8472,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>126174316</v>
       </c>
@@ -9830,7 +8510,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>126174669</v>
       </c>
@@ -9868,7 +8548,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>126176463</v>
       </c>
@@ -9906,7 +8586,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>126176884</v>
       </c>
@@ -9944,7 +8624,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>126185047</v>
       </c>
@@ -9982,7 +8662,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>126185760</v>
       </c>
@@ -10020,7 +8700,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>126187183</v>
       </c>
@@ -10058,7 +8738,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>126187745</v>
       </c>
@@ -10096,7 +8776,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>126192174</v>
       </c>
@@ -10134,7 +8814,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>126192469</v>
       </c>
@@ -10172,7 +8852,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>126192814</v>
       </c>
@@ -10210,7 +8890,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>126193665</v>
       </c>
@@ -10248,7 +8928,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>126193855</v>
       </c>
@@ -10286,7 +8966,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>126194373</v>
       </c>
@@ -10324,7 +9004,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>126195588</v>
       </c>
@@ -10362,7 +9042,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>126197992</v>
       </c>
@@ -10400,7 +9080,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>126198450</v>
       </c>
@@ -10438,7 +9118,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>126198510</v>
       </c>
@@ -10476,7 +9156,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>126198929</v>
       </c>
@@ -10514,7 +9194,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>126201454</v>
       </c>
@@ -10552,7 +9232,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>126201460</v>
       </c>
@@ -10590,7 +9270,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>126201930</v>
       </c>
@@ -10628,7 +9308,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>126201991</v>
       </c>
@@ -10666,7 +9346,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>126212316</v>
       </c>
@@ -10704,7 +9384,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>126213617</v>
       </c>
@@ -10742,7 +9422,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>126216332</v>
       </c>
@@ -10780,7 +9460,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>126218950</v>
       </c>
@@ -10818,7 +9498,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>126230676</v>
       </c>
@@ -10856,7 +9536,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>126231536</v>
       </c>
@@ -10894,7 +9574,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>126237618</v>
       </c>
@@ -10932,7 +9612,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>126245598</v>
       </c>
@@ -10970,7 +9650,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>126265244</v>
       </c>
@@ -11008,7 +9688,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>126265499</v>
       </c>
@@ -11046,7 +9726,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>126266542</v>
       </c>
@@ -11084,7 +9764,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>126268776</v>
       </c>
@@ -11122,7 +9802,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>126280119</v>
       </c>
@@ -11160,7 +9840,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>126280477</v>
       </c>
@@ -11198,7 +9878,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>126281587</v>
       </c>
@@ -11236,7 +9916,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>126281992</v>
       </c>
@@ -11305,31 +9985,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72528DB3-C92F-44B0-BC43-0ABEFE5C7F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494F4DA1-EF9E-4DF8-ADED-D3FA85E6BBBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q104"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,16 +585,16 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>125937480</v>
+        <v>124182824</v>
       </c>
       <c r="E2">
         <v>2002</v>
       </c>
       <c r="F2" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G2" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="I2">
         <v>42</v>
@@ -623,10 +623,10 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>125951571</v>
+        <v>127334698</v>
       </c>
       <c r="E3">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F3" s="2">
         <v>45394</v>
@@ -638,7 +638,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -661,13 +661,13 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>127182328</v>
+        <v>127336434</v>
       </c>
       <c r="E4">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45394</v>
+        <v>45395</v>
       </c>
       <c r="G4" s="2">
         <v>45394</v>
@@ -676,7 +676,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,13 +699,13 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>127184318</v>
+        <v>127342981</v>
       </c>
       <c r="E5">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45394</v>
+        <v>45395</v>
       </c>
       <c r="G5" s="2">
         <v>45394</v>
@@ -714,7 +714,7 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,22 +737,22 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>127293631</v>
+        <v>123751819</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45391</v>
+        <v>45397</v>
       </c>
       <c r="G6" s="2">
-        <v>45391</v>
+        <v>45397</v>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -775,22 +775,22 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>127302383</v>
+        <v>124482773</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45391</v>
+        <v>45397</v>
       </c>
       <c r="G7" s="2">
-        <v>45391</v>
+        <v>45394</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -813,22 +813,22 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>127309129</v>
+        <v>124557374</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45392</v>
+        <v>45397</v>
       </c>
       <c r="G8" s="2">
-        <v>45392</v>
+        <v>45397</v>
       </c>
       <c r="I8">
         <v>42</v>
       </c>
       <c r="J8">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -851,22 +851,22 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>127315951</v>
+        <v>124732885</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45392</v>
+        <v>45397</v>
       </c>
       <c r="G9" s="2">
-        <v>45392</v>
+        <v>45394</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -889,22 +889,22 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>127317129</v>
+        <v>124810819</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45393</v>
+        <v>45397</v>
       </c>
       <c r="G10" s="2">
-        <v>45392</v>
+        <v>45394</v>
       </c>
       <c r="I10">
         <v>42</v>
       </c>
       <c r="J10">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -927,22 +927,22 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>127319087</v>
+        <v>125450927</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45393</v>
+        <v>45397</v>
       </c>
       <c r="G11" s="2">
-        <v>45392</v>
+        <v>45391</v>
       </c>
       <c r="I11">
         <v>42</v>
       </c>
       <c r="J11">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -965,22 +965,22 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>127327029</v>
+        <v>125585620</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G12" s="2">
-        <v>45393</v>
+        <v>45397</v>
       </c>
       <c r="I12">
         <v>42</v>
       </c>
       <c r="J12">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>123744943</v>
+        <v>125595299</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G13" s="2">
-        <v>45394</v>
+        <v>45395</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>123762419</v>
+        <v>125836120</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G14" s="2">
-        <v>45394</v>
+        <v>45387</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>123867019</v>
+        <v>126218119</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45394</v>
+        <v>45398</v>
       </c>
       <c r="G15" s="2">
-        <v>45394</v>
+        <v>45398</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>123877936</v>
+        <v>126548288</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G16" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,13 +1155,13 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>123937642</v>
+        <v>126631879</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G17" s="2">
         <v>45394</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>124400918</v>
+        <v>126793207</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G18" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,13 +1231,13 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>124671883</v>
+        <v>126899045</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G19" s="2">
         <v>45394</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>124879750</v>
+        <v>126944734</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G20" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>125061183</v>
+        <v>126985163</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45395</v>
+        <v>45397</v>
       </c>
       <c r="G21" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>125296400</v>
+        <v>127105312</v>
       </c>
       <c r="E22">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G22" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1383,16 +1383,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>125356130</v>
+        <v>127120690</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45395</v>
+        <v>45397</v>
       </c>
       <c r="G23" s="2">
-        <v>45393</v>
+        <v>45394</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1421,22 +1421,22 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>125466097</v>
+        <v>127251790</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45394</v>
+        <v>45387</v>
       </c>
       <c r="G24" s="2">
-        <v>45391</v>
+        <v>45386</v>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1459,13 +1459,13 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>125523112</v>
+        <v>127309850</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45394</v>
+        <v>45393</v>
       </c>
       <c r="G25" s="2">
         <v>45392</v>
@@ -1474,7 +1474,7 @@
         <v>42</v>
       </c>
       <c r="J25">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>125767029</v>
+        <v>124411489</v>
       </c>
       <c r="E26">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F26" s="2">
-        <v>45394</v>
+        <v>45384</v>
       </c>
       <c r="G26" s="2">
-        <v>45394</v>
+        <v>45371</v>
       </c>
       <c r="I26">
         <v>42</v>
       </c>
       <c r="J26">
-        <v>8001</v>
+        <v>8017</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>125817755</v>
+        <v>124001307</v>
       </c>
       <c r="E27">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F27" s="2">
+        <v>45397</v>
+      </c>
+      <c r="G27" s="2">
         <v>45394</v>
       </c>
-      <c r="G27" s="2">
-        <v>45391</v>
-      </c>
       <c r="I27">
         <v>42</v>
       </c>
       <c r="J27">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>125889123</v>
+        <v>127353311</v>
       </c>
       <c r="E28">
         <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G28" s="2">
-        <v>45393</v>
+        <v>45397</v>
       </c>
       <c r="I28">
         <v>42</v>
       </c>
       <c r="J28">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -1611,22 +1611,22 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>125900777</v>
+        <v>127355865</v>
       </c>
       <c r="E29">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F29" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G29" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="I29">
         <v>42</v>
       </c>
       <c r="J29">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>125904222</v>
+        <v>127356136</v>
       </c>
       <c r="E30">
         <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45395</v>
+        <v>45397</v>
       </c>
       <c r="G30" s="2">
-        <v>45395</v>
+        <v>45397</v>
       </c>
       <c r="I30">
         <v>42</v>
       </c>
       <c r="J30">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1687,22 +1687,22 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>126046471</v>
+        <v>127362490</v>
       </c>
       <c r="E31">
         <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G31" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="I31">
         <v>42</v>
       </c>
       <c r="J31">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>126086224</v>
+        <v>127363286</v>
       </c>
       <c r="E32">
         <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="G32" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="I32">
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -1761,2744 +1761,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>126150829</v>
-      </c>
-      <c r="E33">
-        <v>1211</v>
-      </c>
-      <c r="F33" s="2">
-        <v>45395</v>
-      </c>
-      <c r="G33" s="2">
-        <v>45395</v>
-      </c>
-      <c r="I33">
-        <v>42</v>
-      </c>
-      <c r="J33">
-        <v>8001</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>126173538</v>
-      </c>
-      <c r="E34">
-        <v>1211</v>
-      </c>
-      <c r="F34" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G34" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I34">
-        <v>42</v>
-      </c>
-      <c r="J34">
-        <v>8001</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>126198253</v>
-      </c>
-      <c r="E35">
-        <v>1211</v>
-      </c>
-      <c r="F35" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G35" s="2">
-        <v>45391</v>
-      </c>
-      <c r="I35">
-        <v>42</v>
-      </c>
-      <c r="J35">
-        <v>8001</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>126230009</v>
-      </c>
-      <c r="E36">
-        <v>1211</v>
-      </c>
-      <c r="F36" s="2">
-        <v>45395</v>
-      </c>
-      <c r="G36" s="2">
-        <v>45395</v>
-      </c>
-      <c r="I36">
-        <v>42</v>
-      </c>
-      <c r="J36">
-        <v>8001</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>126266855</v>
-      </c>
-      <c r="E37">
-        <v>1211</v>
-      </c>
-      <c r="F37" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G37" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I37">
-        <v>42</v>
-      </c>
-      <c r="J37">
-        <v>8001</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>126377061</v>
-      </c>
-      <c r="E38">
-        <v>1211</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G38" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I38">
-        <v>42</v>
-      </c>
-      <c r="J38">
-        <v>8001</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>126406052</v>
-      </c>
-      <c r="E39">
-        <v>1212</v>
-      </c>
-      <c r="F39" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G39" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I39">
-        <v>42</v>
-      </c>
-      <c r="J39">
-        <v>8001</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>126433221</v>
-      </c>
-      <c r="E40">
-        <v>1211</v>
-      </c>
-      <c r="F40" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G40" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I40">
-        <v>42</v>
-      </c>
-      <c r="J40">
-        <v>8001</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>126640609</v>
-      </c>
-      <c r="E41">
-        <v>1211</v>
-      </c>
-      <c r="F41" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G41" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I41">
-        <v>42</v>
-      </c>
-      <c r="J41">
-        <v>8001</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>126723170</v>
-      </c>
-      <c r="E42">
-        <v>1211</v>
-      </c>
-      <c r="F42" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G42" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I42">
-        <v>42</v>
-      </c>
-      <c r="J42">
-        <v>8001</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>126740507</v>
-      </c>
-      <c r="E43">
-        <v>1211</v>
-      </c>
-      <c r="F43" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G43" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I43">
-        <v>42</v>
-      </c>
-      <c r="J43">
-        <v>8001</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>126775725</v>
-      </c>
-      <c r="E44">
-        <v>1212</v>
-      </c>
-      <c r="F44" s="2">
-        <v>45395</v>
-      </c>
-      <c r="G44" s="2">
-        <v>45395</v>
-      </c>
-      <c r="I44">
-        <v>42</v>
-      </c>
-      <c r="J44">
-        <v>8001</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="Q44">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>126783355</v>
-      </c>
-      <c r="E45">
-        <v>1211</v>
-      </c>
-      <c r="F45" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G45" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I45">
-        <v>42</v>
-      </c>
-      <c r="J45">
-        <v>8001</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
-      <c r="P45">
-        <v>0</v>
-      </c>
-      <c r="Q45">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>126797412</v>
-      </c>
-      <c r="E46">
-        <v>1211</v>
-      </c>
-      <c r="F46" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G46" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I46">
-        <v>42</v>
-      </c>
-      <c r="J46">
-        <v>8001</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>126891500</v>
-      </c>
-      <c r="E47">
-        <v>1212</v>
-      </c>
-      <c r="F47" s="2">
-        <v>45395</v>
-      </c>
-      <c r="G47" s="2">
-        <v>45393</v>
-      </c>
-      <c r="I47">
-        <v>42</v>
-      </c>
-      <c r="J47">
-        <v>8001</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>126993232</v>
-      </c>
-      <c r="E48">
-        <v>1211</v>
-      </c>
-      <c r="F48" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G48" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I48">
-        <v>42</v>
-      </c>
-      <c r="J48">
-        <v>8001</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A49">
-        <v>127029838</v>
-      </c>
-      <c r="E49">
-        <v>1211</v>
-      </c>
-      <c r="F49" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G49" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I49">
-        <v>42</v>
-      </c>
-      <c r="J49">
-        <v>8001</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>127108468</v>
-      </c>
-      <c r="E50">
-        <v>1211</v>
-      </c>
-      <c r="F50" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G50" s="2">
-        <v>45393</v>
-      </c>
-      <c r="I50">
-        <v>42</v>
-      </c>
-      <c r="J50">
-        <v>8001</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>127158669</v>
-      </c>
-      <c r="E51">
-        <v>1211</v>
-      </c>
-      <c r="F51" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G51" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I51">
-        <v>42</v>
-      </c>
-      <c r="J51">
-        <v>8001</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>0</v>
-      </c>
-      <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A52">
-        <v>127296738</v>
-      </c>
-      <c r="E52">
-        <v>1211</v>
-      </c>
-      <c r="F52" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G52" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I52">
-        <v>42</v>
-      </c>
-      <c r="J52">
-        <v>8001</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
-        <v>0</v>
-      </c>
-      <c r="P52">
-        <v>0</v>
-      </c>
-      <c r="Q52">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A53">
-        <v>127304218</v>
-      </c>
-      <c r="E53">
-        <v>1211</v>
-      </c>
-      <c r="F53" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G53" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I53">
-        <v>42</v>
-      </c>
-      <c r="J53">
-        <v>8001</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53">
-        <v>0</v>
-      </c>
-      <c r="P53">
-        <v>0</v>
-      </c>
-      <c r="Q53">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>127310902</v>
-      </c>
-      <c r="E54">
-        <v>1211</v>
-      </c>
-      <c r="F54" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G54" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I54">
-        <v>42</v>
-      </c>
-      <c r="J54">
-        <v>8001</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
-      <c r="O54">
-        <v>0</v>
-      </c>
-      <c r="P54">
-        <v>0</v>
-      </c>
-      <c r="Q54">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>127315238</v>
-      </c>
-      <c r="E55">
-        <v>1211</v>
-      </c>
-      <c r="F55" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G55" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I55">
-        <v>42</v>
-      </c>
-      <c r="J55">
-        <v>8001</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55">
-        <v>0</v>
-      </c>
-      <c r="P55">
-        <v>0</v>
-      </c>
-      <c r="Q55">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A56">
-        <v>127251790</v>
-      </c>
-      <c r="E56">
-        <v>1211</v>
-      </c>
-      <c r="F56" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G56" s="2">
-        <v>45386</v>
-      </c>
-      <c r="I56">
-        <v>42</v>
-      </c>
-      <c r="J56">
-        <v>8021</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56">
-        <v>0</v>
-      </c>
-      <c r="P56">
-        <v>0</v>
-      </c>
-      <c r="Q56">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A57">
-        <v>124411489</v>
-      </c>
-      <c r="E57">
-        <v>601</v>
-      </c>
-      <c r="F57" s="2">
-        <v>45384</v>
-      </c>
-      <c r="G57" s="2">
-        <v>45371</v>
-      </c>
-      <c r="I57">
-        <v>42</v>
-      </c>
-      <c r="J57">
-        <v>8017</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57">
-        <v>0</v>
-      </c>
-      <c r="P57">
-        <v>0</v>
-      </c>
-      <c r="Q57">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A58">
-        <v>127247523</v>
-      </c>
-      <c r="E58">
-        <v>601</v>
-      </c>
-      <c r="F58" s="2">
-        <v>45386</v>
-      </c>
-      <c r="G58" s="2">
-        <v>45386</v>
-      </c>
-      <c r="I58">
-        <v>42</v>
-      </c>
-      <c r="J58">
-        <v>8013</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58">
-        <v>0</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58">
-        <v>0</v>
-      </c>
-      <c r="P58">
-        <v>0</v>
-      </c>
-      <c r="Q58">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A59">
-        <v>127249160</v>
-      </c>
-      <c r="E59">
-        <v>609</v>
-      </c>
-      <c r="F59" s="2">
-        <v>45386</v>
-      </c>
-      <c r="G59" s="2">
-        <v>45386</v>
-      </c>
-      <c r="I59">
-        <v>42</v>
-      </c>
-      <c r="J59">
-        <v>8004</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
-      <c r="M59">
-        <v>0</v>
-      </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="O59">
-        <v>0</v>
-      </c>
-      <c r="P59">
-        <v>0</v>
-      </c>
-      <c r="Q59">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A60">
-        <v>127254845</v>
-      </c>
-      <c r="E60">
-        <v>601</v>
-      </c>
-      <c r="F60" s="2">
-        <v>45386</v>
-      </c>
-      <c r="G60" s="2">
-        <v>45386</v>
-      </c>
-      <c r="I60">
-        <v>42</v>
-      </c>
-      <c r="J60">
-        <v>8013</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
-        <v>0</v>
-      </c>
-      <c r="P60">
-        <v>0</v>
-      </c>
-      <c r="Q60">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A61">
-        <v>127262498</v>
-      </c>
-      <c r="E61">
-        <v>601</v>
-      </c>
-      <c r="F61" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G61" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I61">
-        <v>42</v>
-      </c>
-      <c r="J61">
-        <v>8013</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>0</v>
-      </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>127262503</v>
-      </c>
-      <c r="E62">
-        <v>601</v>
-      </c>
-      <c r="F62" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G62" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I62">
-        <v>42</v>
-      </c>
-      <c r="J62">
-        <v>8013</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A63">
-        <v>127262588</v>
-      </c>
-      <c r="E63">
-        <v>601</v>
-      </c>
-      <c r="F63" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G63" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I63">
-        <v>42</v>
-      </c>
-      <c r="J63">
-        <v>8013</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A64">
-        <v>127262593</v>
-      </c>
-      <c r="E64">
-        <v>601</v>
-      </c>
-      <c r="F64" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G64" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I64">
-        <v>42</v>
-      </c>
-      <c r="J64">
-        <v>8013</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A65">
-        <v>127264101</v>
-      </c>
-      <c r="E65">
-        <v>609</v>
-      </c>
-      <c r="F65" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G65" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I65">
-        <v>42</v>
-      </c>
-      <c r="J65">
-        <v>8004</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A66">
-        <v>127234160</v>
-      </c>
-      <c r="E66">
-        <v>601</v>
-      </c>
-      <c r="F66" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G66" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I66">
-        <v>42</v>
-      </c>
-      <c r="J66">
-        <v>8004</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>0</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A67">
-        <v>127234586</v>
-      </c>
-      <c r="E67">
-        <v>601</v>
-      </c>
-      <c r="F67" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G67" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I67">
-        <v>42</v>
-      </c>
-      <c r="J67">
-        <v>8004</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A68">
-        <v>127236285</v>
-      </c>
-      <c r="E68">
-        <v>601</v>
-      </c>
-      <c r="F68" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G68" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I68">
-        <v>42</v>
-      </c>
-      <c r="J68">
-        <v>8004</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A69">
-        <v>127236547</v>
-      </c>
-      <c r="E69">
-        <v>601</v>
-      </c>
-      <c r="F69" s="2">
-        <v>45385</v>
-      </c>
-      <c r="G69" s="2">
-        <v>45385</v>
-      </c>
-      <c r="I69">
-        <v>42</v>
-      </c>
-      <c r="J69">
-        <v>8004</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>127268036</v>
-      </c>
-      <c r="E70">
-        <v>601</v>
-      </c>
-      <c r="F70" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G70" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I70">
-        <v>42</v>
-      </c>
-      <c r="J70">
-        <v>8004</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>0</v>
-      </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A71">
-        <v>127268527</v>
-      </c>
-      <c r="E71">
-        <v>601</v>
-      </c>
-      <c r="F71" s="2">
-        <v>45387</v>
-      </c>
-      <c r="G71" s="2">
-        <v>45387</v>
-      </c>
-      <c r="I71">
-        <v>42</v>
-      </c>
-      <c r="J71">
-        <v>8004</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A72">
-        <v>124860530</v>
-      </c>
-      <c r="E72">
-        <v>1211</v>
-      </c>
-      <c r="F72" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G72" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I72">
-        <v>42</v>
-      </c>
-      <c r="J72">
-        <v>715</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <v>0</v>
-      </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <v>0</v>
-      </c>
-      <c r="P72">
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A73">
-        <v>126370896</v>
-      </c>
-      <c r="E73">
-        <v>1211</v>
-      </c>
-      <c r="F73" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G73" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I73">
-        <v>42</v>
-      </c>
-      <c r="J73">
-        <v>715</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <v>0</v>
-      </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73">
-        <v>0</v>
-      </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A74">
-        <v>127303625</v>
-      </c>
-      <c r="E74">
-        <v>1212</v>
-      </c>
-      <c r="F74" s="2">
-        <v>45391</v>
-      </c>
-      <c r="G74" s="2">
-        <v>45391</v>
-      </c>
-      <c r="I74">
-        <v>42</v>
-      </c>
-      <c r="J74">
-        <v>715</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <v>0</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <v>0</v>
-      </c>
-      <c r="P74">
-        <v>0</v>
-      </c>
-      <c r="Q74">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A75">
-        <v>127308333</v>
-      </c>
-      <c r="E75">
-        <v>1211</v>
-      </c>
-      <c r="F75" s="2">
-        <v>45392</v>
-      </c>
-      <c r="G75" s="2">
-        <v>45392</v>
-      </c>
-      <c r="I75">
-        <v>42</v>
-      </c>
-      <c r="J75">
-        <v>715</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
-      </c>
-      <c r="P75">
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A76">
-        <v>127320182</v>
-      </c>
-      <c r="E76">
-        <v>1211</v>
-      </c>
-      <c r="F76" s="2">
-        <v>45393</v>
-      </c>
-      <c r="G76" s="2">
-        <v>45393</v>
-      </c>
-      <c r="I76">
-        <v>42</v>
-      </c>
-      <c r="J76">
-        <v>715</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76">
-        <v>0</v>
-      </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
-      <c r="O76">
-        <v>0</v>
-      </c>
-      <c r="P76">
-        <v>0</v>
-      </c>
-      <c r="Q76">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A77">
-        <v>127322046</v>
-      </c>
-      <c r="E77">
-        <v>1212</v>
-      </c>
-      <c r="F77" s="2">
-        <v>45393</v>
-      </c>
-      <c r="G77" s="2">
-        <v>45393</v>
-      </c>
-      <c r="I77">
-        <v>42</v>
-      </c>
-      <c r="J77">
-        <v>715</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <v>0</v>
-      </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
-      <c r="O77">
-        <v>0</v>
-      </c>
-      <c r="P77">
-        <v>0</v>
-      </c>
-      <c r="Q77">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A78">
-        <v>127322619</v>
-      </c>
-      <c r="E78">
-        <v>1211</v>
-      </c>
-      <c r="F78" s="2">
-        <v>45393</v>
-      </c>
-      <c r="G78" s="2">
-        <v>45393</v>
-      </c>
-      <c r="I78">
-        <v>42</v>
-      </c>
-      <c r="J78">
-        <v>715</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78">
-        <v>0</v>
-      </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
-      <c r="O78">
-        <v>0</v>
-      </c>
-      <c r="P78">
-        <v>0</v>
-      </c>
-      <c r="Q78">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A79">
-        <v>127323339</v>
-      </c>
-      <c r="E79">
-        <v>1211</v>
-      </c>
-      <c r="F79" s="2">
-        <v>45393</v>
-      </c>
-      <c r="G79" s="2">
-        <v>45393</v>
-      </c>
-      <c r="I79">
-        <v>42</v>
-      </c>
-      <c r="J79">
-        <v>715</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79">
-        <v>0</v>
-      </c>
-      <c r="P79">
-        <v>0</v>
-      </c>
-      <c r="Q79">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A80">
-        <v>127324041</v>
-      </c>
-      <c r="E80">
-        <v>1211</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45393</v>
-      </c>
-      <c r="G80" s="2">
-        <v>45393</v>
-      </c>
-      <c r="I80">
-        <v>42</v>
-      </c>
-      <c r="J80">
-        <v>715</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>0</v>
-      </c>
-      <c r="P80">
-        <v>0</v>
-      </c>
-      <c r="Q80">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A81">
-        <v>127325358</v>
-      </c>
-      <c r="E81">
-        <v>1212</v>
-      </c>
-      <c r="F81" s="2">
-        <v>45393</v>
-      </c>
-      <c r="G81" s="2">
-        <v>45393</v>
-      </c>
-      <c r="I81">
-        <v>42</v>
-      </c>
-      <c r="J81">
-        <v>715</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
-        <v>0</v>
-      </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
-      <c r="O81">
-        <v>0</v>
-      </c>
-      <c r="P81">
-        <v>0</v>
-      </c>
-      <c r="Q81">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A82">
-        <v>127325774</v>
-      </c>
-      <c r="E82">
-        <v>1212</v>
-      </c>
-      <c r="F82" s="2">
-        <v>45393</v>
-      </c>
-      <c r="G82" s="2">
-        <v>45393</v>
-      </c>
-      <c r="I82">
-        <v>42</v>
-      </c>
-      <c r="J82">
-        <v>715</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>0</v>
-      </c>
-      <c r="P82">
-        <v>0</v>
-      </c>
-      <c r="Q82">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A83">
-        <v>127325966</v>
-      </c>
-      <c r="E83">
-        <v>1211</v>
-      </c>
-      <c r="F83" s="2">
-        <v>45393</v>
-      </c>
-      <c r="G83" s="2">
-        <v>45393</v>
-      </c>
-      <c r="I83">
-        <v>42</v>
-      </c>
-      <c r="J83">
-        <v>715</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
-      <c r="O83">
-        <v>0</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
-      <c r="Q83">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A84">
-        <v>127327524</v>
-      </c>
-      <c r="E84">
-        <v>1211</v>
-      </c>
-      <c r="F84" s="2">
-        <v>45393</v>
-      </c>
-      <c r="G84" s="2">
-        <v>45393</v>
-      </c>
-      <c r="I84">
-        <v>42</v>
-      </c>
-      <c r="J84">
-        <v>715</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84">
-        <v>0</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A85">
-        <v>127328699</v>
-      </c>
-      <c r="E85">
-        <v>1212</v>
-      </c>
-      <c r="F85" s="2">
-        <v>45393</v>
-      </c>
-      <c r="G85" s="2">
-        <v>45393</v>
-      </c>
-      <c r="I85">
-        <v>42</v>
-      </c>
-      <c r="J85">
-        <v>715</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
-        <v>0</v>
-      </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>0</v>
-      </c>
-      <c r="P85">
-        <v>0</v>
-      </c>
-      <c r="Q85">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A86">
-        <v>127332712</v>
-      </c>
-      <c r="E86">
-        <v>1211</v>
-      </c>
-      <c r="F86" s="2">
-        <v>45393</v>
-      </c>
-      <c r="G86" s="2">
-        <v>45393</v>
-      </c>
-      <c r="I86">
-        <v>42</v>
-      </c>
-      <c r="J86">
-        <v>715</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86">
-        <v>0</v>
-      </c>
-      <c r="P86">
-        <v>0</v>
-      </c>
-      <c r="Q86">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A87">
-        <v>127336391</v>
-      </c>
-      <c r="E87">
-        <v>1211</v>
-      </c>
-      <c r="F87" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G87" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I87">
-        <v>42</v>
-      </c>
-      <c r="J87">
-        <v>715</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
-      <c r="M87">
-        <v>0</v>
-      </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
-      <c r="O87">
-        <v>0</v>
-      </c>
-      <c r="P87">
-        <v>0</v>
-      </c>
-      <c r="Q87">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A88">
-        <v>127336521</v>
-      </c>
-      <c r="E88">
-        <v>1212</v>
-      </c>
-      <c r="F88" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G88" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I88">
-        <v>42</v>
-      </c>
-      <c r="J88">
-        <v>715</v>
-      </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88">
-        <v>0</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88">
-        <v>0</v>
-      </c>
-      <c r="P88">
-        <v>0</v>
-      </c>
-      <c r="Q88">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A89">
-        <v>127337536</v>
-      </c>
-      <c r="E89">
-        <v>1211</v>
-      </c>
-      <c r="F89" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G89" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I89">
-        <v>42</v>
-      </c>
-      <c r="J89">
-        <v>715</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
-        <v>0</v>
-      </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <v>0</v>
-      </c>
-      <c r="P89">
-        <v>0</v>
-      </c>
-      <c r="Q89">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A90">
-        <v>127338324</v>
-      </c>
-      <c r="E90">
-        <v>1211</v>
-      </c>
-      <c r="F90" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G90" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I90">
-        <v>42</v>
-      </c>
-      <c r="J90">
-        <v>715</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A91">
-        <v>127339045</v>
-      </c>
-      <c r="E91">
-        <v>1211</v>
-      </c>
-      <c r="F91" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G91" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I91">
-        <v>42</v>
-      </c>
-      <c r="J91">
-        <v>715</v>
-      </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="M91">
-        <v>0</v>
-      </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
-      <c r="O91">
-        <v>0</v>
-      </c>
-      <c r="P91">
-        <v>0</v>
-      </c>
-      <c r="Q91">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A92">
-        <v>127339571</v>
-      </c>
-      <c r="E92">
-        <v>1211</v>
-      </c>
-      <c r="F92" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G92" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I92">
-        <v>42</v>
-      </c>
-      <c r="J92">
-        <v>715</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
-        <v>0</v>
-      </c>
-      <c r="N92">
-        <v>0</v>
-      </c>
-      <c r="O92">
-        <v>0</v>
-      </c>
-      <c r="P92">
-        <v>0</v>
-      </c>
-      <c r="Q92">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A93">
-        <v>127340090</v>
-      </c>
-      <c r="E93">
-        <v>1212</v>
-      </c>
-      <c r="F93" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G93" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I93">
-        <v>42</v>
-      </c>
-      <c r="J93">
-        <v>715</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
-        <v>0</v>
-      </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
-      <c r="O93">
-        <v>0</v>
-      </c>
-      <c r="P93">
-        <v>0</v>
-      </c>
-      <c r="Q93">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A94">
-        <v>127340727</v>
-      </c>
-      <c r="E94">
-        <v>1212</v>
-      </c>
-      <c r="F94" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G94" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I94">
-        <v>42</v>
-      </c>
-      <c r="J94">
-        <v>715</v>
-      </c>
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="M94">
-        <v>0</v>
-      </c>
-      <c r="N94">
-        <v>0</v>
-      </c>
-      <c r="O94">
-        <v>0</v>
-      </c>
-      <c r="P94">
-        <v>0</v>
-      </c>
-      <c r="Q94">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A95">
-        <v>127341103</v>
-      </c>
-      <c r="E95">
-        <v>1212</v>
-      </c>
-      <c r="F95" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G95" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I95">
-        <v>42</v>
-      </c>
-      <c r="J95">
-        <v>715</v>
-      </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="M95">
-        <v>0</v>
-      </c>
-      <c r="N95">
-        <v>0</v>
-      </c>
-      <c r="O95">
-        <v>0</v>
-      </c>
-      <c r="P95">
-        <v>0</v>
-      </c>
-      <c r="Q95">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A96">
-        <v>127342902</v>
-      </c>
-      <c r="E96">
-        <v>1211</v>
-      </c>
-      <c r="F96" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G96" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I96">
-        <v>42</v>
-      </c>
-      <c r="J96">
-        <v>715</v>
-      </c>
-      <c r="L96">
-        <v>0</v>
-      </c>
-      <c r="M96">
-        <v>0</v>
-      </c>
-      <c r="N96">
-        <v>0</v>
-      </c>
-      <c r="O96">
-        <v>0</v>
-      </c>
-      <c r="P96">
-        <v>0</v>
-      </c>
-      <c r="Q96">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A97">
-        <v>127343948</v>
-      </c>
-      <c r="E97">
-        <v>1211</v>
-      </c>
-      <c r="F97" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G97" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I97">
-        <v>42</v>
-      </c>
-      <c r="J97">
-        <v>715</v>
-      </c>
-      <c r="L97">
-        <v>0</v>
-      </c>
-      <c r="M97">
-        <v>0</v>
-      </c>
-      <c r="N97">
-        <v>0</v>
-      </c>
-      <c r="O97">
-        <v>0</v>
-      </c>
-      <c r="P97">
-        <v>0</v>
-      </c>
-      <c r="Q97">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A98">
-        <v>127344261</v>
-      </c>
-      <c r="E98">
-        <v>1211</v>
-      </c>
-      <c r="F98" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G98" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I98">
-        <v>42</v>
-      </c>
-      <c r="J98">
-        <v>715</v>
-      </c>
-      <c r="L98">
-        <v>0</v>
-      </c>
-      <c r="M98">
-        <v>0</v>
-      </c>
-      <c r="N98">
-        <v>0</v>
-      </c>
-      <c r="O98">
-        <v>0</v>
-      </c>
-      <c r="P98">
-        <v>0</v>
-      </c>
-      <c r="Q98">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A99">
-        <v>127346363</v>
-      </c>
-      <c r="E99">
-        <v>1212</v>
-      </c>
-      <c r="F99" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G99" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I99">
-        <v>42</v>
-      </c>
-      <c r="J99">
-        <v>715</v>
-      </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-      <c r="M99">
-        <v>0</v>
-      </c>
-      <c r="N99">
-        <v>0</v>
-      </c>
-      <c r="O99">
-        <v>0</v>
-      </c>
-      <c r="P99">
-        <v>0</v>
-      </c>
-      <c r="Q99">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A100">
-        <v>127347371</v>
-      </c>
-      <c r="E100">
-        <v>1211</v>
-      </c>
-      <c r="F100" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G100" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I100">
-        <v>42</v>
-      </c>
-      <c r="J100">
-        <v>715</v>
-      </c>
-      <c r="L100">
-        <v>0</v>
-      </c>
-      <c r="M100">
-        <v>0</v>
-      </c>
-      <c r="N100">
-        <v>0</v>
-      </c>
-      <c r="O100">
-        <v>0</v>
-      </c>
-      <c r="P100">
-        <v>0</v>
-      </c>
-      <c r="Q100">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A101">
-        <v>127347828</v>
-      </c>
-      <c r="E101">
-        <v>1211</v>
-      </c>
-      <c r="F101" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G101" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I101">
-        <v>42</v>
-      </c>
-      <c r="J101">
-        <v>715</v>
-      </c>
-      <c r="L101">
-        <v>0</v>
-      </c>
-      <c r="M101">
-        <v>0</v>
-      </c>
-      <c r="N101">
-        <v>0</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>0</v>
-      </c>
-      <c r="Q101">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A102">
-        <v>127348916</v>
-      </c>
-      <c r="E102">
-        <v>1211</v>
-      </c>
-      <c r="F102" s="2">
-        <v>45394</v>
-      </c>
-      <c r="G102" s="2">
-        <v>45394</v>
-      </c>
-      <c r="I102">
-        <v>42</v>
-      </c>
-      <c r="J102">
-        <v>715</v>
-      </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-      <c r="M102">
-        <v>0</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
-        <v>0</v>
-      </c>
-      <c r="P102">
-        <v>0</v>
-      </c>
-      <c r="Q102">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A103">
-        <v>127349741</v>
-      </c>
-      <c r="E103">
-        <v>1211</v>
-      </c>
-      <c r="F103" s="2">
-        <v>45395</v>
-      </c>
-      <c r="G103" s="2">
-        <v>45395</v>
-      </c>
-      <c r="I103">
-        <v>42</v>
-      </c>
-      <c r="J103">
-        <v>715</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="M103">
-        <v>0</v>
-      </c>
-      <c r="N103">
-        <v>0</v>
-      </c>
-      <c r="O103">
-        <v>0</v>
-      </c>
-      <c r="P103">
-        <v>0</v>
-      </c>
-      <c r="Q103">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A104">
-        <v>127351493</v>
-      </c>
-      <c r="E104">
-        <v>1212</v>
-      </c>
-      <c r="F104" s="2">
-        <v>45396</v>
-      </c>
-      <c r="G104" s="2">
-        <v>45396</v>
-      </c>
-      <c r="I104">
-        <v>42</v>
-      </c>
-      <c r="J104">
-        <v>715</v>
-      </c>
-      <c r="L104">
-        <v>0</v>
-      </c>
-      <c r="M104">
-        <v>0</v>
-      </c>
-      <c r="N104">
-        <v>0</v>
-      </c>
-      <c r="O104">
-        <v>0</v>
-      </c>
-      <c r="P104">
-        <v>0</v>
-      </c>
-      <c r="Q104">
-        <v>61</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q104" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -12088,31 +9351,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494F4DA1-EF9E-4DF8-ADED-D3FA85E6BBBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE0B3D1-10A4-4C18-9231-969E95770290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$93</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q93"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,16 +585,16 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>124182824</v>
+        <v>125658570</v>
       </c>
       <c r="E2">
         <v>2002</v>
       </c>
       <c r="F2" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="G2" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="I2">
         <v>42</v>
@@ -623,22 +623,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>127334698</v>
+        <v>126142913</v>
       </c>
       <c r="E3">
-        <v>1211</v>
+        <v>2002</v>
       </c>
       <c r="F3" s="2">
-        <v>45394</v>
+        <v>45400</v>
       </c>
       <c r="G3" s="2">
-        <v>45394</v>
+        <v>45400</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>1735</v>
+        <v>8004</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -661,16 +661,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>127336434</v>
+        <v>127352309</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45395</v>
+        <v>45398</v>
       </c>
       <c r="G4" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="I4">
         <v>42</v>
@@ -699,16 +699,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>127342981</v>
+        <v>127352673</v>
       </c>
       <c r="E5">
         <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45395</v>
+        <v>45397</v>
       </c>
       <c r="G5" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="I5">
         <v>42</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>123751819</v>
+        <v>127355463</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45397</v>
+        <v>45398</v>
       </c>
       <c r="G6" s="2">
         <v>45397</v>
@@ -752,7 +752,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -775,7 +775,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>124482773</v>
+        <v>127357498</v>
       </c>
       <c r="E7">
         <v>1211</v>
@@ -784,13 +784,13 @@
         <v>45397</v>
       </c>
       <c r="G7" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -813,7 +813,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>124557374</v>
+        <v>127363944</v>
       </c>
       <c r="E8">
         <v>1211</v>
@@ -828,7 +828,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -851,7 +851,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>124732885</v>
+        <v>127364168</v>
       </c>
       <c r="E9">
         <v>1211</v>
@@ -860,13 +860,13 @@
         <v>45397</v>
       </c>
       <c r="G9" s="2">
-        <v>45394</v>
+        <v>45397</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -889,16 +889,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>124810819</v>
+        <v>123651355</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="G10" s="2">
-        <v>45394</v>
+        <v>45400</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -927,16 +927,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>125450927</v>
+        <v>123665058</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="G11" s="2">
-        <v>45391</v>
+        <v>45400</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -965,16 +965,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>125585620</v>
+        <v>123755711</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="G12" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>125595299</v>
+        <v>123845664</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="G13" s="2">
-        <v>45395</v>
+        <v>45399</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>125836120</v>
+        <v>124082886</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="G14" s="2">
-        <v>45387</v>
+        <v>45399</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>126218119</v>
+        <v>124103386</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45398</v>
+        <v>45399</v>
       </c>
       <c r="G15" s="2">
-        <v>45398</v>
+        <v>45399</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,13 +1117,13 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>126548288</v>
+        <v>124188182</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="G16" s="2">
         <v>45397</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>126631879</v>
+        <v>124214931</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="G17" s="2">
-        <v>45394</v>
+        <v>45399</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>126793207</v>
+        <v>124403676</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="G18" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>126899045</v>
+        <v>124471306</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="G19" s="2">
-        <v>45394</v>
+        <v>45399</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>126944734</v>
+        <v>124505796</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="G20" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>126985163</v>
+        <v>124522057</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="G21" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>127105312</v>
+        <v>124529758</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="G22" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1383,16 +1383,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>127120690</v>
+        <v>124586494</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="G23" s="2">
-        <v>45394</v>
+        <v>45399</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1421,22 +1421,22 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>127251790</v>
+        <v>124678082</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45387</v>
+        <v>45400</v>
       </c>
       <c r="G24" s="2">
-        <v>45386</v>
+        <v>45400</v>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1459,22 +1459,22 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>127309850</v>
+        <v>124866183</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45393</v>
+        <v>45400</v>
       </c>
       <c r="G25" s="2">
-        <v>45392</v>
+        <v>45400</v>
       </c>
       <c r="I25">
         <v>42</v>
       </c>
       <c r="J25">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>124411489</v>
+        <v>124894979</v>
       </c>
       <c r="E26">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45384</v>
+        <v>45400</v>
       </c>
       <c r="G26" s="2">
-        <v>45371</v>
+        <v>45400</v>
       </c>
       <c r="I26">
         <v>42</v>
       </c>
       <c r="J26">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>124001307</v>
+        <v>125113290</v>
       </c>
       <c r="E27">
         <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="G27" s="2">
-        <v>45394</v>
+        <v>45400</v>
       </c>
       <c r="I27">
         <v>42</v>
       </c>
       <c r="J27">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>127353311</v>
+        <v>125128912</v>
       </c>
       <c r="E28">
         <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="G28" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="I28">
         <v>42</v>
       </c>
       <c r="J28">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -1611,22 +1611,22 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>127355865</v>
+        <v>125178765</v>
       </c>
       <c r="E29">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="G29" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="I29">
         <v>42</v>
       </c>
       <c r="J29">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>127356136</v>
+        <v>125261573</v>
       </c>
       <c r="E30">
         <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="G30" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="I30">
         <v>42</v>
       </c>
       <c r="J30">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1687,22 +1687,22 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>127362490</v>
+        <v>125278835</v>
       </c>
       <c r="E31">
         <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="G31" s="2">
-        <v>45397</v>
+        <v>45399</v>
       </c>
       <c r="I31">
         <v>42</v>
       </c>
       <c r="J31">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -1725,39 +1725,2357 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>127363286</v>
+        <v>125587828</v>
       </c>
       <c r="E32">
+        <v>1212</v>
+      </c>
+      <c r="F32" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G32" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I32">
+        <v>42</v>
+      </c>
+      <c r="J32">
+        <v>8001</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>125677370</v>
+      </c>
+      <c r="E33">
+        <v>1212</v>
+      </c>
+      <c r="F33" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G33" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I33">
+        <v>42</v>
+      </c>
+      <c r="J33">
+        <v>8001</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>125678877</v>
+      </c>
+      <c r="E34">
         <v>1211</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F34" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G34" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I34">
+        <v>42</v>
+      </c>
+      <c r="J34">
+        <v>8001</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>125838464</v>
+      </c>
+      <c r="E35">
+        <v>1211</v>
+      </c>
+      <c r="F35" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G35" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I35">
+        <v>42</v>
+      </c>
+      <c r="J35">
+        <v>8001</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>125929785</v>
+      </c>
+      <c r="E36">
+        <v>1211</v>
+      </c>
+      <c r="F36" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G36" s="2">
         <v>45397</v>
       </c>
-      <c r="G32" s="2">
-        <v>45397</v>
-      </c>
-      <c r="I32">
-        <v>42</v>
-      </c>
-      <c r="J32">
+      <c r="I36">
+        <v>42</v>
+      </c>
+      <c r="J36">
+        <v>8001</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>126113984</v>
+      </c>
+      <c r="E37">
+        <v>1211</v>
+      </c>
+      <c r="F37" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G37" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I37">
+        <v>42</v>
+      </c>
+      <c r="J37">
+        <v>8001</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>126247661</v>
+      </c>
+      <c r="E38">
+        <v>1211</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I38">
+        <v>42</v>
+      </c>
+      <c r="J38">
+        <v>8001</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>126268537</v>
+      </c>
+      <c r="E39">
+        <v>1211</v>
+      </c>
+      <c r="F39" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G39" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I39">
+        <v>42</v>
+      </c>
+      <c r="J39">
+        <v>8001</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>126332872</v>
+      </c>
+      <c r="E40">
+        <v>1211</v>
+      </c>
+      <c r="F40" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G40" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I40">
+        <v>42</v>
+      </c>
+      <c r="J40">
+        <v>8001</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>126471895</v>
+      </c>
+      <c r="E41">
+        <v>1211</v>
+      </c>
+      <c r="F41" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G41" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I41">
+        <v>42</v>
+      </c>
+      <c r="J41">
+        <v>8001</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>126589532</v>
+      </c>
+      <c r="E42">
+        <v>1211</v>
+      </c>
+      <c r="F42" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G42" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I42">
+        <v>42</v>
+      </c>
+      <c r="J42">
+        <v>8001</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>126661313</v>
+      </c>
+      <c r="E43">
+        <v>1211</v>
+      </c>
+      <c r="F43" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G43" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I43">
+        <v>42</v>
+      </c>
+      <c r="J43">
+        <v>8001</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>126681668</v>
+      </c>
+      <c r="E44">
+        <v>1211</v>
+      </c>
+      <c r="F44" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G44" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I44">
+        <v>42</v>
+      </c>
+      <c r="J44">
+        <v>8001</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>126774137</v>
+      </c>
+      <c r="E45">
+        <v>1211</v>
+      </c>
+      <c r="F45" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G45" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I45">
+        <v>42</v>
+      </c>
+      <c r="J45">
+        <v>8001</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>126825541</v>
+      </c>
+      <c r="E46">
+        <v>1211</v>
+      </c>
+      <c r="F46" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G46" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I46">
+        <v>42</v>
+      </c>
+      <c r="J46">
+        <v>8001</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>126867056</v>
+      </c>
+      <c r="E47">
+        <v>1211</v>
+      </c>
+      <c r="F47" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G47" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I47">
+        <v>42</v>
+      </c>
+      <c r="J47">
+        <v>8001</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>126873688</v>
+      </c>
+      <c r="E48">
+        <v>1211</v>
+      </c>
+      <c r="F48" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G48" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I48">
+        <v>42</v>
+      </c>
+      <c r="J48">
+        <v>8001</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>126884567</v>
+      </c>
+      <c r="E49">
+        <v>1211</v>
+      </c>
+      <c r="F49" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G49" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I49">
+        <v>42</v>
+      </c>
+      <c r="J49">
+        <v>8001</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>126907298</v>
+      </c>
+      <c r="E50">
+        <v>1211</v>
+      </c>
+      <c r="F50" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G50" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I50">
+        <v>42</v>
+      </c>
+      <c r="J50">
+        <v>8001</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>127022913</v>
+      </c>
+      <c r="E51">
+        <v>1211</v>
+      </c>
+      <c r="F51" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G51" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I51">
+        <v>42</v>
+      </c>
+      <c r="J51">
+        <v>8001</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>127153356</v>
+      </c>
+      <c r="E52">
+        <v>1211</v>
+      </c>
+      <c r="F52" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G52" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I52">
+        <v>42</v>
+      </c>
+      <c r="J52">
+        <v>8001</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>127309850</v>
+      </c>
+      <c r="E53">
+        <v>1211</v>
+      </c>
+      <c r="F53" s="2">
+        <v>45393</v>
+      </c>
+      <c r="G53" s="2">
+        <v>45392</v>
+      </c>
+      <c r="I53">
+        <v>42</v>
+      </c>
+      <c r="J53">
+        <v>8021</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>124411489</v>
+      </c>
+      <c r="E54">
+        <v>601</v>
+      </c>
+      <c r="F54" s="2">
+        <v>45384</v>
+      </c>
+      <c r="G54" s="2">
+        <v>45371</v>
+      </c>
+      <c r="I54">
+        <v>42</v>
+      </c>
+      <c r="J54">
+        <v>8017</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>127282661</v>
+      </c>
+      <c r="E55">
+        <v>601</v>
+      </c>
+      <c r="F55" s="2">
+        <v>45398</v>
+      </c>
+      <c r="G55" s="2">
+        <v>45390</v>
+      </c>
+      <c r="I55">
+        <v>42</v>
+      </c>
+      <c r="J55">
+        <v>8001</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>127283043</v>
+      </c>
+      <c r="E56">
+        <v>601</v>
+      </c>
+      <c r="F56" s="2">
+        <v>45390</v>
+      </c>
+      <c r="G56" s="2">
+        <v>45390</v>
+      </c>
+      <c r="I56">
+        <v>42</v>
+      </c>
+      <c r="J56">
+        <v>8004</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>127283250</v>
+      </c>
+      <c r="E57">
+        <v>601</v>
+      </c>
+      <c r="F57" s="2">
+        <v>45390</v>
+      </c>
+      <c r="G57" s="2">
+        <v>45390</v>
+      </c>
+      <c r="I57">
+        <v>42</v>
+      </c>
+      <c r="J57">
+        <v>8004</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>127287098</v>
+      </c>
+      <c r="E58">
+        <v>609</v>
+      </c>
+      <c r="F58" s="2">
+        <v>45390</v>
+      </c>
+      <c r="G58" s="2">
+        <v>45390</v>
+      </c>
+      <c r="I58">
+        <v>42</v>
+      </c>
+      <c r="J58">
+        <v>8004</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>127287421</v>
+      </c>
+      <c r="E59">
+        <v>609</v>
+      </c>
+      <c r="F59" s="2">
+        <v>45390</v>
+      </c>
+      <c r="G59" s="2">
+        <v>45390</v>
+      </c>
+      <c r="I59">
+        <v>42</v>
+      </c>
+      <c r="J59">
+        <v>8004</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>127287790</v>
+      </c>
+      <c r="E60">
+        <v>609</v>
+      </c>
+      <c r="F60" s="2">
+        <v>45390</v>
+      </c>
+      <c r="G60" s="2">
+        <v>45390</v>
+      </c>
+      <c r="I60">
+        <v>42</v>
+      </c>
+      <c r="J60">
+        <v>8004</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>127288009</v>
+      </c>
+      <c r="E61">
+        <v>609</v>
+      </c>
+      <c r="F61" s="2">
+        <v>45390</v>
+      </c>
+      <c r="G61" s="2">
+        <v>45390</v>
+      </c>
+      <c r="I61">
+        <v>42</v>
+      </c>
+      <c r="J61">
+        <v>8004</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>127288242</v>
+      </c>
+      <c r="E62">
+        <v>609</v>
+      </c>
+      <c r="F62" s="2">
+        <v>45390</v>
+      </c>
+      <c r="G62" s="2">
+        <v>45390</v>
+      </c>
+      <c r="I62">
+        <v>42</v>
+      </c>
+      <c r="J62">
+        <v>8004</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>127289224</v>
+      </c>
+      <c r="E63">
+        <v>609</v>
+      </c>
+      <c r="F63" s="2">
+        <v>45390</v>
+      </c>
+      <c r="G63" s="2">
+        <v>45390</v>
+      </c>
+      <c r="I63">
+        <v>42</v>
+      </c>
+      <c r="J63">
+        <v>8004</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>127291450</v>
+      </c>
+      <c r="E64">
+        <v>609</v>
+      </c>
+      <c r="F64" s="2">
+        <v>45390</v>
+      </c>
+      <c r="G64" s="2">
+        <v>45390</v>
+      </c>
+      <c r="I64">
+        <v>42</v>
+      </c>
+      <c r="J64">
+        <v>8004</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>127291621</v>
+      </c>
+      <c r="E65">
+        <v>609</v>
+      </c>
+      <c r="F65" s="2">
+        <v>45390</v>
+      </c>
+      <c r="G65" s="2">
+        <v>45390</v>
+      </c>
+      <c r="I65">
+        <v>42</v>
+      </c>
+      <c r="J65">
+        <v>8004</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>127294708</v>
+      </c>
+      <c r="E66">
+        <v>601</v>
+      </c>
+      <c r="F66" s="2">
+        <v>45391</v>
+      </c>
+      <c r="G66" s="2">
+        <v>45391</v>
+      </c>
+      <c r="I66">
+        <v>42</v>
+      </c>
+      <c r="J66">
+        <v>8004</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>127295952</v>
+      </c>
+      <c r="E67">
+        <v>609</v>
+      </c>
+      <c r="F67" s="2">
+        <v>45391</v>
+      </c>
+      <c r="G67" s="2">
+        <v>45391</v>
+      </c>
+      <c r="I67">
+        <v>42</v>
+      </c>
+      <c r="J67">
+        <v>8004</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>127296975</v>
+      </c>
+      <c r="E68">
+        <v>609</v>
+      </c>
+      <c r="F68" s="2">
+        <v>45391</v>
+      </c>
+      <c r="G68" s="2">
+        <v>45391</v>
+      </c>
+      <c r="I68">
+        <v>42</v>
+      </c>
+      <c r="J68">
+        <v>8004</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>125452848</v>
+      </c>
+      <c r="E69">
+        <v>1211</v>
+      </c>
+      <c r="F69" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G69" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I69">
+        <v>42</v>
+      </c>
+      <c r="J69">
         <v>715</v>
       </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>127381640</v>
+      </c>
+      <c r="E70">
+        <v>1211</v>
+      </c>
+      <c r="F70" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G70" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I70">
+        <v>42</v>
+      </c>
+      <c r="J70">
+        <v>715</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>127382408</v>
+      </c>
+      <c r="E71">
+        <v>1212</v>
+      </c>
+      <c r="F71" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G71" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I71">
+        <v>42</v>
+      </c>
+      <c r="J71">
+        <v>715</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>127383312</v>
+      </c>
+      <c r="E72">
+        <v>1211</v>
+      </c>
+      <c r="F72" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G72" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I72">
+        <v>42</v>
+      </c>
+      <c r="J72">
+        <v>715</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>127383947</v>
+      </c>
+      <c r="E73">
+        <v>1212</v>
+      </c>
+      <c r="F73" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G73" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I73">
+        <v>42</v>
+      </c>
+      <c r="J73">
+        <v>715</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>127384918</v>
+      </c>
+      <c r="E74">
+        <v>1212</v>
+      </c>
+      <c r="F74" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G74" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I74">
+        <v>42</v>
+      </c>
+      <c r="J74">
+        <v>715</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>127385704</v>
+      </c>
+      <c r="E75">
+        <v>1212</v>
+      </c>
+      <c r="F75" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G75" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I75">
+        <v>42</v>
+      </c>
+      <c r="J75">
+        <v>715</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>127386254</v>
+      </c>
+      <c r="E76">
+        <v>1212</v>
+      </c>
+      <c r="F76" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G76" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I76">
+        <v>42</v>
+      </c>
+      <c r="J76">
+        <v>715</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>127387135</v>
+      </c>
+      <c r="E77">
+        <v>1211</v>
+      </c>
+      <c r="F77" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G77" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I77">
+        <v>42</v>
+      </c>
+      <c r="J77">
+        <v>715</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>127387736</v>
+      </c>
+      <c r="E78">
+        <v>1211</v>
+      </c>
+      <c r="F78" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G78" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I78">
+        <v>42</v>
+      </c>
+      <c r="J78">
+        <v>715</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>127388183</v>
+      </c>
+      <c r="E79">
+        <v>1211</v>
+      </c>
+      <c r="F79" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G79" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I79">
+        <v>42</v>
+      </c>
+      <c r="J79">
+        <v>715</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>127388754</v>
+      </c>
+      <c r="E80">
+        <v>1212</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I80">
+        <v>42</v>
+      </c>
+      <c r="J80">
+        <v>715</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>127389615</v>
+      </c>
+      <c r="E81">
+        <v>1212</v>
+      </c>
+      <c r="F81" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G81" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I81">
+        <v>42</v>
+      </c>
+      <c r="J81">
+        <v>715</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>127390143</v>
+      </c>
+      <c r="E82">
+        <v>1211</v>
+      </c>
+      <c r="F82" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G82" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I82">
+        <v>42</v>
+      </c>
+      <c r="J82">
+        <v>715</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>127390259</v>
+      </c>
+      <c r="E83">
+        <v>1212</v>
+      </c>
+      <c r="F83" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G83" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I83">
+        <v>42</v>
+      </c>
+      <c r="J83">
+        <v>715</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>127390896</v>
+      </c>
+      <c r="E84">
+        <v>1212</v>
+      </c>
+      <c r="F84" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G84" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I84">
+        <v>42</v>
+      </c>
+      <c r="J84">
+        <v>715</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>127391627</v>
+      </c>
+      <c r="E85">
+        <v>1212</v>
+      </c>
+      <c r="F85" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G85" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I85">
+        <v>42</v>
+      </c>
+      <c r="J85">
+        <v>715</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>127392192</v>
+      </c>
+      <c r="E86">
+        <v>1211</v>
+      </c>
+      <c r="F86" s="2">
+        <v>45399</v>
+      </c>
+      <c r="G86" s="2">
+        <v>45399</v>
+      </c>
+      <c r="I86">
+        <v>42</v>
+      </c>
+      <c r="J86">
+        <v>715</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>127395539</v>
+      </c>
+      <c r="E87">
+        <v>1211</v>
+      </c>
+      <c r="F87" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G87" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I87">
+        <v>42</v>
+      </c>
+      <c r="J87">
+        <v>715</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>127396118</v>
+      </c>
+      <c r="E88">
+        <v>1212</v>
+      </c>
+      <c r="F88" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G88" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I88">
+        <v>42</v>
+      </c>
+      <c r="J88">
+        <v>715</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>127396205</v>
+      </c>
+      <c r="E89">
+        <v>1211</v>
+      </c>
+      <c r="F89" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G89" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I89">
+        <v>42</v>
+      </c>
+      <c r="J89">
+        <v>715</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>127397821</v>
+      </c>
+      <c r="E90">
+        <v>1212</v>
+      </c>
+      <c r="F90" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G90" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I90">
+        <v>42</v>
+      </c>
+      <c r="J90">
+        <v>715</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>127399742</v>
+      </c>
+      <c r="E91">
+        <v>1212</v>
+      </c>
+      <c r="F91" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G91" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I91">
+        <v>42</v>
+      </c>
+      <c r="J91">
+        <v>715</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>127404994</v>
+      </c>
+      <c r="E92">
+        <v>1211</v>
+      </c>
+      <c r="F92" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G92" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I92">
+        <v>42</v>
+      </c>
+      <c r="J92">
+        <v>715</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>127407474</v>
+      </c>
+      <c r="E93">
+        <v>1211</v>
+      </c>
+      <c r="F93" s="2">
+        <v>45400</v>
+      </c>
+      <c r="G93" s="2">
+        <v>45400</v>
+      </c>
+      <c r="I93">
+        <v>42</v>
+      </c>
+      <c r="J93">
+        <v>715</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
         <v>61</v>
       </c>
     </row>
@@ -9351,31 +11669,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AE0B3D1-10A4-4C18-9231-969E95770290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34167D01-8999-4960-8937-834BFA735D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$71</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q93"/>
+  <dimension ref="A1:Q71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,22 +585,22 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>125658570</v>
+        <v>127368689</v>
       </c>
       <c r="E2">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F2" s="2">
-        <v>45400</v>
+        <v>45398</v>
       </c>
       <c r="G2" s="2">
-        <v>45400</v>
+        <v>45398</v>
       </c>
       <c r="I2">
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -623,22 +623,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>126142913</v>
+        <v>127377274</v>
       </c>
       <c r="E3">
-        <v>2002</v>
+        <v>1211</v>
       </c>
       <c r="F3" s="2">
-        <v>45400</v>
+        <v>45399</v>
       </c>
       <c r="G3" s="2">
-        <v>45400</v>
+        <v>45398</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8004</v>
+        <v>1735</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -661,7 +661,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>127352309</v>
+        <v>127377452</v>
       </c>
       <c r="E4">
         <v>1211</v>
@@ -670,7 +670,7 @@
         <v>45398</v>
       </c>
       <c r="G4" s="2">
-        <v>45397</v>
+        <v>45398</v>
       </c>
       <c r="I4">
         <v>42</v>
@@ -699,16 +699,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>127352673</v>
+        <v>127395260</v>
       </c>
       <c r="E5">
         <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45397</v>
+        <v>45401</v>
       </c>
       <c r="G5" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="I5">
         <v>42</v>
@@ -737,16 +737,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>127355463</v>
+        <v>127401847</v>
       </c>
       <c r="E6">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F6" s="2">
-        <v>45398</v>
+        <v>45400</v>
       </c>
       <c r="G6" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="I6">
         <v>42</v>
@@ -775,16 +775,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>127357498</v>
+        <v>127407764</v>
       </c>
       <c r="E7">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F7" s="2">
-        <v>45397</v>
+        <v>45401</v>
       </c>
       <c r="G7" s="2">
-        <v>45397</v>
+        <v>45400</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -813,22 +813,22 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>127363944</v>
+        <v>123826014</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45397</v>
+        <v>45401</v>
       </c>
       <c r="G8" s="2">
-        <v>45397</v>
+        <v>45401</v>
       </c>
       <c r="I8">
         <v>42</v>
       </c>
       <c r="J8">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -851,22 +851,22 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>127364168</v>
+        <v>123870326</v>
       </c>
       <c r="E9">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F9" s="2">
-        <v>45397</v>
+        <v>45401</v>
       </c>
       <c r="G9" s="2">
-        <v>45397</v>
+        <v>45401</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -889,16 +889,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>123651355</v>
+        <v>123894782</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45400</v>
+        <v>45402</v>
       </c>
       <c r="G10" s="2">
-        <v>45400</v>
+        <v>45399</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -927,16 +927,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>123665058</v>
+        <v>123897883</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="G11" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -965,13 +965,13 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>123755711</v>
+        <v>124061770</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="G12" s="2">
         <v>45399</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>123845664</v>
+        <v>124122242</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="G13" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>124082886</v>
+        <v>124132268</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="G14" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>124103386</v>
+        <v>124262946</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="G15" s="2">
-        <v>45399</v>
+        <v>45398</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>124188182</v>
+        <v>124424827</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="G16" s="2">
-        <v>45397</v>
+        <v>45401</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>124214931</v>
+        <v>124433797</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="G17" s="2">
-        <v>45399</v>
+        <v>45400</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>124403676</v>
+        <v>124474059</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="G18" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>124471306</v>
+        <v>124574627</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45400</v>
+        <v>45402</v>
       </c>
       <c r="G19" s="2">
-        <v>45399</v>
+        <v>45402</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>124505796</v>
+        <v>124652517</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45399</v>
+        <v>45402</v>
       </c>
       <c r="G20" s="2">
-        <v>45399</v>
+        <v>45397</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>124522057</v>
+        <v>124801330</v>
       </c>
       <c r="E21">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F21" s="2">
-        <v>45400</v>
+        <v>45402</v>
       </c>
       <c r="G21" s="2">
-        <v>45399</v>
+        <v>45402</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>124529758</v>
+        <v>124811785</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45400</v>
+        <v>45402</v>
       </c>
       <c r="G22" s="2">
-        <v>45400</v>
+        <v>45402</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1383,16 +1383,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>124586494</v>
+        <v>124881062</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="G23" s="2">
-        <v>45399</v>
+        <v>45400</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1421,16 +1421,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>124678082</v>
+        <v>125194964</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="G24" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1459,16 +1459,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>124866183</v>
+        <v>125199750</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="G25" s="2">
-        <v>45400</v>
+        <v>45399</v>
       </c>
       <c r="I25">
         <v>42</v>
@@ -1497,16 +1497,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>124894979</v>
+        <v>125300357</v>
       </c>
       <c r="E26">
         <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="G26" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="I26">
         <v>42</v>
@@ -1535,13 +1535,13 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>125113290</v>
+        <v>125377517</v>
       </c>
       <c r="E27">
         <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45400</v>
+        <v>45403</v>
       </c>
       <c r="G27" s="2">
         <v>45400</v>
@@ -1573,16 +1573,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>125128912</v>
+        <v>125589369</v>
       </c>
       <c r="E28">
         <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="G28" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="I28">
         <v>42</v>
@@ -1611,16 +1611,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>125178765</v>
+        <v>125652620</v>
       </c>
       <c r="E29">
         <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="G29" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="I29">
         <v>42</v>
@@ -1649,16 +1649,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>125261573</v>
+        <v>126357992</v>
       </c>
       <c r="E30">
         <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="G30" s="2">
-        <v>45400</v>
+        <v>45399</v>
       </c>
       <c r="I30">
         <v>42</v>
@@ -1687,16 +1687,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>125278835</v>
+        <v>126621600</v>
       </c>
       <c r="E31">
         <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="G31" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="I31">
         <v>42</v>
@@ -1725,16 +1725,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>125587828</v>
+        <v>126735524</v>
       </c>
       <c r="E32">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="G32" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="I32">
         <v>42</v>
@@ -1763,16 +1763,16 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>125677370</v>
+        <v>126855184</v>
       </c>
       <c r="E33">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F33" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="G33" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="I33">
         <v>42</v>
@@ -1801,16 +1801,16 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>125678877</v>
+        <v>127342315</v>
       </c>
       <c r="E34">
         <v>1211</v>
       </c>
       <c r="F34" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="G34" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="I34">
         <v>42</v>
@@ -1839,22 +1839,22 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>125838464</v>
+        <v>127309850</v>
       </c>
       <c r="E35">
         <v>1211</v>
       </c>
       <c r="F35" s="2">
-        <v>45400</v>
+        <v>45393</v>
       </c>
       <c r="G35" s="2">
-        <v>45400</v>
+        <v>45392</v>
       </c>
       <c r="I35">
         <v>42</v>
       </c>
       <c r="J35">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>125929785</v>
+        <v>124411489</v>
       </c>
       <c r="E36">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F36" s="2">
-        <v>45399</v>
+        <v>45384</v>
       </c>
       <c r="G36" s="2">
-        <v>45397</v>
+        <v>45371</v>
       </c>
       <c r="I36">
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8001</v>
+        <v>8017</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -1915,22 +1915,22 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>126113984</v>
+        <v>127312459</v>
       </c>
       <c r="E37">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F37" s="2">
-        <v>45400</v>
+        <v>45392</v>
       </c>
       <c r="G37" s="2">
-        <v>45399</v>
+        <v>45392</v>
       </c>
       <c r="I37">
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>126247661</v>
+        <v>127312464</v>
       </c>
       <c r="E38">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F38" s="2">
-        <v>45400</v>
+        <v>45392</v>
       </c>
       <c r="G38" s="2">
-        <v>45400</v>
+        <v>45392</v>
       </c>
       <c r="I38">
         <v>42</v>
       </c>
       <c r="J38">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -1991,22 +1991,22 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>126268537</v>
+        <v>127320000</v>
       </c>
       <c r="E39">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F39" s="2">
-        <v>45400</v>
+        <v>45393</v>
       </c>
       <c r="G39" s="2">
-        <v>45400</v>
+        <v>45393</v>
       </c>
       <c r="I39">
         <v>42</v>
       </c>
       <c r="J39">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>126332872</v>
+        <v>127347280</v>
       </c>
       <c r="E40">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F40" s="2">
-        <v>45399</v>
+        <v>45394</v>
       </c>
       <c r="G40" s="2">
-        <v>45399</v>
+        <v>45394</v>
       </c>
       <c r="I40">
         <v>42</v>
       </c>
       <c r="J40">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2067,22 +2067,22 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>126471895</v>
+        <v>127299521</v>
       </c>
       <c r="E41">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F41" s="2">
-        <v>45400</v>
+        <v>45392</v>
       </c>
       <c r="G41" s="2">
-        <v>45400</v>
+        <v>45392</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8001</v>
+        <v>1117</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>126589532</v>
+        <v>127307303</v>
       </c>
       <c r="E42">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F42" s="2">
-        <v>45399</v>
+        <v>45392</v>
       </c>
       <c r="G42" s="2">
-        <v>45399</v>
+        <v>45392</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2143,22 +2143,22 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>126661313</v>
+        <v>127307339</v>
       </c>
       <c r="E43">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F43" s="2">
-        <v>45399</v>
+        <v>45392</v>
       </c>
       <c r="G43" s="2">
-        <v>45399</v>
+        <v>45392</v>
       </c>
       <c r="I43">
         <v>42</v>
       </c>
       <c r="J43">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>126681668</v>
+        <v>127308657</v>
       </c>
       <c r="E44">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F44" s="2">
-        <v>45400</v>
+        <v>45392</v>
       </c>
       <c r="G44" s="2">
-        <v>45400</v>
+        <v>45392</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2219,22 +2219,22 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>126774137</v>
+        <v>127312127</v>
       </c>
       <c r="E45">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F45" s="2">
-        <v>45400</v>
+        <v>45393</v>
       </c>
       <c r="G45" s="2">
-        <v>45400</v>
+        <v>45393</v>
       </c>
       <c r="I45">
         <v>42</v>
       </c>
       <c r="J45">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>126825541</v>
+        <v>127313376</v>
       </c>
       <c r="E46">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F46" s="2">
-        <v>45399</v>
+        <v>45393</v>
       </c>
       <c r="G46" s="2">
-        <v>45399</v>
+        <v>45393</v>
       </c>
       <c r="I46">
         <v>42</v>
       </c>
       <c r="J46">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2295,22 +2295,22 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>126867056</v>
+        <v>127313525</v>
       </c>
       <c r="E47">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F47" s="2">
-        <v>45400</v>
+        <v>45393</v>
       </c>
       <c r="G47" s="2">
-        <v>45400</v>
+        <v>45393</v>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2333,22 +2333,22 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>126873688</v>
+        <v>127331477</v>
       </c>
       <c r="E48">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F48" s="2">
-        <v>45400</v>
+        <v>45393</v>
       </c>
       <c r="G48" s="2">
-        <v>45400</v>
+        <v>45393</v>
       </c>
       <c r="I48">
         <v>42</v>
       </c>
       <c r="J48">
-        <v>8001</v>
+        <v>8003</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2371,22 +2371,22 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>126884567</v>
+        <v>127333912</v>
       </c>
       <c r="E49">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F49" s="2">
-        <v>45400</v>
+        <v>45394</v>
       </c>
       <c r="G49" s="2">
-        <v>45400</v>
+        <v>45394</v>
       </c>
       <c r="I49">
         <v>42</v>
       </c>
       <c r="J49">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>126907298</v>
+        <v>127338461</v>
       </c>
       <c r="E50">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F50" s="2">
-        <v>45399</v>
+        <v>45394</v>
       </c>
       <c r="G50" s="2">
-        <v>45399</v>
+        <v>45394</v>
       </c>
       <c r="I50">
         <v>42</v>
       </c>
       <c r="J50">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2447,22 +2447,22 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>127022913</v>
+        <v>127344251</v>
       </c>
       <c r="E51">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F51" s="2">
-        <v>45400</v>
+        <v>45394</v>
       </c>
       <c r="G51" s="2">
-        <v>45400</v>
+        <v>45394</v>
       </c>
       <c r="I51">
         <v>42</v>
       </c>
       <c r="J51">
-        <v>8001</v>
+        <v>1117</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2485,22 +2485,22 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>127153356</v>
+        <v>127348773</v>
       </c>
       <c r="E52">
-        <v>1211</v>
+        <v>609</v>
       </c>
       <c r="F52" s="2">
-        <v>45400</v>
+        <v>45394</v>
       </c>
       <c r="G52" s="2">
-        <v>45399</v>
+        <v>45394</v>
       </c>
       <c r="I52">
         <v>42</v>
       </c>
       <c r="J52">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>127309850</v>
+        <v>127411473</v>
       </c>
       <c r="E53">
         <v>1211</v>
       </c>
       <c r="F53" s="2">
-        <v>45393</v>
+        <v>45401</v>
       </c>
       <c r="G53" s="2">
-        <v>45392</v>
+        <v>45401</v>
       </c>
       <c r="I53">
         <v>42</v>
       </c>
       <c r="J53">
-        <v>8021</v>
+        <v>715</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -2561,22 +2561,22 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>124411489</v>
+        <v>127411795</v>
       </c>
       <c r="E54">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F54" s="2">
-        <v>45384</v>
+        <v>45401</v>
       </c>
       <c r="G54" s="2">
-        <v>45371</v>
+        <v>45401</v>
       </c>
       <c r="I54">
         <v>42</v>
       </c>
       <c r="J54">
-        <v>8017</v>
+        <v>715</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -2599,22 +2599,22 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>127282661</v>
+        <v>127412852</v>
       </c>
       <c r="E55">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F55" s="2">
-        <v>45398</v>
+        <v>45401</v>
       </c>
       <c r="G55" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="I55">
         <v>42</v>
       </c>
       <c r="J55">
-        <v>8001</v>
+        <v>715</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -2637,22 +2637,22 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>127283043</v>
+        <v>127413157</v>
       </c>
       <c r="E56">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F56" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="G56" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="I56">
         <v>42</v>
       </c>
       <c r="J56">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -2675,22 +2675,22 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>127283250</v>
+        <v>127413361</v>
       </c>
       <c r="E57">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F57" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="G57" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="I57">
         <v>42</v>
       </c>
       <c r="J57">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -2713,22 +2713,22 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>127287098</v>
+        <v>127413379</v>
       </c>
       <c r="E58">
-        <v>609</v>
+        <v>1212</v>
       </c>
       <c r="F58" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="G58" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="I58">
         <v>42</v>
       </c>
       <c r="J58">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -2751,22 +2751,22 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>127287421</v>
+        <v>127414015</v>
       </c>
       <c r="E59">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F59" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="G59" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="I59">
         <v>42</v>
       </c>
       <c r="J59">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -2789,22 +2789,22 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>127287790</v>
+        <v>127414108</v>
       </c>
       <c r="E60">
-        <v>609</v>
+        <v>1212</v>
       </c>
       <c r="F60" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="G60" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="I60">
         <v>42</v>
       </c>
       <c r="J60">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -2827,22 +2827,22 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>127288009</v>
+        <v>127414329</v>
       </c>
       <c r="E61">
-        <v>609</v>
+        <v>1212</v>
       </c>
       <c r="F61" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="G61" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="I61">
         <v>42</v>
       </c>
       <c r="J61">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -2865,22 +2865,22 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>127288242</v>
+        <v>127415258</v>
       </c>
       <c r="E62">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F62" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="G62" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="I62">
         <v>42</v>
       </c>
       <c r="J62">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -2903,22 +2903,22 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>127289224</v>
+        <v>127415815</v>
       </c>
       <c r="E63">
-        <v>609</v>
+        <v>1212</v>
       </c>
       <c r="F63" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="G63" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="I63">
         <v>42</v>
       </c>
       <c r="J63">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -2941,22 +2941,22 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>127291450</v>
+        <v>127416923</v>
       </c>
       <c r="E64">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F64" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="G64" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="I64">
         <v>42</v>
       </c>
       <c r="J64">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>127291621</v>
+        <v>127416988</v>
       </c>
       <c r="E65">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F65" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="G65" s="2">
-        <v>45390</v>
+        <v>45401</v>
       </c>
       <c r="I65">
         <v>42</v>
       </c>
       <c r="J65">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>127294708</v>
+        <v>127417791</v>
       </c>
       <c r="E66">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F66" s="2">
-        <v>45391</v>
+        <v>45401</v>
       </c>
       <c r="G66" s="2">
-        <v>45391</v>
+        <v>45401</v>
       </c>
       <c r="I66">
         <v>42</v>
       </c>
       <c r="J66">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>127295952</v>
+        <v>127419650</v>
       </c>
       <c r="E67">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F67" s="2">
-        <v>45391</v>
+        <v>45401</v>
       </c>
       <c r="G67" s="2">
-        <v>45391</v>
+        <v>45401</v>
       </c>
       <c r="I67">
         <v>42</v>
       </c>
       <c r="J67">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L67">
         <v>0</v>
@@ -3093,22 +3093,22 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>127296975</v>
+        <v>127420762</v>
       </c>
       <c r="E68">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F68" s="2">
-        <v>45391</v>
+        <v>45401</v>
       </c>
       <c r="G68" s="2">
-        <v>45391</v>
+        <v>45401</v>
       </c>
       <c r="I68">
         <v>42</v>
       </c>
       <c r="J68">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -3131,16 +3131,16 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>125452848</v>
+        <v>127422054</v>
       </c>
       <c r="E69">
         <v>1211</v>
       </c>
       <c r="F69" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="G69" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="I69">
         <v>42</v>
@@ -3169,16 +3169,16 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>127381640</v>
+        <v>127422209</v>
       </c>
       <c r="E70">
         <v>1211</v>
       </c>
       <c r="F70" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="G70" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="I70">
         <v>42</v>
@@ -3207,16 +3207,16 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>127382408</v>
+        <v>127425916</v>
       </c>
       <c r="E71">
         <v>1212</v>
       </c>
       <c r="F71" s="2">
-        <v>45399</v>
+        <v>45403</v>
       </c>
       <c r="G71" s="2">
-        <v>45399</v>
+        <v>45403</v>
       </c>
       <c r="I71">
         <v>42</v>
@@ -3240,842 +3240,6 @@
         <v>0</v>
       </c>
       <c r="Q71">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A72">
-        <v>127383312</v>
-      </c>
-      <c r="E72">
-        <v>1211</v>
-      </c>
-      <c r="F72" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G72" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I72">
-        <v>42</v>
-      </c>
-      <c r="J72">
-        <v>715</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <v>0</v>
-      </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <v>0</v>
-      </c>
-      <c r="P72">
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A73">
-        <v>127383947</v>
-      </c>
-      <c r="E73">
-        <v>1212</v>
-      </c>
-      <c r="F73" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G73" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I73">
-        <v>42</v>
-      </c>
-      <c r="J73">
-        <v>715</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <v>0</v>
-      </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73">
-        <v>0</v>
-      </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A74">
-        <v>127384918</v>
-      </c>
-      <c r="E74">
-        <v>1212</v>
-      </c>
-      <c r="F74" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G74" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I74">
-        <v>42</v>
-      </c>
-      <c r="J74">
-        <v>715</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <v>0</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <v>0</v>
-      </c>
-      <c r="P74">
-        <v>0</v>
-      </c>
-      <c r="Q74">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A75">
-        <v>127385704</v>
-      </c>
-      <c r="E75">
-        <v>1212</v>
-      </c>
-      <c r="F75" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G75" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I75">
-        <v>42</v>
-      </c>
-      <c r="J75">
-        <v>715</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
-      </c>
-      <c r="P75">
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A76">
-        <v>127386254</v>
-      </c>
-      <c r="E76">
-        <v>1212</v>
-      </c>
-      <c r="F76" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G76" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I76">
-        <v>42</v>
-      </c>
-      <c r="J76">
-        <v>715</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76">
-        <v>0</v>
-      </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
-      <c r="O76">
-        <v>0</v>
-      </c>
-      <c r="P76">
-        <v>0</v>
-      </c>
-      <c r="Q76">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A77">
-        <v>127387135</v>
-      </c>
-      <c r="E77">
-        <v>1211</v>
-      </c>
-      <c r="F77" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G77" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I77">
-        <v>42</v>
-      </c>
-      <c r="J77">
-        <v>715</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <v>0</v>
-      </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
-      <c r="O77">
-        <v>0</v>
-      </c>
-      <c r="P77">
-        <v>0</v>
-      </c>
-      <c r="Q77">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A78">
-        <v>127387736</v>
-      </c>
-      <c r="E78">
-        <v>1211</v>
-      </c>
-      <c r="F78" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G78" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I78">
-        <v>42</v>
-      </c>
-      <c r="J78">
-        <v>715</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78">
-        <v>0</v>
-      </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
-      <c r="O78">
-        <v>0</v>
-      </c>
-      <c r="P78">
-        <v>0</v>
-      </c>
-      <c r="Q78">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A79">
-        <v>127388183</v>
-      </c>
-      <c r="E79">
-        <v>1211</v>
-      </c>
-      <c r="F79" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G79" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I79">
-        <v>42</v>
-      </c>
-      <c r="J79">
-        <v>715</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79">
-        <v>0</v>
-      </c>
-      <c r="P79">
-        <v>0</v>
-      </c>
-      <c r="Q79">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A80">
-        <v>127388754</v>
-      </c>
-      <c r="E80">
-        <v>1212</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G80" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I80">
-        <v>42</v>
-      </c>
-      <c r="J80">
-        <v>715</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>0</v>
-      </c>
-      <c r="P80">
-        <v>0</v>
-      </c>
-      <c r="Q80">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A81">
-        <v>127389615</v>
-      </c>
-      <c r="E81">
-        <v>1212</v>
-      </c>
-      <c r="F81" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G81" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I81">
-        <v>42</v>
-      </c>
-      <c r="J81">
-        <v>715</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
-        <v>0</v>
-      </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
-      <c r="O81">
-        <v>0</v>
-      </c>
-      <c r="P81">
-        <v>0</v>
-      </c>
-      <c r="Q81">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A82">
-        <v>127390143</v>
-      </c>
-      <c r="E82">
-        <v>1211</v>
-      </c>
-      <c r="F82" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G82" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I82">
-        <v>42</v>
-      </c>
-      <c r="J82">
-        <v>715</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>0</v>
-      </c>
-      <c r="P82">
-        <v>0</v>
-      </c>
-      <c r="Q82">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A83">
-        <v>127390259</v>
-      </c>
-      <c r="E83">
-        <v>1212</v>
-      </c>
-      <c r="F83" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G83" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I83">
-        <v>42</v>
-      </c>
-      <c r="J83">
-        <v>715</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
-      <c r="O83">
-        <v>0</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
-      <c r="Q83">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A84">
-        <v>127390896</v>
-      </c>
-      <c r="E84">
-        <v>1212</v>
-      </c>
-      <c r="F84" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G84" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I84">
-        <v>42</v>
-      </c>
-      <c r="J84">
-        <v>715</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84">
-        <v>0</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A85">
-        <v>127391627</v>
-      </c>
-      <c r="E85">
-        <v>1212</v>
-      </c>
-      <c r="F85" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G85" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I85">
-        <v>42</v>
-      </c>
-      <c r="J85">
-        <v>715</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
-        <v>0</v>
-      </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>0</v>
-      </c>
-      <c r="P85">
-        <v>0</v>
-      </c>
-      <c r="Q85">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A86">
-        <v>127392192</v>
-      </c>
-      <c r="E86">
-        <v>1211</v>
-      </c>
-      <c r="F86" s="2">
-        <v>45399</v>
-      </c>
-      <c r="G86" s="2">
-        <v>45399</v>
-      </c>
-      <c r="I86">
-        <v>42</v>
-      </c>
-      <c r="J86">
-        <v>715</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86">
-        <v>0</v>
-      </c>
-      <c r="P86">
-        <v>0</v>
-      </c>
-      <c r="Q86">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A87">
-        <v>127395539</v>
-      </c>
-      <c r="E87">
-        <v>1211</v>
-      </c>
-      <c r="F87" s="2">
-        <v>45400</v>
-      </c>
-      <c r="G87" s="2">
-        <v>45400</v>
-      </c>
-      <c r="I87">
-        <v>42</v>
-      </c>
-      <c r="J87">
-        <v>715</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
-      <c r="M87">
-        <v>0</v>
-      </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
-      <c r="O87">
-        <v>0</v>
-      </c>
-      <c r="P87">
-        <v>0</v>
-      </c>
-      <c r="Q87">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A88">
-        <v>127396118</v>
-      </c>
-      <c r="E88">
-        <v>1212</v>
-      </c>
-      <c r="F88" s="2">
-        <v>45400</v>
-      </c>
-      <c r="G88" s="2">
-        <v>45400</v>
-      </c>
-      <c r="I88">
-        <v>42</v>
-      </c>
-      <c r="J88">
-        <v>715</v>
-      </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88">
-        <v>0</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88">
-        <v>0</v>
-      </c>
-      <c r="P88">
-        <v>0</v>
-      </c>
-      <c r="Q88">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A89">
-        <v>127396205</v>
-      </c>
-      <c r="E89">
-        <v>1211</v>
-      </c>
-      <c r="F89" s="2">
-        <v>45400</v>
-      </c>
-      <c r="G89" s="2">
-        <v>45400</v>
-      </c>
-      <c r="I89">
-        <v>42</v>
-      </c>
-      <c r="J89">
-        <v>715</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
-        <v>0</v>
-      </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <v>0</v>
-      </c>
-      <c r="P89">
-        <v>0</v>
-      </c>
-      <c r="Q89">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A90">
-        <v>127397821</v>
-      </c>
-      <c r="E90">
-        <v>1212</v>
-      </c>
-      <c r="F90" s="2">
-        <v>45400</v>
-      </c>
-      <c r="G90" s="2">
-        <v>45400</v>
-      </c>
-      <c r="I90">
-        <v>42</v>
-      </c>
-      <c r="J90">
-        <v>715</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A91">
-        <v>127399742</v>
-      </c>
-      <c r="E91">
-        <v>1212</v>
-      </c>
-      <c r="F91" s="2">
-        <v>45400</v>
-      </c>
-      <c r="G91" s="2">
-        <v>45400</v>
-      </c>
-      <c r="I91">
-        <v>42</v>
-      </c>
-      <c r="J91">
-        <v>715</v>
-      </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="M91">
-        <v>0</v>
-      </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
-      <c r="O91">
-        <v>0</v>
-      </c>
-      <c r="P91">
-        <v>0</v>
-      </c>
-      <c r="Q91">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A92">
-        <v>127404994</v>
-      </c>
-      <c r="E92">
-        <v>1211</v>
-      </c>
-      <c r="F92" s="2">
-        <v>45400</v>
-      </c>
-      <c r="G92" s="2">
-        <v>45400</v>
-      </c>
-      <c r="I92">
-        <v>42</v>
-      </c>
-      <c r="J92">
-        <v>715</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
-        <v>0</v>
-      </c>
-      <c r="N92">
-        <v>0</v>
-      </c>
-      <c r="O92">
-        <v>0</v>
-      </c>
-      <c r="P92">
-        <v>0</v>
-      </c>
-      <c r="Q92">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A93">
-        <v>127407474</v>
-      </c>
-      <c r="E93">
-        <v>1211</v>
-      </c>
-      <c r="F93" s="2">
-        <v>45400</v>
-      </c>
-      <c r="G93" s="2">
-        <v>45400</v>
-      </c>
-      <c r="I93">
-        <v>42</v>
-      </c>
-      <c r="J93">
-        <v>715</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
-        <v>0</v>
-      </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
-      <c r="O93">
-        <v>0</v>
-      </c>
-      <c r="P93">
-        <v>0</v>
-      </c>
-      <c r="Q93">
         <v>61</v>
       </c>
     </row>
@@ -11669,31 +10833,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34167D01-8999-4960-8937-834BFA735D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDE97EA-B99A-4E82-9B7D-2F79A19160E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,16 +585,16 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>127368689</v>
+        <v>127410111</v>
       </c>
       <c r="E2">
         <v>1211</v>
       </c>
       <c r="F2" s="2">
-        <v>45398</v>
+        <v>45401</v>
       </c>
       <c r="G2" s="2">
-        <v>45398</v>
+        <v>45401</v>
       </c>
       <c r="I2">
         <v>42</v>
@@ -623,16 +623,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>127377274</v>
+        <v>127411415</v>
       </c>
       <c r="E3">
         <v>1211</v>
       </c>
       <c r="F3" s="2">
-        <v>45399</v>
+        <v>45401</v>
       </c>
       <c r="G3" s="2">
-        <v>45398</v>
+        <v>45401</v>
       </c>
       <c r="I3">
         <v>42</v>
@@ -661,16 +661,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>127377452</v>
+        <v>127414642</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45398</v>
+        <v>45402</v>
       </c>
       <c r="G4" s="2">
-        <v>45398</v>
+        <v>45401</v>
       </c>
       <c r="I4">
         <v>42</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>127395260</v>
+        <v>127416978</v>
       </c>
       <c r="E5">
         <v>1211</v>
@@ -708,7 +708,7 @@
         <v>45401</v>
       </c>
       <c r="G5" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="I5">
         <v>42</v>
@@ -737,16 +737,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>127401847</v>
+        <v>127417589</v>
       </c>
       <c r="E6">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="G6" s="2">
-        <v>45400</v>
+        <v>45401</v>
       </c>
       <c r="I6">
         <v>42</v>
@@ -775,16 +775,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>127407764</v>
+        <v>127420089</v>
       </c>
       <c r="E7">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F7" s="2">
+        <v>45402</v>
+      </c>
+      <c r="G7" s="2">
         <v>45401</v>
-      </c>
-      <c r="G7" s="2">
-        <v>45400</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -813,7 +813,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>123826014</v>
+        <v>127421064</v>
       </c>
       <c r="E8">
         <v>1211</v>
@@ -828,7 +828,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -851,16 +851,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>123870326</v>
+        <v>123613027</v>
       </c>
       <c r="E9">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G9" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -889,16 +889,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>123894782</v>
+        <v>123666597</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45402</v>
+        <v>45404</v>
       </c>
       <c r="G10" s="2">
-        <v>45399</v>
+        <v>45404</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -927,16 +927,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>123897883</v>
+        <v>123686158</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G11" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -965,13 +965,13 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>124061770</v>
+        <v>123757259</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G12" s="2">
         <v>45399</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>124122242</v>
+        <v>123962354</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G13" s="2">
-        <v>45401</v>
+        <v>45399</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>124132268</v>
+        <v>124327675</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G14" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>124262946</v>
+        <v>124447500</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G15" s="2">
-        <v>45398</v>
+        <v>45404</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>124424827</v>
+        <v>124763351</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G16" s="2">
-        <v>45401</v>
+        <v>45402</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>124433797</v>
+        <v>125001981</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G17" s="2">
-        <v>45400</v>
+        <v>45398</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>124474059</v>
+        <v>125057327</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G18" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>124574627</v>
+        <v>125126506</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45402</v>
+        <v>45404</v>
       </c>
       <c r="G19" s="2">
-        <v>45402</v>
+        <v>45404</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>124652517</v>
+        <v>125253827</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45402</v>
+        <v>45404</v>
       </c>
       <c r="G20" s="2">
-        <v>45397</v>
+        <v>45401</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>124801330</v>
+        <v>125483027</v>
       </c>
       <c r="E21">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45402</v>
+        <v>45404</v>
       </c>
       <c r="G21" s="2">
-        <v>45402</v>
+        <v>45398</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>124811785</v>
+        <v>125571866</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45402</v>
+        <v>45404</v>
       </c>
       <c r="G22" s="2">
-        <v>45402</v>
+        <v>45400</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1383,16 +1383,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>124881062</v>
+        <v>125734972</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G23" s="2">
-        <v>45400</v>
+        <v>45404</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1421,16 +1421,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>125194964</v>
+        <v>126055987</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G24" s="2">
-        <v>45401</v>
+        <v>45400</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1459,16 +1459,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>125199750</v>
+        <v>126146917</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
+        <v>45404</v>
+      </c>
+      <c r="G25" s="2">
         <v>45401</v>
-      </c>
-      <c r="G25" s="2">
-        <v>45399</v>
       </c>
       <c r="I25">
         <v>42</v>
@@ -1497,16 +1497,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>125300357</v>
+        <v>126166318</v>
       </c>
       <c r="E26">
         <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G26" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="I26">
         <v>42</v>
@@ -1535,16 +1535,16 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>125377517</v>
+        <v>126198634</v>
       </c>
       <c r="E27">
         <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45403</v>
+        <v>45404</v>
       </c>
       <c r="G27" s="2">
-        <v>45400</v>
+        <v>45404</v>
       </c>
       <c r="I27">
         <v>42</v>
@@ -1573,16 +1573,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>125589369</v>
+        <v>126209205</v>
       </c>
       <c r="E28">
         <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G28" s="2">
-        <v>45401</v>
+        <v>45400</v>
       </c>
       <c r="I28">
         <v>42</v>
@@ -1611,16 +1611,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>125652620</v>
+        <v>126346386</v>
       </c>
       <c r="E29">
         <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G29" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="I29">
         <v>42</v>
@@ -1649,16 +1649,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>126357992</v>
+        <v>126450740</v>
       </c>
       <c r="E30">
         <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G30" s="2">
-        <v>45399</v>
+        <v>45404</v>
       </c>
       <c r="I30">
         <v>42</v>
@@ -1687,16 +1687,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>126621600</v>
+        <v>126451516</v>
       </c>
       <c r="E31">
         <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G31" s="2">
-        <v>45401</v>
+        <v>45397</v>
       </c>
       <c r="I31">
         <v>42</v>
@@ -1725,16 +1725,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>126735524</v>
+        <v>126533656</v>
       </c>
       <c r="E32">
         <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G32" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="I32">
         <v>42</v>
@@ -1763,13 +1763,13 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>126855184</v>
+        <v>126643864</v>
       </c>
       <c r="E33">
         <v>1211</v>
       </c>
       <c r="F33" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G33" s="2">
         <v>45401</v>
@@ -1801,16 +1801,16 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>127342315</v>
+        <v>126929994</v>
       </c>
       <c r="E34">
         <v>1211</v>
       </c>
       <c r="F34" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G34" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="I34">
         <v>42</v>
@@ -1839,22 +1839,22 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>127309850</v>
+        <v>127093956</v>
       </c>
       <c r="E35">
         <v>1211</v>
       </c>
       <c r="F35" s="2">
-        <v>45393</v>
+        <v>45404</v>
       </c>
       <c r="G35" s="2">
-        <v>45392</v>
+        <v>45404</v>
       </c>
       <c r="I35">
         <v>42</v>
       </c>
       <c r="J35">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>124411489</v>
+        <v>127100703</v>
       </c>
       <c r="E36">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F36" s="2">
-        <v>45384</v>
+        <v>45404</v>
       </c>
       <c r="G36" s="2">
-        <v>45371</v>
+        <v>45401</v>
       </c>
       <c r="I36">
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -1915,22 +1915,22 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>127312459</v>
+        <v>127135075</v>
       </c>
       <c r="E37">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F37" s="2">
-        <v>45392</v>
+        <v>45404</v>
       </c>
       <c r="G37" s="2">
-        <v>45392</v>
+        <v>45404</v>
       </c>
       <c r="I37">
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>127312464</v>
+        <v>127138722</v>
       </c>
       <c r="E38">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>45392</v>
+        <v>45404</v>
       </c>
       <c r="G38" s="2">
-        <v>45392</v>
+        <v>45404</v>
       </c>
       <c r="I38">
         <v>42</v>
       </c>
       <c r="J38">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -1991,22 +1991,22 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>127320000</v>
+        <v>127212283</v>
       </c>
       <c r="E39">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F39" s="2">
-        <v>45393</v>
+        <v>45404</v>
       </c>
       <c r="G39" s="2">
-        <v>45393</v>
+        <v>45404</v>
       </c>
       <c r="I39">
         <v>42</v>
       </c>
       <c r="J39">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>127347280</v>
+        <v>127281598</v>
       </c>
       <c r="E40">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F40" s="2">
-        <v>45394</v>
+        <v>45404</v>
       </c>
       <c r="G40" s="2">
-        <v>45394</v>
+        <v>45402</v>
       </c>
       <c r="I40">
         <v>42</v>
       </c>
       <c r="J40">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2067,22 +2067,22 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>127299521</v>
+        <v>127282165</v>
       </c>
       <c r="E41">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F41" s="2">
-        <v>45392</v>
+        <v>45404</v>
       </c>
       <c r="G41" s="2">
-        <v>45392</v>
+        <v>45404</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>1117</v>
+        <v>8001</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>127307303</v>
+        <v>127397269</v>
       </c>
       <c r="E42">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F42" s="2">
-        <v>45392</v>
+        <v>45404</v>
       </c>
       <c r="G42" s="2">
-        <v>45392</v>
+        <v>45404</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2143,22 +2143,22 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>127307339</v>
+        <v>110074933</v>
       </c>
       <c r="E43">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F43" s="2">
-        <v>45392</v>
+        <v>43453</v>
       </c>
       <c r="G43" s="2">
-        <v>45392</v>
+        <v>43441</v>
       </c>
       <c r="I43">
         <v>42</v>
       </c>
       <c r="J43">
-        <v>8004</v>
+        <v>8023</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>127308657</v>
+        <v>123058958</v>
       </c>
       <c r="E44">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F44" s="2">
-        <v>45392</v>
+        <v>44995</v>
       </c>
       <c r="G44" s="2">
-        <v>45392</v>
+        <v>44993</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2219,22 +2219,22 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>127312127</v>
+        <v>127309850</v>
       </c>
       <c r="E45">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F45" s="2">
         <v>45393</v>
       </c>
       <c r="G45" s="2">
-        <v>45393</v>
+        <v>45392</v>
       </c>
       <c r="I45">
         <v>42</v>
       </c>
       <c r="J45">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>127313376</v>
+        <v>124411489</v>
       </c>
       <c r="E46">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F46" s="2">
-        <v>45393</v>
+        <v>45384</v>
       </c>
       <c r="G46" s="2">
-        <v>45393</v>
+        <v>45371</v>
       </c>
       <c r="I46">
         <v>42</v>
       </c>
       <c r="J46">
-        <v>8004</v>
+        <v>8017</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2295,22 +2295,22 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>127313525</v>
+        <v>126954503</v>
       </c>
       <c r="E47">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F47" s="2">
-        <v>45393</v>
+        <v>45378</v>
       </c>
       <c r="G47" s="2">
-        <v>45393</v>
+        <v>45378</v>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>8004</v>
+        <v>8017</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2333,22 +2333,22 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>127331477</v>
+        <v>109403368</v>
       </c>
       <c r="E48">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F48" s="2">
-        <v>45393</v>
+        <v>43346</v>
       </c>
       <c r="G48" s="2">
-        <v>45393</v>
+        <v>43346</v>
       </c>
       <c r="I48">
         <v>42</v>
       </c>
       <c r="J48">
-        <v>8003</v>
+        <v>715</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2371,22 +2371,22 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>127333912</v>
+        <v>109455583</v>
       </c>
       <c r="E49">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F49" s="2">
-        <v>45394</v>
+        <v>43354</v>
       </c>
       <c r="G49" s="2">
-        <v>45394</v>
+        <v>43354</v>
       </c>
       <c r="I49">
         <v>42</v>
       </c>
       <c r="J49">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>127338461</v>
+        <v>109707680</v>
       </c>
       <c r="E50">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F50" s="2">
-        <v>45394</v>
+        <v>43396</v>
       </c>
       <c r="G50" s="2">
-        <v>45394</v>
+        <v>43396</v>
       </c>
       <c r="I50">
         <v>42</v>
       </c>
       <c r="J50">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2447,22 +2447,22 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>127344251</v>
+        <v>113706291</v>
       </c>
       <c r="E51">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F51" s="2">
-        <v>45394</v>
+        <v>43945</v>
       </c>
       <c r="G51" s="2">
-        <v>45394</v>
+        <v>43945</v>
       </c>
       <c r="I51">
         <v>42</v>
       </c>
       <c r="J51">
-        <v>1117</v>
+        <v>715</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2485,22 +2485,22 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>127348773</v>
+        <v>114296869</v>
       </c>
       <c r="E52">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F52" s="2">
-        <v>45394</v>
+        <v>44057</v>
       </c>
       <c r="G52" s="2">
-        <v>45394</v>
+        <v>44057</v>
       </c>
       <c r="I52">
         <v>42</v>
       </c>
       <c r="J52">
-        <v>8004</v>
+        <v>715</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -2523,16 +2523,16 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>127411473</v>
+        <v>114763565</v>
       </c>
       <c r="E53">
         <v>1211</v>
       </c>
       <c r="F53" s="2">
-        <v>45401</v>
+        <v>44156</v>
       </c>
       <c r="G53" s="2">
-        <v>45401</v>
+        <v>44153</v>
       </c>
       <c r="I53">
         <v>42</v>
@@ -2561,16 +2561,16 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>127411795</v>
+        <v>114852173</v>
       </c>
       <c r="E54">
         <v>1211</v>
       </c>
       <c r="F54" s="2">
-        <v>45401</v>
+        <v>44171</v>
       </c>
       <c r="G54" s="2">
-        <v>45401</v>
+        <v>44168</v>
       </c>
       <c r="I54">
         <v>42</v>
@@ -2599,16 +2599,16 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>127412852</v>
+        <v>127427768</v>
       </c>
       <c r="E55">
         <v>1211</v>
       </c>
       <c r="F55" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G55" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="I55">
         <v>42</v>
@@ -2637,16 +2637,16 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>127413157</v>
+        <v>127431616</v>
       </c>
       <c r="E56">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F56" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G56" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="I56">
         <v>42</v>
@@ -2675,16 +2675,16 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>127413361</v>
+        <v>127431989</v>
       </c>
       <c r="E57">
         <v>1211</v>
       </c>
       <c r="F57" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G57" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="I57">
         <v>42</v>
@@ -2713,16 +2713,16 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>127413379</v>
+        <v>127435418</v>
       </c>
       <c r="E58">
         <v>1212</v>
       </c>
       <c r="F58" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G58" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="I58">
         <v>42</v>
@@ -2751,16 +2751,16 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>127414015</v>
+        <v>127438479</v>
       </c>
       <c r="E59">
         <v>1211</v>
       </c>
       <c r="F59" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="G59" s="2">
-        <v>45401</v>
+        <v>45404</v>
       </c>
       <c r="I59">
         <v>42</v>
@@ -2784,462 +2784,6 @@
         <v>0</v>
       </c>
       <c r="Q59">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A60">
-        <v>127414108</v>
-      </c>
-      <c r="E60">
-        <v>1212</v>
-      </c>
-      <c r="F60" s="2">
-        <v>45401</v>
-      </c>
-      <c r="G60" s="2">
-        <v>45401</v>
-      </c>
-      <c r="I60">
-        <v>42</v>
-      </c>
-      <c r="J60">
-        <v>715</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
-        <v>0</v>
-      </c>
-      <c r="P60">
-        <v>0</v>
-      </c>
-      <c r="Q60">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A61">
-        <v>127414329</v>
-      </c>
-      <c r="E61">
-        <v>1212</v>
-      </c>
-      <c r="F61" s="2">
-        <v>45401</v>
-      </c>
-      <c r="G61" s="2">
-        <v>45401</v>
-      </c>
-      <c r="I61">
-        <v>42</v>
-      </c>
-      <c r="J61">
-        <v>715</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>0</v>
-      </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>127415258</v>
-      </c>
-      <c r="E62">
-        <v>1211</v>
-      </c>
-      <c r="F62" s="2">
-        <v>45401</v>
-      </c>
-      <c r="G62" s="2">
-        <v>45401</v>
-      </c>
-      <c r="I62">
-        <v>42</v>
-      </c>
-      <c r="J62">
-        <v>715</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A63">
-        <v>127415815</v>
-      </c>
-      <c r="E63">
-        <v>1212</v>
-      </c>
-      <c r="F63" s="2">
-        <v>45401</v>
-      </c>
-      <c r="G63" s="2">
-        <v>45401</v>
-      </c>
-      <c r="I63">
-        <v>42</v>
-      </c>
-      <c r="J63">
-        <v>715</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A64">
-        <v>127416923</v>
-      </c>
-      <c r="E64">
-        <v>1211</v>
-      </c>
-      <c r="F64" s="2">
-        <v>45401</v>
-      </c>
-      <c r="G64" s="2">
-        <v>45401</v>
-      </c>
-      <c r="I64">
-        <v>42</v>
-      </c>
-      <c r="J64">
-        <v>715</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A65">
-        <v>127416988</v>
-      </c>
-      <c r="E65">
-        <v>1211</v>
-      </c>
-      <c r="F65" s="2">
-        <v>45401</v>
-      </c>
-      <c r="G65" s="2">
-        <v>45401</v>
-      </c>
-      <c r="I65">
-        <v>42</v>
-      </c>
-      <c r="J65">
-        <v>715</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A66">
-        <v>127417791</v>
-      </c>
-      <c r="E66">
-        <v>1211</v>
-      </c>
-      <c r="F66" s="2">
-        <v>45401</v>
-      </c>
-      <c r="G66" s="2">
-        <v>45401</v>
-      </c>
-      <c r="I66">
-        <v>42</v>
-      </c>
-      <c r="J66">
-        <v>715</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>0</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A67">
-        <v>127419650</v>
-      </c>
-      <c r="E67">
-        <v>1211</v>
-      </c>
-      <c r="F67" s="2">
-        <v>45401</v>
-      </c>
-      <c r="G67" s="2">
-        <v>45401</v>
-      </c>
-      <c r="I67">
-        <v>42</v>
-      </c>
-      <c r="J67">
-        <v>715</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A68">
-        <v>127420762</v>
-      </c>
-      <c r="E68">
-        <v>1211</v>
-      </c>
-      <c r="F68" s="2">
-        <v>45401</v>
-      </c>
-      <c r="G68" s="2">
-        <v>45401</v>
-      </c>
-      <c r="I68">
-        <v>42</v>
-      </c>
-      <c r="J68">
-        <v>715</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A69">
-        <v>127422054</v>
-      </c>
-      <c r="E69">
-        <v>1211</v>
-      </c>
-      <c r="F69" s="2">
-        <v>45401</v>
-      </c>
-      <c r="G69" s="2">
-        <v>45401</v>
-      </c>
-      <c r="I69">
-        <v>42</v>
-      </c>
-      <c r="J69">
-        <v>715</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>127422209</v>
-      </c>
-      <c r="E70">
-        <v>1211</v>
-      </c>
-      <c r="F70" s="2">
-        <v>45401</v>
-      </c>
-      <c r="G70" s="2">
-        <v>45401</v>
-      </c>
-      <c r="I70">
-        <v>42</v>
-      </c>
-      <c r="J70">
-        <v>715</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>0</v>
-      </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A71">
-        <v>127425916</v>
-      </c>
-      <c r="E71">
-        <v>1212</v>
-      </c>
-      <c r="F71" s="2">
-        <v>45403</v>
-      </c>
-      <c r="G71" s="2">
-        <v>45403</v>
-      </c>
-      <c r="I71">
-        <v>42</v>
-      </c>
-      <c r="J71">
-        <v>715</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
         <v>61</v>
       </c>
     </row>
@@ -10833,31 +10377,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AF83B1-644C-4B78-ACD0-D2BB46069C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11871C0A-D4A6-4153-9F93-F348ABEEA517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiel" sheetId="28" r:id="rId1"/>
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$93</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,18 +507,18 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Q93"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
@@ -526,11 +526,11 @@
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,9 +583,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>124634633</v>
+        <v>127504158</v>
       </c>
       <c r="E2">
         <v>1211</v>
@@ -600,7 +600,7 @@
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -621,9 +621,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>124944830</v>
+        <v>127507143</v>
       </c>
       <c r="E3">
         <v>1212</v>
@@ -638,7 +638,7 @@
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -659,12 +659,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>125293161</v>
+        <v>127512143</v>
       </c>
       <c r="E4">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F4" s="2">
         <v>45411</v>
@@ -676,7 +676,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -697,12 +697,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>125502295</v>
+        <v>127514750</v>
       </c>
       <c r="E5">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F5" s="2">
         <v>45411</v>
@@ -714,7 +714,7 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -735,18 +735,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>125563177</v>
+        <v>123769917</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G6" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="I6">
         <v>42</v>
@@ -773,15 +773,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>125932968</v>
+        <v>123886393</v>
       </c>
       <c r="E7">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G7" s="2">
         <v>45411</v>
@@ -811,18 +811,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>126026943</v>
+        <v>123934492</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G8" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="I8">
         <v>42</v>
@@ -849,18 +849,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>126154897</v>
+        <v>124005068</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="G9" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -887,18 +887,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>126369052</v>
+        <v>124270935</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G10" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -925,18 +925,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>126596974</v>
+        <v>124409962</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G11" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -963,18 +963,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>126600033</v>
+        <v>124449648</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G12" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1001,18 +1001,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>126943318</v>
+        <v>124602882</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G13" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1039,18 +1039,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>127069799</v>
+        <v>124743039</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G14" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1077,18 +1077,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>127198970</v>
+        <v>124769075</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G15" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1115,18 +1115,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>127386285</v>
+        <v>124849715</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45408</v>
+        <v>45414</v>
       </c>
       <c r="G16" s="2">
-        <v>45399</v>
+        <v>45414</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1153,24 +1153,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>127472186</v>
+        <v>124854860</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45408</v>
+        <v>45412</v>
       </c>
       <c r="G17" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="I17">
         <v>42</v>
       </c>
       <c r="J17">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1191,24 +1191,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>126954503</v>
+        <v>124897328</v>
       </c>
       <c r="E18">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45378</v>
+        <v>45414</v>
       </c>
       <c r="G18" s="2">
-        <v>45378</v>
+        <v>45414</v>
       </c>
       <c r="I18">
         <v>42</v>
       </c>
       <c r="J18">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1229,24 +1229,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>127473991</v>
+        <v>125012611</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="G19" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="I19">
         <v>42</v>
       </c>
       <c r="J19">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1267,24 +1267,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>127474589</v>
+        <v>125181637</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="G20" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="I20">
         <v>42</v>
       </c>
       <c r="J20">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1305,24 +1305,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>127476293</v>
+        <v>125193787</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="G21" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="I21">
         <v>42</v>
       </c>
       <c r="J21">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1343,24 +1343,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>127478936</v>
+        <v>125200319</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45407</v>
+        <v>45414</v>
       </c>
       <c r="G22" s="2">
-        <v>45407</v>
+        <v>45414</v>
       </c>
       <c r="I22">
         <v>42</v>
       </c>
       <c r="J22">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1381,24 +1381,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>127479267</v>
+        <v>125203365</v>
       </c>
       <c r="E23">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="G23" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="I23">
         <v>42</v>
       </c>
       <c r="J23">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1419,24 +1419,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>127479485</v>
+        <v>125258579</v>
       </c>
       <c r="E24">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45407</v>
+        <v>45414</v>
       </c>
       <c r="G24" s="2">
-        <v>45407</v>
+        <v>45414</v>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1457,24 +1457,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>127480035</v>
+        <v>125307304</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="G25" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="I25">
         <v>42</v>
       </c>
       <c r="J25">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1495,24 +1495,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>127480915</v>
+        <v>125495976</v>
       </c>
       <c r="E26">
         <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45407</v>
+        <v>45414</v>
       </c>
       <c r="G26" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="I26">
         <v>42</v>
       </c>
       <c r="J26">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1533,24 +1533,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>127481581</v>
+        <v>125788104</v>
       </c>
       <c r="E27">
         <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="G27" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="I27">
         <v>42</v>
       </c>
       <c r="J27">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1571,24 +1571,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>127482007</v>
+        <v>125888553</v>
       </c>
       <c r="E28">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F28" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="G28" s="2">
-        <v>45407</v>
+        <v>45412</v>
       </c>
       <c r="I28">
         <v>42</v>
       </c>
       <c r="J28">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -1609,24 +1609,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>127491086</v>
+        <v>126083147</v>
       </c>
       <c r="E29">
         <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45408</v>
+        <v>45414</v>
       </c>
       <c r="G29" s="2">
-        <v>45408</v>
+        <v>45411</v>
       </c>
       <c r="I29">
         <v>42</v>
       </c>
       <c r="J29">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -1647,24 +1647,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>127492992</v>
+        <v>126096321</v>
       </c>
       <c r="E30">
         <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45408</v>
+        <v>45414</v>
       </c>
       <c r="G30" s="2">
-        <v>45408</v>
+        <v>45412</v>
       </c>
       <c r="I30">
         <v>42</v>
       </c>
       <c r="J30">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1685,24 +1685,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>127496547</v>
+        <v>126116510</v>
       </c>
       <c r="E31">
         <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45408</v>
+        <v>45414</v>
       </c>
       <c r="G31" s="2">
-        <v>45408</v>
+        <v>45414</v>
       </c>
       <c r="I31">
         <v>42</v>
       </c>
       <c r="J31">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -1723,24 +1723,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>127496783</v>
+        <v>126170466</v>
       </c>
       <c r="E32">
         <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>45408</v>
+        <v>45414</v>
       </c>
       <c r="G32" s="2">
-        <v>45408</v>
+        <v>45414</v>
       </c>
       <c r="I32">
         <v>42</v>
       </c>
       <c r="J32">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -1761,24 +1761,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>127505791</v>
+        <v>126174137</v>
       </c>
       <c r="E33">
         <v>1211</v>
       </c>
       <c r="F33" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G33" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="I33">
         <v>42</v>
       </c>
       <c r="J33">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -1799,24 +1799,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>127506001</v>
+        <v>126308525</v>
       </c>
       <c r="E34">
         <v>1211</v>
       </c>
       <c r="F34" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G34" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="I34">
         <v>42</v>
       </c>
       <c r="J34">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -1837,24 +1837,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>127506100</v>
+        <v>126332089</v>
       </c>
       <c r="E35">
         <v>1211</v>
       </c>
       <c r="F35" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="G35" s="2">
-        <v>45411</v>
+        <v>45408</v>
       </c>
       <c r="I35">
         <v>42</v>
       </c>
       <c r="J35">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -1875,24 +1875,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>127506321</v>
+        <v>126434242</v>
       </c>
       <c r="E36">
         <v>1211</v>
       </c>
       <c r="F36" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G36" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="I36">
         <v>42</v>
       </c>
       <c r="J36">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -1913,24 +1913,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>127506470</v>
+        <v>126516958</v>
       </c>
       <c r="E37">
         <v>1211</v>
       </c>
       <c r="F37" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G37" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="I37">
         <v>42</v>
       </c>
       <c r="J37">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -1951,24 +1951,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>127506610</v>
+        <v>126559351</v>
       </c>
       <c r="E38">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="G38" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I38">
         <v>42</v>
       </c>
       <c r="J38">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -1989,24 +1989,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>127507247</v>
+        <v>126638467</v>
       </c>
       <c r="E39">
         <v>1211</v>
       </c>
       <c r="F39" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="G39" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I39">
         <v>42</v>
       </c>
       <c r="J39">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2027,24 +2027,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>127507329</v>
+        <v>126699676</v>
       </c>
       <c r="E40">
         <v>1211</v>
       </c>
       <c r="F40" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="G40" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I40">
         <v>42</v>
       </c>
       <c r="J40">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2065,24 +2065,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>127507932</v>
+        <v>126734568</v>
       </c>
       <c r="E41">
         <v>1211</v>
       </c>
       <c r="F41" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="G41" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2103,24 +2103,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>127508811</v>
+        <v>126776245</v>
       </c>
       <c r="E42">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F42" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="G42" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2141,24 +2141,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>127509227</v>
+        <v>126852653</v>
       </c>
       <c r="E43">
         <v>1211</v>
       </c>
       <c r="F43" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G43" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="I43">
         <v>42</v>
       </c>
       <c r="J43">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2179,24 +2179,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>127509797</v>
+        <v>126917817</v>
       </c>
       <c r="E44">
         <v>1211</v>
       </c>
       <c r="F44" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="G44" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2217,24 +2217,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>127510715</v>
+        <v>127024637</v>
       </c>
       <c r="E45">
         <v>1211</v>
       </c>
       <c r="F45" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="G45" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I45">
         <v>42</v>
       </c>
       <c r="J45">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2255,24 +2255,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>127511581</v>
+        <v>127053596</v>
       </c>
       <c r="E46">
         <v>1211</v>
       </c>
       <c r="F46" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G46" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="I46">
         <v>42</v>
       </c>
       <c r="J46">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2293,24 +2293,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>127514600</v>
+        <v>127092522</v>
       </c>
       <c r="E47">
         <v>1211</v>
       </c>
       <c r="F47" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="G47" s="2">
-        <v>45411</v>
+        <v>45414</v>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2331,9 +2331,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>127516546</v>
+        <v>127104328</v>
       </c>
       <c r="E48">
         <v>1211</v>
@@ -2348,7 +2348,7 @@
         <v>42</v>
       </c>
       <c r="J48">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2369,9 +2369,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>127516604</v>
+        <v>127161588</v>
       </c>
       <c r="E49">
         <v>1211</v>
@@ -2386,7 +2386,7 @@
         <v>42</v>
       </c>
       <c r="J49">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2407,24 +2407,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>127516680</v>
+        <v>127188575</v>
       </c>
       <c r="E50">
         <v>1211</v>
       </c>
       <c r="F50" s="2">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="G50" s="2">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="I50">
         <v>42</v>
       </c>
       <c r="J50">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2445,24 +2445,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>127518482</v>
+        <v>127255939</v>
       </c>
       <c r="E51">
         <v>1211</v>
       </c>
       <c r="F51" s="2">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="G51" s="2">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="I51">
         <v>42</v>
       </c>
       <c r="J51">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2483,9 +2483,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>127518976</v>
+        <v>127303365</v>
       </c>
       <c r="E52">
         <v>1211</v>
@@ -2500,7 +2500,7 @@
         <v>42</v>
       </c>
       <c r="J52">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -2521,9 +2521,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>127518985</v>
+        <v>127444453</v>
       </c>
       <c r="E53">
         <v>1211</v>
@@ -2538,7 +2538,7 @@
         <v>42</v>
       </c>
       <c r="J53">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -2559,24 +2559,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>127519347</v>
+        <v>127464776</v>
       </c>
       <c r="E54">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F54" s="2">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="G54" s="2">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="I54">
         <v>42</v>
       </c>
       <c r="J54">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -2597,24 +2597,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>127519431</v>
+        <v>127472186</v>
       </c>
       <c r="E55">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F55" s="2">
-        <v>45412</v>
+        <v>45408</v>
       </c>
       <c r="G55" s="2">
-        <v>45412</v>
+        <v>45407</v>
       </c>
       <c r="I55">
         <v>42</v>
       </c>
       <c r="J55">
-        <v>715</v>
+        <v>8021</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -2635,18 +2635,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>127520572</v>
+        <v>127491086</v>
       </c>
       <c r="E56">
         <v>1211</v>
       </c>
       <c r="F56" s="2">
-        <v>45412</v>
+        <v>45408</v>
       </c>
       <c r="G56" s="2">
-        <v>45412</v>
+        <v>45408</v>
       </c>
       <c r="I56">
         <v>42</v>
@@ -2673,18 +2673,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>127520744</v>
+        <v>127492992</v>
       </c>
       <c r="E57">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F57" s="2">
-        <v>45412</v>
+        <v>45408</v>
       </c>
       <c r="G57" s="2">
-        <v>45412</v>
+        <v>45408</v>
       </c>
       <c r="I57">
         <v>42</v>
@@ -2711,18 +2711,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>127520821</v>
+        <v>127496547</v>
       </c>
       <c r="E58">
         <v>1211</v>
       </c>
       <c r="F58" s="2">
-        <v>45412</v>
+        <v>45408</v>
       </c>
       <c r="G58" s="2">
-        <v>45412</v>
+        <v>45408</v>
       </c>
       <c r="I58">
         <v>42</v>
@@ -2749,18 +2749,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>127521058</v>
+        <v>127496783</v>
       </c>
       <c r="E59">
         <v>1211</v>
       </c>
       <c r="F59" s="2">
-        <v>45412</v>
+        <v>45408</v>
       </c>
       <c r="G59" s="2">
-        <v>45412</v>
+        <v>45408</v>
       </c>
       <c r="I59">
         <v>42</v>
@@ -2787,18 +2787,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>127521241</v>
+        <v>127506001</v>
       </c>
       <c r="E60">
         <v>1211</v>
       </c>
       <c r="F60" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="G60" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="I60">
         <v>42</v>
@@ -2825,18 +2825,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>127521721</v>
+        <v>127506321</v>
       </c>
       <c r="E61">
         <v>1211</v>
       </c>
       <c r="F61" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="G61" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="I61">
         <v>42</v>
@@ -2863,18 +2863,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>127521958</v>
+        <v>127506470</v>
       </c>
       <c r="E62">
         <v>1211</v>
       </c>
       <c r="F62" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="G62" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="I62">
         <v>42</v>
@@ -2901,18 +2901,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>127522152</v>
+        <v>127507932</v>
       </c>
       <c r="E63">
         <v>1211</v>
       </c>
       <c r="F63" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="G63" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="I63">
         <v>42</v>
@@ -2939,9 +2939,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>127523392</v>
+        <v>127516546</v>
       </c>
       <c r="E64">
         <v>1211</v>
@@ -2977,9 +2977,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>127523537</v>
+        <v>127516604</v>
       </c>
       <c r="E65">
         <v>1211</v>
@@ -3015,9 +3015,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>127524445</v>
+        <v>127516680</v>
       </c>
       <c r="E66">
         <v>1211</v>
@@ -3053,9 +3053,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>127526934</v>
+        <v>127518482</v>
       </c>
       <c r="E67">
         <v>1211</v>
@@ -3091,9 +3091,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>127528123</v>
+        <v>127518976</v>
       </c>
       <c r="E68">
         <v>1211</v>
@@ -3129,9 +3129,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>127528259</v>
+        <v>127518985</v>
       </c>
       <c r="E69">
         <v>1211</v>
@@ -3167,9 +3167,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>127529638</v>
+        <v>127519347</v>
       </c>
       <c r="E70">
         <v>1212</v>
@@ -3205,8 +3205,881 @@
         <v>61</v>
       </c>
     </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>127519431</v>
+      </c>
+      <c r="E71">
+        <v>1212</v>
+      </c>
+      <c r="F71" s="2">
+        <v>45412</v>
+      </c>
+      <c r="G71" s="2">
+        <v>45412</v>
+      </c>
+      <c r="I71">
+        <v>42</v>
+      </c>
+      <c r="J71">
+        <v>715</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>127520572</v>
+      </c>
+      <c r="E72">
+        <v>1211</v>
+      </c>
+      <c r="F72" s="2">
+        <v>45412</v>
+      </c>
+      <c r="G72" s="2">
+        <v>45412</v>
+      </c>
+      <c r="I72">
+        <v>42</v>
+      </c>
+      <c r="J72">
+        <v>715</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>127520744</v>
+      </c>
+      <c r="E73">
+        <v>1212</v>
+      </c>
+      <c r="F73" s="2">
+        <v>45412</v>
+      </c>
+      <c r="G73" s="2">
+        <v>45412</v>
+      </c>
+      <c r="I73">
+        <v>42</v>
+      </c>
+      <c r="J73">
+        <v>715</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>127520821</v>
+      </c>
+      <c r="E74">
+        <v>1211</v>
+      </c>
+      <c r="F74" s="2">
+        <v>45412</v>
+      </c>
+      <c r="G74" s="2">
+        <v>45412</v>
+      </c>
+      <c r="I74">
+        <v>42</v>
+      </c>
+      <c r="J74">
+        <v>715</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>127521058</v>
+      </c>
+      <c r="E75">
+        <v>1211</v>
+      </c>
+      <c r="F75" s="2">
+        <v>45412</v>
+      </c>
+      <c r="G75" s="2">
+        <v>45412</v>
+      </c>
+      <c r="I75">
+        <v>42</v>
+      </c>
+      <c r="J75">
+        <v>715</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>127521721</v>
+      </c>
+      <c r="E76">
+        <v>1211</v>
+      </c>
+      <c r="F76" s="2">
+        <v>45412</v>
+      </c>
+      <c r="G76" s="2">
+        <v>45412</v>
+      </c>
+      <c r="I76">
+        <v>42</v>
+      </c>
+      <c r="J76">
+        <v>715</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>127521958</v>
+      </c>
+      <c r="E77">
+        <v>1211</v>
+      </c>
+      <c r="F77" s="2">
+        <v>45412</v>
+      </c>
+      <c r="G77" s="2">
+        <v>45412</v>
+      </c>
+      <c r="I77">
+        <v>42</v>
+      </c>
+      <c r="J77">
+        <v>715</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>127522152</v>
+      </c>
+      <c r="E78">
+        <v>1211</v>
+      </c>
+      <c r="F78" s="2">
+        <v>45412</v>
+      </c>
+      <c r="G78" s="2">
+        <v>45412</v>
+      </c>
+      <c r="I78">
+        <v>42</v>
+      </c>
+      <c r="J78">
+        <v>715</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>127523537</v>
+      </c>
+      <c r="E79">
+        <v>1211</v>
+      </c>
+      <c r="F79" s="2">
+        <v>45412</v>
+      </c>
+      <c r="G79" s="2">
+        <v>45412</v>
+      </c>
+      <c r="I79">
+        <v>42</v>
+      </c>
+      <c r="J79">
+        <v>715</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>127524445</v>
+      </c>
+      <c r="E80">
+        <v>1211</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="I80">
+        <v>42</v>
+      </c>
+      <c r="J80">
+        <v>715</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>127526934</v>
+      </c>
+      <c r="E81">
+        <v>1211</v>
+      </c>
+      <c r="F81" s="2">
+        <v>45412</v>
+      </c>
+      <c r="G81" s="2">
+        <v>45412</v>
+      </c>
+      <c r="I81">
+        <v>42</v>
+      </c>
+      <c r="J81">
+        <v>715</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>127528259</v>
+      </c>
+      <c r="E82">
+        <v>1211</v>
+      </c>
+      <c r="F82" s="2">
+        <v>45412</v>
+      </c>
+      <c r="G82" s="2">
+        <v>45412</v>
+      </c>
+      <c r="I82">
+        <v>42</v>
+      </c>
+      <c r="J82">
+        <v>715</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>127529638</v>
+      </c>
+      <c r="E83">
+        <v>1212</v>
+      </c>
+      <c r="F83" s="2">
+        <v>45412</v>
+      </c>
+      <c r="G83" s="2">
+        <v>45412</v>
+      </c>
+      <c r="I83">
+        <v>42</v>
+      </c>
+      <c r="J83">
+        <v>715</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>127537870</v>
+      </c>
+      <c r="E84">
+        <v>1211</v>
+      </c>
+      <c r="F84" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G84" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I84">
+        <v>42</v>
+      </c>
+      <c r="J84">
+        <v>715</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>127539010</v>
+      </c>
+      <c r="E85">
+        <v>1211</v>
+      </c>
+      <c r="F85" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G85" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I85">
+        <v>42</v>
+      </c>
+      <c r="J85">
+        <v>715</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>127539155</v>
+      </c>
+      <c r="E86">
+        <v>1211</v>
+      </c>
+      <c r="F86" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G86" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I86">
+        <v>42</v>
+      </c>
+      <c r="J86">
+        <v>715</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>127539244</v>
+      </c>
+      <c r="E87">
+        <v>1211</v>
+      </c>
+      <c r="F87" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G87" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I87">
+        <v>42</v>
+      </c>
+      <c r="J87">
+        <v>715</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>127539817</v>
+      </c>
+      <c r="E88">
+        <v>1211</v>
+      </c>
+      <c r="F88" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G88" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I88">
+        <v>42</v>
+      </c>
+      <c r="J88">
+        <v>715</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>127542100</v>
+      </c>
+      <c r="E89">
+        <v>1211</v>
+      </c>
+      <c r="F89" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G89" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I89">
+        <v>42</v>
+      </c>
+      <c r="J89">
+        <v>715</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>127542359</v>
+      </c>
+      <c r="E90">
+        <v>1211</v>
+      </c>
+      <c r="F90" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G90" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I90">
+        <v>42</v>
+      </c>
+      <c r="J90">
+        <v>715</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>127544295</v>
+      </c>
+      <c r="E91">
+        <v>1212</v>
+      </c>
+      <c r="F91" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G91" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I91">
+        <v>42</v>
+      </c>
+      <c r="J91">
+        <v>715</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>127545566</v>
+      </c>
+      <c r="E92">
+        <v>1211</v>
+      </c>
+      <c r="F92" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G92" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I92">
+        <v>42</v>
+      </c>
+      <c r="J92">
+        <v>715</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>127546295</v>
+      </c>
+      <c r="E93">
+        <v>1212</v>
+      </c>
+      <c r="F93" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G93" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I93">
+        <v>42</v>
+      </c>
+      <c r="J93">
+        <v>715</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q70" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -3221,12 +4094,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{249CD703-0AE7-46A1-BA6D-A19361B97C73}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:Q198"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -3279,7 +4152,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>125887260</v>
       </c>
@@ -3317,7 +4190,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>125890823</v>
       </c>
@@ -3355,7 +4228,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>125891086</v>
       </c>
@@ -3393,7 +4266,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>125892224</v>
       </c>
@@ -3431,7 +4304,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>125892709</v>
       </c>
@@ -3469,7 +4342,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>125892901</v>
       </c>
@@ -3507,7 +4380,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>125892906</v>
       </c>
@@ -3545,7 +4418,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>125893564</v>
       </c>
@@ -3583,7 +4456,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>125893722</v>
       </c>
@@ -3621,7 +4494,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>125895193</v>
       </c>
@@ -3659,7 +4532,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>125896177</v>
       </c>
@@ -3697,7 +4570,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>125898007</v>
       </c>
@@ -3735,7 +4608,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>125900254</v>
       </c>
@@ -3773,7 +4646,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>125901787</v>
       </c>
@@ -3811,7 +4684,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>125901795</v>
       </c>
@@ -3849,7 +4722,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>125903262</v>
       </c>
@@ -3887,7 +4760,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>125904221</v>
       </c>
@@ -3925,7 +4798,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>125904238</v>
       </c>
@@ -3963,7 +4836,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>125907420</v>
       </c>
@@ -4001,7 +4874,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>125907797</v>
       </c>
@@ -4039,7 +4912,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>125908056</v>
       </c>
@@ -4077,7 +4950,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>125908177</v>
       </c>
@@ -4115,7 +4988,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>125908231</v>
       </c>
@@ -4153,7 +5026,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>125908843</v>
       </c>
@@ -4191,7 +5064,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>125909142</v>
       </c>
@@ -4229,7 +5102,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>125909933</v>
       </c>
@@ -4267,7 +5140,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>125910114</v>
       </c>
@@ -4305,7 +5178,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>125910400</v>
       </c>
@@ -4343,7 +5216,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>125910838</v>
       </c>
@@ -4381,7 +5254,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>125912176</v>
       </c>
@@ -4419,7 +5292,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>125912843</v>
       </c>
@@ -4457,7 +5330,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>125913133</v>
       </c>
@@ -4495,7 +5368,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>125913427</v>
       </c>
@@ -4533,7 +5406,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>125914356</v>
       </c>
@@ -4571,7 +5444,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>125914668</v>
       </c>
@@ -4609,7 +5482,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>125914978</v>
       </c>
@@ -4647,7 +5520,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>125918666</v>
       </c>
@@ -4685,7 +5558,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>125920065</v>
       </c>
@@ -4723,7 +5596,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>125924508</v>
       </c>
@@ -4761,7 +5634,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>125926112</v>
       </c>
@@ -4799,7 +5672,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>125927235</v>
       </c>
@@ -4837,7 +5710,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>125927477</v>
       </c>
@@ -4875,7 +5748,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>125927712</v>
       </c>
@@ -4913,7 +5786,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>125927811</v>
       </c>
@@ -4951,7 +5824,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>125928500</v>
       </c>
@@ -4989,7 +5862,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>125928781</v>
       </c>
@@ -5027,7 +5900,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>125928935</v>
       </c>
@@ -5065,7 +5938,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>125929845</v>
       </c>
@@ -5103,7 +5976,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>125930432</v>
       </c>
@@ -5141,7 +6014,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>125931903</v>
       </c>
@@ -5179,7 +6052,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>125932521</v>
       </c>
@@ -5217,7 +6090,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>125932669</v>
       </c>
@@ -5255,7 +6128,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>125933582</v>
       </c>
@@ -5293,7 +6166,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>125933608</v>
       </c>
@@ -5331,7 +6204,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>125935767</v>
       </c>
@@ -5369,7 +6242,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>125938612</v>
       </c>
@@ -5407,7 +6280,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>125944749</v>
       </c>
@@ -5445,7 +6318,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>125945240</v>
       </c>
@@ -5483,7 +6356,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>125949456</v>
       </c>
@@ -5521,7 +6394,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>125958349</v>
       </c>
@@ -5559,7 +6432,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>125958503</v>
       </c>
@@ -5597,7 +6470,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>125960344</v>
       </c>
@@ -5635,7 +6508,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>125962131</v>
       </c>
@@ -5673,7 +6546,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>125965767</v>
       </c>
@@ -5711,7 +6584,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>125965877</v>
       </c>
@@ -5749,7 +6622,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>125969356</v>
       </c>
@@ -5787,7 +6660,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>125971901</v>
       </c>
@@ -5825,7 +6698,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>125976084</v>
       </c>
@@ -5863,7 +6736,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>125976278</v>
       </c>
@@ -5901,7 +6774,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>125977146</v>
       </c>
@@ -5939,7 +6812,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>125977504</v>
       </c>
@@ -5977,7 +6850,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>125981162</v>
       </c>
@@ -6015,7 +6888,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>125983181</v>
       </c>
@@ -6053,7 +6926,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>125983593</v>
       </c>
@@ -6091,7 +6964,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>125984782</v>
       </c>
@@ -6129,7 +7002,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>125992174</v>
       </c>
@@ -6167,7 +7040,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>125992452</v>
       </c>
@@ -6205,7 +7078,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>125997050</v>
       </c>
@@ -6243,7 +7116,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>126009389</v>
       </c>
@@ -6281,7 +7154,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>126012544</v>
       </c>
@@ -6319,7 +7192,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>126013965</v>
       </c>
@@ -6357,7 +7230,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>126015225</v>
       </c>
@@ -6395,7 +7268,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>126015257</v>
       </c>
@@ -6433,7 +7306,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>126020235</v>
       </c>
@@ -6471,7 +7344,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>126028210</v>
       </c>
@@ -6509,7 +7382,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>126028956</v>
       </c>
@@ -6547,7 +7420,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>126029328</v>
       </c>
@@ -6585,7 +7458,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>126029650</v>
       </c>
@@ -6623,7 +7496,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>126029868</v>
       </c>
@@ -6661,7 +7534,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>126033233</v>
       </c>
@@ -6699,7 +7572,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>126036666</v>
       </c>
@@ -6737,7 +7610,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>126037292</v>
       </c>
@@ -6775,7 +7648,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>126040785</v>
       </c>
@@ -6813,7 +7686,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>126040979</v>
       </c>
@@ -6851,7 +7724,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>126041187</v>
       </c>
@@ -6889,7 +7762,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>126043144</v>
       </c>
@@ -6927,7 +7800,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>126045060</v>
       </c>
@@ -6965,7 +7838,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>126045520</v>
       </c>
@@ -7003,7 +7876,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>126049650</v>
       </c>
@@ -7041,7 +7914,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>126051286</v>
       </c>
@@ -7079,7 +7952,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>126052567</v>
       </c>
@@ -7117,7 +7990,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>126057040</v>
       </c>
@@ -7155,7 +8028,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>126057529</v>
       </c>
@@ -7193,7 +8066,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>126057835</v>
       </c>
@@ -7231,7 +8104,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>126058412</v>
       </c>
@@ -7269,7 +8142,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>126063955</v>
       </c>
@@ -7307,7 +8180,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>126064498</v>
       </c>
@@ -7345,7 +8218,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>126065211</v>
       </c>
@@ -7383,7 +8256,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>126074608</v>
       </c>
@@ -7421,7 +8294,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>126078394</v>
       </c>
@@ -7459,7 +8332,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>126080342</v>
       </c>
@@ -7497,7 +8370,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>126082448</v>
       </c>
@@ -7535,7 +8408,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>126082622</v>
       </c>
@@ -7573,7 +8446,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>126084723</v>
       </c>
@@ -7611,7 +8484,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>126086747</v>
       </c>
@@ -7649,7 +8522,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>126088025</v>
       </c>
@@ -7687,7 +8560,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>126088302</v>
       </c>
@@ -7725,7 +8598,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>126088413</v>
       </c>
@@ -7763,7 +8636,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>126088528</v>
       </c>
@@ -7801,7 +8674,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>126089277</v>
       </c>
@@ -7839,7 +8712,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>126089435</v>
       </c>
@@ -7877,7 +8750,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>126090634</v>
       </c>
@@ -7915,7 +8788,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>126093282</v>
       </c>
@@ -7953,7 +8826,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>126093649</v>
       </c>
@@ -7991,7 +8864,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>126097132</v>
       </c>
@@ -8029,7 +8902,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>126098812</v>
       </c>
@@ -8067,7 +8940,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>126099189</v>
       </c>
@@ -8105,7 +8978,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>126099880</v>
       </c>
@@ -8143,7 +9016,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>126100047</v>
       </c>
@@ -8181,7 +9054,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>126101516</v>
       </c>
@@ -8219,7 +9092,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>126102394</v>
       </c>
@@ -8257,7 +9130,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>126104952</v>
       </c>
@@ -8295,7 +9168,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>126106789</v>
       </c>
@@ -8333,7 +9206,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>126111482</v>
       </c>
@@ -8371,7 +9244,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>126111872</v>
       </c>
@@ -8409,7 +9282,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>126119068</v>
       </c>
@@ -8447,7 +9320,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>126120069</v>
       </c>
@@ -8485,7 +9358,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>126120915</v>
       </c>
@@ -8523,7 +9396,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>126120976</v>
       </c>
@@ -8561,7 +9434,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>126122910</v>
       </c>
@@ -8599,7 +9472,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>126130699</v>
       </c>
@@ -8637,7 +9510,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>126131117</v>
       </c>
@@ -8675,7 +9548,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>126136404</v>
       </c>
@@ -8713,7 +9586,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>126140055</v>
       </c>
@@ -8751,7 +9624,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>126147040</v>
       </c>
@@ -8789,7 +9662,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>126155748</v>
       </c>
@@ -8827,7 +9700,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>126155838</v>
       </c>
@@ -8865,7 +9738,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>126157906</v>
       </c>
@@ -8903,7 +9776,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>126158151</v>
       </c>
@@ -8941,7 +9814,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>126162518</v>
       </c>
@@ -8979,7 +9852,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>126164369</v>
       </c>
@@ -9017,7 +9890,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>126164882</v>
       </c>
@@ -9055,7 +9928,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>126165476</v>
       </c>
@@ -9093,7 +9966,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>126165996</v>
       </c>
@@ -9131,7 +10004,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>126167070</v>
       </c>
@@ -9169,7 +10042,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>126168025</v>
       </c>
@@ -9207,7 +10080,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>126168249</v>
       </c>
@@ -9245,7 +10118,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>126173180</v>
       </c>
@@ -9283,7 +10156,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>126174316</v>
       </c>
@@ -9321,7 +10194,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>126174669</v>
       </c>
@@ -9359,7 +10232,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>126176463</v>
       </c>
@@ -9397,7 +10270,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>126176884</v>
       </c>
@@ -9435,7 +10308,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>126185047</v>
       </c>
@@ -9473,7 +10346,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>126185760</v>
       </c>
@@ -9511,7 +10384,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>126187183</v>
       </c>
@@ -9549,7 +10422,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>126187745</v>
       </c>
@@ -9587,7 +10460,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>126192174</v>
       </c>
@@ -9625,7 +10498,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>126192469</v>
       </c>
@@ -9663,7 +10536,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>126192814</v>
       </c>
@@ -9701,7 +10574,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>126193665</v>
       </c>
@@ -9739,7 +10612,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>126193855</v>
       </c>
@@ -9777,7 +10650,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>126194373</v>
       </c>
@@ -9815,7 +10688,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>126195588</v>
       </c>
@@ -9853,7 +10726,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>126197992</v>
       </c>
@@ -9891,7 +10764,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>126198450</v>
       </c>
@@ -9929,7 +10802,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>126198510</v>
       </c>
@@ -9967,7 +10840,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>126198929</v>
       </c>
@@ -10005,7 +10878,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>126201454</v>
       </c>
@@ -10043,7 +10916,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>126201460</v>
       </c>
@@ -10081,7 +10954,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>126201930</v>
       </c>
@@ -10119,7 +10992,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>126201991</v>
       </c>
@@ -10157,7 +11030,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>126212316</v>
       </c>
@@ -10195,7 +11068,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>126213617</v>
       </c>
@@ -10233,7 +11106,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>126216332</v>
       </c>
@@ -10271,7 +11144,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>126218950</v>
       </c>
@@ -10309,7 +11182,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>126230676</v>
       </c>
@@ -10347,7 +11220,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>126231536</v>
       </c>
@@ -10385,7 +11258,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>126237618</v>
       </c>
@@ -10423,7 +11296,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>126245598</v>
       </c>
@@ -10461,7 +11334,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>126265244</v>
       </c>
@@ -10499,7 +11372,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>126265499</v>
       </c>
@@ -10537,7 +11410,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>126266542</v>
       </c>
@@ -10575,7 +11448,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>126268776</v>
       </c>
@@ -10613,7 +11486,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>126280119</v>
       </c>
@@ -10651,7 +11524,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>126280477</v>
       </c>
@@ -10689,7 +11562,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>126281587</v>
       </c>
@@ -10727,7 +11600,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>126281992</v>
       </c>
@@ -10796,31 +11669,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11871C0A-D4A6-4153-9F93-F348ABEEA517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823A5FCE-93C0-4670-BC96-1E2EF3C42B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fiel" sheetId="28" r:id="rId1"/>
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$92</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -504,21 +504,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q92"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
@@ -526,11 +526,11 @@
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -583,56 +583,56 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>127504158</v>
+        <v>123539151</v>
       </c>
       <c r="E2">
+        <v>2013</v>
+      </c>
+      <c r="F2" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G2" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I2">
+        <v>42</v>
+      </c>
+      <c r="J2">
+        <v>8001</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>127516439</v>
+      </c>
+      <c r="E3">
         <v>1211</v>
       </c>
-      <c r="F2" s="2">
-        <v>45411</v>
-      </c>
-      <c r="G2" s="2">
-        <v>45411</v>
-      </c>
-      <c r="I2">
-        <v>42</v>
-      </c>
-      <c r="J2">
-        <v>1735</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>127507143</v>
-      </c>
-      <c r="E3">
-        <v>1212</v>
-      </c>
       <c r="F3" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="G3" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I3">
         <v>42</v>
@@ -659,18 +659,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>127512143</v>
+        <v>127521560</v>
       </c>
       <c r="E4">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45411</v>
+        <v>45413</v>
       </c>
       <c r="G4" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I4">
         <v>42</v>
@@ -697,18 +697,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>127514750</v>
+        <v>127522199</v>
       </c>
       <c r="E5">
         <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="G5" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I5">
         <v>42</v>
@@ -735,24 +735,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>123769917</v>
+        <v>127522573</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45414</v>
+        <v>45412</v>
       </c>
       <c r="G6" s="2">
-        <v>45414</v>
+        <v>45412</v>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -773,24 +773,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>123886393</v>
+        <v>127522743</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45414</v>
+        <v>45413</v>
       </c>
       <c r="G7" s="2">
-        <v>45411</v>
+        <v>45412</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -811,24 +811,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>123934492</v>
+        <v>127524776</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45414</v>
+        <v>45412</v>
       </c>
       <c r="G8" s="2">
-        <v>45414</v>
+        <v>45412</v>
       </c>
       <c r="I8">
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -849,9 +849,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>124005068</v>
+        <v>127526213</v>
       </c>
       <c r="E9">
         <v>1211</v>
@@ -866,7 +866,7 @@
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -887,15 +887,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>124270935</v>
+        <v>127532590</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G10" s="2">
         <v>45414</v>
@@ -904,7 +904,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -925,15 +925,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>124409962</v>
+        <v>127533334</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G11" s="2">
         <v>45414</v>
@@ -942,7 +942,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -963,9 +963,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>124449648</v>
+        <v>127539662</v>
       </c>
       <c r="E12">
         <v>1211</v>
@@ -980,7 +980,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1001,9 +1001,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>124602882</v>
+        <v>127540090</v>
       </c>
       <c r="E13">
         <v>1211</v>
@@ -1012,13 +1012,13 @@
         <v>45414</v>
       </c>
       <c r="G13" s="2">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="I13">
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1039,18 +1039,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>124743039</v>
+        <v>124155906</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G14" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1077,18 +1077,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>124769075</v>
+        <v>124160803</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G15" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1115,18 +1115,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>124849715</v>
+        <v>124530189</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G16" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1153,18 +1153,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>124854860</v>
+        <v>124766075</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G17" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1191,15 +1191,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>124897328</v>
+        <v>125021105</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45414</v>
+        <v>45416</v>
       </c>
       <c r="G18" s="2">
         <v>45414</v>
@@ -1229,18 +1229,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>125012611</v>
+        <v>125147451</v>
       </c>
       <c r="E19">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F19" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G19" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1267,18 +1267,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>125181637</v>
+        <v>125299048</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45412</v>
+        <v>45416</v>
       </c>
       <c r="G20" s="2">
-        <v>45412</v>
+        <v>45416</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1305,18 +1305,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>125193787</v>
+        <v>125654267</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G21" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1343,18 +1343,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>125200319</v>
+        <v>125722018</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G22" s="2">
-        <v>45414</v>
+        <v>45411</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1381,15 +1381,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>125203365</v>
+        <v>125953972</v>
       </c>
       <c r="E23">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F23" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G23" s="2">
         <v>45412</v>
@@ -1419,18 +1419,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>125258579</v>
+        <v>126143026</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G24" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1457,18 +1457,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>125307304</v>
+        <v>126188075</v>
       </c>
       <c r="E25">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F25" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G25" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I25">
         <v>42</v>
@@ -1495,18 +1495,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>125495976</v>
+        <v>126364812</v>
       </c>
       <c r="E26">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F26" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G26" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I26">
         <v>42</v>
@@ -1533,18 +1533,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>125788104</v>
+        <v>126395866</v>
       </c>
       <c r="E27">
         <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45412</v>
+        <v>45416</v>
       </c>
       <c r="G27" s="2">
-        <v>45412</v>
+        <v>45416</v>
       </c>
       <c r="I27">
         <v>42</v>
@@ -1571,18 +1571,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>125888553</v>
+        <v>126466669</v>
       </c>
       <c r="E28">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45412</v>
+        <v>45416</v>
       </c>
       <c r="G28" s="2">
-        <v>45412</v>
+        <v>45416</v>
       </c>
       <c r="I28">
         <v>42</v>
@@ -1609,18 +1609,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>126083147</v>
+        <v>126521579</v>
       </c>
       <c r="E29">
         <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G29" s="2">
-        <v>45411</v>
+        <v>45415</v>
       </c>
       <c r="I29">
         <v>42</v>
@@ -1647,18 +1647,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>126096321</v>
+        <v>126633928</v>
       </c>
       <c r="E30">
         <v>1211</v>
       </c>
       <c r="F30" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G30" s="2">
         <v>45414</v>
-      </c>
-      <c r="G30" s="2">
-        <v>45412</v>
       </c>
       <c r="I30">
         <v>42</v>
@@ -1685,18 +1685,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>126116510</v>
+        <v>126728778</v>
       </c>
       <c r="E31">
         <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45414</v>
+        <v>45416</v>
       </c>
       <c r="G31" s="2">
-        <v>45414</v>
+        <v>45416</v>
       </c>
       <c r="I31">
         <v>42</v>
@@ -1723,18 +1723,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>126170466</v>
+        <v>126839642</v>
       </c>
       <c r="E32">
         <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>45414</v>
+        <v>45416</v>
       </c>
       <c r="G32" s="2">
-        <v>45414</v>
+        <v>45416</v>
       </c>
       <c r="I32">
         <v>42</v>
@@ -1761,18 +1761,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>126174137</v>
+        <v>126898108</v>
       </c>
       <c r="E33">
         <v>1211</v>
       </c>
       <c r="F33" s="2">
-        <v>45414</v>
+        <v>45416</v>
       </c>
       <c r="G33" s="2">
-        <v>45414</v>
+        <v>45416</v>
       </c>
       <c r="I33">
         <v>42</v>
@@ -1799,18 +1799,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>126308525</v>
+        <v>127038041</v>
       </c>
       <c r="E34">
         <v>1211</v>
       </c>
       <c r="F34" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G34" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I34">
         <v>42</v>
@@ -1837,18 +1837,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>126332089</v>
+        <v>127060509</v>
       </c>
       <c r="E35">
         <v>1211</v>
       </c>
       <c r="F35" s="2">
-        <v>45412</v>
+        <v>45416</v>
       </c>
       <c r="G35" s="2">
-        <v>45408</v>
+        <v>45416</v>
       </c>
       <c r="I35">
         <v>42</v>
@@ -1875,18 +1875,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>126434242</v>
+        <v>127087057</v>
       </c>
       <c r="E36">
         <v>1211</v>
       </c>
       <c r="F36" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G36" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I36">
         <v>42</v>
@@ -1913,18 +1913,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>126516958</v>
+        <v>127327684</v>
       </c>
       <c r="E37">
         <v>1211</v>
       </c>
       <c r="F37" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G37" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I37">
         <v>42</v>
@@ -1951,18 +1951,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>126559351</v>
+        <v>127425908</v>
       </c>
       <c r="E38">
         <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G38" s="2">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="I38">
         <v>42</v>
@@ -1989,18 +1989,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>126638467</v>
+        <v>127438094</v>
       </c>
       <c r="E39">
         <v>1211</v>
       </c>
       <c r="F39" s="2">
-        <v>45412</v>
+        <v>45416</v>
       </c>
       <c r="G39" s="2">
-        <v>45412</v>
+        <v>45416</v>
       </c>
       <c r="I39">
         <v>42</v>
@@ -2027,18 +2027,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>126699676</v>
+        <v>127465460</v>
       </c>
       <c r="E40">
         <v>1211</v>
       </c>
       <c r="F40" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G40" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I40">
         <v>42</v>
@@ -2065,18 +2065,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>126734568</v>
+        <v>127547830</v>
       </c>
       <c r="E41">
         <v>1211</v>
       </c>
       <c r="F41" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G41" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I41">
         <v>42</v>
@@ -2103,24 +2103,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>126776245</v>
+        <v>110074933</v>
       </c>
       <c r="E42">
         <v>1211</v>
       </c>
       <c r="F42" s="2">
-        <v>45412</v>
+        <v>43453</v>
       </c>
       <c r="G42" s="2">
-        <v>45412</v>
+        <v>43441</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>8001</v>
+        <v>8023</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2141,18 +2141,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>126852653</v>
+        <v>123058958</v>
       </c>
       <c r="E43">
         <v>1211</v>
       </c>
       <c r="F43" s="2">
-        <v>45414</v>
+        <v>44995</v>
       </c>
       <c r="G43" s="2">
-        <v>45414</v>
+        <v>44993</v>
       </c>
       <c r="I43">
         <v>42</v>
@@ -2179,24 +2179,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>126917817</v>
+        <v>127472186</v>
       </c>
       <c r="E44">
         <v>1211</v>
       </c>
       <c r="F44" s="2">
-        <v>45412</v>
+        <v>45408</v>
       </c>
       <c r="G44" s="2">
-        <v>45412</v>
+        <v>45407</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2217,9 +2217,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>127024637</v>
+        <v>127504091</v>
       </c>
       <c r="E45">
         <v>1211</v>
@@ -2228,13 +2228,13 @@
         <v>45412</v>
       </c>
       <c r="G45" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="I45">
         <v>42</v>
       </c>
       <c r="J45">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2255,24 +2255,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>127053596</v>
+        <v>127513307</v>
       </c>
       <c r="E46">
         <v>1211</v>
       </c>
       <c r="F46" s="2">
-        <v>45414</v>
+        <v>45412</v>
       </c>
       <c r="G46" s="2">
-        <v>45414</v>
+        <v>45411</v>
       </c>
       <c r="I46">
         <v>42</v>
       </c>
       <c r="J46">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2293,24 +2293,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>127092522</v>
+        <v>126954503</v>
       </c>
       <c r="E47">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F47" s="2">
-        <v>45414</v>
+        <v>45378</v>
       </c>
       <c r="G47" s="2">
-        <v>45414</v>
+        <v>45378</v>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>8001</v>
+        <v>8017</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2331,24 +2331,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>127104328</v>
+        <v>127457430</v>
       </c>
       <c r="E48">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F48" s="2">
-        <v>45412</v>
+        <v>45406</v>
       </c>
       <c r="G48" s="2">
-        <v>45412</v>
+        <v>45406</v>
       </c>
       <c r="I48">
         <v>42</v>
       </c>
       <c r="J48">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2369,24 +2369,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>127161588</v>
+        <v>127457488</v>
       </c>
       <c r="E49">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F49" s="2">
-        <v>45412</v>
+        <v>45406</v>
       </c>
       <c r="G49" s="2">
-        <v>45412</v>
+        <v>45406</v>
       </c>
       <c r="I49">
         <v>42</v>
       </c>
       <c r="J49">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2407,24 +2407,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>127188575</v>
+        <v>127463290</v>
       </c>
       <c r="E50">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F50" s="2">
-        <v>45414</v>
+        <v>45406</v>
       </c>
       <c r="G50" s="2">
-        <v>45414</v>
+        <v>45406</v>
       </c>
       <c r="I50">
         <v>42</v>
       </c>
       <c r="J50">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2445,24 +2445,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>127255939</v>
+        <v>127463362</v>
       </c>
       <c r="E51">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F51" s="2">
-        <v>45414</v>
+        <v>45406</v>
       </c>
       <c r="G51" s="2">
-        <v>45414</v>
+        <v>45406</v>
       </c>
       <c r="I51">
         <v>42</v>
       </c>
       <c r="J51">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2483,24 +2483,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>127303365</v>
+        <v>127473527</v>
       </c>
       <c r="E52">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F52" s="2">
-        <v>45412</v>
+        <v>45407</v>
       </c>
       <c r="G52" s="2">
-        <v>45412</v>
+        <v>45407</v>
       </c>
       <c r="I52">
         <v>42</v>
       </c>
       <c r="J52">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -2521,24 +2521,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>127444453</v>
+        <v>127474916</v>
       </c>
       <c r="E53">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F53" s="2">
-        <v>45412</v>
+        <v>45407</v>
       </c>
       <c r="G53" s="2">
-        <v>45412</v>
+        <v>45407</v>
       </c>
       <c r="I53">
         <v>42</v>
       </c>
       <c r="J53">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -2559,24 +2559,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>127464776</v>
+        <v>127476626</v>
       </c>
       <c r="E54">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F54" s="2">
-        <v>45414</v>
+        <v>45407</v>
       </c>
       <c r="G54" s="2">
-        <v>45414</v>
+        <v>45407</v>
       </c>
       <c r="I54">
         <v>42</v>
       </c>
       <c r="J54">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -2597,15 +2597,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>127472186</v>
+        <v>127476711</v>
       </c>
       <c r="E55">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F55" s="2">
-        <v>45408</v>
+        <v>45407</v>
       </c>
       <c r="G55" s="2">
         <v>45407</v>
@@ -2614,7 +2614,7 @@
         <v>42</v>
       </c>
       <c r="J55">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -2635,24 +2635,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>127491086</v>
+        <v>127478746</v>
       </c>
       <c r="E56">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F56" s="2">
-        <v>45408</v>
+        <v>45407</v>
       </c>
       <c r="G56" s="2">
-        <v>45408</v>
+        <v>45407</v>
       </c>
       <c r="I56">
         <v>42</v>
       </c>
       <c r="J56">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -2673,24 +2673,24 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>127492992</v>
+        <v>127479650</v>
       </c>
       <c r="E57">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F57" s="2">
-        <v>45408</v>
+        <v>45407</v>
       </c>
       <c r="G57" s="2">
-        <v>45408</v>
+        <v>45407</v>
       </c>
       <c r="I57">
         <v>42</v>
       </c>
       <c r="J57">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -2711,12 +2711,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>127496547</v>
+        <v>127483267</v>
       </c>
       <c r="E58">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F58" s="2">
         <v>45408</v>
@@ -2728,7 +2728,7 @@
         <v>42</v>
       </c>
       <c r="J58">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -2749,12 +2749,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>127496783</v>
+        <v>127486659</v>
       </c>
       <c r="E59">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F59" s="2">
         <v>45408</v>
@@ -2766,7 +2766,7 @@
         <v>42</v>
       </c>
       <c r="J59">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -2787,246 +2787,246 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60">
+        <v>127486705</v>
+      </c>
+      <c r="E60">
+        <v>601</v>
+      </c>
+      <c r="F60" s="2">
+        <v>45408</v>
+      </c>
+      <c r="G60" s="2">
+        <v>45408</v>
+      </c>
+      <c r="I60">
+        <v>42</v>
+      </c>
+      <c r="J60">
+        <v>8004</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>127487214</v>
+      </c>
+      <c r="E61">
+        <v>601</v>
+      </c>
+      <c r="F61" s="2">
+        <v>45408</v>
+      </c>
+      <c r="G61" s="2">
+        <v>45408</v>
+      </c>
+      <c r="I61">
+        <v>42</v>
+      </c>
+      <c r="J61">
+        <v>8004</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>127487262</v>
+      </c>
+      <c r="E62">
+        <v>601</v>
+      </c>
+      <c r="F62" s="2">
+        <v>45408</v>
+      </c>
+      <c r="G62" s="2">
+        <v>45408</v>
+      </c>
+      <c r="I62">
+        <v>42</v>
+      </c>
+      <c r="J62">
+        <v>8004</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>127494377</v>
+      </c>
+      <c r="E63">
+        <v>601</v>
+      </c>
+      <c r="F63" s="2">
+        <v>45408</v>
+      </c>
+      <c r="G63" s="2">
+        <v>45408</v>
+      </c>
+      <c r="I63">
+        <v>42</v>
+      </c>
+      <c r="J63">
+        <v>8004</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>127494456</v>
+      </c>
+      <c r="E64">
+        <v>601</v>
+      </c>
+      <c r="F64" s="2">
+        <v>45408</v>
+      </c>
+      <c r="G64" s="2">
+        <v>45408</v>
+      </c>
+      <c r="I64">
+        <v>42</v>
+      </c>
+      <c r="J64">
+        <v>8004</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>127496155</v>
+      </c>
+      <c r="E65">
+        <v>601</v>
+      </c>
+      <c r="F65" s="2">
+        <v>45408</v>
+      </c>
+      <c r="G65" s="2">
+        <v>45408</v>
+      </c>
+      <c r="I65">
+        <v>42</v>
+      </c>
+      <c r="J65">
+        <v>1117</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A66">
         <v>127506001</v>
-      </c>
-      <c r="E60">
-        <v>1211</v>
-      </c>
-      <c r="F60" s="2">
-        <v>45411</v>
-      </c>
-      <c r="G60" s="2">
-        <v>45411</v>
-      </c>
-      <c r="I60">
-        <v>42</v>
-      </c>
-      <c r="J60">
-        <v>715</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
-        <v>0</v>
-      </c>
-      <c r="P60">
-        <v>0</v>
-      </c>
-      <c r="Q60">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>127506321</v>
-      </c>
-      <c r="E61">
-        <v>1211</v>
-      </c>
-      <c r="F61" s="2">
-        <v>45411</v>
-      </c>
-      <c r="G61" s="2">
-        <v>45411</v>
-      </c>
-      <c r="I61">
-        <v>42</v>
-      </c>
-      <c r="J61">
-        <v>715</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>0</v>
-      </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>127506470</v>
-      </c>
-      <c r="E62">
-        <v>1211</v>
-      </c>
-      <c r="F62" s="2">
-        <v>45411</v>
-      </c>
-      <c r="G62" s="2">
-        <v>45411</v>
-      </c>
-      <c r="I62">
-        <v>42</v>
-      </c>
-      <c r="J62">
-        <v>715</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>127507932</v>
-      </c>
-      <c r="E63">
-        <v>1211</v>
-      </c>
-      <c r="F63" s="2">
-        <v>45411</v>
-      </c>
-      <c r="G63" s="2">
-        <v>45411</v>
-      </c>
-      <c r="I63">
-        <v>42</v>
-      </c>
-      <c r="J63">
-        <v>715</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>127516546</v>
-      </c>
-      <c r="E64">
-        <v>1211</v>
-      </c>
-      <c r="F64" s="2">
-        <v>45412</v>
-      </c>
-      <c r="G64" s="2">
-        <v>45412</v>
-      </c>
-      <c r="I64">
-        <v>42</v>
-      </c>
-      <c r="J64">
-        <v>715</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>127516604</v>
-      </c>
-      <c r="E65">
-        <v>1211</v>
-      </c>
-      <c r="F65" s="2">
-        <v>45412</v>
-      </c>
-      <c r="G65" s="2">
-        <v>45412</v>
-      </c>
-      <c r="I65">
-        <v>42</v>
-      </c>
-      <c r="J65">
-        <v>715</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>127516680</v>
       </c>
       <c r="E66">
         <v>1211</v>
       </c>
       <c r="F66" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="G66" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="I66">
         <v>42</v>
@@ -3053,18 +3053,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>127518482</v>
+        <v>127506321</v>
       </c>
       <c r="E67">
         <v>1211</v>
       </c>
       <c r="F67" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="G67" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="I67">
         <v>42</v>
@@ -3091,18 +3091,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>127518976</v>
+        <v>127506470</v>
       </c>
       <c r="E68">
         <v>1211</v>
       </c>
       <c r="F68" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="G68" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="I68">
         <v>42</v>
@@ -3129,18 +3129,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>127518985</v>
+        <v>127507932</v>
       </c>
       <c r="E69">
         <v>1211</v>
       </c>
       <c r="F69" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="G69" s="2">
-        <v>45412</v>
+        <v>45411</v>
       </c>
       <c r="I69">
         <v>42</v>
@@ -3167,12 +3167,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>127519347</v>
+        <v>127524445</v>
       </c>
       <c r="E70">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F70" s="2">
         <v>45412</v>
@@ -3205,12 +3205,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>127519431</v>
+        <v>127528259</v>
       </c>
       <c r="E71">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F71" s="2">
         <v>45412</v>
@@ -3243,18 +3243,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>127520572</v>
+        <v>127539817</v>
       </c>
       <c r="E72">
         <v>1211</v>
       </c>
       <c r="F72" s="2">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="G72" s="2">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="I72">
         <v>42</v>
@@ -3281,18 +3281,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>127520744</v>
+        <v>127545566</v>
       </c>
       <c r="E73">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F73" s="2">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="G73" s="2">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="I73">
         <v>42</v>
@@ -3319,18 +3319,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>127520821</v>
+        <v>127549467</v>
       </c>
       <c r="E74">
         <v>1211</v>
       </c>
       <c r="F74" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G74" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I74">
         <v>42</v>
@@ -3357,18 +3357,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>127521058</v>
+        <v>127550585</v>
       </c>
       <c r="E75">
         <v>1211</v>
       </c>
       <c r="F75" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G75" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I75">
         <v>42</v>
@@ -3395,18 +3395,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>127521721</v>
+        <v>127551223</v>
       </c>
       <c r="E76">
         <v>1211</v>
       </c>
       <c r="F76" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G76" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I76">
         <v>42</v>
@@ -3433,18 +3433,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>127521958</v>
+        <v>127552675</v>
       </c>
       <c r="E77">
         <v>1211</v>
       </c>
       <c r="F77" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G77" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I77">
         <v>42</v>
@@ -3471,18 +3471,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>127522152</v>
+        <v>127553107</v>
       </c>
       <c r="E78">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F78" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G78" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I78">
         <v>42</v>
@@ -3509,18 +3509,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>127523537</v>
+        <v>127554447</v>
       </c>
       <c r="E79">
         <v>1211</v>
       </c>
       <c r="F79" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G79" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I79">
         <v>42</v>
@@ -3547,18 +3547,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>127524445</v>
+        <v>127554620</v>
       </c>
       <c r="E80">
         <v>1211</v>
       </c>
       <c r="F80" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G80" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I80">
         <v>42</v>
@@ -3585,18 +3585,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>127526934</v>
+        <v>127554894</v>
       </c>
       <c r="E81">
         <v>1211</v>
       </c>
       <c r="F81" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G81" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I81">
         <v>42</v>
@@ -3623,18 +3623,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>127528259</v>
+        <v>127556709</v>
       </c>
       <c r="E82">
         <v>1211</v>
       </c>
       <c r="F82" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G82" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I82">
         <v>42</v>
@@ -3661,18 +3661,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>127529638</v>
+        <v>127557825</v>
       </c>
       <c r="E83">
         <v>1212</v>
       </c>
       <c r="F83" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="G83" s="2">
-        <v>45412</v>
+        <v>45415</v>
       </c>
       <c r="I83">
         <v>42</v>
@@ -3699,18 +3699,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>127537870</v>
+        <v>127558479</v>
       </c>
       <c r="E84">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F84" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G84" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I84">
         <v>42</v>
@@ -3737,18 +3737,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>127539010</v>
+        <v>127558489</v>
       </c>
       <c r="E85">
         <v>1211</v>
       </c>
       <c r="F85" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G85" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I85">
         <v>42</v>
@@ -3775,18 +3775,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>127539155</v>
+        <v>127558723</v>
       </c>
       <c r="E86">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F86" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G86" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I86">
         <v>42</v>
@@ -3813,18 +3813,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>127539244</v>
+        <v>127558966</v>
       </c>
       <c r="E87">
         <v>1211</v>
       </c>
       <c r="F87" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G87" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I87">
         <v>42</v>
@@ -3851,18 +3851,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>127539817</v>
+        <v>127563716</v>
       </c>
       <c r="E88">
         <v>1211</v>
       </c>
       <c r="F88" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G88" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I88">
         <v>42</v>
@@ -3889,18 +3889,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>127542100</v>
+        <v>127564897</v>
       </c>
       <c r="E89">
         <v>1211</v>
       </c>
       <c r="F89" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G89" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I89">
         <v>42</v>
@@ -3927,18 +3927,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>127542359</v>
+        <v>127565084</v>
       </c>
       <c r="E90">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F90" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G90" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I90">
         <v>42</v>
@@ -3965,18 +3965,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>127544295</v>
+        <v>127567356</v>
       </c>
       <c r="E91">
         <v>1212</v>
       </c>
       <c r="F91" s="2">
-        <v>45414</v>
+        <v>45416</v>
       </c>
       <c r="G91" s="2">
-        <v>45414</v>
+        <v>45416</v>
       </c>
       <c r="I91">
         <v>42</v>
@@ -4003,18 +4003,18 @@
         <v>61</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>127545566</v>
+        <v>127567361</v>
       </c>
       <c r="E92">
         <v>1211</v>
       </c>
       <c r="F92" s="2">
-        <v>45414</v>
+        <v>45416</v>
       </c>
       <c r="G92" s="2">
-        <v>45414</v>
+        <v>45416</v>
       </c>
       <c r="I92">
         <v>42</v>
@@ -4041,45 +4041,14 @@
         <v>61</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>127546295</v>
-      </c>
-      <c r="E93">
-        <v>1212</v>
-      </c>
-      <c r="F93" s="2">
-        <v>45414</v>
-      </c>
-      <c r="G93" s="2">
-        <v>45414</v>
-      </c>
-      <c r="I93">
-        <v>42</v>
-      </c>
-      <c r="J93">
-        <v>715</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
-        <v>0</v>
-      </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
-      <c r="O93">
-        <v>0</v>
-      </c>
-      <c r="P93">
-        <v>0</v>
-      </c>
-      <c r="Q93">
-        <v>61</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:Q92" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="8001"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -4094,12 +4063,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{249CD703-0AE7-46A1-BA6D-A19361B97C73}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:Q198"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -4152,7 +4121,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>125887260</v>
       </c>
@@ -4190,7 +4159,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>125890823</v>
       </c>
@@ -4228,7 +4197,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>125891086</v>
       </c>
@@ -4266,7 +4235,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>125892224</v>
       </c>
@@ -4304,7 +4273,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>125892709</v>
       </c>
@@ -4342,7 +4311,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>125892901</v>
       </c>
@@ -4380,7 +4349,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>125892906</v>
       </c>
@@ -4418,7 +4387,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>125893564</v>
       </c>
@@ -4456,7 +4425,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>125893722</v>
       </c>
@@ -4494,7 +4463,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>125895193</v>
       </c>
@@ -4532,7 +4501,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>125896177</v>
       </c>
@@ -4570,7 +4539,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>125898007</v>
       </c>
@@ -4608,7 +4577,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>125900254</v>
       </c>
@@ -4646,7 +4615,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>125901787</v>
       </c>
@@ -4684,7 +4653,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>125901795</v>
       </c>
@@ -4722,7 +4691,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>125903262</v>
       </c>
@@ -4760,7 +4729,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>125904221</v>
       </c>
@@ -4798,7 +4767,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>125904238</v>
       </c>
@@ -4836,7 +4805,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>125907420</v>
       </c>
@@ -4874,7 +4843,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>125907797</v>
       </c>
@@ -4912,7 +4881,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>125908056</v>
       </c>
@@ -4950,7 +4919,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>125908177</v>
       </c>
@@ -4988,7 +4957,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>125908231</v>
       </c>
@@ -5026,7 +4995,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>125908843</v>
       </c>
@@ -5064,7 +5033,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>125909142</v>
       </c>
@@ -5102,7 +5071,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>125909933</v>
       </c>
@@ -5140,7 +5109,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>125910114</v>
       </c>
@@ -5178,7 +5147,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>125910400</v>
       </c>
@@ -5216,7 +5185,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>125910838</v>
       </c>
@@ -5254,7 +5223,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>125912176</v>
       </c>
@@ -5292,7 +5261,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>125912843</v>
       </c>
@@ -5330,7 +5299,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>125913133</v>
       </c>
@@ -5368,7 +5337,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>125913427</v>
       </c>
@@ -5406,7 +5375,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>125914356</v>
       </c>
@@ -5444,7 +5413,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>125914668</v>
       </c>
@@ -5482,7 +5451,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>125914978</v>
       </c>
@@ -5520,7 +5489,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>125918666</v>
       </c>
@@ -5558,7 +5527,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>125920065</v>
       </c>
@@ -5596,7 +5565,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>125924508</v>
       </c>
@@ -5634,7 +5603,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>125926112</v>
       </c>
@@ -5672,7 +5641,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>125927235</v>
       </c>
@@ -5710,7 +5679,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>125927477</v>
       </c>
@@ -5748,7 +5717,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>125927712</v>
       </c>
@@ -5786,7 +5755,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>125927811</v>
       </c>
@@ -5824,7 +5793,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>125928500</v>
       </c>
@@ -5862,7 +5831,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>125928781</v>
       </c>
@@ -5900,7 +5869,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>125928935</v>
       </c>
@@ -5938,7 +5907,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>125929845</v>
       </c>
@@ -5976,7 +5945,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>125930432</v>
       </c>
@@ -6014,7 +5983,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>125931903</v>
       </c>
@@ -6052,7 +6021,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>125932521</v>
       </c>
@@ -6090,7 +6059,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>125932669</v>
       </c>
@@ -6128,7 +6097,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>125933582</v>
       </c>
@@ -6166,7 +6135,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>125933608</v>
       </c>
@@ -6204,7 +6173,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>125935767</v>
       </c>
@@ -6242,7 +6211,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>125938612</v>
       </c>
@@ -6280,7 +6249,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>125944749</v>
       </c>
@@ -6318,7 +6287,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>125945240</v>
       </c>
@@ -6356,7 +6325,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>125949456</v>
       </c>
@@ -6394,7 +6363,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>125958349</v>
       </c>
@@ -6432,7 +6401,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>125958503</v>
       </c>
@@ -6470,7 +6439,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>125960344</v>
       </c>
@@ -6508,7 +6477,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>125962131</v>
       </c>
@@ -6546,7 +6515,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>125965767</v>
       </c>
@@ -6584,7 +6553,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>125965877</v>
       </c>
@@ -6622,7 +6591,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>125969356</v>
       </c>
@@ -6660,7 +6629,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>125971901</v>
       </c>
@@ -6698,7 +6667,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>125976084</v>
       </c>
@@ -6736,7 +6705,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>125976278</v>
       </c>
@@ -6774,7 +6743,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>125977146</v>
       </c>
@@ -6812,7 +6781,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>125977504</v>
       </c>
@@ -6850,7 +6819,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>125981162</v>
       </c>
@@ -6888,7 +6857,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>125983181</v>
       </c>
@@ -6926,7 +6895,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>125983593</v>
       </c>
@@ -6964,7 +6933,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>125984782</v>
       </c>
@@ -7002,7 +6971,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>125992174</v>
       </c>
@@ -7040,7 +7009,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>125992452</v>
       </c>
@@ -7078,7 +7047,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>125997050</v>
       </c>
@@ -7116,7 +7085,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>126009389</v>
       </c>
@@ -7154,7 +7123,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>126012544</v>
       </c>
@@ -7192,7 +7161,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>126013965</v>
       </c>
@@ -7230,7 +7199,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>126015225</v>
       </c>
@@ -7268,7 +7237,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>126015257</v>
       </c>
@@ -7306,7 +7275,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>126020235</v>
       </c>
@@ -7344,7 +7313,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>126028210</v>
       </c>
@@ -7382,7 +7351,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>126028956</v>
       </c>
@@ -7420,7 +7389,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>126029328</v>
       </c>
@@ -7458,7 +7427,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>126029650</v>
       </c>
@@ -7496,7 +7465,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>126029868</v>
       </c>
@@ -7534,7 +7503,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>126033233</v>
       </c>
@@ -7572,7 +7541,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>126036666</v>
       </c>
@@ -7610,7 +7579,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>126037292</v>
       </c>
@@ -7648,7 +7617,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>126040785</v>
       </c>
@@ -7686,7 +7655,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>126040979</v>
       </c>
@@ -7724,7 +7693,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>126041187</v>
       </c>
@@ -7762,7 +7731,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>126043144</v>
       </c>
@@ -7800,7 +7769,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>126045060</v>
       </c>
@@ -7838,7 +7807,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>126045520</v>
       </c>
@@ -7876,7 +7845,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>126049650</v>
       </c>
@@ -7914,7 +7883,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>126051286</v>
       </c>
@@ -7952,7 +7921,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>126052567</v>
       </c>
@@ -7990,7 +7959,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>126057040</v>
       </c>
@@ -8028,7 +7997,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>126057529</v>
       </c>
@@ -8066,7 +8035,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>126057835</v>
       </c>
@@ -8104,7 +8073,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>126058412</v>
       </c>
@@ -8142,7 +8111,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>126063955</v>
       </c>
@@ -8180,7 +8149,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>126064498</v>
       </c>
@@ -8218,7 +8187,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>126065211</v>
       </c>
@@ -8256,7 +8225,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>126074608</v>
       </c>
@@ -8294,7 +8263,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>126078394</v>
       </c>
@@ -8332,7 +8301,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>126080342</v>
       </c>
@@ -8370,7 +8339,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>126082448</v>
       </c>
@@ -8408,7 +8377,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>126082622</v>
       </c>
@@ -8446,7 +8415,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>126084723</v>
       </c>
@@ -8484,7 +8453,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>126086747</v>
       </c>
@@ -8522,7 +8491,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>126088025</v>
       </c>
@@ -8560,7 +8529,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>126088302</v>
       </c>
@@ -8598,7 +8567,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>126088413</v>
       </c>
@@ -8636,7 +8605,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>126088528</v>
       </c>
@@ -8674,7 +8643,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>126089277</v>
       </c>
@@ -8712,7 +8681,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>126089435</v>
       </c>
@@ -8750,7 +8719,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>126090634</v>
       </c>
@@ -8788,7 +8757,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>126093282</v>
       </c>
@@ -8826,7 +8795,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>126093649</v>
       </c>
@@ -8864,7 +8833,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>126097132</v>
       </c>
@@ -8902,7 +8871,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126098812</v>
       </c>
@@ -8940,7 +8909,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>126099189</v>
       </c>
@@ -8978,7 +8947,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>126099880</v>
       </c>
@@ -9016,7 +8985,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>126100047</v>
       </c>
@@ -9054,7 +9023,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>126101516</v>
       </c>
@@ -9092,7 +9061,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>126102394</v>
       </c>
@@ -9130,7 +9099,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>126104952</v>
       </c>
@@ -9168,7 +9137,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>126106789</v>
       </c>
@@ -9206,7 +9175,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>126111482</v>
       </c>
@@ -9244,7 +9213,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>126111872</v>
       </c>
@@ -9282,7 +9251,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>126119068</v>
       </c>
@@ -9320,7 +9289,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>126120069</v>
       </c>
@@ -9358,7 +9327,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>126120915</v>
       </c>
@@ -9396,7 +9365,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>126120976</v>
       </c>
@@ -9434,7 +9403,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>126122910</v>
       </c>
@@ -9472,7 +9441,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>126130699</v>
       </c>
@@ -9510,7 +9479,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>126131117</v>
       </c>
@@ -9548,7 +9517,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>126136404</v>
       </c>
@@ -9586,7 +9555,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>126140055</v>
       </c>
@@ -9624,7 +9593,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>126147040</v>
       </c>
@@ -9662,7 +9631,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>126155748</v>
       </c>
@@ -9700,7 +9669,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>126155838</v>
       </c>
@@ -9738,7 +9707,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>126157906</v>
       </c>
@@ -9776,7 +9745,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>126158151</v>
       </c>
@@ -9814,7 +9783,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>126162518</v>
       </c>
@@ -9852,7 +9821,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>126164369</v>
       </c>
@@ -9890,7 +9859,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>126164882</v>
       </c>
@@ -9928,7 +9897,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>126165476</v>
       </c>
@@ -9966,7 +9935,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>126165996</v>
       </c>
@@ -10004,7 +9973,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>126167070</v>
       </c>
@@ -10042,7 +10011,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>126168025</v>
       </c>
@@ -10080,7 +10049,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>126168249</v>
       </c>
@@ -10118,7 +10087,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>126173180</v>
       </c>
@@ -10156,7 +10125,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>126174316</v>
       </c>
@@ -10194,7 +10163,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>126174669</v>
       </c>
@@ -10232,7 +10201,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>126176463</v>
       </c>
@@ -10270,7 +10239,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>126176884</v>
       </c>
@@ -10308,7 +10277,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>126185047</v>
       </c>
@@ -10346,7 +10315,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>126185760</v>
       </c>
@@ -10384,7 +10353,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>126187183</v>
       </c>
@@ -10422,7 +10391,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>126187745</v>
       </c>
@@ -10460,7 +10429,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>126192174</v>
       </c>
@@ -10498,7 +10467,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>126192469</v>
       </c>
@@ -10536,7 +10505,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>126192814</v>
       </c>
@@ -10574,7 +10543,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>126193665</v>
       </c>
@@ -10612,7 +10581,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>126193855</v>
       </c>
@@ -10650,7 +10619,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>126194373</v>
       </c>
@@ -10688,7 +10657,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>126195588</v>
       </c>
@@ -10726,7 +10695,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>126197992</v>
       </c>
@@ -10764,7 +10733,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>126198450</v>
       </c>
@@ -10802,7 +10771,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>126198510</v>
       </c>
@@ -10840,7 +10809,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>126198929</v>
       </c>
@@ -10878,7 +10847,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>126201454</v>
       </c>
@@ -10916,7 +10885,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>126201460</v>
       </c>
@@ -10954,7 +10923,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>126201930</v>
       </c>
@@ -10992,7 +10961,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>126201991</v>
       </c>
@@ -11030,7 +10999,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>126212316</v>
       </c>
@@ -11068,7 +11037,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>126213617</v>
       </c>
@@ -11106,7 +11075,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>126216332</v>
       </c>
@@ -11144,7 +11113,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>126218950</v>
       </c>
@@ -11182,7 +11151,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>126230676</v>
       </c>
@@ -11220,7 +11189,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>126231536</v>
       </c>
@@ -11258,7 +11227,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>126237618</v>
       </c>
@@ -11296,7 +11265,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>126245598</v>
       </c>
@@ -11334,7 +11303,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>126265244</v>
       </c>
@@ -11372,7 +11341,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>126265499</v>
       </c>
@@ -11410,7 +11379,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>126266542</v>
       </c>
@@ -11448,7 +11417,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>126268776</v>
       </c>
@@ -11486,7 +11455,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>126280119</v>
       </c>
@@ -11524,7 +11493,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>126280477</v>
       </c>
@@ -11562,7 +11531,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>126281587</v>
       </c>
@@ -11600,7 +11569,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>126281992</v>
       </c>
@@ -11669,31 +11638,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D2B01D-303A-4156-984A-A289EEBF737A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67223145-D046-4016-9EF9-233676816943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$155</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q102"/>
+  <dimension ref="A1:Q155"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,7 +585,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>127578014</v>
+        <v>127588906</v>
       </c>
       <c r="E2">
         <v>1211</v>
@@ -594,7 +594,7 @@
         <v>45419</v>
       </c>
       <c r="G2" s="2">
-        <v>45418</v>
+        <v>45419</v>
       </c>
       <c r="I2">
         <v>42</v>
@@ -623,16 +623,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>127583908</v>
+        <v>127595033</v>
       </c>
       <c r="E3">
         <v>1211</v>
       </c>
       <c r="F3" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G3" s="2">
         <v>45419</v>
-      </c>
-      <c r="G3" s="2">
-        <v>45418</v>
       </c>
       <c r="I3">
         <v>42</v>
@@ -661,22 +661,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>123977991</v>
+        <v>127598911</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45419</v>
+        <v>45420</v>
       </c>
       <c r="G4" s="2">
-        <v>45419</v>
+        <v>45420</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>124043012</v>
+        <v>127600395</v>
       </c>
       <c r="E5">
         <v>1211</v>
@@ -708,13 +708,13 @@
         <v>45420</v>
       </c>
       <c r="G5" s="2">
-        <v>45419</v>
+        <v>45420</v>
       </c>
       <c r="I5">
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>124056414</v>
+        <v>127604612</v>
       </c>
       <c r="E6">
         <v>1211</v>
@@ -752,7 +752,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -775,13 +775,13 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>124378501</v>
+        <v>127605783</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G7" s="2">
         <v>45420</v>
@@ -790,7 +790,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -813,13 +813,13 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>124463914</v>
+        <v>127610407</v>
       </c>
       <c r="E8">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G8" s="2">
         <v>45420</v>
@@ -828,7 +828,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -851,22 +851,22 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>124611138</v>
+        <v>127620258</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G9" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -889,22 +889,22 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>124879412</v>
+        <v>127621797</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G10" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="I10">
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -927,22 +927,22 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>124948371</v>
+        <v>127623456</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="G11" s="2">
-        <v>45418</v>
+        <v>45421</v>
       </c>
       <c r="I11">
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -965,22 +965,22 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>125599664</v>
+        <v>127626165</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G12" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="I12">
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>125814482</v>
+        <v>123999748</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45420</v>
+        <v>45423</v>
       </c>
       <c r="G13" s="2">
-        <v>45419</v>
+        <v>45423</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>125933586</v>
+        <v>124010504</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="G14" s="2">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>126359183</v>
+        <v>124116058</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45420</v>
+        <v>45423</v>
       </c>
       <c r="G15" s="2">
-        <v>45420</v>
+        <v>45423</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>126496494</v>
+        <v>124229268</v>
       </c>
       <c r="E16">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="G16" s="2">
-        <v>45414</v>
+        <v>45422</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>126521053</v>
+        <v>124231591</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G17" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>126563728</v>
+        <v>124263771</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="G18" s="2">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,13 +1231,13 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>126595878</v>
+        <v>124482647</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="G19" s="2">
         <v>45420</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>126737102</v>
+        <v>124685437</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G20" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>126995189</v>
+        <v>124718126</v>
       </c>
       <c r="E21">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G21" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>127334175</v>
+        <v>124774467</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G22" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="I22">
         <v>42</v>
@@ -1383,22 +1383,22 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>127472186</v>
+        <v>124810592</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45408</v>
+        <v>45422</v>
       </c>
       <c r="G23" s="2">
-        <v>45407</v>
+        <v>45422</v>
       </c>
       <c r="I23">
         <v>42</v>
       </c>
       <c r="J23">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1421,16 +1421,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>127499597</v>
+        <v>124998917</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45415</v>
+        <v>45423</v>
       </c>
       <c r="G24" s="2">
-        <v>45409</v>
+        <v>45421</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1459,22 +1459,22 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>127504091</v>
+        <v>125035729</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="G25" s="2">
-        <v>45411</v>
+        <v>45421</v>
       </c>
       <c r="I25">
         <v>42</v>
       </c>
       <c r="J25">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>127513307</v>
+        <v>125102890</v>
       </c>
       <c r="E26">
         <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="G26" s="2">
-        <v>45411</v>
+        <v>45422</v>
       </c>
       <c r="I26">
         <v>42</v>
       </c>
       <c r="J26">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>127532403</v>
+        <v>125132910</v>
       </c>
       <c r="E27">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45415</v>
+        <v>45422</v>
       </c>
       <c r="G27" s="2">
-        <v>45414</v>
+        <v>45422</v>
       </c>
       <c r="I27">
         <v>42</v>
       </c>
       <c r="J27">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>127559170</v>
+        <v>125189616</v>
       </c>
       <c r="E28">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45416</v>
+        <v>45422</v>
       </c>
       <c r="G28" s="2">
-        <v>45415</v>
+        <v>45422</v>
       </c>
       <c r="I28">
         <v>42</v>
       </c>
       <c r="J28">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -1611,22 +1611,22 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>126954503</v>
+        <v>125191992</v>
       </c>
       <c r="E29">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45378</v>
+        <v>45421</v>
       </c>
       <c r="G29" s="2">
-        <v>45378</v>
+        <v>45421</v>
       </c>
       <c r="I29">
         <v>42</v>
       </c>
       <c r="J29">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>127515920</v>
+        <v>125205423</v>
       </c>
       <c r="E30">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="G30" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="I30">
         <v>42</v>
       </c>
       <c r="J30">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1687,22 +1687,22 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>127515922</v>
+        <v>125223046</v>
       </c>
       <c r="E31">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="G31" s="2">
-        <v>45412</v>
+        <v>45419</v>
       </c>
       <c r="I31">
         <v>42</v>
       </c>
       <c r="J31">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>127515924</v>
+        <v>125275645</v>
       </c>
       <c r="E32">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>45412</v>
+        <v>45423</v>
       </c>
       <c r="G32" s="2">
-        <v>45412</v>
+        <v>45423</v>
       </c>
       <c r="I32">
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -1763,22 +1763,22 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>127515977</v>
+        <v>125567560</v>
       </c>
       <c r="E33">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F33" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="G33" s="2">
-        <v>45412</v>
+        <v>45420</v>
       </c>
       <c r="I33">
         <v>42</v>
       </c>
       <c r="J33">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -1801,22 +1801,22 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>127517736</v>
+        <v>125587833</v>
       </c>
       <c r="E34">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F34" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="G34" s="2">
-        <v>45412</v>
+        <v>45418</v>
       </c>
       <c r="I34">
         <v>42</v>
       </c>
       <c r="J34">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -1839,22 +1839,22 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>127518122</v>
+        <v>125592672</v>
       </c>
       <c r="E35">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F35" s="2">
-        <v>45412</v>
+        <v>45423</v>
       </c>
       <c r="G35" s="2">
-        <v>45412</v>
+        <v>45423</v>
       </c>
       <c r="I35">
         <v>42</v>
       </c>
       <c r="J35">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>127522505</v>
+        <v>125626824</v>
       </c>
       <c r="E36">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F36" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="G36" s="2">
-        <v>45412</v>
+        <v>45419</v>
       </c>
       <c r="I36">
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -1915,22 +1915,22 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>127522929</v>
+        <v>125696467</v>
       </c>
       <c r="E37">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F37" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="G37" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="I37">
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>127524781</v>
+        <v>125717979</v>
       </c>
       <c r="E38">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="G38" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="I38">
         <v>42</v>
       </c>
       <c r="J38">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -1991,22 +1991,22 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>127527159</v>
+        <v>125744890</v>
       </c>
       <c r="E39">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F39" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="G39" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="I39">
         <v>42</v>
       </c>
       <c r="J39">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>127527565</v>
+        <v>126124268</v>
       </c>
       <c r="E40">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F40" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="G40" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="I40">
         <v>42</v>
       </c>
       <c r="J40">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2067,22 +2067,22 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>127527762</v>
+        <v>126138124</v>
       </c>
       <c r="E41">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F41" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="G41" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>127528749</v>
+        <v>126152073</v>
       </c>
       <c r="E42">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F42" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="G42" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2143,22 +2143,22 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>127508268</v>
+        <v>126152382</v>
       </c>
       <c r="E43">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F43" s="2">
-        <v>45421</v>
+        <v>45422</v>
       </c>
       <c r="G43" s="2">
-        <v>45411</v>
+        <v>45419</v>
       </c>
       <c r="I43">
         <v>42</v>
       </c>
       <c r="J43">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>127508767</v>
+        <v>126164146</v>
       </c>
       <c r="E44">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F44" s="2">
-        <v>45421</v>
+        <v>45422</v>
       </c>
       <c r="G44" s="2">
-        <v>45411</v>
+        <v>45422</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2219,22 +2219,22 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>127509574</v>
+        <v>126267937</v>
       </c>
       <c r="E45">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F45" s="2">
-        <v>45421</v>
+        <v>45423</v>
       </c>
       <c r="G45" s="2">
-        <v>45411</v>
+        <v>45423</v>
       </c>
       <c r="I45">
         <v>42</v>
       </c>
       <c r="J45">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>127509623</v>
+        <v>126321161</v>
       </c>
       <c r="E46">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F46" s="2">
         <v>45421</v>
       </c>
       <c r="G46" s="2">
-        <v>45411</v>
+        <v>45419</v>
       </c>
       <c r="I46">
         <v>42</v>
       </c>
       <c r="J46">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2295,22 +2295,22 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>127509629</v>
+        <v>126323517</v>
       </c>
       <c r="E47">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F47" s="2">
         <v>45421</v>
       </c>
       <c r="G47" s="2">
-        <v>45411</v>
+        <v>45421</v>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2333,22 +2333,22 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>127509671</v>
+        <v>126336686</v>
       </c>
       <c r="E48">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F48" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G48" s="2">
         <v>45421</v>
       </c>
-      <c r="G48" s="2">
-        <v>45411</v>
-      </c>
       <c r="I48">
         <v>42</v>
       </c>
       <c r="J48">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2371,22 +2371,22 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>127510059</v>
+        <v>126410600</v>
       </c>
       <c r="E49">
-        <v>609</v>
+        <v>1212</v>
       </c>
       <c r="F49" s="2">
-        <v>45421</v>
+        <v>45422</v>
       </c>
       <c r="G49" s="2">
-        <v>45411</v>
+        <v>45422</v>
       </c>
       <c r="I49">
         <v>42</v>
       </c>
       <c r="J49">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>127510303</v>
+        <v>126448809</v>
       </c>
       <c r="E50">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F50" s="2">
-        <v>45421</v>
+        <v>45422</v>
       </c>
       <c r="G50" s="2">
-        <v>45411</v>
+        <v>45422</v>
       </c>
       <c r="I50">
         <v>42</v>
       </c>
       <c r="J50">
-        <v>8003</v>
+        <v>8001</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2447,22 +2447,22 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>127510707</v>
+        <v>126576610</v>
       </c>
       <c r="E51">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F51" s="2">
         <v>45421</v>
       </c>
       <c r="G51" s="2">
-        <v>45411</v>
+        <v>45418</v>
       </c>
       <c r="I51">
         <v>42</v>
       </c>
       <c r="J51">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2485,22 +2485,22 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>127511145</v>
+        <v>126623471</v>
       </c>
       <c r="E52">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F52" s="2">
         <v>45421</v>
       </c>
       <c r="G52" s="2">
-        <v>45411</v>
+        <v>45421</v>
       </c>
       <c r="I52">
         <v>42</v>
       </c>
       <c r="J52">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>127511751</v>
+        <v>126627134</v>
       </c>
       <c r="E53">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F53" s="2">
-        <v>45421</v>
+        <v>45422</v>
       </c>
       <c r="G53" s="2">
-        <v>45411</v>
+        <v>45422</v>
       </c>
       <c r="I53">
         <v>42</v>
       </c>
       <c r="J53">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L53">
         <v>0</v>
@@ -2561,22 +2561,22 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>127512479</v>
+        <v>126659149</v>
       </c>
       <c r="E54">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F54" s="2">
-        <v>45421</v>
+        <v>45422</v>
       </c>
       <c r="G54" s="2">
-        <v>45411</v>
+        <v>45420</v>
       </c>
       <c r="I54">
         <v>42</v>
       </c>
       <c r="J54">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -2599,22 +2599,22 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>127514314</v>
+        <v>126699438</v>
       </c>
       <c r="E55">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F55" s="2">
-        <v>45421</v>
+        <v>45422</v>
       </c>
       <c r="G55" s="2">
-        <v>45411</v>
+        <v>45422</v>
       </c>
       <c r="I55">
         <v>42</v>
       </c>
       <c r="J55">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -2637,22 +2637,22 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>127514370</v>
+        <v>126721524</v>
       </c>
       <c r="E56">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F56" s="2">
-        <v>45421</v>
+        <v>45422</v>
       </c>
       <c r="G56" s="2">
-        <v>45411</v>
+        <v>45422</v>
       </c>
       <c r="I56">
         <v>42</v>
       </c>
       <c r="J56">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -2675,22 +2675,22 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>127517121</v>
+        <v>126734527</v>
       </c>
       <c r="E57">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F57" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="G57" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="I57">
         <v>42</v>
       </c>
       <c r="J57">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -2713,22 +2713,22 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>127517195</v>
+        <v>126914404</v>
       </c>
       <c r="E58">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F58" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="G58" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="I58">
         <v>42</v>
       </c>
       <c r="J58">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -2751,22 +2751,22 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>127518114</v>
+        <v>126924317</v>
       </c>
       <c r="E59">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F59" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="G59" s="2">
-        <v>45412</v>
+        <v>45420</v>
       </c>
       <c r="I59">
         <v>42</v>
       </c>
       <c r="J59">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -2789,22 +2789,22 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>127519262</v>
+        <v>126926643</v>
       </c>
       <c r="E60">
-        <v>609</v>
+        <v>1211</v>
       </c>
       <c r="F60" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="G60" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="I60">
         <v>42</v>
       </c>
       <c r="J60">
-        <v>1117</v>
+        <v>8001</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -2827,22 +2827,22 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>127522934</v>
+        <v>126979905</v>
       </c>
       <c r="E61">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F61" s="2">
-        <v>45412</v>
+        <v>45421</v>
       </c>
       <c r="G61" s="2">
-        <v>45412</v>
+        <v>45419</v>
       </c>
       <c r="I61">
         <v>42</v>
       </c>
       <c r="J61">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -2865,22 +2865,22 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>127523827</v>
+        <v>126993832</v>
       </c>
       <c r="E62">
-        <v>609</v>
+        <v>1212</v>
       </c>
       <c r="F62" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="G62" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="I62">
         <v>42</v>
       </c>
       <c r="J62">
-        <v>1117</v>
+        <v>8001</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -2903,22 +2903,22 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>127526962</v>
+        <v>127057150</v>
       </c>
       <c r="E63">
-        <v>609</v>
+        <v>1212</v>
       </c>
       <c r="F63" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="G63" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="I63">
         <v>42</v>
       </c>
       <c r="J63">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -2941,22 +2941,22 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>127528497</v>
+        <v>127299192</v>
       </c>
       <c r="E64">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F64" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="G64" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="I64">
         <v>42</v>
       </c>
       <c r="J64">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>127571444</v>
+        <v>127331404</v>
       </c>
       <c r="E65">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F65" s="2">
-        <v>45418</v>
+        <v>45422</v>
       </c>
       <c r="G65" s="2">
-        <v>45418</v>
+        <v>45422</v>
       </c>
       <c r="I65">
         <v>42</v>
       </c>
       <c r="J65">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>127580488</v>
+        <v>127364165</v>
       </c>
       <c r="E66">
         <v>1211</v>
       </c>
       <c r="F66" s="2">
-        <v>45418</v>
+        <v>45422</v>
       </c>
       <c r="G66" s="2">
-        <v>45418</v>
+        <v>45422</v>
       </c>
       <c r="I66">
         <v>42</v>
       </c>
       <c r="J66">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>127591293</v>
+        <v>127368061</v>
       </c>
       <c r="E67">
         <v>1211</v>
       </c>
       <c r="F67" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="G67" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="I67">
         <v>42</v>
       </c>
       <c r="J67">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L67">
         <v>0</v>
@@ -3093,22 +3093,22 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>127598848</v>
+        <v>127394918</v>
       </c>
       <c r="E68">
         <v>1211</v>
       </c>
       <c r="F68" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G68" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="I68">
         <v>42</v>
       </c>
       <c r="J68">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>127600473</v>
+        <v>127413677</v>
       </c>
       <c r="E69">
         <v>1211</v>
       </c>
       <c r="F69" s="2">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="G69" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="I69">
         <v>42</v>
       </c>
       <c r="J69">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -3169,22 +3169,22 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>127601057</v>
+        <v>127474021</v>
       </c>
       <c r="E70">
         <v>1211</v>
       </c>
       <c r="F70" s="2">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="G70" s="2">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="I70">
         <v>42</v>
       </c>
       <c r="J70">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>127602293</v>
+        <v>127512624</v>
       </c>
       <c r="E71">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F71" s="2">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="G71" s="2">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="I71">
         <v>42</v>
       </c>
       <c r="J71">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -3245,22 +3245,22 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>127602407</v>
+        <v>110074933</v>
       </c>
       <c r="E72">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F72" s="2">
-        <v>45420</v>
+        <v>43453</v>
       </c>
       <c r="G72" s="2">
-        <v>45420</v>
+        <v>43441</v>
       </c>
       <c r="I72">
         <v>42</v>
       </c>
       <c r="J72">
-        <v>715</v>
+        <v>8023</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>127603151</v>
+        <v>127472186</v>
       </c>
       <c r="E73">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F73" s="2">
-        <v>45420</v>
+        <v>45408</v>
       </c>
       <c r="G73" s="2">
-        <v>45420</v>
+        <v>45407</v>
       </c>
       <c r="I73">
         <v>42</v>
       </c>
       <c r="J73">
-        <v>715</v>
+        <v>8021</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -3321,22 +3321,22 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>127603533</v>
+        <v>127504091</v>
       </c>
       <c r="E74">
         <v>1211</v>
       </c>
       <c r="F74" s="2">
-        <v>45420</v>
+        <v>45412</v>
       </c>
       <c r="G74" s="2">
-        <v>45420</v>
+        <v>45411</v>
       </c>
       <c r="I74">
         <v>42</v>
       </c>
       <c r="J74">
-        <v>715</v>
+        <v>8021</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -3359,22 +3359,22 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>127603587</v>
+        <v>127513307</v>
       </c>
       <c r="E75">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F75" s="2">
-        <v>45420</v>
+        <v>45412</v>
       </c>
       <c r="G75" s="2">
-        <v>45420</v>
+        <v>45411</v>
       </c>
       <c r="I75">
         <v>42</v>
       </c>
       <c r="J75">
-        <v>715</v>
+        <v>8021</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -3397,22 +3397,22 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>127603700</v>
+        <v>127532403</v>
       </c>
       <c r="E76">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F76" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="G76" s="2">
-        <v>45420</v>
+        <v>45414</v>
       </c>
       <c r="I76">
         <v>42</v>
       </c>
       <c r="J76">
-        <v>715</v>
+        <v>8021</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -3435,22 +3435,22 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>127606895</v>
+        <v>127559170</v>
       </c>
       <c r="E77">
         <v>1212</v>
       </c>
       <c r="F77" s="2">
-        <v>45420</v>
+        <v>45416</v>
       </c>
       <c r="G77" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="I77">
         <v>42</v>
       </c>
       <c r="J77">
-        <v>715</v>
+        <v>8021</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -3473,22 +3473,22 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>127607612</v>
+        <v>127574714</v>
       </c>
       <c r="E78">
         <v>1212</v>
       </c>
       <c r="F78" s="2">
-        <v>45420</v>
+        <v>45419</v>
       </c>
       <c r="G78" s="2">
-        <v>45420</v>
+        <v>45418</v>
       </c>
       <c r="I78">
         <v>42</v>
       </c>
       <c r="J78">
-        <v>715</v>
+        <v>8021</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>127608815</v>
+        <v>127586030</v>
       </c>
       <c r="E79">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F79" s="2">
         <v>45420</v>
       </c>
       <c r="G79" s="2">
-        <v>45420</v>
+        <v>45419</v>
       </c>
       <c r="I79">
         <v>42</v>
       </c>
       <c r="J79">
-        <v>715</v>
+        <v>8021</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -3549,22 +3549,22 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>127609325</v>
+        <v>127590782</v>
       </c>
       <c r="E80">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F80" s="2">
         <v>45420</v>
       </c>
       <c r="G80" s="2">
-        <v>45420</v>
+        <v>45419</v>
       </c>
       <c r="I80">
         <v>42</v>
       </c>
       <c r="J80">
-        <v>715</v>
+        <v>8021</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -3587,7 +3587,7 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>127610630</v>
+        <v>127596160</v>
       </c>
       <c r="E81">
         <v>1212</v>
@@ -3596,13 +3596,13 @@
         <v>45420</v>
       </c>
       <c r="G81" s="2">
-        <v>45420</v>
+        <v>45419</v>
       </c>
       <c r="I81">
         <v>42</v>
       </c>
       <c r="J81">
-        <v>715</v>
+        <v>8021</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -3625,22 +3625,22 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>127610782</v>
+        <v>126954503</v>
       </c>
       <c r="E82">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F82" s="2">
-        <v>45420</v>
+        <v>45378</v>
       </c>
       <c r="G82" s="2">
-        <v>45420</v>
+        <v>45378</v>
       </c>
       <c r="I82">
         <v>42</v>
       </c>
       <c r="J82">
-        <v>715</v>
+        <v>8017</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -3663,22 +3663,22 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>127611019</v>
+        <v>127534142</v>
       </c>
       <c r="E83">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F83" s="2">
-        <v>45420</v>
+        <v>45414</v>
       </c>
       <c r="G83" s="2">
-        <v>45420</v>
+        <v>45414</v>
       </c>
       <c r="I83">
         <v>42</v>
       </c>
       <c r="J83">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -3701,22 +3701,22 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>127611062</v>
+        <v>127542118</v>
       </c>
       <c r="E84">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F84" s="2">
-        <v>45420</v>
+        <v>45414</v>
       </c>
       <c r="G84" s="2">
-        <v>45420</v>
+        <v>45414</v>
       </c>
       <c r="I84">
         <v>42</v>
       </c>
       <c r="J84">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -3739,22 +3739,22 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>127611214</v>
+        <v>127544459</v>
       </c>
       <c r="E85">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F85" s="2">
-        <v>45420</v>
+        <v>45414</v>
       </c>
       <c r="G85" s="2">
-        <v>45420</v>
+        <v>45414</v>
       </c>
       <c r="I85">
         <v>42</v>
       </c>
       <c r="J85">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -3777,22 +3777,22 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>127611787</v>
+        <v>127549174</v>
       </c>
       <c r="E86">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F86" s="2">
-        <v>45420</v>
+        <v>45419</v>
       </c>
       <c r="G86" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="I86">
         <v>42</v>
       </c>
       <c r="J86">
-        <v>715</v>
+        <v>8013</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -3815,22 +3815,22 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>127611817</v>
+        <v>127550861</v>
       </c>
       <c r="E87">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F87" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="G87" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="I87">
         <v>42</v>
       </c>
       <c r="J87">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -3853,22 +3853,22 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>127614238</v>
+        <v>127551008</v>
       </c>
       <c r="E88">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F88" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="G88" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="I88">
         <v>42</v>
       </c>
       <c r="J88">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -3891,22 +3891,22 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>127616494</v>
+        <v>127552223</v>
       </c>
       <c r="E89">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F89" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="G89" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="I89">
         <v>42</v>
       </c>
       <c r="J89">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -3929,22 +3929,22 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>127616565</v>
+        <v>127552526</v>
       </c>
       <c r="E90">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F90" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="G90" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="I90">
         <v>42</v>
       </c>
       <c r="J90">
-        <v>715</v>
+        <v>8013</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -3967,22 +3967,22 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>127618308</v>
+        <v>127552694</v>
       </c>
       <c r="E91">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F91" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="G91" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="I91">
         <v>42</v>
       </c>
       <c r="J91">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>127618684</v>
+        <v>127556719</v>
       </c>
       <c r="E92">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F92" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="G92" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="I92">
         <v>42</v>
       </c>
       <c r="J92">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -4043,22 +4043,22 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>127618800</v>
+        <v>127559436</v>
       </c>
       <c r="E93">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F93" s="2">
-        <v>45421</v>
+        <v>45423</v>
       </c>
       <c r="G93" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="I93">
         <v>42</v>
       </c>
       <c r="J93">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -4081,22 +4081,22 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>127619032</v>
+        <v>127562876</v>
       </c>
       <c r="E94">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F94" s="2">
-        <v>45421</v>
+        <v>45419</v>
       </c>
       <c r="G94" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="I94">
         <v>42</v>
       </c>
       <c r="J94">
-        <v>715</v>
+        <v>8013</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -4119,22 +4119,22 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>127619269</v>
+        <v>127564491</v>
       </c>
       <c r="E95">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F95" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="G95" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="I95">
         <v>42</v>
       </c>
       <c r="J95">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -4157,22 +4157,22 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>127620399</v>
+        <v>127542118</v>
       </c>
       <c r="E96">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F96" s="2">
-        <v>45421</v>
+        <v>45414</v>
       </c>
       <c r="G96" s="2">
-        <v>45421</v>
+        <v>45414</v>
       </c>
       <c r="I96">
         <v>42</v>
       </c>
       <c r="J96">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -4195,22 +4195,22 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>127622277</v>
+        <v>127544459</v>
       </c>
       <c r="E97">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F97" s="2">
-        <v>45421</v>
+        <v>45414</v>
       </c>
       <c r="G97" s="2">
-        <v>45421</v>
+        <v>45414</v>
       </c>
       <c r="I97">
         <v>42</v>
       </c>
       <c r="J97">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -4233,22 +4233,22 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>127623751</v>
+        <v>127533433</v>
       </c>
       <c r="E98">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F98" s="2">
-        <v>45421</v>
+        <v>45414</v>
       </c>
       <c r="G98" s="2">
-        <v>45421</v>
+        <v>45414</v>
       </c>
       <c r="I98">
         <v>42</v>
       </c>
       <c r="J98">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -4271,22 +4271,22 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>127624022</v>
+        <v>127533628</v>
       </c>
       <c r="E99">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F99" s="2">
-        <v>45421</v>
+        <v>45414</v>
       </c>
       <c r="G99" s="2">
-        <v>45421</v>
+        <v>45414</v>
       </c>
       <c r="I99">
         <v>42</v>
       </c>
       <c r="J99">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -4309,22 +4309,22 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>127624071</v>
+        <v>127534054</v>
       </c>
       <c r="E100">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F100" s="2">
-        <v>45421</v>
+        <v>45414</v>
       </c>
       <c r="G100" s="2">
-        <v>45421</v>
+        <v>45414</v>
       </c>
       <c r="I100">
         <v>42</v>
       </c>
       <c r="J100">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -4347,22 +4347,22 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>127624357</v>
+        <v>127536309</v>
       </c>
       <c r="E101">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F101" s="2">
-        <v>45421</v>
+        <v>45414</v>
       </c>
       <c r="G101" s="2">
-        <v>45421</v>
+        <v>45414</v>
       </c>
       <c r="I101">
         <v>42</v>
       </c>
       <c r="J101">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -4385,44 +4385,2058 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>127625102</v>
+        <v>127543311</v>
       </c>
       <c r="E102">
+        <v>609</v>
+      </c>
+      <c r="F102" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G102" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I102">
+        <v>42</v>
+      </c>
+      <c r="J102">
+        <v>8004</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>127545463</v>
+      </c>
+      <c r="E103">
+        <v>601</v>
+      </c>
+      <c r="F103" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G103" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I103">
+        <v>42</v>
+      </c>
+      <c r="J103">
+        <v>8004</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>127546045</v>
+      </c>
+      <c r="E104">
+        <v>601</v>
+      </c>
+      <c r="F104" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G104" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I104">
+        <v>42</v>
+      </c>
+      <c r="J104">
+        <v>8004</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>127546154</v>
+      </c>
+      <c r="E105">
+        <v>601</v>
+      </c>
+      <c r="F105" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G105" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I105">
+        <v>42</v>
+      </c>
+      <c r="J105">
+        <v>1117</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>127546690</v>
+      </c>
+      <c r="E106">
+        <v>601</v>
+      </c>
+      <c r="F106" s="2">
+        <v>45414</v>
+      </c>
+      <c r="G106" s="2">
+        <v>45414</v>
+      </c>
+      <c r="I106">
+        <v>42</v>
+      </c>
+      <c r="J106">
+        <v>8004</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>127549808</v>
+      </c>
+      <c r="E107">
+        <v>601</v>
+      </c>
+      <c r="F107" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G107" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I107">
+        <v>42</v>
+      </c>
+      <c r="J107">
+        <v>8004</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>127549970</v>
+      </c>
+      <c r="E108">
+        <v>601</v>
+      </c>
+      <c r="F108" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G108" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I108">
+        <v>42</v>
+      </c>
+      <c r="J108">
+        <v>8004</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>127550043</v>
+      </c>
+      <c r="E109">
+        <v>601</v>
+      </c>
+      <c r="F109" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G109" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I109">
+        <v>42</v>
+      </c>
+      <c r="J109">
+        <v>1117</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>127552386</v>
+      </c>
+      <c r="E110">
+        <v>601</v>
+      </c>
+      <c r="F110" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G110" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I110">
+        <v>42</v>
+      </c>
+      <c r="J110">
+        <v>8004</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>127553235</v>
+      </c>
+      <c r="E111">
+        <v>601</v>
+      </c>
+      <c r="F111" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G111" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I111">
+        <v>42</v>
+      </c>
+      <c r="J111">
+        <v>1117</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>127553323</v>
+      </c>
+      <c r="E112">
+        <v>601</v>
+      </c>
+      <c r="F112" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G112" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I112">
+        <v>42</v>
+      </c>
+      <c r="J112">
+        <v>8004</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>127553396</v>
+      </c>
+      <c r="E113">
+        <v>601</v>
+      </c>
+      <c r="F113" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G113" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I113">
+        <v>42</v>
+      </c>
+      <c r="J113">
+        <v>8004</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>127553437</v>
+      </c>
+      <c r="E114">
+        <v>601</v>
+      </c>
+      <c r="F114" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G114" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I114">
+        <v>42</v>
+      </c>
+      <c r="J114">
+        <v>8004</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>127553486</v>
+      </c>
+      <c r="E115">
+        <v>601</v>
+      </c>
+      <c r="F115" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G115" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I115">
+        <v>42</v>
+      </c>
+      <c r="J115">
+        <v>8004</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>127553515</v>
+      </c>
+      <c r="E116">
+        <v>601</v>
+      </c>
+      <c r="F116" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G116" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I116">
+        <v>42</v>
+      </c>
+      <c r="J116">
+        <v>1117</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>127553612</v>
+      </c>
+      <c r="E117">
+        <v>601</v>
+      </c>
+      <c r="F117" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G117" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I117">
+        <v>42</v>
+      </c>
+      <c r="J117">
+        <v>8004</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>127553655</v>
+      </c>
+      <c r="E118">
+        <v>601</v>
+      </c>
+      <c r="F118" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G118" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I118">
+        <v>42</v>
+      </c>
+      <c r="J118">
+        <v>8004</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>127554506</v>
+      </c>
+      <c r="E119">
+        <v>601</v>
+      </c>
+      <c r="F119" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G119" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I119">
+        <v>42</v>
+      </c>
+      <c r="J119">
+        <v>8004</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>127555101</v>
+      </c>
+      <c r="E120">
+        <v>601</v>
+      </c>
+      <c r="F120" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G120" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I120">
+        <v>42</v>
+      </c>
+      <c r="J120">
+        <v>8004</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>127555739</v>
+      </c>
+      <c r="E121">
+        <v>601</v>
+      </c>
+      <c r="F121" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G121" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I121">
+        <v>42</v>
+      </c>
+      <c r="J121">
+        <v>8004</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>127556130</v>
+      </c>
+      <c r="E122">
+        <v>601</v>
+      </c>
+      <c r="F122" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G122" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I122">
+        <v>42</v>
+      </c>
+      <c r="J122">
+        <v>8004</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>127556443</v>
+      </c>
+      <c r="E123">
+        <v>601</v>
+      </c>
+      <c r="F123" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G123" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I123">
+        <v>42</v>
+      </c>
+      <c r="J123">
+        <v>8004</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+      <c r="Q123">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>127560800</v>
+      </c>
+      <c r="E124">
+        <v>601</v>
+      </c>
+      <c r="F124" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G124" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I124">
+        <v>42</v>
+      </c>
+      <c r="J124">
+        <v>8004</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>127561777</v>
+      </c>
+      <c r="E125">
+        <v>601</v>
+      </c>
+      <c r="F125" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G125" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I125">
+        <v>42</v>
+      </c>
+      <c r="J125">
+        <v>8004</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="Q125">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>127561855</v>
+      </c>
+      <c r="E126">
+        <v>601</v>
+      </c>
+      <c r="F126" s="2">
+        <v>45415</v>
+      </c>
+      <c r="G126" s="2">
+        <v>45415</v>
+      </c>
+      <c r="I126">
+        <v>42</v>
+      </c>
+      <c r="J126">
+        <v>8004</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>127571444</v>
+      </c>
+      <c r="E127">
+        <v>1212</v>
+      </c>
+      <c r="F127" s="2">
+        <v>45418</v>
+      </c>
+      <c r="G127" s="2">
+        <v>45418</v>
+      </c>
+      <c r="I127">
+        <v>42</v>
+      </c>
+      <c r="J127">
+        <v>715</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>127580488</v>
+      </c>
+      <c r="E128">
         <v>1211</v>
       </c>
-      <c r="F102" s="2">
+      <c r="F128" s="2">
+        <v>45418</v>
+      </c>
+      <c r="G128" s="2">
+        <v>45418</v>
+      </c>
+      <c r="I128">
+        <v>42</v>
+      </c>
+      <c r="J128">
+        <v>715</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>127591293</v>
+      </c>
+      <c r="E129">
+        <v>1211</v>
+      </c>
+      <c r="F129" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G129" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I129">
+        <v>42</v>
+      </c>
+      <c r="J129">
+        <v>715</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+      <c r="Q129">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>127607612</v>
+      </c>
+      <c r="E130">
+        <v>1212</v>
+      </c>
+      <c r="F130" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G130" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I130">
+        <v>42</v>
+      </c>
+      <c r="J130">
+        <v>715</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>127609325</v>
+      </c>
+      <c r="E131">
+        <v>1211</v>
+      </c>
+      <c r="F131" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G131" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I131">
+        <v>42</v>
+      </c>
+      <c r="J131">
+        <v>715</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>127611019</v>
+      </c>
+      <c r="E132">
+        <v>1211</v>
+      </c>
+      <c r="F132" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G132" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I132">
+        <v>42</v>
+      </c>
+      <c r="J132">
+        <v>715</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>127611787</v>
+      </c>
+      <c r="E133">
+        <v>1211</v>
+      </c>
+      <c r="F133" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G133" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I133">
+        <v>42</v>
+      </c>
+      <c r="J133">
+        <v>715</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>127619032</v>
+      </c>
+      <c r="E134">
+        <v>1212</v>
+      </c>
+      <c r="F134" s="2">
         <v>45421</v>
       </c>
-      <c r="G102" s="2">
+      <c r="G134" s="2">
         <v>45421</v>
       </c>
-      <c r="I102">
-        <v>42</v>
-      </c>
-      <c r="J102">
+      <c r="I134">
+        <v>42</v>
+      </c>
+      <c r="J134">
         <v>715</v>
       </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-      <c r="M102">
-        <v>0</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
-        <v>0</v>
-      </c>
-      <c r="P102">
-        <v>0</v>
-      </c>
-      <c r="Q102">
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>127624022</v>
+      </c>
+      <c r="E135">
+        <v>1211</v>
+      </c>
+      <c r="F135" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G135" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I135">
+        <v>42</v>
+      </c>
+      <c r="J135">
+        <v>715</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>127628393</v>
+      </c>
+      <c r="E136">
+        <v>1212</v>
+      </c>
+      <c r="F136" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G136" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I136">
+        <v>42</v>
+      </c>
+      <c r="J136">
+        <v>715</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>127628545</v>
+      </c>
+      <c r="E137">
+        <v>1212</v>
+      </c>
+      <c r="F137" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G137" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I137">
+        <v>42</v>
+      </c>
+      <c r="J137">
+        <v>715</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>127630298</v>
+      </c>
+      <c r="E138">
+        <v>1211</v>
+      </c>
+      <c r="F138" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G138" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I138">
+        <v>42</v>
+      </c>
+      <c r="J138">
+        <v>715</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>127631419</v>
+      </c>
+      <c r="E139">
+        <v>1212</v>
+      </c>
+      <c r="F139" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G139" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I139">
+        <v>42</v>
+      </c>
+      <c r="J139">
+        <v>715</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>127631639</v>
+      </c>
+      <c r="E140">
+        <v>1211</v>
+      </c>
+      <c r="F140" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G140" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I140">
+        <v>42</v>
+      </c>
+      <c r="J140">
+        <v>715</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>127633655</v>
+      </c>
+      <c r="E141">
+        <v>1211</v>
+      </c>
+      <c r="F141" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G141" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I141">
+        <v>42</v>
+      </c>
+      <c r="J141">
+        <v>715</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>127634011</v>
+      </c>
+      <c r="E142">
+        <v>1212</v>
+      </c>
+      <c r="F142" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G142" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I142">
+        <v>42</v>
+      </c>
+      <c r="J142">
+        <v>715</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>127634347</v>
+      </c>
+      <c r="E143">
+        <v>1211</v>
+      </c>
+      <c r="F143" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G143" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I143">
+        <v>42</v>
+      </c>
+      <c r="J143">
+        <v>715</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>127636233</v>
+      </c>
+      <c r="E144">
+        <v>1212</v>
+      </c>
+      <c r="F144" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G144" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I144">
+        <v>42</v>
+      </c>
+      <c r="J144">
+        <v>715</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>0</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>0</v>
+      </c>
+      <c r="Q144">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>127637187</v>
+      </c>
+      <c r="E145">
+        <v>1212</v>
+      </c>
+      <c r="F145" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G145" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I145">
+        <v>42</v>
+      </c>
+      <c r="J145">
+        <v>715</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>0</v>
+      </c>
+      <c r="Q145">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>127637287</v>
+      </c>
+      <c r="E146">
+        <v>1211</v>
+      </c>
+      <c r="F146" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G146" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I146">
+        <v>42</v>
+      </c>
+      <c r="J146">
+        <v>715</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>127639022</v>
+      </c>
+      <c r="E147">
+        <v>1211</v>
+      </c>
+      <c r="F147" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G147" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I147">
+        <v>42</v>
+      </c>
+      <c r="J147">
+        <v>715</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>0</v>
+      </c>
+      <c r="Q147">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>127639025</v>
+      </c>
+      <c r="E148">
+        <v>1211</v>
+      </c>
+      <c r="F148" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G148" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I148">
+        <v>42</v>
+      </c>
+      <c r="J148">
+        <v>715</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>0</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>0</v>
+      </c>
+      <c r="Q148">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>127640122</v>
+      </c>
+      <c r="E149">
+        <v>1211</v>
+      </c>
+      <c r="F149" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G149" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I149">
+        <v>42</v>
+      </c>
+      <c r="J149">
+        <v>715</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <v>0</v>
+      </c>
+      <c r="Q149">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>127640177</v>
+      </c>
+      <c r="E150">
+        <v>1212</v>
+      </c>
+      <c r="F150" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G150" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I150">
+        <v>42</v>
+      </c>
+      <c r="J150">
+        <v>715</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>0</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>0</v>
+      </c>
+      <c r="Q150">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>127640933</v>
+      </c>
+      <c r="E151">
+        <v>1212</v>
+      </c>
+      <c r="F151" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G151" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I151">
+        <v>42</v>
+      </c>
+      <c r="J151">
+        <v>715</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>0</v>
+      </c>
+      <c r="N151">
+        <v>0</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>0</v>
+      </c>
+      <c r="Q151">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>127643154</v>
+      </c>
+      <c r="E152">
+        <v>1211</v>
+      </c>
+      <c r="F152" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G152" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I152">
+        <v>42</v>
+      </c>
+      <c r="J152">
+        <v>715</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>0</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>0</v>
+      </c>
+      <c r="Q152">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>127643336</v>
+      </c>
+      <c r="E153">
+        <v>1212</v>
+      </c>
+      <c r="F153" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G153" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I153">
+        <v>42</v>
+      </c>
+      <c r="J153">
+        <v>715</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>0</v>
+      </c>
+      <c r="Q153">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>127643427</v>
+      </c>
+      <c r="E154">
+        <v>1212</v>
+      </c>
+      <c r="F154" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G154" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I154">
+        <v>42</v>
+      </c>
+      <c r="J154">
+        <v>715</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>0</v>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>0</v>
+      </c>
+      <c r="Q154">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>127644114</v>
+      </c>
+      <c r="E155">
+        <v>1212</v>
+      </c>
+      <c r="F155" s="2">
+        <v>45423</v>
+      </c>
+      <c r="G155" s="2">
+        <v>45423</v>
+      </c>
+      <c r="I155">
+        <v>42</v>
+      </c>
+      <c r="J155">
+        <v>715</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <v>0</v>
+      </c>
+      <c r="Q155">
         <v>61</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q102" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}"/>
+  <autoFilter ref="A1:Q155" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -12012,31 +14026,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9B08607-E0CE-4FBD-9D16-E9D463346826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A1D5C6-83D8-4CBE-BC56-E3DA09268476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -585,22 +585,22 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>127628809</v>
+        <v>124240054</v>
       </c>
       <c r="E2">
         <v>1211</v>
       </c>
       <c r="F2" s="2">
-        <v>45422</v>
+        <v>45426</v>
       </c>
       <c r="G2" s="2">
-        <v>45422</v>
+        <v>45426</v>
       </c>
       <c r="I2">
         <v>42</v>
       </c>
       <c r="J2">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -623,22 +623,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>127629209</v>
+        <v>124445777</v>
       </c>
       <c r="E3">
         <v>1211</v>
       </c>
       <c r="F3" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="G3" s="2">
-        <v>45422</v>
+        <v>45421</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -661,22 +661,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>127629777</v>
+        <v>124492237</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="G4" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,22 +699,22 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>127632784</v>
+        <v>124511324</v>
       </c>
       <c r="E5">
         <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="G5" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="I5">
         <v>42</v>
       </c>
       <c r="J5">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>127636164</v>
+        <v>124635421</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45423</v>
+        <v>45426</v>
       </c>
       <c r="G6" s="2">
         <v>45422</v>
@@ -752,7 +752,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -775,16 +775,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>123817937</v>
+        <v>124714668</v>
       </c>
       <c r="E7">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F7" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G7" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -813,7 +813,7 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>124445777</v>
+        <v>124787316</v>
       </c>
       <c r="E8">
         <v>1211</v>
@@ -822,7 +822,7 @@
         <v>45425</v>
       </c>
       <c r="G8" s="2">
-        <v>45421</v>
+        <v>45425</v>
       </c>
       <c r="I8">
         <v>42</v>
@@ -851,16 +851,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>124492237</v>
+        <v>124920757</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G9" s="2">
-        <v>45425</v>
+        <v>45421</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -889,16 +889,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>124511324</v>
+        <v>125009890</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G10" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -927,16 +927,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>124750211</v>
+        <v>125090798</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G11" s="2">
-        <v>45422</v>
+        <v>45426</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -965,16 +965,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>124787316</v>
+        <v>125187864</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G12" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>125200894</v>
+        <v>125254911</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G13" s="2">
-        <v>45422</v>
+        <v>45426</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>125604061</v>
+        <v>125485448</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G16" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>125773630</v>
+        <v>125588437</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G17" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>125965417</v>
+        <v>125602301</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G18" s="2">
-        <v>45425</v>
+        <v>45422</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,7 +1231,7 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>126062814</v>
+        <v>125604061</v>
       </c>
       <c r="E19">
         <v>1211</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>126410600</v>
+        <v>125773630</v>
       </c>
       <c r="E20">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="G20" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>126448809</v>
+        <v>125965417</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="G21" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1345,7 +1345,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>126572051</v>
+        <v>126062814</v>
       </c>
       <c r="E22">
         <v>1211</v>
@@ -1383,16 +1383,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>126576610</v>
+        <v>126071375</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
+        <v>45426</v>
+      </c>
+      <c r="G23" s="2">
         <v>45421</v>
-      </c>
-      <c r="G23" s="2">
-        <v>45418</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1421,16 +1421,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>126623471</v>
+        <v>126135960</v>
       </c>
       <c r="E24">
         <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45421</v>
+        <v>45426</v>
       </c>
       <c r="G24" s="2">
-        <v>45421</v>
+        <v>45426</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1459,16 +1459,16 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>126627134</v>
+        <v>126264125</v>
       </c>
       <c r="E25">
         <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45422</v>
+        <v>45426</v>
       </c>
       <c r="G25" s="2">
-        <v>45422</v>
+        <v>45426</v>
       </c>
       <c r="I25">
         <v>42</v>
@@ -1497,16 +1497,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>126659149</v>
+        <v>126410600</v>
       </c>
       <c r="E26">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F26" s="2">
         <v>45422</v>
       </c>
       <c r="G26" s="2">
-        <v>45420</v>
+        <v>45422</v>
       </c>
       <c r="I26">
         <v>42</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>126699438</v>
+        <v>126448809</v>
       </c>
       <c r="E27">
         <v>1211</v>
@@ -1573,16 +1573,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>126721524</v>
+        <v>126461863</v>
       </c>
       <c r="E28">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F28" s="2">
-        <v>45422</v>
+        <v>45426</v>
       </c>
       <c r="G28" s="2">
-        <v>45422</v>
+        <v>45426</v>
       </c>
       <c r="I28">
         <v>42</v>
@@ -1611,16 +1611,16 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>126734527</v>
+        <v>126510475</v>
       </c>
       <c r="E29">
         <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45422</v>
+        <v>45426</v>
       </c>
       <c r="G29" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="I29">
         <v>42</v>
@@ -1649,16 +1649,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>126924317</v>
+        <v>126513956</v>
       </c>
       <c r="E30">
         <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45422</v>
+        <v>45426</v>
       </c>
       <c r="G30" s="2">
-        <v>45420</v>
+        <v>45426</v>
       </c>
       <c r="I30">
         <v>42</v>
@@ -1687,16 +1687,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>126926643</v>
+        <v>126572051</v>
       </c>
       <c r="E31">
         <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="G31" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="I31">
         <v>42</v>
@@ -1725,16 +1725,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>126934766</v>
+        <v>126576610</v>
       </c>
       <c r="E32">
         <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>45425</v>
+        <v>45421</v>
       </c>
       <c r="G32" s="2">
-        <v>45425</v>
+        <v>45418</v>
       </c>
       <c r="I32">
         <v>42</v>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>126979905</v>
+        <v>126623471</v>
       </c>
       <c r="E33">
         <v>1211</v>
@@ -1772,7 +1772,7 @@
         <v>45421</v>
       </c>
       <c r="G33" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="I33">
         <v>42</v>
@@ -1801,16 +1801,16 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>126993832</v>
+        <v>126625901</v>
       </c>
       <c r="E34">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F34" s="2">
-        <v>45422</v>
+        <v>45426</v>
       </c>
       <c r="G34" s="2">
-        <v>45422</v>
+        <v>45426</v>
       </c>
       <c r="I34">
         <v>42</v>
@@ -1839,16 +1839,16 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>127049740</v>
+        <v>126627134</v>
       </c>
       <c r="E35">
         <v>1211</v>
       </c>
       <c r="F35" s="2">
-        <v>45425</v>
+        <v>45422</v>
       </c>
       <c r="G35" s="2">
-        <v>45425</v>
+        <v>45422</v>
       </c>
       <c r="I35">
         <v>42</v>
@@ -1877,16 +1877,16 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>127057150</v>
+        <v>126659149</v>
       </c>
       <c r="E36">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F36" s="2">
         <v>45422</v>
       </c>
       <c r="G36" s="2">
-        <v>45422</v>
+        <v>45420</v>
       </c>
       <c r="I36">
         <v>42</v>
@@ -1915,16 +1915,16 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>127212556</v>
+        <v>126699438</v>
       </c>
       <c r="E37">
         <v>1211</v>
       </c>
       <c r="F37" s="2">
-        <v>45425</v>
+        <v>45422</v>
       </c>
       <c r="G37" s="2">
-        <v>45425</v>
+        <v>45422</v>
       </c>
       <c r="I37">
         <v>42</v>
@@ -1953,16 +1953,16 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>127217397</v>
+        <v>126721524</v>
       </c>
       <c r="E38">
         <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>45425</v>
+        <v>45422</v>
       </c>
       <c r="G38" s="2">
-        <v>45425</v>
+        <v>45422</v>
       </c>
       <c r="I38">
         <v>42</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>127299192</v>
+        <v>126728365</v>
       </c>
       <c r="E39">
         <v>1211</v>
       </c>
       <c r="F39" s="2">
-        <v>45422</v>
+        <v>45426</v>
       </c>
       <c r="G39" s="2">
         <v>45422</v>
@@ -2029,7 +2029,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>127331404</v>
+        <v>126734527</v>
       </c>
       <c r="E40">
         <v>1211</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>127364165</v>
+        <v>126924317</v>
       </c>
       <c r="E41">
         <v>1211</v>
@@ -2076,7 +2076,7 @@
         <v>45422</v>
       </c>
       <c r="G41" s="2">
-        <v>45422</v>
+        <v>45420</v>
       </c>
       <c r="I41">
         <v>42</v>
@@ -2105,7 +2105,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>127368061</v>
+        <v>126926643</v>
       </c>
       <c r="E42">
         <v>1211</v>
@@ -2143,16 +2143,16 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>127394918</v>
+        <v>126934766</v>
       </c>
       <c r="E43">
         <v>1211</v>
       </c>
       <c r="F43" s="2">
-        <v>45421</v>
+        <v>45425</v>
       </c>
       <c r="G43" s="2">
-        <v>45421</v>
+        <v>45425</v>
       </c>
       <c r="I43">
         <v>42</v>
@@ -2181,16 +2181,16 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>127455295</v>
+        <v>126979905</v>
       </c>
       <c r="E44">
         <v>1211</v>
       </c>
       <c r="F44" s="2">
-        <v>45425</v>
+        <v>45421</v>
       </c>
       <c r="G44" s="2">
-        <v>45420</v>
+        <v>45419</v>
       </c>
       <c r="I44">
         <v>42</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>127512624</v>
+        <v>126993832</v>
       </c>
       <c r="E45">
         <v>1212</v>
@@ -2257,7 +2257,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>127530897</v>
+        <v>127049740</v>
       </c>
       <c r="E46">
         <v>1211</v>
@@ -2295,16 +2295,16 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>127594837</v>
+        <v>127057150</v>
       </c>
       <c r="E47">
         <v>1212</v>
       </c>
       <c r="F47" s="2">
-        <v>45425</v>
+        <v>45422</v>
       </c>
       <c r="G47" s="2">
-        <v>45425</v>
+        <v>45422</v>
       </c>
       <c r="I47">
         <v>42</v>
@@ -2333,22 +2333,22 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>110074933</v>
+        <v>127212556</v>
       </c>
       <c r="E48">
         <v>1211</v>
       </c>
       <c r="F48" s="2">
-        <v>43453</v>
+        <v>45425</v>
       </c>
       <c r="G48" s="2">
-        <v>43441</v>
+        <v>45425</v>
       </c>
       <c r="I48">
         <v>42</v>
       </c>
       <c r="J48">
-        <v>8023</v>
+        <v>8001</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2371,16 +2371,16 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>123058958</v>
+        <v>127217397</v>
       </c>
       <c r="E49">
         <v>1211</v>
       </c>
       <c r="F49" s="2">
-        <v>44995</v>
+        <v>45425</v>
       </c>
       <c r="G49" s="2">
-        <v>44993</v>
+        <v>45425</v>
       </c>
       <c r="I49">
         <v>42</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>127472186</v>
+        <v>127272776</v>
       </c>
       <c r="E50">
         <v>1211</v>
       </c>
       <c r="F50" s="2">
-        <v>45408</v>
+        <v>45426</v>
       </c>
       <c r="G50" s="2">
-        <v>45407</v>
+        <v>45426</v>
       </c>
       <c r="I50">
         <v>42</v>
       </c>
       <c r="J50">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -2447,22 +2447,22 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>127504091</v>
+        <v>127299192</v>
       </c>
       <c r="E51">
         <v>1211</v>
       </c>
       <c r="F51" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="G51" s="2">
-        <v>45411</v>
+        <v>45422</v>
       </c>
       <c r="I51">
         <v>42</v>
       </c>
       <c r="J51">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L51">
         <v>0</v>
@@ -2485,16 +2485,16 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>127504637</v>
+        <v>127331404</v>
       </c>
       <c r="E52">
         <v>1211</v>
       </c>
       <c r="F52" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="G52" s="2">
-        <v>45411</v>
+        <v>45422</v>
       </c>
       <c r="I52">
         <v>42</v>
@@ -2523,16 +2523,16 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>127507059</v>
+        <v>127364165</v>
       </c>
       <c r="E53">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F53" s="2">
-        <v>45418</v>
+        <v>45422</v>
       </c>
       <c r="G53" s="2">
-        <v>45411</v>
+        <v>45422</v>
       </c>
       <c r="I53">
         <v>42</v>
@@ -2561,22 +2561,22 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>127513307</v>
+        <v>127368061</v>
       </c>
       <c r="E54">
         <v>1211</v>
       </c>
       <c r="F54" s="2">
-        <v>45412</v>
+        <v>45422</v>
       </c>
       <c r="G54" s="2">
-        <v>45411</v>
+        <v>45422</v>
       </c>
       <c r="I54">
         <v>42</v>
       </c>
       <c r="J54">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -2599,22 +2599,22 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>127532403</v>
+        <v>127394918</v>
       </c>
       <c r="E55">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F55" s="2">
-        <v>45415</v>
+        <v>45421</v>
       </c>
       <c r="G55" s="2">
-        <v>45414</v>
+        <v>45421</v>
       </c>
       <c r="I55">
         <v>42</v>
       </c>
       <c r="J55">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -2637,22 +2637,22 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>127596160</v>
+        <v>127408551</v>
       </c>
       <c r="E56">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F56" s="2">
-        <v>45420</v>
+        <v>45426</v>
       </c>
       <c r="G56" s="2">
-        <v>45419</v>
+        <v>45426</v>
       </c>
       <c r="I56">
         <v>42</v>
       </c>
       <c r="J56">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -2675,22 +2675,22 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>127609255</v>
+        <v>127438868</v>
       </c>
       <c r="E57">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F57" s="2">
-        <v>45421</v>
+        <v>45426</v>
       </c>
       <c r="G57" s="2">
-        <v>45420</v>
+        <v>45426</v>
       </c>
       <c r="I57">
         <v>42</v>
       </c>
       <c r="J57">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L57">
         <v>0</v>
@@ -2713,22 +2713,22 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>126954503</v>
+        <v>127455295</v>
       </c>
       <c r="E58">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F58" s="2">
-        <v>45378</v>
+        <v>45425</v>
       </c>
       <c r="G58" s="2">
-        <v>45378</v>
+        <v>45420</v>
       </c>
       <c r="I58">
         <v>42</v>
       </c>
       <c r="J58">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -2751,22 +2751,22 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>127542118</v>
+        <v>127512624</v>
       </c>
       <c r="E59">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F59" s="2">
-        <v>45425</v>
+        <v>45422</v>
       </c>
       <c r="G59" s="2">
-        <v>45414</v>
+        <v>45422</v>
       </c>
       <c r="I59">
         <v>42</v>
       </c>
       <c r="J59">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -2789,22 +2789,22 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>127544459</v>
+        <v>127530897</v>
       </c>
       <c r="E60">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F60" s="2">
         <v>45425</v>
       </c>
       <c r="G60" s="2">
-        <v>45414</v>
+        <v>45425</v>
       </c>
       <c r="I60">
         <v>42</v>
       </c>
       <c r="J60">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -2827,22 +2827,22 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>127549174</v>
+        <v>127594837</v>
       </c>
       <c r="E61">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F61" s="2">
-        <v>45419</v>
+        <v>45425</v>
       </c>
       <c r="G61" s="2">
-        <v>45415</v>
+        <v>45425</v>
       </c>
       <c r="I61">
         <v>42</v>
       </c>
       <c r="J61">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L61">
         <v>0</v>
@@ -2865,22 +2865,22 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>127550861</v>
+        <v>110074933</v>
       </c>
       <c r="E62">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F62" s="2">
-        <v>45415</v>
+        <v>43453</v>
       </c>
       <c r="G62" s="2">
-        <v>45415</v>
+        <v>43441</v>
       </c>
       <c r="I62">
         <v>42</v>
       </c>
       <c r="J62">
-        <v>8004</v>
+        <v>8023</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -2903,22 +2903,22 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>127551008</v>
+        <v>123058958</v>
       </c>
       <c r="E63">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F63" s="2">
-        <v>45415</v>
+        <v>44995</v>
       </c>
       <c r="G63" s="2">
-        <v>45415</v>
+        <v>44993</v>
       </c>
       <c r="I63">
         <v>42</v>
       </c>
       <c r="J63">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -2941,22 +2941,22 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>127552223</v>
+        <v>127472186</v>
       </c>
       <c r="E64">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F64" s="2">
-        <v>45415</v>
+        <v>45408</v>
       </c>
       <c r="G64" s="2">
-        <v>45415</v>
+        <v>45407</v>
       </c>
       <c r="I64">
         <v>42</v>
       </c>
       <c r="J64">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>127552526</v>
+        <v>127504091</v>
       </c>
       <c r="E65">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F65" s="2">
-        <v>45415</v>
+        <v>45412</v>
       </c>
       <c r="G65" s="2">
-        <v>45415</v>
+        <v>45411</v>
       </c>
       <c r="I65">
         <v>42</v>
       </c>
       <c r="J65">
-        <v>8013</v>
+        <v>8021</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>127552694</v>
+        <v>127504637</v>
       </c>
       <c r="E66">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F66" s="2">
-        <v>45415</v>
+        <v>45419</v>
       </c>
       <c r="G66" s="2">
-        <v>45415</v>
+        <v>45411</v>
       </c>
       <c r="I66">
         <v>42</v>
       </c>
       <c r="J66">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>127556719</v>
+        <v>127507059</v>
       </c>
       <c r="E67">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F67" s="2">
-        <v>45415</v>
+        <v>45418</v>
       </c>
       <c r="G67" s="2">
-        <v>45415</v>
+        <v>45411</v>
       </c>
       <c r="I67">
         <v>42</v>
       </c>
       <c r="J67">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L67">
         <v>0</v>
@@ -3093,22 +3093,22 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>127559436</v>
+        <v>127513307</v>
       </c>
       <c r="E68">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F68" s="2">
-        <v>45423</v>
+        <v>45412</v>
       </c>
       <c r="G68" s="2">
-        <v>45415</v>
+        <v>45411</v>
       </c>
       <c r="I68">
         <v>42</v>
       </c>
       <c r="J68">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="L68">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>127562876</v>
+        <v>127532403</v>
       </c>
       <c r="E69">
-        <v>601</v>
+        <v>1213</v>
       </c>
       <c r="F69" s="2">
-        <v>45419</v>
+        <v>45415</v>
       </c>
       <c r="G69" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="I69">
         <v>42</v>
       </c>
       <c r="J69">
-        <v>8013</v>
+        <v>8021</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -3169,22 +3169,22 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>127564491</v>
+        <v>127596160</v>
       </c>
       <c r="E70">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F70" s="2">
-        <v>45415</v>
+        <v>45420</v>
       </c>
       <c r="G70" s="2">
-        <v>45415</v>
+        <v>45419</v>
       </c>
       <c r="I70">
         <v>42</v>
       </c>
       <c r="J70">
-        <v>8004</v>
+        <v>8021</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>127542118</v>
+        <v>127609255</v>
       </c>
       <c r="E71">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F71" s="2">
-        <v>45425</v>
+        <v>45421</v>
       </c>
       <c r="G71" s="2">
-        <v>45414</v>
+        <v>45420</v>
       </c>
       <c r="I71">
         <v>42</v>
       </c>
       <c r="J71">
-        <v>8013</v>
+        <v>8021</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -3245,22 +3245,22 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>127544459</v>
+        <v>126954503</v>
       </c>
       <c r="E72">
         <v>601</v>
       </c>
       <c r="F72" s="2">
-        <v>45425</v>
+        <v>45378</v>
       </c>
       <c r="G72" s="2">
-        <v>45414</v>
+        <v>45378</v>
       </c>
       <c r="I72">
         <v>42</v>
       </c>
       <c r="J72">
-        <v>8013</v>
+        <v>8017</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>127533433</v>
+        <v>127542118</v>
       </c>
       <c r="E73">
         <v>601</v>
       </c>
       <c r="F73" s="2">
-        <v>45414</v>
+        <v>45425</v>
       </c>
       <c r="G73" s="2">
         <v>45414</v>
@@ -3298,7 +3298,7 @@
         <v>42</v>
       </c>
       <c r="J73">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -3321,13 +3321,13 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>127533628</v>
+        <v>127544459</v>
       </c>
       <c r="E74">
         <v>601</v>
       </c>
       <c r="F74" s="2">
-        <v>45414</v>
+        <v>45425</v>
       </c>
       <c r="G74" s="2">
         <v>45414</v>
@@ -3336,7 +3336,7 @@
         <v>42</v>
       </c>
       <c r="J74">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -3359,22 +3359,22 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>127534054</v>
+        <v>127549174</v>
       </c>
       <c r="E75">
         <v>601</v>
       </c>
       <c r="F75" s="2">
-        <v>45414</v>
+        <v>45419</v>
       </c>
       <c r="G75" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I75">
         <v>42</v>
       </c>
       <c r="J75">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -3397,16 +3397,16 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>127536309</v>
+        <v>127550861</v>
       </c>
       <c r="E76">
         <v>601</v>
       </c>
       <c r="F76" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G76" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I76">
         <v>42</v>
@@ -3435,16 +3435,16 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>127543311</v>
+        <v>127551008</v>
       </c>
       <c r="E77">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F77" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G77" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I77">
         <v>42</v>
@@ -3473,16 +3473,16 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>127545463</v>
+        <v>127552223</v>
       </c>
       <c r="E78">
         <v>601</v>
       </c>
       <c r="F78" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G78" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I78">
         <v>42</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>127546045</v>
+        <v>127552526</v>
       </c>
       <c r="E79">
         <v>601</v>
       </c>
       <c r="F79" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G79" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I79">
         <v>42</v>
       </c>
       <c r="J79">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -3549,22 +3549,22 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>127546154</v>
+        <v>127552694</v>
       </c>
       <c r="E80">
         <v>601</v>
       </c>
       <c r="F80" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G80" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I80">
         <v>42</v>
       </c>
       <c r="J80">
-        <v>1117</v>
+        <v>8004</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -3587,16 +3587,16 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>127546690</v>
+        <v>127556719</v>
       </c>
       <c r="E81">
         <v>601</v>
       </c>
       <c r="F81" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="G81" s="2">
-        <v>45414</v>
+        <v>45415</v>
       </c>
       <c r="I81">
         <v>42</v>
@@ -3625,13 +3625,13 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>127549808</v>
+        <v>127559436</v>
       </c>
       <c r="E82">
         <v>601</v>
       </c>
       <c r="F82" s="2">
-        <v>45415</v>
+        <v>45423</v>
       </c>
       <c r="G82" s="2">
         <v>45415</v>
@@ -3640,7 +3640,7 @@
         <v>42</v>
       </c>
       <c r="J82">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -3663,13 +3663,13 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>127549970</v>
+        <v>127562876</v>
       </c>
       <c r="E83">
         <v>601</v>
       </c>
       <c r="F83" s="2">
-        <v>45415</v>
+        <v>45419</v>
       </c>
       <c r="G83" s="2">
         <v>45415</v>
@@ -3678,7 +3678,7 @@
         <v>42</v>
       </c>
       <c r="J83">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -3701,7 +3701,7 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>127550043</v>
+        <v>127564491</v>
       </c>
       <c r="E84">
         <v>601</v>
@@ -3716,7 +3716,7 @@
         <v>42</v>
       </c>
       <c r="J84">
-        <v>1117</v>
+        <v>8004</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -3739,22 +3739,22 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>127552386</v>
+        <v>127542118</v>
       </c>
       <c r="E85">
         <v>601</v>
       </c>
       <c r="F85" s="2">
-        <v>45415</v>
+        <v>45425</v>
       </c>
       <c r="G85" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="I85">
         <v>42</v>
       </c>
       <c r="J85">
-        <v>8004</v>
+        <v>8013</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -3777,22 +3777,22 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>127553235</v>
+        <v>127544459</v>
       </c>
       <c r="E86">
         <v>601</v>
       </c>
       <c r="F86" s="2">
-        <v>45415</v>
+        <v>45425</v>
       </c>
       <c r="G86" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="I86">
         <v>42</v>
       </c>
       <c r="J86">
-        <v>1117</v>
+        <v>8013</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -3815,16 +3815,16 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>127553323</v>
+        <v>127533433</v>
       </c>
       <c r="E87">
         <v>601</v>
       </c>
       <c r="F87" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="G87" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="I87">
         <v>42</v>
@@ -3853,16 +3853,16 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>127553396</v>
+        <v>127533628</v>
       </c>
       <c r="E88">
         <v>601</v>
       </c>
       <c r="F88" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="G88" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="I88">
         <v>42</v>
@@ -3891,16 +3891,16 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>127553437</v>
+        <v>127534054</v>
       </c>
       <c r="E89">
         <v>601</v>
       </c>
       <c r="F89" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="G89" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="I89">
         <v>42</v>
@@ -3929,16 +3929,16 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>127553486</v>
+        <v>127536309</v>
       </c>
       <c r="E90">
         <v>601</v>
       </c>
       <c r="F90" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="G90" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="I90">
         <v>42</v>
@@ -3967,22 +3967,22 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>127553515</v>
+        <v>127543311</v>
       </c>
       <c r="E91">
-        <v>601</v>
+        <v>609</v>
       </c>
       <c r="F91" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="G91" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="I91">
         <v>42</v>
       </c>
       <c r="J91">
-        <v>1117</v>
+        <v>8004</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -4005,16 +4005,16 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>127553612</v>
+        <v>127545463</v>
       </c>
       <c r="E92">
         <v>601</v>
       </c>
       <c r="F92" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="G92" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="I92">
         <v>42</v>
@@ -4043,16 +4043,16 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>127553655</v>
+        <v>127546045</v>
       </c>
       <c r="E93">
         <v>601</v>
       </c>
       <c r="F93" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="G93" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="I93">
         <v>42</v>
@@ -4081,22 +4081,22 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>127554506</v>
+        <v>127546154</v>
       </c>
       <c r="E94">
         <v>601</v>
       </c>
       <c r="F94" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="G94" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="I94">
         <v>42</v>
       </c>
       <c r="J94">
-        <v>8004</v>
+        <v>1117</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -4119,16 +4119,16 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>127555101</v>
+        <v>127546690</v>
       </c>
       <c r="E95">
         <v>601</v>
       </c>
       <c r="F95" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="G95" s="2">
-        <v>45415</v>
+        <v>45414</v>
       </c>
       <c r="I95">
         <v>42</v>
@@ -4157,7 +4157,7 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>127555739</v>
+        <v>127549808</v>
       </c>
       <c r="E96">
         <v>601</v>
@@ -4195,7 +4195,7 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>127556130</v>
+        <v>127549970</v>
       </c>
       <c r="E97">
         <v>601</v>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>127556443</v>
+        <v>127550043</v>
       </c>
       <c r="E98">
         <v>601</v>
@@ -4248,7 +4248,7 @@
         <v>42</v>
       </c>
       <c r="J98">
-        <v>8004</v>
+        <v>1117</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -4271,7 +4271,7 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>127560800</v>
+        <v>127552386</v>
       </c>
       <c r="E99">
         <v>601</v>
@@ -4309,7 +4309,7 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>127561777</v>
+        <v>127553235</v>
       </c>
       <c r="E100">
         <v>601</v>
@@ -4324,7 +4324,7 @@
         <v>42</v>
       </c>
       <c r="J100">
-        <v>8004</v>
+        <v>1117</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -4347,7 +4347,7 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>127561855</v>
+        <v>127553323</v>
       </c>
       <c r="E101">
         <v>601</v>
@@ -4385,22 +4385,22 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>127591293</v>
+        <v>127553396</v>
       </c>
       <c r="E102">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F102" s="2">
-        <v>45419</v>
+        <v>45415</v>
       </c>
       <c r="G102" s="2">
-        <v>45419</v>
+        <v>45415</v>
       </c>
       <c r="I102">
         <v>42</v>
       </c>
       <c r="J102">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -4423,22 +4423,22 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>127607612</v>
+        <v>127553437</v>
       </c>
       <c r="E103">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F103" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="G103" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="I103">
         <v>42</v>
       </c>
       <c r="J103">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -4461,22 +4461,22 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>127609325</v>
+        <v>127553486</v>
       </c>
       <c r="E104">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F104" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="G104" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="I104">
         <v>42</v>
       </c>
       <c r="J104">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>127611019</v>
+        <v>127553515</v>
       </c>
       <c r="E105">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F105" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="G105" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="I105">
         <v>42</v>
       </c>
       <c r="J105">
-        <v>715</v>
+        <v>1117</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>127611787</v>
+        <v>127553612</v>
       </c>
       <c r="E106">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F106" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="G106" s="2">
-        <v>45420</v>
+        <v>45415</v>
       </c>
       <c r="I106">
         <v>42</v>
       </c>
       <c r="J106">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L106">
         <v>0</v>
@@ -4575,22 +4575,22 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>127619032</v>
+        <v>127553655</v>
       </c>
       <c r="E107">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F107" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="G107" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="I107">
         <v>42</v>
       </c>
       <c r="J107">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>127624022</v>
+        <v>127554506</v>
       </c>
       <c r="E108">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F108" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="G108" s="2">
-        <v>45421</v>
+        <v>45415</v>
       </c>
       <c r="I108">
         <v>42</v>
       </c>
       <c r="J108">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -4651,22 +4651,22 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>127628393</v>
+        <v>127555101</v>
       </c>
       <c r="E109">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F109" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="G109" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="I109">
         <v>42</v>
       </c>
       <c r="J109">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L109">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>127628545</v>
+        <v>127555739</v>
       </c>
       <c r="E110">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F110" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="G110" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="I110">
         <v>42</v>
       </c>
       <c r="J110">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -4727,22 +4727,22 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>127630298</v>
+        <v>127556130</v>
       </c>
       <c r="E111">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F111" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="G111" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="I111">
         <v>42</v>
       </c>
       <c r="J111">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L111">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>127631419</v>
+        <v>127556443</v>
       </c>
       <c r="E112">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F112" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="G112" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="I112">
         <v>42</v>
       </c>
       <c r="J112">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L112">
         <v>0</v>
@@ -4803,22 +4803,22 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>127631639</v>
+        <v>127560800</v>
       </c>
       <c r="E113">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F113" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="G113" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="I113">
         <v>42</v>
       </c>
       <c r="J113">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L113">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>127633655</v>
+        <v>127561777</v>
       </c>
       <c r="E114">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F114" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="G114" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="I114">
         <v>42</v>
       </c>
       <c r="J114">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L114">
         <v>0</v>
@@ -4879,22 +4879,22 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>127634011</v>
+        <v>127561855</v>
       </c>
       <c r="E115">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F115" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="G115" s="2">
-        <v>45422</v>
+        <v>45415</v>
       </c>
       <c r="I115">
         <v>42</v>
       </c>
       <c r="J115">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L115">
         <v>0</v>
@@ -4917,16 +4917,16 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>127634347</v>
+        <v>127607612</v>
       </c>
       <c r="E116">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F116" s="2">
-        <v>45422</v>
+        <v>45420</v>
       </c>
       <c r="G116" s="2">
-        <v>45422</v>
+        <v>45420</v>
       </c>
       <c r="I116">
         <v>42</v>
@@ -4955,16 +4955,16 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>127636233</v>
+        <v>127609325</v>
       </c>
       <c r="E117">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F117" s="2">
-        <v>45422</v>
+        <v>45420</v>
       </c>
       <c r="G117" s="2">
-        <v>45422</v>
+        <v>45420</v>
       </c>
       <c r="I117">
         <v>42</v>
@@ -4993,16 +4993,16 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>127637187</v>
+        <v>127611787</v>
       </c>
       <c r="E118">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F118" s="2">
-        <v>45422</v>
+        <v>45420</v>
       </c>
       <c r="G118" s="2">
-        <v>45422</v>
+        <v>45420</v>
       </c>
       <c r="I118">
         <v>42</v>
@@ -5031,16 +5031,16 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>127637287</v>
+        <v>127619032</v>
       </c>
       <c r="E119">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F119" s="2">
-        <v>45422</v>
+        <v>45421</v>
       </c>
       <c r="G119" s="2">
-        <v>45422</v>
+        <v>45421</v>
       </c>
       <c r="I119">
         <v>42</v>
@@ -5069,16 +5069,16 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>127639025</v>
+        <v>127624022</v>
       </c>
       <c r="E120">
         <v>1211</v>
       </c>
       <c r="F120" s="2">
-        <v>45422</v>
+        <v>45421</v>
       </c>
       <c r="G120" s="2">
-        <v>45422</v>
+        <v>45421</v>
       </c>
       <c r="I120">
         <v>42</v>
@@ -5107,7 +5107,7 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>127640122</v>
+        <v>127639025</v>
       </c>
       <c r="E121">
         <v>1211</v>
@@ -5145,16 +5145,16 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>127640177</v>
+        <v>127647899</v>
       </c>
       <c r="E122">
         <v>1212</v>
       </c>
       <c r="F122" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="G122" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="I122">
         <v>42</v>
@@ -5183,16 +5183,16 @@
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>127640933</v>
+        <v>127648834</v>
       </c>
       <c r="E123">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F123" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="G123" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="I123">
         <v>42</v>
@@ -5221,16 +5221,16 @@
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>127643154</v>
+        <v>127648897</v>
       </c>
       <c r="E124">
         <v>1211</v>
       </c>
       <c r="F124" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="G124" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="I124">
         <v>42</v>
@@ -5259,16 +5259,16 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>127643336</v>
+        <v>127650317</v>
       </c>
       <c r="E125">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F125" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="G125" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="I125">
         <v>42</v>
@@ -5297,16 +5297,16 @@
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>127643427</v>
+        <v>127650608</v>
       </c>
       <c r="E126">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F126" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="G126" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="I126">
         <v>42</v>
@@ -5335,16 +5335,16 @@
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>127644114</v>
+        <v>127651435</v>
       </c>
       <c r="E127">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F127" s="2">
-        <v>45423</v>
+        <v>45425</v>
       </c>
       <c r="G127" s="2">
-        <v>45423</v>
+        <v>45425</v>
       </c>
       <c r="I127">
         <v>42</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>127647899</v>
+        <v>127651793</v>
       </c>
       <c r="E128">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F128" s="2">
         <v>45425</v>
@@ -5411,10 +5411,10 @@
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>127648834</v>
+        <v>127652675</v>
       </c>
       <c r="E129">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F129" s="2">
         <v>45425</v>
@@ -5449,7 +5449,7 @@
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>127648897</v>
+        <v>127652945</v>
       </c>
       <c r="E130">
         <v>1211</v>
@@ -5487,10 +5487,10 @@
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>127650317</v>
+        <v>127654250</v>
       </c>
       <c r="E131">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F131" s="2">
         <v>45425</v>
@@ -5525,16 +5525,16 @@
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>127650608</v>
+        <v>127662660</v>
       </c>
       <c r="E132">
         <v>1211</v>
       </c>
       <c r="F132" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G132" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="I132">
         <v>42</v>
@@ -5563,16 +5563,16 @@
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>127651435</v>
+        <v>127662966</v>
       </c>
       <c r="E133">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F133" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G133" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="I133">
         <v>42</v>
@@ -5601,16 +5601,16 @@
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>127651793</v>
+        <v>127664777</v>
       </c>
       <c r="E134">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F134" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G134" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="I134">
         <v>42</v>
@@ -5639,16 +5639,16 @@
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>127652675</v>
+        <v>127664815</v>
       </c>
       <c r="E135">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F135" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G135" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="I135">
         <v>42</v>
@@ -5677,16 +5677,16 @@
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>127652945</v>
+        <v>127665493</v>
       </c>
       <c r="E136">
         <v>1211</v>
       </c>
       <c r="F136" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G136" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="I136">
         <v>42</v>
@@ -5715,16 +5715,16 @@
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>127654250</v>
+        <v>127665972</v>
       </c>
       <c r="E137">
         <v>1212</v>
       </c>
       <c r="F137" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="G137" s="2">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="I137">
         <v>42</v>
@@ -5752,20 +5752,156 @@
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
+      <c r="A138">
+        <v>127666857</v>
+      </c>
+      <c r="E138">
+        <v>1212</v>
+      </c>
+      <c r="F138" s="2">
+        <v>45426</v>
+      </c>
+      <c r="G138" s="2">
+        <v>45426</v>
+      </c>
+      <c r="I138">
+        <v>42</v>
+      </c>
+      <c r="J138">
+        <v>715</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>61</v>
+      </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F139" s="2"/>
-      <c r="G139" s="2"/>
+      <c r="A139">
+        <v>127668164</v>
+      </c>
+      <c r="E139">
+        <v>1212</v>
+      </c>
+      <c r="F139" s="2">
+        <v>45426</v>
+      </c>
+      <c r="G139" s="2">
+        <v>45426</v>
+      </c>
+      <c r="I139">
+        <v>42</v>
+      </c>
+      <c r="J139">
+        <v>715</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>61</v>
+      </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
+      <c r="A140">
+        <v>127668207</v>
+      </c>
+      <c r="E140">
+        <v>1211</v>
+      </c>
+      <c r="F140" s="2">
+        <v>45426</v>
+      </c>
+      <c r="G140" s="2">
+        <v>45426</v>
+      </c>
+      <c r="I140">
+        <v>42</v>
+      </c>
+      <c r="J140">
+        <v>715</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>61</v>
+      </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="F141" s="2"/>
-      <c r="G141" s="2"/>
+      <c r="A141">
+        <v>127669264</v>
+      </c>
+      <c r="E141">
+        <v>1211</v>
+      </c>
+      <c r="F141" s="2">
+        <v>45426</v>
+      </c>
+      <c r="G141" s="2">
+        <v>45426</v>
+      </c>
+      <c r="I141">
+        <v>42</v>
+      </c>
+      <c r="J141">
+        <v>715</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>61</v>
+      </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="F142" s="2"/>
@@ -13414,31 +13550,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B06A1B0-6E23-410F-B26F-28AE4698825D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3502E3-9894-40E9-B7BB-64ABF6F50721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,22 +585,22 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>127472186</v>
+        <v>127650880</v>
       </c>
       <c r="E2">
         <v>1211</v>
       </c>
       <c r="F2" s="2">
-        <v>45408</v>
+        <v>45425</v>
       </c>
       <c r="G2" s="2">
-        <v>45407</v>
+        <v>45425</v>
       </c>
       <c r="I2">
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -623,22 +623,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>127504091</v>
+        <v>127657362</v>
       </c>
       <c r="E3">
         <v>1211</v>
       </c>
       <c r="F3" s="2">
-        <v>45412</v>
+        <v>45425</v>
       </c>
       <c r="G3" s="2">
-        <v>45411</v>
+        <v>45425</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8021</v>
+        <v>1735</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -661,22 +661,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>127513307</v>
+        <v>124136688</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45412</v>
+        <v>45427</v>
       </c>
       <c r="G4" s="2">
-        <v>45411</v>
+        <v>45427</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,22 +699,22 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>127532403</v>
+        <v>124190824</v>
       </c>
       <c r="E5">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45415</v>
+        <v>45427</v>
       </c>
       <c r="G5" s="2">
-        <v>45414</v>
+        <v>45427</v>
       </c>
       <c r="I5">
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,22 +737,22 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>127596160</v>
+        <v>124450113</v>
       </c>
       <c r="E6">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45420</v>
+        <v>45427</v>
       </c>
       <c r="G6" s="2">
-        <v>45419</v>
+        <v>45427</v>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -775,22 +775,22 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>127609255</v>
+        <v>125006076</v>
       </c>
       <c r="E7">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45421</v>
+        <v>45427</v>
       </c>
       <c r="G7" s="2">
-        <v>45420</v>
+        <v>45427</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -813,22 +813,22 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>126954503</v>
+        <v>125541063</v>
       </c>
       <c r="E8">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45378</v>
+        <v>45427</v>
       </c>
       <c r="G8" s="2">
-        <v>45378</v>
+        <v>45427</v>
       </c>
       <c r="I8">
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -851,22 +851,22 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>127576104</v>
+        <v>125588345</v>
       </c>
       <c r="E9">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F9" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="G9" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -889,22 +889,22 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>127576513</v>
+        <v>126070690</v>
       </c>
       <c r="E10">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="G10" s="2">
-        <v>45418</v>
+        <v>45422</v>
       </c>
       <c r="I10">
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -927,22 +927,22 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>127576560</v>
+        <v>126121295</v>
       </c>
       <c r="E11">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="G11" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="I11">
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -965,22 +965,22 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>127576766</v>
+        <v>126174817</v>
       </c>
       <c r="E12">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="G12" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="I12">
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1003,22 +1003,22 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>127576905</v>
+        <v>126744041</v>
       </c>
       <c r="E13">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="G13" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="I13">
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>127578137</v>
+        <v>126879618</v>
       </c>
       <c r="E14">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="G14" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="I14">
         <v>42</v>
       </c>
       <c r="J14">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1079,22 +1079,22 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>127579885</v>
+        <v>127399208</v>
       </c>
       <c r="E15">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="G15" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="I15">
         <v>42</v>
       </c>
       <c r="J15">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1117,22 +1117,22 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>127581930</v>
+        <v>127409475</v>
       </c>
       <c r="E16">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="G16" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="I16">
         <v>42</v>
       </c>
       <c r="J16">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1155,22 +1155,22 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>127579885</v>
+        <v>127599028</v>
       </c>
       <c r="E17">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="G17" s="2">
-        <v>45418</v>
+        <v>45427</v>
       </c>
       <c r="I17">
         <v>42</v>
       </c>
       <c r="J17">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -1193,22 +1193,22 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>127581930</v>
+        <v>110074933</v>
       </c>
       <c r="E18">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45418</v>
+        <v>43453</v>
       </c>
       <c r="G18" s="2">
-        <v>45418</v>
+        <v>43441</v>
       </c>
       <c r="I18">
         <v>42</v>
       </c>
       <c r="J18">
-        <v>8004</v>
+        <v>8023</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1231,22 +1231,22 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>127571299</v>
+        <v>126954503</v>
       </c>
       <c r="E19">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="F19" s="2">
-        <v>45418</v>
+        <v>45378</v>
       </c>
       <c r="G19" s="2">
-        <v>45418</v>
+        <v>45378</v>
       </c>
       <c r="I19">
         <v>42</v>
       </c>
       <c r="J19">
-        <v>8004</v>
+        <v>8017</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1269,22 +1269,22 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>127619032</v>
+        <v>127584638</v>
       </c>
       <c r="E20">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F20" s="2">
-        <v>45421</v>
+        <v>45419</v>
       </c>
       <c r="G20" s="2">
-        <v>45421</v>
+        <v>45419</v>
       </c>
       <c r="I20">
         <v>42</v>
       </c>
       <c r="J20">
-        <v>715</v>
+        <v>8013</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1307,22 +1307,22 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>127624022</v>
+        <v>127584645</v>
       </c>
       <c r="E21">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F21" s="2">
-        <v>45421</v>
+        <v>45419</v>
       </c>
       <c r="G21" s="2">
-        <v>45421</v>
+        <v>45419</v>
       </c>
       <c r="I21">
         <v>42</v>
       </c>
       <c r="J21">
-        <v>715</v>
+        <v>8013</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1345,22 +1345,22 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>127639025</v>
+        <v>127584649</v>
       </c>
       <c r="E22">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F22" s="2">
-        <v>45422</v>
+        <v>45419</v>
       </c>
       <c r="G22" s="2">
-        <v>45422</v>
+        <v>45419</v>
       </c>
       <c r="I22">
         <v>42</v>
       </c>
       <c r="J22">
-        <v>715</v>
+        <v>8013</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1383,22 +1383,22 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>127650317</v>
+        <v>127588846</v>
       </c>
       <c r="E23">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F23" s="2">
-        <v>45425</v>
+        <v>45419</v>
       </c>
       <c r="G23" s="2">
-        <v>45425</v>
+        <v>45419</v>
       </c>
       <c r="I23">
         <v>42</v>
       </c>
       <c r="J23">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1421,22 +1421,22 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>127651793</v>
+        <v>127588939</v>
       </c>
       <c r="E24">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F24" s="2">
-        <v>45425</v>
+        <v>45419</v>
       </c>
       <c r="G24" s="2">
-        <v>45425</v>
+        <v>45419</v>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>715</v>
+        <v>8013</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1459,22 +1459,22 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>127674433</v>
+        <v>127589162</v>
       </c>
       <c r="E25">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F25" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="G25" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="I25">
         <v>42</v>
       </c>
       <c r="J25">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>127674616</v>
+        <v>127589682</v>
       </c>
       <c r="E26">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F26" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="G26" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="I26">
         <v>42</v>
       </c>
       <c r="J26">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>127675213</v>
+        <v>127589696</v>
       </c>
       <c r="E27">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F27" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="G27" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="I27">
         <v>42</v>
       </c>
       <c r="J27">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>127677894</v>
+        <v>127589924</v>
       </c>
       <c r="E28">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F28" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="G28" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="I28">
         <v>42</v>
       </c>
       <c r="J28">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -1611,22 +1611,22 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>127679740</v>
+        <v>127590134</v>
       </c>
       <c r="E29">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F29" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="G29" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="I29">
         <v>42</v>
       </c>
       <c r="J29">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>127680079</v>
+        <v>127590692</v>
       </c>
       <c r="E30">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F30" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="G30" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="I30">
         <v>42</v>
       </c>
       <c r="J30">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1687,22 +1687,22 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>127681321</v>
+        <v>127590881</v>
       </c>
       <c r="E31">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F31" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="G31" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="I31">
         <v>42</v>
       </c>
       <c r="J31">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>127681439</v>
+        <v>127591586</v>
       </c>
       <c r="E32">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F32" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="G32" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="I32">
         <v>42</v>
       </c>
       <c r="J32">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -1763,22 +1763,22 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>127682264</v>
+        <v>127592035</v>
       </c>
       <c r="E33">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F33" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="G33" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="I33">
         <v>42</v>
       </c>
       <c r="J33">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -1801,22 +1801,22 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>127682399</v>
+        <v>127592607</v>
       </c>
       <c r="E34">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F34" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="G34" s="2">
-        <v>45427</v>
+        <v>45419</v>
       </c>
       <c r="I34">
         <v>42</v>
       </c>
       <c r="J34">
-        <v>715</v>
+        <v>8004</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -1839,44 +1839,614 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>127684743</v>
+        <v>127593826</v>
       </c>
       <c r="E35">
+        <v>601</v>
+      </c>
+      <c r="F35" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G35" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I35">
+        <v>42</v>
+      </c>
+      <c r="J35">
+        <v>8004</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>127594087</v>
+      </c>
+      <c r="E36">
+        <v>601</v>
+      </c>
+      <c r="F36" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G36" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I36">
+        <v>42</v>
+      </c>
+      <c r="J36">
+        <v>8004</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>127595805</v>
+      </c>
+      <c r="E37">
+        <v>601</v>
+      </c>
+      <c r="F37" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G37" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I37">
+        <v>42</v>
+      </c>
+      <c r="J37">
+        <v>8004</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>127595879</v>
+      </c>
+      <c r="E38">
+        <v>601</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I38">
+        <v>42</v>
+      </c>
+      <c r="J38">
+        <v>8004</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>127596105</v>
+      </c>
+      <c r="E39">
+        <v>601</v>
+      </c>
+      <c r="F39" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G39" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I39">
+        <v>42</v>
+      </c>
+      <c r="J39">
+        <v>8004</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>127596181</v>
+      </c>
+      <c r="E40">
+        <v>601</v>
+      </c>
+      <c r="F40" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G40" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I40">
+        <v>42</v>
+      </c>
+      <c r="J40">
+        <v>8004</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>127596567</v>
+      </c>
+      <c r="E41">
+        <v>601</v>
+      </c>
+      <c r="F41" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G41" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I41">
+        <v>42</v>
+      </c>
+      <c r="J41">
+        <v>8004</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>127689835</v>
+      </c>
+      <c r="E42">
         <v>1211</v>
       </c>
-      <c r="F35" s="2">
-        <v>45427</v>
-      </c>
-      <c r="G35" s="2">
-        <v>45427</v>
-      </c>
-      <c r="I35">
-        <v>42</v>
-      </c>
-      <c r="J35">
+      <c r="F42" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G42" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I42">
+        <v>42</v>
+      </c>
+      <c r="J42">
         <v>715</v>
       </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>127691633</v>
+      </c>
+      <c r="E43">
+        <v>1212</v>
+      </c>
+      <c r="F43" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G43" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I43">
+        <v>42</v>
+      </c>
+      <c r="J43">
+        <v>715</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>127692332</v>
+      </c>
+      <c r="E44">
+        <v>1212</v>
+      </c>
+      <c r="F44" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G44" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I44">
+        <v>42</v>
+      </c>
+      <c r="J44">
+        <v>715</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>127692428</v>
+      </c>
+      <c r="E45">
+        <v>1211</v>
+      </c>
+      <c r="F45" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G45" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I45">
+        <v>42</v>
+      </c>
+      <c r="J45">
+        <v>715</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>127693309</v>
+      </c>
+      <c r="E46">
+        <v>1211</v>
+      </c>
+      <c r="F46" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G46" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I46">
+        <v>42</v>
+      </c>
+      <c r="J46">
+        <v>715</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>127693313</v>
+      </c>
+      <c r="E47">
+        <v>1211</v>
+      </c>
+      <c r="F47" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G47" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I47">
+        <v>42</v>
+      </c>
+      <c r="J47">
+        <v>715</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>127694259</v>
+      </c>
+      <c r="E48">
+        <v>1211</v>
+      </c>
+      <c r="F48" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G48" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I48">
+        <v>42</v>
+      </c>
+      <c r="J48">
+        <v>715</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>127696190</v>
+      </c>
+      <c r="E49">
+        <v>1212</v>
+      </c>
+      <c r="F49" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G49" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I49">
+        <v>42</v>
+      </c>
+      <c r="J49">
+        <v>715</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>127697440</v>
+      </c>
+      <c r="E50">
+        <v>1211</v>
+      </c>
+      <c r="F50" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G50" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I50">
+        <v>42</v>
+      </c>
+      <c r="J50">
+        <v>715</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
         <v>61</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q35" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}"/>
+  <autoFilter ref="A1:Q50" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>

--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3502E3-9894-40E9-B7BB-64ABF6F50721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2044CFC5-A190-4FCF-BDDA-70708ECB1F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$167</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q167"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,16 +585,16 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>127650880</v>
+        <v>127677397</v>
       </c>
       <c r="E2">
         <v>1211</v>
       </c>
       <c r="F2" s="2">
-        <v>45425</v>
+        <v>45428</v>
       </c>
       <c r="G2" s="2">
-        <v>45425</v>
+        <v>45427</v>
       </c>
       <c r="I2">
         <v>42</v>
@@ -623,16 +623,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>127657362</v>
+        <v>127678516</v>
       </c>
       <c r="E3">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F3" s="2">
-        <v>45425</v>
+        <v>45427</v>
       </c>
       <c r="G3" s="2">
-        <v>45425</v>
+        <v>45427</v>
       </c>
       <c r="I3">
         <v>42</v>
@@ -661,13 +661,13 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>124136688</v>
+        <v>127680312</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G4" s="2">
         <v>45427</v>
@@ -676,7 +676,7 @@
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,13 +699,13 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>124190824</v>
+        <v>127680551</v>
       </c>
       <c r="E5">
         <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G5" s="2">
         <v>45427</v>
@@ -714,7 +714,7 @@
         <v>42</v>
       </c>
       <c r="J5">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>124450113</v>
+        <v>127683408</v>
       </c>
       <c r="E6">
         <v>1211</v>
@@ -752,7 +752,7 @@
         <v>42</v>
       </c>
       <c r="J6">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -775,7 +775,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>125006076</v>
+        <v>127683415</v>
       </c>
       <c r="E7">
         <v>1211</v>
@@ -790,7 +790,7 @@
         <v>42</v>
       </c>
       <c r="J7">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -813,13 +813,13 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>125541063</v>
+        <v>127686897</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G8" s="2">
         <v>45427</v>
@@ -828,7 +828,7 @@
         <v>42</v>
       </c>
       <c r="J8">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -851,22 +851,22 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>125588345</v>
+        <v>127689861</v>
       </c>
       <c r="E9">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G9" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -889,22 +889,22 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>126070690</v>
+        <v>127690780</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G10" s="2">
-        <v>45422</v>
+        <v>45428</v>
       </c>
       <c r="I10">
         <v>42</v>
       </c>
       <c r="J10">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -927,22 +927,22 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>126121295</v>
+        <v>127694205</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="G11" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="I11">
         <v>42</v>
       </c>
       <c r="J11">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -965,22 +965,22 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>126174817</v>
+        <v>127695138</v>
       </c>
       <c r="E12">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="F12" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G12" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="I12">
         <v>42</v>
       </c>
       <c r="J12">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1003,22 +1003,22 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>126744041</v>
+        <v>127697983</v>
       </c>
       <c r="E13">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F13" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G13" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="I13">
         <v>42</v>
       </c>
       <c r="J13">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>126879618</v>
+        <v>127699757</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="G14" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="I14">
         <v>42</v>
       </c>
       <c r="J14">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1079,22 +1079,22 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>127399208</v>
+        <v>127699831</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G15" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="I15">
         <v>42</v>
       </c>
       <c r="J15">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1117,22 +1117,22 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>127409475</v>
+        <v>127701357</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="G16" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="I16">
         <v>42</v>
       </c>
       <c r="J16">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>127599028</v>
+        <v>124085593</v>
       </c>
       <c r="E17">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F17" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G17" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,22 +1193,22 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>110074933</v>
+        <v>124114081</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>43453</v>
+        <v>45429</v>
       </c>
       <c r="G18" s="2">
-        <v>43441</v>
+        <v>45429</v>
       </c>
       <c r="I18">
         <v>42</v>
       </c>
       <c r="J18">
-        <v>8023</v>
+        <v>8001</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1231,22 +1231,22 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>126954503</v>
+        <v>124199837</v>
       </c>
       <c r="E19">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45378</v>
+        <v>45428</v>
       </c>
       <c r="G19" s="2">
-        <v>45378</v>
+        <v>45428</v>
       </c>
       <c r="I19">
         <v>42</v>
       </c>
       <c r="J19">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1269,22 +1269,22 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>127584638</v>
+        <v>124241728</v>
       </c>
       <c r="E20">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="G20" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="I20">
         <v>42</v>
       </c>
       <c r="J20">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1307,22 +1307,22 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>127584645</v>
+        <v>124382401</v>
       </c>
       <c r="E21">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="G21" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="I21">
         <v>42</v>
       </c>
       <c r="J21">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1345,22 +1345,22 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>127584649</v>
+        <v>124382473</v>
       </c>
       <c r="E22">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45419</v>
+        <v>45430</v>
       </c>
       <c r="G22" s="2">
-        <v>45419</v>
+        <v>45429</v>
       </c>
       <c r="I22">
         <v>42</v>
       </c>
       <c r="J22">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1383,22 +1383,22 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>127588846</v>
+        <v>124509919</v>
       </c>
       <c r="E23">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="G23" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="I23">
         <v>42</v>
       </c>
       <c r="J23">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1421,22 +1421,22 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>127588939</v>
+        <v>124526674</v>
       </c>
       <c r="E24">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F24" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="G24" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8013</v>
+        <v>8001</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1459,22 +1459,22 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>127589162</v>
+        <v>124556596</v>
       </c>
       <c r="E25">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45419</v>
+        <v>45430</v>
       </c>
       <c r="G25" s="2">
-        <v>45419</v>
+        <v>45430</v>
       </c>
       <c r="I25">
         <v>42</v>
       </c>
       <c r="J25">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>127589682</v>
+        <v>124580685</v>
       </c>
       <c r="E26">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F26" s="2">
-        <v>45419</v>
+        <v>45430</v>
       </c>
       <c r="G26" s="2">
-        <v>45419</v>
+        <v>45430</v>
       </c>
       <c r="I26">
         <v>42</v>
       </c>
       <c r="J26">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>127589696</v>
+        <v>124736297</v>
       </c>
       <c r="E27">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F27" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="G27" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="I27">
         <v>42</v>
       </c>
       <c r="J27">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>127589924</v>
+        <v>124805931</v>
       </c>
       <c r="E28">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45419</v>
+        <v>45429</v>
       </c>
       <c r="G28" s="2">
-        <v>45419</v>
+        <v>45429</v>
       </c>
       <c r="I28">
         <v>42</v>
       </c>
       <c r="J28">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -1611,22 +1611,22 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>127590134</v>
+        <v>124829987</v>
       </c>
       <c r="E29">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F29" s="2">
-        <v>45419</v>
+        <v>45429</v>
       </c>
       <c r="G29" s="2">
-        <v>45419</v>
+        <v>45429</v>
       </c>
       <c r="I29">
         <v>42</v>
       </c>
       <c r="J29">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>127590692</v>
+        <v>124876290</v>
       </c>
       <c r="E30">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="G30" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="I30">
         <v>42</v>
       </c>
       <c r="J30">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -1687,22 +1687,22 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>127590881</v>
+        <v>125006076</v>
       </c>
       <c r="E31">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45419</v>
+        <v>45427</v>
       </c>
       <c r="G31" s="2">
-        <v>45419</v>
+        <v>45427</v>
       </c>
       <c r="I31">
         <v>42</v>
       </c>
       <c r="J31">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>127591586</v>
+        <v>125052952</v>
       </c>
       <c r="E32">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>45419</v>
+        <v>45429</v>
       </c>
       <c r="G32" s="2">
-        <v>45419</v>
+        <v>45429</v>
       </c>
       <c r="I32">
         <v>42</v>
       </c>
       <c r="J32">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L32">
         <v>0</v>
@@ -1763,22 +1763,22 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>127592035</v>
+        <v>125184702</v>
       </c>
       <c r="E33">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F33" s="2">
-        <v>45419</v>
+        <v>45429</v>
       </c>
       <c r="G33" s="2">
-        <v>45419</v>
+        <v>45429</v>
       </c>
       <c r="I33">
         <v>42</v>
       </c>
       <c r="J33">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -1801,22 +1801,22 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>127592607</v>
+        <v>125195701</v>
       </c>
       <c r="E34">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F34" s="2">
-        <v>45419</v>
+        <v>45429</v>
       </c>
       <c r="G34" s="2">
-        <v>45419</v>
+        <v>45426</v>
       </c>
       <c r="I34">
         <v>42</v>
       </c>
       <c r="J34">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -1839,22 +1839,22 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>127593826</v>
+        <v>125304585</v>
       </c>
       <c r="E35">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F35" s="2">
-        <v>45419</v>
+        <v>45430</v>
       </c>
       <c r="G35" s="2">
-        <v>45419</v>
+        <v>45430</v>
       </c>
       <c r="I35">
         <v>42</v>
       </c>
       <c r="J35">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>127594087</v>
+        <v>125384268</v>
       </c>
       <c r="E36">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F36" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="G36" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="I36">
         <v>42</v>
       </c>
       <c r="J36">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -1915,22 +1915,22 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>127595805</v>
+        <v>125422780</v>
       </c>
       <c r="E37">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F37" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="G37" s="2">
-        <v>45419</v>
+        <v>45427</v>
       </c>
       <c r="I37">
         <v>42</v>
       </c>
       <c r="J37">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>127595879</v>
+        <v>125426528</v>
       </c>
       <c r="E38">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="G38" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="I38">
         <v>42</v>
       </c>
       <c r="J38">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -1991,22 +1991,22 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>127596105</v>
+        <v>125430469</v>
       </c>
       <c r="E39">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F39" s="2">
-        <v>45419</v>
+        <v>45429</v>
       </c>
       <c r="G39" s="2">
-        <v>45419</v>
+        <v>45428</v>
       </c>
       <c r="I39">
         <v>42</v>
       </c>
       <c r="J39">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>127596181</v>
+        <v>125505055</v>
       </c>
       <c r="E40">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F40" s="2">
-        <v>45419</v>
+        <v>45429</v>
       </c>
       <c r="G40" s="2">
-        <v>45419</v>
+        <v>45429</v>
       </c>
       <c r="I40">
         <v>42</v>
       </c>
       <c r="J40">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -2067,22 +2067,22 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>127596567</v>
+        <v>125541063</v>
       </c>
       <c r="E41">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F41" s="2">
-        <v>45419</v>
+        <v>45427</v>
       </c>
       <c r="G41" s="2">
-        <v>45419</v>
+        <v>45427</v>
       </c>
       <c r="I41">
         <v>42</v>
       </c>
       <c r="J41">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -2105,22 +2105,22 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>127689835</v>
+        <v>125574465</v>
       </c>
       <c r="E42">
         <v>1211</v>
       </c>
       <c r="F42" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G42" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I42">
         <v>42</v>
       </c>
       <c r="J42">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -2143,22 +2143,22 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>127691633</v>
+        <v>125588345</v>
       </c>
       <c r="E43">
         <v>1212</v>
       </c>
       <c r="F43" s="2">
-        <v>45428</v>
+        <v>45427</v>
       </c>
       <c r="G43" s="2">
-        <v>45428</v>
+        <v>45427</v>
       </c>
       <c r="I43">
         <v>42</v>
       </c>
       <c r="J43">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -2181,22 +2181,22 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>127692332</v>
+        <v>125650786</v>
       </c>
       <c r="E44">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F44" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G44" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I44">
         <v>42</v>
       </c>
       <c r="J44">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L44">
         <v>0</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>127692428</v>
+        <v>125691862</v>
       </c>
       <c r="E45">
         <v>1211</v>
@@ -2234,7 +2234,7 @@
         <v>42</v>
       </c>
       <c r="J45">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -2257,22 +2257,22 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>127693309</v>
+        <v>125769830</v>
       </c>
       <c r="E46">
         <v>1211</v>
       </c>
       <c r="F46" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G46" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I46">
         <v>42</v>
       </c>
       <c r="J46">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -2295,22 +2295,22 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>127693313</v>
+        <v>125782283</v>
       </c>
       <c r="E47">
         <v>1211</v>
       </c>
       <c r="F47" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G47" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I47">
         <v>42</v>
       </c>
       <c r="J47">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -2333,22 +2333,22 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>127694259</v>
+        <v>125934594</v>
       </c>
       <c r="E48">
         <v>1211</v>
       </c>
       <c r="F48" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G48" s="2">
-        <v>45428</v>
+        <v>45426</v>
       </c>
       <c r="I48">
         <v>42</v>
       </c>
       <c r="J48">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -2371,22 +2371,22 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>127696190</v>
+        <v>125982656</v>
       </c>
       <c r="E49">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F49" s="2">
-        <v>45428</v>
+        <v>45430</v>
       </c>
       <c r="G49" s="2">
-        <v>45428</v>
+        <v>45430</v>
       </c>
       <c r="I49">
         <v>42</v>
       </c>
       <c r="J49">
-        <v>715</v>
+        <v>8001</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -2409,44 +2409,4490 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>127697440</v>
+        <v>126014517</v>
       </c>
       <c r="E50">
         <v>1211</v>
       </c>
       <c r="F50" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G50" s="2">
+        <v>45426</v>
+      </c>
+      <c r="I50">
+        <v>42</v>
+      </c>
+      <c r="J50">
+        <v>8001</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>126033754</v>
+      </c>
+      <c r="E51">
+        <v>1211</v>
+      </c>
+      <c r="F51" s="2">
+        <v>45430</v>
+      </c>
+      <c r="G51" s="2">
+        <v>45430</v>
+      </c>
+      <c r="I51">
+        <v>42</v>
+      </c>
+      <c r="J51">
+        <v>8001</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>126070690</v>
+      </c>
+      <c r="E52">
+        <v>1211</v>
+      </c>
+      <c r="F52" s="2">
+        <v>45427</v>
+      </c>
+      <c r="G52" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I52">
+        <v>42</v>
+      </c>
+      <c r="J52">
+        <v>8001</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>126075570</v>
+      </c>
+      <c r="E53">
+        <v>1211</v>
+      </c>
+      <c r="F53" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G53" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I53">
+        <v>42</v>
+      </c>
+      <c r="J53">
+        <v>8001</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>126085447</v>
+      </c>
+      <c r="E54">
+        <v>1211</v>
+      </c>
+      <c r="F54" s="2">
+        <v>45430</v>
+      </c>
+      <c r="G54" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I54">
+        <v>42</v>
+      </c>
+      <c r="J54">
+        <v>8001</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>126091614</v>
+      </c>
+      <c r="E55">
+        <v>1211</v>
+      </c>
+      <c r="F55" s="2">
         <v>45428</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G55" s="2">
         <v>45428</v>
       </c>
-      <c r="I50">
-        <v>42</v>
-      </c>
-      <c r="J50">
-        <v>715</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
+      <c r="I55">
+        <v>42</v>
+      </c>
+      <c r="J55">
+        <v>8001</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>126121295</v>
+      </c>
+      <c r="E56">
+        <v>1211</v>
+      </c>
+      <c r="F56" s="2">
+        <v>45427</v>
+      </c>
+      <c r="G56" s="2">
+        <v>45427</v>
+      </c>
+      <c r="I56">
+        <v>42</v>
+      </c>
+      <c r="J56">
+        <v>8001</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>126261196</v>
+      </c>
+      <c r="E57">
+        <v>1211</v>
+      </c>
+      <c r="F57" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G57" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I57">
+        <v>42</v>
+      </c>
+      <c r="J57">
+        <v>8001</v>
+      </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>126384960</v>
+      </c>
+      <c r="E58">
+        <v>1211</v>
+      </c>
+      <c r="F58" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G58" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I58">
+        <v>42</v>
+      </c>
+      <c r="J58">
+        <v>8001</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>126611925</v>
+      </c>
+      <c r="E59">
+        <v>1211</v>
+      </c>
+      <c r="F59" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G59" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I59">
+        <v>42</v>
+      </c>
+      <c r="J59">
+        <v>8001</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>126618728</v>
+      </c>
+      <c r="E60">
+        <v>1211</v>
+      </c>
+      <c r="F60" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G60" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I60">
+        <v>42</v>
+      </c>
+      <c r="J60">
+        <v>8001</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>126704127</v>
+      </c>
+      <c r="E61">
+        <v>1211</v>
+      </c>
+      <c r="F61" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G61" s="2">
+        <v>45427</v>
+      </c>
+      <c r="I61">
+        <v>42</v>
+      </c>
+      <c r="J61">
+        <v>8001</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>126744041</v>
+      </c>
+      <c r="E62">
+        <v>1211</v>
+      </c>
+      <c r="F62" s="2">
+        <v>45427</v>
+      </c>
+      <c r="G62" s="2">
+        <v>45427</v>
+      </c>
+      <c r="I62">
+        <v>42</v>
+      </c>
+      <c r="J62">
+        <v>8001</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>126753264</v>
+      </c>
+      <c r="E63">
+        <v>1211</v>
+      </c>
+      <c r="F63" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G63" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I63">
+        <v>42</v>
+      </c>
+      <c r="J63">
+        <v>8001</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>126838674</v>
+      </c>
+      <c r="E64">
+        <v>1211</v>
+      </c>
+      <c r="F64" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G64" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I64">
+        <v>42</v>
+      </c>
+      <c r="J64">
+        <v>8001</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>126867169</v>
+      </c>
+      <c r="E65">
+        <v>1211</v>
+      </c>
+      <c r="F65" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G65" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I65">
+        <v>42</v>
+      </c>
+      <c r="J65">
+        <v>8001</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>126879618</v>
+      </c>
+      <c r="E66">
+        <v>1211</v>
+      </c>
+      <c r="F66" s="2">
+        <v>45427</v>
+      </c>
+      <c r="G66" s="2">
+        <v>45427</v>
+      </c>
+      <c r="I66">
+        <v>42</v>
+      </c>
+      <c r="J66">
+        <v>8001</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>0</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>126880595</v>
+      </c>
+      <c r="E67">
+        <v>1212</v>
+      </c>
+      <c r="F67" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G67" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I67">
+        <v>42</v>
+      </c>
+      <c r="J67">
+        <v>8001</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>126930388</v>
+      </c>
+      <c r="E68">
+        <v>1211</v>
+      </c>
+      <c r="F68" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G68" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I68">
+        <v>42</v>
+      </c>
+      <c r="J68">
+        <v>8001</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>126963758</v>
+      </c>
+      <c r="E69">
+        <v>1211</v>
+      </c>
+      <c r="F69" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G69" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I69">
+        <v>42</v>
+      </c>
+      <c r="J69">
+        <v>8001</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>126971134</v>
+      </c>
+      <c r="E70">
+        <v>1211</v>
+      </c>
+      <c r="F70" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G70" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I70">
+        <v>42</v>
+      </c>
+      <c r="J70">
+        <v>8001</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>126976721</v>
+      </c>
+      <c r="E71">
+        <v>1212</v>
+      </c>
+      <c r="F71" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G71" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I71">
+        <v>42</v>
+      </c>
+      <c r="J71">
+        <v>8001</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>127013708</v>
+      </c>
+      <c r="E72">
+        <v>1211</v>
+      </c>
+      <c r="F72" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G72" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I72">
+        <v>42</v>
+      </c>
+      <c r="J72">
+        <v>8001</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>127013931</v>
+      </c>
+      <c r="E73">
+        <v>1211</v>
+      </c>
+      <c r="F73" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G73" s="2">
+        <v>45426</v>
+      </c>
+      <c r="I73">
+        <v>42</v>
+      </c>
+      <c r="J73">
+        <v>8001</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>127054069</v>
+      </c>
+      <c r="E74">
+        <v>1211</v>
+      </c>
+      <c r="F74" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G74" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I74">
+        <v>42</v>
+      </c>
+      <c r="J74">
+        <v>8001</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>127080906</v>
+      </c>
+      <c r="E75">
+        <v>1211</v>
+      </c>
+      <c r="F75" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G75" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I75">
+        <v>42</v>
+      </c>
+      <c r="J75">
+        <v>8001</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>127103245</v>
+      </c>
+      <c r="E76">
+        <v>1211</v>
+      </c>
+      <c r="F76" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G76" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I76">
+        <v>42</v>
+      </c>
+      <c r="J76">
+        <v>8001</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>127261315</v>
+      </c>
+      <c r="E77">
+        <v>1211</v>
+      </c>
+      <c r="F77" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G77" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I77">
+        <v>42</v>
+      </c>
+      <c r="J77">
+        <v>8001</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>127326475</v>
+      </c>
+      <c r="E78">
+        <v>1211</v>
+      </c>
+      <c r="F78" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G78" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I78">
+        <v>42</v>
+      </c>
+      <c r="J78">
+        <v>8001</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>127333904</v>
+      </c>
+      <c r="E79">
+        <v>1211</v>
+      </c>
+      <c r="F79" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G79" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I79">
+        <v>42</v>
+      </c>
+      <c r="J79">
+        <v>8001</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>127339851</v>
+      </c>
+      <c r="E80">
+        <v>1211</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I80">
+        <v>42</v>
+      </c>
+      <c r="J80">
+        <v>8001</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>127368628</v>
+      </c>
+      <c r="E81">
+        <v>1211</v>
+      </c>
+      <c r="F81" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G81" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I81">
+        <v>42</v>
+      </c>
+      <c r="J81">
+        <v>8001</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>127399208</v>
+      </c>
+      <c r="E82">
+        <v>1211</v>
+      </c>
+      <c r="F82" s="2">
+        <v>45427</v>
+      </c>
+      <c r="G82" s="2">
+        <v>45427</v>
+      </c>
+      <c r="I82">
+        <v>42</v>
+      </c>
+      <c r="J82">
+        <v>8001</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>127409475</v>
+      </c>
+      <c r="E83">
+        <v>1211</v>
+      </c>
+      <c r="F83" s="2">
+        <v>45427</v>
+      </c>
+      <c r="G83" s="2">
+        <v>45427</v>
+      </c>
+      <c r="I83">
+        <v>42</v>
+      </c>
+      <c r="J83">
+        <v>8001</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>127412856</v>
+      </c>
+      <c r="E84">
+        <v>1211</v>
+      </c>
+      <c r="F84" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G84" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I84">
+        <v>42</v>
+      </c>
+      <c r="J84">
+        <v>8001</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>127443739</v>
+      </c>
+      <c r="E85">
+        <v>1212</v>
+      </c>
+      <c r="F85" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G85" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I85">
+        <v>42</v>
+      </c>
+      <c r="J85">
+        <v>8001</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>127547571</v>
+      </c>
+      <c r="E86">
+        <v>1211</v>
+      </c>
+      <c r="F86" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G86" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I86">
+        <v>42</v>
+      </c>
+      <c r="J86">
+        <v>8001</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>127563914</v>
+      </c>
+      <c r="E87">
+        <v>1211</v>
+      </c>
+      <c r="F87" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G87" s="2">
+        <v>45427</v>
+      </c>
+      <c r="I87">
+        <v>42</v>
+      </c>
+      <c r="J87">
+        <v>8001</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>127599028</v>
+      </c>
+      <c r="E88">
+        <v>1211</v>
+      </c>
+      <c r="F88" s="2">
+        <v>45427</v>
+      </c>
+      <c r="G88" s="2">
+        <v>45427</v>
+      </c>
+      <c r="I88">
+        <v>42</v>
+      </c>
+      <c r="J88">
+        <v>8001</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>127606707</v>
+      </c>
+      <c r="E89">
+        <v>1211</v>
+      </c>
+      <c r="F89" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G89" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I89">
+        <v>42</v>
+      </c>
+      <c r="J89">
+        <v>8001</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>127621540</v>
+      </c>
+      <c r="E90">
+        <v>1211</v>
+      </c>
+      <c r="F90" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G90" s="2">
+        <v>45425</v>
+      </c>
+      <c r="I90">
+        <v>42</v>
+      </c>
+      <c r="J90">
+        <v>8001</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>127681123</v>
+      </c>
+      <c r="E91">
+        <v>1211</v>
+      </c>
+      <c r="F91" s="2">
+        <v>45428</v>
+      </c>
+      <c r="G91" s="2">
+        <v>45428</v>
+      </c>
+      <c r="I91">
+        <v>42</v>
+      </c>
+      <c r="J91">
+        <v>8001</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>110074933</v>
+      </c>
+      <c r="E92">
+        <v>1211</v>
+      </c>
+      <c r="F92" s="2">
+        <v>43453</v>
+      </c>
+      <c r="G92" s="2">
+        <v>43441</v>
+      </c>
+      <c r="I92">
+        <v>42</v>
+      </c>
+      <c r="J92">
+        <v>8023</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>123058958</v>
+      </c>
+      <c r="E93">
+        <v>1211</v>
+      </c>
+      <c r="F93" s="2">
+        <v>44995</v>
+      </c>
+      <c r="G93" s="2">
+        <v>44993</v>
+      </c>
+      <c r="I93">
+        <v>42</v>
+      </c>
+      <c r="J93">
+        <v>8001</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>127599474</v>
+      </c>
+      <c r="E94">
+        <v>1212</v>
+      </c>
+      <c r="F94" s="2">
+        <v>45427</v>
+      </c>
+      <c r="G94" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I94">
+        <v>42</v>
+      </c>
+      <c r="J94">
+        <v>8001</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>127646444</v>
+      </c>
+      <c r="E95">
+        <v>1212</v>
+      </c>
+      <c r="F95" s="2">
+        <v>45426</v>
+      </c>
+      <c r="G95" s="2">
+        <v>45425</v>
+      </c>
+      <c r="I95">
+        <v>42</v>
+      </c>
+      <c r="J95">
+        <v>8021</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>126954503</v>
+      </c>
+      <c r="E96">
+        <v>601</v>
+      </c>
+      <c r="F96" s="2">
+        <v>45378</v>
+      </c>
+      <c r="G96" s="2">
+        <v>45378</v>
+      </c>
+      <c r="I96">
+        <v>42</v>
+      </c>
+      <c r="J96">
+        <v>8017</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>127584638</v>
+      </c>
+      <c r="E97">
+        <v>601</v>
+      </c>
+      <c r="F97" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G97" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I97">
+        <v>42</v>
+      </c>
+      <c r="J97">
+        <v>8013</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>127584645</v>
+      </c>
+      <c r="E98">
+        <v>601</v>
+      </c>
+      <c r="F98" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G98" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I98">
+        <v>42</v>
+      </c>
+      <c r="J98">
+        <v>8013</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>127584649</v>
+      </c>
+      <c r="E99">
+        <v>601</v>
+      </c>
+      <c r="F99" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G99" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I99">
+        <v>42</v>
+      </c>
+      <c r="J99">
+        <v>8013</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>0</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>127588846</v>
+      </c>
+      <c r="E100">
+        <v>601</v>
+      </c>
+      <c r="F100" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G100" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I100">
+        <v>42</v>
+      </c>
+      <c r="J100">
+        <v>8004</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>127588939</v>
+      </c>
+      <c r="E101">
+        <v>601</v>
+      </c>
+      <c r="F101" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G101" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I101">
+        <v>42</v>
+      </c>
+      <c r="J101">
+        <v>8013</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>0</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+      <c r="Q101">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>127606044</v>
+      </c>
+      <c r="E102">
+        <v>601</v>
+      </c>
+      <c r="F102" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G102" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I102">
+        <v>42</v>
+      </c>
+      <c r="J102">
+        <v>8004</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>127607597</v>
+      </c>
+      <c r="E103">
+        <v>601</v>
+      </c>
+      <c r="F103" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G103" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I103">
+        <v>42</v>
+      </c>
+      <c r="J103">
+        <v>8004</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>127608440</v>
+      </c>
+      <c r="E104">
+        <v>601</v>
+      </c>
+      <c r="F104" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G104" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I104">
+        <v>42</v>
+      </c>
+      <c r="J104">
+        <v>8004</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>127611442</v>
+      </c>
+      <c r="E105">
+        <v>601</v>
+      </c>
+      <c r="F105" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G105" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I105">
+        <v>42</v>
+      </c>
+      <c r="J105">
+        <v>8004</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+      <c r="Q105">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>127634669</v>
+      </c>
+      <c r="E106">
+        <v>601</v>
+      </c>
+      <c r="F106" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G106" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I106">
+        <v>42</v>
+      </c>
+      <c r="J106">
+        <v>8013</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+      <c r="Q106">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>127639948</v>
+      </c>
+      <c r="E107">
+        <v>601</v>
+      </c>
+      <c r="F107" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G107" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I107">
+        <v>42</v>
+      </c>
+      <c r="J107">
+        <v>8004</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="Q107">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>127587095</v>
+      </c>
+      <c r="E108">
+        <v>601</v>
+      </c>
+      <c r="F108" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G108" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I108">
+        <v>42</v>
+      </c>
+      <c r="J108">
+        <v>8004</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+      <c r="Q108">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>127589162</v>
+      </c>
+      <c r="E109">
+        <v>601</v>
+      </c>
+      <c r="F109" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G109" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I109">
+        <v>42</v>
+      </c>
+      <c r="J109">
+        <v>8004</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+      <c r="Q109">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>127589682</v>
+      </c>
+      <c r="E110">
+        <v>601</v>
+      </c>
+      <c r="F110" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G110" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I110">
+        <v>42</v>
+      </c>
+      <c r="J110">
+        <v>8004</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+      <c r="Q110">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>127589696</v>
+      </c>
+      <c r="E111">
+        <v>601</v>
+      </c>
+      <c r="F111" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G111" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I111">
+        <v>42</v>
+      </c>
+      <c r="J111">
+        <v>8004</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>127589924</v>
+      </c>
+      <c r="E112">
+        <v>601</v>
+      </c>
+      <c r="F112" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G112" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I112">
+        <v>42</v>
+      </c>
+      <c r="J112">
+        <v>8004</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>0</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>0</v>
+      </c>
+      <c r="Q112">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>127590134</v>
+      </c>
+      <c r="E113">
+        <v>601</v>
+      </c>
+      <c r="F113" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G113" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I113">
+        <v>42</v>
+      </c>
+      <c r="J113">
+        <v>8004</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+      <c r="Q113">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>127590692</v>
+      </c>
+      <c r="E114">
+        <v>601</v>
+      </c>
+      <c r="F114" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G114" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I114">
+        <v>42</v>
+      </c>
+      <c r="J114">
+        <v>8004</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+      <c r="Q114">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>127590881</v>
+      </c>
+      <c r="E115">
+        <v>601</v>
+      </c>
+      <c r="F115" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G115" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I115">
+        <v>42</v>
+      </c>
+      <c r="J115">
+        <v>8004</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+      <c r="Q115">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>127591586</v>
+      </c>
+      <c r="E116">
+        <v>601</v>
+      </c>
+      <c r="F116" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G116" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I116">
+        <v>42</v>
+      </c>
+      <c r="J116">
+        <v>8004</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>0</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+      <c r="Q116">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>127592035</v>
+      </c>
+      <c r="E117">
+        <v>601</v>
+      </c>
+      <c r="F117" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G117" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I117">
+        <v>42</v>
+      </c>
+      <c r="J117">
+        <v>8004</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>127592607</v>
+      </c>
+      <c r="E118">
+        <v>601</v>
+      </c>
+      <c r="F118" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G118" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I118">
+        <v>42</v>
+      </c>
+      <c r="J118">
+        <v>8004</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>0</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+      <c r="Q118">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>127593826</v>
+      </c>
+      <c r="E119">
+        <v>601</v>
+      </c>
+      <c r="F119" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G119" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I119">
+        <v>42</v>
+      </c>
+      <c r="J119">
+        <v>8004</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+      <c r="Q119">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>127594087</v>
+      </c>
+      <c r="E120">
+        <v>601</v>
+      </c>
+      <c r="F120" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G120" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I120">
+        <v>42</v>
+      </c>
+      <c r="J120">
+        <v>8004</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+      <c r="Q120">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>127595805</v>
+      </c>
+      <c r="E121">
+        <v>601</v>
+      </c>
+      <c r="F121" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G121" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I121">
+        <v>42</v>
+      </c>
+      <c r="J121">
+        <v>8004</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+      <c r="Q121">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>127595879</v>
+      </c>
+      <c r="E122">
+        <v>601</v>
+      </c>
+      <c r="F122" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G122" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I122">
+        <v>42</v>
+      </c>
+      <c r="J122">
+        <v>8004</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+      <c r="Q122">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>127596105</v>
+      </c>
+      <c r="E123">
+        <v>601</v>
+      </c>
+      <c r="F123" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G123" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I123">
+        <v>42</v>
+      </c>
+      <c r="J123">
+        <v>8004</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>0</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+      <c r="Q123">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>127596181</v>
+      </c>
+      <c r="E124">
+        <v>601</v>
+      </c>
+      <c r="F124" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G124" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I124">
+        <v>42</v>
+      </c>
+      <c r="J124">
+        <v>8004</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>0</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+      <c r="Q124">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>127596567</v>
+      </c>
+      <c r="E125">
+        <v>601</v>
+      </c>
+      <c r="F125" s="2">
+        <v>45419</v>
+      </c>
+      <c r="G125" s="2">
+        <v>45419</v>
+      </c>
+      <c r="I125">
+        <v>42</v>
+      </c>
+      <c r="J125">
+        <v>8004</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+      <c r="Q125">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>127599677</v>
+      </c>
+      <c r="E126">
+        <v>601</v>
+      </c>
+      <c r="F126" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G126" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I126">
+        <v>42</v>
+      </c>
+      <c r="J126">
+        <v>8004</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>127599688</v>
+      </c>
+      <c r="E127">
+        <v>601</v>
+      </c>
+      <c r="F127" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G127" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I127">
+        <v>42</v>
+      </c>
+      <c r="J127">
+        <v>8004</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>127599736</v>
+      </c>
+      <c r="E128">
+        <v>601</v>
+      </c>
+      <c r="F128" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G128" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I128">
+        <v>42</v>
+      </c>
+      <c r="J128">
+        <v>8004</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+      <c r="Q128">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>127600440</v>
+      </c>
+      <c r="E129">
+        <v>601</v>
+      </c>
+      <c r="F129" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G129" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I129">
+        <v>42</v>
+      </c>
+      <c r="J129">
+        <v>8004</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+      <c r="Q129">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>127601326</v>
+      </c>
+      <c r="E130">
+        <v>601</v>
+      </c>
+      <c r="F130" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G130" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I130">
+        <v>42</v>
+      </c>
+      <c r="J130">
+        <v>8004</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+      <c r="Q130">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>127603188</v>
+      </c>
+      <c r="E131">
+        <v>601</v>
+      </c>
+      <c r="F131" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G131" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I131">
+        <v>42</v>
+      </c>
+      <c r="J131">
+        <v>8004</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+      <c r="Q131">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>127607057</v>
+      </c>
+      <c r="E132">
+        <v>601</v>
+      </c>
+      <c r="F132" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G132" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I132">
+        <v>42</v>
+      </c>
+      <c r="J132">
+        <v>8004</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+      <c r="Q132">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>127607600</v>
+      </c>
+      <c r="E133">
+        <v>601</v>
+      </c>
+      <c r="F133" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G133" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I133">
+        <v>42</v>
+      </c>
+      <c r="J133">
+        <v>8004</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+      <c r="Q133">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>127608657</v>
+      </c>
+      <c r="E134">
+        <v>601</v>
+      </c>
+      <c r="F134" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G134" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I134">
+        <v>42</v>
+      </c>
+      <c r="J134">
+        <v>8004</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+      <c r="Q134">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>127609113</v>
+      </c>
+      <c r="E135">
+        <v>601</v>
+      </c>
+      <c r="F135" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G135" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I135">
+        <v>42</v>
+      </c>
+      <c r="J135">
+        <v>8004</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+      <c r="Q135">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>127611000</v>
+      </c>
+      <c r="E136">
+        <v>601</v>
+      </c>
+      <c r="F136" s="2">
+        <v>45420</v>
+      </c>
+      <c r="G136" s="2">
+        <v>45420</v>
+      </c>
+      <c r="I136">
+        <v>42</v>
+      </c>
+      <c r="J136">
+        <v>8004</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>0</v>
+      </c>
+      <c r="Q136">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>127613425</v>
+      </c>
+      <c r="E137">
+        <v>601</v>
+      </c>
+      <c r="F137" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G137" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I137">
+        <v>42</v>
+      </c>
+      <c r="J137">
+        <v>8004</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+      <c r="Q137">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>127614787</v>
+      </c>
+      <c r="E138">
+        <v>601</v>
+      </c>
+      <c r="F138" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G138" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I138">
+        <v>42</v>
+      </c>
+      <c r="J138">
+        <v>8004</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="Q138">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>127614848</v>
+      </c>
+      <c r="E139">
+        <v>601</v>
+      </c>
+      <c r="F139" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G139" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I139">
+        <v>42</v>
+      </c>
+      <c r="J139">
+        <v>8004</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>0</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+      <c r="Q139">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>127615043</v>
+      </c>
+      <c r="E140">
+        <v>601</v>
+      </c>
+      <c r="F140" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G140" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I140">
+        <v>42</v>
+      </c>
+      <c r="J140">
+        <v>8004</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>0</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+      <c r="Q140">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>127615223</v>
+      </c>
+      <c r="E141">
+        <v>601</v>
+      </c>
+      <c r="F141" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G141" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I141">
+        <v>42</v>
+      </c>
+      <c r="J141">
+        <v>1118</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>0</v>
+      </c>
+      <c r="N141">
+        <v>0</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+      <c r="Q141">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>127615674</v>
+      </c>
+      <c r="E142">
+        <v>601</v>
+      </c>
+      <c r="F142" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G142" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I142">
+        <v>42</v>
+      </c>
+      <c r="J142">
+        <v>8004</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+      <c r="Q142">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>127617067</v>
+      </c>
+      <c r="E143">
+        <v>601</v>
+      </c>
+      <c r="F143" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G143" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I143">
+        <v>42</v>
+      </c>
+      <c r="J143">
+        <v>8004</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>0</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+      <c r="Q143">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>127617452</v>
+      </c>
+      <c r="E144">
+        <v>601</v>
+      </c>
+      <c r="F144" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G144" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I144">
+        <v>42</v>
+      </c>
+      <c r="J144">
+        <v>8004</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>0</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>0</v>
+      </c>
+      <c r="Q144">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>127617660</v>
+      </c>
+      <c r="E145">
+        <v>601</v>
+      </c>
+      <c r="F145" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G145" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I145">
+        <v>42</v>
+      </c>
+      <c r="J145">
+        <v>8004</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>0</v>
+      </c>
+      <c r="Q145">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>127617713</v>
+      </c>
+      <c r="E146">
+        <v>601</v>
+      </c>
+      <c r="F146" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G146" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I146">
+        <v>42</v>
+      </c>
+      <c r="J146">
+        <v>8004</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="N146">
+        <v>0</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+      <c r="Q146">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>127617908</v>
+      </c>
+      <c r="E147">
+        <v>601</v>
+      </c>
+      <c r="F147" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G147" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I147">
+        <v>42</v>
+      </c>
+      <c r="J147">
+        <v>8004</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>0</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>0</v>
+      </c>
+      <c r="Q147">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>127618188</v>
+      </c>
+      <c r="E148">
+        <v>601</v>
+      </c>
+      <c r="F148" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G148" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I148">
+        <v>42</v>
+      </c>
+      <c r="J148">
+        <v>8004</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>0</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>0</v>
+      </c>
+      <c r="Q148">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>127618341</v>
+      </c>
+      <c r="E149">
+        <v>601</v>
+      </c>
+      <c r="F149" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G149" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I149">
+        <v>42</v>
+      </c>
+      <c r="J149">
+        <v>8004</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <v>0</v>
+      </c>
+      <c r="Q149">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>127620400</v>
+      </c>
+      <c r="E150">
+        <v>601</v>
+      </c>
+      <c r="F150" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G150" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I150">
+        <v>42</v>
+      </c>
+      <c r="J150">
+        <v>8004</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>0</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>0</v>
+      </c>
+      <c r="Q150">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>127620868</v>
+      </c>
+      <c r="E151">
+        <v>601</v>
+      </c>
+      <c r="F151" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G151" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I151">
+        <v>42</v>
+      </c>
+      <c r="J151">
+        <v>8004</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>0</v>
+      </c>
+      <c r="N151">
+        <v>0</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>0</v>
+      </c>
+      <c r="Q151">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>127621058</v>
+      </c>
+      <c r="E152">
+        <v>601</v>
+      </c>
+      <c r="F152" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G152" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I152">
+        <v>42</v>
+      </c>
+      <c r="J152">
+        <v>8004</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>0</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>0</v>
+      </c>
+      <c r="Q152">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>127621380</v>
+      </c>
+      <c r="E153">
+        <v>601</v>
+      </c>
+      <c r="F153" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G153" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I153">
+        <v>42</v>
+      </c>
+      <c r="J153">
+        <v>8004</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>0</v>
+      </c>
+      <c r="N153">
+        <v>0</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>0</v>
+      </c>
+      <c r="Q153">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>127623027</v>
+      </c>
+      <c r="E154">
+        <v>601</v>
+      </c>
+      <c r="F154" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G154" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I154">
+        <v>42</v>
+      </c>
+      <c r="J154">
+        <v>8004</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>0</v>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>0</v>
+      </c>
+      <c r="Q154">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>127623363</v>
+      </c>
+      <c r="E155">
+        <v>601</v>
+      </c>
+      <c r="F155" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G155" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I155">
+        <v>42</v>
+      </c>
+      <c r="J155">
+        <v>8004</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="N155">
+        <v>0</v>
+      </c>
+      <c r="O155">
+        <v>0</v>
+      </c>
+      <c r="P155">
+        <v>0</v>
+      </c>
+      <c r="Q155">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <v>127624138</v>
+      </c>
+      <c r="E156">
+        <v>601</v>
+      </c>
+      <c r="F156" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G156" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I156">
+        <v>42</v>
+      </c>
+      <c r="J156">
+        <v>8004</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156">
+        <v>0</v>
+      </c>
+      <c r="Q156">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A157">
+        <v>127624307</v>
+      </c>
+      <c r="E157">
+        <v>601</v>
+      </c>
+      <c r="F157" s="2">
+        <v>45421</v>
+      </c>
+      <c r="G157" s="2">
+        <v>45421</v>
+      </c>
+      <c r="I157">
+        <v>42</v>
+      </c>
+      <c r="J157">
+        <v>8004</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>0</v>
+      </c>
+      <c r="O157">
+        <v>0</v>
+      </c>
+      <c r="P157">
+        <v>0</v>
+      </c>
+      <c r="Q157">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <v>127630088</v>
+      </c>
+      <c r="E158">
+        <v>601</v>
+      </c>
+      <c r="F158" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G158" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I158">
+        <v>42</v>
+      </c>
+      <c r="J158">
+        <v>8004</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
+      </c>
+      <c r="N158">
+        <v>0</v>
+      </c>
+      <c r="O158">
+        <v>0</v>
+      </c>
+      <c r="P158">
+        <v>0</v>
+      </c>
+      <c r="Q158">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <v>127632152</v>
+      </c>
+      <c r="E159">
+        <v>601</v>
+      </c>
+      <c r="F159" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G159" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I159">
+        <v>42</v>
+      </c>
+      <c r="J159">
+        <v>8004</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="N159">
+        <v>0</v>
+      </c>
+      <c r="O159">
+        <v>0</v>
+      </c>
+      <c r="P159">
+        <v>0</v>
+      </c>
+      <c r="Q159">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A160">
+        <v>127633361</v>
+      </c>
+      <c r="E160">
+        <v>601</v>
+      </c>
+      <c r="F160" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G160" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I160">
+        <v>42</v>
+      </c>
+      <c r="J160">
+        <v>8004</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>0</v>
+      </c>
+      <c r="O160">
+        <v>0</v>
+      </c>
+      <c r="P160">
+        <v>0</v>
+      </c>
+      <c r="Q160">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A161">
+        <v>127633633</v>
+      </c>
+      <c r="E161">
+        <v>601</v>
+      </c>
+      <c r="F161" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G161" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I161">
+        <v>42</v>
+      </c>
+      <c r="J161">
+        <v>8004</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161">
+        <v>0</v>
+      </c>
+      <c r="N161">
+        <v>0</v>
+      </c>
+      <c r="O161">
+        <v>0</v>
+      </c>
+      <c r="P161">
+        <v>0</v>
+      </c>
+      <c r="Q161">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A162">
+        <v>127634043</v>
+      </c>
+      <c r="E162">
+        <v>601</v>
+      </c>
+      <c r="F162" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G162" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I162">
+        <v>42</v>
+      </c>
+      <c r="J162">
+        <v>8004</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="M162">
+        <v>0</v>
+      </c>
+      <c r="N162">
+        <v>0</v>
+      </c>
+      <c r="O162">
+        <v>0</v>
+      </c>
+      <c r="P162">
+        <v>0</v>
+      </c>
+      <c r="Q162">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A163">
+        <v>127637095</v>
+      </c>
+      <c r="E163">
+        <v>601</v>
+      </c>
+      <c r="F163" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G163" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I163">
+        <v>42</v>
+      </c>
+      <c r="J163">
+        <v>8004</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="N163">
+        <v>0</v>
+      </c>
+      <c r="O163">
+        <v>0</v>
+      </c>
+      <c r="P163">
+        <v>0</v>
+      </c>
+      <c r="Q163">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A164">
+        <v>127639129</v>
+      </c>
+      <c r="E164">
+        <v>601</v>
+      </c>
+      <c r="F164" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G164" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I164">
+        <v>42</v>
+      </c>
+      <c r="J164">
+        <v>8004</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164">
+        <v>0</v>
+      </c>
+      <c r="O164">
+        <v>0</v>
+      </c>
+      <c r="P164">
+        <v>0</v>
+      </c>
+      <c r="Q164">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A165">
+        <v>127639536</v>
+      </c>
+      <c r="E165">
+        <v>601</v>
+      </c>
+      <c r="F165" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G165" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I165">
+        <v>42</v>
+      </c>
+      <c r="J165">
+        <v>8004</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="N165">
+        <v>0</v>
+      </c>
+      <c r="O165">
+        <v>0</v>
+      </c>
+      <c r="P165">
+        <v>0</v>
+      </c>
+      <c r="Q165">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A166">
+        <v>127640835</v>
+      </c>
+      <c r="E166">
+        <v>601</v>
+      </c>
+      <c r="F166" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G166" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I166">
+        <v>42</v>
+      </c>
+      <c r="J166">
+        <v>8004</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166">
+        <v>0</v>
+      </c>
+      <c r="O166">
+        <v>0</v>
+      </c>
+      <c r="P166">
+        <v>0</v>
+      </c>
+      <c r="Q166">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A167">
+        <v>127641271</v>
+      </c>
+      <c r="E167">
+        <v>601</v>
+      </c>
+      <c r="F167" s="2">
+        <v>45422</v>
+      </c>
+      <c r="G167" s="2">
+        <v>45422</v>
+      </c>
+      <c r="I167">
+        <v>42</v>
+      </c>
+      <c r="J167">
+        <v>8004</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="N167">
+        <v>0</v>
+      </c>
+      <c r="O167">
+        <v>0</v>
+      </c>
+      <c r="P167">
+        <v>0</v>
+      </c>
+      <c r="Q167">
         <v>61</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q50" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}"/>
+  <autoFilter ref="A1:Q167" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -10036,31 +14482,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2044CFC5-A190-4FCF-BDDA-70708ECB1F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9CFC66-BE6E-4D5A-B9EE-0A3763CEE9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$122</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q167"/>
+  <dimension ref="A1:Q122"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,16 +585,16 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>127677397</v>
+        <v>127707556</v>
       </c>
       <c r="E2">
         <v>1211</v>
       </c>
       <c r="F2" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G2" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="I2">
         <v>42</v>
@@ -623,16 +623,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>127678516</v>
+        <v>127709320</v>
       </c>
       <c r="E3">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F3" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="G3" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="I3">
         <v>42</v>
@@ -661,16 +661,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>127680312</v>
+        <v>127710005</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G4" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="I4">
         <v>42</v>
@@ -699,16 +699,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>127680551</v>
+        <v>127713128</v>
       </c>
       <c r="E5">
         <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G5" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="I5">
         <v>42</v>
@@ -737,16 +737,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>127683408</v>
+        <v>127713615</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="G6" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="I6">
         <v>42</v>
@@ -775,16 +775,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>127683415</v>
+        <v>127714268</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="G7" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -813,22 +813,22 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>127686897</v>
+        <v>124085593</v>
       </c>
       <c r="E8">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F8" s="2">
         <v>45428</v>
       </c>
       <c r="G8" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="I8">
         <v>42</v>
       </c>
       <c r="J8">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -851,22 +851,22 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>127689861</v>
+        <v>124114081</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G9" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I9">
         <v>42</v>
       </c>
       <c r="J9">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>127690780</v>
+        <v>124199837</v>
       </c>
       <c r="E10">
         <v>1211</v>
@@ -904,7 +904,7 @@
         <v>42</v>
       </c>
       <c r="J10">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -927,13 +927,13 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>127694205</v>
+        <v>124241728</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="G11" s="2">
         <v>45428</v>
@@ -942,7 +942,7 @@
         <v>42</v>
       </c>
       <c r="J11">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -965,10 +965,10 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>127695138</v>
+        <v>124382401</v>
       </c>
       <c r="E12">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F12" s="2">
         <v>45428</v>
@@ -980,7 +980,7 @@
         <v>42</v>
       </c>
       <c r="J12">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1003,22 +1003,22 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>127697983</v>
+        <v>124382473</v>
       </c>
       <c r="E13">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45428</v>
+        <v>45430</v>
       </c>
       <c r="G13" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I13">
         <v>42</v>
       </c>
       <c r="J13">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -1041,13 +1041,13 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>127699757</v>
+        <v>124509919</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="G14" s="2">
         <v>45428</v>
@@ -1056,7 +1056,7 @@
         <v>42</v>
       </c>
       <c r="J14">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>127699831</v>
+        <v>124526674</v>
       </c>
       <c r="E15">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F15" s="2">
         <v>45428</v>
@@ -1094,7 +1094,7 @@
         <v>42</v>
       </c>
       <c r="J15">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1117,22 +1117,22 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>127701357</v>
+        <v>124556596</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45429</v>
+        <v>45430</v>
       </c>
       <c r="G16" s="2">
-        <v>45428</v>
+        <v>45430</v>
       </c>
       <c r="I16">
         <v>42</v>
       </c>
       <c r="J16">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>124085593</v>
+        <v>124580685</v>
       </c>
       <c r="E17">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45428</v>
+        <v>45430</v>
       </c>
       <c r="G17" s="2">
-        <v>45428</v>
+        <v>45430</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>124114081</v>
+        <v>124736297</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="G18" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>124199837</v>
+        <v>124805931</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G19" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,16 +1269,16 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>124241728</v>
+        <v>124829987</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G20" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I20">
         <v>42</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>124382401</v>
+        <v>124876290</v>
       </c>
       <c r="E21">
         <v>1211</v>
@@ -1345,13 +1345,13 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>124382473</v>
+        <v>125052952</v>
       </c>
       <c r="E22">
         <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45430</v>
+        <v>45429</v>
       </c>
       <c r="G22" s="2">
         <v>45429</v>
@@ -1383,16 +1383,16 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>124509919</v>
+        <v>125184702</v>
       </c>
       <c r="E23">
         <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G23" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1421,16 +1421,16 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>124526674</v>
+        <v>125195701</v>
       </c>
       <c r="E24">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G24" s="2">
-        <v>45428</v>
+        <v>45426</v>
       </c>
       <c r="I24">
         <v>42</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>124556596</v>
+        <v>125304585</v>
       </c>
       <c r="E25">
         <v>1211</v>
@@ -1497,16 +1497,16 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>124580685</v>
+        <v>125384268</v>
       </c>
       <c r="E26">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F26" s="2">
-        <v>45430</v>
+        <v>45428</v>
       </c>
       <c r="G26" s="2">
-        <v>45430</v>
+        <v>45428</v>
       </c>
       <c r="I26">
         <v>42</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>124736297</v>
+        <v>125422780</v>
       </c>
       <c r="E27">
         <v>1211</v>
@@ -1544,7 +1544,7 @@
         <v>45428</v>
       </c>
       <c r="G27" s="2">
-        <v>45428</v>
+        <v>45427</v>
       </c>
       <c r="I27">
         <v>42</v>
@@ -1573,16 +1573,16 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>124805931</v>
+        <v>125426528</v>
       </c>
       <c r="E28">
         <v>1211</v>
       </c>
       <c r="F28" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="G28" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="I28">
         <v>42</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
-        <v>124829987</v>
+        <v>125505055</v>
       </c>
       <c r="E29">
         <v>1211</v>
@@ -1649,16 +1649,16 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
-        <v>124876290</v>
+        <v>125574465</v>
       </c>
       <c r="E30">
         <v>1211</v>
       </c>
       <c r="F30" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G30" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I30">
         <v>42</v>
@@ -1687,16 +1687,16 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
-        <v>125006076</v>
+        <v>125650786</v>
       </c>
       <c r="E31">
         <v>1211</v>
       </c>
       <c r="F31" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="G31" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="I31">
         <v>42</v>
@@ -1725,16 +1725,16 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
-        <v>125052952</v>
+        <v>125691862</v>
       </c>
       <c r="E32">
         <v>1211</v>
       </c>
       <c r="F32" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="G32" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="I32">
         <v>42</v>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
-        <v>125184702</v>
+        <v>125769830</v>
       </c>
       <c r="E33">
         <v>1211</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
-        <v>125195701</v>
+        <v>125782283</v>
       </c>
       <c r="E34">
         <v>1211</v>
@@ -1810,7 +1810,7 @@
         <v>45429</v>
       </c>
       <c r="G34" s="2">
-        <v>45426</v>
+        <v>45429</v>
       </c>
       <c r="I34">
         <v>42</v>
@@ -1839,16 +1839,16 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
-        <v>125304585</v>
+        <v>125934594</v>
       </c>
       <c r="E35">
         <v>1211</v>
       </c>
       <c r="F35" s="2">
-        <v>45430</v>
+        <v>45429</v>
       </c>
       <c r="G35" s="2">
-        <v>45430</v>
+        <v>45426</v>
       </c>
       <c r="I35">
         <v>42</v>
@@ -1877,16 +1877,16 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
-        <v>125384268</v>
+        <v>125982656</v>
       </c>
       <c r="E36">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F36" s="2">
-        <v>45428</v>
+        <v>45430</v>
       </c>
       <c r="G36" s="2">
-        <v>45428</v>
+        <v>45430</v>
       </c>
       <c r="I36">
         <v>42</v>
@@ -1915,16 +1915,16 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
-        <v>125422780</v>
+        <v>126014517</v>
       </c>
       <c r="E37">
         <v>1211</v>
       </c>
       <c r="F37" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G37" s="2">
-        <v>45427</v>
+        <v>45426</v>
       </c>
       <c r="I37">
         <v>42</v>
@@ -1953,16 +1953,16 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
-        <v>125426528</v>
+        <v>126033754</v>
       </c>
       <c r="E38">
         <v>1211</v>
       </c>
       <c r="F38" s="2">
-        <v>45428</v>
+        <v>45430</v>
       </c>
       <c r="G38" s="2">
-        <v>45428</v>
+        <v>45430</v>
       </c>
       <c r="I38">
         <v>42</v>
@@ -1991,7 +1991,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
-        <v>125430469</v>
+        <v>126075570</v>
       </c>
       <c r="E39">
         <v>1211</v>
@@ -2000,7 +2000,7 @@
         <v>45429</v>
       </c>
       <c r="G39" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I39">
         <v>42</v>
@@ -2029,13 +2029,13 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
-        <v>125505055</v>
+        <v>126085447</v>
       </c>
       <c r="E40">
         <v>1211</v>
       </c>
       <c r="F40" s="2">
-        <v>45429</v>
+        <v>45430</v>
       </c>
       <c r="G40" s="2">
         <v>45429</v>
@@ -2067,16 +2067,16 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
-        <v>125541063</v>
+        <v>126091614</v>
       </c>
       <c r="E41">
         <v>1211</v>
       </c>
       <c r="F41" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G41" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="I41">
         <v>42</v>
@@ -2105,16 +2105,16 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
-        <v>125574465</v>
+        <v>126384960</v>
       </c>
       <c r="E42">
         <v>1211</v>
       </c>
       <c r="F42" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="G42" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="I42">
         <v>42</v>
@@ -2143,16 +2143,16 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
-        <v>125588345</v>
+        <v>126611925</v>
       </c>
       <c r="E43">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F43" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G43" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="I43">
         <v>42</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
-        <v>125650786</v>
+        <v>126618728</v>
       </c>
       <c r="E44">
         <v>1211</v>
@@ -2219,16 +2219,16 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
-        <v>125691862</v>
+        <v>126704127</v>
       </c>
       <c r="E45">
         <v>1211</v>
       </c>
       <c r="F45" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G45" s="2">
-        <v>45428</v>
+        <v>45427</v>
       </c>
       <c r="I45">
         <v>42</v>
@@ -2257,16 +2257,16 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>125769830</v>
+        <v>126753264</v>
       </c>
       <c r="E46">
         <v>1211</v>
       </c>
       <c r="F46" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="G46" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="I46">
         <v>42</v>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
-        <v>125782283</v>
+        <v>126838674</v>
       </c>
       <c r="E47">
         <v>1211</v>
@@ -2333,16 +2333,16 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
-        <v>125934594</v>
+        <v>126867169</v>
       </c>
       <c r="E48">
         <v>1211</v>
       </c>
       <c r="F48" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="G48" s="2">
-        <v>45426</v>
+        <v>45428</v>
       </c>
       <c r="I48">
         <v>42</v>
@@ -2371,16 +2371,16 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
-        <v>125982656</v>
+        <v>126930388</v>
       </c>
       <c r="E49">
         <v>1211</v>
       </c>
       <c r="F49" s="2">
-        <v>45430</v>
+        <v>45429</v>
       </c>
       <c r="G49" s="2">
-        <v>45430</v>
+        <v>45429</v>
       </c>
       <c r="I49">
         <v>42</v>
@@ -2409,16 +2409,16 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
-        <v>126014517</v>
+        <v>126963758</v>
       </c>
       <c r="E50">
         <v>1211</v>
       </c>
       <c r="F50" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="G50" s="2">
-        <v>45426</v>
+        <v>45428</v>
       </c>
       <c r="I50">
         <v>42</v>
@@ -2447,16 +2447,16 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
-        <v>126033754</v>
+        <v>126971134</v>
       </c>
       <c r="E51">
         <v>1211</v>
       </c>
       <c r="F51" s="2">
-        <v>45430</v>
+        <v>45428</v>
       </c>
       <c r="G51" s="2">
-        <v>45430</v>
+        <v>45428</v>
       </c>
       <c r="I51">
         <v>42</v>
@@ -2485,16 +2485,16 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
-        <v>126070690</v>
+        <v>126976721</v>
       </c>
       <c r="E52">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F52" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G52" s="2">
-        <v>45422</v>
+        <v>45428</v>
       </c>
       <c r="I52">
         <v>42</v>
@@ -2523,7 +2523,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
-        <v>126075570</v>
+        <v>127013708</v>
       </c>
       <c r="E53">
         <v>1211</v>
@@ -2561,16 +2561,16 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>126085447</v>
+        <v>127013931</v>
       </c>
       <c r="E54">
         <v>1211</v>
       </c>
       <c r="F54" s="2">
-        <v>45430</v>
+        <v>45428</v>
       </c>
       <c r="G54" s="2">
-        <v>45429</v>
+        <v>45426</v>
       </c>
       <c r="I54">
         <v>42</v>
@@ -2599,16 +2599,16 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>126091614</v>
+        <v>127054069</v>
       </c>
       <c r="E55">
         <v>1211</v>
       </c>
       <c r="F55" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G55" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I55">
         <v>42</v>
@@ -2637,16 +2637,16 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
-        <v>126121295</v>
+        <v>127080906</v>
       </c>
       <c r="E56">
         <v>1211</v>
       </c>
       <c r="F56" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="G56" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="I56">
         <v>42</v>
@@ -2675,16 +2675,16 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
-        <v>126261196</v>
+        <v>127103245</v>
       </c>
       <c r="E57">
         <v>1211</v>
       </c>
       <c r="F57" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G57" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I57">
         <v>42</v>
@@ -2713,16 +2713,16 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>126384960</v>
+        <v>127261315</v>
       </c>
       <c r="E58">
         <v>1211</v>
       </c>
       <c r="F58" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G58" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I58">
         <v>42</v>
@@ -2751,7 +2751,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>126611925</v>
+        <v>127326475</v>
       </c>
       <c r="E59">
         <v>1211</v>
@@ -2789,16 +2789,16 @@
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
-        <v>126618728</v>
+        <v>127333904</v>
       </c>
       <c r="E60">
         <v>1211</v>
       </c>
       <c r="F60" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="G60" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="I60">
         <v>42</v>
@@ -2827,16 +2827,16 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
-        <v>126704127</v>
+        <v>127339851</v>
       </c>
       <c r="E61">
         <v>1211</v>
       </c>
       <c r="F61" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="G61" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="I61">
         <v>42</v>
@@ -2865,16 +2865,16 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>126744041</v>
+        <v>127368628</v>
       </c>
       <c r="E62">
         <v>1211</v>
       </c>
       <c r="F62" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G62" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="I62">
         <v>42</v>
@@ -2903,16 +2903,16 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>126753264</v>
+        <v>127412856</v>
       </c>
       <c r="E63">
         <v>1211</v>
       </c>
       <c r="F63" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G63" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I63">
         <v>42</v>
@@ -2941,16 +2941,16 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
-        <v>126838674</v>
+        <v>127443739</v>
       </c>
       <c r="E64">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F64" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="G64" s="2">
-        <v>45429</v>
+        <v>45428</v>
       </c>
       <c r="I64">
         <v>42</v>
@@ -2979,16 +2979,16 @@
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>126867169</v>
+        <v>127547571</v>
       </c>
       <c r="E65">
         <v>1211</v>
       </c>
       <c r="F65" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G65" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I65">
         <v>42</v>
@@ -3017,13 +3017,13 @@
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
-        <v>126879618</v>
+        <v>127563914</v>
       </c>
       <c r="E66">
         <v>1211</v>
       </c>
       <c r="F66" s="2">
-        <v>45427</v>
+        <v>45428</v>
       </c>
       <c r="G66" s="2">
         <v>45427</v>
@@ -3055,16 +3055,16 @@
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>126880595</v>
+        <v>127606707</v>
       </c>
       <c r="E67">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F67" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G67" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="I67">
         <v>42</v>
@@ -3093,7 +3093,7 @@
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>126930388</v>
+        <v>127621540</v>
       </c>
       <c r="E68">
         <v>1211</v>
@@ -3102,7 +3102,7 @@
         <v>45429</v>
       </c>
       <c r="G68" s="2">
-        <v>45429</v>
+        <v>45425</v>
       </c>
       <c r="I68">
         <v>42</v>
@@ -3131,7 +3131,7 @@
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
-        <v>126963758</v>
+        <v>127681123</v>
       </c>
       <c r="E69">
         <v>1211</v>
@@ -3169,22 +3169,22 @@
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>126971134</v>
+        <v>110074933</v>
       </c>
       <c r="E70">
         <v>1211</v>
       </c>
       <c r="F70" s="2">
-        <v>45428</v>
+        <v>43453</v>
       </c>
       <c r="G70" s="2">
-        <v>45428</v>
+        <v>43441</v>
       </c>
       <c r="I70">
         <v>42</v>
       </c>
       <c r="J70">
-        <v>8001</v>
+        <v>8023</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -3207,16 +3207,16 @@
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>126976721</v>
+        <v>127599474</v>
       </c>
       <c r="E71">
         <v>1212</v>
       </c>
       <c r="F71" s="2">
-        <v>45428</v>
+        <v>45427</v>
       </c>
       <c r="G71" s="2">
-        <v>45428</v>
+        <v>45420</v>
       </c>
       <c r="I71">
         <v>42</v>
@@ -3245,22 +3245,22 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
-        <v>127013708</v>
+        <v>127646444</v>
       </c>
       <c r="E72">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F72" s="2">
-        <v>45429</v>
+        <v>45426</v>
       </c>
       <c r="G72" s="2">
-        <v>45429</v>
+        <v>45425</v>
       </c>
       <c r="I72">
         <v>42</v>
       </c>
       <c r="J72">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
-        <v>127013931</v>
+        <v>126954503</v>
       </c>
       <c r="E73">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F73" s="2">
-        <v>45428</v>
+        <v>45378</v>
       </c>
       <c r="G73" s="2">
-        <v>45426</v>
+        <v>45378</v>
       </c>
       <c r="I73">
         <v>42</v>
       </c>
       <c r="J73">
-        <v>8001</v>
+        <v>8017</v>
       </c>
       <c r="L73">
         <v>0</v>
@@ -3321,22 +3321,22 @@
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
-        <v>127054069</v>
+        <v>127606044</v>
       </c>
       <c r="E74">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F74" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="G74" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="I74">
         <v>42</v>
       </c>
       <c r="J74">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -3359,22 +3359,22 @@
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
-        <v>127080906</v>
+        <v>127607597</v>
       </c>
       <c r="E75">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F75" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="G75" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="I75">
         <v>42</v>
       </c>
       <c r="J75">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -3397,22 +3397,22 @@
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
-        <v>127103245</v>
+        <v>127608440</v>
       </c>
       <c r="E76">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F76" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="G76" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="I76">
         <v>42</v>
       </c>
       <c r="J76">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -3435,22 +3435,22 @@
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
-        <v>127261315</v>
+        <v>127611442</v>
       </c>
       <c r="E77">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F77" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="G77" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="I77">
         <v>42</v>
       </c>
       <c r="J77">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L77">
         <v>0</v>
@@ -3473,22 +3473,22 @@
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
-        <v>127326475</v>
+        <v>127634669</v>
       </c>
       <c r="E78">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F78" s="2">
-        <v>45428</v>
+        <v>45422</v>
       </c>
       <c r="G78" s="2">
-        <v>45428</v>
+        <v>45422</v>
       </c>
       <c r="I78">
         <v>42</v>
       </c>
       <c r="J78">
-        <v>8001</v>
+        <v>8013</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
-        <v>127333904</v>
+        <v>127639948</v>
       </c>
       <c r="E79">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F79" s="2">
-        <v>45428</v>
+        <v>45422</v>
       </c>
       <c r="G79" s="2">
-        <v>45428</v>
+        <v>45422</v>
       </c>
       <c r="I79">
         <v>42</v>
       </c>
       <c r="J79">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -3549,22 +3549,22 @@
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
-        <v>127339851</v>
+        <v>127587095</v>
       </c>
       <c r="E80">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F80" s="2">
-        <v>45428</v>
+        <v>45420</v>
       </c>
       <c r="G80" s="2">
-        <v>45428</v>
+        <v>45420</v>
       </c>
       <c r="I80">
         <v>42</v>
       </c>
       <c r="J80">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
-        <v>127368628</v>
+        <v>127599677</v>
       </c>
       <c r="E81">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F81" s="2">
-        <v>45428</v>
+        <v>45420</v>
       </c>
       <c r="G81" s="2">
-        <v>45428</v>
+        <v>45420</v>
       </c>
       <c r="I81">
         <v>42</v>
       </c>
       <c r="J81">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -3625,22 +3625,22 @@
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
-        <v>127399208</v>
+        <v>127599688</v>
       </c>
       <c r="E82">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F82" s="2">
-        <v>45427</v>
+        <v>45420</v>
       </c>
       <c r="G82" s="2">
-        <v>45427</v>
+        <v>45420</v>
       </c>
       <c r="I82">
         <v>42</v>
       </c>
       <c r="J82">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L82">
         <v>0</v>
@@ -3663,22 +3663,22 @@
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
-        <v>127409475</v>
+        <v>127599736</v>
       </c>
       <c r="E83">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F83" s="2">
-        <v>45427</v>
+        <v>45420</v>
       </c>
       <c r="G83" s="2">
-        <v>45427</v>
+        <v>45420</v>
       </c>
       <c r="I83">
         <v>42</v>
       </c>
       <c r="J83">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -3701,22 +3701,22 @@
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
-        <v>127412856</v>
+        <v>127600440</v>
       </c>
       <c r="E84">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F84" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="G84" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="I84">
         <v>42</v>
       </c>
       <c r="J84">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L84">
         <v>0</v>
@@ -3739,22 +3739,22 @@
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
-        <v>127443739</v>
+        <v>127601326</v>
       </c>
       <c r="E85">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F85" s="2">
-        <v>45428</v>
+        <v>45420</v>
       </c>
       <c r="G85" s="2">
-        <v>45428</v>
+        <v>45420</v>
       </c>
       <c r="I85">
         <v>42</v>
       </c>
       <c r="J85">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -3777,22 +3777,22 @@
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
-        <v>127547571</v>
+        <v>127603188</v>
       </c>
       <c r="E86">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F86" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="G86" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="I86">
         <v>42</v>
       </c>
       <c r="J86">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L86">
         <v>0</v>
@@ -3815,22 +3815,22 @@
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
-        <v>127563914</v>
+        <v>127607057</v>
       </c>
       <c r="E87">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F87" s="2">
-        <v>45428</v>
+        <v>45420</v>
       </c>
       <c r="G87" s="2">
-        <v>45427</v>
+        <v>45420</v>
       </c>
       <c r="I87">
         <v>42</v>
       </c>
       <c r="J87">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -3853,22 +3853,22 @@
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
-        <v>127599028</v>
+        <v>127607600</v>
       </c>
       <c r="E88">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F88" s="2">
-        <v>45427</v>
+        <v>45420</v>
       </c>
       <c r="G88" s="2">
-        <v>45427</v>
+        <v>45420</v>
       </c>
       <c r="I88">
         <v>42</v>
       </c>
       <c r="J88">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -3891,22 +3891,22 @@
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
-        <v>127606707</v>
+        <v>127608657</v>
       </c>
       <c r="E89">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F89" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="G89" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="I89">
         <v>42</v>
       </c>
       <c r="J89">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -3929,22 +3929,22 @@
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
-        <v>127621540</v>
+        <v>127609113</v>
       </c>
       <c r="E90">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F90" s="2">
-        <v>45429</v>
+        <v>45420</v>
       </c>
       <c r="G90" s="2">
-        <v>45425</v>
+        <v>45420</v>
       </c>
       <c r="I90">
         <v>42</v>
       </c>
       <c r="J90">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L90">
         <v>0</v>
@@ -3967,22 +3967,22 @@
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
-        <v>127681123</v>
+        <v>127611000</v>
       </c>
       <c r="E91">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F91" s="2">
-        <v>45428</v>
+        <v>45420</v>
       </c>
       <c r="G91" s="2">
-        <v>45428</v>
+        <v>45420</v>
       </c>
       <c r="I91">
         <v>42</v>
       </c>
       <c r="J91">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
-        <v>110074933</v>
+        <v>127613425</v>
       </c>
       <c r="E92">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F92" s="2">
-        <v>43453</v>
+        <v>45421</v>
       </c>
       <c r="G92" s="2">
-        <v>43441</v>
+        <v>45421</v>
       </c>
       <c r="I92">
         <v>42</v>
       </c>
       <c r="J92">
-        <v>8023</v>
+        <v>8004</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -4043,22 +4043,22 @@
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
-        <v>123058958</v>
+        <v>127614787</v>
       </c>
       <c r="E93">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F93" s="2">
-        <v>44995</v>
+        <v>45421</v>
       </c>
       <c r="G93" s="2">
-        <v>44993</v>
+        <v>45421</v>
       </c>
       <c r="I93">
         <v>42</v>
       </c>
       <c r="J93">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -4081,22 +4081,22 @@
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
-        <v>127599474</v>
+        <v>127614848</v>
       </c>
       <c r="E94">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F94" s="2">
-        <v>45427</v>
+        <v>45421</v>
       </c>
       <c r="G94" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="I94">
         <v>42</v>
       </c>
       <c r="J94">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -4119,22 +4119,22 @@
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
-        <v>127646444</v>
+        <v>127615043</v>
       </c>
       <c r="E95">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F95" s="2">
-        <v>45426</v>
+        <v>45421</v>
       </c>
       <c r="G95" s="2">
-        <v>45425</v>
+        <v>45421</v>
       </c>
       <c r="I95">
         <v>42</v>
       </c>
       <c r="J95">
-        <v>8021</v>
+        <v>8004</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -4157,22 +4157,22 @@
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
-        <v>126954503</v>
+        <v>127615223</v>
       </c>
       <c r="E96">
         <v>601</v>
       </c>
       <c r="F96" s="2">
-        <v>45378</v>
+        <v>45421</v>
       </c>
       <c r="G96" s="2">
-        <v>45378</v>
+        <v>45421</v>
       </c>
       <c r="I96">
         <v>42</v>
       </c>
       <c r="J96">
-        <v>8017</v>
+        <v>1118</v>
       </c>
       <c r="L96">
         <v>0</v>
@@ -4195,22 +4195,22 @@
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
-        <v>127584638</v>
+        <v>127615674</v>
       </c>
       <c r="E97">
         <v>601</v>
       </c>
       <c r="F97" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="G97" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="I97">
         <v>42</v>
       </c>
       <c r="J97">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -4233,22 +4233,22 @@
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
-        <v>127584645</v>
+        <v>127617067</v>
       </c>
       <c r="E98">
         <v>601</v>
       </c>
       <c r="F98" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="G98" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="I98">
         <v>42</v>
       </c>
       <c r="J98">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -4271,22 +4271,22 @@
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
-        <v>127584649</v>
+        <v>127617452</v>
       </c>
       <c r="E99">
         <v>601</v>
       </c>
       <c r="F99" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="G99" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="I99">
         <v>42</v>
       </c>
       <c r="J99">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="L99">
         <v>0</v>
@@ -4309,16 +4309,16 @@
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
-        <v>127588846</v>
+        <v>127617660</v>
       </c>
       <c r="E100">
         <v>601</v>
       </c>
       <c r="F100" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="G100" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="I100">
         <v>42</v>
@@ -4347,22 +4347,22 @@
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
-        <v>127588939</v>
+        <v>127617713</v>
       </c>
       <c r="E101">
         <v>601</v>
       </c>
       <c r="F101" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="G101" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="I101">
         <v>42</v>
       </c>
       <c r="J101">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="L101">
         <v>0</v>
@@ -4385,16 +4385,16 @@
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
-        <v>127606044</v>
+        <v>127617908</v>
       </c>
       <c r="E102">
         <v>601</v>
       </c>
       <c r="F102" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G102" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="I102">
         <v>42</v>
@@ -4423,16 +4423,16 @@
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
-        <v>127607597</v>
+        <v>127618188</v>
       </c>
       <c r="E103">
         <v>601</v>
       </c>
       <c r="F103" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G103" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="I103">
         <v>42</v>
@@ -4461,16 +4461,16 @@
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
-        <v>127608440</v>
+        <v>127618341</v>
       </c>
       <c r="E104">
         <v>601</v>
       </c>
       <c r="F104" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G104" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="I104">
         <v>42</v>
@@ -4499,16 +4499,16 @@
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
-        <v>127611442</v>
+        <v>127620400</v>
       </c>
       <c r="E105">
         <v>601</v>
       </c>
       <c r="F105" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G105" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="I105">
         <v>42</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
-        <v>127634669</v>
+        <v>127620868</v>
       </c>
       <c r="E106">
         <v>601</v>
       </c>
       <c r="F106" s="2">
-        <v>45422</v>
+        <v>45421</v>
       </c>
       <c r="G106" s="2">
-        <v>45422</v>
+        <v>45421</v>
       </c>
       <c r="I106">
         <v>42</v>
       </c>
       <c r="J106">
-        <v>8013</v>
+        <v>8004</v>
       </c>
       <c r="L106">
         <v>0</v>
@@ -4575,16 +4575,16 @@
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
-        <v>127639948</v>
+        <v>127621058</v>
       </c>
       <c r="E107">
         <v>601</v>
       </c>
       <c r="F107" s="2">
-        <v>45422</v>
+        <v>45421</v>
       </c>
       <c r="G107" s="2">
-        <v>45422</v>
+        <v>45421</v>
       </c>
       <c r="I107">
         <v>42</v>
@@ -4613,16 +4613,16 @@
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
-        <v>127587095</v>
+        <v>127621380</v>
       </c>
       <c r="E108">
         <v>601</v>
       </c>
       <c r="F108" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="G108" s="2">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="I108">
         <v>42</v>
@@ -4651,16 +4651,16 @@
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109">
-        <v>127589162</v>
+        <v>127623027</v>
       </c>
       <c r="E109">
         <v>601</v>
       </c>
       <c r="F109" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="G109" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="I109">
         <v>42</v>
@@ -4689,16 +4689,16 @@
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110">
-        <v>127589682</v>
+        <v>127623363</v>
       </c>
       <c r="E110">
         <v>601</v>
       </c>
       <c r="F110" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="G110" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="I110">
         <v>42</v>
@@ -4727,16 +4727,16 @@
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111">
-        <v>127589696</v>
+        <v>127624138</v>
       </c>
       <c r="E111">
         <v>601</v>
       </c>
       <c r="F111" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="G111" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="I111">
         <v>42</v>
@@ -4765,16 +4765,16 @@
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112">
-        <v>127589924</v>
+        <v>127624307</v>
       </c>
       <c r="E112">
         <v>601</v>
       </c>
       <c r="F112" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="G112" s="2">
-        <v>45419</v>
+        <v>45421</v>
       </c>
       <c r="I112">
         <v>42</v>
@@ -4803,16 +4803,16 @@
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113">
-        <v>127590134</v>
+        <v>127630088</v>
       </c>
       <c r="E113">
         <v>601</v>
       </c>
       <c r="F113" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="G113" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="I113">
         <v>42</v>
@@ -4841,16 +4841,16 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A114">
-        <v>127590692</v>
+        <v>127632152</v>
       </c>
       <c r="E114">
         <v>601</v>
       </c>
       <c r="F114" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="G114" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="I114">
         <v>42</v>
@@ -4879,16 +4879,16 @@
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A115">
-        <v>127590881</v>
+        <v>127633361</v>
       </c>
       <c r="E115">
         <v>601</v>
       </c>
       <c r="F115" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="G115" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="I115">
         <v>42</v>
@@ -4917,16 +4917,16 @@
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A116">
-        <v>127591586</v>
+        <v>127633633</v>
       </c>
       <c r="E116">
         <v>601</v>
       </c>
       <c r="F116" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="G116" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="I116">
         <v>42</v>
@@ -4955,16 +4955,16 @@
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A117">
-        <v>127592035</v>
+        <v>127634043</v>
       </c>
       <c r="E117">
         <v>601</v>
       </c>
       <c r="F117" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="G117" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="I117">
         <v>42</v>
@@ -4993,16 +4993,16 @@
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A118">
-        <v>127592607</v>
+        <v>127637095</v>
       </c>
       <c r="E118">
         <v>601</v>
       </c>
       <c r="F118" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="G118" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="I118">
         <v>42</v>
@@ -5031,16 +5031,16 @@
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A119">
-        <v>127593826</v>
+        <v>127639129</v>
       </c>
       <c r="E119">
         <v>601</v>
       </c>
       <c r="F119" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="G119" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="I119">
         <v>42</v>
@@ -5069,16 +5069,16 @@
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A120">
-        <v>127594087</v>
+        <v>127639536</v>
       </c>
       <c r="E120">
         <v>601</v>
       </c>
       <c r="F120" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="G120" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="I120">
         <v>42</v>
@@ -5107,16 +5107,16 @@
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A121">
-        <v>127595805</v>
+        <v>127640835</v>
       </c>
       <c r="E121">
         <v>601</v>
       </c>
       <c r="F121" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="G121" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="I121">
         <v>42</v>
@@ -5145,16 +5145,16 @@
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122">
-        <v>127595879</v>
+        <v>127641271</v>
       </c>
       <c r="E122">
         <v>601</v>
       </c>
       <c r="F122" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="G122" s="2">
-        <v>45419</v>
+        <v>45422</v>
       </c>
       <c r="I122">
         <v>42</v>
@@ -5181,1718 +5181,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A123">
-        <v>127596105</v>
-      </c>
-      <c r="E123">
-        <v>601</v>
-      </c>
-      <c r="F123" s="2">
-        <v>45419</v>
-      </c>
-      <c r="G123" s="2">
-        <v>45419</v>
-      </c>
-      <c r="I123">
-        <v>42</v>
-      </c>
-      <c r="J123">
-        <v>8004</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123">
-        <v>0</v>
-      </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
-      <c r="O123">
-        <v>0</v>
-      </c>
-      <c r="P123">
-        <v>0</v>
-      </c>
-      <c r="Q123">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A124">
-        <v>127596181</v>
-      </c>
-      <c r="E124">
-        <v>601</v>
-      </c>
-      <c r="F124" s="2">
-        <v>45419</v>
-      </c>
-      <c r="G124" s="2">
-        <v>45419</v>
-      </c>
-      <c r="I124">
-        <v>42</v>
-      </c>
-      <c r="J124">
-        <v>8004</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124">
-        <v>0</v>
-      </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
-      <c r="O124">
-        <v>0</v>
-      </c>
-      <c r="P124">
-        <v>0</v>
-      </c>
-      <c r="Q124">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A125">
-        <v>127596567</v>
-      </c>
-      <c r="E125">
-        <v>601</v>
-      </c>
-      <c r="F125" s="2">
-        <v>45419</v>
-      </c>
-      <c r="G125" s="2">
-        <v>45419</v>
-      </c>
-      <c r="I125">
-        <v>42</v>
-      </c>
-      <c r="J125">
-        <v>8004</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125">
-        <v>0</v>
-      </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
-      <c r="O125">
-        <v>0</v>
-      </c>
-      <c r="P125">
-        <v>0</v>
-      </c>
-      <c r="Q125">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A126">
-        <v>127599677</v>
-      </c>
-      <c r="E126">
-        <v>601</v>
-      </c>
-      <c r="F126" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G126" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I126">
-        <v>42</v>
-      </c>
-      <c r="J126">
-        <v>8004</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126">
-        <v>0</v>
-      </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
-      <c r="O126">
-        <v>0</v>
-      </c>
-      <c r="P126">
-        <v>0</v>
-      </c>
-      <c r="Q126">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A127">
-        <v>127599688</v>
-      </c>
-      <c r="E127">
-        <v>601</v>
-      </c>
-      <c r="F127" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G127" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I127">
-        <v>42</v>
-      </c>
-      <c r="J127">
-        <v>8004</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127">
-        <v>0</v>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A128">
-        <v>127599736</v>
-      </c>
-      <c r="E128">
-        <v>601</v>
-      </c>
-      <c r="F128" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G128" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I128">
-        <v>42</v>
-      </c>
-      <c r="J128">
-        <v>8004</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128">
-        <v>0</v>
-      </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
-      <c r="O128">
-        <v>0</v>
-      </c>
-      <c r="P128">
-        <v>0</v>
-      </c>
-      <c r="Q128">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A129">
-        <v>127600440</v>
-      </c>
-      <c r="E129">
-        <v>601</v>
-      </c>
-      <c r="F129" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G129" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I129">
-        <v>42</v>
-      </c>
-      <c r="J129">
-        <v>8004</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129">
-        <v>0</v>
-      </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>0</v>
-      </c>
-      <c r="P129">
-        <v>0</v>
-      </c>
-      <c r="Q129">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A130">
-        <v>127601326</v>
-      </c>
-      <c r="E130">
-        <v>601</v>
-      </c>
-      <c r="F130" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G130" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I130">
-        <v>42</v>
-      </c>
-      <c r="J130">
-        <v>8004</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130">
-        <v>0</v>
-      </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
-        <v>0</v>
-      </c>
-      <c r="P130">
-        <v>0</v>
-      </c>
-      <c r="Q130">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A131">
-        <v>127603188</v>
-      </c>
-      <c r="E131">
-        <v>601</v>
-      </c>
-      <c r="F131" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G131" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I131">
-        <v>42</v>
-      </c>
-      <c r="J131">
-        <v>8004</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131">
-        <v>0</v>
-      </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>0</v>
-      </c>
-      <c r="P131">
-        <v>0</v>
-      </c>
-      <c r="Q131">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A132">
-        <v>127607057</v>
-      </c>
-      <c r="E132">
-        <v>601</v>
-      </c>
-      <c r="F132" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G132" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I132">
-        <v>42</v>
-      </c>
-      <c r="J132">
-        <v>8004</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132">
-        <v>0</v>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
-        <v>0</v>
-      </c>
-      <c r="Q132">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A133">
-        <v>127607600</v>
-      </c>
-      <c r="E133">
-        <v>601</v>
-      </c>
-      <c r="F133" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G133" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I133">
-        <v>42</v>
-      </c>
-      <c r="J133">
-        <v>8004</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133">
-        <v>0</v>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>0</v>
-      </c>
-      <c r="P133">
-        <v>0</v>
-      </c>
-      <c r="Q133">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A134">
-        <v>127608657</v>
-      </c>
-      <c r="E134">
-        <v>601</v>
-      </c>
-      <c r="F134" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G134" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I134">
-        <v>42</v>
-      </c>
-      <c r="J134">
-        <v>8004</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134">
-        <v>0</v>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
-        <v>0</v>
-      </c>
-      <c r="Q134">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A135">
-        <v>127609113</v>
-      </c>
-      <c r="E135">
-        <v>601</v>
-      </c>
-      <c r="F135" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G135" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I135">
-        <v>42</v>
-      </c>
-      <c r="J135">
-        <v>8004</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135">
-        <v>0</v>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
-        <v>0</v>
-      </c>
-      <c r="Q135">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A136">
-        <v>127611000</v>
-      </c>
-      <c r="E136">
-        <v>601</v>
-      </c>
-      <c r="F136" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G136" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I136">
-        <v>42</v>
-      </c>
-      <c r="J136">
-        <v>8004</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136">
-        <v>0</v>
-      </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
-        <v>0</v>
-      </c>
-      <c r="P136">
-        <v>0</v>
-      </c>
-      <c r="Q136">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A137">
-        <v>127613425</v>
-      </c>
-      <c r="E137">
-        <v>601</v>
-      </c>
-      <c r="F137" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G137" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I137">
-        <v>42</v>
-      </c>
-      <c r="J137">
-        <v>8004</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137">
-        <v>0</v>
-      </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
-      <c r="O137">
-        <v>0</v>
-      </c>
-      <c r="P137">
-        <v>0</v>
-      </c>
-      <c r="Q137">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A138">
-        <v>127614787</v>
-      </c>
-      <c r="E138">
-        <v>601</v>
-      </c>
-      <c r="F138" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G138" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I138">
-        <v>42</v>
-      </c>
-      <c r="J138">
-        <v>8004</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138">
-        <v>0</v>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A139">
-        <v>127614848</v>
-      </c>
-      <c r="E139">
-        <v>601</v>
-      </c>
-      <c r="F139" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G139" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I139">
-        <v>42</v>
-      </c>
-      <c r="J139">
-        <v>8004</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139">
-        <v>0</v>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A140">
-        <v>127615043</v>
-      </c>
-      <c r="E140">
-        <v>601</v>
-      </c>
-      <c r="F140" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G140" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I140">
-        <v>42</v>
-      </c>
-      <c r="J140">
-        <v>8004</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140">
-        <v>0</v>
-      </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
-      <c r="O140">
-        <v>0</v>
-      </c>
-      <c r="P140">
-        <v>0</v>
-      </c>
-      <c r="Q140">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A141">
-        <v>127615223</v>
-      </c>
-      <c r="E141">
-        <v>601</v>
-      </c>
-      <c r="F141" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G141" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I141">
-        <v>42</v>
-      </c>
-      <c r="J141">
-        <v>1118</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141">
-        <v>0</v>
-      </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
-      <c r="O141">
-        <v>0</v>
-      </c>
-      <c r="P141">
-        <v>0</v>
-      </c>
-      <c r="Q141">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A142">
-        <v>127615674</v>
-      </c>
-      <c r="E142">
-        <v>601</v>
-      </c>
-      <c r="F142" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G142" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I142">
-        <v>42</v>
-      </c>
-      <c r="J142">
-        <v>8004</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="M142">
-        <v>0</v>
-      </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
-      <c r="O142">
-        <v>0</v>
-      </c>
-      <c r="P142">
-        <v>0</v>
-      </c>
-      <c r="Q142">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A143">
-        <v>127617067</v>
-      </c>
-      <c r="E143">
-        <v>601</v>
-      </c>
-      <c r="F143" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G143" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I143">
-        <v>42</v>
-      </c>
-      <c r="J143">
-        <v>8004</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="M143">
-        <v>0</v>
-      </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
-      <c r="O143">
-        <v>0</v>
-      </c>
-      <c r="P143">
-        <v>0</v>
-      </c>
-      <c r="Q143">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A144">
-        <v>127617452</v>
-      </c>
-      <c r="E144">
-        <v>601</v>
-      </c>
-      <c r="F144" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G144" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I144">
-        <v>42</v>
-      </c>
-      <c r="J144">
-        <v>8004</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="M144">
-        <v>0</v>
-      </c>
-      <c r="N144">
-        <v>0</v>
-      </c>
-      <c r="O144">
-        <v>0</v>
-      </c>
-      <c r="P144">
-        <v>0</v>
-      </c>
-      <c r="Q144">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A145">
-        <v>127617660</v>
-      </c>
-      <c r="E145">
-        <v>601</v>
-      </c>
-      <c r="F145" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G145" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I145">
-        <v>42</v>
-      </c>
-      <c r="J145">
-        <v>8004</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="M145">
-        <v>0</v>
-      </c>
-      <c r="N145">
-        <v>0</v>
-      </c>
-      <c r="O145">
-        <v>0</v>
-      </c>
-      <c r="P145">
-        <v>0</v>
-      </c>
-      <c r="Q145">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A146">
-        <v>127617713</v>
-      </c>
-      <c r="E146">
-        <v>601</v>
-      </c>
-      <c r="F146" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G146" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I146">
-        <v>42</v>
-      </c>
-      <c r="J146">
-        <v>8004</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146">
-        <v>0</v>
-      </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
-      <c r="O146">
-        <v>0</v>
-      </c>
-      <c r="P146">
-        <v>0</v>
-      </c>
-      <c r="Q146">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A147">
-        <v>127617908</v>
-      </c>
-      <c r="E147">
-        <v>601</v>
-      </c>
-      <c r="F147" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G147" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I147">
-        <v>42</v>
-      </c>
-      <c r="J147">
-        <v>8004</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147">
-        <v>0</v>
-      </c>
-      <c r="N147">
-        <v>0</v>
-      </c>
-      <c r="O147">
-        <v>0</v>
-      </c>
-      <c r="P147">
-        <v>0</v>
-      </c>
-      <c r="Q147">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A148">
-        <v>127618188</v>
-      </c>
-      <c r="E148">
-        <v>601</v>
-      </c>
-      <c r="F148" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G148" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I148">
-        <v>42</v>
-      </c>
-      <c r="J148">
-        <v>8004</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148">
-        <v>0</v>
-      </c>
-      <c r="N148">
-        <v>0</v>
-      </c>
-      <c r="O148">
-        <v>0</v>
-      </c>
-      <c r="P148">
-        <v>0</v>
-      </c>
-      <c r="Q148">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A149">
-        <v>127618341</v>
-      </c>
-      <c r="E149">
-        <v>601</v>
-      </c>
-      <c r="F149" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G149" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I149">
-        <v>42</v>
-      </c>
-      <c r="J149">
-        <v>8004</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="M149">
-        <v>0</v>
-      </c>
-      <c r="N149">
-        <v>0</v>
-      </c>
-      <c r="O149">
-        <v>0</v>
-      </c>
-      <c r="P149">
-        <v>0</v>
-      </c>
-      <c r="Q149">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A150">
-        <v>127620400</v>
-      </c>
-      <c r="E150">
-        <v>601</v>
-      </c>
-      <c r="F150" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G150" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I150">
-        <v>42</v>
-      </c>
-      <c r="J150">
-        <v>8004</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="M150">
-        <v>0</v>
-      </c>
-      <c r="N150">
-        <v>0</v>
-      </c>
-      <c r="O150">
-        <v>0</v>
-      </c>
-      <c r="P150">
-        <v>0</v>
-      </c>
-      <c r="Q150">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A151">
-        <v>127620868</v>
-      </c>
-      <c r="E151">
-        <v>601</v>
-      </c>
-      <c r="F151" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G151" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I151">
-        <v>42</v>
-      </c>
-      <c r="J151">
-        <v>8004</v>
-      </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-      <c r="M151">
-        <v>0</v>
-      </c>
-      <c r="N151">
-        <v>0</v>
-      </c>
-      <c r="O151">
-        <v>0</v>
-      </c>
-      <c r="P151">
-        <v>0</v>
-      </c>
-      <c r="Q151">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A152">
-        <v>127621058</v>
-      </c>
-      <c r="E152">
-        <v>601</v>
-      </c>
-      <c r="F152" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G152" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I152">
-        <v>42</v>
-      </c>
-      <c r="J152">
-        <v>8004</v>
-      </c>
-      <c r="L152">
-        <v>0</v>
-      </c>
-      <c r="M152">
-        <v>0</v>
-      </c>
-      <c r="N152">
-        <v>0</v>
-      </c>
-      <c r="O152">
-        <v>0</v>
-      </c>
-      <c r="P152">
-        <v>0</v>
-      </c>
-      <c r="Q152">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A153">
-        <v>127621380</v>
-      </c>
-      <c r="E153">
-        <v>601</v>
-      </c>
-      <c r="F153" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G153" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I153">
-        <v>42</v>
-      </c>
-      <c r="J153">
-        <v>8004</v>
-      </c>
-      <c r="L153">
-        <v>0</v>
-      </c>
-      <c r="M153">
-        <v>0</v>
-      </c>
-      <c r="N153">
-        <v>0</v>
-      </c>
-      <c r="O153">
-        <v>0</v>
-      </c>
-      <c r="P153">
-        <v>0</v>
-      </c>
-      <c r="Q153">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A154">
-        <v>127623027</v>
-      </c>
-      <c r="E154">
-        <v>601</v>
-      </c>
-      <c r="F154" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G154" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I154">
-        <v>42</v>
-      </c>
-      <c r="J154">
-        <v>8004</v>
-      </c>
-      <c r="L154">
-        <v>0</v>
-      </c>
-      <c r="M154">
-        <v>0</v>
-      </c>
-      <c r="N154">
-        <v>0</v>
-      </c>
-      <c r="O154">
-        <v>0</v>
-      </c>
-      <c r="P154">
-        <v>0</v>
-      </c>
-      <c r="Q154">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A155">
-        <v>127623363</v>
-      </c>
-      <c r="E155">
-        <v>601</v>
-      </c>
-      <c r="F155" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G155" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I155">
-        <v>42</v>
-      </c>
-      <c r="J155">
-        <v>8004</v>
-      </c>
-      <c r="L155">
-        <v>0</v>
-      </c>
-      <c r="M155">
-        <v>0</v>
-      </c>
-      <c r="N155">
-        <v>0</v>
-      </c>
-      <c r="O155">
-        <v>0</v>
-      </c>
-      <c r="P155">
-        <v>0</v>
-      </c>
-      <c r="Q155">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A156">
-        <v>127624138</v>
-      </c>
-      <c r="E156">
-        <v>601</v>
-      </c>
-      <c r="F156" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G156" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I156">
-        <v>42</v>
-      </c>
-      <c r="J156">
-        <v>8004</v>
-      </c>
-      <c r="L156">
-        <v>0</v>
-      </c>
-      <c r="M156">
-        <v>0</v>
-      </c>
-      <c r="N156">
-        <v>0</v>
-      </c>
-      <c r="O156">
-        <v>0</v>
-      </c>
-      <c r="P156">
-        <v>0</v>
-      </c>
-      <c r="Q156">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A157">
-        <v>127624307</v>
-      </c>
-      <c r="E157">
-        <v>601</v>
-      </c>
-      <c r="F157" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G157" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I157">
-        <v>42</v>
-      </c>
-      <c r="J157">
-        <v>8004</v>
-      </c>
-      <c r="L157">
-        <v>0</v>
-      </c>
-      <c r="M157">
-        <v>0</v>
-      </c>
-      <c r="N157">
-        <v>0</v>
-      </c>
-      <c r="O157">
-        <v>0</v>
-      </c>
-      <c r="P157">
-        <v>0</v>
-      </c>
-      <c r="Q157">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A158">
-        <v>127630088</v>
-      </c>
-      <c r="E158">
-        <v>601</v>
-      </c>
-      <c r="F158" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G158" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I158">
-        <v>42</v>
-      </c>
-      <c r="J158">
-        <v>8004</v>
-      </c>
-      <c r="L158">
-        <v>0</v>
-      </c>
-      <c r="M158">
-        <v>0</v>
-      </c>
-      <c r="N158">
-        <v>0</v>
-      </c>
-      <c r="O158">
-        <v>0</v>
-      </c>
-      <c r="P158">
-        <v>0</v>
-      </c>
-      <c r="Q158">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A159">
-        <v>127632152</v>
-      </c>
-      <c r="E159">
-        <v>601</v>
-      </c>
-      <c r="F159" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G159" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I159">
-        <v>42</v>
-      </c>
-      <c r="J159">
-        <v>8004</v>
-      </c>
-      <c r="L159">
-        <v>0</v>
-      </c>
-      <c r="M159">
-        <v>0</v>
-      </c>
-      <c r="N159">
-        <v>0</v>
-      </c>
-      <c r="O159">
-        <v>0</v>
-      </c>
-      <c r="P159">
-        <v>0</v>
-      </c>
-      <c r="Q159">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A160">
-        <v>127633361</v>
-      </c>
-      <c r="E160">
-        <v>601</v>
-      </c>
-      <c r="F160" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G160" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I160">
-        <v>42</v>
-      </c>
-      <c r="J160">
-        <v>8004</v>
-      </c>
-      <c r="L160">
-        <v>0</v>
-      </c>
-      <c r="M160">
-        <v>0</v>
-      </c>
-      <c r="N160">
-        <v>0</v>
-      </c>
-      <c r="O160">
-        <v>0</v>
-      </c>
-      <c r="P160">
-        <v>0</v>
-      </c>
-      <c r="Q160">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A161">
-        <v>127633633</v>
-      </c>
-      <c r="E161">
-        <v>601</v>
-      </c>
-      <c r="F161" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G161" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I161">
-        <v>42</v>
-      </c>
-      <c r="J161">
-        <v>8004</v>
-      </c>
-      <c r="L161">
-        <v>0</v>
-      </c>
-      <c r="M161">
-        <v>0</v>
-      </c>
-      <c r="N161">
-        <v>0</v>
-      </c>
-      <c r="O161">
-        <v>0</v>
-      </c>
-      <c r="P161">
-        <v>0</v>
-      </c>
-      <c r="Q161">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A162">
-        <v>127634043</v>
-      </c>
-      <c r="E162">
-        <v>601</v>
-      </c>
-      <c r="F162" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G162" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I162">
-        <v>42</v>
-      </c>
-      <c r="J162">
-        <v>8004</v>
-      </c>
-      <c r="L162">
-        <v>0</v>
-      </c>
-      <c r="M162">
-        <v>0</v>
-      </c>
-      <c r="N162">
-        <v>0</v>
-      </c>
-      <c r="O162">
-        <v>0</v>
-      </c>
-      <c r="P162">
-        <v>0</v>
-      </c>
-      <c r="Q162">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A163">
-        <v>127637095</v>
-      </c>
-      <c r="E163">
-        <v>601</v>
-      </c>
-      <c r="F163" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G163" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I163">
-        <v>42</v>
-      </c>
-      <c r="J163">
-        <v>8004</v>
-      </c>
-      <c r="L163">
-        <v>0</v>
-      </c>
-      <c r="M163">
-        <v>0</v>
-      </c>
-      <c r="N163">
-        <v>0</v>
-      </c>
-      <c r="O163">
-        <v>0</v>
-      </c>
-      <c r="P163">
-        <v>0</v>
-      </c>
-      <c r="Q163">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A164">
-        <v>127639129</v>
-      </c>
-      <c r="E164">
-        <v>601</v>
-      </c>
-      <c r="F164" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G164" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I164">
-        <v>42</v>
-      </c>
-      <c r="J164">
-        <v>8004</v>
-      </c>
-      <c r="L164">
-        <v>0</v>
-      </c>
-      <c r="M164">
-        <v>0</v>
-      </c>
-      <c r="N164">
-        <v>0</v>
-      </c>
-      <c r="O164">
-        <v>0</v>
-      </c>
-      <c r="P164">
-        <v>0</v>
-      </c>
-      <c r="Q164">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A165">
-        <v>127639536</v>
-      </c>
-      <c r="E165">
-        <v>601</v>
-      </c>
-      <c r="F165" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G165" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I165">
-        <v>42</v>
-      </c>
-      <c r="J165">
-        <v>8004</v>
-      </c>
-      <c r="L165">
-        <v>0</v>
-      </c>
-      <c r="M165">
-        <v>0</v>
-      </c>
-      <c r="N165">
-        <v>0</v>
-      </c>
-      <c r="O165">
-        <v>0</v>
-      </c>
-      <c r="P165">
-        <v>0</v>
-      </c>
-      <c r="Q165">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A166">
-        <v>127640835</v>
-      </c>
-      <c r="E166">
-        <v>601</v>
-      </c>
-      <c r="F166" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G166" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I166">
-        <v>42</v>
-      </c>
-      <c r="J166">
-        <v>8004</v>
-      </c>
-      <c r="L166">
-        <v>0</v>
-      </c>
-      <c r="M166">
-        <v>0</v>
-      </c>
-      <c r="N166">
-        <v>0</v>
-      </c>
-      <c r="O166">
-        <v>0</v>
-      </c>
-      <c r="P166">
-        <v>0</v>
-      </c>
-      <c r="Q166">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A167">
-        <v>127641271</v>
-      </c>
-      <c r="E167">
-        <v>601</v>
-      </c>
-      <c r="F167" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G167" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I167">
-        <v>42</v>
-      </c>
-      <c r="J167">
-        <v>8004</v>
-      </c>
-      <c r="L167">
-        <v>0</v>
-      </c>
-      <c r="M167">
-        <v>0</v>
-      </c>
-      <c r="N167">
-        <v>0</v>
-      </c>
-      <c r="O167">
-        <v>0</v>
-      </c>
-      <c r="P167">
-        <v>0</v>
-      </c>
-      <c r="Q167">
-        <v>61</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q167" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -14482,31 +12771,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9CFC66-BE6E-4D5A-B9EE-0A3763CEE9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27A2D9A-D9A0-4483-B2D3-038BE5927FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q122"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,22 +585,22 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>127707556</v>
+        <v>124071525</v>
       </c>
       <c r="E2">
         <v>1211</v>
       </c>
       <c r="F2" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="G2" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="I2">
         <v>42</v>
       </c>
       <c r="J2">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -623,22 +623,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>127709320</v>
+        <v>124190216</v>
       </c>
       <c r="E3">
         <v>1211</v>
       </c>
       <c r="F3" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="G3" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -661,22 +661,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>127710005</v>
+        <v>124404434</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="G4" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,22 +699,22 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>127713128</v>
+        <v>124507801</v>
       </c>
       <c r="E5">
         <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="G5" s="2">
-        <v>45429</v>
+        <v>45427</v>
       </c>
       <c r="I5">
         <v>42</v>
       </c>
       <c r="J5">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,22 +737,22 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>127713615</v>
+        <v>124903448</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="G6" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="I6">
         <v>42</v>
       </c>
       <c r="J6">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -775,22 +775,22 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>127714268</v>
+        <v>124984936</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="G7" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="I7">
         <v>42</v>
       </c>
       <c r="J7">
-        <v>1735</v>
+        <v>8001</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -813,16 +813,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>124085593</v>
+        <v>125225166</v>
       </c>
       <c r="E8">
         <v>1212</v>
       </c>
       <c r="F8" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="G8" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="I8">
         <v>42</v>
@@ -851,16 +851,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>124114081</v>
+        <v>125312442</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="G9" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -889,16 +889,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>124199837</v>
+        <v>125447920</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="G10" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -927,13 +927,13 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>124241728</v>
+        <v>125608616</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="G11" s="2">
         <v>45428</v>
@@ -965,16 +965,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>124382401</v>
+        <v>125795596</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="G12" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>124382473</v>
+        <v>125841757</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45430</v>
+        <v>45432</v>
       </c>
       <c r="G13" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>124509919</v>
+        <v>125916183</v>
       </c>
       <c r="E14">
         <v>1211</v>
       </c>
       <c r="F14" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="G14" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>124526674</v>
+        <v>126315474</v>
       </c>
       <c r="E15">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="G15" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>124556596</v>
+        <v>126784997</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45430</v>
+        <v>45432</v>
       </c>
       <c r="G16" s="2">
-        <v>45430</v>
+        <v>45432</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>124580685</v>
+        <v>127321922</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45430</v>
+        <v>45432</v>
       </c>
       <c r="G17" s="2">
-        <v>45430</v>
+        <v>45432</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>124736297</v>
+        <v>127485644</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="G18" s="2">
-        <v>45428</v>
+        <v>45432</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>124805931</v>
+        <v>127672277</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="G19" s="2">
-        <v>45429</v>
+        <v>45432</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,22 +1269,22 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>124829987</v>
+        <v>110074933</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>45429</v>
+        <v>43453</v>
       </c>
       <c r="G20" s="2">
-        <v>45429</v>
+        <v>43441</v>
       </c>
       <c r="I20">
         <v>42</v>
       </c>
       <c r="J20">
-        <v>8001</v>
+        <v>8023</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>124876290</v>
+        <v>127627998</v>
       </c>
       <c r="E21">
         <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45428</v>
+        <v>45429</v>
       </c>
       <c r="G21" s="2">
-        <v>45428</v>
+        <v>45422</v>
       </c>
       <c r="I21">
         <v>42</v>
@@ -1345,22 +1345,22 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>125052952</v>
+        <v>127646444</v>
       </c>
       <c r="E22">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F22" s="2">
-        <v>45429</v>
+        <v>45426</v>
       </c>
       <c r="G22" s="2">
-        <v>45429</v>
+        <v>45425</v>
       </c>
       <c r="I22">
         <v>42</v>
       </c>
       <c r="J22">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1383,7 +1383,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>125184702</v>
+        <v>127660003</v>
       </c>
       <c r="E23">
         <v>1211</v>
@@ -1392,7 +1392,7 @@
         <v>45429</v>
       </c>
       <c r="G23" s="2">
-        <v>45429</v>
+        <v>45426</v>
       </c>
       <c r="I23">
         <v>42</v>
@@ -1421,22 +1421,22 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>125195701</v>
+        <v>126954503</v>
       </c>
       <c r="E24">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F24" s="2">
-        <v>45429</v>
+        <v>45378</v>
       </c>
       <c r="G24" s="2">
-        <v>45426</v>
+        <v>45378</v>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8001</v>
+        <v>8017</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1457,3731 +1457,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>125304585</v>
-      </c>
-      <c r="E25">
-        <v>1211</v>
-      </c>
-      <c r="F25" s="2">
-        <v>45430</v>
-      </c>
-      <c r="G25" s="2">
-        <v>45430</v>
-      </c>
-      <c r="I25">
-        <v>42</v>
-      </c>
-      <c r="J25">
-        <v>8001</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>125384268</v>
-      </c>
-      <c r="E26">
-        <v>1212</v>
-      </c>
-      <c r="F26" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G26" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I26">
-        <v>42</v>
-      </c>
-      <c r="J26">
-        <v>8001</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>125422780</v>
-      </c>
-      <c r="E27">
-        <v>1211</v>
-      </c>
-      <c r="F27" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G27" s="2">
-        <v>45427</v>
-      </c>
-      <c r="I27">
-        <v>42</v>
-      </c>
-      <c r="J27">
-        <v>8001</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>125426528</v>
-      </c>
-      <c r="E28">
-        <v>1211</v>
-      </c>
-      <c r="F28" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G28" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I28">
-        <v>42</v>
-      </c>
-      <c r="J28">
-        <v>8001</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>125505055</v>
-      </c>
-      <c r="E29">
-        <v>1211</v>
-      </c>
-      <c r="F29" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G29" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I29">
-        <v>42</v>
-      </c>
-      <c r="J29">
-        <v>8001</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>125574465</v>
-      </c>
-      <c r="E30">
-        <v>1211</v>
-      </c>
-      <c r="F30" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G30" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I30">
-        <v>42</v>
-      </c>
-      <c r="J30">
-        <v>8001</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>125650786</v>
-      </c>
-      <c r="E31">
-        <v>1211</v>
-      </c>
-      <c r="F31" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G31" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I31">
-        <v>42</v>
-      </c>
-      <c r="J31">
-        <v>8001</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>125691862</v>
-      </c>
-      <c r="E32">
-        <v>1211</v>
-      </c>
-      <c r="F32" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G32" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I32">
-        <v>42</v>
-      </c>
-      <c r="J32">
-        <v>8001</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>125769830</v>
-      </c>
-      <c r="E33">
-        <v>1211</v>
-      </c>
-      <c r="F33" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G33" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I33">
-        <v>42</v>
-      </c>
-      <c r="J33">
-        <v>8001</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>125782283</v>
-      </c>
-      <c r="E34">
-        <v>1211</v>
-      </c>
-      <c r="F34" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G34" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I34">
-        <v>42</v>
-      </c>
-      <c r="J34">
-        <v>8001</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>125934594</v>
-      </c>
-      <c r="E35">
-        <v>1211</v>
-      </c>
-      <c r="F35" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G35" s="2">
-        <v>45426</v>
-      </c>
-      <c r="I35">
-        <v>42</v>
-      </c>
-      <c r="J35">
-        <v>8001</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>125982656</v>
-      </c>
-      <c r="E36">
-        <v>1211</v>
-      </c>
-      <c r="F36" s="2">
-        <v>45430</v>
-      </c>
-      <c r="G36" s="2">
-        <v>45430</v>
-      </c>
-      <c r="I36">
-        <v>42</v>
-      </c>
-      <c r="J36">
-        <v>8001</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>0</v>
-      </c>
-      <c r="Q36">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>126014517</v>
-      </c>
-      <c r="E37">
-        <v>1211</v>
-      </c>
-      <c r="F37" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G37" s="2">
-        <v>45426</v>
-      </c>
-      <c r="I37">
-        <v>42</v>
-      </c>
-      <c r="J37">
-        <v>8001</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
-        <v>0</v>
-      </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>0</v>
-      </c>
-      <c r="Q37">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>126033754</v>
-      </c>
-      <c r="E38">
-        <v>1211</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45430</v>
-      </c>
-      <c r="G38" s="2">
-        <v>45430</v>
-      </c>
-      <c r="I38">
-        <v>42</v>
-      </c>
-      <c r="J38">
-        <v>8001</v>
-      </c>
-      <c r="L38">
-        <v>0</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>0</v>
-      </c>
-      <c r="Q38">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>126075570</v>
-      </c>
-      <c r="E39">
-        <v>1211</v>
-      </c>
-      <c r="F39" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G39" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I39">
-        <v>42</v>
-      </c>
-      <c r="J39">
-        <v>8001</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>0</v>
-      </c>
-      <c r="Q39">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>126085447</v>
-      </c>
-      <c r="E40">
-        <v>1211</v>
-      </c>
-      <c r="F40" s="2">
-        <v>45430</v>
-      </c>
-      <c r="G40" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I40">
-        <v>42</v>
-      </c>
-      <c r="J40">
-        <v>8001</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
-      <c r="P40">
-        <v>0</v>
-      </c>
-      <c r="Q40">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>126091614</v>
-      </c>
-      <c r="E41">
-        <v>1211</v>
-      </c>
-      <c r="F41" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G41" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I41">
-        <v>42</v>
-      </c>
-      <c r="J41">
-        <v>8001</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-      <c r="P41">
-        <v>0</v>
-      </c>
-      <c r="Q41">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>126384960</v>
-      </c>
-      <c r="E42">
-        <v>1211</v>
-      </c>
-      <c r="F42" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G42" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I42">
-        <v>42</v>
-      </c>
-      <c r="J42">
-        <v>8001</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
-      <c r="P42">
-        <v>0</v>
-      </c>
-      <c r="Q42">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>126611925</v>
-      </c>
-      <c r="E43">
-        <v>1211</v>
-      </c>
-      <c r="F43" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G43" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I43">
-        <v>42</v>
-      </c>
-      <c r="J43">
-        <v>8001</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
-      <c r="P43">
-        <v>0</v>
-      </c>
-      <c r="Q43">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>126618728</v>
-      </c>
-      <c r="E44">
-        <v>1211</v>
-      </c>
-      <c r="F44" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G44" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I44">
-        <v>42</v>
-      </c>
-      <c r="J44">
-        <v>8001</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44">
-        <v>0</v>
-      </c>
-      <c r="Q44">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>126704127</v>
-      </c>
-      <c r="E45">
-        <v>1211</v>
-      </c>
-      <c r="F45" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G45" s="2">
-        <v>45427</v>
-      </c>
-      <c r="I45">
-        <v>42</v>
-      </c>
-      <c r="J45">
-        <v>8001</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
-      <c r="P45">
-        <v>0</v>
-      </c>
-      <c r="Q45">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>126753264</v>
-      </c>
-      <c r="E46">
-        <v>1211</v>
-      </c>
-      <c r="F46" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G46" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I46">
-        <v>42</v>
-      </c>
-      <c r="J46">
-        <v>8001</v>
-      </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
-        <v>0</v>
-      </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>0</v>
-      </c>
-      <c r="Q46">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>126838674</v>
-      </c>
-      <c r="E47">
-        <v>1211</v>
-      </c>
-      <c r="F47" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G47" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I47">
-        <v>42</v>
-      </c>
-      <c r="J47">
-        <v>8001</v>
-      </c>
-      <c r="L47">
-        <v>0</v>
-      </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>126867169</v>
-      </c>
-      <c r="E48">
-        <v>1211</v>
-      </c>
-      <c r="F48" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G48" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I48">
-        <v>42</v>
-      </c>
-      <c r="J48">
-        <v>8001</v>
-      </c>
-      <c r="L48">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A49">
-        <v>126930388</v>
-      </c>
-      <c r="E49">
-        <v>1211</v>
-      </c>
-      <c r="F49" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G49" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I49">
-        <v>42</v>
-      </c>
-      <c r="J49">
-        <v>8001</v>
-      </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
-      <c r="P49">
-        <v>0</v>
-      </c>
-      <c r="Q49">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>126963758</v>
-      </c>
-      <c r="E50">
-        <v>1211</v>
-      </c>
-      <c r="F50" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G50" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I50">
-        <v>42</v>
-      </c>
-      <c r="J50">
-        <v>8001</v>
-      </c>
-      <c r="L50">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50">
-        <v>0</v>
-      </c>
-      <c r="P50">
-        <v>0</v>
-      </c>
-      <c r="Q50">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>126971134</v>
-      </c>
-      <c r="E51">
-        <v>1211</v>
-      </c>
-      <c r="F51" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G51" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I51">
-        <v>42</v>
-      </c>
-      <c r="J51">
-        <v>8001</v>
-      </c>
-      <c r="L51">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51">
-        <v>0</v>
-      </c>
-      <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A52">
-        <v>126976721</v>
-      </c>
-      <c r="E52">
-        <v>1212</v>
-      </c>
-      <c r="F52" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G52" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I52">
-        <v>42</v>
-      </c>
-      <c r="J52">
-        <v>8001</v>
-      </c>
-      <c r="L52">
-        <v>0</v>
-      </c>
-      <c r="M52">
-        <v>0</v>
-      </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
-      <c r="O52">
-        <v>0</v>
-      </c>
-      <c r="P52">
-        <v>0</v>
-      </c>
-      <c r="Q52">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A53">
-        <v>127013708</v>
-      </c>
-      <c r="E53">
-        <v>1211</v>
-      </c>
-      <c r="F53" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G53" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I53">
-        <v>42</v>
-      </c>
-      <c r="J53">
-        <v>8001</v>
-      </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
-        <v>0</v>
-      </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
-      <c r="O53">
-        <v>0</v>
-      </c>
-      <c r="P53">
-        <v>0</v>
-      </c>
-      <c r="Q53">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>127013931</v>
-      </c>
-      <c r="E54">
-        <v>1211</v>
-      </c>
-      <c r="F54" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G54" s="2">
-        <v>45426</v>
-      </c>
-      <c r="I54">
-        <v>42</v>
-      </c>
-      <c r="J54">
-        <v>8001</v>
-      </c>
-      <c r="L54">
-        <v>0</v>
-      </c>
-      <c r="M54">
-        <v>0</v>
-      </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
-      <c r="O54">
-        <v>0</v>
-      </c>
-      <c r="P54">
-        <v>0</v>
-      </c>
-      <c r="Q54">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>127054069</v>
-      </c>
-      <c r="E55">
-        <v>1211</v>
-      </c>
-      <c r="F55" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G55" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I55">
-        <v>42</v>
-      </c>
-      <c r="J55">
-        <v>8001</v>
-      </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
-        <v>0</v>
-      </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
-      <c r="O55">
-        <v>0</v>
-      </c>
-      <c r="P55">
-        <v>0</v>
-      </c>
-      <c r="Q55">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A56">
-        <v>127080906</v>
-      </c>
-      <c r="E56">
-        <v>1211</v>
-      </c>
-      <c r="F56" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G56" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I56">
-        <v>42</v>
-      </c>
-      <c r="J56">
-        <v>8001</v>
-      </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56">
-        <v>0</v>
-      </c>
-      <c r="P56">
-        <v>0</v>
-      </c>
-      <c r="Q56">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A57">
-        <v>127103245</v>
-      </c>
-      <c r="E57">
-        <v>1211</v>
-      </c>
-      <c r="F57" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G57" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I57">
-        <v>42</v>
-      </c>
-      <c r="J57">
-        <v>8001</v>
-      </c>
-      <c r="L57">
-        <v>0</v>
-      </c>
-      <c r="M57">
-        <v>0</v>
-      </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
-      <c r="O57">
-        <v>0</v>
-      </c>
-      <c r="P57">
-        <v>0</v>
-      </c>
-      <c r="Q57">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A58">
-        <v>127261315</v>
-      </c>
-      <c r="E58">
-        <v>1211</v>
-      </c>
-      <c r="F58" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G58" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I58">
-        <v>42</v>
-      </c>
-      <c r="J58">
-        <v>8001</v>
-      </c>
-      <c r="L58">
-        <v>0</v>
-      </c>
-      <c r="M58">
-        <v>0</v>
-      </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
-      <c r="O58">
-        <v>0</v>
-      </c>
-      <c r="P58">
-        <v>0</v>
-      </c>
-      <c r="Q58">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A59">
-        <v>127326475</v>
-      </c>
-      <c r="E59">
-        <v>1211</v>
-      </c>
-      <c r="F59" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G59" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I59">
-        <v>42</v>
-      </c>
-      <c r="J59">
-        <v>8001</v>
-      </c>
-      <c r="L59">
-        <v>0</v>
-      </c>
-      <c r="M59">
-        <v>0</v>
-      </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="O59">
-        <v>0</v>
-      </c>
-      <c r="P59">
-        <v>0</v>
-      </c>
-      <c r="Q59">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A60">
-        <v>127333904</v>
-      </c>
-      <c r="E60">
-        <v>1211</v>
-      </c>
-      <c r="F60" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G60" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I60">
-        <v>42</v>
-      </c>
-      <c r="J60">
-        <v>8001</v>
-      </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>0</v>
-      </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
-      <c r="O60">
-        <v>0</v>
-      </c>
-      <c r="P60">
-        <v>0</v>
-      </c>
-      <c r="Q60">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A61">
-        <v>127339851</v>
-      </c>
-      <c r="E61">
-        <v>1211</v>
-      </c>
-      <c r="F61" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G61" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I61">
-        <v>42</v>
-      </c>
-      <c r="J61">
-        <v>8001</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
-      </c>
-      <c r="M61">
-        <v>0</v>
-      </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>0</v>
-      </c>
-      <c r="P61">
-        <v>0</v>
-      </c>
-      <c r="Q61">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>127368628</v>
-      </c>
-      <c r="E62">
-        <v>1211</v>
-      </c>
-      <c r="F62" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G62" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I62">
-        <v>42</v>
-      </c>
-      <c r="J62">
-        <v>8001</v>
-      </c>
-      <c r="L62">
-        <v>0</v>
-      </c>
-      <c r="M62">
-        <v>0</v>
-      </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A63">
-        <v>127412856</v>
-      </c>
-      <c r="E63">
-        <v>1211</v>
-      </c>
-      <c r="F63" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G63" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I63">
-        <v>42</v>
-      </c>
-      <c r="J63">
-        <v>8001</v>
-      </c>
-      <c r="L63">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <v>0</v>
-      </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A64">
-        <v>127443739</v>
-      </c>
-      <c r="E64">
-        <v>1212</v>
-      </c>
-      <c r="F64" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G64" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I64">
-        <v>42</v>
-      </c>
-      <c r="J64">
-        <v>8001</v>
-      </c>
-      <c r="L64">
-        <v>0</v>
-      </c>
-      <c r="M64">
-        <v>0</v>
-      </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A65">
-        <v>127547571</v>
-      </c>
-      <c r="E65">
-        <v>1211</v>
-      </c>
-      <c r="F65" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G65" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I65">
-        <v>42</v>
-      </c>
-      <c r="J65">
-        <v>8001</v>
-      </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A66">
-        <v>127563914</v>
-      </c>
-      <c r="E66">
-        <v>1211</v>
-      </c>
-      <c r="F66" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G66" s="2">
-        <v>45427</v>
-      </c>
-      <c r="I66">
-        <v>42</v>
-      </c>
-      <c r="J66">
-        <v>8001</v>
-      </c>
-      <c r="L66">
-        <v>0</v>
-      </c>
-      <c r="M66">
-        <v>0</v>
-      </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
-      <c r="O66">
-        <v>0</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A67">
-        <v>127606707</v>
-      </c>
-      <c r="E67">
-        <v>1211</v>
-      </c>
-      <c r="F67" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G67" s="2">
-        <v>45429</v>
-      </c>
-      <c r="I67">
-        <v>42</v>
-      </c>
-      <c r="J67">
-        <v>8001</v>
-      </c>
-      <c r="L67">
-        <v>0</v>
-      </c>
-      <c r="M67">
-        <v>0</v>
-      </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A68">
-        <v>127621540</v>
-      </c>
-      <c r="E68">
-        <v>1211</v>
-      </c>
-      <c r="F68" s="2">
-        <v>45429</v>
-      </c>
-      <c r="G68" s="2">
-        <v>45425</v>
-      </c>
-      <c r="I68">
-        <v>42</v>
-      </c>
-      <c r="J68">
-        <v>8001</v>
-      </c>
-      <c r="L68">
-        <v>0</v>
-      </c>
-      <c r="M68">
-        <v>0</v>
-      </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>0</v>
-      </c>
-      <c r="P68">
-        <v>0</v>
-      </c>
-      <c r="Q68">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A69">
-        <v>127681123</v>
-      </c>
-      <c r="E69">
-        <v>1211</v>
-      </c>
-      <c r="F69" s="2">
-        <v>45428</v>
-      </c>
-      <c r="G69" s="2">
-        <v>45428</v>
-      </c>
-      <c r="I69">
-        <v>42</v>
-      </c>
-      <c r="J69">
-        <v>8001</v>
-      </c>
-      <c r="L69">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>0</v>
-      </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
-      <c r="O69">
-        <v>0</v>
-      </c>
-      <c r="P69">
-        <v>0</v>
-      </c>
-      <c r="Q69">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>110074933</v>
-      </c>
-      <c r="E70">
-        <v>1211</v>
-      </c>
-      <c r="F70" s="2">
-        <v>43453</v>
-      </c>
-      <c r="G70" s="2">
-        <v>43441</v>
-      </c>
-      <c r="I70">
-        <v>42</v>
-      </c>
-      <c r="J70">
-        <v>8023</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70">
-        <v>0</v>
-      </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A71">
-        <v>127599474</v>
-      </c>
-      <c r="E71">
-        <v>1212</v>
-      </c>
-      <c r="F71" s="2">
-        <v>45427</v>
-      </c>
-      <c r="G71" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I71">
-        <v>42</v>
-      </c>
-      <c r="J71">
-        <v>8001</v>
-      </c>
-      <c r="L71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
-      <c r="P71">
-        <v>0</v>
-      </c>
-      <c r="Q71">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A72">
-        <v>127646444</v>
-      </c>
-      <c r="E72">
-        <v>1212</v>
-      </c>
-      <c r="F72" s="2">
-        <v>45426</v>
-      </c>
-      <c r="G72" s="2">
-        <v>45425</v>
-      </c>
-      <c r="I72">
-        <v>42</v>
-      </c>
-      <c r="J72">
-        <v>8021</v>
-      </c>
-      <c r="L72">
-        <v>0</v>
-      </c>
-      <c r="M72">
-        <v>0</v>
-      </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <v>0</v>
-      </c>
-      <c r="P72">
-        <v>0</v>
-      </c>
-      <c r="Q72">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A73">
-        <v>126954503</v>
-      </c>
-      <c r="E73">
-        <v>601</v>
-      </c>
-      <c r="F73" s="2">
-        <v>45378</v>
-      </c>
-      <c r="G73" s="2">
-        <v>45378</v>
-      </c>
-      <c r="I73">
-        <v>42</v>
-      </c>
-      <c r="J73">
-        <v>8017</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <v>0</v>
-      </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73">
-        <v>0</v>
-      </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A74">
-        <v>127606044</v>
-      </c>
-      <c r="E74">
-        <v>601</v>
-      </c>
-      <c r="F74" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G74" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I74">
-        <v>42</v>
-      </c>
-      <c r="J74">
-        <v>8004</v>
-      </c>
-      <c r="L74">
-        <v>0</v>
-      </c>
-      <c r="M74">
-        <v>0</v>
-      </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <v>0</v>
-      </c>
-      <c r="P74">
-        <v>0</v>
-      </c>
-      <c r="Q74">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A75">
-        <v>127607597</v>
-      </c>
-      <c r="E75">
-        <v>601</v>
-      </c>
-      <c r="F75" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G75" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I75">
-        <v>42</v>
-      </c>
-      <c r="J75">
-        <v>8004</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
-      </c>
-      <c r="P75">
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A76">
-        <v>127608440</v>
-      </c>
-      <c r="E76">
-        <v>601</v>
-      </c>
-      <c r="F76" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G76" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I76">
-        <v>42</v>
-      </c>
-      <c r="J76">
-        <v>8004</v>
-      </c>
-      <c r="L76">
-        <v>0</v>
-      </c>
-      <c r="M76">
-        <v>0</v>
-      </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
-      <c r="O76">
-        <v>0</v>
-      </c>
-      <c r="P76">
-        <v>0</v>
-      </c>
-      <c r="Q76">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A77">
-        <v>127611442</v>
-      </c>
-      <c r="E77">
-        <v>601</v>
-      </c>
-      <c r="F77" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G77" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I77">
-        <v>42</v>
-      </c>
-      <c r="J77">
-        <v>8004</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <v>0</v>
-      </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
-      <c r="O77">
-        <v>0</v>
-      </c>
-      <c r="P77">
-        <v>0</v>
-      </c>
-      <c r="Q77">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A78">
-        <v>127634669</v>
-      </c>
-      <c r="E78">
-        <v>601</v>
-      </c>
-      <c r="F78" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G78" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I78">
-        <v>42</v>
-      </c>
-      <c r="J78">
-        <v>8013</v>
-      </c>
-      <c r="L78">
-        <v>0</v>
-      </c>
-      <c r="M78">
-        <v>0</v>
-      </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
-      <c r="O78">
-        <v>0</v>
-      </c>
-      <c r="P78">
-        <v>0</v>
-      </c>
-      <c r="Q78">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A79">
-        <v>127639948</v>
-      </c>
-      <c r="E79">
-        <v>601</v>
-      </c>
-      <c r="F79" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G79" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I79">
-        <v>42</v>
-      </c>
-      <c r="J79">
-        <v>8004</v>
-      </c>
-      <c r="L79">
-        <v>0</v>
-      </c>
-      <c r="M79">
-        <v>0</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="O79">
-        <v>0</v>
-      </c>
-      <c r="P79">
-        <v>0</v>
-      </c>
-      <c r="Q79">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A80">
-        <v>127587095</v>
-      </c>
-      <c r="E80">
-        <v>601</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G80" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I80">
-        <v>42</v>
-      </c>
-      <c r="J80">
-        <v>8004</v>
-      </c>
-      <c r="L80">
-        <v>0</v>
-      </c>
-      <c r="M80">
-        <v>0</v>
-      </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>0</v>
-      </c>
-      <c r="P80">
-        <v>0</v>
-      </c>
-      <c r="Q80">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A81">
-        <v>127599677</v>
-      </c>
-      <c r="E81">
-        <v>601</v>
-      </c>
-      <c r="F81" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G81" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I81">
-        <v>42</v>
-      </c>
-      <c r="J81">
-        <v>8004</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
-        <v>0</v>
-      </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
-      <c r="O81">
-        <v>0</v>
-      </c>
-      <c r="P81">
-        <v>0</v>
-      </c>
-      <c r="Q81">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A82">
-        <v>127599688</v>
-      </c>
-      <c r="E82">
-        <v>601</v>
-      </c>
-      <c r="F82" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G82" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I82">
-        <v>42</v>
-      </c>
-      <c r="J82">
-        <v>8004</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>0</v>
-      </c>
-      <c r="P82">
-        <v>0</v>
-      </c>
-      <c r="Q82">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A83">
-        <v>127599736</v>
-      </c>
-      <c r="E83">
-        <v>601</v>
-      </c>
-      <c r="F83" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G83" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I83">
-        <v>42</v>
-      </c>
-      <c r="J83">
-        <v>8004</v>
-      </c>
-      <c r="L83">
-        <v>0</v>
-      </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
-      <c r="O83">
-        <v>0</v>
-      </c>
-      <c r="P83">
-        <v>0</v>
-      </c>
-      <c r="Q83">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A84">
-        <v>127600440</v>
-      </c>
-      <c r="E84">
-        <v>601</v>
-      </c>
-      <c r="F84" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G84" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I84">
-        <v>42</v>
-      </c>
-      <c r="J84">
-        <v>8004</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84">
-        <v>0</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A85">
-        <v>127601326</v>
-      </c>
-      <c r="E85">
-        <v>601</v>
-      </c>
-      <c r="F85" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G85" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I85">
-        <v>42</v>
-      </c>
-      <c r="J85">
-        <v>8004</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85">
-        <v>0</v>
-      </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>0</v>
-      </c>
-      <c r="P85">
-        <v>0</v>
-      </c>
-      <c r="Q85">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A86">
-        <v>127603188</v>
-      </c>
-      <c r="E86">
-        <v>601</v>
-      </c>
-      <c r="F86" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G86" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I86">
-        <v>42</v>
-      </c>
-      <c r="J86">
-        <v>8004</v>
-      </c>
-      <c r="L86">
-        <v>0</v>
-      </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
-      <c r="O86">
-        <v>0</v>
-      </c>
-      <c r="P86">
-        <v>0</v>
-      </c>
-      <c r="Q86">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A87">
-        <v>127607057</v>
-      </c>
-      <c r="E87">
-        <v>601</v>
-      </c>
-      <c r="F87" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G87" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I87">
-        <v>42</v>
-      </c>
-      <c r="J87">
-        <v>8004</v>
-      </c>
-      <c r="L87">
-        <v>0</v>
-      </c>
-      <c r="M87">
-        <v>0</v>
-      </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
-      <c r="O87">
-        <v>0</v>
-      </c>
-      <c r="P87">
-        <v>0</v>
-      </c>
-      <c r="Q87">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A88">
-        <v>127607600</v>
-      </c>
-      <c r="E88">
-        <v>601</v>
-      </c>
-      <c r="F88" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G88" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I88">
-        <v>42</v>
-      </c>
-      <c r="J88">
-        <v>8004</v>
-      </c>
-      <c r="L88">
-        <v>0</v>
-      </c>
-      <c r="M88">
-        <v>0</v>
-      </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
-      <c r="O88">
-        <v>0</v>
-      </c>
-      <c r="P88">
-        <v>0</v>
-      </c>
-      <c r="Q88">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A89">
-        <v>127608657</v>
-      </c>
-      <c r="E89">
-        <v>601</v>
-      </c>
-      <c r="F89" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G89" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I89">
-        <v>42</v>
-      </c>
-      <c r="J89">
-        <v>8004</v>
-      </c>
-      <c r="L89">
-        <v>0</v>
-      </c>
-      <c r="M89">
-        <v>0</v>
-      </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <v>0</v>
-      </c>
-      <c r="P89">
-        <v>0</v>
-      </c>
-      <c r="Q89">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A90">
-        <v>127609113</v>
-      </c>
-      <c r="E90">
-        <v>601</v>
-      </c>
-      <c r="F90" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G90" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I90">
-        <v>42</v>
-      </c>
-      <c r="J90">
-        <v>8004</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A91">
-        <v>127611000</v>
-      </c>
-      <c r="E91">
-        <v>601</v>
-      </c>
-      <c r="F91" s="2">
-        <v>45420</v>
-      </c>
-      <c r="G91" s="2">
-        <v>45420</v>
-      </c>
-      <c r="I91">
-        <v>42</v>
-      </c>
-      <c r="J91">
-        <v>8004</v>
-      </c>
-      <c r="L91">
-        <v>0</v>
-      </c>
-      <c r="M91">
-        <v>0</v>
-      </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
-      <c r="O91">
-        <v>0</v>
-      </c>
-      <c r="P91">
-        <v>0</v>
-      </c>
-      <c r="Q91">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A92">
-        <v>127613425</v>
-      </c>
-      <c r="E92">
-        <v>601</v>
-      </c>
-      <c r="F92" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G92" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I92">
-        <v>42</v>
-      </c>
-      <c r="J92">
-        <v>8004</v>
-      </c>
-      <c r="L92">
-        <v>0</v>
-      </c>
-      <c r="M92">
-        <v>0</v>
-      </c>
-      <c r="N92">
-        <v>0</v>
-      </c>
-      <c r="O92">
-        <v>0</v>
-      </c>
-      <c r="P92">
-        <v>0</v>
-      </c>
-      <c r="Q92">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A93">
-        <v>127614787</v>
-      </c>
-      <c r="E93">
-        <v>601</v>
-      </c>
-      <c r="F93" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G93" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I93">
-        <v>42</v>
-      </c>
-      <c r="J93">
-        <v>8004</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
-        <v>0</v>
-      </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
-      <c r="O93">
-        <v>0</v>
-      </c>
-      <c r="P93">
-        <v>0</v>
-      </c>
-      <c r="Q93">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A94">
-        <v>127614848</v>
-      </c>
-      <c r="E94">
-        <v>601</v>
-      </c>
-      <c r="F94" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G94" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I94">
-        <v>42</v>
-      </c>
-      <c r="J94">
-        <v>8004</v>
-      </c>
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="M94">
-        <v>0</v>
-      </c>
-      <c r="N94">
-        <v>0</v>
-      </c>
-      <c r="O94">
-        <v>0</v>
-      </c>
-      <c r="P94">
-        <v>0</v>
-      </c>
-      <c r="Q94">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A95">
-        <v>127615043</v>
-      </c>
-      <c r="E95">
-        <v>601</v>
-      </c>
-      <c r="F95" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G95" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I95">
-        <v>42</v>
-      </c>
-      <c r="J95">
-        <v>8004</v>
-      </c>
-      <c r="L95">
-        <v>0</v>
-      </c>
-      <c r="M95">
-        <v>0</v>
-      </c>
-      <c r="N95">
-        <v>0</v>
-      </c>
-      <c r="O95">
-        <v>0</v>
-      </c>
-      <c r="P95">
-        <v>0</v>
-      </c>
-      <c r="Q95">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A96">
-        <v>127615223</v>
-      </c>
-      <c r="E96">
-        <v>601</v>
-      </c>
-      <c r="F96" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G96" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I96">
-        <v>42</v>
-      </c>
-      <c r="J96">
-        <v>1118</v>
-      </c>
-      <c r="L96">
-        <v>0</v>
-      </c>
-      <c r="M96">
-        <v>0</v>
-      </c>
-      <c r="N96">
-        <v>0</v>
-      </c>
-      <c r="O96">
-        <v>0</v>
-      </c>
-      <c r="P96">
-        <v>0</v>
-      </c>
-      <c r="Q96">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A97">
-        <v>127615674</v>
-      </c>
-      <c r="E97">
-        <v>601</v>
-      </c>
-      <c r="F97" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G97" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I97">
-        <v>42</v>
-      </c>
-      <c r="J97">
-        <v>8004</v>
-      </c>
-      <c r="L97">
-        <v>0</v>
-      </c>
-      <c r="M97">
-        <v>0</v>
-      </c>
-      <c r="N97">
-        <v>0</v>
-      </c>
-      <c r="O97">
-        <v>0</v>
-      </c>
-      <c r="P97">
-        <v>0</v>
-      </c>
-      <c r="Q97">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A98">
-        <v>127617067</v>
-      </c>
-      <c r="E98">
-        <v>601</v>
-      </c>
-      <c r="F98" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G98" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I98">
-        <v>42</v>
-      </c>
-      <c r="J98">
-        <v>8004</v>
-      </c>
-      <c r="L98">
-        <v>0</v>
-      </c>
-      <c r="M98">
-        <v>0</v>
-      </c>
-      <c r="N98">
-        <v>0</v>
-      </c>
-      <c r="O98">
-        <v>0</v>
-      </c>
-      <c r="P98">
-        <v>0</v>
-      </c>
-      <c r="Q98">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A99">
-        <v>127617452</v>
-      </c>
-      <c r="E99">
-        <v>601</v>
-      </c>
-      <c r="F99" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G99" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I99">
-        <v>42</v>
-      </c>
-      <c r="J99">
-        <v>8004</v>
-      </c>
-      <c r="L99">
-        <v>0</v>
-      </c>
-      <c r="M99">
-        <v>0</v>
-      </c>
-      <c r="N99">
-        <v>0</v>
-      </c>
-      <c r="O99">
-        <v>0</v>
-      </c>
-      <c r="P99">
-        <v>0</v>
-      </c>
-      <c r="Q99">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A100">
-        <v>127617660</v>
-      </c>
-      <c r="E100">
-        <v>601</v>
-      </c>
-      <c r="F100" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G100" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I100">
-        <v>42</v>
-      </c>
-      <c r="J100">
-        <v>8004</v>
-      </c>
-      <c r="L100">
-        <v>0</v>
-      </c>
-      <c r="M100">
-        <v>0</v>
-      </c>
-      <c r="N100">
-        <v>0</v>
-      </c>
-      <c r="O100">
-        <v>0</v>
-      </c>
-      <c r="P100">
-        <v>0</v>
-      </c>
-      <c r="Q100">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A101">
-        <v>127617713</v>
-      </c>
-      <c r="E101">
-        <v>601</v>
-      </c>
-      <c r="F101" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G101" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I101">
-        <v>42</v>
-      </c>
-      <c r="J101">
-        <v>8004</v>
-      </c>
-      <c r="L101">
-        <v>0</v>
-      </c>
-      <c r="M101">
-        <v>0</v>
-      </c>
-      <c r="N101">
-        <v>0</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>0</v>
-      </c>
-      <c r="Q101">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A102">
-        <v>127617908</v>
-      </c>
-      <c r="E102">
-        <v>601</v>
-      </c>
-      <c r="F102" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G102" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I102">
-        <v>42</v>
-      </c>
-      <c r="J102">
-        <v>8004</v>
-      </c>
-      <c r="L102">
-        <v>0</v>
-      </c>
-      <c r="M102">
-        <v>0</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
-        <v>0</v>
-      </c>
-      <c r="P102">
-        <v>0</v>
-      </c>
-      <c r="Q102">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A103">
-        <v>127618188</v>
-      </c>
-      <c r="E103">
-        <v>601</v>
-      </c>
-      <c r="F103" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G103" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I103">
-        <v>42</v>
-      </c>
-      <c r="J103">
-        <v>8004</v>
-      </c>
-      <c r="L103">
-        <v>0</v>
-      </c>
-      <c r="M103">
-        <v>0</v>
-      </c>
-      <c r="N103">
-        <v>0</v>
-      </c>
-      <c r="O103">
-        <v>0</v>
-      </c>
-      <c r="P103">
-        <v>0</v>
-      </c>
-      <c r="Q103">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A104">
-        <v>127618341</v>
-      </c>
-      <c r="E104">
-        <v>601</v>
-      </c>
-      <c r="F104" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G104" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I104">
-        <v>42</v>
-      </c>
-      <c r="J104">
-        <v>8004</v>
-      </c>
-      <c r="L104">
-        <v>0</v>
-      </c>
-      <c r="M104">
-        <v>0</v>
-      </c>
-      <c r="N104">
-        <v>0</v>
-      </c>
-      <c r="O104">
-        <v>0</v>
-      </c>
-      <c r="P104">
-        <v>0</v>
-      </c>
-      <c r="Q104">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A105">
-        <v>127620400</v>
-      </c>
-      <c r="E105">
-        <v>601</v>
-      </c>
-      <c r="F105" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G105" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I105">
-        <v>42</v>
-      </c>
-      <c r="J105">
-        <v>8004</v>
-      </c>
-      <c r="L105">
-        <v>0</v>
-      </c>
-      <c r="M105">
-        <v>0</v>
-      </c>
-      <c r="N105">
-        <v>0</v>
-      </c>
-      <c r="O105">
-        <v>0</v>
-      </c>
-      <c r="P105">
-        <v>0</v>
-      </c>
-      <c r="Q105">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A106">
-        <v>127620868</v>
-      </c>
-      <c r="E106">
-        <v>601</v>
-      </c>
-      <c r="F106" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G106" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I106">
-        <v>42</v>
-      </c>
-      <c r="J106">
-        <v>8004</v>
-      </c>
-      <c r="L106">
-        <v>0</v>
-      </c>
-      <c r="M106">
-        <v>0</v>
-      </c>
-      <c r="N106">
-        <v>0</v>
-      </c>
-      <c r="O106">
-        <v>0</v>
-      </c>
-      <c r="P106">
-        <v>0</v>
-      </c>
-      <c r="Q106">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A107">
-        <v>127621058</v>
-      </c>
-      <c r="E107">
-        <v>601</v>
-      </c>
-      <c r="F107" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G107" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I107">
-        <v>42</v>
-      </c>
-      <c r="J107">
-        <v>8004</v>
-      </c>
-      <c r="L107">
-        <v>0</v>
-      </c>
-      <c r="M107">
-        <v>0</v>
-      </c>
-      <c r="N107">
-        <v>0</v>
-      </c>
-      <c r="O107">
-        <v>0</v>
-      </c>
-      <c r="P107">
-        <v>0</v>
-      </c>
-      <c r="Q107">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A108">
-        <v>127621380</v>
-      </c>
-      <c r="E108">
-        <v>601</v>
-      </c>
-      <c r="F108" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G108" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I108">
-        <v>42</v>
-      </c>
-      <c r="J108">
-        <v>8004</v>
-      </c>
-      <c r="L108">
-        <v>0</v>
-      </c>
-      <c r="M108">
-        <v>0</v>
-      </c>
-      <c r="N108">
-        <v>0</v>
-      </c>
-      <c r="O108">
-        <v>0</v>
-      </c>
-      <c r="P108">
-        <v>0</v>
-      </c>
-      <c r="Q108">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A109">
-        <v>127623027</v>
-      </c>
-      <c r="E109">
-        <v>601</v>
-      </c>
-      <c r="F109" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G109" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I109">
-        <v>42</v>
-      </c>
-      <c r="J109">
-        <v>8004</v>
-      </c>
-      <c r="L109">
-        <v>0</v>
-      </c>
-      <c r="M109">
-        <v>0</v>
-      </c>
-      <c r="N109">
-        <v>0</v>
-      </c>
-      <c r="O109">
-        <v>0</v>
-      </c>
-      <c r="P109">
-        <v>0</v>
-      </c>
-      <c r="Q109">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A110">
-        <v>127623363</v>
-      </c>
-      <c r="E110">
-        <v>601</v>
-      </c>
-      <c r="F110" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G110" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I110">
-        <v>42</v>
-      </c>
-      <c r="J110">
-        <v>8004</v>
-      </c>
-      <c r="L110">
-        <v>0</v>
-      </c>
-      <c r="M110">
-        <v>0</v>
-      </c>
-      <c r="N110">
-        <v>0</v>
-      </c>
-      <c r="O110">
-        <v>0</v>
-      </c>
-      <c r="P110">
-        <v>0</v>
-      </c>
-      <c r="Q110">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A111">
-        <v>127624138</v>
-      </c>
-      <c r="E111">
-        <v>601</v>
-      </c>
-      <c r="F111" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G111" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I111">
-        <v>42</v>
-      </c>
-      <c r="J111">
-        <v>8004</v>
-      </c>
-      <c r="L111">
-        <v>0</v>
-      </c>
-      <c r="M111">
-        <v>0</v>
-      </c>
-      <c r="N111">
-        <v>0</v>
-      </c>
-      <c r="O111">
-        <v>0</v>
-      </c>
-      <c r="P111">
-        <v>0</v>
-      </c>
-      <c r="Q111">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A112">
-        <v>127624307</v>
-      </c>
-      <c r="E112">
-        <v>601</v>
-      </c>
-      <c r="F112" s="2">
-        <v>45421</v>
-      </c>
-      <c r="G112" s="2">
-        <v>45421</v>
-      </c>
-      <c r="I112">
-        <v>42</v>
-      </c>
-      <c r="J112">
-        <v>8004</v>
-      </c>
-      <c r="L112">
-        <v>0</v>
-      </c>
-      <c r="M112">
-        <v>0</v>
-      </c>
-      <c r="N112">
-        <v>0</v>
-      </c>
-      <c r="O112">
-        <v>0</v>
-      </c>
-      <c r="P112">
-        <v>0</v>
-      </c>
-      <c r="Q112">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A113">
-        <v>127630088</v>
-      </c>
-      <c r="E113">
-        <v>601</v>
-      </c>
-      <c r="F113" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G113" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I113">
-        <v>42</v>
-      </c>
-      <c r="J113">
-        <v>8004</v>
-      </c>
-      <c r="L113">
-        <v>0</v>
-      </c>
-      <c r="M113">
-        <v>0</v>
-      </c>
-      <c r="N113">
-        <v>0</v>
-      </c>
-      <c r="O113">
-        <v>0</v>
-      </c>
-      <c r="P113">
-        <v>0</v>
-      </c>
-      <c r="Q113">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A114">
-        <v>127632152</v>
-      </c>
-      <c r="E114">
-        <v>601</v>
-      </c>
-      <c r="F114" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G114" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I114">
-        <v>42</v>
-      </c>
-      <c r="J114">
-        <v>8004</v>
-      </c>
-      <c r="L114">
-        <v>0</v>
-      </c>
-      <c r="M114">
-        <v>0</v>
-      </c>
-      <c r="N114">
-        <v>0</v>
-      </c>
-      <c r="O114">
-        <v>0</v>
-      </c>
-      <c r="P114">
-        <v>0</v>
-      </c>
-      <c r="Q114">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A115">
-        <v>127633361</v>
-      </c>
-      <c r="E115">
-        <v>601</v>
-      </c>
-      <c r="F115" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G115" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I115">
-        <v>42</v>
-      </c>
-      <c r="J115">
-        <v>8004</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="M115">
-        <v>0</v>
-      </c>
-      <c r="N115">
-        <v>0</v>
-      </c>
-      <c r="O115">
-        <v>0</v>
-      </c>
-      <c r="P115">
-        <v>0</v>
-      </c>
-      <c r="Q115">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A116">
-        <v>127633633</v>
-      </c>
-      <c r="E116">
-        <v>601</v>
-      </c>
-      <c r="F116" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G116" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I116">
-        <v>42</v>
-      </c>
-      <c r="J116">
-        <v>8004</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="M116">
-        <v>0</v>
-      </c>
-      <c r="N116">
-        <v>0</v>
-      </c>
-      <c r="O116">
-        <v>0</v>
-      </c>
-      <c r="P116">
-        <v>0</v>
-      </c>
-      <c r="Q116">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A117">
-        <v>127634043</v>
-      </c>
-      <c r="E117">
-        <v>601</v>
-      </c>
-      <c r="F117" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G117" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I117">
-        <v>42</v>
-      </c>
-      <c r="J117">
-        <v>8004</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="M117">
-        <v>0</v>
-      </c>
-      <c r="N117">
-        <v>0</v>
-      </c>
-      <c r="O117">
-        <v>0</v>
-      </c>
-      <c r="P117">
-        <v>0</v>
-      </c>
-      <c r="Q117">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A118">
-        <v>127637095</v>
-      </c>
-      <c r="E118">
-        <v>601</v>
-      </c>
-      <c r="F118" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G118" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I118">
-        <v>42</v>
-      </c>
-      <c r="J118">
-        <v>8004</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118">
-        <v>0</v>
-      </c>
-      <c r="N118">
-        <v>0</v>
-      </c>
-      <c r="O118">
-        <v>0</v>
-      </c>
-      <c r="P118">
-        <v>0</v>
-      </c>
-      <c r="Q118">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A119">
-        <v>127639129</v>
-      </c>
-      <c r="E119">
-        <v>601</v>
-      </c>
-      <c r="F119" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G119" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I119">
-        <v>42</v>
-      </c>
-      <c r="J119">
-        <v>8004</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119">
-        <v>0</v>
-      </c>
-      <c r="N119">
-        <v>0</v>
-      </c>
-      <c r="O119">
-        <v>0</v>
-      </c>
-      <c r="P119">
-        <v>0</v>
-      </c>
-      <c r="Q119">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A120">
-        <v>127639536</v>
-      </c>
-      <c r="E120">
-        <v>601</v>
-      </c>
-      <c r="F120" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G120" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I120">
-        <v>42</v>
-      </c>
-      <c r="J120">
-        <v>8004</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120">
-        <v>0</v>
-      </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
-      <c r="O120">
-        <v>0</v>
-      </c>
-      <c r="P120">
-        <v>0</v>
-      </c>
-      <c r="Q120">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A121">
-        <v>127640835</v>
-      </c>
-      <c r="E121">
-        <v>601</v>
-      </c>
-      <c r="F121" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G121" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I121">
-        <v>42</v>
-      </c>
-      <c r="J121">
-        <v>8004</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="M121">
-        <v>0</v>
-      </c>
-      <c r="N121">
-        <v>0</v>
-      </c>
-      <c r="O121">
-        <v>0</v>
-      </c>
-      <c r="P121">
-        <v>0</v>
-      </c>
-      <c r="Q121">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A122">
-        <v>127641271</v>
-      </c>
-      <c r="E122">
-        <v>601</v>
-      </c>
-      <c r="F122" s="2">
-        <v>45422</v>
-      </c>
-      <c r="G122" s="2">
-        <v>45422</v>
-      </c>
-      <c r="I122">
-        <v>42</v>
-      </c>
-      <c r="J122">
-        <v>8004</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122">
-        <v>0</v>
-      </c>
-      <c r="N122">
-        <v>0</v>
-      </c>
-      <c r="O122">
-        <v>0</v>
-      </c>
-      <c r="P122">
-        <v>0</v>
-      </c>
-      <c r="Q122">
-        <v>61</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:Q24" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -12771,31 +9048,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27A2D9A-D9A0-4483-B2D3-038BE5927FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BABEC6F-14D7-4166-94C5-6E758D2359FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,16 +585,16 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>124071525</v>
+        <v>124322317</v>
       </c>
       <c r="E2">
         <v>1211</v>
       </c>
       <c r="F2" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G2" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I2">
         <v>42</v>
@@ -623,16 +623,16 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>124190216</v>
+        <v>124578551</v>
       </c>
       <c r="E3">
         <v>1211</v>
       </c>
       <c r="F3" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G3" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I3">
         <v>42</v>
@@ -661,16 +661,16 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>124404434</v>
+        <v>124643712</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G4" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I4">
         <v>42</v>
@@ -699,16 +699,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>124507801</v>
+        <v>124687104</v>
       </c>
       <c r="E5">
         <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G5" s="2">
-        <v>45427</v>
+        <v>45429</v>
       </c>
       <c r="I5">
         <v>42</v>
@@ -737,16 +737,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>124903448</v>
+        <v>125845098</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G6" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I6">
         <v>42</v>
@@ -775,16 +775,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>124984936</v>
+        <v>125967516</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G7" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -813,16 +813,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>125225166</v>
+        <v>126182553</v>
       </c>
       <c r="E8">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G8" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I8">
         <v>42</v>
@@ -851,16 +851,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>125312442</v>
+        <v>126586810</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G9" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -889,16 +889,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>125447920</v>
+        <v>126587232</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G10" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -927,16 +927,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>125608616</v>
+        <v>126590524</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G11" s="2">
-        <v>45428</v>
+        <v>45433</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -965,16 +965,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>125795596</v>
+        <v>126777196</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G12" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>125841757</v>
+        <v>126867156</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G13" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>125916183</v>
+        <v>127031097</v>
       </c>
       <c r="E14">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F14" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G14" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>126315474</v>
+        <v>127081387</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G15" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>126784997</v>
+        <v>127207147</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G16" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,16 +1155,16 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>127321922</v>
+        <v>127261490</v>
       </c>
       <c r="E17">
         <v>1211</v>
       </c>
       <c r="F17" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G17" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I17">
         <v>42</v>
@@ -1193,16 +1193,16 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>127485644</v>
+        <v>127665698</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G18" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I18">
         <v>42</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>127672277</v>
+        <v>127728263</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="G19" s="2">
-        <v>45432</v>
+        <v>45433</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1307,22 +1307,22 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>127627998</v>
+        <v>127646444</v>
       </c>
       <c r="E21">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F21" s="2">
-        <v>45429</v>
+        <v>45426</v>
       </c>
       <c r="G21" s="2">
-        <v>45422</v>
+        <v>45425</v>
       </c>
       <c r="I21">
         <v>42</v>
       </c>
       <c r="J21">
-        <v>8001</v>
+        <v>8021</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1345,22 +1345,22 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>127646444</v>
+        <v>126954503</v>
       </c>
       <c r="E22">
-        <v>1212</v>
+        <v>601</v>
       </c>
       <c r="F22" s="2">
-        <v>45426</v>
+        <v>45378</v>
       </c>
       <c r="G22" s="2">
-        <v>45425</v>
+        <v>45378</v>
       </c>
       <c r="I22">
         <v>42</v>
       </c>
       <c r="J22">
-        <v>8021</v>
+        <v>8017</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1383,22 +1383,22 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>127660003</v>
+        <v>127654363</v>
       </c>
       <c r="E23">
-        <v>1211</v>
+        <v>601</v>
       </c>
       <c r="F23" s="2">
-        <v>45429</v>
+        <v>45425</v>
       </c>
       <c r="G23" s="2">
-        <v>45426</v>
+        <v>45425</v>
       </c>
       <c r="I23">
         <v>42</v>
       </c>
       <c r="J23">
-        <v>8001</v>
+        <v>8004</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1421,22 +1421,22 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>126954503</v>
+        <v>127656383</v>
       </c>
       <c r="E24">
         <v>601</v>
       </c>
       <c r="F24" s="2">
-        <v>45378</v>
+        <v>45425</v>
       </c>
       <c r="G24" s="2">
-        <v>45378</v>
+        <v>45425</v>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8017</v>
+        <v>8004</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1457,8 +1457,1110 @@
         <v>61</v>
       </c>
     </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>127647388</v>
+      </c>
+      <c r="E25">
+        <v>601</v>
+      </c>
+      <c r="F25" s="2">
+        <v>45425</v>
+      </c>
+      <c r="G25" s="2">
+        <v>45425</v>
+      </c>
+      <c r="I25">
+        <v>42</v>
+      </c>
+      <c r="J25">
+        <v>8004</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>127647869</v>
+      </c>
+      <c r="E26">
+        <v>601</v>
+      </c>
+      <c r="F26" s="2">
+        <v>45425</v>
+      </c>
+      <c r="G26" s="2">
+        <v>45425</v>
+      </c>
+      <c r="I26">
+        <v>42</v>
+      </c>
+      <c r="J26">
+        <v>8004</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>127648484</v>
+      </c>
+      <c r="E27">
+        <v>601</v>
+      </c>
+      <c r="F27" s="2">
+        <v>45425</v>
+      </c>
+      <c r="G27" s="2">
+        <v>45425</v>
+      </c>
+      <c r="I27">
+        <v>42</v>
+      </c>
+      <c r="J27">
+        <v>8004</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>127649518</v>
+      </c>
+      <c r="E28">
+        <v>601</v>
+      </c>
+      <c r="F28" s="2">
+        <v>45425</v>
+      </c>
+      <c r="G28" s="2">
+        <v>45425</v>
+      </c>
+      <c r="I28">
+        <v>42</v>
+      </c>
+      <c r="J28">
+        <v>8004</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>127650554</v>
+      </c>
+      <c r="E29">
+        <v>601</v>
+      </c>
+      <c r="F29" s="2">
+        <v>45425</v>
+      </c>
+      <c r="G29" s="2">
+        <v>45425</v>
+      </c>
+      <c r="I29">
+        <v>42</v>
+      </c>
+      <c r="J29">
+        <v>8004</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>127651479</v>
+      </c>
+      <c r="E30">
+        <v>601</v>
+      </c>
+      <c r="F30" s="2">
+        <v>45425</v>
+      </c>
+      <c r="G30" s="2">
+        <v>45425</v>
+      </c>
+      <c r="I30">
+        <v>42</v>
+      </c>
+      <c r="J30">
+        <v>8004</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>127652000</v>
+      </c>
+      <c r="E31">
+        <v>601</v>
+      </c>
+      <c r="F31" s="2">
+        <v>45425</v>
+      </c>
+      <c r="G31" s="2">
+        <v>45425</v>
+      </c>
+      <c r="I31">
+        <v>42</v>
+      </c>
+      <c r="J31">
+        <v>8004</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>127655554</v>
+      </c>
+      <c r="E32">
+        <v>601</v>
+      </c>
+      <c r="F32" s="2">
+        <v>45425</v>
+      </c>
+      <c r="G32" s="2">
+        <v>45425</v>
+      </c>
+      <c r="I32">
+        <v>42</v>
+      </c>
+      <c r="J32">
+        <v>8004</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>127704545</v>
+      </c>
+      <c r="E33">
+        <v>1212</v>
+      </c>
+      <c r="F33" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G33" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I33">
+        <v>42</v>
+      </c>
+      <c r="J33">
+        <v>715</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+      <c r="Q33">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>127704832</v>
+      </c>
+      <c r="E34">
+        <v>1212</v>
+      </c>
+      <c r="F34" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G34" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I34">
+        <v>42</v>
+      </c>
+      <c r="J34">
+        <v>715</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>127704977</v>
+      </c>
+      <c r="E35">
+        <v>1211</v>
+      </c>
+      <c r="F35" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G35" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I35">
+        <v>42</v>
+      </c>
+      <c r="J35">
+        <v>715</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+      <c r="Q35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>127705147</v>
+      </c>
+      <c r="E36">
+        <v>1211</v>
+      </c>
+      <c r="F36" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G36" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I36">
+        <v>42</v>
+      </c>
+      <c r="J36">
+        <v>715</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+      <c r="Q36">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>127705252</v>
+      </c>
+      <c r="E37">
+        <v>1211</v>
+      </c>
+      <c r="F37" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G37" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I37">
+        <v>42</v>
+      </c>
+      <c r="J37">
+        <v>715</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+      <c r="Q37">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>127706085</v>
+      </c>
+      <c r="E38">
+        <v>1212</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I38">
+        <v>42</v>
+      </c>
+      <c r="J38">
+        <v>715</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+      <c r="Q38">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>127706494</v>
+      </c>
+      <c r="E39">
+        <v>1212</v>
+      </c>
+      <c r="F39" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G39" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I39">
+        <v>42</v>
+      </c>
+      <c r="J39">
+        <v>715</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+      <c r="Q39">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>127710090</v>
+      </c>
+      <c r="E40">
+        <v>1212</v>
+      </c>
+      <c r="F40" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G40" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I40">
+        <v>42</v>
+      </c>
+      <c r="J40">
+        <v>715</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>127710254</v>
+      </c>
+      <c r="E41">
+        <v>1212</v>
+      </c>
+      <c r="F41" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G41" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I41">
+        <v>42</v>
+      </c>
+      <c r="J41">
+        <v>715</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>127710579</v>
+      </c>
+      <c r="E42">
+        <v>1212</v>
+      </c>
+      <c r="F42" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G42" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I42">
+        <v>42</v>
+      </c>
+      <c r="J42">
+        <v>715</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>127711059</v>
+      </c>
+      <c r="E43">
+        <v>1212</v>
+      </c>
+      <c r="F43" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G43" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I43">
+        <v>42</v>
+      </c>
+      <c r="J43">
+        <v>715</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>127712634</v>
+      </c>
+      <c r="E44">
+        <v>1211</v>
+      </c>
+      <c r="F44" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G44" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I44">
+        <v>42</v>
+      </c>
+      <c r="J44">
+        <v>715</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>127713795</v>
+      </c>
+      <c r="E45">
+        <v>1211</v>
+      </c>
+      <c r="F45" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G45" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I45">
+        <v>42</v>
+      </c>
+      <c r="J45">
+        <v>715</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>127714561</v>
+      </c>
+      <c r="E46">
+        <v>1211</v>
+      </c>
+      <c r="F46" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G46" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I46">
+        <v>42</v>
+      </c>
+      <c r="J46">
+        <v>715</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+      <c r="Q46">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>127716130</v>
+      </c>
+      <c r="E47">
+        <v>1211</v>
+      </c>
+      <c r="F47" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G47" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I47">
+        <v>42</v>
+      </c>
+      <c r="J47">
+        <v>715</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>127716137</v>
+      </c>
+      <c r="E48">
+        <v>1212</v>
+      </c>
+      <c r="F48" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G48" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I48">
+        <v>42</v>
+      </c>
+      <c r="J48">
+        <v>715</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+      <c r="Q48">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>127716748</v>
+      </c>
+      <c r="E49">
+        <v>1211</v>
+      </c>
+      <c r="F49" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G49" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I49">
+        <v>42</v>
+      </c>
+      <c r="J49">
+        <v>715</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>127716921</v>
+      </c>
+      <c r="E50">
+        <v>1212</v>
+      </c>
+      <c r="F50" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G50" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I50">
+        <v>42</v>
+      </c>
+      <c r="J50">
+        <v>715</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+      <c r="Q50">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>127717107</v>
+      </c>
+      <c r="E51">
+        <v>1211</v>
+      </c>
+      <c r="F51" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G51" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I51">
+        <v>42</v>
+      </c>
+      <c r="J51">
+        <v>715</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+      <c r="Q51">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>127717263</v>
+      </c>
+      <c r="E52">
+        <v>1211</v>
+      </c>
+      <c r="F52" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G52" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I52">
+        <v>42</v>
+      </c>
+      <c r="J52">
+        <v>715</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>127718833</v>
+      </c>
+      <c r="E53">
+        <v>1211</v>
+      </c>
+      <c r="F53" s="2">
+        <v>45429</v>
+      </c>
+      <c r="G53" s="2">
+        <v>45429</v>
+      </c>
+      <c r="I53">
+        <v>42</v>
+      </c>
+      <c r="J53">
+        <v>715</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q24" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}"/>
+  <autoFilter ref="A1:Q53" xr:uid="{101BD072-E540-4E4C-A013-C85F44BE8DDE}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
@@ -9048,31 +10150,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTAxOTQ2PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjgvMDUvMjAxOSAxNzoxNTowNTwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOC8wNS8yMDE5ICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F68678F-A570-4B20-8354-5C143309CEAF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA74A62-E908-4C3E-A1D4-6DC1121C84E7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Fiel.xlsx
+++ b/Treinamento/Fiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BABEC6F-14D7-4166-94C5-6E758D2359FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C06A473-C319-4D69-AC27-5951FACD5CCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="29" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Fiel!$A$1:$Q$93</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Planilha1!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -507,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:Q93"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" bestFit="1" customWidth="1"/>
@@ -585,22 +585,22 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>124322317</v>
+        <v>127729274</v>
       </c>
       <c r="E2">
         <v>1211</v>
       </c>
       <c r="F2" s="2">
-        <v>45433</v>
+        <v>45432</v>
       </c>
       <c r="G2" s="2">
-        <v>45433</v>
+        <v>45432</v>
       </c>
       <c r="I2">
         <v>42</v>
       </c>
       <c r="J2">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -623,22 +623,22 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>124578551</v>
+        <v>127731031</v>
       </c>
       <c r="E3">
         <v>1211</v>
       </c>
       <c r="F3" s="2">
-        <v>45433</v>
+        <v>45432</v>
       </c>
       <c r="G3" s="2">
-        <v>45433</v>
+        <v>45432</v>
       </c>
       <c r="I3">
         <v>42</v>
       </c>
       <c r="J3">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -661,22 +661,22 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>124643712</v>
+        <v>127735063</v>
       </c>
       <c r="E4">
         <v>1211</v>
       </c>
       <c r="F4" s="2">
-        <v>45433</v>
+        <v>45432</v>
       </c>
       <c r="G4" s="2">
-        <v>45433</v>
+        <v>45432</v>
       </c>
       <c r="I4">
         <v>42</v>
       </c>
       <c r="J4">
-        <v>8001</v>
+        <v>1735</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,16 +699,16 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>124687104</v>
+        <v>124063561</v>
       </c>
       <c r="E5">
         <v>1211</v>
       </c>
       <c r="F5" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="G5" s="2">
-        <v>45429</v>
+        <v>45434</v>
       </c>
       <c r="I5">
         <v>42</v>
@@ -737,16 +737,16 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>125845098</v>
+        <v>124199265</v>
       </c>
       <c r="E6">
         <v>1211</v>
       </c>
       <c r="F6" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="G6" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="I6">
         <v>42</v>
@@ -775,16 +775,16 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>125967516</v>
+        <v>124344865</v>
       </c>
       <c r="E7">
         <v>1211</v>
       </c>
       <c r="F7" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="G7" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="I7">
         <v>42</v>
@@ -813,13 +813,13 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>126182553</v>
+        <v>124399528</v>
       </c>
       <c r="E8">
         <v>1211</v>
       </c>
       <c r="F8" s="2">
-        <v>45433</v>
+        <v>45435</v>
       </c>
       <c r="G8" s="2">
         <v>45433</v>
@@ -851,16 +851,16 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>126586810</v>
+        <v>124436487</v>
       </c>
       <c r="E9">
         <v>1211</v>
       </c>
       <c r="F9" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="G9" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="I9">
         <v>42</v>
@@ -889,16 +889,16 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>126587232</v>
+        <v>124494053</v>
       </c>
       <c r="E10">
         <v>1211</v>
       </c>
       <c r="F10" s="2">
-        <v>45433</v>
+        <v>45435</v>
       </c>
       <c r="G10" s="2">
-        <v>45433</v>
+        <v>45432</v>
       </c>
       <c r="I10">
         <v>42</v>
@@ -927,16 +927,16 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
-        <v>126590524</v>
+        <v>124689609</v>
       </c>
       <c r="E11">
         <v>1211</v>
       </c>
       <c r="F11" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="G11" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="I11">
         <v>42</v>
@@ -965,16 +965,16 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
-        <v>126777196</v>
+        <v>124775895</v>
       </c>
       <c r="E12">
         <v>1211</v>
       </c>
       <c r="F12" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="G12" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="I12">
         <v>42</v>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
-        <v>126867156</v>
+        <v>124924901</v>
       </c>
       <c r="E13">
         <v>1211</v>
       </c>
       <c r="F13" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="G13" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="I13">
         <v>42</v>
@@ -1041,16 +1041,16 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
-        <v>127031097</v>
+        <v>125075179</v>
       </c>
       <c r="E14">
         <v>1212</v>
       </c>
       <c r="F14" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="G14" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="I14">
         <v>42</v>
@@ -1079,16 +1079,16 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
-        <v>127081387</v>
+        <v>125196288</v>
       </c>
       <c r="E15">
         <v>1211</v>
       </c>
       <c r="F15" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="G15" s="2">
-        <v>45433</v>
+        <v>45428</v>
       </c>
       <c r="I15">
         <v>42</v>
@@ -1117,16 +1117,16 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
-        <v>127207147</v>
+        <v>125259470</v>
       </c>
       <c r="E16">
         <v>1211</v>
       </c>
       <c r="F16" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="G16" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="I16">
         <v>42</v>
@@ -1155,13 +1155,13 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
-        <v>127261490</v>
+        <v>125699696</v>
       </c>
       <c r="E17">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F17" s="2">
-        <v>45433</v>
+        <v>45435</v>
       </c>
       <c r="G17" s="2">
         <v>45433</v>
@@ -1193,13 +1193,13 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
-        <v>127665698</v>
+        <v>125914938</v>
       </c>
       <c r="E18">
         <v>1211</v>
       </c>
       <c r="F18" s="2">
-        <v>45433</v>
+        <v>45435</v>
       </c>
       <c r="G18" s="2">
         <v>45433</v>
@@ -1231,16 +1231,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
-        <v>127728263</v>
+        <v>125919910</v>
       </c>
       <c r="E19">
         <v>1211</v>
       </c>
       <c r="F19" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="G19" s="2">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="I19">
         <v>42</v>
@@ -1269,22 +1269,22 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>110074933</v>
+        <v>126108323</v>
       </c>
       <c r="E20">
         <v>1211</v>
       </c>
       <c r="F20" s="2">
-        <v>43453</v>
+        <v>45435</v>
       </c>
       <c r="G20" s="2">
-        <v>43441</v>
+        <v>45432</v>
       </c>
       <c r="I20">
         <v>42</v>
       </c>
       <c r="J20">
-        <v>8023</v>
+        <v>8001</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1307,22 +1307,22 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>127646444</v>
+        <v>126436804</v>
       </c>
       <c r="E21">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="F21" s="2">
-        <v>45426</v>
+        <v>45434</v>
       </c>
       <c r="G21" s="2">
-        <v>45425</v>
+        <v>45434</v>
       </c>
       <c r="I21">
         <v>42</v>
       </c>
       <c r="J21">
-        <v>8021</v>
+        <v>8001</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1345,22 +1345,22 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>126954503</v>
+        <v>126469566</v>
       </c>
       <c r="E22">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F22" s="2">
-        <v>45378</v>
+        <v>45434</v>
       </c>
       <c r="G22" s="2">
-        <v>45378</v>
+        <v>45434</v>
       </c>
       <c r="I22">
         <v>42</v>
       </c>
       <c r="J22">
-        <v>8017</v>
+        <v>8001</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1383,22 +1383,22 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>127654363</v>
+        <v>126496582</v>
       </c>
       <c r="E23">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F23" s="2">
-        <v>45425</v>
+        <v>45434</v>
       </c>
       <c r="G23" s="2">
-        <v>45425</v>
+        <v>45434</v>
       </c>
       <c r="I23">
         <v>42</v>
       </c>
       <c r="J23">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1421,22 +1421,22 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>127656383</v>
+        <v>126729111</v>
       </c>
       <c r="E24">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F24" s="2">
-        <v>45425</v>
+        <v>45434</v>
       </c>
       <c r="G24" s="2">
-        <v>45425</v>
+        <v>45434</v>
       </c>
       <c r="I24">
         <v>42</v>
       </c>
       <c r="J24">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1459,22 +1459,22 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>127647388</v>
+        <v>126819042</v>
       </c>
       <c r="E25">
-        <v>601</v>
+        <v>1211</v>
       </c>
       <c r="F25" s="2">
-        <v>45425</v>
+        <v>45435</v>
       </c>
       <c r="G25" s="2">
-        <v>45425</v>
+        <v>45432</v>
       </c>
       <c r="I25">
         <v>42</v>
       </c>
       <c r="J25">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>127647869</v>
+        <v>126849803</v>
       </c>
       <c r="E26">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F26" s="2">
-        <v>45425</v>
+        <v>45434</v>
       </c>
       <c r="G26" s="2">
-        <v>45425</v>
+        <v>45429</v>
       </c>
       <c r="I26">
         <v>42</v>
       </c>
       <c r="J26">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>127648484</v>
+        <v>126933151</v>
       </c>
       <c r="E27">
-        <v>601</v>
+        <v>1212</v>
       </c>
       <c r="F27" s="2">
-        <v>45425</v>
+        <v>45434</v>
       </c>
       <c r="G27" s="2">
-        <v>45425</v>
+        <v>45434</v>
       </c>
       <c r="I27">
         <v>42</v>
       </c>
       <c r="J27">
-        <v>8004</v>
+        <v>8001</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>127649518</v>
+        <v>12